--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BA72510-B63C-0F43-BD67-2C72639DB06E}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{053772BF-543F-5C4A-893B-EAF5AB8AC049}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19740" activeTab="1" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="397">
   <si>
     <t>SRX400
 Tested Numbers</t>
@@ -335,9 +335,6 @@
   </si>
   <si>
     <t>Max FW HTTP concurrent Session capacity</t>
-  </si>
-  <si>
-    <t>Max FW HTTP concurrent Session capacity - with Scaled L3L4 mode</t>
   </si>
   <si>
     <t>Max AppSec Sessions(unified policy)</t>
@@ -1151,12 +1148,6 @@
     <t>ß</t>
   </si>
   <si>
-    <t>80K</t>
-  </si>
-  <si>
-    <t>PR 1954675</t>
-  </si>
-  <si>
     <t>PR 1954327</t>
   </si>
   <si>
@@ -1246,13 +1237,73 @@
     <t>190 CPS / 110 Mbps</t>
   </si>
   <si>
-    <t>160 CPS / 90 Mbps</t>
-  </si>
-  <si>
     <t>55 CPS / 30 Mbps</t>
   </si>
   <si>
     <t>1570 CPS / 894 Mbps</t>
+  </si>
+  <si>
+    <t>556 CPS / 318 Mbps</t>
+  </si>
+  <si>
+    <t>1620 CPS /911 Mbps</t>
+  </si>
+  <si>
+    <t>1596 CPS /903 Mbps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppSec+ UTM NG-WF(100% cache) </t>
+  </si>
+  <si>
+    <t>1579 CPS / 893 Mbps</t>
+  </si>
+  <si>
+    <t>400K</t>
+  </si>
+  <si>
+    <t>200K</t>
+  </si>
+  <si>
+    <t>796 CPS / 440 Mbps</t>
+  </si>
+  <si>
+    <t>448 CPS / 237 Mbps</t>
+  </si>
+  <si>
+    <t>428 CPS / 228 Mbps</t>
+  </si>
+  <si>
+    <t>444 CPS / 234 Mbps</t>
+  </si>
+  <si>
+    <t>Max UTM-NG-WF Sessions capacity</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>Max UTM-EWF Sessions capacity</t>
+  </si>
+  <si>
+    <t>Max UTM- NG-WF Sessions capacity</t>
+  </si>
+  <si>
+    <t>165 CPS / 91 Mbps</t>
+  </si>
+  <si>
+    <t>164 CPS / 91 Mbps</t>
+  </si>
+  <si>
+    <t>141 CPS / 85 Mbps</t>
+  </si>
+  <si>
+    <t>149 CPS / 86 Mbps</t>
+  </si>
+  <si>
+    <t>119 CPS / 71 Mbps</t>
+  </si>
+  <si>
+    <t>123 CPS / 74 Mbps</t>
   </si>
 </sst>
 </file>
@@ -1597,7 +1648,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1801,6 +1852,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2133,2158 +2196,2158 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="C1" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="D1" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="E1" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="F1" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="G1" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="H1" s="68" t="s">
         <v>114</v>
-      </c>
-      <c r="H1" s="68" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="C2" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="E2" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="F2" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="68" t="s">
-        <v>120</v>
-      </c>
       <c r="G2" s="68" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H2" s="68" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="68" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="C3" s="68" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="E3" s="68" t="s">
         <v>125</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="F3" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="F3" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3" s="68" t="s">
+      <c r="H3" s="68" t="s">
         <v>127</v>
-      </c>
-      <c r="H3" s="68" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="68" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="68" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="C4" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F4" s="68" t="s">
+      <c r="G4" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H4" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="G4" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="H4" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B5" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="68" t="s">
+      <c r="H5" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H5" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="F6" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G6" s="68" t="s">
+      <c r="H6" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H6" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="C7" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="68" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="E7" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="68" t="s">
+      <c r="F7" s="68" t="s">
         <v>138</v>
       </c>
-      <c r="E7" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="68" t="s">
-        <v>139</v>
-      </c>
       <c r="G7" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="68" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="C8" s="68" t="s">
+      <c r="E8" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="68" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" s="68" t="s">
-        <v>119</v>
-      </c>
       <c r="F8" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G8" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H8" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="68" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="68" t="s">
+      <c r="E9" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" s="68" t="s">
-        <v>119</v>
-      </c>
       <c r="F9" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H9" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="68" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="68" t="s">
+      <c r="C10" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="68" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="68" t="s">
+      <c r="G10" s="68" t="s">
+        <v>145</v>
+      </c>
+      <c r="H10" s="68" t="s">
         <v>146</v>
-      </c>
-      <c r="G10" s="68" t="s">
-        <v>146</v>
-      </c>
-      <c r="H10" s="68" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="68" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="68" t="s">
+      <c r="C11" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" s="68" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="68" t="s">
+      <c r="H11" s="68" t="s">
         <v>150</v>
-      </c>
-      <c r="H11" s="68" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="B12" s="68" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="C12" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="68" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="68" t="s">
+      <c r="F12" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="68" t="s">
         <v>154</v>
-      </c>
-      <c r="F12" s="68" t="s">
-        <v>132</v>
-      </c>
-      <c r="G12" s="68" t="s">
-        <v>132</v>
-      </c>
-      <c r="H12" s="68" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="68" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B13" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="68" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="68" t="s">
+      <c r="F13" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="G13" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13" s="68" t="s">
         <v>154</v>
-      </c>
-      <c r="F13" s="68" t="s">
-        <v>132</v>
-      </c>
-      <c r="G13" s="68" t="s">
-        <v>132</v>
-      </c>
-      <c r="H13" s="68" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B14" s="68" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="E14" s="68" t="s">
-        <v>119</v>
-      </c>
       <c r="F14" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G14" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H14" s="68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B15" s="68" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C15" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="68" t="s">
-        <v>119</v>
-      </c>
       <c r="F15" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G15" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H15" s="68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="68" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="68" t="s">
+      <c r="C16" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="C16" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F16" s="68" t="s">
+      <c r="G16" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H16" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G16" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H16" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B17" s="68" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F17" s="68" t="s">
+      <c r="G17" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H17" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G17" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H17" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" s="68" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="C18" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="68" t="s">
+      <c r="G18" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H18" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G18" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H18" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B19" s="68" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" s="68" t="s">
+      <c r="G19" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G19" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H19" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="68" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="C20" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="E20" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F20" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E20" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F20" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="G20" s="68" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H20" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="68" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21" s="68" t="s">
+        <v>166</v>
+      </c>
+      <c r="C21" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="E21" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G21" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="H21" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B22" s="68" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="E22" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E22" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F22" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="G22" s="68" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H22" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="68" t="s">
+        <v>171</v>
+      </c>
+      <c r="B23" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="68" t="s">
-        <v>173</v>
-      </c>
       <c r="C23" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F23" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G23" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H23" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="68" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B24" s="68" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E24" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F24" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G24" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H24" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="68" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B25" s="68" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E25" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F25" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G25" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H25" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="68" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="68" t="s">
         <v>176</v>
       </c>
-      <c r="B26" s="68" t="s">
+      <c r="C26" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E26" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E26" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F26" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" s="68" t="s">
-        <v>178</v>
-      </c>
       <c r="H26" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B27" s="68" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E27" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="C27" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E27" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F27" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G27" s="68" t="s">
-        <v>178</v>
-      </c>
       <c r="H27" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B28" s="68" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E28" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F28" s="68" t="s">
-        <v>178</v>
-      </c>
       <c r="G28" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H28" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="68" t="s">
         <v>181</v>
       </c>
-      <c r="B29" s="68" t="s">
+      <c r="C29" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G29" s="68" t="s">
         <v>182</v>
       </c>
-      <c r="C29" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F29" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="68" t="s">
-        <v>183</v>
-      </c>
       <c r="H29" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="68" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B30" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F30" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G30" s="68" t="s">
         <v>182</v>
       </c>
-      <c r="C30" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G30" s="68" t="s">
-        <v>183</v>
-      </c>
       <c r="H30" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="68" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B31" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F31" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G31" s="68" t="s">
         <v>182</v>
       </c>
-      <c r="C31" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F31" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G31" s="68" t="s">
-        <v>183</v>
-      </c>
       <c r="H31" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="68" t="s">
         <v>186</v>
       </c>
-      <c r="B32" s="68" t="s">
+      <c r="C32" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F32" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="C32" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F32" s="68" t="s">
-        <v>188</v>
-      </c>
       <c r="G32" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H32" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B33" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F33" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="C33" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F33" s="68" t="s">
-        <v>188</v>
-      </c>
       <c r="G33" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H33" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="68" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B34" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G34" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="C34" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F34" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G34" s="68" t="s">
-        <v>188</v>
-      </c>
       <c r="H34" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="69" t="s">
         <v>191</v>
       </c>
-      <c r="B35" s="69" t="s">
-        <v>192</v>
-      </c>
       <c r="C35" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E35" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F35" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G35" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E35" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F35" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="H35" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="68" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B36" s="69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C36" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E36" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G36" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E36" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F36" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G36" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="H36" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="68" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B37" s="69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C37" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F37" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G37" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E37" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F37" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G37" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="H37" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="69" t="s">
         <v>195</v>
       </c>
-      <c r="B38" s="69" t="s">
-        <v>196</v>
-      </c>
       <c r="C38" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E38" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F38" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G38" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H38" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B39" s="69" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C39" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E39" s="68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F39" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G39" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H39" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="68" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" s="69" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C40" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E40" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F40" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G40" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H40" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="68" t="s">
+        <v>198</v>
+      </c>
+      <c r="B41" s="69" t="s">
         <v>199</v>
       </c>
-      <c r="B41" s="69" t="s">
+      <c r="C41" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="C41" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" s="68" t="s">
-        <v>201</v>
-      </c>
       <c r="E41" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F41" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G41" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H41" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H41" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="68" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B42" s="69" t="s">
+        <v>199</v>
+      </c>
+      <c r="C42" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="C42" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" s="68" t="s">
-        <v>201</v>
-      </c>
       <c r="E42" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F42" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G42" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H42" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H42" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="68" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B43" s="69" t="s">
+        <v>199</v>
+      </c>
+      <c r="C43" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="C43" s="68" t="s">
+      <c r="E43" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="D43" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="E43" s="68" t="s">
-        <v>119</v>
-      </c>
       <c r="F43" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G43" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H43" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H43" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="B44" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="B44" s="68" t="s">
+      <c r="C44" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="C44" s="68" t="s">
+      <c r="E44" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="E44" s="68" t="s">
+      <c r="F44" s="68" t="s">
         <v>207</v>
-      </c>
-      <c r="F44" s="68" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="68" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B45" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="C45" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="E45" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="E45" s="68" t="s">
+      <c r="F45" s="68" t="s">
         <v>207</v>
-      </c>
-      <c r="F45" s="68" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="68" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B46" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="E46" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="E46" s="68" t="s">
+      <c r="F46" s="68" t="s">
         <v>207</v>
-      </c>
-      <c r="F46" s="68" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="68" t="s">
+        <v>210</v>
+      </c>
+      <c r="B47" s="69" t="s">
         <v>211</v>
       </c>
-      <c r="B47" s="69" t="s">
-        <v>212</v>
-      </c>
       <c r="C47" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E47" s="68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F47" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="68" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B48" s="69" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C48" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E48" s="68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F48" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="68" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B49" s="69" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C49" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E49" s="68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F49" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="B50" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="B50" s="68" t="s">
+      <c r="C50" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="D50" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="D50" s="68" t="s">
+      <c r="E50" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F50" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G50" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="E50" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F50" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G50" s="68" t="s">
+      <c r="H50" s="68" t="s">
         <v>219</v>
-      </c>
-      <c r="H50" s="68" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="68" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B51" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="C51" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="C51" s="68" t="s">
+      <c r="D51" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="D51" s="68" t="s">
+      <c r="E51" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F51" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G51" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="E51" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F51" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G51" s="68" t="s">
+      <c r="H51" s="68" t="s">
         <v>219</v>
-      </c>
-      <c r="H51" s="68" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="68" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B52" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="C52" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="D52" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="D52" s="68" t="s">
+      <c r="E52" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F52" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G52" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="E52" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F52" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G52" s="68" t="s">
+      <c r="H52" s="68" t="s">
         <v>219</v>
-      </c>
-      <c r="H52" s="68" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="68" t="s">
+        <v>222</v>
+      </c>
+      <c r="B53" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="B53" s="68" t="s">
+      <c r="C53" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E53" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="68" t="s">
         <v>224</v>
       </c>
-      <c r="C53" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E53" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F53" s="68" t="s">
-        <v>225</v>
-      </c>
       <c r="G53" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H53" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="68" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B54" s="68" t="s">
+        <v>223</v>
+      </c>
+      <c r="C54" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E54" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" s="68" t="s">
         <v>224</v>
       </c>
-      <c r="C54" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E54" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F54" s="68" t="s">
-        <v>225</v>
-      </c>
       <c r="G54" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H54" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="68" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B55" s="68" t="s">
+        <v>223</v>
+      </c>
+      <c r="C55" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E55" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F55" s="68" t="s">
         <v>224</v>
       </c>
-      <c r="C55" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E55" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F55" s="68" t="s">
-        <v>225</v>
-      </c>
       <c r="G55" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H55" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="B56" s="69" t="s">
         <v>228</v>
       </c>
-      <c r="B56" s="69" t="s">
-        <v>229</v>
-      </c>
       <c r="C56" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E56" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F56" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G56" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H56" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H56" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B57" s="69" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C57" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E57" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F57" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G57" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H57" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H57" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B58" s="69" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C58" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E58" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F58" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G58" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H58" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H58" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="68" t="s">
+        <v>231</v>
+      </c>
+      <c r="B59" s="68" t="s">
         <v>232</v>
       </c>
-      <c r="B59" s="68" t="s">
-        <v>233</v>
-      </c>
       <c r="C59" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E59" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F59" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G59" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H59" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="68" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B60" s="68" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C60" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E60" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F60" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G60" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H60" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="68" t="s">
+        <v>234</v>
+      </c>
+      <c r="B61" s="68" t="s">
         <v>235</v>
       </c>
-      <c r="B61" s="68" t="s">
-        <v>236</v>
-      </c>
       <c r="C61" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E61" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F61" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G61" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H61" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="68" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B62" s="68" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C62" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E62" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F62" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G62" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H62" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="68" t="s">
+        <v>237</v>
+      </c>
+      <c r="B63" s="68" t="s">
         <v>238</v>
       </c>
-      <c r="B63" s="68" t="s">
-        <v>239</v>
-      </c>
       <c r="C63" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E63" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F63" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G63" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H63" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B64" s="68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C64" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E64" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F64" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G64" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H64" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="B65" s="69" t="s">
         <v>241</v>
       </c>
-      <c r="B65" s="69" t="s">
+      <c r="C65" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E65" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F65" s="68" t="s">
         <v>242</v>
       </c>
-      <c r="C65" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E65" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F65" s="68" t="s">
+      <c r="G65" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="H65" s="68" t="s">
         <v>243</v>
-      </c>
-      <c r="G65" s="68" t="s">
-        <v>243</v>
-      </c>
-      <c r="H65" s="68" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B66" s="69" t="s">
+        <v>241</v>
+      </c>
+      <c r="C66" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E66" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F66" s="68" t="s">
         <v>242</v>
       </c>
-      <c r="C66" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E66" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F66" s="68" t="s">
+      <c r="G66" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="H66" s="68" t="s">
         <v>243</v>
-      </c>
-      <c r="G66" s="68" t="s">
-        <v>243</v>
-      </c>
-      <c r="H66" s="68" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="68" t="s">
+        <v>245</v>
+      </c>
+      <c r="B67" s="69" t="s">
         <v>246</v>
       </c>
-      <c r="B67" s="69" t="s">
+      <c r="C67" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D67" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="E67" s="68" t="s">
         <v>247</v>
       </c>
-      <c r="C67" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="D67" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="E67" s="68" t="s">
+      <c r="F67" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G67" s="68" t="s">
         <v>248</v>
       </c>
-      <c r="F67" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G67" s="68" t="s">
-        <v>249</v>
-      </c>
       <c r="H67" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="68" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B68" s="69" t="s">
+        <v>246</v>
+      </c>
+      <c r="C68" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E68" s="68" t="s">
         <v>247</v>
       </c>
-      <c r="C68" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E68" s="68" t="s">
+      <c r="F68" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G68" s="68" t="s">
         <v>248</v>
       </c>
-      <c r="F68" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G68" s="68" t="s">
-        <v>249</v>
-      </c>
       <c r="H68" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="B69" s="69" t="s">
         <v>251</v>
       </c>
-      <c r="B69" s="69" t="s">
+      <c r="C69" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D69" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="E69" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F69" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G69" s="68" t="s">
         <v>252</v>
       </c>
-      <c r="C69" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="D69" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="E69" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F69" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G69" s="68" t="s">
+      <c r="H69" s="68" t="s">
         <v>253</v>
-      </c>
-      <c r="H69" s="68" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B70" s="69" t="s">
+        <v>251</v>
+      </c>
+      <c r="C70" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E70" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F70" s="68" t="s">
         <v>252</v>
       </c>
-      <c r="C70" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E70" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F70" s="68" t="s">
+      <c r="G70" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="H70" s="68" t="s">
         <v>253</v>
-      </c>
-      <c r="G70" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="H70" s="68" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="B71" s="69" t="s">
         <v>256</v>
       </c>
-      <c r="B71" s="69" t="s">
-        <v>257</v>
-      </c>
       <c r="C71" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D71" s="68" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E71" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F71" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G71" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H71" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="68" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B72" s="69" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C72" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D72" s="68" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E72" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F72" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G72" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H72" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="B73" s="68" t="s">
         <v>259</v>
       </c>
-      <c r="B73" s="68" t="s">
+      <c r="C73" s="68" t="s">
         <v>260</v>
       </c>
-      <c r="C73" s="68" t="s">
+      <c r="E73" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F73" s="68" t="s">
         <v>261</v>
       </c>
-      <c r="E73" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F73" s="68" t="s">
+      <c r="G73" s="68" t="s">
+        <v>261</v>
+      </c>
+      <c r="H73" s="68" t="s">
         <v>262</v>
-      </c>
-      <c r="G73" s="68" t="s">
-        <v>262</v>
-      </c>
-      <c r="H73" s="68" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="68" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B74" s="68" t="s">
+        <v>259</v>
+      </c>
+      <c r="C74" s="68" t="s">
         <v>260</v>
       </c>
-      <c r="C74" s="68" t="s">
+      <c r="E74" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F74" s="68" t="s">
         <v>261</v>
       </c>
-      <c r="E74" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F74" s="68" t="s">
+      <c r="G74" s="68" t="s">
+        <v>261</v>
+      </c>
+      <c r="H74" s="68" t="s">
         <v>262</v>
-      </c>
-      <c r="G74" s="68" t="s">
-        <v>262</v>
-      </c>
-      <c r="H74" s="68" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="B75" s="68" t="s">
         <v>265</v>
       </c>
-      <c r="B75" s="68" t="s">
+      <c r="C75" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E75" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F75" s="68" t="s">
         <v>266</v>
       </c>
-      <c r="C75" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E75" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F75" s="68" t="s">
-        <v>267</v>
-      </c>
       <c r="G75" s="68" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H75" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="68" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B76" s="68" t="s">
+        <v>265</v>
+      </c>
+      <c r="C76" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E76" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F76" s="68" t="s">
         <v>266</v>
       </c>
-      <c r="C76" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E76" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F76" s="68" t="s">
-        <v>267</v>
-      </c>
       <c r="G76" s="68" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H76" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="B77" s="68" t="s">
         <v>269</v>
       </c>
-      <c r="B77" s="68" t="s">
-        <v>270</v>
-      </c>
       <c r="C77" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E77" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F77" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G77" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H77" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="68" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B78" s="68" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C78" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E78" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F78" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G78" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H78" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="B79" s="68" t="s">
         <v>272</v>
       </c>
-      <c r="B79" s="68" t="s">
-        <v>273</v>
-      </c>
       <c r="C79" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E79" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F79" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G79" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H79" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="68" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B80" s="68" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C80" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E80" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F80" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G80" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H80" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="68" t="s">
+        <v>274</v>
+      </c>
+      <c r="B81" s="68" t="s">
         <v>275</v>
       </c>
-      <c r="B81" s="68" t="s">
-        <v>276</v>
-      </c>
       <c r="C81" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E81" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F81" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G81" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H81" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="68" t="s">
+        <v>276</v>
+      </c>
+      <c r="B82" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="C82" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E82" s="68" t="s">
         <v>277</v>
       </c>
-      <c r="B82" s="68" t="s">
-        <v>276</v>
-      </c>
-      <c r="C82" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E82" s="68" t="s">
-        <v>278</v>
-      </c>
       <c r="F82" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G82" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H82" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="68" t="s">
+        <v>278</v>
+      </c>
+      <c r="B83" s="69" t="s">
         <v>279</v>
       </c>
-      <c r="B83" s="69" t="s">
+      <c r="C83" s="68" t="s">
         <v>280</v>
       </c>
-      <c r="C83" s="68" t="s">
-        <v>281</v>
-      </c>
       <c r="E83" s="68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F83" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="68" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B84" s="69" t="s">
+        <v>279</v>
+      </c>
+      <c r="C84" s="68" t="s">
         <v>280</v>
       </c>
-      <c r="C84" s="68" t="s">
-        <v>281</v>
-      </c>
       <c r="E84" s="68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F84" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="68" t="s">
+        <v>282</v>
+      </c>
+      <c r="B85" s="69" t="s">
         <v>283</v>
       </c>
-      <c r="B85" s="69" t="s">
+      <c r="C85" s="68" t="s">
         <v>284</v>
       </c>
-      <c r="C85" s="68" t="s">
-        <v>285</v>
-      </c>
       <c r="E85" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F85" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="G85" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="H85" s="68" t="s">
         <v>253</v>
-      </c>
-      <c r="G85" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="H85" s="68" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="68" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B86" s="69" t="s">
+        <v>283</v>
+      </c>
+      <c r="C86" s="68" t="s">
         <v>284</v>
       </c>
-      <c r="C86" s="68" t="s">
-        <v>285</v>
-      </c>
       <c r="E86" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F86" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="G86" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="H86" s="68" t="s">
         <v>253</v>
-      </c>
-      <c r="G86" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="H86" s="68" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="B87" s="68" t="s">
         <v>287</v>
       </c>
-      <c r="B87" s="68" t="s">
-        <v>288</v>
-      </c>
       <c r="C87" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E87" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F87" s="68" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G87" s="68" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H87" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="68" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B88" s="68" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C88" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E88" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F88" s="68" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G88" s="68" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H88" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="68" t="s">
+        <v>289</v>
+      </c>
+      <c r="B89" s="68" t="s">
         <v>290</v>
       </c>
-      <c r="B89" s="68" t="s">
-        <v>291</v>
-      </c>
       <c r="C89" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E89" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F89" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G89" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H89" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="68" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B90" s="68" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C90" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E90" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F90" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G90" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H90" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="B91" s="68" t="s">
         <v>293</v>
       </c>
-      <c r="B91" s="68" t="s">
+      <c r="C91" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E91" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F91" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="C91" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E91" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F91" s="68" t="s">
-        <v>295</v>
-      </c>
       <c r="G91" s="68" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H91" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="68" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B92" s="68" t="s">
+        <v>293</v>
+      </c>
+      <c r="C92" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E92" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F92" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="C92" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E92" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F92" s="68" t="s">
-        <v>295</v>
-      </c>
       <c r="G92" s="68" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H92" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="68" t="s">
+        <v>296</v>
+      </c>
+      <c r="B93" s="68" t="s">
         <v>297</v>
       </c>
-      <c r="B93" s="68" t="s">
-        <v>298</v>
-      </c>
       <c r="C93" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E93" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F93" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="G93" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H93" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G93" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H93" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="68" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B94" s="68" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C94" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E94" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F94" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="G94" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H94" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G94" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H94" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4348,7 +4411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC397FCC-74C1-4D09-ACC0-E463BF5527EB}">
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="87.83203125" customWidth="1"/>
@@ -4361,7 +4424,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B1" s="72" t="s">
         <v>0</v>
@@ -4377,22 +4440,22 @@
         <v>2</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C2" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" s="40" t="s">
         <v>338</v>
-      </c>
-      <c r="D2" s="40" t="s">
-        <v>339</v>
       </c>
       <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C3" s="15">
         <v>95</v>
@@ -4404,10 +4467,10 @@
     </row>
     <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C4" s="15">
         <v>80</v>
@@ -4420,9 +4483,15 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" s="4">
+        <v>92</v>
+      </c>
+      <c r="D5" s="4">
+        <v>73</v>
+      </c>
       <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4430,7 +4499,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C6" s="1">
         <v>95</v>
@@ -4445,7 +4514,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C7" s="4">
         <v>95</v>
@@ -4459,7 +4528,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C8" s="4">
         <v>91</v>
@@ -4472,138 +4541,186 @@
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="59"/>
+      <c r="B9" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" s="4">
+        <v>96</v>
+      </c>
+      <c r="D9" s="59">
+        <v>73</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="B10" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" s="4">
+        <v>93</v>
+      </c>
+      <c r="D10" s="4">
+        <v>74</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="59"/>
+        <v>379</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C11" s="4">
+        <v>93</v>
+      </c>
+      <c r="D11" s="4">
+        <v>74</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="59"/>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C13" s="1">
+        <v>94</v>
+      </c>
+      <c r="D13" s="4">
+        <v>76</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C14" s="4">
+        <v>95</v>
+      </c>
+      <c r="D14" s="4">
+        <v>76</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C15" s="1">
+        <v>95</v>
+      </c>
+      <c r="D15" s="4">
+        <v>76</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
+      <c r="A16" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="1"/>
+      <c r="C16" s="46"/>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="43" t="s">
+      <c r="A17" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
+      <c r="B17" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C17" s="7">
+        <v>96</v>
+      </c>
+      <c r="D17" s="7">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="C19" s="40" t="s">
+      <c r="B18" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D18" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D19" s="40" t="s">
-        <v>339</v>
+    </row>
+    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>372</v>
+      </c>
+      <c r="C19" s="27">
+        <v>85</v>
+      </c>
+      <c r="D19" s="55">
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="44" t="s">
-        <v>375</v>
-      </c>
-      <c r="C20" s="27">
-        <v>85</v>
-      </c>
-      <c r="D20" s="55">
-        <v>41</v>
+      <c r="A20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C20" s="23">
+        <v>90</v>
+      </c>
+      <c r="D20" s="57">
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="C21" s="23">
-        <v>90</v>
-      </c>
-      <c r="D21" s="57">
-        <v>59</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="57"/>
     </row>
     <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="57"/>
+        <v>26</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C22" s="10">
+        <v>90</v>
+      </c>
+      <c r="D22" s="57">
+        <v>69</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C23" s="10">
         <v>90</v>
@@ -4614,490 +4731,528 @@
     </row>
     <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="C24" s="10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D24" s="57">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="57"/>
+        <v>29</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C25" s="10">
+        <v>91</v>
+      </c>
+      <c r="D25" s="57">
+        <v>55</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="57"/>
+        <v>30</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C26" s="10">
+        <v>93</v>
+      </c>
+      <c r="D26" s="57">
+        <v>59</v>
+      </c>
     </row>
     <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="57"/>
+        <v>31</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C27" s="10">
+        <v>92</v>
+      </c>
+      <c r="D27" s="57">
+        <v>56</v>
+      </c>
     </row>
     <row r="28" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="57"/>
-    </row>
-    <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="57"/>
-    </row>
-    <row r="30" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
+      <c r="B28" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C28" s="10">
+        <v>93</v>
+      </c>
+      <c r="D28" s="57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="39" t="s">
-        <v>359</v>
-      </c>
-      <c r="C30" s="40" t="s">
+      <c r="B29" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D29" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D30" s="40" t="s">
-        <v>339</v>
-      </c>
+    </row>
+    <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="57"/>
     </row>
     <row r="31" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="B31" s="6"/>
       <c r="C31" s="47"/>
       <c r="D31" s="57"/>
     </row>
     <row r="32" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="47"/>
       <c r="D32" s="57"/>
     </row>
-    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="47"/>
-      <c r="D33" s="57"/>
-    </row>
-    <row r="34" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="54"/>
-    </row>
-    <row r="35" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
+      <c r="D33" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="C35" s="40" t="s">
+      <c r="B34" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D34" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D35" s="40" t="s">
-        <v>339</v>
+    </row>
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="4">
+        <v>20000</v>
+      </c>
+      <c r="C35" s="48">
+        <v>90</v>
+      </c>
+      <c r="D35" s="64">
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B36" s="4">
-        <v>20000</v>
-      </c>
-      <c r="C36" s="48">
+        <v>19330</v>
+      </c>
+      <c r="C36" s="4">
+        <v>92</v>
+      </c>
+      <c r="D36" s="64">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C37" s="4">
         <v>90</v>
       </c>
-      <c r="D36" s="64">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="64"/>
-    </row>
-    <row r="38" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="60">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B38" s="4">
-        <v>10000</v>
+        <v>2400</v>
       </c>
       <c r="C38" s="4">
         <v>90</v>
       </c>
       <c r="D38" s="60">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="4">
-        <v>2400</v>
-      </c>
-      <c r="C39" s="4">
-        <v>90</v>
-      </c>
-      <c r="D39" s="60">
-        <v>40</v>
+      <c r="A39" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="15">
+        <v>2250</v>
+      </c>
+      <c r="C39" s="15">
+        <v>96</v>
+      </c>
+      <c r="D39" s="15">
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
+        <v>44</v>
+      </c>
+      <c r="B40" s="45"/>
+      <c r="C40" s="45"/>
       <c r="D40" s="15"/>
     </row>
     <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="45"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="15"/>
+      <c r="A41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1550</v>
+      </c>
+      <c r="C41" s="4">
+        <v>88</v>
+      </c>
+      <c r="D41" s="4">
+        <v>41</v>
+      </c>
     </row>
     <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B42" s="4">
-        <v>1550</v>
-      </c>
-      <c r="C42" s="4">
-        <v>88</v>
+        <v>400</v>
+      </c>
+      <c r="C42" s="1">
+        <v>97</v>
       </c>
       <c r="D42" s="4">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" s="4">
-        <v>400</v>
-      </c>
-      <c r="C43" s="1">
-        <v>97</v>
-      </c>
-      <c r="D43" s="4">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="29" t="s">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="C45" s="40" t="s">
-        <v>338</v>
-      </c>
-      <c r="D45" s="40" t="s">
+      <c r="B44" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="C44" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D44" s="40" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C45" s="33">
+        <v>98</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="C46" s="33">
+        <v>354</v>
+      </c>
+      <c r="C46" s="49">
         <v>98</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C47" s="49">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="C47" s="23">
+        <v>90</v>
+      </c>
+      <c r="D47" s="57" t="s">
+        <v>317</v>
+      </c>
+      <c r="E47" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C48" s="23">
         <v>98</v>
       </c>
-      <c r="D47" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C48" s="23">
-        <v>90</v>
-      </c>
-      <c r="D48" s="57" t="s">
-        <v>318</v>
-      </c>
-      <c r="E48" t="s">
-        <v>370</v>
+      <c r="D48" s="59" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="57"/>
+    </row>
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C50" s="23">
+        <v>99</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C51" s="32">
+        <v>98</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C52" s="23">
+        <v>99</v>
+      </c>
+      <c r="D52" s="24"/>
+    </row>
+    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C53" s="31">
+        <v>99</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C54" s="23">
+        <v>98</v>
+      </c>
+      <c r="D54" s="59" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="C49" s="23">
-        <v>98</v>
-      </c>
-      <c r="D49" s="59" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="57"/>
-    </row>
-    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="C51" s="23">
-        <v>99</v>
-      </c>
-      <c r="D51" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C52" s="32">
-        <v>98</v>
-      </c>
-      <c r="D52" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="C53" s="23">
-        <v>99</v>
-      </c>
-      <c r="D53" s="24"/>
-    </row>
-    <row r="54" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="C54" s="31">
-        <v>99</v>
-      </c>
-      <c r="D54" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="C55" s="23">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C56" s="23">
+        <v>99</v>
+      </c>
+      <c r="D56" s="59" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C57" s="23">
         <v>98</v>
       </c>
-      <c r="D56" s="59" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="C57" s="23">
-        <v>99</v>
-      </c>
-      <c r="D57" s="59" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="C58" s="23">
-        <v>98</v>
-      </c>
-      <c r="D58" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D57" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="55"/>
+    </row>
+    <row r="59" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B59" s="4"/>
-      <c r="C59" s="58"/>
-      <c r="D59" s="55"/>
-    </row>
-    <row r="60" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C59" s="23"/>
+      <c r="D59" s="57"/>
+    </row>
+    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="23"/>
       <c r="D60" s="57"/>
     </row>
-    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="23"/>
       <c r="D61" s="57"/>
     </row>
-    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B62" s="4"/>
-      <c r="C62" s="23"/>
+      <c r="C62" s="32"/>
       <c r="D62" s="57"/>
     </row>
-    <row r="63" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B63" s="4"/>
-      <c r="C63" s="32"/>
+      <c r="C63" s="23"/>
       <c r="D63" s="57"/>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B64" s="4"/>
-      <c r="C64" s="23"/>
+      <c r="C64" s="53"/>
       <c r="D64" s="57"/>
     </row>
-    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="53"/>
+    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="6"/>
+      <c r="C65" s="52"/>
       <c r="D65" s="57"/>
     </row>
-    <row r="66" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66" s="6"/>
-      <c r="C66" s="52"/>
-      <c r="D66" s="57"/>
-    </row>
-    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="28" t="s">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B67" s="20" t="s">
+      <c r="B66" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C67" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="D67" s="67"/>
+      <c r="C66" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="D66" s="67"/>
+    </row>
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="24"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="57"/>
     </row>
     <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B68" s="24"/>
       <c r="C68" s="10"/>
@@ -5105,7 +5260,7 @@
     </row>
     <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B69" s="24"/>
       <c r="C69" s="10"/>
@@ -5113,7 +5268,7 @@
     </row>
     <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B70" s="24"/>
       <c r="C70" s="10"/>
@@ -5121,7 +5276,7 @@
     </row>
     <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B71" s="24"/>
       <c r="C71" s="10"/>
@@ -5129,7 +5284,7 @@
     </row>
     <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B72" s="24"/>
       <c r="C72" s="10"/>
@@ -5137,7 +5292,7 @@
     </row>
     <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B73" s="24"/>
       <c r="C73" s="10"/>
@@ -5145,7 +5300,7 @@
     </row>
     <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B74" s="24"/>
       <c r="C74" s="10"/>
@@ -5153,7 +5308,7 @@
     </row>
     <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B75" s="24"/>
       <c r="C75" s="10"/>
@@ -5161,7 +5316,7 @@
     </row>
     <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B76" s="24"/>
       <c r="C76" s="10"/>
@@ -5169,7 +5324,7 @@
     </row>
     <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B77" s="24"/>
       <c r="C77" s="10"/>
@@ -5177,7 +5332,7 @@
     </row>
     <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B78" s="24"/>
       <c r="C78" s="10"/>
@@ -5185,7 +5340,7 @@
     </row>
     <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B79" s="24"/>
       <c r="C79" s="10"/>
@@ -5193,47 +5348,47 @@
     </row>
     <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="10"/>
+        <v>85</v>
+      </c>
+      <c r="B80" s="33"/>
+      <c r="C80" s="23"/>
       <c r="D80" s="57"/>
     </row>
     <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B81" s="33"/>
-      <c r="C81" s="23"/>
+      <c r="A81" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="24"/>
+      <c r="C81" s="32"/>
       <c r="D81" s="57"/>
     </row>
     <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A82" s="43" t="s">
-        <v>86</v>
+      <c r="A82" s="51" t="s">
+        <v>87</v>
       </c>
       <c r="B82" s="24"/>
       <c r="C82" s="32"/>
       <c r="D82" s="57"/>
     </row>
     <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="B83" s="24"/>
-      <c r="C83" s="32"/>
+      <c r="A83" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="33"/>
+      <c r="C83" s="23"/>
       <c r="D83" s="57"/>
     </row>
     <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A84" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B84" s="33"/>
-      <c r="C84" s="23"/>
+      <c r="A84" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="24"/>
+      <c r="C84" s="10"/>
       <c r="D84" s="57"/>
     </row>
     <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B85" s="24"/>
       <c r="C85" s="10"/>
@@ -5241,15 +5396,15 @@
     </row>
     <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B86" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="B86" s="10"/>
       <c r="C86" s="10"/>
       <c r="D86" s="57"/>
     </row>
     <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
@@ -5257,15 +5412,15 @@
     </row>
     <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B88" s="10"/>
+        <v>93</v>
+      </c>
+      <c r="B88" s="24"/>
       <c r="C88" s="10"/>
       <c r="D88" s="57"/>
     </row>
     <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B89" s="24"/>
       <c r="C89" s="10"/>
@@ -5273,7 +5428,7 @@
     </row>
     <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B90" s="24"/>
       <c r="C90" s="10"/>
@@ -5281,67 +5436,99 @@
     </row>
     <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B91" s="24"/>
-      <c r="C91" s="10"/>
-      <c r="D91" s="57"/>
+        <v>96</v>
+      </c>
+      <c r="B91" s="10">
+        <v>80000</v>
+      </c>
+      <c r="C91" s="10">
+        <v>55</v>
+      </c>
+      <c r="D91" s="57">
+        <v>35</v>
+      </c>
     </row>
     <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B92" s="10"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="57"/>
+        <v>97</v>
+      </c>
+      <c r="B92" s="24">
+        <v>80000</v>
+      </c>
+      <c r="C92" s="10">
+        <v>60</v>
+      </c>
+      <c r="D92" s="57">
+        <v>37</v>
+      </c>
     </row>
     <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B93" s="24"/>
-      <c r="C93" s="24"/>
-      <c r="D93" s="57"/>
+        <v>98</v>
+      </c>
+      <c r="B93" s="70">
+        <v>51000</v>
+      </c>
+      <c r="C93" s="57"/>
+      <c r="D93" s="71" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B94" s="24"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="57"/>
+        <v>389</v>
+      </c>
+      <c r="B94" s="24">
+        <v>32000</v>
+      </c>
+      <c r="C94" s="76">
+        <v>56</v>
+      </c>
+      <c r="D94" s="56">
+        <v>40</v>
+      </c>
     </row>
     <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B95" s="24"/>
-      <c r="C95" s="10"/>
-      <c r="D95" s="57"/>
+        <v>387</v>
+      </c>
+      <c r="B95" s="24">
+        <v>32000</v>
+      </c>
+      <c r="C95" s="26">
+        <v>57</v>
+      </c>
+      <c r="D95" s="56">
+        <v>58</v>
+      </c>
     </row>
     <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B96" s="24"/>
-      <c r="C96" s="26"/>
-      <c r="D96" s="56"/>
+      <c r="B96" s="34"/>
+      <c r="C96" s="35"/>
+      <c r="D96" s="10"/>
     </row>
     <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B97" s="34"/>
-      <c r="C97" s="35"/>
-      <c r="D97" s="10"/>
+      <c r="B97" s="75">
+        <v>26000</v>
+      </c>
+      <c r="C97" s="70"/>
+      <c r="D97" s="70" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="98" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="10"/>
-      <c r="D98" s="10"/>
+      <c r="B98" s="75"/>
+      <c r="C98" s="70"/>
+      <c r="D98" s="70"/>
     </row>
     <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
@@ -5355,7 +5542,7 @@
       <c r="A100" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B100" s="24"/>
+      <c r="B100" s="16"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
     </row>
@@ -5363,7 +5550,7 @@
       <c r="A101" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B101" s="16"/>
+      <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
     </row>
@@ -5371,17 +5558,13 @@
       <c r="A102" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B102" s="10"/>
+      <c r="B102" s="24"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
     </row>
-    <row r="103" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A103" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B103" s="24"/>
-      <c r="C103" s="10"/>
-      <c r="D103" s="10"/>
+    <row r="103" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I103" s="11"/>
+      <c r="J103" s="11"/>
     </row>
     <row r="104" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I104" s="11"/>
@@ -5394,10 +5577,6 @@
     <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I106" s="11"/>
       <c r="J106" s="11"/>
-    </row>
-    <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I107" s="11"/>
-      <c r="J107" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5422,10 +5601,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>1</v>
@@ -5437,21 +5616,21 @@
         <v>2</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C2" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" s="40" t="s">
         <v>338</v>
-      </c>
-      <c r="D2" s="40" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C3" s="59">
         <v>91</v>
@@ -5462,10 +5641,10 @@
     </row>
     <row r="4" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C4" s="4">
         <v>70</v>
@@ -5474,7 +5653,7 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5490,7 +5669,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C6" s="4">
         <v>94</v>
@@ -5504,7 +5683,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C7" s="59">
         <v>96</v>
@@ -5539,91 +5718,97 @@
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="59"/>
+        <v>379</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="59"/>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="59"/>
       <c r="D12" s="59"/>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="B13" s="1"/>
       <c r="C13" s="4"/>
       <c r="D13" s="59"/>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="59"/>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
       <c r="C15" s="4"/>
       <c r="D15" s="59"/>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="1"/>
+      <c r="A16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="46"/>
       <c r="C16" s="4"/>
       <c r="D16" s="59"/>
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="4"/>
+      <c r="A17" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
       <c r="D17" s="59"/>
     </row>
-    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="59"/>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
+    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B18" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C18" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D18" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D19" s="40" t="s">
-        <v>339</v>
+    </row>
+    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="C19" s="55">
+        <v>92</v>
+      </c>
+      <c r="D19" s="59">
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>351</v>
-      </c>
-      <c r="C20" s="55">
-        <v>92</v>
+      <c r="A20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="C20" s="57">
+        <v>95</v>
       </c>
       <c r="D20" s="59">
         <v>63</v>
@@ -5631,68 +5816,62 @@
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="C21" s="57">
-        <v>95</v>
-      </c>
-      <c r="D21" s="59">
-        <v>63</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="59"/>
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="59"/>
+        <v>26</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="C22" s="57">
+        <v>93</v>
+      </c>
+      <c r="D22" s="59">
+        <v>64</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>349</v>
       </c>
       <c r="C23" s="57">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D23" s="59">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="C24" s="57">
-        <v>92</v>
-      </c>
-      <c r="D24" s="59">
-        <v>61</v>
+        <v>28</v>
+      </c>
+      <c r="B24" s="10"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="59"/>
+      <c r="F24" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="57"/>
       <c r="D25" s="59"/>
-      <c r="F25" t="s">
-        <v>352</v>
-      </c>
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="57"/>
@@ -5700,7 +5879,7 @@
     </row>
     <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="57"/>
@@ -5708,37 +5887,37 @@
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="57"/>
       <c r="D28" s="59"/>
     </row>
-    <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="59"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B29" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C29" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D29" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D30" s="40" t="s">
-        <v>339</v>
-      </c>
+    </row>
+    <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="47"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="59"/>
     </row>
     <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="47"/>
       <c r="C31" s="57"/>
@@ -5746,421 +5925,421 @@
     </row>
     <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B32" s="47"/>
       <c r="C32" s="57"/>
       <c r="D32" s="59"/>
     </row>
-    <row r="33" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B33" s="47"/>
-      <c r="C33" s="57"/>
+      <c r="C33" s="54"/>
       <c r="D33" s="59"/>
     </row>
-    <row r="34" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="47"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="59"/>
-    </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B34" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="40" t="s">
+      <c r="C34" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D34" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D35" s="40" t="s">
-        <v>339</v>
+    </row>
+    <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="48">
+        <v>26000</v>
+      </c>
+      <c r="C35" s="64">
+        <v>90</v>
+      </c>
+      <c r="D35" s="59">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="48">
-        <v>26000</v>
+        <v>40</v>
+      </c>
+      <c r="B36" s="4">
+        <v>25400</v>
       </c>
       <c r="C36" s="64">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D36" s="59">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B37" s="4">
-        <v>25400</v>
-      </c>
-      <c r="C37" s="64">
-        <v>93</v>
+        <v>13300</v>
+      </c>
+      <c r="C37" s="60">
+        <v>95</v>
       </c>
       <c r="D37" s="59">
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B38" s="4">
-        <v>13300</v>
+        <v>3200</v>
       </c>
       <c r="C38" s="60">
         <v>95</v>
       </c>
       <c r="D38" s="59">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="4">
-        <v>3200</v>
-      </c>
-      <c r="C39" s="60">
-        <v>95</v>
-      </c>
-      <c r="D39" s="59">
-        <v>38</v>
-      </c>
+      <c r="A39" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="59"/>
     </row>
     <row r="40" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="15"/>
+        <v>44</v>
+      </c>
+      <c r="B40" s="45"/>
       <c r="C40" s="15"/>
       <c r="D40" s="59"/>
     </row>
     <row r="41" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="45"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="59"/>
+      <c r="A41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1810</v>
+      </c>
+      <c r="C41" s="4">
+        <v>95</v>
+      </c>
+      <c r="D41" s="59">
+        <v>68</v>
+      </c>
     </row>
     <row r="42" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="4">
-        <v>1810</v>
+        <v>46</v>
+      </c>
+      <c r="B42" s="1">
+        <v>460</v>
       </c>
       <c r="C42" s="4">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D42" s="59">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" s="1">
-        <v>460</v>
-      </c>
-      <c r="C43" s="4">
-        <v>93</v>
-      </c>
-      <c r="D43" s="59">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="59"/>
-    </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="29" t="s">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="59"/>
+    </row>
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B44" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C45" s="40" t="s">
-        <v>338</v>
-      </c>
-      <c r="D45" s="40" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C44" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="C45" s="24">
+        <v>98</v>
+      </c>
+      <c r="D45" s="59" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" s="33" t="s">
-        <v>319</v>
+        <v>50</v>
+      </c>
+      <c r="B46" s="49" t="s">
+        <v>321</v>
       </c>
       <c r="C46" s="24">
         <v>98</v>
       </c>
       <c r="D46" s="59" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="49" t="s">
-        <v>322</v>
-      </c>
-      <c r="C47" s="24">
-        <v>98</v>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="C47" s="57">
+        <v>96</v>
       </c>
       <c r="D47" s="59" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="23" t="s">
-        <v>324</v>
+      <c r="A48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="49" t="s">
+        <v>320</v>
       </c>
       <c r="C48" s="57">
         <v>96</v>
       </c>
       <c r="D48" s="59" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49" s="49" t="s">
-        <v>321</v>
-      </c>
-      <c r="C49" s="57">
-        <v>96</v>
-      </c>
-      <c r="D49" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="23"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="59"/>
+    </row>
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="23" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50" s="23"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="59"/>
-    </row>
-    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="C50" s="55">
+        <v>98</v>
+      </c>
+      <c r="D50" s="59" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="32" t="s">
         <v>334</v>
       </c>
-      <c r="C51" s="55">
+      <c r="C51" s="57">
         <v>98</v>
       </c>
       <c r="D51" s="59" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="32" t="s">
-        <v>335</v>
+        <v>56</v>
+      </c>
+      <c r="B52" s="58" t="s">
+        <v>331</v>
       </c>
       <c r="C52" s="57">
+        <v>99</v>
+      </c>
+      <c r="D52" s="59" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="C53" s="65">
+        <v>99</v>
+      </c>
+      <c r="D53" s="59" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="C54" s="66">
         <v>98</v>
       </c>
-      <c r="D52" s="59" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" s="58" t="s">
-        <v>332</v>
-      </c>
-      <c r="C53" s="57">
-        <v>99</v>
-      </c>
-      <c r="D53" s="59" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="31" t="s">
-        <v>331</v>
-      </c>
-      <c r="C54" s="65">
-        <v>99</v>
-      </c>
       <c r="D54" s="59" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="18" t="s">
-        <v>58</v>
+      <c r="A55" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C55" s="66">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C56" s="66">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D56" s="59" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="C57" s="66">
+    </row>
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="C57" s="57">
         <v>96</v>
       </c>
       <c r="D57" s="59" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" s="25" t="s">
-        <v>320</v>
-      </c>
-      <c r="C58" s="57">
-        <v>96</v>
-      </c>
-      <c r="D58" s="59" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="23"/>
+      <c r="C58" s="55"/>
+      <c r="D58" s="59"/>
+    </row>
+    <row r="59" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B59" s="23"/>
-      <c r="C59" s="55"/>
+      <c r="C59" s="57"/>
       <c r="D59" s="59"/>
     </row>
-    <row r="60" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B60" s="23"/>
       <c r="C60" s="57"/>
       <c r="D60" s="59"/>
     </row>
-    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B61" s="23"/>
       <c r="C61" s="57"/>
       <c r="D61" s="59"/>
     </row>
-    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B62" s="23"/>
+        <v>66</v>
+      </c>
+      <c r="B62" s="32"/>
       <c r="C62" s="57"/>
       <c r="D62" s="59"/>
     </row>
-    <row r="63" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B63" s="32"/>
+        <v>67</v>
+      </c>
+      <c r="B63" s="23"/>
       <c r="C63" s="57"/>
       <c r="D63" s="59"/>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B64" s="23"/>
+        <v>68</v>
+      </c>
+      <c r="B64" s="53"/>
       <c r="C64" s="57"/>
       <c r="D64" s="59"/>
     </row>
-    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65" s="53"/>
+    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="52"/>
       <c r="C65" s="57"/>
       <c r="D65" s="59"/>
     </row>
-    <row r="66" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66" s="52"/>
-      <c r="C66" s="57"/>
-      <c r="D66" s="59"/>
-    </row>
-    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="28" t="s">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B67" s="30" t="s">
+      <c r="B66" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C67" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="D67" s="67" t="s">
-        <v>341</v>
-      </c>
+      <c r="C66" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="D66" s="67" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="10"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="57"/>
     </row>
     <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B68" s="10"/>
       <c r="C68" s="57"/>
@@ -6168,7 +6347,7 @@
     </row>
     <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B69" s="10"/>
       <c r="C69" s="57"/>
@@ -6176,7 +6355,7 @@
     </row>
     <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B70" s="10"/>
       <c r="C70" s="57"/>
@@ -6184,7 +6363,7 @@
     </row>
     <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B71" s="10"/>
       <c r="C71" s="57"/>
@@ -6192,7 +6371,7 @@
     </row>
     <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B72" s="10"/>
       <c r="C72" s="57"/>
@@ -6200,7 +6379,7 @@
     </row>
     <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B73" s="10"/>
       <c r="C73" s="57"/>
@@ -6208,15 +6387,17 @@
     </row>
     <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B74" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="B74" s="10">
+        <v>1536</v>
+      </c>
       <c r="C74" s="57"/>
       <c r="D74" s="57"/>
     </row>
     <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B75" s="10"/>
       <c r="C75" s="57"/>
@@ -6224,7 +6405,7 @@
     </row>
     <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B76" s="10"/>
       <c r="C76" s="57"/>
@@ -6232,7 +6413,7 @@
     </row>
     <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="57"/>
@@ -6240,7 +6421,7 @@
     </row>
     <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B78" s="10"/>
       <c r="C78" s="57"/>
@@ -6248,7 +6429,7 @@
     </row>
     <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B79" s="10"/>
       <c r="C79" s="57"/>
@@ -6256,47 +6437,47 @@
     </row>
     <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B80" s="10"/>
+        <v>85</v>
+      </c>
+      <c r="B80" s="23"/>
       <c r="C80" s="57"/>
       <c r="D80" s="57"/>
     </row>
     <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B81" s="23"/>
+      <c r="A81" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="32"/>
       <c r="C81" s="57"/>
       <c r="D81" s="57"/>
     </row>
     <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A82" s="43" t="s">
-        <v>86</v>
+      <c r="A82" s="51" t="s">
+        <v>87</v>
       </c>
       <c r="B82" s="32"/>
       <c r="C82" s="57"/>
       <c r="D82" s="57"/>
     </row>
     <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="B83" s="32"/>
+      <c r="A83" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="23"/>
       <c r="C83" s="57"/>
       <c r="D83" s="57"/>
     </row>
     <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A84" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B84" s="23"/>
+      <c r="A84" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="10"/>
       <c r="C84" s="57"/>
       <c r="D84" s="57"/>
     </row>
     <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B85" s="10"/>
       <c r="C85" s="57"/>
@@ -6304,39 +6485,35 @@
     </row>
     <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B86" s="10"/>
-      <c r="C86" s="57"/>
-      <c r="D86" s="57"/>
+        <v>91</v>
+      </c>
+      <c r="B86" s="74" t="s">
+        <v>381</v>
+      </c>
+      <c r="C86" s="71"/>
+      <c r="D86" s="71"/>
     </row>
     <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B87" s="70" t="s">
-        <v>353</v>
+        <v>92</v>
+      </c>
+      <c r="B87" s="74" t="s">
+        <v>382</v>
       </c>
       <c r="C87" s="71"/>
-      <c r="D87" s="71" t="s">
-        <v>354</v>
-      </c>
+      <c r="D87" s="71"/>
     </row>
     <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B88" s="70" t="s">
-        <v>353</v>
-      </c>
-      <c r="C88" s="71"/>
-      <c r="D88" s="71" t="s">
-        <v>354</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="B88" s="10"/>
+      <c r="C88" s="57"/>
+      <c r="D88" s="57"/>
     </row>
     <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="57"/>
@@ -6344,7 +6521,7 @@
     </row>
     <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="57"/>
@@ -6352,51 +6529,55 @@
     </row>
     <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B91" s="10"/>
-      <c r="C91" s="57"/>
-      <c r="D91" s="57"/>
+        <v>96</v>
+      </c>
+      <c r="B91" s="10">
+        <v>96000</v>
+      </c>
+      <c r="C91" s="57">
+        <v>50</v>
+      </c>
+      <c r="D91" s="57">
+        <v>35</v>
+      </c>
     </row>
     <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B92" s="10">
         <v>96000</v>
       </c>
       <c r="C92" s="57">
-        <v>50</v>
-      </c>
-      <c r="D92" s="57"/>
+        <v>55</v>
+      </c>
+      <c r="D92" s="57">
+        <v>35</v>
+      </c>
     </row>
     <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="10">
-        <v>96000</v>
-      </c>
-      <c r="C93" s="57">
-        <v>55</v>
-      </c>
-      <c r="D93" s="57"/>
+      <c r="B93" s="70">
+        <v>51000</v>
+      </c>
+      <c r="C93" s="57"/>
+      <c r="D93" s="71" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B94" s="70">
-        <v>51000</v>
-      </c>
-      <c r="C94" s="57"/>
-      <c r="D94" s="71" t="s">
-        <v>355</v>
-      </c>
+      <c r="B94" s="77"/>
+      <c r="C94" s="56"/>
+      <c r="D94" s="71"/>
     </row>
     <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="B95" s="26"/>
       <c r="C95" s="56"/>
@@ -6404,7 +6585,7 @@
     </row>
     <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B96" s="35"/>
       <c r="C96" s="10"/>
@@ -6412,7 +6593,7 @@
     </row>
     <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
@@ -6420,7 +6601,7 @@
     </row>
     <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B98" s="10">
         <v>1200</v>
@@ -6434,7 +6615,7 @@
     </row>
     <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
@@ -6442,7 +6623,7 @@
     </row>
     <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
@@ -6450,7 +6631,7 @@
     </row>
     <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
@@ -6458,7 +6639,7 @@
     </row>
     <row r="102" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
@@ -6498,10 +6679,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A1" s="50" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>1</v>
@@ -6556,10 +6737,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" s="60" t="s">
         <v>315</v>
-      </c>
-      <c r="C8" s="60" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -6567,10 +6748,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C9" s="59" t="s">
         <v>313</v>
-      </c>
-      <c r="C9" s="59" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6669,10 +6850,10 @@
         <v>24</v>
       </c>
       <c r="B23" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C23" s="57" t="s">
         <v>301</v>
-      </c>
-      <c r="C23" s="57" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6687,10 +6868,10 @@
         <v>26</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -6698,10 +6879,10 @@
         <v>27</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C26" s="57" t="s">
         <v>303</v>
-      </c>
-      <c r="C26" s="57" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6800,10 +6981,10 @@
         <v>41</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C40" s="60" t="s">
         <v>311</v>
-      </c>
-      <c r="C40" s="60" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -6811,10 +6992,10 @@
         <v>42</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6843,10 +7024,10 @@
         <v>46</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">

--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sshivang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{053772BF-543F-5C4A-893B-EAF5AB8AC049}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD6FC04-8FAA-5B40-B3B5-2D5B862F6C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19740" activeTab="1" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="17280" windowHeight="19980" activeTab="1" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="380">
   <si>
     <t>SRX400
 Tested Numbers</t>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>Max FW HTTP concurrent Session capacity</t>
+  </si>
+  <si>
+    <t>Max FW HTTP concurrent Session capacity - with Scaled L3L4 mode</t>
   </si>
   <si>
     <t>Max AppSec Sessions(unified policy)</t>
@@ -1148,6 +1151,12 @@
     <t>ß</t>
   </si>
   <si>
+    <t>80K</t>
+  </si>
+  <si>
+    <t>PR 1954675</t>
+  </si>
+  <si>
     <t>PR 1954327</t>
   </si>
   <si>
@@ -1237,73 +1246,13 @@
     <t>190 CPS / 110 Mbps</t>
   </si>
   <si>
+    <t>160 CPS / 90 Mbps</t>
+  </si>
+  <si>
     <t>55 CPS / 30 Mbps</t>
   </si>
   <si>
     <t>1570 CPS / 894 Mbps</t>
-  </si>
-  <si>
-    <t>556 CPS / 318 Mbps</t>
-  </si>
-  <si>
-    <t>1620 CPS /911 Mbps</t>
-  </si>
-  <si>
-    <t>1596 CPS /903 Mbps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppSec+ UTM NG-WF(100% cache) </t>
-  </si>
-  <si>
-    <t>1579 CPS / 893 Mbps</t>
-  </si>
-  <si>
-    <t>400K</t>
-  </si>
-  <si>
-    <t>200K</t>
-  </si>
-  <si>
-    <t>796 CPS / 440 Mbps</t>
-  </si>
-  <si>
-    <t>448 CPS / 237 Mbps</t>
-  </si>
-  <si>
-    <t>428 CPS / 228 Mbps</t>
-  </si>
-  <si>
-    <t>444 CPS / 234 Mbps</t>
-  </si>
-  <si>
-    <t>Max UTM-NG-WF Sessions capacity</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>Max UTM-EWF Sessions capacity</t>
-  </si>
-  <si>
-    <t>Max UTM- NG-WF Sessions capacity</t>
-  </si>
-  <si>
-    <t>165 CPS / 91 Mbps</t>
-  </si>
-  <si>
-    <t>164 CPS / 91 Mbps</t>
-  </si>
-  <si>
-    <t>141 CPS / 85 Mbps</t>
-  </si>
-  <si>
-    <t>149 CPS / 86 Mbps</t>
-  </si>
-  <si>
-    <t>119 CPS / 71 Mbps</t>
-  </si>
-  <si>
-    <t>123 CPS / 74 Mbps</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1597,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1853,18 +1802,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1881,10 +1818,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2196,2158 +2129,2158 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B1" s="68" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C1" s="68" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D1" s="68" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E1" s="68" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F1" s="68" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G1" s="68" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H1" s="68" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B2" s="68" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C2" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F2" s="68" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G2" s="68" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H2" s="68" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="68" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" s="68" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F3" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G3" s="68" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H3" s="68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B4" s="68" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E4" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F4" s="68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G4" s="68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H4" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H5" s="68" t="s">
         <v>132</v>
-      </c>
-      <c r="B5" s="68" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="68" t="s">
-        <v>130</v>
-      </c>
-      <c r="H5" s="68" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="68" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F6" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G6" s="68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H6" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="68" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B7" s="68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C7" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E7" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F7" s="68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G7" s="68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H7" s="68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="B8" s="68" t="s">
-        <v>136</v>
-      </c>
-      <c r="C8" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="D8" s="68" t="s">
-        <v>140</v>
-      </c>
-      <c r="E8" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="F8" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="G8" s="68" t="s">
-        <v>138</v>
-      </c>
       <c r="H8" s="68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B9" s="68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E9" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F9" s="68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H9" s="68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="68" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B10" s="68" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C10" s="68" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E10" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F10" s="68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G10" s="68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H10" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="68" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" s="68" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E11" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F11" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G11" s="68" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H11" s="68" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="68" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" s="68" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E12" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F12" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G12" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H12" s="68" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="68" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="H13" s="68" t="s">
         <v>155</v>
-      </c>
-      <c r="B13" s="68" t="s">
-        <v>152</v>
-      </c>
-      <c r="C13" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="E13" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="F13" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="G13" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="H13" s="68" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="68" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B14" s="68" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C14" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E14" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F14" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G14" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H14" s="68" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="68" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B15" s="68" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C15" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E15" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F15" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G15" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H15" s="68" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B16" s="68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C16" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E16" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F16" s="68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G16" s="68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H16" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="H17" s="68" t="s">
         <v>162</v>
-      </c>
-      <c r="B17" s="68" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" s="68" t="s">
-        <v>160</v>
-      </c>
-      <c r="G17" s="68" t="s">
-        <v>160</v>
-      </c>
-      <c r="H17" s="68" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="68" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B18" s="68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E18" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F18" s="68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G18" s="68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H18" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="68" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B19" s="68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E19" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F19" s="68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G19" s="68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H19" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="68" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B20" s="68" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E20" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F20" s="68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G20" s="68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H20" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="68" t="s">
+        <v>170</v>
+      </c>
+      <c r="B21" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" s="68" t="s">
         <v>169</v>
       </c>
-      <c r="B21" s="68" t="s">
-        <v>166</v>
-      </c>
-      <c r="C21" s="68" t="s">
-        <v>167</v>
-      </c>
-      <c r="E21" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="F21" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="G21" s="68" t="s">
-        <v>168</v>
-      </c>
       <c r="H21" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B22" s="68" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C22" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E22" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F22" s="68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G22" s="68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H22" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="68" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B23" s="68" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C23" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F23" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G23" s="68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H23" s="68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24" s="68" t="s">
         <v>173</v>
       </c>
-      <c r="B24" s="68" t="s">
-        <v>172</v>
-      </c>
       <c r="C24" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E24" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F24" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G24" s="68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H24" s="68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="68" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B25" s="68" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E25" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F25" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G25" s="68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H25" s="68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="68" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B26" s="68" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C26" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E26" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F26" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G26" s="68" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H26" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="68" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="F27" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="68" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="68" t="s">
-        <v>176</v>
-      </c>
-      <c r="C27" s="68" t="s">
-        <v>167</v>
-      </c>
-      <c r="E27" s="68" t="s">
-        <v>134</v>
-      </c>
-      <c r="F27" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="G27" s="68" t="s">
-        <v>177</v>
-      </c>
       <c r="H27" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="68" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B28" s="68" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C28" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E28" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F28" s="68" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G28" s="68" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H28" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="68" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B29" s="68" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C29" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E29" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F29" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G29" s="68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H29" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="B30" s="68" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="F30" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" s="68" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="68" t="s">
-        <v>181</v>
-      </c>
-      <c r="C30" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="68" t="s">
-        <v>134</v>
-      </c>
-      <c r="F30" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="G30" s="68" t="s">
-        <v>182</v>
-      </c>
       <c r="H30" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="68" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B31" s="68" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C31" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E31" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F31" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G31" s="68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H31" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="68" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B32" s="68" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C32" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E32" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F32" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G32" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H32" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B33" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F33" s="68" t="s">
         <v>188</v>
       </c>
-      <c r="B33" s="68" t="s">
-        <v>186</v>
-      </c>
-      <c r="C33" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="E33" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="F33" s="68" t="s">
-        <v>187</v>
-      </c>
       <c r="G33" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H33" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="68" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B34" s="68" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C34" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E34" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F34" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G34" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H34" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="68" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B35" s="69" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C35" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E35" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G35" s="68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H35" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="B36" s="69" t="s">
         <v>192</v>
       </c>
-      <c r="B36" s="69" t="s">
-        <v>191</v>
-      </c>
       <c r="C36" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E36" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G36" s="68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H36" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="68" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B37" s="69" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C37" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E37" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F37" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G37" s="68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H37" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="68" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B38" s="69" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C38" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E38" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F38" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G38" s="68" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H38" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="B39" s="69" t="s">
         <v>196</v>
       </c>
-      <c r="B39" s="69" t="s">
-        <v>195</v>
-      </c>
       <c r="C39" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E39" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F39" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G39" s="68" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H39" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="68" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B40" s="69" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C40" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E40" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F40" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G40" s="68" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H40" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="68" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B41" s="69" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C41" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D41" s="68" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E41" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F41" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G41" s="68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H41" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" s="69" t="s">
+        <v>200</v>
+      </c>
+      <c r="C42" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42" s="68" t="s">
         <v>201</v>
       </c>
-      <c r="B42" s="69" t="s">
-        <v>199</v>
-      </c>
-      <c r="C42" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="D42" s="68" t="s">
-        <v>200</v>
-      </c>
       <c r="E42" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F42" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G42" s="68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H42" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B43" s="69" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C43" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D43" s="68" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E43" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F43" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G43" s="68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H43" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="68" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B44" s="68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C44" s="68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E44" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F44" s="68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="68" t="s">
+        <v>209</v>
+      </c>
+      <c r="B45" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="C45" s="68" t="s">
+        <v>206</v>
+      </c>
+      <c r="E45" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="F45" s="68" t="s">
         <v>208</v>
-      </c>
-      <c r="B45" s="68" t="s">
-        <v>204</v>
-      </c>
-      <c r="C45" s="68" t="s">
-        <v>205</v>
-      </c>
-      <c r="E45" s="68" t="s">
-        <v>206</v>
-      </c>
-      <c r="F45" s="68" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="68" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B46" s="68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C46" s="68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E46" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F46" s="68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="68" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B47" s="69" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C47" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E47" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F47" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="B48" s="69" t="s">
         <v>212</v>
       </c>
-      <c r="B48" s="69" t="s">
-        <v>211</v>
-      </c>
       <c r="C48" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E48" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F48" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="68" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B49" s="69" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C49" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E49" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F49" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B50" s="68" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C50" s="68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D50" s="68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E50" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F50" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G50" s="68" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H50" s="68" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="68" t="s">
+        <v>221</v>
+      </c>
+      <c r="B51" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="C51" s="68" t="s">
+        <v>217</v>
+      </c>
+      <c r="D51" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="E51" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="F51" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="G51" s="68" t="s">
+        <v>219</v>
+      </c>
+      <c r="H51" s="68" t="s">
         <v>220</v>
-      </c>
-      <c r="B51" s="68" t="s">
-        <v>215</v>
-      </c>
-      <c r="C51" s="68" t="s">
-        <v>216</v>
-      </c>
-      <c r="D51" s="68" t="s">
-        <v>217</v>
-      </c>
-      <c r="E51" s="68" t="s">
-        <v>134</v>
-      </c>
-      <c r="F51" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="G51" s="68" t="s">
-        <v>218</v>
-      </c>
-      <c r="H51" s="68" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B52" s="68" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C52" s="68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D52" s="68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E52" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F52" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G52" s="68" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H52" s="68" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B53" s="68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C53" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E53" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F53" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G53" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H53" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="B54" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="C54" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E54" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="F54" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="B54" s="68" t="s">
-        <v>223</v>
-      </c>
-      <c r="C54" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="E54" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="F54" s="68" t="s">
-        <v>224</v>
-      </c>
       <c r="G54" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H54" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="68" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B55" s="68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C55" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E55" s="68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F55" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G55" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H55" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="68" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B56" s="69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C56" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E56" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F56" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G56" s="68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H56" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="68" t="s">
+        <v>230</v>
+      </c>
+      <c r="B57" s="69" t="s">
         <v>229</v>
       </c>
-      <c r="B57" s="69" t="s">
-        <v>228</v>
-      </c>
       <c r="C57" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E57" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F57" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G57" s="68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H57" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="68" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B58" s="69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C58" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E58" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F58" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G58" s="68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H58" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="68" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B59" s="68" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C59" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E59" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F59" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G59" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H59" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="68" t="s">
+        <v>234</v>
+      </c>
+      <c r="B60" s="68" t="s">
         <v>233</v>
       </c>
-      <c r="B60" s="68" t="s">
-        <v>232</v>
-      </c>
       <c r="C60" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E60" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F60" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G60" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H60" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="68" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B61" s="68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C61" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E61" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F61" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G61" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H61" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="68" t="s">
+        <v>237</v>
+      </c>
+      <c r="B62" s="68" t="s">
         <v>236</v>
       </c>
-      <c r="B62" s="68" t="s">
-        <v>235</v>
-      </c>
       <c r="C62" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E62" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F62" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G62" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H62" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="68" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B63" s="68" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C63" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E63" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F63" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G63" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H63" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="B64" s="68" t="s">
         <v>239</v>
       </c>
-      <c r="B64" s="68" t="s">
-        <v>238</v>
-      </c>
       <c r="C64" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E64" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F64" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G64" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H64" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="68" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B65" s="69" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C65" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E65" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F65" s="68" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G65" s="68" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H65" s="68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="68" t="s">
+        <v>245</v>
+      </c>
+      <c r="B66" s="69" t="s">
+        <v>242</v>
+      </c>
+      <c r="C66" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E66" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F66" s="68" t="s">
+        <v>243</v>
+      </c>
+      <c r="G66" s="68" t="s">
+        <v>243</v>
+      </c>
+      <c r="H66" s="68" t="s">
         <v>244</v>
-      </c>
-      <c r="B66" s="69" t="s">
-        <v>241</v>
-      </c>
-      <c r="C66" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="E66" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="F66" s="68" t="s">
-        <v>242</v>
-      </c>
-      <c r="G66" s="68" t="s">
-        <v>242</v>
-      </c>
-      <c r="H66" s="68" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="68" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B67" s="69" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C67" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D67" s="68" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E67" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F67" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G67" s="68" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H67" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="B68" s="69" t="s">
+        <v>247</v>
+      </c>
+      <c r="C68" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E68" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="F68" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="G68" s="68" t="s">
         <v>249</v>
       </c>
-      <c r="B68" s="69" t="s">
-        <v>246</v>
-      </c>
-      <c r="C68" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="E68" s="68" t="s">
-        <v>247</v>
-      </c>
-      <c r="F68" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="G68" s="68" t="s">
-        <v>248</v>
-      </c>
       <c r="H68" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="68" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B69" s="69" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C69" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D69" s="68" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E69" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F69" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G69" s="68" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H69" s="68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="B70" s="69" t="s">
+        <v>252</v>
+      </c>
+      <c r="C70" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E70" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="F70" s="68" t="s">
+        <v>253</v>
+      </c>
+      <c r="G70" s="68" t="s">
+        <v>253</v>
+      </c>
+      <c r="H70" s="68" t="s">
         <v>254</v>
-      </c>
-      <c r="B70" s="69" t="s">
-        <v>251</v>
-      </c>
-      <c r="C70" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="E70" s="68" t="s">
-        <v>134</v>
-      </c>
-      <c r="F70" s="68" t="s">
-        <v>252</v>
-      </c>
-      <c r="G70" s="68" t="s">
-        <v>252</v>
-      </c>
-      <c r="H70" s="68" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="68" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B71" s="69" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C71" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D71" s="68" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E71" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F71" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G71" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H71" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="B72" s="69" t="s">
         <v>257</v>
       </c>
-      <c r="B72" s="69" t="s">
-        <v>256</v>
-      </c>
       <c r="C72" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D72" s="68" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E72" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F72" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G72" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H72" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="68" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B73" s="68" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C73" s="68" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E73" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F73" s="68" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G73" s="68" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H73" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="B74" s="68" t="s">
+        <v>260</v>
+      </c>
+      <c r="C74" s="68" t="s">
+        <v>261</v>
+      </c>
+      <c r="E74" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F74" s="68" t="s">
+        <v>262</v>
+      </c>
+      <c r="G74" s="68" t="s">
+        <v>262</v>
+      </c>
+      <c r="H74" s="68" t="s">
         <v>263</v>
-      </c>
-      <c r="B74" s="68" t="s">
-        <v>259</v>
-      </c>
-      <c r="C74" s="68" t="s">
-        <v>260</v>
-      </c>
-      <c r="E74" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="F74" s="68" t="s">
-        <v>261</v>
-      </c>
-      <c r="G74" s="68" t="s">
-        <v>261</v>
-      </c>
-      <c r="H74" s="68" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="68" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B75" s="68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C75" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E75" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F75" s="68" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G75" s="68" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H75" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="B76" s="68" t="s">
+        <v>266</v>
+      </c>
+      <c r="C76" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E76" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F76" s="68" t="s">
         <v>267</v>
       </c>
-      <c r="B76" s="68" t="s">
-        <v>265</v>
-      </c>
-      <c r="C76" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="E76" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="F76" s="68" t="s">
-        <v>266</v>
-      </c>
       <c r="G76" s="68" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H76" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="68" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B77" s="68" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C77" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E77" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F77" s="68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G77" s="68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H77" s="68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="B78" s="68" t="s">
         <v>270</v>
       </c>
-      <c r="B78" s="68" t="s">
-        <v>269</v>
-      </c>
       <c r="C78" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E78" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F78" s="68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G78" s="68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H78" s="68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B79" s="68" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C79" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E79" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F79" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G79" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H79" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="68" t="s">
+        <v>274</v>
+      </c>
+      <c r="B80" s="68" t="s">
         <v>273</v>
       </c>
-      <c r="B80" s="68" t="s">
-        <v>272</v>
-      </c>
       <c r="C80" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E80" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F80" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G80" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H80" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B81" s="68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C81" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E81" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F81" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G81" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H81" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="68" t="s">
+        <v>277</v>
+      </c>
+      <c r="B82" s="68" t="s">
         <v>276</v>
       </c>
-      <c r="B82" s="68" t="s">
-        <v>275</v>
-      </c>
       <c r="C82" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E82" s="68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F82" s="68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G82" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H82" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="68" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B83" s="69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C83" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E83" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F83" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="68" t="s">
+        <v>282</v>
+      </c>
+      <c r="B84" s="69" t="s">
+        <v>280</v>
+      </c>
+      <c r="C84" s="68" t="s">
         <v>281</v>
       </c>
-      <c r="B84" s="69" t="s">
-        <v>279</v>
-      </c>
-      <c r="C84" s="68" t="s">
-        <v>280</v>
-      </c>
       <c r="E84" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F84" s="68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="68" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B85" s="69" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C85" s="68" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E85" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F85" s="68" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G85" s="68" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H85" s="68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="B86" s="69" t="s">
+        <v>284</v>
+      </c>
+      <c r="C86" s="68" t="s">
         <v>285</v>
       </c>
-      <c r="B86" s="69" t="s">
-        <v>283</v>
-      </c>
-      <c r="C86" s="68" t="s">
-        <v>284</v>
-      </c>
       <c r="E86" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F86" s="68" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G86" s="68" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H86" s="68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="68" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B87" s="68" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C87" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E87" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F87" s="68" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G87" s="68" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H87" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="68" t="s">
+        <v>289</v>
+      </c>
+      <c r="B88" s="68" t="s">
         <v>288</v>
       </c>
-      <c r="B88" s="68" t="s">
-        <v>287</v>
-      </c>
       <c r="C88" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E88" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F88" s="68" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G88" s="68" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H88" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="68" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B89" s="68" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C89" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E89" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F89" s="68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G89" s="68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H89" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="B90" s="68" t="s">
         <v>291</v>
       </c>
-      <c r="B90" s="68" t="s">
-        <v>290</v>
-      </c>
       <c r="C90" s="68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E90" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F90" s="68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G90" s="68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H90" s="68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="68" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B91" s="68" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C91" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E91" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F91" s="68" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G91" s="68" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H91" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="68" t="s">
+        <v>296</v>
+      </c>
+      <c r="B92" s="68" t="s">
+        <v>294</v>
+      </c>
+      <c r="C92" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="E92" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F92" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="B92" s="68" t="s">
-        <v>293</v>
-      </c>
-      <c r="C92" s="68" t="s">
-        <v>167</v>
-      </c>
-      <c r="E92" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="F92" s="68" t="s">
-        <v>294</v>
-      </c>
       <c r="G92" s="68" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H92" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="68" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B93" s="68" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C93" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E93" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F93" s="68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G93" s="68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H93" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="68" t="s">
+        <v>299</v>
+      </c>
+      <c r="B94" s="68" t="s">
         <v>298</v>
       </c>
-      <c r="B94" s="68" t="s">
-        <v>297</v>
-      </c>
       <c r="C94" s="68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E94" s="68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F94" s="68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G94" s="68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H94" s="68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4411,7 +4344,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC397FCC-74C1-4D09-ACC0-E463BF5527EB}">
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="87.83203125" customWidth="1"/>
@@ -4424,7 +4357,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B1" s="72" t="s">
         <v>0</v>
@@ -4440,22 +4373,22 @@
         <v>2</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D2" s="40" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C3" s="15">
         <v>95</v>
@@ -4467,10 +4400,10 @@
     </row>
     <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C4" s="15">
         <v>80</v>
@@ -4483,15 +4416,9 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="C5" s="4">
-        <v>92</v>
-      </c>
-      <c r="D5" s="4">
-        <v>73</v>
-      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4499,7 +4426,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C6" s="1">
         <v>95</v>
@@ -4514,7 +4441,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C7" s="4">
         <v>95</v>
@@ -4528,7 +4455,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C8" s="4">
         <v>91</v>
@@ -4541,186 +4468,138 @@
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="C9" s="4">
-        <v>96</v>
-      </c>
-      <c r="D9" s="59">
-        <v>73</v>
-      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="59"/>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="C10" s="4">
-        <v>93</v>
-      </c>
-      <c r="D10" s="4">
-        <v>74</v>
-      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C11" s="4">
-        <v>93</v>
-      </c>
-      <c r="D11" s="4">
-        <v>74</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="59"/>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="59"/>
+        <v>15</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="C13" s="1">
-        <v>94</v>
-      </c>
-      <c r="D13" s="4">
-        <v>76</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="C14" s="4">
-        <v>95</v>
-      </c>
-      <c r="D14" s="4">
-        <v>76</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="C15" s="1">
-        <v>95</v>
-      </c>
-      <c r="D15" s="4">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="43" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="C17" s="7">
-        <v>96</v>
-      </c>
-      <c r="D17" s="7">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="38" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="D18" s="40" t="s">
+      <c r="B19" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="C19" s="40" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
+      <c r="D19" s="40" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="44" t="s">
-        <v>372</v>
-      </c>
-      <c r="C19" s="27">
+      <c r="B20" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="C20" s="27">
         <v>85</v>
       </c>
-      <c r="D19" s="55">
+      <c r="D20" s="55">
         <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="C20" s="23">
-        <v>90</v>
-      </c>
-      <c r="D20" s="57">
-        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="57"/>
+        <v>24</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C21" s="23">
+        <v>90</v>
+      </c>
+      <c r="D21" s="57">
+        <v>59</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="C22" s="10">
-        <v>90</v>
-      </c>
-      <c r="D22" s="57">
-        <v>69</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="57"/>
     </row>
     <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C23" s="10">
         <v>90</v>
@@ -4731,528 +4610,490 @@
     </row>
     <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="C24" s="10">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D24" s="57">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="C25" s="10">
-        <v>91</v>
-      </c>
-      <c r="D25" s="57">
-        <v>55</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="57"/>
     </row>
     <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="C26" s="10">
-        <v>93</v>
-      </c>
-      <c r="D26" s="57">
-        <v>59</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="57"/>
     </row>
     <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="C27" s="10">
-        <v>92</v>
-      </c>
-      <c r="D27" s="57">
-        <v>56</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="57"/>
     </row>
     <row r="28" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="57"/>
+    </row>
+    <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="C28" s="10">
-        <v>93</v>
-      </c>
-      <c r="D28" s="57">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
+      <c r="B29" s="6"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="57"/>
+    </row>
+    <row r="30" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="39" t="s">
-        <v>356</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="D29" s="40" t="s">
+      <c r="B30" s="39" t="s">
+        <v>359</v>
+      </c>
+      <c r="C30" s="40" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="57"/>
+      <c r="D30" s="40" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="31" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="B31" s="4"/>
       <c r="C31" s="47"/>
       <c r="D31" s="57"/>
     </row>
     <row r="32" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="47"/>
       <c r="D32" s="57"/>
     </row>
-    <row r="33" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="47"/>
-      <c r="D33" s="24" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="29" t="s">
+      <c r="D33" s="57"/>
+    </row>
+    <row r="34" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="54"/>
+    </row>
+    <row r="35" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="D34" s="40" t="s">
+      <c r="B35" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="C35" s="40" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="4">
-        <v>20000</v>
-      </c>
-      <c r="C35" s="48">
-        <v>90</v>
-      </c>
-      <c r="D35" s="64">
-        <v>34</v>
+      <c r="D35" s="40" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="4">
+        <v>20000</v>
+      </c>
+      <c r="C36" s="48">
+        <v>90</v>
+      </c>
+      <c r="D36" s="64">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="4">
-        <v>19330</v>
-      </c>
-      <c r="C36" s="4">
-        <v>92</v>
-      </c>
-      <c r="D36" s="64">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="64"/>
+    </row>
+    <row r="38" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B38" s="4">
         <v>10000</v>
-      </c>
-      <c r="C37" s="4">
-        <v>90</v>
-      </c>
-      <c r="D37" s="60">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="4">
-        <v>2400</v>
       </c>
       <c r="C38" s="4">
         <v>90</v>
       </c>
       <c r="D38" s="60">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="4">
+        <v>2400</v>
+      </c>
+      <c r="C39" s="4">
+        <v>90</v>
+      </c>
+      <c r="D39" s="60">
         <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="15">
-        <v>2250</v>
-      </c>
-      <c r="C39" s="15">
-        <v>96</v>
-      </c>
-      <c r="D39" s="15">
-        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+    </row>
+    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="15"/>
-    </row>
-    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="4">
-        <v>1550</v>
-      </c>
-      <c r="C41" s="4">
-        <v>88</v>
-      </c>
-      <c r="D41" s="4">
-        <v>41</v>
-      </c>
+      <c r="B41" s="45"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="15"/>
     </row>
     <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" s="4">
-        <v>400</v>
-      </c>
-      <c r="C42" s="1">
-        <v>97</v>
+        <v>1550</v>
+      </c>
+      <c r="C42" s="4">
+        <v>88</v>
       </c>
       <c r="D42" s="4">
-        <v>74</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="4">
+        <v>400</v>
+      </c>
+      <c r="C43" s="1">
+        <v>97</v>
+      </c>
+      <c r="D43" s="4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="29" t="s">
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+    </row>
+    <row r="45" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="C44" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="D44" s="40" t="s">
+      <c r="B45" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="C45" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="D45" s="40" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="13" t="s">
+    <row r="46" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="C45" s="33">
+      <c r="B46" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C46" s="33">
         <v>98</v>
       </c>
-      <c r="D45" s="24" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="13" t="s">
+      <c r="D46" s="24" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="C46" s="49">
+      <c r="B47" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C47" s="49">
         <v>98</v>
       </c>
-      <c r="D46" s="24" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="8" t="s">
+      <c r="D47" s="24" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="C47" s="23">
+      <c r="B48" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C48" s="23">
         <v>90</v>
       </c>
-      <c r="D47" s="57" t="s">
-        <v>317</v>
-      </c>
-      <c r="E47" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="C48" s="23">
-        <v>98</v>
-      </c>
-      <c r="D48" s="59" t="s">
-        <v>332</v>
+      <c r="D48" s="57" t="s">
+        <v>318</v>
+      </c>
+      <c r="E48" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C49" s="23">
+        <v>98</v>
+      </c>
+      <c r="D49" s="59" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="57"/>
-    </row>
-    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="8" t="s">
+      <c r="B50" s="4"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="57"/>
+    </row>
+    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="C50" s="23">
+      <c r="B51" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C51" s="23">
         <v>99</v>
       </c>
-      <c r="D50" s="24" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="8" t="s">
+      <c r="D51" s="24" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="C51" s="32">
+      <c r="B52" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C52" s="32">
         <v>98</v>
       </c>
-      <c r="D51" s="24" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="8" t="s">
+      <c r="D52" s="24" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B53" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C53" s="23">
+        <v>99</v>
+      </c>
+      <c r="D53" s="24"/>
+    </row>
+    <row r="54" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="C54" s="31">
+        <v>99</v>
+      </c>
+      <c r="D54" s="24" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="C52" s="23">
-        <v>99</v>
-      </c>
-      <c r="D52" s="24"/>
-    </row>
-    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>359</v>
-      </c>
-      <c r="C53" s="31">
-        <v>99</v>
-      </c>
-      <c r="D53" s="24" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A54" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="C54" s="23">
-        <v>98</v>
-      </c>
-      <c r="D54" s="59" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>361</v>
       </c>
       <c r="C55" s="23">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C56" s="23">
+        <v>98</v>
+      </c>
+      <c r="D56" s="59" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="C56" s="23">
+      <c r="B57" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C57" s="23">
         <v>99</v>
       </c>
-      <c r="D56" s="59" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="9" t="s">
+      <c r="D57" s="59" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C57" s="23">
+      <c r="B58" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C58" s="23">
         <v>98</v>
       </c>
-      <c r="D57" s="24" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
+      <c r="D58" s="24" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="55"/>
-    </row>
-    <row r="59" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
+      <c r="B59" s="4"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="55"/>
+    </row>
+    <row r="60" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="57"/>
-    </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="23"/>
       <c r="D60" s="57"/>
     </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="23"/>
       <c r="D61" s="57"/>
     </row>
-    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="57"/>
+    </row>
+    <row r="63" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="57"/>
-    </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="B63" s="4"/>
-      <c r="C63" s="23"/>
+      <c r="C63" s="32"/>
       <c r="D63" s="57"/>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="57"/>
+    </row>
+    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="53"/>
-      <c r="D64" s="57"/>
-    </row>
-    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="3" t="s">
+      <c r="B65" s="4"/>
+      <c r="C65" s="53"/>
+      <c r="D65" s="57"/>
+    </row>
+    <row r="66" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="52"/>
-      <c r="D65" s="57"/>
-    </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="28" t="s">
+      <c r="B66" s="6"/>
+      <c r="C66" s="52"/>
+      <c r="D66" s="57"/>
+    </row>
+    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B66" s="20" t="s">
+      <c r="B67" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C66" s="30" t="s">
-        <v>337</v>
-      </c>
-      <c r="D66" s="67"/>
-    </row>
-    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A67" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B67" s="24"/>
-      <c r="C67" s="10"/>
-      <c r="D67" s="57"/>
+      <c r="C67" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="D67" s="67"/>
     </row>
     <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B68" s="24"/>
       <c r="C68" s="10"/>
@@ -5260,7 +5101,7 @@
     </row>
     <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B69" s="24"/>
       <c r="C69" s="10"/>
@@ -5268,7 +5109,7 @@
     </row>
     <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B70" s="24"/>
       <c r="C70" s="10"/>
@@ -5276,7 +5117,7 @@
     </row>
     <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71" s="24"/>
       <c r="C71" s="10"/>
@@ -5284,7 +5125,7 @@
     </row>
     <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B72" s="24"/>
       <c r="C72" s="10"/>
@@ -5292,7 +5133,7 @@
     </row>
     <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73" s="24"/>
       <c r="C73" s="10"/>
@@ -5300,7 +5141,7 @@
     </row>
     <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B74" s="24"/>
       <c r="C74" s="10"/>
@@ -5308,7 +5149,7 @@
     </row>
     <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75" s="24"/>
       <c r="C75" s="10"/>
@@ -5316,7 +5157,7 @@
     </row>
     <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B76" s="24"/>
       <c r="C76" s="10"/>
@@ -5324,7 +5165,7 @@
     </row>
     <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B77" s="24"/>
       <c r="C77" s="10"/>
@@ -5332,7 +5173,7 @@
     </row>
     <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B78" s="24"/>
       <c r="C78" s="10"/>
@@ -5340,7 +5181,7 @@
     </row>
     <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B79" s="24"/>
       <c r="C79" s="10"/>
@@ -5348,47 +5189,47 @@
     </row>
     <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="24"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="57"/>
+    </row>
+    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="33"/>
-      <c r="C80" s="23"/>
-      <c r="D80" s="57"/>
-    </row>
-    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A81" s="43" t="s">
+      <c r="B81" s="33"/>
+      <c r="C81" s="23"/>
+      <c r="D81" s="57"/>
+    </row>
+    <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A82" s="43" t="s">
         <v>86</v>
-      </c>
-      <c r="B81" s="24"/>
-      <c r="C81" s="32"/>
-      <c r="D81" s="57"/>
-    </row>
-    <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A82" s="51" t="s">
-        <v>87</v>
       </c>
       <c r="B82" s="24"/>
       <c r="C82" s="32"/>
       <c r="D82" s="57"/>
     </row>
     <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" s="22" t="s">
+      <c r="A83" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="24"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="57"/>
+    </row>
+    <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A84" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B83" s="33"/>
-      <c r="C83" s="23"/>
-      <c r="D83" s="57"/>
-    </row>
-    <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A84" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B84" s="24"/>
-      <c r="C84" s="10"/>
+      <c r="B84" s="33"/>
+      <c r="C84" s="23"/>
       <c r="D84" s="57"/>
     </row>
     <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B85" s="24"/>
       <c r="C85" s="10"/>
@@ -5396,15 +5237,15 @@
     </row>
     <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B86" s="10"/>
+        <v>90</v>
+      </c>
+      <c r="B86" s="24"/>
       <c r="C86" s="10"/>
       <c r="D86" s="57"/>
     </row>
     <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
@@ -5412,15 +5253,15 @@
     </row>
     <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B88" s="24"/>
+        <v>92</v>
+      </c>
+      <c r="B88" s="10"/>
       <c r="C88" s="10"/>
       <c r="D88" s="57"/>
     </row>
     <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B89" s="24"/>
       <c r="C89" s="10"/>
@@ -5428,7 +5269,7 @@
     </row>
     <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B90" s="24"/>
       <c r="C90" s="10"/>
@@ -5436,99 +5277,67 @@
     </row>
     <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B91" s="10">
-        <v>80000</v>
-      </c>
-      <c r="C91" s="10">
-        <v>55</v>
-      </c>
-      <c r="D91" s="57">
-        <v>35</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="B91" s="24"/>
+      <c r="C91" s="10"/>
+      <c r="D91" s="57"/>
     </row>
     <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B92" s="24">
-        <v>80000</v>
-      </c>
-      <c r="C92" s="10">
-        <v>60</v>
-      </c>
-      <c r="D92" s="57">
-        <v>37</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="B92" s="10"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="57"/>
     </row>
     <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B93" s="70">
-        <v>51000</v>
-      </c>
-      <c r="C93" s="57"/>
-      <c r="D93" s="71" t="s">
-        <v>352</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="B93" s="24"/>
+      <c r="C93" s="24"/>
+      <c r="D93" s="57"/>
     </row>
     <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B94" s="24">
-        <v>32000</v>
-      </c>
-      <c r="C94" s="76">
-        <v>56</v>
-      </c>
-      <c r="D94" s="56">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="B94" s="24"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="57"/>
     </row>
     <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B95" s="24">
-        <v>32000</v>
-      </c>
-      <c r="C95" s="26">
-        <v>57</v>
-      </c>
-      <c r="D95" s="56">
-        <v>58</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="B95" s="24"/>
+      <c r="C95" s="10"/>
+      <c r="D95" s="57"/>
     </row>
     <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B96" s="34"/>
-      <c r="C96" s="35"/>
-      <c r="D96" s="10"/>
+      <c r="B96" s="24"/>
+      <c r="C96" s="26"/>
+      <c r="D96" s="56"/>
     </row>
     <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B97" s="75">
-        <v>26000</v>
-      </c>
-      <c r="C97" s="70"/>
-      <c r="D97" s="70" t="s">
-        <v>388</v>
-      </c>
+      <c r="B97" s="34"/>
+      <c r="C97" s="35"/>
+      <c r="D97" s="10"/>
     </row>
     <row r="98" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B98" s="75"/>
-      <c r="C98" s="70"/>
-      <c r="D98" s="70"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="10"/>
     </row>
     <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
@@ -5542,7 +5351,7 @@
       <c r="A100" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B100" s="16"/>
+      <c r="B100" s="24"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
     </row>
@@ -5550,7 +5359,7 @@
       <c r="A101" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B101" s="10"/>
+      <c r="B101" s="16"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
     </row>
@@ -5558,13 +5367,17 @@
       <c r="A102" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B102" s="24"/>
+      <c r="B102" s="10"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
     </row>
-    <row r="103" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I103" s="11"/>
-      <c r="J103" s="11"/>
+    <row r="103" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B103" s="24"/>
+      <c r="C103" s="10"/>
+      <c r="D103" s="10"/>
     </row>
     <row r="104" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I104" s="11"/>
@@ -5577,6 +5390,10 @@
     <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I106" s="11"/>
       <c r="J106" s="11"/>
+    </row>
+    <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I107" s="11"/>
+      <c r="J107" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5601,10 +5418,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>1</v>
@@ -5616,21 +5433,21 @@
         <v>2</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D2" s="40" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C3" s="59">
         <v>91</v>
@@ -5641,10 +5458,10 @@
     </row>
     <row r="4" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C4" s="4">
         <v>70</v>
@@ -5653,7 +5470,7 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5669,7 +5486,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C6" s="4">
         <v>94</v>
@@ -5683,7 +5500,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C7" s="59">
         <v>96</v>
@@ -5718,97 +5535,91 @@
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="59"/>
       <c r="D11" s="59"/>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="59"/>
+        <v>15</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="59"/>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="59"/>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="B14" s="1"/>
       <c r="C14" s="4"/>
       <c r="D14" s="59"/>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="59"/>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="46"/>
+      <c r="A16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1"/>
       <c r="C16" s="4"/>
       <c r="D16" s="59"/>
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="46"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="59"/>
+    </row>
+    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="59"/>
-    </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="38" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="59"/>
+    </row>
+    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B19" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="D18" s="40" t="s">
+      <c r="C19" s="40" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
+      <c r="D19" s="40" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="27" t="s">
-        <v>350</v>
-      </c>
-      <c r="C19" s="55">
+      <c r="B20" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="C20" s="55">
         <v>92</v>
-      </c>
-      <c r="D19" s="59">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="C20" s="57">
-        <v>95</v>
       </c>
       <c r="D20" s="59">
         <v>63</v>
@@ -5816,62 +5627,68 @@
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="59"/>
+        <v>24</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="C21" s="57">
+        <v>95</v>
+      </c>
+      <c r="D21" s="59">
+        <v>63</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="C22" s="57">
-        <v>93</v>
-      </c>
-      <c r="D22" s="59">
-        <v>64</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="59"/>
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>349</v>
       </c>
       <c r="C23" s="57">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D23" s="59">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="59"/>
-      <c r="F24" t="s">
-        <v>351</v>
+        <v>27</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="C24" s="57">
+        <v>92</v>
+      </c>
+      <c r="D24" s="59">
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="57"/>
       <c r="D25" s="59"/>
+      <c r="F25" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="57"/>
@@ -5879,7 +5696,7 @@
     </row>
     <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="57"/>
@@ -5887,37 +5704,37 @@
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="57"/>
       <c r="D28" s="59"/>
     </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
+    <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="10"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="59"/>
+    </row>
+    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B30" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="D29" s="40" t="s">
+      <c r="C30" s="40" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="47"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="59"/>
+      <c r="D30" s="40" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="47"/>
       <c r="C31" s="57"/>
@@ -5925,421 +5742,421 @@
     </row>
     <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="47"/>
       <c r="C32" s="57"/>
       <c r="D32" s="59"/>
     </row>
-    <row r="33" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="47"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="59"/>
+    </row>
+    <row r="34" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="59"/>
-    </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="29" t="s">
+      <c r="B34" s="47"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="59"/>
+    </row>
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B35" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="D34" s="40" t="s">
+      <c r="C35" s="40" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="48">
-        <v>26000</v>
-      </c>
-      <c r="C35" s="64">
-        <v>90</v>
-      </c>
-      <c r="D35" s="59">
-        <v>38</v>
+      <c r="D35" s="40" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="48">
+        <v>26000</v>
+      </c>
+      <c r="C36" s="64">
+        <v>90</v>
+      </c>
+      <c r="D36" s="59">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B37" s="4">
         <v>25400</v>
       </c>
-      <c r="C36" s="64">
+      <c r="C37" s="64">
         <v>93</v>
-      </c>
-      <c r="D36" s="59">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="4">
-        <v>13300</v>
-      </c>
-      <c r="C37" s="60">
-        <v>95</v>
       </c>
       <c r="D37" s="59">
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" s="4">
-        <v>3200</v>
+        <v>13300</v>
       </c>
       <c r="C38" s="60">
         <v>95</v>
       </c>
       <c r="D38" s="59">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="4">
+        <v>3200</v>
+      </c>
+      <c r="C39" s="60">
+        <v>95</v>
+      </c>
+      <c r="D39" s="59">
         <v>38</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="59"/>
     </row>
     <row r="40" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="45"/>
+        <v>43</v>
+      </c>
+      <c r="B40" s="15"/>
       <c r="C40" s="15"/>
       <c r="D40" s="59"/>
     </row>
     <row r="41" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="4">
-        <v>1810</v>
-      </c>
-      <c r="C41" s="4">
-        <v>95</v>
-      </c>
-      <c r="D41" s="59">
-        <v>68</v>
-      </c>
+      <c r="A41" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="45"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="59"/>
     </row>
     <row r="42" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="1">
-        <v>460</v>
+        <v>45</v>
+      </c>
+      <c r="B42" s="4">
+        <v>1810</v>
       </c>
       <c r="C42" s="4">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D42" s="59">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="1">
+        <v>460</v>
+      </c>
+      <c r="C43" s="4">
+        <v>93</v>
+      </c>
+      <c r="D43" s="59">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="59"/>
-    </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="29" t="s">
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="59"/>
+    </row>
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B45" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C44" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="D44" s="40" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="13" t="s">
+      <c r="C45" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="D45" s="40" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="C45" s="24">
-        <v>98</v>
-      </c>
-      <c r="D45" s="59" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B46" s="49" t="s">
-        <v>321</v>
+      <c r="B46" s="33" t="s">
+        <v>319</v>
       </c>
       <c r="C46" s="24">
         <v>98</v>
       </c>
       <c r="D46" s="59" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="8" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="49" t="s">
+        <v>322</v>
+      </c>
+      <c r="C47" s="24">
+        <v>98</v>
+      </c>
+      <c r="D47" s="59" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="C47" s="57">
-        <v>96</v>
-      </c>
-      <c r="D47" s="59" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B48" s="49" t="s">
-        <v>320</v>
+      <c r="B48" s="23" t="s">
+        <v>324</v>
       </c>
       <c r="C48" s="57">
         <v>96</v>
       </c>
       <c r="D48" s="59" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="49" t="s">
+        <v>321</v>
+      </c>
+      <c r="C49" s="57">
+        <v>96</v>
+      </c>
+      <c r="D49" s="59" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B49" s="23"/>
-      <c r="C49" s="57"/>
-      <c r="D49" s="59"/>
-    </row>
-    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="8" t="s">
+      <c r="B50" s="23"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="59"/>
+    </row>
+    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="C50" s="55">
+      <c r="B51" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="C51" s="55">
         <v>98</v>
       </c>
-      <c r="D50" s="59" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="8" t="s">
+      <c r="D51" s="59" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="32" t="s">
-        <v>334</v>
-      </c>
-      <c r="C51" s="57">
+      <c r="B52" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="C52" s="57">
         <v>98</v>
       </c>
-      <c r="D51" s="59" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="8" t="s">
+      <c r="D52" s="59" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="58" t="s">
+      <c r="B53" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="C53" s="57">
+        <v>99</v>
+      </c>
+      <c r="D53" s="59" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="31" t="s">
         <v>331</v>
       </c>
-      <c r="C52" s="57">
+      <c r="C54" s="65">
         <v>99</v>
       </c>
-      <c r="D52" s="59" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B53" s="31" t="s">
-        <v>330</v>
-      </c>
-      <c r="C53" s="65">
-        <v>99</v>
-      </c>
-      <c r="D53" s="59" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A54" s="18" t="s">
+      <c r="D54" s="59" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="C54" s="66">
-        <v>98</v>
-      </c>
-      <c r="D54" s="59" t="s">
+      <c r="B55" s="23" t="s">
         <v>325</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B55" s="23" t="s">
-        <v>326</v>
       </c>
       <c r="C55" s="66">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="23" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="19" t="s">
+      <c r="C56" s="66">
+        <v>98</v>
+      </c>
+      <c r="D56" s="59" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="C56" s="66">
+      <c r="B57" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="C57" s="66">
         <v>96</v>
       </c>
-      <c r="D56" s="59" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="9" t="s">
+      <c r="D57" s="59" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B57" s="25" t="s">
-        <v>319</v>
-      </c>
-      <c r="C57" s="57">
+      <c r="B58" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="C58" s="57">
         <v>96</v>
       </c>
-      <c r="D57" s="59" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
+      <c r="D58" s="59" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B58" s="23"/>
-      <c r="C58" s="55"/>
-      <c r="D58" s="59"/>
-    </row>
-    <row r="59" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
+      <c r="B59" s="23"/>
+      <c r="C59" s="55"/>
+      <c r="D59" s="59"/>
+    </row>
+    <row r="60" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B59" s="23"/>
-      <c r="C59" s="57"/>
-      <c r="D59" s="59"/>
-    </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="B60" s="23"/>
       <c r="C60" s="57"/>
       <c r="D60" s="59"/>
     </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" s="23"/>
       <c r="C61" s="57"/>
       <c r="D61" s="59"/>
     </row>
-    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B62" s="32"/>
+        <v>65</v>
+      </c>
+      <c r="B62" s="23"/>
       <c r="C62" s="57"/>
       <c r="D62" s="59"/>
     </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B63" s="23"/>
+        <v>66</v>
+      </c>
+      <c r="B63" s="32"/>
       <c r="C63" s="57"/>
       <c r="D63" s="59"/>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B64" s="53"/>
+        <v>67</v>
+      </c>
+      <c r="B64" s="23"/>
       <c r="C64" s="57"/>
       <c r="D64" s="59"/>
     </row>
-    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B65" s="52"/>
+    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65" s="53"/>
       <c r="C65" s="57"/>
       <c r="D65" s="59"/>
     </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="28" t="s">
+    <row r="66" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" s="52"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="59"/>
+    </row>
+    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B66" s="30" t="s">
+      <c r="B67" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C66" s="67" t="s">
-        <v>337</v>
-      </c>
-      <c r="D66" s="67" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A67" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B67" s="10"/>
-      <c r="C67" s="57"/>
-      <c r="D67" s="57"/>
+      <c r="C67" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="D67" s="67" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B68" s="10"/>
       <c r="C68" s="57"/>
@@ -6347,7 +6164,7 @@
     </row>
     <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B69" s="10"/>
       <c r="C69" s="57"/>
@@ -6355,7 +6172,7 @@
     </row>
     <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B70" s="10"/>
       <c r="C70" s="57"/>
@@ -6363,7 +6180,7 @@
     </row>
     <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71" s="10"/>
       <c r="C71" s="57"/>
@@ -6371,7 +6188,7 @@
     </row>
     <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B72" s="10"/>
       <c r="C72" s="57"/>
@@ -6379,7 +6196,7 @@
     </row>
     <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73" s="10"/>
       <c r="C73" s="57"/>
@@ -6387,17 +6204,15 @@
     </row>
     <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B74" s="10">
-        <v>1536</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="B74" s="10"/>
       <c r="C74" s="57"/>
       <c r="D74" s="57"/>
     </row>
     <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75" s="10"/>
       <c r="C75" s="57"/>
@@ -6405,7 +6220,7 @@
     </row>
     <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B76" s="10"/>
       <c r="C76" s="57"/>
@@ -6413,7 +6228,7 @@
     </row>
     <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="57"/>
@@ -6421,7 +6236,7 @@
     </row>
     <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B78" s="10"/>
       <c r="C78" s="57"/>
@@ -6429,7 +6244,7 @@
     </row>
     <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B79" s="10"/>
       <c r="C79" s="57"/>
@@ -6437,47 +6252,47 @@
     </row>
     <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B80" s="23"/>
+        <v>84</v>
+      </c>
+      <c r="B80" s="10"/>
       <c r="C80" s="57"/>
       <c r="D80" s="57"/>
     </row>
     <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A81" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="B81" s="32"/>
+      <c r="A81" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" s="23"/>
       <c r="C81" s="57"/>
       <c r="D81" s="57"/>
     </row>
     <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A82" s="51" t="s">
-        <v>87</v>
+      <c r="A82" s="43" t="s">
+        <v>86</v>
       </c>
       <c r="B82" s="32"/>
       <c r="C82" s="57"/>
       <c r="D82" s="57"/>
     </row>
     <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B83" s="23"/>
+      <c r="A83" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="32"/>
       <c r="C83" s="57"/>
       <c r="D83" s="57"/>
     </row>
     <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A84" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B84" s="10"/>
+      <c r="A84" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" s="23"/>
       <c r="C84" s="57"/>
       <c r="D84" s="57"/>
     </row>
     <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B85" s="10"/>
       <c r="C85" s="57"/>
@@ -6485,35 +6300,39 @@
     </row>
     <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B86" s="74" t="s">
-        <v>381</v>
-      </c>
-      <c r="C86" s="71"/>
-      <c r="D86" s="71"/>
+        <v>90</v>
+      </c>
+      <c r="B86" s="10"/>
+      <c r="C86" s="57"/>
+      <c r="D86" s="57"/>
     </row>
     <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B87" s="74" t="s">
-        <v>382</v>
+        <v>91</v>
+      </c>
+      <c r="B87" s="70" t="s">
+        <v>353</v>
       </c>
       <c r="C87" s="71"/>
-      <c r="D87" s="71"/>
+      <c r="D87" s="71" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B88" s="10"/>
-      <c r="C88" s="57"/>
-      <c r="D88" s="57"/>
+        <v>92</v>
+      </c>
+      <c r="B88" s="70" t="s">
+        <v>353</v>
+      </c>
+      <c r="C88" s="71"/>
+      <c r="D88" s="71" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="57"/>
@@ -6521,7 +6340,7 @@
     </row>
     <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="57"/>
@@ -6529,55 +6348,51 @@
     </row>
     <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B91" s="10">
-        <v>96000</v>
-      </c>
-      <c r="C91" s="57">
-        <v>50</v>
-      </c>
-      <c r="D91" s="57">
-        <v>35</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="B91" s="10"/>
+      <c r="C91" s="57"/>
+      <c r="D91" s="57"/>
     </row>
     <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B92" s="10">
         <v>96000</v>
       </c>
       <c r="C92" s="57">
-        <v>55</v>
-      </c>
-      <c r="D92" s="57">
-        <v>35</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D92" s="57"/>
     </row>
     <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="70">
-        <v>51000</v>
-      </c>
-      <c r="C93" s="57"/>
-      <c r="D93" s="71" t="s">
-        <v>352</v>
-      </c>
+      <c r="B93" s="10">
+        <v>96000</v>
+      </c>
+      <c r="C93" s="57">
+        <v>55</v>
+      </c>
+      <c r="D93" s="57"/>
     </row>
     <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B94" s="77"/>
-      <c r="C94" s="56"/>
-      <c r="D94" s="71"/>
+      <c r="B94" s="70">
+        <v>51000</v>
+      </c>
+      <c r="C94" s="57"/>
+      <c r="D94" s="71" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>390</v>
+        <v>100</v>
       </c>
       <c r="B95" s="26"/>
       <c r="C95" s="56"/>
@@ -6585,7 +6400,7 @@
     </row>
     <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B96" s="35"/>
       <c r="C96" s="10"/>
@@ -6593,7 +6408,7 @@
     </row>
     <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
@@ -6601,7 +6416,7 @@
     </row>
     <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B98" s="10">
         <v>1200</v>
@@ -6615,7 +6430,7 @@
     </row>
     <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
@@ -6623,7 +6438,7 @@
     </row>
     <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
@@ -6631,7 +6446,7 @@
     </row>
     <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
@@ -6639,7 +6454,7 @@
     </row>
     <row r="102" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
@@ -6679,10 +6494,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A1" s="50" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>1</v>
@@ -6737,10 +6552,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C8" s="60" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -6748,10 +6563,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6850,10 +6665,10 @@
         <v>24</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6868,10 +6683,10 @@
         <v>26</v>
       </c>
       <c r="B25" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C25" s="57" t="s">
         <v>305</v>
-      </c>
-      <c r="C25" s="57" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -6879,10 +6694,10 @@
         <v>27</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6981,10 +6796,10 @@
         <v>41</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -6992,10 +6807,10 @@
         <v>42</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -7024,10 +6839,10 @@
         <v>46</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -7043,20 +6858,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010092711BC64AAEC84E9EF800276F1AD52C" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba397f1440615f1339f1f20b24e67478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9bf4d24f-a117-48f7-91e1-2035a8c734fd" xmlns:ns3="0b7692b1-2532-40e4-a300-4d7fced4a07a" xmlns:ns4="cb645b5b-9a36-43da-96bf-ab72ec91ddff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74828cee37efa74eab9b700f6a6651cc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
@@ -7304,6 +7105,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7403,22 +7218,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7434,6 +7233,22 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sshivang/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD6FC04-8FAA-5B40-B3B5-2D5B862F6C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{053772BF-543F-5C4A-893B-EAF5AB8AC049}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="17280" windowHeight="19980" activeTab="1" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19740" activeTab="1" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="397">
   <si>
     <t>SRX400
 Tested Numbers</t>
@@ -335,9 +335,6 @@
   </si>
   <si>
     <t>Max FW HTTP concurrent Session capacity</t>
-  </si>
-  <si>
-    <t>Max FW HTTP concurrent Session capacity - with Scaled L3L4 mode</t>
   </si>
   <si>
     <t>Max AppSec Sessions(unified policy)</t>
@@ -1151,12 +1148,6 @@
     <t>ß</t>
   </si>
   <si>
-    <t>80K</t>
-  </si>
-  <si>
-    <t>PR 1954675</t>
-  </si>
-  <si>
     <t>PR 1954327</t>
   </si>
   <si>
@@ -1246,13 +1237,73 @@
     <t>190 CPS / 110 Mbps</t>
   </si>
   <si>
-    <t>160 CPS / 90 Mbps</t>
-  </si>
-  <si>
     <t>55 CPS / 30 Mbps</t>
   </si>
   <si>
     <t>1570 CPS / 894 Mbps</t>
+  </si>
+  <si>
+    <t>556 CPS / 318 Mbps</t>
+  </si>
+  <si>
+    <t>1620 CPS /911 Mbps</t>
+  </si>
+  <si>
+    <t>1596 CPS /903 Mbps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppSec+ UTM NG-WF(100% cache) </t>
+  </si>
+  <si>
+    <t>1579 CPS / 893 Mbps</t>
+  </si>
+  <si>
+    <t>400K</t>
+  </si>
+  <si>
+    <t>200K</t>
+  </si>
+  <si>
+    <t>796 CPS / 440 Mbps</t>
+  </si>
+  <si>
+    <t>448 CPS / 237 Mbps</t>
+  </si>
+  <si>
+    <t>428 CPS / 228 Mbps</t>
+  </si>
+  <si>
+    <t>444 CPS / 234 Mbps</t>
+  </si>
+  <si>
+    <t>Max UTM-NG-WF Sessions capacity</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>Max UTM-EWF Sessions capacity</t>
+  </si>
+  <si>
+    <t>Max UTM- NG-WF Sessions capacity</t>
+  </si>
+  <si>
+    <t>165 CPS / 91 Mbps</t>
+  </si>
+  <si>
+    <t>164 CPS / 91 Mbps</t>
+  </si>
+  <si>
+    <t>141 CPS / 85 Mbps</t>
+  </si>
+  <si>
+    <t>149 CPS / 86 Mbps</t>
+  </si>
+  <si>
+    <t>119 CPS / 71 Mbps</t>
+  </si>
+  <si>
+    <t>123 CPS / 74 Mbps</t>
   </si>
 </sst>
 </file>
@@ -1597,7 +1648,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1802,6 +1853,18 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1818,6 +1881,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2129,2158 +2196,2158 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="C1" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="D1" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="E1" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="F1" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="G1" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="H1" s="68" t="s">
         <v>114</v>
-      </c>
-      <c r="H1" s="68" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="C2" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="E2" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="F2" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="68" t="s">
-        <v>120</v>
-      </c>
       <c r="G2" s="68" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H2" s="68" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="68" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="C3" s="68" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="E3" s="68" t="s">
         <v>125</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="F3" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="F3" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3" s="68" t="s">
+      <c r="H3" s="68" t="s">
         <v>127</v>
-      </c>
-      <c r="H3" s="68" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="68" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="68" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="C4" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F4" s="68" t="s">
+      <c r="G4" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H4" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="G4" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="H4" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B5" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="68" t="s">
+      <c r="H5" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H5" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="F6" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G6" s="68" t="s">
+      <c r="H6" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H6" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="C7" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="68" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="E7" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="68" t="s">
+      <c r="F7" s="68" t="s">
         <v>138</v>
       </c>
-      <c r="E7" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="68" t="s">
-        <v>139</v>
-      </c>
       <c r="G7" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="68" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="C8" s="68" t="s">
+      <c r="E8" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="68" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" s="68" t="s">
-        <v>119</v>
-      </c>
       <c r="F8" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G8" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H8" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="68" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="68" t="s">
+      <c r="E9" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" s="68" t="s">
-        <v>119</v>
-      </c>
       <c r="F9" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H9" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="68" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="68" t="s">
+      <c r="C10" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="68" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="68" t="s">
+      <c r="G10" s="68" t="s">
+        <v>145</v>
+      </c>
+      <c r="H10" s="68" t="s">
         <v>146</v>
-      </c>
-      <c r="G10" s="68" t="s">
-        <v>146</v>
-      </c>
-      <c r="H10" s="68" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="68" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="68" t="s">
+      <c r="C11" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" s="68" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="68" t="s">
+      <c r="H11" s="68" t="s">
         <v>150</v>
-      </c>
-      <c r="H11" s="68" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="B12" s="68" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="C12" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="68" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="68" t="s">
+      <c r="F12" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="68" t="s">
         <v>154</v>
-      </c>
-      <c r="F12" s="68" t="s">
-        <v>132</v>
-      </c>
-      <c r="G12" s="68" t="s">
-        <v>132</v>
-      </c>
-      <c r="H12" s="68" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="68" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B13" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="68" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="68" t="s">
+      <c r="F13" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="G13" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13" s="68" t="s">
         <v>154</v>
-      </c>
-      <c r="F13" s="68" t="s">
-        <v>132</v>
-      </c>
-      <c r="G13" s="68" t="s">
-        <v>132</v>
-      </c>
-      <c r="H13" s="68" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B14" s="68" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="E14" s="68" t="s">
-        <v>119</v>
-      </c>
       <c r="F14" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G14" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H14" s="68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B15" s="68" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C15" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="68" t="s">
-        <v>119</v>
-      </c>
       <c r="F15" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G15" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H15" s="68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="68" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="68" t="s">
+      <c r="C16" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="C16" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F16" s="68" t="s">
+      <c r="G16" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H16" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G16" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H16" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B17" s="68" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F17" s="68" t="s">
+      <c r="G17" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H17" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G17" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H17" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" s="68" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="C18" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="68" t="s">
+      <c r="G18" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H18" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G18" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H18" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B19" s="68" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" s="68" t="s">
+      <c r="G19" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G19" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H19" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="68" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="C20" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="E20" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F20" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E20" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F20" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="G20" s="68" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H20" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="68" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21" s="68" t="s">
+        <v>166</v>
+      </c>
+      <c r="C21" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="E21" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G21" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="H21" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B22" s="68" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="E22" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E22" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F22" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="G22" s="68" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H22" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="68" t="s">
+        <v>171</v>
+      </c>
+      <c r="B23" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="68" t="s">
-        <v>173</v>
-      </c>
       <c r="C23" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F23" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G23" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H23" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="68" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B24" s="68" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E24" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F24" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G24" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H24" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="68" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B25" s="68" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E25" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F25" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G25" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H25" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="68" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="68" t="s">
         <v>176</v>
       </c>
-      <c r="B26" s="68" t="s">
+      <c r="C26" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E26" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E26" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F26" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" s="68" t="s">
-        <v>178</v>
-      </c>
       <c r="H26" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B27" s="68" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E27" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="C27" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E27" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F27" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G27" s="68" t="s">
-        <v>178</v>
-      </c>
       <c r="H27" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B28" s="68" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E28" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F28" s="68" t="s">
-        <v>178</v>
-      </c>
       <c r="G28" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H28" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="68" t="s">
         <v>181</v>
       </c>
-      <c r="B29" s="68" t="s">
+      <c r="C29" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G29" s="68" t="s">
         <v>182</v>
       </c>
-      <c r="C29" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F29" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="68" t="s">
-        <v>183</v>
-      </c>
       <c r="H29" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="68" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B30" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F30" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G30" s="68" t="s">
         <v>182</v>
       </c>
-      <c r="C30" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G30" s="68" t="s">
-        <v>183</v>
-      </c>
       <c r="H30" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="68" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B31" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F31" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G31" s="68" t="s">
         <v>182</v>
       </c>
-      <c r="C31" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F31" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G31" s="68" t="s">
-        <v>183</v>
-      </c>
       <c r="H31" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="68" t="s">
         <v>186</v>
       </c>
-      <c r="B32" s="68" t="s">
+      <c r="C32" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F32" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="C32" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F32" s="68" t="s">
-        <v>188</v>
-      </c>
       <c r="G32" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H32" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B33" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F33" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="C33" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F33" s="68" t="s">
-        <v>188</v>
-      </c>
       <c r="G33" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H33" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="68" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B34" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G34" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="C34" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F34" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G34" s="68" t="s">
-        <v>188</v>
-      </c>
       <c r="H34" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="69" t="s">
         <v>191</v>
       </c>
-      <c r="B35" s="69" t="s">
-        <v>192</v>
-      </c>
       <c r="C35" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E35" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F35" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G35" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E35" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F35" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="H35" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="68" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B36" s="69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C36" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E36" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G36" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E36" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F36" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G36" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="H36" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="68" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B37" s="69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C37" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F37" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G37" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E37" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F37" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G37" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="H37" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="69" t="s">
         <v>195</v>
       </c>
-      <c r="B38" s="69" t="s">
-        <v>196</v>
-      </c>
       <c r="C38" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E38" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F38" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G38" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H38" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B39" s="69" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C39" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E39" s="68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F39" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G39" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H39" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="68" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" s="69" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C40" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E40" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F40" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G40" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H40" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="68" t="s">
+        <v>198</v>
+      </c>
+      <c r="B41" s="69" t="s">
         <v>199</v>
       </c>
-      <c r="B41" s="69" t="s">
+      <c r="C41" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="C41" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" s="68" t="s">
-        <v>201</v>
-      </c>
       <c r="E41" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F41" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G41" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H41" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H41" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="68" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B42" s="69" t="s">
+        <v>199</v>
+      </c>
+      <c r="C42" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="C42" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" s="68" t="s">
-        <v>201</v>
-      </c>
       <c r="E42" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F42" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G42" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H42" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H42" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="68" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B43" s="69" t="s">
+        <v>199</v>
+      </c>
+      <c r="C43" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="C43" s="68" t="s">
+      <c r="E43" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="D43" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="E43" s="68" t="s">
-        <v>119</v>
-      </c>
       <c r="F43" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G43" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H43" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H43" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="B44" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="B44" s="68" t="s">
+      <c r="C44" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="C44" s="68" t="s">
+      <c r="E44" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="E44" s="68" t="s">
+      <c r="F44" s="68" t="s">
         <v>207</v>
-      </c>
-      <c r="F44" s="68" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="68" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B45" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="C45" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="E45" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="E45" s="68" t="s">
+      <c r="F45" s="68" t="s">
         <v>207</v>
-      </c>
-      <c r="F45" s="68" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="68" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B46" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="E46" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="E46" s="68" t="s">
+      <c r="F46" s="68" t="s">
         <v>207</v>
-      </c>
-      <c r="F46" s="68" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="68" t="s">
+        <v>210</v>
+      </c>
+      <c r="B47" s="69" t="s">
         <v>211</v>
       </c>
-      <c r="B47" s="69" t="s">
-        <v>212</v>
-      </c>
       <c r="C47" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E47" s="68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F47" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="68" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B48" s="69" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C48" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E48" s="68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F48" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="68" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B49" s="69" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C49" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E49" s="68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F49" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="B50" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="B50" s="68" t="s">
+      <c r="C50" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="D50" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="D50" s="68" t="s">
+      <c r="E50" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F50" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G50" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="E50" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F50" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G50" s="68" t="s">
+      <c r="H50" s="68" t="s">
         <v>219</v>
-      </c>
-      <c r="H50" s="68" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="68" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B51" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="C51" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="C51" s="68" t="s">
+      <c r="D51" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="D51" s="68" t="s">
+      <c r="E51" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F51" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G51" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="E51" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F51" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G51" s="68" t="s">
+      <c r="H51" s="68" t="s">
         <v>219</v>
-      </c>
-      <c r="H51" s="68" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="68" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B52" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="C52" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="D52" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="D52" s="68" t="s">
+      <c r="E52" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F52" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G52" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="E52" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F52" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G52" s="68" t="s">
+      <c r="H52" s="68" t="s">
         <v>219</v>
-      </c>
-      <c r="H52" s="68" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="68" t="s">
+        <v>222</v>
+      </c>
+      <c r="B53" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="B53" s="68" t="s">
+      <c r="C53" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E53" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="68" t="s">
         <v>224</v>
       </c>
-      <c r="C53" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E53" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F53" s="68" t="s">
-        <v>225</v>
-      </c>
       <c r="G53" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H53" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="68" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B54" s="68" t="s">
+        <v>223</v>
+      </c>
+      <c r="C54" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E54" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" s="68" t="s">
         <v>224</v>
       </c>
-      <c r="C54" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E54" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F54" s="68" t="s">
-        <v>225</v>
-      </c>
       <c r="G54" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H54" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="68" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B55" s="68" t="s">
+        <v>223</v>
+      </c>
+      <c r="C55" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E55" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F55" s="68" t="s">
         <v>224</v>
       </c>
-      <c r="C55" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E55" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F55" s="68" t="s">
-        <v>225</v>
-      </c>
       <c r="G55" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H55" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="B56" s="69" t="s">
         <v>228</v>
       </c>
-      <c r="B56" s="69" t="s">
-        <v>229</v>
-      </c>
       <c r="C56" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E56" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F56" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G56" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H56" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H56" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B57" s="69" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C57" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E57" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F57" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G57" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H57" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H57" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B58" s="69" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C58" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E58" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F58" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G58" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="H58" s="68" t="s">
         <v>131</v>
-      </c>
-      <c r="H58" s="68" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="68" t="s">
+        <v>231</v>
+      </c>
+      <c r="B59" s="68" t="s">
         <v>232</v>
       </c>
-      <c r="B59" s="68" t="s">
-        <v>233</v>
-      </c>
       <c r="C59" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E59" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F59" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G59" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H59" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="68" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B60" s="68" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C60" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E60" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F60" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G60" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H60" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="68" t="s">
+        <v>234</v>
+      </c>
+      <c r="B61" s="68" t="s">
         <v>235</v>
       </c>
-      <c r="B61" s="68" t="s">
-        <v>236</v>
-      </c>
       <c r="C61" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E61" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F61" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G61" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H61" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="68" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B62" s="68" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C62" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E62" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F62" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G62" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H62" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="68" t="s">
+        <v>237</v>
+      </c>
+      <c r="B63" s="68" t="s">
         <v>238</v>
       </c>
-      <c r="B63" s="68" t="s">
-        <v>239</v>
-      </c>
       <c r="C63" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E63" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F63" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G63" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H63" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B64" s="68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C64" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E64" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F64" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G64" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H64" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="B65" s="69" t="s">
         <v>241</v>
       </c>
-      <c r="B65" s="69" t="s">
+      <c r="C65" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E65" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F65" s="68" t="s">
         <v>242</v>
       </c>
-      <c r="C65" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E65" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F65" s="68" t="s">
+      <c r="G65" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="H65" s="68" t="s">
         <v>243</v>
-      </c>
-      <c r="G65" s="68" t="s">
-        <v>243</v>
-      </c>
-      <c r="H65" s="68" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B66" s="69" t="s">
+        <v>241</v>
+      </c>
+      <c r="C66" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E66" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F66" s="68" t="s">
         <v>242</v>
       </c>
-      <c r="C66" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E66" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F66" s="68" t="s">
+      <c r="G66" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="H66" s="68" t="s">
         <v>243</v>
-      </c>
-      <c r="G66" s="68" t="s">
-        <v>243</v>
-      </c>
-      <c r="H66" s="68" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="68" t="s">
+        <v>245</v>
+      </c>
+      <c r="B67" s="69" t="s">
         <v>246</v>
       </c>
-      <c r="B67" s="69" t="s">
+      <c r="C67" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D67" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="E67" s="68" t="s">
         <v>247</v>
       </c>
-      <c r="C67" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="D67" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="E67" s="68" t="s">
+      <c r="F67" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G67" s="68" t="s">
         <v>248</v>
       </c>
-      <c r="F67" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G67" s="68" t="s">
-        <v>249</v>
-      </c>
       <c r="H67" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="68" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B68" s="69" t="s">
+        <v>246</v>
+      </c>
+      <c r="C68" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E68" s="68" t="s">
         <v>247</v>
       </c>
-      <c r="C68" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E68" s="68" t="s">
+      <c r="F68" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G68" s="68" t="s">
         <v>248</v>
       </c>
-      <c r="F68" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G68" s="68" t="s">
-        <v>249</v>
-      </c>
       <c r="H68" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="B69" s="69" t="s">
         <v>251</v>
       </c>
-      <c r="B69" s="69" t="s">
+      <c r="C69" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D69" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="E69" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F69" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G69" s="68" t="s">
         <v>252</v>
       </c>
-      <c r="C69" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="D69" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="E69" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F69" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G69" s="68" t="s">
+      <c r="H69" s="68" t="s">
         <v>253</v>
-      </c>
-      <c r="H69" s="68" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B70" s="69" t="s">
+        <v>251</v>
+      </c>
+      <c r="C70" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E70" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F70" s="68" t="s">
         <v>252</v>
       </c>
-      <c r="C70" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E70" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="F70" s="68" t="s">
+      <c r="G70" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="H70" s="68" t="s">
         <v>253</v>
-      </c>
-      <c r="G70" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="H70" s="68" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="B71" s="69" t="s">
         <v>256</v>
       </c>
-      <c r="B71" s="69" t="s">
-        <v>257</v>
-      </c>
       <c r="C71" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D71" s="68" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E71" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F71" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G71" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H71" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="68" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B72" s="69" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C72" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D72" s="68" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E72" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F72" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G72" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H72" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="B73" s="68" t="s">
         <v>259</v>
       </c>
-      <c r="B73" s="68" t="s">
+      <c r="C73" s="68" t="s">
         <v>260</v>
       </c>
-      <c r="C73" s="68" t="s">
+      <c r="E73" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F73" s="68" t="s">
         <v>261</v>
       </c>
-      <c r="E73" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F73" s="68" t="s">
+      <c r="G73" s="68" t="s">
+        <v>261</v>
+      </c>
+      <c r="H73" s="68" t="s">
         <v>262</v>
-      </c>
-      <c r="G73" s="68" t="s">
-        <v>262</v>
-      </c>
-      <c r="H73" s="68" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="68" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B74" s="68" t="s">
+        <v>259</v>
+      </c>
+      <c r="C74" s="68" t="s">
         <v>260</v>
       </c>
-      <c r="C74" s="68" t="s">
+      <c r="E74" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F74" s="68" t="s">
         <v>261</v>
       </c>
-      <c r="E74" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F74" s="68" t="s">
+      <c r="G74" s="68" t="s">
+        <v>261</v>
+      </c>
+      <c r="H74" s="68" t="s">
         <v>262</v>
-      </c>
-      <c r="G74" s="68" t="s">
-        <v>262</v>
-      </c>
-      <c r="H74" s="68" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="B75" s="68" t="s">
         <v>265</v>
       </c>
-      <c r="B75" s="68" t="s">
+      <c r="C75" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E75" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F75" s="68" t="s">
         <v>266</v>
       </c>
-      <c r="C75" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E75" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F75" s="68" t="s">
-        <v>267</v>
-      </c>
       <c r="G75" s="68" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H75" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="68" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B76" s="68" t="s">
+        <v>265</v>
+      </c>
+      <c r="C76" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E76" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F76" s="68" t="s">
         <v>266</v>
       </c>
-      <c r="C76" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E76" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F76" s="68" t="s">
-        <v>267</v>
-      </c>
       <c r="G76" s="68" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H76" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="B77" s="68" t="s">
         <v>269</v>
       </c>
-      <c r="B77" s="68" t="s">
-        <v>270</v>
-      </c>
       <c r="C77" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E77" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F77" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G77" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H77" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="68" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B78" s="68" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C78" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E78" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F78" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G78" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H78" s="68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="B79" s="68" t="s">
         <v>272</v>
       </c>
-      <c r="B79" s="68" t="s">
-        <v>273</v>
-      </c>
       <c r="C79" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E79" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F79" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G79" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H79" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="68" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B80" s="68" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C80" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E80" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F80" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G80" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H80" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="68" t="s">
+        <v>274</v>
+      </c>
+      <c r="B81" s="68" t="s">
         <v>275</v>
       </c>
-      <c r="B81" s="68" t="s">
-        <v>276</v>
-      </c>
       <c r="C81" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E81" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F81" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G81" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H81" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="68" t="s">
+        <v>276</v>
+      </c>
+      <c r="B82" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="C82" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E82" s="68" t="s">
         <v>277</v>
       </c>
-      <c r="B82" s="68" t="s">
-        <v>276</v>
-      </c>
-      <c r="C82" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E82" s="68" t="s">
-        <v>278</v>
-      </c>
       <c r="F82" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G82" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H82" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="68" t="s">
+        <v>278</v>
+      </c>
+      <c r="B83" s="69" t="s">
         <v>279</v>
       </c>
-      <c r="B83" s="69" t="s">
+      <c r="C83" s="68" t="s">
         <v>280</v>
       </c>
-      <c r="C83" s="68" t="s">
-        <v>281</v>
-      </c>
       <c r="E83" s="68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F83" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="68" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B84" s="69" t="s">
+        <v>279</v>
+      </c>
+      <c r="C84" s="68" t="s">
         <v>280</v>
       </c>
-      <c r="C84" s="68" t="s">
-        <v>281</v>
-      </c>
       <c r="E84" s="68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F84" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="68" t="s">
+        <v>282</v>
+      </c>
+      <c r="B85" s="69" t="s">
         <v>283</v>
       </c>
-      <c r="B85" s="69" t="s">
+      <c r="C85" s="68" t="s">
         <v>284</v>
       </c>
-      <c r="C85" s="68" t="s">
-        <v>285</v>
-      </c>
       <c r="E85" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F85" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="G85" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="H85" s="68" t="s">
         <v>253</v>
-      </c>
-      <c r="G85" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="H85" s="68" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="68" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B86" s="69" t="s">
+        <v>283</v>
+      </c>
+      <c r="C86" s="68" t="s">
         <v>284</v>
       </c>
-      <c r="C86" s="68" t="s">
-        <v>285</v>
-      </c>
       <c r="E86" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F86" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="G86" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="H86" s="68" t="s">
         <v>253</v>
-      </c>
-      <c r="G86" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="H86" s="68" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="B87" s="68" t="s">
         <v>287</v>
       </c>
-      <c r="B87" s="68" t="s">
-        <v>288</v>
-      </c>
       <c r="C87" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E87" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F87" s="68" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G87" s="68" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H87" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="68" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B88" s="68" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C88" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E88" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F88" s="68" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G88" s="68" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H88" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="68" t="s">
+        <v>289</v>
+      </c>
+      <c r="B89" s="68" t="s">
         <v>290</v>
       </c>
-      <c r="B89" s="68" t="s">
-        <v>291</v>
-      </c>
       <c r="C89" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E89" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F89" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G89" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H89" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="68" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B90" s="68" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C90" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E90" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F90" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G90" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H90" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="B91" s="68" t="s">
         <v>293</v>
       </c>
-      <c r="B91" s="68" t="s">
+      <c r="C91" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E91" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F91" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="C91" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E91" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F91" s="68" t="s">
-        <v>295</v>
-      </c>
       <c r="G91" s="68" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H91" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="68" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B92" s="68" t="s">
+        <v>293</v>
+      </c>
+      <c r="C92" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="E92" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F92" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="C92" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E92" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F92" s="68" t="s">
-        <v>295</v>
-      </c>
       <c r="G92" s="68" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H92" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="68" t="s">
+        <v>296</v>
+      </c>
+      <c r="B93" s="68" t="s">
         <v>297</v>
       </c>
-      <c r="B93" s="68" t="s">
-        <v>298</v>
-      </c>
       <c r="C93" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E93" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F93" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="G93" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H93" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G93" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H93" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="68" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B94" s="68" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C94" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E94" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F94" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="G94" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="H94" s="68" t="s">
         <v>161</v>
-      </c>
-      <c r="G94" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="H94" s="68" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4344,7 +4411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC397FCC-74C1-4D09-ACC0-E463BF5527EB}">
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="87.83203125" customWidth="1"/>
@@ -4357,7 +4424,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B1" s="72" t="s">
         <v>0</v>
@@ -4373,22 +4440,22 @@
         <v>2</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C2" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" s="40" t="s">
         <v>338</v>
-      </c>
-      <c r="D2" s="40" t="s">
-        <v>339</v>
       </c>
       <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C3" s="15">
         <v>95</v>
@@ -4400,10 +4467,10 @@
     </row>
     <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C4" s="15">
         <v>80</v>
@@ -4416,9 +4483,15 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" s="4">
+        <v>92</v>
+      </c>
+      <c r="D5" s="4">
+        <v>73</v>
+      </c>
       <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4426,7 +4499,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C6" s="1">
         <v>95</v>
@@ -4441,7 +4514,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C7" s="4">
         <v>95</v>
@@ -4455,7 +4528,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C8" s="4">
         <v>91</v>
@@ -4468,138 +4541,186 @@
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="59"/>
+      <c r="B9" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" s="4">
+        <v>96</v>
+      </c>
+      <c r="D9" s="59">
+        <v>73</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="B10" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" s="4">
+        <v>93</v>
+      </c>
+      <c r="D10" s="4">
+        <v>74</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="59"/>
+        <v>379</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C11" s="4">
+        <v>93</v>
+      </c>
+      <c r="D11" s="4">
+        <v>74</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="59"/>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C13" s="1">
+        <v>94</v>
+      </c>
+      <c r="D13" s="4">
+        <v>76</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C14" s="4">
+        <v>95</v>
+      </c>
+      <c r="D14" s="4">
+        <v>76</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C15" s="1">
+        <v>95</v>
+      </c>
+      <c r="D15" s="4">
+        <v>76</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
+      <c r="A16" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="1"/>
+      <c r="C16" s="46"/>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="43" t="s">
+      <c r="A17" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
+      <c r="B17" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C17" s="7">
+        <v>96</v>
+      </c>
+      <c r="D17" s="7">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="C19" s="40" t="s">
+      <c r="B18" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D18" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D19" s="40" t="s">
-        <v>339</v>
+    </row>
+    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>372</v>
+      </c>
+      <c r="C19" s="27">
+        <v>85</v>
+      </c>
+      <c r="D19" s="55">
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="44" t="s">
-        <v>375</v>
-      </c>
-      <c r="C20" s="27">
-        <v>85</v>
-      </c>
-      <c r="D20" s="55">
-        <v>41</v>
+      <c r="A20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C20" s="23">
+        <v>90</v>
+      </c>
+      <c r="D20" s="57">
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="C21" s="23">
-        <v>90</v>
-      </c>
-      <c r="D21" s="57">
-        <v>59</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="57"/>
     </row>
     <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="57"/>
+        <v>26</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C22" s="10">
+        <v>90</v>
+      </c>
+      <c r="D22" s="57">
+        <v>69</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C23" s="10">
         <v>90</v>
@@ -4610,490 +4731,528 @@
     </row>
     <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="C24" s="10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D24" s="57">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="57"/>
+        <v>29</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C25" s="10">
+        <v>91</v>
+      </c>
+      <c r="D25" s="57">
+        <v>55</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="57"/>
+        <v>30</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C26" s="10">
+        <v>93</v>
+      </c>
+      <c r="D26" s="57">
+        <v>59</v>
+      </c>
     </row>
     <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="57"/>
+        <v>31</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C27" s="10">
+        <v>92</v>
+      </c>
+      <c r="D27" s="57">
+        <v>56</v>
+      </c>
     </row>
     <row r="28" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="57"/>
-    </row>
-    <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="57"/>
-    </row>
-    <row r="30" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
+      <c r="B28" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C28" s="10">
+        <v>93</v>
+      </c>
+      <c r="D28" s="57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="39" t="s">
-        <v>359</v>
-      </c>
-      <c r="C30" s="40" t="s">
+      <c r="B29" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D29" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D30" s="40" t="s">
-        <v>339</v>
-      </c>
+    </row>
+    <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="57"/>
     </row>
     <row r="31" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="B31" s="6"/>
       <c r="C31" s="47"/>
       <c r="D31" s="57"/>
     </row>
     <row r="32" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="47"/>
       <c r="D32" s="57"/>
     </row>
-    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="47"/>
-      <c r="D33" s="57"/>
-    </row>
-    <row r="34" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="54"/>
-    </row>
-    <row r="35" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
+      <c r="D33" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="C35" s="40" t="s">
+      <c r="B34" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D34" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D35" s="40" t="s">
-        <v>339</v>
+    </row>
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="4">
+        <v>20000</v>
+      </c>
+      <c r="C35" s="48">
+        <v>90</v>
+      </c>
+      <c r="D35" s="64">
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B36" s="4">
-        <v>20000</v>
-      </c>
-      <c r="C36" s="48">
+        <v>19330</v>
+      </c>
+      <c r="C36" s="4">
+        <v>92</v>
+      </c>
+      <c r="D36" s="64">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C37" s="4">
         <v>90</v>
       </c>
-      <c r="D36" s="64">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="64"/>
-    </row>
-    <row r="38" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="60">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B38" s="4">
-        <v>10000</v>
+        <v>2400</v>
       </c>
       <c r="C38" s="4">
         <v>90</v>
       </c>
       <c r="D38" s="60">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="4">
-        <v>2400</v>
-      </c>
-      <c r="C39" s="4">
-        <v>90</v>
-      </c>
-      <c r="D39" s="60">
-        <v>40</v>
+      <c r="A39" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="15">
+        <v>2250</v>
+      </c>
+      <c r="C39" s="15">
+        <v>96</v>
+      </c>
+      <c r="D39" s="15">
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
+        <v>44</v>
+      </c>
+      <c r="B40" s="45"/>
+      <c r="C40" s="45"/>
       <c r="D40" s="15"/>
     </row>
     <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="45"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="15"/>
+      <c r="A41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1550</v>
+      </c>
+      <c r="C41" s="4">
+        <v>88</v>
+      </c>
+      <c r="D41" s="4">
+        <v>41</v>
+      </c>
     </row>
     <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B42" s="4">
-        <v>1550</v>
-      </c>
-      <c r="C42" s="4">
-        <v>88</v>
+        <v>400</v>
+      </c>
+      <c r="C42" s="1">
+        <v>97</v>
       </c>
       <c r="D42" s="4">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" s="4">
-        <v>400</v>
-      </c>
-      <c r="C43" s="1">
-        <v>97</v>
-      </c>
-      <c r="D43" s="4">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="29" t="s">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="C45" s="40" t="s">
-        <v>338</v>
-      </c>
-      <c r="D45" s="40" t="s">
+      <c r="B44" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="C44" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D44" s="40" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C45" s="33">
+        <v>98</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="C46" s="33">
+        <v>354</v>
+      </c>
+      <c r="C46" s="49">
         <v>98</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C47" s="49">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="C47" s="23">
+        <v>90</v>
+      </c>
+      <c r="D47" s="57" t="s">
+        <v>317</v>
+      </c>
+      <c r="E47" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C48" s="23">
         <v>98</v>
       </c>
-      <c r="D47" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C48" s="23">
-        <v>90</v>
-      </c>
-      <c r="D48" s="57" t="s">
-        <v>318</v>
-      </c>
-      <c r="E48" t="s">
-        <v>370</v>
+      <c r="D48" s="59" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="57"/>
+    </row>
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C50" s="23">
+        <v>99</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C51" s="32">
+        <v>98</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C52" s="23">
+        <v>99</v>
+      </c>
+      <c r="D52" s="24"/>
+    </row>
+    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C53" s="31">
+        <v>99</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C54" s="23">
+        <v>98</v>
+      </c>
+      <c r="D54" s="59" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="C49" s="23">
-        <v>98</v>
-      </c>
-      <c r="D49" s="59" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="57"/>
-    </row>
-    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="C51" s="23">
-        <v>99</v>
-      </c>
-      <c r="D51" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C52" s="32">
-        <v>98</v>
-      </c>
-      <c r="D52" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="C53" s="23">
-        <v>99</v>
-      </c>
-      <c r="D53" s="24"/>
-    </row>
-    <row r="54" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="C54" s="31">
-        <v>99</v>
-      </c>
-      <c r="D54" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="C55" s="23">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C56" s="23">
+        <v>99</v>
+      </c>
+      <c r="D56" s="59" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C57" s="23">
         <v>98</v>
       </c>
-      <c r="D56" s="59" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="C57" s="23">
-        <v>99</v>
-      </c>
-      <c r="D57" s="59" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="C58" s="23">
-        <v>98</v>
-      </c>
-      <c r="D58" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D57" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="55"/>
+    </row>
+    <row r="59" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B59" s="4"/>
-      <c r="C59" s="58"/>
-      <c r="D59" s="55"/>
-    </row>
-    <row r="60" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C59" s="23"/>
+      <c r="D59" s="57"/>
+    </row>
+    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="23"/>
       <c r="D60" s="57"/>
     </row>
-    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="23"/>
       <c r="D61" s="57"/>
     </row>
-    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B62" s="4"/>
-      <c r="C62" s="23"/>
+      <c r="C62" s="32"/>
       <c r="D62" s="57"/>
     </row>
-    <row r="63" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B63" s="4"/>
-      <c r="C63" s="32"/>
+      <c r="C63" s="23"/>
       <c r="D63" s="57"/>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B64" s="4"/>
-      <c r="C64" s="23"/>
+      <c r="C64" s="53"/>
       <c r="D64" s="57"/>
     </row>
-    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="53"/>
+    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="6"/>
+      <c r="C65" s="52"/>
       <c r="D65" s="57"/>
     </row>
-    <row r="66" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66" s="6"/>
-      <c r="C66" s="52"/>
-      <c r="D66" s="57"/>
-    </row>
-    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="28" t="s">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B67" s="20" t="s">
+      <c r="B66" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C67" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="D67" s="67"/>
+      <c r="C66" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="D66" s="67"/>
+    </row>
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="24"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="57"/>
     </row>
     <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B68" s="24"/>
       <c r="C68" s="10"/>
@@ -5101,7 +5260,7 @@
     </row>
     <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B69" s="24"/>
       <c r="C69" s="10"/>
@@ -5109,7 +5268,7 @@
     </row>
     <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B70" s="24"/>
       <c r="C70" s="10"/>
@@ -5117,7 +5276,7 @@
     </row>
     <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B71" s="24"/>
       <c r="C71" s="10"/>
@@ -5125,7 +5284,7 @@
     </row>
     <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B72" s="24"/>
       <c r="C72" s="10"/>
@@ -5133,7 +5292,7 @@
     </row>
     <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B73" s="24"/>
       <c r="C73" s="10"/>
@@ -5141,7 +5300,7 @@
     </row>
     <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B74" s="24"/>
       <c r="C74" s="10"/>
@@ -5149,7 +5308,7 @@
     </row>
     <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B75" s="24"/>
       <c r="C75" s="10"/>
@@ -5157,7 +5316,7 @@
     </row>
     <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B76" s="24"/>
       <c r="C76" s="10"/>
@@ -5165,7 +5324,7 @@
     </row>
     <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B77" s="24"/>
       <c r="C77" s="10"/>
@@ -5173,7 +5332,7 @@
     </row>
     <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B78" s="24"/>
       <c r="C78" s="10"/>
@@ -5181,7 +5340,7 @@
     </row>
     <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B79" s="24"/>
       <c r="C79" s="10"/>
@@ -5189,47 +5348,47 @@
     </row>
     <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="10"/>
+        <v>85</v>
+      </c>
+      <c r="B80" s="33"/>
+      <c r="C80" s="23"/>
       <c r="D80" s="57"/>
     </row>
     <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B81" s="33"/>
-      <c r="C81" s="23"/>
+      <c r="A81" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="24"/>
+      <c r="C81" s="32"/>
       <c r="D81" s="57"/>
     </row>
     <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A82" s="43" t="s">
-        <v>86</v>
+      <c r="A82" s="51" t="s">
+        <v>87</v>
       </c>
       <c r="B82" s="24"/>
       <c r="C82" s="32"/>
       <c r="D82" s="57"/>
     </row>
     <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="B83" s="24"/>
-      <c r="C83" s="32"/>
+      <c r="A83" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="33"/>
+      <c r="C83" s="23"/>
       <c r="D83" s="57"/>
     </row>
     <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A84" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B84" s="33"/>
-      <c r="C84" s="23"/>
+      <c r="A84" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="24"/>
+      <c r="C84" s="10"/>
       <c r="D84" s="57"/>
     </row>
     <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B85" s="24"/>
       <c r="C85" s="10"/>
@@ -5237,15 +5396,15 @@
     </row>
     <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B86" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="B86" s="10"/>
       <c r="C86" s="10"/>
       <c r="D86" s="57"/>
     </row>
     <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
@@ -5253,15 +5412,15 @@
     </row>
     <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B88" s="10"/>
+        <v>93</v>
+      </c>
+      <c r="B88" s="24"/>
       <c r="C88" s="10"/>
       <c r="D88" s="57"/>
     </row>
     <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B89" s="24"/>
       <c r="C89" s="10"/>
@@ -5269,7 +5428,7 @@
     </row>
     <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B90" s="24"/>
       <c r="C90" s="10"/>
@@ -5277,67 +5436,99 @@
     </row>
     <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B91" s="24"/>
-      <c r="C91" s="10"/>
-      <c r="D91" s="57"/>
+        <v>96</v>
+      </c>
+      <c r="B91" s="10">
+        <v>80000</v>
+      </c>
+      <c r="C91" s="10">
+        <v>55</v>
+      </c>
+      <c r="D91" s="57">
+        <v>35</v>
+      </c>
     </row>
     <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B92" s="10"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="57"/>
+        <v>97</v>
+      </c>
+      <c r="B92" s="24">
+        <v>80000</v>
+      </c>
+      <c r="C92" s="10">
+        <v>60</v>
+      </c>
+      <c r="D92" s="57">
+        <v>37</v>
+      </c>
     </row>
     <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B93" s="24"/>
-      <c r="C93" s="24"/>
-      <c r="D93" s="57"/>
+        <v>98</v>
+      </c>
+      <c r="B93" s="70">
+        <v>51000</v>
+      </c>
+      <c r="C93" s="57"/>
+      <c r="D93" s="71" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B94" s="24"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="57"/>
+        <v>389</v>
+      </c>
+      <c r="B94" s="24">
+        <v>32000</v>
+      </c>
+      <c r="C94" s="76">
+        <v>56</v>
+      </c>
+      <c r="D94" s="56">
+        <v>40</v>
+      </c>
     </row>
     <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B95" s="24"/>
-      <c r="C95" s="10"/>
-      <c r="D95" s="57"/>
+        <v>387</v>
+      </c>
+      <c r="B95" s="24">
+        <v>32000</v>
+      </c>
+      <c r="C95" s="26">
+        <v>57</v>
+      </c>
+      <c r="D95" s="56">
+        <v>58</v>
+      </c>
     </row>
     <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B96" s="24"/>
-      <c r="C96" s="26"/>
-      <c r="D96" s="56"/>
+      <c r="B96" s="34"/>
+      <c r="C96" s="35"/>
+      <c r="D96" s="10"/>
     </row>
     <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B97" s="34"/>
-      <c r="C97" s="35"/>
-      <c r="D97" s="10"/>
+      <c r="B97" s="75">
+        <v>26000</v>
+      </c>
+      <c r="C97" s="70"/>
+      <c r="D97" s="70" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="98" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="10"/>
-      <c r="D98" s="10"/>
+      <c r="B98" s="75"/>
+      <c r="C98" s="70"/>
+      <c r="D98" s="70"/>
     </row>
     <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
@@ -5351,7 +5542,7 @@
       <c r="A100" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B100" s="24"/>
+      <c r="B100" s="16"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
     </row>
@@ -5359,7 +5550,7 @@
       <c r="A101" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B101" s="16"/>
+      <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
     </row>
@@ -5367,17 +5558,13 @@
       <c r="A102" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B102" s="10"/>
+      <c r="B102" s="24"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
     </row>
-    <row r="103" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A103" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B103" s="24"/>
-      <c r="C103" s="10"/>
-      <c r="D103" s="10"/>
+    <row r="103" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I103" s="11"/>
+      <c r="J103" s="11"/>
     </row>
     <row r="104" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I104" s="11"/>
@@ -5390,10 +5577,6 @@
     <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I106" s="11"/>
       <c r="J106" s="11"/>
-    </row>
-    <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I107" s="11"/>
-      <c r="J107" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5418,10 +5601,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>1</v>
@@ -5433,21 +5616,21 @@
         <v>2</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C2" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" s="40" t="s">
         <v>338</v>
-      </c>
-      <c r="D2" s="40" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C3" s="59">
         <v>91</v>
@@ -5458,10 +5641,10 @@
     </row>
     <row r="4" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C4" s="4">
         <v>70</v>
@@ -5470,7 +5653,7 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5486,7 +5669,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C6" s="4">
         <v>94</v>
@@ -5500,7 +5683,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C7" s="59">
         <v>96</v>
@@ -5535,91 +5718,97 @@
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="59"/>
+        <v>379</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="59"/>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="59"/>
       <c r="D12" s="59"/>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="B13" s="1"/>
       <c r="C13" s="4"/>
       <c r="D13" s="59"/>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="59"/>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
       <c r="C15" s="4"/>
       <c r="D15" s="59"/>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="1"/>
+      <c r="A16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="46"/>
       <c r="C16" s="4"/>
       <c r="D16" s="59"/>
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="4"/>
+      <c r="A17" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
       <c r="D17" s="59"/>
     </row>
-    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="59"/>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
+    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B18" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C18" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D18" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D19" s="40" t="s">
-        <v>339</v>
+    </row>
+    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="C19" s="55">
+        <v>92</v>
+      </c>
+      <c r="D19" s="59">
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>351</v>
-      </c>
-      <c r="C20" s="55">
-        <v>92</v>
+      <c r="A20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="C20" s="57">
+        <v>95</v>
       </c>
       <c r="D20" s="59">
         <v>63</v>
@@ -5627,68 +5816,62 @@
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="C21" s="57">
-        <v>95</v>
-      </c>
-      <c r="D21" s="59">
-        <v>63</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="59"/>
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="59"/>
+        <v>26</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="C22" s="57">
+        <v>93</v>
+      </c>
+      <c r="D22" s="59">
+        <v>64</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>349</v>
       </c>
       <c r="C23" s="57">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D23" s="59">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="C24" s="57">
-        <v>92</v>
-      </c>
-      <c r="D24" s="59">
-        <v>61</v>
+        <v>28</v>
+      </c>
+      <c r="B24" s="10"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="59"/>
+      <c r="F24" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="57"/>
       <c r="D25" s="59"/>
-      <c r="F25" t="s">
-        <v>352</v>
-      </c>
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="57"/>
@@ -5696,7 +5879,7 @@
     </row>
     <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="57"/>
@@ -5704,37 +5887,37 @@
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="57"/>
       <c r="D28" s="59"/>
     </row>
-    <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="59"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B29" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C29" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D29" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D30" s="40" t="s">
-        <v>339</v>
-      </c>
+    </row>
+    <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="47"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="59"/>
     </row>
     <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="47"/>
       <c r="C31" s="57"/>
@@ -5742,421 +5925,421 @@
     </row>
     <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B32" s="47"/>
       <c r="C32" s="57"/>
       <c r="D32" s="59"/>
     </row>
-    <row r="33" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B33" s="47"/>
-      <c r="C33" s="57"/>
+      <c r="C33" s="54"/>
       <c r="D33" s="59"/>
     </row>
-    <row r="34" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="47"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="59"/>
-    </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B34" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="40" t="s">
+      <c r="C34" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D34" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D35" s="40" t="s">
-        <v>339</v>
+    </row>
+    <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="48">
+        <v>26000</v>
+      </c>
+      <c r="C35" s="64">
+        <v>90</v>
+      </c>
+      <c r="D35" s="59">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="48">
-        <v>26000</v>
+        <v>40</v>
+      </c>
+      <c r="B36" s="4">
+        <v>25400</v>
       </c>
       <c r="C36" s="64">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D36" s="59">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B37" s="4">
-        <v>25400</v>
-      </c>
-      <c r="C37" s="64">
-        <v>93</v>
+        <v>13300</v>
+      </c>
+      <c r="C37" s="60">
+        <v>95</v>
       </c>
       <c r="D37" s="59">
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B38" s="4">
-        <v>13300</v>
+        <v>3200</v>
       </c>
       <c r="C38" s="60">
         <v>95</v>
       </c>
       <c r="D38" s="59">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="4">
-        <v>3200</v>
-      </c>
-      <c r="C39" s="60">
-        <v>95</v>
-      </c>
-      <c r="D39" s="59">
-        <v>38</v>
-      </c>
+      <c r="A39" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="59"/>
     </row>
     <row r="40" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="15"/>
+        <v>44</v>
+      </c>
+      <c r="B40" s="45"/>
       <c r="C40" s="15"/>
       <c r="D40" s="59"/>
     </row>
     <row r="41" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="45"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="59"/>
+      <c r="A41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1810</v>
+      </c>
+      <c r="C41" s="4">
+        <v>95</v>
+      </c>
+      <c r="D41" s="59">
+        <v>68</v>
+      </c>
     </row>
     <row r="42" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="4">
-        <v>1810</v>
+        <v>46</v>
+      </c>
+      <c r="B42" s="1">
+        <v>460</v>
       </c>
       <c r="C42" s="4">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D42" s="59">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" s="1">
-        <v>460</v>
-      </c>
-      <c r="C43" s="4">
-        <v>93</v>
-      </c>
-      <c r="D43" s="59">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="59"/>
-    </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="29" t="s">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="59"/>
+    </row>
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B44" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C45" s="40" t="s">
-        <v>338</v>
-      </c>
-      <c r="D45" s="40" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C44" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="C45" s="24">
+        <v>98</v>
+      </c>
+      <c r="D45" s="59" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" s="33" t="s">
-        <v>319</v>
+        <v>50</v>
+      </c>
+      <c r="B46" s="49" t="s">
+        <v>321</v>
       </c>
       <c r="C46" s="24">
         <v>98</v>
       </c>
       <c r="D46" s="59" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="49" t="s">
-        <v>322</v>
-      </c>
-      <c r="C47" s="24">
-        <v>98</v>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="C47" s="57">
+        <v>96</v>
       </c>
       <c r="D47" s="59" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="23" t="s">
-        <v>324</v>
+      <c r="A48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="49" t="s">
+        <v>320</v>
       </c>
       <c r="C48" s="57">
         <v>96</v>
       </c>
       <c r="D48" s="59" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49" s="49" t="s">
-        <v>321</v>
-      </c>
-      <c r="C49" s="57">
-        <v>96</v>
-      </c>
-      <c r="D49" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="23"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="59"/>
+    </row>
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="23" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50" s="23"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="59"/>
-    </row>
-    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="C50" s="55">
+        <v>98</v>
+      </c>
+      <c r="D50" s="59" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="32" t="s">
         <v>334</v>
       </c>
-      <c r="C51" s="55">
+      <c r="C51" s="57">
         <v>98</v>
       </c>
       <c r="D51" s="59" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="32" t="s">
-        <v>335</v>
+        <v>56</v>
+      </c>
+      <c r="B52" s="58" t="s">
+        <v>331</v>
       </c>
       <c r="C52" s="57">
+        <v>99</v>
+      </c>
+      <c r="D52" s="59" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="C53" s="65">
+        <v>99</v>
+      </c>
+      <c r="D53" s="59" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="C54" s="66">
         <v>98</v>
       </c>
-      <c r="D52" s="59" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" s="58" t="s">
-        <v>332</v>
-      </c>
-      <c r="C53" s="57">
-        <v>99</v>
-      </c>
-      <c r="D53" s="59" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="31" t="s">
-        <v>331</v>
-      </c>
-      <c r="C54" s="65">
-        <v>99</v>
-      </c>
       <c r="D54" s="59" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="18" t="s">
-        <v>58</v>
+      <c r="A55" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C55" s="66">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C56" s="66">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D56" s="59" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="C57" s="66">
+    </row>
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="C57" s="57">
         <v>96</v>
       </c>
       <c r="D57" s="59" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" s="25" t="s">
-        <v>320</v>
-      </c>
-      <c r="C58" s="57">
-        <v>96</v>
-      </c>
-      <c r="D58" s="59" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="23"/>
+      <c r="C58" s="55"/>
+      <c r="D58" s="59"/>
+    </row>
+    <row r="59" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B59" s="23"/>
-      <c r="C59" s="55"/>
+      <c r="C59" s="57"/>
       <c r="D59" s="59"/>
     </row>
-    <row r="60" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B60" s="23"/>
       <c r="C60" s="57"/>
       <c r="D60" s="59"/>
     </row>
-    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B61" s="23"/>
       <c r="C61" s="57"/>
       <c r="D61" s="59"/>
     </row>
-    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B62" s="23"/>
+        <v>66</v>
+      </c>
+      <c r="B62" s="32"/>
       <c r="C62" s="57"/>
       <c r="D62" s="59"/>
     </row>
-    <row r="63" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B63" s="32"/>
+        <v>67</v>
+      </c>
+      <c r="B63" s="23"/>
       <c r="C63" s="57"/>
       <c r="D63" s="59"/>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B64" s="23"/>
+        <v>68</v>
+      </c>
+      <c r="B64" s="53"/>
       <c r="C64" s="57"/>
       <c r="D64" s="59"/>
     </row>
-    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65" s="53"/>
+    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="52"/>
       <c r="C65" s="57"/>
       <c r="D65" s="59"/>
     </row>
-    <row r="66" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66" s="52"/>
-      <c r="C66" s="57"/>
-      <c r="D66" s="59"/>
-    </row>
-    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="28" t="s">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B67" s="30" t="s">
+      <c r="B66" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C67" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="D67" s="67" t="s">
-        <v>341</v>
-      </c>
+      <c r="C66" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="D66" s="67" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="10"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="57"/>
     </row>
     <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B68" s="10"/>
       <c r="C68" s="57"/>
@@ -6164,7 +6347,7 @@
     </row>
     <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B69" s="10"/>
       <c r="C69" s="57"/>
@@ -6172,7 +6355,7 @@
     </row>
     <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B70" s="10"/>
       <c r="C70" s="57"/>
@@ -6180,7 +6363,7 @@
     </row>
     <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B71" s="10"/>
       <c r="C71" s="57"/>
@@ -6188,7 +6371,7 @@
     </row>
     <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B72" s="10"/>
       <c r="C72" s="57"/>
@@ -6196,7 +6379,7 @@
     </row>
     <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B73" s="10"/>
       <c r="C73" s="57"/>
@@ -6204,15 +6387,17 @@
     </row>
     <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B74" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="B74" s="10">
+        <v>1536</v>
+      </c>
       <c r="C74" s="57"/>
       <c r="D74" s="57"/>
     </row>
     <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B75" s="10"/>
       <c r="C75" s="57"/>
@@ -6220,7 +6405,7 @@
     </row>
     <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B76" s="10"/>
       <c r="C76" s="57"/>
@@ -6228,7 +6413,7 @@
     </row>
     <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="57"/>
@@ -6236,7 +6421,7 @@
     </row>
     <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B78" s="10"/>
       <c r="C78" s="57"/>
@@ -6244,7 +6429,7 @@
     </row>
     <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B79" s="10"/>
       <c r="C79" s="57"/>
@@ -6252,47 +6437,47 @@
     </row>
     <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B80" s="10"/>
+        <v>85</v>
+      </c>
+      <c r="B80" s="23"/>
       <c r="C80" s="57"/>
       <c r="D80" s="57"/>
     </row>
     <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B81" s="23"/>
+      <c r="A81" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="32"/>
       <c r="C81" s="57"/>
       <c r="D81" s="57"/>
     </row>
     <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A82" s="43" t="s">
-        <v>86</v>
+      <c r="A82" s="51" t="s">
+        <v>87</v>
       </c>
       <c r="B82" s="32"/>
       <c r="C82" s="57"/>
       <c r="D82" s="57"/>
     </row>
     <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="B83" s="32"/>
+      <c r="A83" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="23"/>
       <c r="C83" s="57"/>
       <c r="D83" s="57"/>
     </row>
     <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A84" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B84" s="23"/>
+      <c r="A84" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="10"/>
       <c r="C84" s="57"/>
       <c r="D84" s="57"/>
     </row>
     <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B85" s="10"/>
       <c r="C85" s="57"/>
@@ -6300,39 +6485,35 @@
     </row>
     <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B86" s="10"/>
-      <c r="C86" s="57"/>
-      <c r="D86" s="57"/>
+        <v>91</v>
+      </c>
+      <c r="B86" s="74" t="s">
+        <v>381</v>
+      </c>
+      <c r="C86" s="71"/>
+      <c r="D86" s="71"/>
     </row>
     <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B87" s="70" t="s">
-        <v>353</v>
+        <v>92</v>
+      </c>
+      <c r="B87" s="74" t="s">
+        <v>382</v>
       </c>
       <c r="C87" s="71"/>
-      <c r="D87" s="71" t="s">
-        <v>354</v>
-      </c>
+      <c r="D87" s="71"/>
     </row>
     <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B88" s="70" t="s">
-        <v>353</v>
-      </c>
-      <c r="C88" s="71"/>
-      <c r="D88" s="71" t="s">
-        <v>354</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="B88" s="10"/>
+      <c r="C88" s="57"/>
+      <c r="D88" s="57"/>
     </row>
     <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="57"/>
@@ -6340,7 +6521,7 @@
     </row>
     <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="57"/>
@@ -6348,51 +6529,55 @@
     </row>
     <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B91" s="10"/>
-      <c r="C91" s="57"/>
-      <c r="D91" s="57"/>
+        <v>96</v>
+      </c>
+      <c r="B91" s="10">
+        <v>96000</v>
+      </c>
+      <c r="C91" s="57">
+        <v>50</v>
+      </c>
+      <c r="D91" s="57">
+        <v>35</v>
+      </c>
     </row>
     <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B92" s="10">
         <v>96000</v>
       </c>
       <c r="C92" s="57">
-        <v>50</v>
-      </c>
-      <c r="D92" s="57"/>
+        <v>55</v>
+      </c>
+      <c r="D92" s="57">
+        <v>35</v>
+      </c>
     </row>
     <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="10">
-        <v>96000</v>
-      </c>
-      <c r="C93" s="57">
-        <v>55</v>
-      </c>
-      <c r="D93" s="57"/>
+      <c r="B93" s="70">
+        <v>51000</v>
+      </c>
+      <c r="C93" s="57"/>
+      <c r="D93" s="71" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B94" s="70">
-        <v>51000</v>
-      </c>
-      <c r="C94" s="57"/>
-      <c r="D94" s="71" t="s">
-        <v>355</v>
-      </c>
+      <c r="B94" s="77"/>
+      <c r="C94" s="56"/>
+      <c r="D94" s="71"/>
     </row>
     <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="B95" s="26"/>
       <c r="C95" s="56"/>
@@ -6400,7 +6585,7 @@
     </row>
     <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B96" s="35"/>
       <c r="C96" s="10"/>
@@ -6408,7 +6593,7 @@
     </row>
     <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
@@ -6416,7 +6601,7 @@
     </row>
     <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B98" s="10">
         <v>1200</v>
@@ -6430,7 +6615,7 @@
     </row>
     <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
@@ -6438,7 +6623,7 @@
     </row>
     <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
@@ -6446,7 +6631,7 @@
     </row>
     <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
@@ -6454,7 +6639,7 @@
     </row>
     <row r="102" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
@@ -6494,10 +6679,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A1" s="50" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>1</v>
@@ -6552,10 +6737,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" s="60" t="s">
         <v>315</v>
-      </c>
-      <c r="C8" s="60" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -6563,10 +6748,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C9" s="59" t="s">
         <v>313</v>
-      </c>
-      <c r="C9" s="59" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6665,10 +6850,10 @@
         <v>24</v>
       </c>
       <c r="B23" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C23" s="57" t="s">
         <v>301</v>
-      </c>
-      <c r="C23" s="57" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6683,10 +6868,10 @@
         <v>26</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -6694,10 +6879,10 @@
         <v>27</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C26" s="57" t="s">
         <v>303</v>
-      </c>
-      <c r="C26" s="57" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6796,10 +6981,10 @@
         <v>41</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C40" s="60" t="s">
         <v>311</v>
-      </c>
-      <c r="C40" s="60" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -6807,10 +6992,10 @@
         <v>42</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6839,10 +7024,10 @@
         <v>46</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
@@ -6858,6 +7043,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010092711BC64AAEC84E9EF800276F1AD52C" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba397f1440615f1339f1f20b24e67478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9bf4d24f-a117-48f7-91e1-2035a8c734fd" xmlns:ns3="0b7692b1-2532-40e4-a300-4d7fced4a07a" xmlns:ns4="cb645b5b-9a36-43da-96bf-ab72ec91ddff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74828cee37efa74eab9b700f6a6651cc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
@@ -7105,20 +7304,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7218,6 +7403,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7233,22 +7434,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="313" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A36155C-B35E-4860-8555-938A055F3044}"/>
+  <xr:revisionPtr revIDLastSave="381" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BF448C6-ACA0-41B6-AF91-530DAF76D438}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19740" firstSheet="2" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19740" firstSheet="1" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="415">
   <si>
     <t>number</t>
   </si>
@@ -678,6 +678,9 @@
     <t>3500 CPS / 1950 Mbps</t>
   </si>
   <si>
+    <t>* Need Additional Port Pair</t>
+  </si>
+  <si>
     <t xml:space="preserve">AppSec + AppQOS with ASC enabled </t>
   </si>
   <si>
@@ -723,6 +726,9 @@
     <t>AppSec + UTM SAV</t>
   </si>
   <si>
+    <t>381 CPS / 211 Mbps</t>
+  </si>
+  <si>
     <t>AppSec + SecIntel+ IDP-Rec + UTM EWF</t>
   </si>
   <si>
@@ -744,6 +750,9 @@
     <t>AppSec + SecIntel+ IDP-Rec + UTM EWF + UTM SAV</t>
   </si>
   <si>
+    <t>307 CPS / 165 Mbps</t>
+  </si>
+  <si>
     <t xml:space="preserve">AppSec + SecIntel+ IDP-Rec + SkyATP Block + DNS </t>
   </si>
   <si>
@@ -766,6 +775,9 @@
   </si>
   <si>
     <t>AppSec + SSL(TLS1.3)</t>
+  </si>
+  <si>
+    <t>125 CPS / 66 Mbps</t>
   </si>
   <si>
     <t xml:space="preserve">AppSec + SSL+ IDP-Recommended policy </t>
@@ -820,54 +832,63 @@
     <t>Firewall + AppSec(Unified policy)</t>
   </si>
   <si>
+    <t>6930 TPS / 3995 Mbps</t>
+  </si>
+  <si>
+    <t>*100 Sessions</t>
+  </si>
+  <si>
     <t>AppSec + IDP-Recommended policy template</t>
   </si>
   <si>
     <t>AppSec + IDP-Rec + UTM EWF(100% cache)</t>
   </si>
   <si>
+    <t>650 TPS / 256 Mbps</t>
+  </si>
+  <si>
+    <t>CPS Performance (Payload: 64B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firewall TCP CPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPv6 Firewall TCP CPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppSec with ASC enabled CPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppSec CPS </t>
+  </si>
+  <si>
+    <t>UTM EWF-100% cache</t>
+  </si>
+  <si>
+    <t>UTM- SAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppSec + TCPProxy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppSec + SSL(TLS1.2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppSec + SSL(TLS1.3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UDP/IPSec Throughput </t>
+  </si>
+  <si>
+    <t>Firewall UDP throughput- Packet size 64bytes</t>
+  </si>
+  <si>
+    <t>654.7 KPPS / 440 Mbps</t>
+  </si>
+  <si>
     <t>*400 Sessions</t>
   </si>
   <si>
-    <t>CPS Performance (Payload: 64B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firewall TCP CPS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPv6 Firewall TCP CPS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppSec with ASC enabled CPS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppSec CPS </t>
-  </si>
-  <si>
-    <t>UTM EWF-100% cache</t>
-  </si>
-  <si>
-    <t>UTM- SAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppSec + TCPProxy </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppSec + SSL(TLS1.2) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppSec + SSL(TLS1.3) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">UDP/IPSec Throughput </t>
-  </si>
-  <si>
-    <t>Firewall UDP throughput- Packet size 64bytes</t>
-  </si>
-  <si>
-    <t>654.7 KPPS / 440 Mbps</t>
-  </si>
-  <si>
     <t>Firewall UDP throughput- Packet size IMIX(ratio: 64:7, 570:4, 1518:1)</t>
   </si>
   <si>
@@ -880,9 +901,6 @@
     <t>487.6 KPPS / 6000 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">We don’t have another pair of ports connected to this 400 device </t>
-  </si>
-  <si>
     <t>Single flow/session Firewall UDP Throughput- IMIX</t>
   </si>
   <si>
@@ -955,6 +973,9 @@
     <t>IPSec(site-2-site) UDP throughput with IKEv2,PSK,AES-GCM256- Packet size 64bytes</t>
   </si>
   <si>
+    <t>PR 1954277 </t>
+  </si>
+  <si>
     <t>IPSec(site-2-site) UDP throughput with IKEv2,PSK,AES-GCM256- Packet size IMIX(ratio 64:7,570:4,1400:1)</t>
   </si>
   <si>
@@ -1078,7 +1099,7 @@
     <t>Max Sky ATP session capacity</t>
   </si>
   <si>
-    <t>PR</t>
+    <t>PR 1957107</t>
   </si>
   <si>
     <t>Max SSL Inspection sessions(TLS1.2)</t>
@@ -1189,6 +1210,9 @@
   </si>
   <si>
     <t>CPS</t>
+  </si>
+  <si>
+    <t>y</t>
   </si>
   <si>
     <t>Sessions</t>
@@ -4498,13 +4522,16 @@
       <c r="D4" s="4">
         <v>70</v>
       </c>
+      <c r="E4" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C5" s="4">
         <v>92</v>
@@ -4516,10 +4543,10 @@
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C6" s="1">
         <v>95</v>
@@ -4531,10 +4558,10 @@
     </row>
     <row r="7" spans="1:5" ht="14.45" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C7" s="4">
         <v>95</v>
@@ -4545,10 +4572,10 @@
     </row>
     <row r="8" spans="1:5" ht="14.1" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C8" s="4">
         <v>91</v>
@@ -4559,10 +4586,10 @@
     </row>
     <row r="9" spans="1:5" ht="15.95">
       <c r="A9" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C9" s="4">
         <v>96</v>
@@ -4573,10 +4600,10 @@
     </row>
     <row r="10" spans="1:5" ht="15.95">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C10" s="4">
         <v>93</v>
@@ -4587,10 +4614,10 @@
     </row>
     <row r="11" spans="1:5" ht="15.95">
       <c r="A11" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C11" s="4">
         <v>93</v>
@@ -4601,18 +4628,24 @@
     </row>
     <row r="12" spans="1:5" ht="15.95">
       <c r="A12" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="59"/>
+        <v>218</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="1">
+        <v>93</v>
+      </c>
+      <c r="D12" s="59">
+        <v>45</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="15.95">
       <c r="A13" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C13" s="1">
         <v>94</v>
@@ -4623,10 +4656,10 @@
     </row>
     <row r="14" spans="1:5" ht="15.95">
       <c r="A14" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C14" s="4">
         <v>95</v>
@@ -4637,10 +4670,10 @@
     </row>
     <row r="15" spans="1:5" ht="15.95">
       <c r="A15" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C15" s="1">
         <v>95</v>
@@ -4651,18 +4684,24 @@
     </row>
     <row r="16" spans="1:5" ht="15.95">
       <c r="A16" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="1:4" ht="15.95">
+        <v>226</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" s="46">
+        <v>94</v>
+      </c>
+      <c r="D16" s="4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.95">
       <c r="A17" s="43" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C17" s="7">
         <v>96</v>
@@ -4671,9 +4710,9 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="40.5" customHeight="1">
+    <row r="18" spans="1:5" ht="40.5" customHeight="1">
       <c r="A18" s="38" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B18" s="39" t="s">
         <v>196</v>
@@ -4685,12 +4724,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.95">
+    <row r="19" spans="1:5" ht="15.95">
       <c r="A19" s="22" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C19" s="27">
         <v>85</v>
@@ -4699,12 +4738,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.95">
+    <row r="20" spans="1:5" ht="15.95">
       <c r="A20" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C20" s="23">
         <v>90</v>
@@ -4713,20 +4752,26 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.95">
+    <row r="21" spans="1:5" ht="15.95">
       <c r="A21" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="57"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.95">
+        <v>235</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C21" s="10">
+        <v>92</v>
+      </c>
+      <c r="D21" s="57">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.95">
       <c r="A22" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C22" s="10">
         <v>90</v>
@@ -4735,12 +4780,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.95">
+    <row r="23" spans="1:5" ht="15.95">
       <c r="A23" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C23" s="10">
         <v>90</v>
@@ -4749,12 +4794,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.95">
+    <row r="24" spans="1:5" ht="15.95">
       <c r="A24" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C24" s="10">
         <v>95</v>
@@ -4763,12 +4808,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.95">
+    <row r="25" spans="1:5" ht="15.95">
       <c r="A25" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C25" s="10">
         <v>91</v>
@@ -4777,12 +4822,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.95">
+    <row r="26" spans="1:5" ht="15.95">
       <c r="A26" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C26" s="10">
         <v>93</v>
@@ -4791,12 +4836,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.95">
+    <row r="27" spans="1:5" ht="15.95">
       <c r="A27" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C27" s="10">
         <v>92</v>
@@ -4805,12 +4850,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.95">
+    <row r="28" spans="1:5" ht="15.95">
       <c r="A28" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C28" s="10">
         <v>93</v>
@@ -4819,12 +4864,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="39" customHeight="1">
+    <row r="29" spans="1:5" ht="39" customHeight="1">
       <c r="A29" s="29" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>197</v>
@@ -4833,43 +4878,74 @@
         <v>198</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.95">
+    <row r="30" spans="1:5" ht="15.95">
       <c r="A30" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="57"/>
-    </row>
-    <row r="31" spans="1:4" ht="15.95">
+        <v>253</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C30" s="47">
+        <v>77</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="E30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.95">
       <c r="A31" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="57"/>
-    </row>
-    <row r="32" spans="1:4" ht="15.95">
+        <v>256</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C31" s="47">
+        <v>77</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="E31" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.95">
       <c r="A32" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="57"/>
+        <v>257</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C32" s="47">
+        <v>77</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="E32" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="33" spans="1:5" ht="17.45" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="47"/>
+        <v>233</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C33" s="47">
+        <v>93</v>
+      </c>
       <c r="D33" s="24" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="41.25" customHeight="1">
       <c r="A34" s="29" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B34" s="39" t="s">
         <v>196</v>
@@ -4883,7 +4959,7 @@
     </row>
     <row r="35" spans="1:5" ht="15.95">
       <c r="A35" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B35" s="4">
         <v>20000</v>
@@ -4897,7 +4973,7 @@
     </row>
     <row r="36" spans="1:5" ht="15.95">
       <c r="A36" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B36" s="4">
         <v>19330</v>
@@ -4911,7 +4987,7 @@
     </row>
     <row r="37" spans="1:5" ht="15.6" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B37" s="4">
         <v>10000</v>
@@ -4925,7 +5001,7 @@
     </row>
     <row r="38" spans="1:5" ht="15.95">
       <c r="A38" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B38" s="4">
         <v>2400</v>
@@ -4939,7 +5015,7 @@
     </row>
     <row r="39" spans="1:5" ht="15.95">
       <c r="A39" s="22" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B39" s="15">
         <v>2250</v>
@@ -4953,15 +5029,21 @@
     </row>
     <row r="40" spans="1:5" ht="15.95">
       <c r="A40" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="15"/>
+        <v>265</v>
+      </c>
+      <c r="B40" s="45">
+        <v>975</v>
+      </c>
+      <c r="C40" s="45">
+        <v>86</v>
+      </c>
+      <c r="D40" s="15">
+        <v>48</v>
+      </c>
     </row>
     <row r="41" spans="1:5" ht="15.95">
       <c r="A41" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B41" s="4">
         <v>1550</v>
@@ -4975,7 +5057,7 @@
     </row>
     <row r="42" spans="1:5" ht="15.95">
       <c r="A42" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B42" s="4">
         <v>400</v>
@@ -4989,15 +5071,21 @@
     </row>
     <row r="43" spans="1:5" ht="15.95">
       <c r="A43" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="B43" s="4">
+        <v>175</v>
+      </c>
+      <c r="C43" s="4">
+        <v>87</v>
+      </c>
+      <c r="D43" s="4">
+        <v>70</v>
+      </c>
     </row>
     <row r="44" spans="1:5" ht="32.25" customHeight="1">
       <c r="A44" s="29" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B44" s="39" t="s">
         <v>196</v>
@@ -5011,66 +5099,66 @@
     </row>
     <row r="45" spans="1:5" ht="18.600000000000001" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C45" s="33">
         <v>98</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="17.45" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C46" s="49">
         <v>98</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.95">
       <c r="A47" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C47" s="23">
         <v>90</v>
       </c>
       <c r="D47" s="57" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="E47" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.95">
       <c r="A48" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C48" s="23">
         <v>98</v>
       </c>
       <c r="D48" s="59" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.95">
       <c r="A49" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="23"/>
@@ -5078,38 +5166,38 @@
     </row>
     <row r="50" spans="1:4" ht="15.95">
       <c r="A50" s="8" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C50" s="23">
         <v>99</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C51" s="32">
         <v>98</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.6" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C52" s="23">
         <v>99</v>
@@ -5118,133 +5206,147 @@
     </row>
     <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C53" s="31">
         <v>99</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.95">
       <c r="A54" s="18" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C54" s="23">
         <v>98</v>
       </c>
       <c r="D54" s="59" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.95">
       <c r="A55" s="19" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C55" s="23">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
       <c r="A56" s="19" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C56" s="23">
         <v>99</v>
       </c>
       <c r="D56" s="59" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.95">
       <c r="A57" s="9" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C57" s="23">
         <v>98</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="17.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="58"/>
-      <c r="D58" s="55"/>
+      <c r="D58" s="70" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="23"/>
-      <c r="D59" s="57"/>
+      <c r="D59" s="70" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="60" spans="1:4" ht="19.5" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="23"/>
-      <c r="D60" s="57"/>
+      <c r="D60" s="70" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="61" spans="1:4" ht="18.75" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="23"/>
-      <c r="D61" s="57"/>
+      <c r="D61" s="70" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="62" spans="1:4" ht="17.45" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="32"/>
-      <c r="D62" s="57"/>
+      <c r="D62" s="70" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="63" spans="1:4" ht="18" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="23"/>
-      <c r="D63" s="57"/>
+      <c r="D63" s="70" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="53"/>
-      <c r="D64" s="57"/>
+      <c r="D64" s="70" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="65" spans="1:4" ht="32.25" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="52"/>
@@ -5252,10 +5354,10 @@
     </row>
     <row r="66" spans="1:4" ht="18" customHeight="1">
       <c r="A66" s="28" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C66" s="30" t="s">
         <v>197</v>
@@ -5264,7 +5366,7 @@
     </row>
     <row r="67" spans="1:4" ht="15.95">
       <c r="A67" s="2" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B67" s="24"/>
       <c r="C67" s="10"/>
@@ -5272,7 +5374,7 @@
     </row>
     <row r="68" spans="1:4" ht="15.95">
       <c r="A68" s="2" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B68" s="24"/>
       <c r="C68" s="10"/>
@@ -5280,7 +5382,7 @@
     </row>
     <row r="69" spans="1:4" ht="15.95">
       <c r="A69" s="2" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B69" s="24"/>
       <c r="C69" s="10"/>
@@ -5288,7 +5390,7 @@
     </row>
     <row r="70" spans="1:4" ht="15.95">
       <c r="A70" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B70" s="24"/>
       <c r="C70" s="10"/>
@@ -5296,7 +5398,7 @@
     </row>
     <row r="71" spans="1:4" ht="15.95">
       <c r="A71" s="2" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B71" s="24"/>
       <c r="C71" s="10"/>
@@ -5304,7 +5406,7 @@
     </row>
     <row r="72" spans="1:4" ht="15.95">
       <c r="A72" s="2" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B72" s="24"/>
       <c r="C72" s="10"/>
@@ -5312,7 +5414,7 @@
     </row>
     <row r="73" spans="1:4" ht="15.95">
       <c r="A73" s="2" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B73" s="24"/>
       <c r="C73" s="10"/>
@@ -5320,7 +5422,7 @@
     </row>
     <row r="74" spans="1:4" ht="15.95">
       <c r="A74" s="2" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B74" s="24"/>
       <c r="C74" s="10"/>
@@ -5328,7 +5430,7 @@
     </row>
     <row r="75" spans="1:4" ht="15.95">
       <c r="A75" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B75" s="24"/>
       <c r="C75" s="10"/>
@@ -5336,7 +5438,7 @@
     </row>
     <row r="76" spans="1:4" ht="15.95">
       <c r="A76" s="2" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B76" s="24"/>
       <c r="C76" s="10"/>
@@ -5344,7 +5446,7 @@
     </row>
     <row r="77" spans="1:4" ht="15.95">
       <c r="A77" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B77" s="24"/>
       <c r="C77" s="10"/>
@@ -5352,7 +5454,7 @@
     </row>
     <row r="78" spans="1:4" ht="15.95">
       <c r="A78" s="2" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B78" s="24"/>
       <c r="C78" s="10"/>
@@ -5360,7 +5462,7 @@
     </row>
     <row r="79" spans="1:4" ht="15.95">
       <c r="A79" s="2" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B79" s="24"/>
       <c r="C79" s="10"/>
@@ -5368,7 +5470,7 @@
     </row>
     <row r="80" spans="1:4" ht="15.95">
       <c r="A80" s="2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B80" s="33"/>
       <c r="C80" s="23"/>
@@ -5376,7 +5478,7 @@
     </row>
     <row r="81" spans="1:4" ht="15.95">
       <c r="A81" s="43" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B81" s="24"/>
       <c r="C81" s="32"/>
@@ -5384,7 +5486,7 @@
     </row>
     <row r="82" spans="1:4" ht="15.95">
       <c r="A82" s="51" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B82" s="24"/>
       <c r="C82" s="32"/>
@@ -5392,7 +5494,7 @@
     </row>
     <row r="83" spans="1:4" ht="15.95">
       <c r="A83" s="22" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B83" s="33"/>
       <c r="C83" s="23"/>
@@ -5400,7 +5502,7 @@
     </row>
     <row r="84" spans="1:4" ht="15.95">
       <c r="A84" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B84" s="24"/>
       <c r="C84" s="10"/>
@@ -5408,7 +5510,7 @@
     </row>
     <row r="85" spans="1:4" ht="15.95">
       <c r="A85" s="2" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B85" s="24"/>
       <c r="C85" s="10"/>
@@ -5416,7 +5518,7 @@
     </row>
     <row r="86" spans="1:4" ht="15.95">
       <c r="A86" s="2" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
@@ -5424,7 +5526,7 @@
     </row>
     <row r="87" spans="1:4" ht="15.95">
       <c r="A87" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
@@ -5432,7 +5534,7 @@
     </row>
     <row r="88" spans="1:4" ht="15.95">
       <c r="A88" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B88" s="24"/>
       <c r="C88" s="10"/>
@@ -5440,7 +5542,7 @@
     </row>
     <row r="89" spans="1:4" ht="15.95">
       <c r="A89" s="2" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B89" s="24"/>
       <c r="C89" s="10"/>
@@ -5448,7 +5550,7 @@
     </row>
     <row r="90" spans="1:4" ht="15.95">
       <c r="A90" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B90" s="24"/>
       <c r="C90" s="10"/>
@@ -5456,7 +5558,7 @@
     </row>
     <row r="91" spans="1:4" ht="15.95">
       <c r="A91" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B91" s="10">
         <v>80000</v>
@@ -5470,7 +5572,7 @@
     </row>
     <row r="92" spans="1:4" ht="15.95">
       <c r="A92" s="2" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B92" s="24">
         <v>80000</v>
@@ -5484,19 +5586,19 @@
     </row>
     <row r="93" spans="1:4" ht="15.95">
       <c r="A93" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B93" s="70">
         <v>51000</v>
       </c>
       <c r="C93" s="57"/>
       <c r="D93" s="71" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.95">
       <c r="A94" s="2" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B94" s="24">
         <v>32000</v>
@@ -5510,7 +5612,7 @@
     </row>
     <row r="95" spans="1:4" ht="15.95">
       <c r="A95" s="2" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B95" s="24">
         <v>32000</v>
@@ -5524,43 +5626,61 @@
     </row>
     <row r="96" spans="1:4" ht="15.95">
       <c r="A96" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="B96" s="34"/>
-      <c r="C96" s="35"/>
-      <c r="D96" s="10"/>
+        <v>341</v>
+      </c>
+      <c r="B96" s="34">
+        <v>8000</v>
+      </c>
+      <c r="C96" s="35">
+        <v>74</v>
+      </c>
+      <c r="D96" s="10">
+        <v>48</v>
+      </c>
     </row>
     <row r="97" spans="1:10" ht="15.95">
       <c r="A97" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B97" s="72">
         <v>26000</v>
       </c>
       <c r="C97" s="70"/>
       <c r="D97" s="70" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="15.95">
       <c r="A98" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B98" s="72"/>
-      <c r="C98" s="70"/>
-      <c r="D98" s="70"/>
+        <v>344</v>
+      </c>
+      <c r="B98" s="24">
+        <v>1000</v>
+      </c>
+      <c r="C98" s="24">
+        <v>99</v>
+      </c>
+      <c r="D98" s="24">
+        <v>57</v>
+      </c>
     </row>
     <row r="99" spans="1:10" ht="15.95">
       <c r="A99" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B99" s="24"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="10"/>
+        <v>345</v>
+      </c>
+      <c r="B99" s="24">
+        <v>300</v>
+      </c>
+      <c r="C99" s="10">
+        <v>99</v>
+      </c>
+      <c r="D99" s="10">
+        <v>69</v>
+      </c>
     </row>
     <row r="100" spans="1:10" ht="15.95">
       <c r="A100" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B100" s="16"/>
       <c r="C100" s="10"/>
@@ -5568,7 +5688,7 @@
     </row>
     <row r="101" spans="1:10" ht="15.95">
       <c r="A101" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
@@ -5576,7 +5696,7 @@
     </row>
     <row r="102" spans="1:10" ht="15.95">
       <c r="A102" s="2" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B102" s="24"/>
       <c r="C102" s="10"/>
@@ -5613,7 +5733,7 @@
   <cols>
     <col min="1" max="1" width="87.85546875" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" style="5" customWidth="1"/>
     <col min="4" max="4" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
@@ -5621,10 +5741,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1">
       <c r="A1" s="50" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>194</v>
@@ -5650,7 +5770,7 @@
         <v>199</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C3" s="59">
         <v>91</v>
@@ -5664,7 +5784,7 @@
         <v>201</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C4" s="4">
         <v>70</v>
@@ -5673,12 +5793,12 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -5686,10 +5806,10 @@
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C6" s="4">
         <v>94</v>
@@ -5700,10 +5820,10 @@
     </row>
     <row r="7" spans="1:5" ht="14.45" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C7" s="59">
         <v>96</v>
@@ -5714,10 +5834,10 @@
     </row>
     <row r="8" spans="1:5" ht="14.1" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C8" s="4">
         <v>90</v>
@@ -5726,12 +5846,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" ht="15.95">
       <c r="A9" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C9" s="59">
         <v>90</v>
@@ -5740,12 +5860,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" ht="15.95">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C10" s="4">
         <v>90</v>
@@ -5756,26 +5876,26 @@
     </row>
     <row r="11" spans="1:5" ht="15.95">
       <c r="A11" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="59"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" ht="15.95">
       <c r="A12" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="59"/>
       <c r="D12" s="59"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="15.95">
       <c r="A13" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C13" s="4">
         <v>90</v>
@@ -5784,12 +5904,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" ht="15.95">
       <c r="A14" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C14" s="4">
         <v>90</v>
@@ -5798,12 +5918,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" ht="15.95">
       <c r="A15" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C15" s="4">
         <v>94</v>
@@ -5814,7 +5934,7 @@
     </row>
     <row r="16" spans="1:5" ht="15.95">
       <c r="A16" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B16" s="46"/>
       <c r="C16" s="4"/>
@@ -5822,7 +5942,7 @@
     </row>
     <row r="17" spans="1:6" ht="15.95">
       <c r="A17" s="43" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -5830,10 +5950,10 @@
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1">
       <c r="A18" s="38" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>197</v>
@@ -5844,10 +5964,10 @@
     </row>
     <row r="19" spans="1:6" ht="15.95">
       <c r="A19" s="22" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C19" s="55">
         <v>92</v>
@@ -5858,10 +5978,10 @@
     </row>
     <row r="20" spans="1:6" ht="15.95">
       <c r="A20" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C20" s="57">
         <v>95</v>
@@ -5872,7 +5992,7 @@
     </row>
     <row r="21" spans="1:6" ht="15.95">
       <c r="A21" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="57"/>
@@ -5880,10 +6000,10 @@
     </row>
     <row r="22" spans="1:6" ht="15.95">
       <c r="A22" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C22" s="57">
         <v>93</v>
@@ -5894,10 +6014,10 @@
     </row>
     <row r="23" spans="1:6" ht="15.95">
       <c r="A23" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C23" s="57">
         <v>92</v>
@@ -5906,12 +6026,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" ht="15.95">
       <c r="A24" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C24" s="57">
         <v>92</v>
@@ -5920,15 +6040,15 @@
         <v>67</v>
       </c>
       <c r="F24" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.95">
       <c r="A25" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C25" s="57">
         <v>92</v>
@@ -5937,12 +6057,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" ht="15.95">
       <c r="A26" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C26" s="57">
         <v>90</v>
@@ -5951,12 +6071,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" ht="15.95">
       <c r="A27" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C27" s="57">
         <v>90</v>
@@ -5965,12 +6085,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" ht="15.95">
       <c r="A28" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C28" s="57">
         <v>92</v>
@@ -5981,10 +6101,10 @@
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1">
       <c r="A29" s="29" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>197</v>
@@ -5995,7 +6115,7 @@
     </row>
     <row r="30" spans="1:6" ht="15.95">
       <c r="A30" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B30" s="47"/>
       <c r="C30" s="57"/>
@@ -6003,7 +6123,7 @@
     </row>
     <row r="31" spans="1:6" ht="15.95">
       <c r="A31" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B31" s="47"/>
       <c r="C31" s="57"/>
@@ -6011,7 +6131,7 @@
     </row>
     <row r="32" spans="1:6" ht="15.95">
       <c r="A32" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B32" s="47"/>
       <c r="C32" s="57"/>
@@ -6019,7 +6139,7 @@
     </row>
     <row r="33" spans="1:4" ht="17.45" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B33" s="47"/>
       <c r="C33" s="54"/>
@@ -6027,10 +6147,10 @@
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1">
       <c r="A34" s="29" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>197</v>
@@ -6041,7 +6161,7 @@
     </row>
     <row r="35" spans="1:4" ht="15.95">
       <c r="A35" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B35" s="48">
         <v>26000</v>
@@ -6055,7 +6175,7 @@
     </row>
     <row r="36" spans="1:4" ht="15.95">
       <c r="A36" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B36" s="4">
         <v>25400</v>
@@ -6069,7 +6189,7 @@
     </row>
     <row r="37" spans="1:4" ht="15.6" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B37" s="4">
         <v>13300</v>
@@ -6083,7 +6203,7 @@
     </row>
     <row r="38" spans="1:4" ht="15.95">
       <c r="A38" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B38" s="4">
         <v>3200</v>
@@ -6095,9 +6215,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" ht="15.95">
       <c r="A39" s="22" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B39" s="15">
         <v>2700</v>
@@ -6111,7 +6231,7 @@
     </row>
     <row r="40" spans="1:4" ht="15.95">
       <c r="A40" s="22" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B40" s="45"/>
       <c r="C40" s="15"/>
@@ -6119,13 +6239,13 @@
     </row>
     <row r="41" spans="1:4" ht="15.95">
       <c r="A41" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B41" s="4">
         <v>1810</v>
       </c>
-      <c r="C41" s="4">
-        <v>95</v>
+      <c r="C41" s="4" t="s">
+        <v>373</v>
       </c>
       <c r="D41" s="59">
         <v>68</v>
@@ -6133,7 +6253,7 @@
     </row>
     <row r="42" spans="1:4" ht="15.95">
       <c r="A42" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B42" s="1">
         <v>460</v>
@@ -6147,7 +6267,7 @@
     </row>
     <row r="43" spans="1:4" ht="15.95">
       <c r="A43" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -6155,77 +6275,77 @@
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1">
       <c r="A44" s="29" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>197</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18.600000000000001" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C45" s="24">
         <v>98</v>
       </c>
       <c r="D45" s="59" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="17.45" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C46" s="24">
         <v>98</v>
       </c>
       <c r="D46" s="59" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.95">
       <c r="A47" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C47" s="57">
         <v>96</v>
       </c>
       <c r="D47" s="59" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.95">
       <c r="A48" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="C48" s="57">
         <v>96</v>
       </c>
       <c r="D48" s="59" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.95">
       <c r="A49" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B49" s="23"/>
       <c r="C49" s="57"/>
@@ -6233,119 +6353,119 @@
     </row>
     <row r="50" spans="1:4" ht="15.95">
       <c r="A50" s="8" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C50" s="55">
         <v>98</v>
       </c>
       <c r="D50" s="59" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C51" s="57">
         <v>98</v>
       </c>
       <c r="D51" s="59" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.6" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C52" s="57">
         <v>99</v>
       </c>
       <c r="D52" s="59" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C53" s="65">
         <v>99</v>
       </c>
       <c r="D53" s="59" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.95">
       <c r="A54" s="18" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C54" s="66">
         <v>98</v>
       </c>
       <c r="D54" s="59" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.95">
       <c r="A55" s="19" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="C55" s="66">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
       <c r="A56" s="19" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C56" s="66">
         <v>96</v>
       </c>
       <c r="D56" s="59" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.95">
       <c r="A57" s="9" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C57" s="57">
         <v>96</v>
       </c>
       <c r="D57" s="59" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="17.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B58" s="23"/>
       <c r="C58" s="55"/>
@@ -6353,7 +6473,7 @@
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B59" s="23"/>
       <c r="C59" s="57"/>
@@ -6361,7 +6481,7 @@
     </row>
     <row r="60" spans="1:4" ht="19.5" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B60" s="23"/>
       <c r="C60" s="57"/>
@@ -6369,7 +6489,7 @@
     </row>
     <row r="61" spans="1:4" ht="18.75" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B61" s="23"/>
       <c r="C61" s="57"/>
@@ -6377,7 +6497,7 @@
     </row>
     <row r="62" spans="1:4" ht="17.45" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B62" s="32"/>
       <c r="C62" s="57"/>
@@ -6385,7 +6505,7 @@
     </row>
     <row r="63" spans="1:4" ht="18" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B63" s="23"/>
       <c r="C63" s="57"/>
@@ -6393,7 +6513,7 @@
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B64" s="53"/>
       <c r="C64" s="57"/>
@@ -6401,7 +6521,7 @@
     </row>
     <row r="65" spans="1:4" ht="32.25" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B65" s="52"/>
       <c r="C65" s="57"/>
@@ -6409,21 +6529,21 @@
     </row>
     <row r="66" spans="1:4" ht="18" customHeight="1">
       <c r="A66" s="28" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B66" s="30" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C66" s="67" t="s">
         <v>197</v>
       </c>
       <c r="D66" s="67" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.95">
       <c r="A67" s="2" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B67" s="10"/>
       <c r="C67" s="57"/>
@@ -6431,7 +6551,7 @@
     </row>
     <row r="68" spans="1:4" ht="15.95">
       <c r="A68" s="2" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B68" s="10"/>
       <c r="C68" s="57"/>
@@ -6439,7 +6559,7 @@
     </row>
     <row r="69" spans="1:4" ht="15.95">
       <c r="A69" s="2" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B69" s="10"/>
       <c r="C69" s="57"/>
@@ -6447,7 +6567,7 @@
     </row>
     <row r="70" spans="1:4" ht="15.95">
       <c r="A70" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B70" s="10"/>
       <c r="C70" s="57"/>
@@ -6455,7 +6575,7 @@
     </row>
     <row r="71" spans="1:4" ht="15.95">
       <c r="A71" s="2" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B71" s="10"/>
       <c r="C71" s="57"/>
@@ -6463,7 +6583,7 @@
     </row>
     <row r="72" spans="1:4" ht="15.95">
       <c r="A72" s="2" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B72" s="10"/>
       <c r="C72" s="57"/>
@@ -6471,7 +6591,7 @@
     </row>
     <row r="73" spans="1:4" ht="15.95">
       <c r="A73" s="2" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B73" s="10"/>
       <c r="C73" s="57"/>
@@ -6479,7 +6599,7 @@
     </row>
     <row r="74" spans="1:4" ht="15.95">
       <c r="A74" s="2" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B74" s="10">
         <v>1536</v>
@@ -6489,7 +6609,7 @@
     </row>
     <row r="75" spans="1:4" ht="15.95">
       <c r="A75" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B75" s="10"/>
       <c r="C75" s="57"/>
@@ -6497,7 +6617,7 @@
     </row>
     <row r="76" spans="1:4" ht="15.95">
       <c r="A76" s="2" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B76" s="10"/>
       <c r="C76" s="57"/>
@@ -6505,7 +6625,7 @@
     </row>
     <row r="77" spans="1:4" ht="15.95">
       <c r="A77" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="57"/>
@@ -6513,7 +6633,7 @@
     </row>
     <row r="78" spans="1:4" ht="15.95">
       <c r="A78" s="2" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B78" s="10"/>
       <c r="C78" s="57"/>
@@ -6521,7 +6641,7 @@
     </row>
     <row r="79" spans="1:4" ht="15.95">
       <c r="A79" s="2" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B79" s="10"/>
       <c r="C79" s="57"/>
@@ -6529,7 +6649,7 @@
     </row>
     <row r="80" spans="1:4" ht="15.95">
       <c r="A80" s="2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B80" s="23"/>
       <c r="C80" s="57"/>
@@ -6537,7 +6657,7 @@
     </row>
     <row r="81" spans="1:4" ht="15.95">
       <c r="A81" s="43" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B81" s="32"/>
       <c r="C81" s="57"/>
@@ -6545,7 +6665,7 @@
     </row>
     <row r="82" spans="1:4" ht="15.95">
       <c r="A82" s="51" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B82" s="32"/>
       <c r="C82" s="57"/>
@@ -6553,7 +6673,7 @@
     </row>
     <row r="83" spans="1:4" ht="15.95">
       <c r="A83" s="22" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B83" s="23"/>
       <c r="C83" s="57"/>
@@ -6561,7 +6681,7 @@
     </row>
     <row r="84" spans="1:4" ht="15.95">
       <c r="A84" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B84" s="10"/>
       <c r="C84" s="57"/>
@@ -6569,7 +6689,7 @@
     </row>
     <row r="85" spans="1:4" ht="15.95">
       <c r="A85" s="2" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B85" s="10"/>
       <c r="C85" s="57"/>
@@ -6577,27 +6697,27 @@
     </row>
     <row r="86" spans="1:4" ht="15.95">
       <c r="A86" s="2" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C86" s="71"/>
       <c r="D86" s="71"/>
     </row>
     <row r="87" spans="1:4" ht="15.95">
       <c r="A87" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C87" s="71"/>
       <c r="D87" s="71"/>
     </row>
     <row r="88" spans="1:4" ht="15.95">
       <c r="A88" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B88" s="10"/>
       <c r="C88" s="57"/>
@@ -6605,7 +6725,7 @@
     </row>
     <row r="89" spans="1:4" ht="15.95">
       <c r="A89" s="2" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="57"/>
@@ -6613,7 +6733,7 @@
     </row>
     <row r="90" spans="1:4" ht="15.95">
       <c r="A90" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="57"/>
@@ -6621,7 +6741,7 @@
     </row>
     <row r="91" spans="1:4" ht="15.95">
       <c r="A91" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B91" s="10">
         <v>96000</v>
@@ -6635,7 +6755,7 @@
     </row>
     <row r="92" spans="1:4" ht="15.95">
       <c r="A92" s="2" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B92" s="10">
         <v>96000</v>
@@ -6649,19 +6769,19 @@
     </row>
     <row r="93" spans="1:4" ht="15.95">
       <c r="A93" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B93" s="70">
         <v>51000</v>
       </c>
       <c r="C93" s="57"/>
       <c r="D93" s="71" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.95">
       <c r="A94" s="2" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B94" s="73"/>
       <c r="C94" s="56"/>
@@ -6669,7 +6789,7 @@
     </row>
     <row r="95" spans="1:4" ht="15.95">
       <c r="A95" s="2" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B95" s="26"/>
       <c r="C95" s="56"/>
@@ -6677,7 +6797,7 @@
     </row>
     <row r="96" spans="1:4" ht="15.95">
       <c r="A96" s="8" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B96" s="35"/>
       <c r="C96" s="10"/>
@@ -6685,7 +6805,7 @@
     </row>
     <row r="97" spans="1:9" ht="15.95">
       <c r="A97" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
@@ -6693,7 +6813,7 @@
     </row>
     <row r="98" spans="1:9" ht="15.95">
       <c r="A98" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B98" s="10">
         <v>1200</v>
@@ -6707,7 +6827,7 @@
     </row>
     <row r="99" spans="1:9" ht="15.95">
       <c r="A99" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
@@ -6715,7 +6835,7 @@
     </row>
     <row r="100" spans="1:9" ht="15.95">
       <c r="A100" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
@@ -6723,7 +6843,7 @@
     </row>
     <row r="101" spans="1:9" ht="15.95">
       <c r="A101" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
@@ -6731,7 +6851,7 @@
     </row>
     <row r="102" spans="1:9" ht="15.95">
       <c r="A102" s="2" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
@@ -6771,10 +6891,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60">
       <c r="A1" s="50" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>194</v>
@@ -6785,346 +6905,346 @@
         <v>195</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C2" s="40"/>
     </row>
     <row r="3" spans="1:3" ht="18.95" hidden="1">
       <c r="A3" s="22" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:3" ht="15.95" hidden="1">
       <c r="A4" s="2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" ht="15.95" hidden="1">
       <c r="A5" s="2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="59"/>
     </row>
     <row r="6" spans="1:3" ht="15.95" hidden="1">
       <c r="A6" s="2" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3" ht="15.95" hidden="1">
       <c r="A7" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3" ht="15.95">
       <c r="A8" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C8" s="60" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.95">
       <c r="A9" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.95" hidden="1">
       <c r="A10" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3" ht="15.95" hidden="1">
       <c r="A11" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="59"/>
     </row>
     <row r="12" spans="1:3" ht="15.95" hidden="1">
       <c r="A12" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:3" ht="15.95" hidden="1">
       <c r="A13" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="59"/>
     </row>
     <row r="14" spans="1:3" ht="15.95" hidden="1">
       <c r="A14" s="2" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="15.95" hidden="1">
       <c r="A15" s="2" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
     <row r="16" spans="1:3" ht="15.95" hidden="1">
       <c r="A16" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3" ht="15.95" hidden="1">
       <c r="A17" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" ht="15.95" hidden="1">
       <c r="A18" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3" ht="15.95" hidden="1">
       <c r="A19" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B19" s="46"/>
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3" ht="15.95" hidden="1">
       <c r="A20" s="43" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
     </row>
     <row r="21" spans="1:3" ht="18.95">
       <c r="A21" s="38" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="61"/>
     </row>
     <row r="22" spans="1:3" ht="15.95" hidden="1">
       <c r="A22" s="22" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="55"/>
     </row>
     <row r="23" spans="1:3" ht="15.95">
       <c r="A23" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.95" hidden="1">
       <c r="A24" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="57"/>
     </row>
     <row r="25" spans="1:3" ht="15.95">
       <c r="A25" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.95">
       <c r="A26" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.95" hidden="1">
       <c r="A27" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="57"/>
     </row>
     <row r="28" spans="1:3" ht="15.95" hidden="1">
       <c r="A28" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="57"/>
     </row>
     <row r="29" spans="1:3" ht="15.95" hidden="1">
       <c r="A29" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B29" s="10"/>
       <c r="C29" s="57"/>
     </row>
     <row r="30" spans="1:3" ht="15.95" hidden="1">
       <c r="A30" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="57"/>
     </row>
     <row r="31" spans="1:3" ht="15.95" hidden="1">
       <c r="A31" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="57"/>
     </row>
     <row r="32" spans="1:3" ht="18.95" hidden="1">
       <c r="A32" s="29" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="62"/>
     </row>
     <row r="33" spans="1:3" ht="15.95" hidden="1">
       <c r="A33" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B33" s="47"/>
       <c r="C33" s="57"/>
     </row>
     <row r="34" spans="1:3" ht="15.95" hidden="1">
       <c r="A34" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B34" s="47"/>
       <c r="C34" s="57"/>
     </row>
     <row r="35" spans="1:3" ht="15.95" hidden="1">
       <c r="A35" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B35" s="47"/>
       <c r="C35" s="57"/>
     </row>
     <row r="36" spans="1:3" ht="15.95" hidden="1">
       <c r="A36" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B36" s="47"/>
       <c r="C36" s="54"/>
     </row>
     <row r="37" spans="1:3" ht="18.95">
       <c r="A37" s="29" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="63"/>
     </row>
     <row r="38" spans="1:3" ht="15.95" hidden="1">
       <c r="A38" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B38" s="48"/>
       <c r="C38" s="64"/>
     </row>
     <row r="39" spans="1:3" ht="15.95" hidden="1">
       <c r="A39" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="64"/>
     </row>
     <row r="40" spans="1:3" ht="15.95">
       <c r="A40" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.95">
       <c r="A41" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.95" hidden="1">
       <c r="A42" s="22" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
     </row>
     <row r="43" spans="1:3" ht="15.95" hidden="1">
       <c r="A43" s="22" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B43" s="45"/>
       <c r="C43" s="15"/>
     </row>
     <row r="44" spans="1:3" ht="15.95" hidden="1">
       <c r="A44" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
     <row r="45" spans="1:3" ht="15.95">
       <c r="A45" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.95" hidden="1">
       <c r="A46" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -7135,6 +7255,118 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cb645b5b-9a36-43da-96bf-ab72ec91ddff" xsi:nil="true"/>
+    <SharedWithUsers xmlns="0b7692b1-2532-40e4-a300-4d7fced4a07a">
+      <UserInfo>
+        <DisplayName>Anand Thulasiram</DisplayName>
+        <AccountId>2178</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Vipin Kumar</DisplayName>
+        <AccountId>64</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sunil  Masineni</DisplayName>
+        <AccountId>5184</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Geetha B K</DisplayName>
+        <AccountId>63</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jagadeesh Rajashekharaiah</DisplayName>
+        <AccountId>13</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Deepasri Chittala</DisplayName>
+        <AccountId>4801</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Weibin Chen</DisplayName>
+        <AccountId>317</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Xiaochen Tang</DisplayName>
+        <AccountId>910</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Anand Antur</DisplayName>
+        <AccountId>670</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Venu Maya</DisplayName>
+        <AccountId>33</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Chockalingam Balasubramanian</DisplayName>
+        <AccountId>682</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Neetu Rathee</DisplayName>
+        <AccountId>4709</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Prasad Shroff</DisplayName>
+        <AccountId>4142</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kedar Dhuru</DisplayName>
+        <AccountId>3907</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sarvesh Batta</DisplayName>
+        <AccountId>21</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Shankar Satyamurthy</DisplayName>
+        <AccountId>3116</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>David Passamonte</DisplayName>
+        <AccountId>5189</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010092711BC64AAEC84E9EF800276F1AD52C" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba397f1440615f1339f1f20b24e67478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9bf4d24f-a117-48f7-91e1-2035a8c734fd" xmlns:ns3="0b7692b1-2532-40e4-a300-4d7fced4a07a" xmlns:ns4="cb645b5b-9a36-43da-96bf-ab72ec91ddff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74828cee37efa74eab9b700f6a6651cc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
@@ -7382,130 +7614,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cb645b5b-9a36-43da-96bf-ab72ec91ddff" xsi:nil="true"/>
-    <SharedWithUsers xmlns="0b7692b1-2532-40e4-a300-4d7fced4a07a">
-      <UserInfo>
-        <DisplayName>Anand Thulasiram</DisplayName>
-        <AccountId>2178</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Vipin Kumar</DisplayName>
-        <AccountId>64</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sunil  Masineni</DisplayName>
-        <AccountId>5184</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Geetha B K</DisplayName>
-        <AccountId>63</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jagadeesh Rajashekharaiah</DisplayName>
-        <AccountId>13</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Deepasri Chittala</DisplayName>
-        <AccountId>4801</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Weibin Chen</DisplayName>
-        <AccountId>317</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Xiaochen Tang</DisplayName>
-        <AccountId>910</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Anand Antur</DisplayName>
-        <AccountId>670</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Venu Maya</DisplayName>
-        <AccountId>33</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Chockalingam Balasubramanian</DisplayName>
-        <AccountId>682</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Neetu Rathee</DisplayName>
-        <AccountId>4709</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Prasad Shroff</DisplayName>
-        <AccountId>4142</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kedar Dhuru</DisplayName>
-        <AccountId>3907</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sarvesh Batta</DisplayName>
-        <AccountId>21</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Shankar Satyamurthy</DisplayName>
-        <AccountId>3116</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>David Passamonte</DisplayName>
-        <AccountId>5189</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
 </file>
--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="381" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BF448C6-ACA0-41B6-AF91-530DAF76D438}"/>
+  <xr:revisionPtr revIDLastSave="507" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FE324C9-AB4A-45FE-80DA-F616BB142F87}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19740" firstSheet="1" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="20140" firstSheet="1" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
     <sheet name="SRX400" sheetId="6" r:id="rId2"/>
     <sheet name="SRX440" sheetId="10" r:id="rId3"/>
     <sheet name="Prelimnary data" sheetId="9" r:id="rId4"/>
+    <sheet name="Second Set Data" sheetId="11" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ISSUES-PR''s'!$A$1:$H$94</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="450">
   <si>
     <t>number</t>
   </si>
@@ -1063,7 +1064,13 @@
     <t>BGP- Total RIB Routes/Size</t>
   </si>
   <si>
+    <t>300K</t>
+  </si>
+  <si>
     <t>BGP- Total FIB Routes/Size</t>
+  </si>
+  <si>
+    <t>150K</t>
   </si>
   <si>
     <t>BGP: Peers</t>
@@ -1170,6 +1177,9 @@
     <t>1700  CPS / 940 Mbps</t>
   </si>
   <si>
+    <t>1800 CPS / 1000 Mbps</t>
+  </si>
+  <si>
     <t>875 CPS / 500 Mbps</t>
   </si>
   <si>
@@ -1179,6 +1189,12 @@
     <t>530 CPS / 300 Mbps</t>
   </si>
   <si>
+    <t>340 CPS / 190 Mbps</t>
+  </si>
+  <si>
+    <t>535 CPS / 305 Mbps</t>
+  </si>
+  <si>
     <t>Throughput</t>
   </si>
   <si>
@@ -1188,6 +1204,9 @@
     <t>252 CPS / 140 Mbps</t>
   </si>
   <si>
+    <t>150 CPS / 82 Mbps</t>
+  </si>
+  <si>
     <t>211 CPS / 122 Mbps</t>
   </si>
   <si>
@@ -1212,9 +1231,6 @@
     <t>CPS</t>
   </si>
   <si>
-    <t>y</t>
-  </si>
-  <si>
     <t>Sessions</t>
   </si>
   <si>
@@ -1254,7 +1270,7 @@
     <t>722.2 KPPS/2155 Mbps</t>
   </si>
   <si>
-    <t>Memory</t>
+    <t>RE Memory</t>
   </si>
   <si>
     <t>400K</t>
@@ -1359,12 +1375,126 @@
   <si>
     <t>CPU: 38, Global Data Shm: 78</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Release: 25.4X300-202604130112.0-EVO
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Testcase Description</t>
+    </r>
+  </si>
+  <si>
+    <t>SRX440</t>
+  </si>
+  <si>
+    <t>SRX400</t>
+  </si>
+  <si>
+    <t>Firewall throughput (IMIX)</t>
+  </si>
+  <si>
+    <t>675.6 KPPS/2016 Mbps</t>
+  </si>
+  <si>
+    <t>601.8 KPPS / 1796 Mbps</t>
+  </si>
+  <si>
+    <t>Firewall throughput (1518B)</t>
+  </si>
+  <si>
+    <t>595.2 KPPS/7324 Mbps</t>
+  </si>
+  <si>
+    <t>IPSec VPN throughput (IMIX)</t>
+  </si>
+  <si>
+    <t>PR 1954277</t>
+  </si>
+  <si>
+    <t>IPSec VPN throughput (1400B)</t>
+  </si>
+  <si>
+    <t>Application security performance (CPS)</t>
+  </si>
+  <si>
+    <t>2077 CPS / 1169 Mbps</t>
+  </si>
+  <si>
+    <t>1611 CPS /891 Mbps</t>
+  </si>
+  <si>
+    <t>Next-generation firewall (CPS)</t>
+  </si>
+  <si>
+    <t>1039 CPS / 596 Mbps</t>
+  </si>
+  <si>
+    <t>829 CPS / 464 Mbps</t>
+  </si>
+  <si>
+    <t>Next-generation firewall performance is measured with firewall, application security, and IPS enabled</t>
+  </si>
+  <si>
+    <t>Secure Web Access Firewall (CPS)</t>
+  </si>
+  <si>
+    <t>762 CPS / 421 Mbps</t>
+  </si>
+  <si>
+    <t>Secure Web Access firewall performance is measured with firewall, application security, IPS, SecIntel, and URL filtering enabled</t>
+  </si>
+  <si>
+    <t>Advanced Threat (CPS)</t>
+  </si>
+  <si>
+    <t>507 CPS / 287 Mbps</t>
+  </si>
+  <si>
+    <t>405 CPS / 216 Mbps</t>
+  </si>
+  <si>
+    <t>Advanced Threat performance is measured with Firewall, Application Security, IPS, SecIntel, URL Filtering and Malware Protection enabled</t>
+  </si>
+  <si>
+    <t>Connections per second (64B)</t>
+  </si>
+  <si>
+    <t>SSL connections per second</t>
+  </si>
+  <si>
+    <t>Maximum concurrent sessions (IPv4 or IPv6)</t>
+  </si>
+  <si>
+    <t>Route table size (RIB) (IPv4)</t>
+  </si>
+  <si>
+    <t>Route table size (FIB) (IPv4)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1443,8 +1573,54 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1479,6 +1655,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1698,11 +1879,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1907,6 +2089,24 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1914,7 +2114,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -2232,7 +2433,7 @@
   <dimension ref="A1:H94"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="18.95"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="68" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="68" customWidth="1"/>
     <col min="2" max="2" width="179.42578125" style="68" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.140625" style="68" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="10.85546875" style="68"/>
@@ -4455,25 +4656,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC397FCC-74C1-4D09-ACC0-E463BF5527EB}">
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="87.85546875" customWidth="1"/>
     <col min="2" max="2" width="35.85546875" style="5" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" style="5" customWidth="1"/>
     <col min="4" max="4" width="28.85546875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1">
       <c r="A1" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="80" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="75"/>
+      <c r="C1" s="81"/>
       <c r="D1" s="36" t="s">
         <v>194</v>
       </c>
@@ -5520,21 +5720,33 @@
       <c r="A86" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B86" s="10"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="57"/>
+      <c r="B86" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C86" s="10">
+        <v>10</v>
+      </c>
+      <c r="D86" s="52">
+        <v>85</v>
+      </c>
     </row>
     <row r="87" spans="1:4" ht="15.95">
       <c r="A87" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B87" s="10"/>
-      <c r="C87" s="10"/>
-      <c r="D87" s="57"/>
+        <v>332</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C87" s="10">
+        <v>10</v>
+      </c>
+      <c r="D87" s="57">
+        <v>85</v>
+      </c>
     </row>
     <row r="88" spans="1:4" ht="15.95">
       <c r="A88" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B88" s="24"/>
       <c r="C88" s="10"/>
@@ -5542,7 +5754,7 @@
     </row>
     <row r="89" spans="1:4" ht="15.95">
       <c r="A89" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B89" s="24"/>
       <c r="C89" s="10"/>
@@ -5550,7 +5762,7 @@
     </row>
     <row r="90" spans="1:4" ht="15.95">
       <c r="A90" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B90" s="24"/>
       <c r="C90" s="10"/>
@@ -5558,7 +5770,7 @@
     </row>
     <row r="91" spans="1:4" ht="15.95">
       <c r="A91" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B91" s="10">
         <v>80000</v>
@@ -5572,7 +5784,7 @@
     </row>
     <row r="92" spans="1:4" ht="15.95">
       <c r="A92" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B92" s="24">
         <v>80000</v>
@@ -5586,19 +5798,19 @@
     </row>
     <row r="93" spans="1:4" ht="15.95">
       <c r="A93" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B93" s="70">
         <v>51000</v>
       </c>
       <c r="C93" s="57"/>
       <c r="D93" s="71" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.95">
       <c r="A94" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B94" s="24">
         <v>32000</v>
@@ -5612,7 +5824,7 @@
     </row>
     <row r="95" spans="1:4" ht="15.95">
       <c r="A95" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B95" s="24">
         <v>32000</v>
@@ -5626,7 +5838,7 @@
     </row>
     <row r="96" spans="1:4" ht="15.95">
       <c r="A96" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B96" s="34">
         <v>8000</v>
@@ -5638,21 +5850,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="15.95">
+    <row r="97" spans="1:9" ht="15.95">
       <c r="A97" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B97" s="72">
         <v>26000</v>
       </c>
       <c r="C97" s="70"/>
       <c r="D97" s="70" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="15.95">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15.95">
       <c r="A98" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B98" s="24">
         <v>1000</v>
@@ -5664,9 +5876,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="15.95">
+    <row r="99" spans="1:9" ht="15.95">
       <c r="A99" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B99" s="24">
         <v>300</v>
@@ -5678,45 +5890,45 @@
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="15.95">
+    <row r="100" spans="1:9" ht="15.95">
       <c r="A100" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B100" s="16"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
     </row>
-    <row r="101" spans="1:10" ht="15.95">
+    <row r="101" spans="1:9" ht="15.95">
       <c r="A101" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
     </row>
-    <row r="102" spans="1:10" ht="15.95">
+    <row r="102" spans="1:9" ht="15.95">
       <c r="A102" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B102" s="24"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
     </row>
-    <row r="103" spans="1:10" ht="15" customHeight="1">
+    <row r="103" spans="1:9" ht="15" customHeight="1">
+      <c r="H103" s="11"/>
       <c r="I103" s="11"/>
-      <c r="J103" s="11"/>
-    </row>
-    <row r="104" spans="1:10" ht="15" customHeight="1">
+    </row>
+    <row r="104" spans="1:9" ht="15" customHeight="1">
+      <c r="H104" s="11"/>
       <c r="I104" s="11"/>
-      <c r="J104" s="11"/>
-    </row>
-    <row r="105" spans="1:10" ht="15" customHeight="1">
+    </row>
+    <row r="105" spans="1:9" ht="15" customHeight="1">
+      <c r="H105" s="11"/>
       <c r="I105" s="11"/>
-      <c r="J105" s="11"/>
-    </row>
-    <row r="106" spans="1:10" ht="15" customHeight="1">
+    </row>
+    <row r="106" spans="1:9" ht="15" customHeight="1">
+      <c r="H106" s="11"/>
       <c r="I106" s="11"/>
-      <c r="J106" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5731,8 +5943,8 @@
   <dimension ref="A1:I106"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="87.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="82.42578125" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" style="5" customWidth="1"/>
     <col min="3" max="3" width="22.140625" style="5" customWidth="1"/>
     <col min="4" max="4" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
@@ -5741,10 +5953,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1">
       <c r="A1" s="50" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>194</v>
@@ -5770,7 +5982,7 @@
         <v>199</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C3" s="59">
         <v>91</v>
@@ -5784,7 +5996,7 @@
         <v>201</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C4" s="4">
         <v>70</v>
@@ -5793,7 +6005,7 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" customHeight="1">
@@ -5809,7 +6021,7 @@
         <v>206</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C6" s="4">
         <v>94</v>
@@ -5823,7 +6035,7 @@
         <v>208</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C7" s="59">
         <v>96</v>
@@ -5837,7 +6049,7 @@
         <v>210</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C8" s="4">
         <v>90</v>
@@ -5851,7 +6063,7 @@
         <v>212</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C9" s="59">
         <v>90</v>
@@ -5865,7 +6077,7 @@
         <v>214</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C10" s="4">
         <v>90</v>
@@ -5874,28 +6086,40 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.95">
+    <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="59"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.95">
+      <c r="B11" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C11" s="4">
+        <v>92</v>
+      </c>
+      <c r="D11" s="59">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
+      <c r="B12" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" s="59">
+        <v>92</v>
+      </c>
+      <c r="D12" s="59">
+        <v>42</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="15.95">
       <c r="A13" s="2" t="s">
         <v>220</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C13" s="4">
         <v>90</v>
@@ -5909,7 +6133,7 @@
         <v>222</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C14" s="4">
         <v>90</v>
@@ -5923,7 +6147,7 @@
         <v>224</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C15" s="4">
         <v>94</v>
@@ -5932,28 +6156,40 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.95">
+    <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="59"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.95">
+      <c r="B16" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="C16" s="4">
+        <v>92</v>
+      </c>
+      <c r="D16" s="59">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="43" t="s">
         <v>228</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="59"/>
+      <c r="B17" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C17" s="7">
+        <v>92</v>
+      </c>
+      <c r="D17" s="59">
+        <v>47</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1">
       <c r="A18" s="38" t="s">
         <v>230</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>197</v>
@@ -5967,7 +6203,7 @@
         <v>231</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C19" s="55">
         <v>92</v>
@@ -5981,7 +6217,7 @@
         <v>233</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C20" s="57">
         <v>95</v>
@@ -5994,16 +6230,22 @@
       <c r="A21" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="59"/>
+      <c r="B21" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="C21" s="57">
+        <v>95</v>
+      </c>
+      <c r="D21" s="59">
+        <v>81</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="15.95">
       <c r="A22" s="2" t="s">
         <v>237</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C22" s="57">
         <v>93</v>
@@ -6017,7 +6259,7 @@
         <v>239</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C23" s="57">
         <v>92</v>
@@ -6031,7 +6273,7 @@
         <v>241</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C24" s="57">
         <v>92</v>
@@ -6040,7 +6282,7 @@
         <v>67</v>
       </c>
       <c r="F24" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.95">
@@ -6048,7 +6290,7 @@
         <v>243</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C25" s="57">
         <v>92</v>
@@ -6062,7 +6304,7 @@
         <v>245</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C26" s="57">
         <v>90</v>
@@ -6076,7 +6318,7 @@
         <v>247</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C27" s="57">
         <v>90</v>
@@ -6090,7 +6332,7 @@
         <v>249</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C28" s="57">
         <v>92</v>
@@ -6104,7 +6346,7 @@
         <v>251</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>197</v>
@@ -6150,7 +6392,7 @@
         <v>259</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>197</v>
@@ -6229,13 +6471,19 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.95">
+    <row r="40" spans="1:4">
       <c r="A40" s="22" t="s">
         <v>265</v>
       </c>
-      <c r="B40" s="45"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="59"/>
+      <c r="B40" s="45">
+        <v>1050</v>
+      </c>
+      <c r="C40" s="15">
+        <v>92</v>
+      </c>
+      <c r="D40" s="59">
+        <v>45</v>
+      </c>
     </row>
     <row r="41" spans="1:4" ht="15.95">
       <c r="A41" s="2" t="s">
@@ -6244,8 +6492,8 @@
       <c r="B41" s="4">
         <v>1810</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>373</v>
+      <c r="C41" s="4">
+        <v>93</v>
       </c>
       <c r="D41" s="59">
         <v>68</v>
@@ -6269,22 +6517,28 @@
       <c r="A43" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="59"/>
+      <c r="B43" s="4">
+        <v>205</v>
+      </c>
+      <c r="C43" s="4">
+        <v>90</v>
+      </c>
+      <c r="D43" s="59">
+        <v>81</v>
+      </c>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1">
       <c r="A44" s="29" t="s">
         <v>269</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>197</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18.600000000000001" customHeight="1">
@@ -6292,7 +6546,7 @@
         <v>270</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C45" s="24">
         <v>98</v>
@@ -6306,7 +6560,7 @@
         <v>273</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C46" s="24">
         <v>98</v>
@@ -6320,7 +6574,7 @@
         <v>275</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C47" s="57">
         <v>96</v>
@@ -6334,7 +6588,7 @@
         <v>277</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C48" s="57">
         <v>96</v>
@@ -6356,7 +6610,7 @@
         <v>281</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C50" s="55">
         <v>98</v>
@@ -6370,7 +6624,7 @@
         <v>283</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C51" s="57">
         <v>98</v>
@@ -6383,8 +6637,8 @@
       <c r="A52" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="B52" s="58" t="s">
-        <v>381</v>
+      <c r="B52" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="C52" s="57">
         <v>99</v>
@@ -6398,7 +6652,7 @@
         <v>287</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C53" s="65">
         <v>99</v>
@@ -6412,7 +6666,7 @@
         <v>289</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C54" s="66">
         <v>98</v>
@@ -6426,7 +6680,7 @@
         <v>292</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C55" s="66">
         <v>98</v>
@@ -6440,7 +6694,7 @@
         <v>295</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C56" s="66">
         <v>96</v>
@@ -6454,7 +6708,7 @@
         <v>298</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C57" s="57">
         <v>96</v>
@@ -6538,7 +6792,7 @@
         <v>197</v>
       </c>
       <c r="D66" s="67" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.95">
@@ -6700,24 +6954,32 @@
         <v>330</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="C86" s="71"/>
-      <c r="D86" s="71"/>
+        <v>393</v>
+      </c>
+      <c r="C86" s="10">
+        <v>10</v>
+      </c>
+      <c r="D86" s="10">
+        <v>84</v>
+      </c>
     </row>
     <row r="87" spans="1:4" ht="15.95">
       <c r="A87" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="C87" s="71"/>
-      <c r="D87" s="71"/>
+        <v>394</v>
+      </c>
+      <c r="C87" s="10">
+        <v>10</v>
+      </c>
+      <c r="D87" s="10">
+        <v>84</v>
+      </c>
     </row>
     <row r="88" spans="1:4" ht="15.95">
       <c r="A88" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B88" s="10"/>
       <c r="C88" s="57"/>
@@ -6725,7 +6987,7 @@
     </row>
     <row r="89" spans="1:4" ht="15.95">
       <c r="A89" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="57"/>
@@ -6733,7 +6995,7 @@
     </row>
     <row r="90" spans="1:4" ht="15.95">
       <c r="A90" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="57"/>
@@ -6741,7 +7003,7 @@
     </row>
     <row r="91" spans="1:4" ht="15.95">
       <c r="A91" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B91" s="10">
         <v>96000</v>
@@ -6755,7 +7017,7 @@
     </row>
     <row r="92" spans="1:4" ht="15.95">
       <c r="A92" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B92" s="10">
         <v>96000</v>
@@ -6769,19 +7031,19 @@
     </row>
     <row r="93" spans="1:4" ht="15.95">
       <c r="A93" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B93" s="70">
         <v>51000</v>
       </c>
       <c r="C93" s="57"/>
       <c r="D93" s="71" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.95">
       <c r="A94" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B94" s="73"/>
       <c r="C94" s="56"/>
@@ -6789,7 +7051,7 @@
     </row>
     <row r="95" spans="1:4" ht="15.95">
       <c r="A95" s="2" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B95" s="26"/>
       <c r="C95" s="56"/>
@@ -6797,7 +7059,7 @@
     </row>
     <row r="96" spans="1:4" ht="15.95">
       <c r="A96" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B96" s="35"/>
       <c r="C96" s="10"/>
@@ -6805,7 +7067,7 @@
     </row>
     <row r="97" spans="1:9" ht="15.95">
       <c r="A97" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
@@ -6813,7 +7075,7 @@
     </row>
     <row r="98" spans="1:9" ht="15.95">
       <c r="A98" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B98" s="10">
         <v>1200</v>
@@ -6827,7 +7089,7 @@
     </row>
     <row r="99" spans="1:9" ht="15.95">
       <c r="A99" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
@@ -6835,7 +7097,7 @@
     </row>
     <row r="100" spans="1:9" ht="15.95">
       <c r="A100" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
@@ -6843,7 +7105,7 @@
     </row>
     <row r="101" spans="1:9" ht="15.95">
       <c r="A101" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
@@ -6851,7 +7113,7 @@
     </row>
     <row r="102" spans="1:9" ht="15.95">
       <c r="A102" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
@@ -6891,10 +7153,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60">
       <c r="A1" s="50" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>194</v>
@@ -6905,34 +7167,34 @@
         <v>195</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C2" s="40"/>
     </row>
     <row r="3" spans="1:3" ht="18.95" hidden="1">
       <c r="A3" s="22" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:3" ht="15.95" hidden="1">
       <c r="A4" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" ht="15.95" hidden="1">
       <c r="A5" s="2" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="59"/>
     </row>
     <row r="6" spans="1:3" ht="15.95" hidden="1">
       <c r="A6" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -6949,10 +7211,10 @@
         <v>206</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C8" s="60" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.95">
@@ -6960,10 +7222,10 @@
         <v>208</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.95" hidden="1">
@@ -6996,14 +7258,14 @@
     </row>
     <row r="14" spans="1:3" ht="15.95" hidden="1">
       <c r="A14" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="15.95" hidden="1">
       <c r="A15" s="2" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -7062,10 +7324,10 @@
         <v>233</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.95" hidden="1">
@@ -7080,10 +7342,10 @@
         <v>237</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.95">
@@ -7091,10 +7353,10 @@
         <v>239</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.95" hidden="1">
@@ -7193,10 +7455,10 @@
         <v>262</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.95">
@@ -7204,10 +7466,10 @@
         <v>263</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.95" hidden="1">
@@ -7236,10 +7498,10 @@
         <v>267</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.95" hidden="1">
@@ -7248,6 +7510,184 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA07167-CEB4-F64B-93AF-8A8BA2B4D0FF}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="62.140625" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" customWidth="1"/>
+    <col min="3" max="3" width="40.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="81">
+      <c r="A1" s="76" t="s">
+        <v>420</v>
+      </c>
+      <c r="B1" s="77" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1" s="78" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="21.95">
+      <c r="A2" s="74" t="s">
+        <v>423</v>
+      </c>
+      <c r="B2" s="75" t="s">
+        <v>424</v>
+      </c>
+      <c r="C2" s="75" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="21.95">
+      <c r="A3" s="74" t="s">
+        <v>426</v>
+      </c>
+      <c r="B3" s="75" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" s="75" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="21.95">
+      <c r="A4" s="74" t="s">
+        <v>428</v>
+      </c>
+      <c r="B4" s="79" t="s">
+        <v>429</v>
+      </c>
+      <c r="C4" s="79" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="21.95">
+      <c r="A5" s="74" t="s">
+        <v>430</v>
+      </c>
+      <c r="B5" s="79" t="s">
+        <v>429</v>
+      </c>
+      <c r="C5" s="79" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="21.95">
+      <c r="A6" s="74" t="s">
+        <v>431</v>
+      </c>
+      <c r="B6" s="75" t="s">
+        <v>432</v>
+      </c>
+      <c r="C6" s="75" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="21.95">
+      <c r="A7" s="74" t="s">
+        <v>434</v>
+      </c>
+      <c r="B7" s="75" t="s">
+        <v>435</v>
+      </c>
+      <c r="C7" s="75" t="s">
+        <v>436</v>
+      </c>
+      <c r="D7" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="21.95">
+      <c r="A8" s="74" t="s">
+        <v>438</v>
+      </c>
+      <c r="B8" s="75" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="75" t="s">
+        <v>439</v>
+      </c>
+      <c r="D8" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="21.95">
+      <c r="A9" s="74" t="s">
+        <v>441</v>
+      </c>
+      <c r="B9" s="75" t="s">
+        <v>442</v>
+      </c>
+      <c r="C9" s="75" t="s">
+        <v>443</v>
+      </c>
+      <c r="D9" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="21.95">
+      <c r="A10" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="B10" s="75">
+        <v>26000</v>
+      </c>
+      <c r="C10" s="75">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="21.95">
+      <c r="A11" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="B11" s="75">
+        <v>445</v>
+      </c>
+      <c r="C11" s="75">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="21.95">
+      <c r="A12" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="B12" s="75">
+        <v>96000</v>
+      </c>
+      <c r="C12" s="75">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="21.95">
+      <c r="A13" s="74" t="s">
+        <v>448</v>
+      </c>
+      <c r="B13" s="75">
+        <v>400000</v>
+      </c>
+      <c r="C13" s="75">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="21.95">
+      <c r="A14" s="74" t="s">
+        <v>449</v>
+      </c>
+      <c r="B14" s="75">
+        <v>200000</v>
+      </c>
+      <c r="C14" s="75">
+        <v>150000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="507" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FE324C9-AB4A-45FE-80DA-F616BB142F87}"/>
+  <xr:revisionPtr revIDLastSave="637" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39540F41-77DD-4392-B620-9ED377082040}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="20140" firstSheet="1" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="1200" yWindow="600" windowWidth="36000" windowHeight="19740" firstSheet="2" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
     <sheet name="SRX400" sheetId="6" r:id="rId2"/>
     <sheet name="SRX440" sheetId="10" r:id="rId3"/>
-    <sheet name="Prelimnary data" sheetId="9" r:id="rId4"/>
-    <sheet name="Second Set Data" sheetId="11" r:id="rId5"/>
+    <sheet name="DS-1" sheetId="12" r:id="rId4"/>
+    <sheet name="Prelimnary data" sheetId="9" r:id="rId5"/>
+    <sheet name="Second Set Data" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ISSUES-PR''s'!$A$1:$H$94</definedName>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="466">
   <si>
     <t>number</t>
   </si>
@@ -830,10 +831,13 @@
 TPS/MBPS</t>
   </si>
   <si>
+    <t>Sessions</t>
+  </si>
+  <si>
     <t>Firewall + AppSec(Unified policy)</t>
   </si>
   <si>
-    <t>6930 TPS / 3995 Mbps</t>
+    <t>10600 TPS / 3995 Mbps</t>
   </si>
   <si>
     <t>*100 Sessions</t>
@@ -1162,6 +1166,9 @@
     <t>** Has to be re-tested with more ports</t>
   </si>
   <si>
+    <t>1920 CPS/ 1025 Mbos</t>
+  </si>
+  <si>
     <t>1085 CPS / 622 Mbps</t>
   </si>
   <si>
@@ -1228,12 +1235,12 @@
     <t>135 CPS / 81 Mbps</t>
   </si>
   <si>
+    <t>800 TPS / 315 Mbps</t>
+  </si>
+  <si>
     <t>CPS</t>
   </si>
   <si>
-    <t>Sessions</t>
-  </si>
-  <si>
     <t>744.1 KPPS/500 Mbps</t>
   </si>
   <si>
@@ -1283,6 +1290,96 @@
   </si>
   <si>
     <t>Max UTM- NG-WF Sessions capacity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Release: 25.4X300-D10-202605310154.0-EVO
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Testcase Description</t>
+  </si>
+  <si>
+    <t>Global data shm / Comments</t>
+  </si>
+  <si>
+    <t>AppSec - HTTP Throughput (64KB)</t>
+  </si>
+  <si>
+    <t>1650 CPS / 920 Mbps</t>
+  </si>
+  <si>
+    <t>2000 CPS / 1350 Mbps</t>
+  </si>
+  <si>
+    <t>AppSec - HTTP  CPS (64B)</t>
+  </si>
+  <si>
+    <t>2400 CPS</t>
+  </si>
+  <si>
+    <t>3000 CPS</t>
+  </si>
+  <si>
+    <t>AppSec + SSL(TLS1.2) - HTTPS Throughput (64KB)</t>
+  </si>
+  <si>
+    <t>240 CPS / 140 Mbps</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Release: 25.4X300-202605180407.0-EVO
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>1650 CPS/928 Mbps</t>
+  </si>
+  <si>
+    <t>240 CPS / 139 Mbps</t>
   </si>
   <si>
     <r>
@@ -1494,7 +1591,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1615,6 +1712,52 @@
     <font>
       <sz val="16"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1884,7 +2027,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2107,10 +2250,75 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4670,10 +4878,10 @@
       <c r="A1" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="B1" s="101" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="81"/>
+      <c r="C1" s="102"/>
       <c r="D1" s="36" t="s">
         <v>194</v>
       </c>
@@ -5075,21 +5283,21 @@
         <v>197</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.95">
       <c r="A30" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C30" s="47">
         <v>77</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E30" t="s">
         <v>203</v>
@@ -5097,16 +5305,16 @@
     </row>
     <row r="31" spans="1:5" ht="15.95">
       <c r="A31" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C31" s="47">
         <v>77</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E31" t="s">
         <v>203</v>
@@ -5114,16 +5322,16 @@
     </row>
     <row r="32" spans="1:5" ht="15.95">
       <c r="A32" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C32" s="47">
         <v>77</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E32" t="s">
         <v>203</v>
@@ -5134,18 +5342,18 @@
         <v>233</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C33" s="47">
         <v>93</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="41.25" customHeight="1">
       <c r="A34" s="29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B34" s="39" t="s">
         <v>196</v>
@@ -5159,7 +5367,7 @@
     </row>
     <row r="35" spans="1:5" ht="15.95">
       <c r="A35" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B35" s="4">
         <v>20000</v>
@@ -5173,7 +5381,7 @@
     </row>
     <row r="36" spans="1:5" ht="15.95">
       <c r="A36" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B36" s="4">
         <v>19330</v>
@@ -5187,7 +5395,7 @@
     </row>
     <row r="37" spans="1:5" ht="15.6" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B37" s="4">
         <v>10000</v>
@@ -5201,7 +5409,7 @@
     </row>
     <row r="38" spans="1:5" ht="15.95">
       <c r="A38" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B38" s="4">
         <v>2400</v>
@@ -5215,7 +5423,7 @@
     </row>
     <row r="39" spans="1:5" ht="15.95">
       <c r="A39" s="22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B39" s="15">
         <v>2250</v>
@@ -5229,7 +5437,7 @@
     </row>
     <row r="40" spans="1:5" ht="15.95">
       <c r="A40" s="22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B40" s="45">
         <v>975</v>
@@ -5243,7 +5451,7 @@
     </row>
     <row r="41" spans="1:5" ht="15.95">
       <c r="A41" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B41" s="4">
         <v>1550</v>
@@ -5257,7 +5465,7 @@
     </row>
     <row r="42" spans="1:5" ht="15.95">
       <c r="A42" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B42" s="4">
         <v>400</v>
@@ -5271,7 +5479,7 @@
     </row>
     <row r="43" spans="1:5" ht="15.95">
       <c r="A43" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B43" s="4">
         <v>175</v>
@@ -5285,7 +5493,7 @@
     </row>
     <row r="44" spans="1:5" ht="32.25" customHeight="1">
       <c r="A44" s="29" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B44" s="39" t="s">
         <v>196</v>
@@ -5294,49 +5502,49 @@
         <v>197</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="18.600000000000001" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C45" s="33">
         <v>98</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="17.45" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C46" s="49">
         <v>98</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.95">
       <c r="A47" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C47" s="23">
         <v>90</v>
       </c>
       <c r="D47" s="57" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E47" t="s">
         <v>203</v>
@@ -5344,21 +5552,21 @@
     </row>
     <row r="48" spans="1:5" ht="15.95">
       <c r="A48" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C48" s="23">
         <v>98</v>
       </c>
       <c r="D48" s="59" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.95">
       <c r="A49" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="23"/>
@@ -5366,38 +5574,38 @@
     </row>
     <row r="50" spans="1:4" ht="15.95">
       <c r="A50" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C50" s="23">
         <v>99</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C51" s="32">
         <v>98</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.6" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C52" s="23">
         <v>99</v>
@@ -5406,147 +5614,147 @@
     </row>
     <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C53" s="31">
         <v>99</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.95">
       <c r="A54" s="18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C54" s="23">
         <v>98</v>
       </c>
       <c r="D54" s="59" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.95">
       <c r="A55" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C55" s="23">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
       <c r="A56" s="19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C56" s="23">
         <v>99</v>
       </c>
       <c r="D56" s="59" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.95">
       <c r="A57" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C57" s="23">
         <v>98</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="17.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="58"/>
       <c r="D58" s="70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="23"/>
       <c r="D59" s="70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="19.5" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="23"/>
       <c r="D60" s="70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="18.75" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="23"/>
       <c r="D61" s="70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="17.45" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="32"/>
       <c r="D62" s="70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="18" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="23"/>
       <c r="D63" s="70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="53"/>
       <c r="D64" s="70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="32.25" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="52"/>
@@ -5554,10 +5762,10 @@
     </row>
     <row r="66" spans="1:4" ht="18" customHeight="1">
       <c r="A66" s="28" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C66" s="30" t="s">
         <v>197</v>
@@ -5566,7 +5774,7 @@
     </row>
     <row r="67" spans="1:4" ht="15.95">
       <c r="A67" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B67" s="24"/>
       <c r="C67" s="10"/>
@@ -5574,7 +5782,7 @@
     </row>
     <row r="68" spans="1:4" ht="15.95">
       <c r="A68" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B68" s="24"/>
       <c r="C68" s="10"/>
@@ -5582,7 +5790,7 @@
     </row>
     <row r="69" spans="1:4" ht="15.95">
       <c r="A69" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B69" s="24"/>
       <c r="C69" s="10"/>
@@ -5590,7 +5798,7 @@
     </row>
     <row r="70" spans="1:4" ht="15.95">
       <c r="A70" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B70" s="24"/>
       <c r="C70" s="10"/>
@@ -5598,7 +5806,7 @@
     </row>
     <row r="71" spans="1:4" ht="15.95">
       <c r="A71" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B71" s="24"/>
       <c r="C71" s="10"/>
@@ -5606,7 +5814,7 @@
     </row>
     <row r="72" spans="1:4" ht="15.95">
       <c r="A72" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B72" s="24"/>
       <c r="C72" s="10"/>
@@ -5614,7 +5822,7 @@
     </row>
     <row r="73" spans="1:4" ht="15.95">
       <c r="A73" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B73" s="24"/>
       <c r="C73" s="10"/>
@@ -5622,7 +5830,7 @@
     </row>
     <row r="74" spans="1:4" ht="15.95">
       <c r="A74" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B74" s="24"/>
       <c r="C74" s="10"/>
@@ -5630,7 +5838,7 @@
     </row>
     <row r="75" spans="1:4" ht="15.95">
       <c r="A75" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B75" s="24"/>
       <c r="C75" s="10"/>
@@ -5638,7 +5846,7 @@
     </row>
     <row r="76" spans="1:4" ht="15.95">
       <c r="A76" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B76" s="24"/>
       <c r="C76" s="10"/>
@@ -5646,7 +5854,7 @@
     </row>
     <row r="77" spans="1:4" ht="15.95">
       <c r="A77" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B77" s="24"/>
       <c r="C77" s="10"/>
@@ -5654,7 +5862,7 @@
     </row>
     <row r="78" spans="1:4" ht="15.95">
       <c r="A78" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B78" s="24"/>
       <c r="C78" s="10"/>
@@ -5662,7 +5870,7 @@
     </row>
     <row r="79" spans="1:4" ht="15.95">
       <c r="A79" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B79" s="24"/>
       <c r="C79" s="10"/>
@@ -5670,7 +5878,7 @@
     </row>
     <row r="80" spans="1:4" ht="15.95">
       <c r="A80" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B80" s="33"/>
       <c r="C80" s="23"/>
@@ -5678,7 +5886,7 @@
     </row>
     <row r="81" spans="1:4" ht="15.95">
       <c r="A81" s="43" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B81" s="24"/>
       <c r="C81" s="32"/>
@@ -5686,7 +5894,7 @@
     </row>
     <row r="82" spans="1:4" ht="15.95">
       <c r="A82" s="51" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B82" s="24"/>
       <c r="C82" s="32"/>
@@ -5694,7 +5902,7 @@
     </row>
     <row r="83" spans="1:4" ht="15.95">
       <c r="A83" s="22" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B83" s="33"/>
       <c r="C83" s="23"/>
@@ -5702,7 +5910,7 @@
     </row>
     <row r="84" spans="1:4" ht="15.95">
       <c r="A84" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B84" s="24"/>
       <c r="C84" s="10"/>
@@ -5710,7 +5918,7 @@
     </row>
     <row r="85" spans="1:4" ht="15.95">
       <c r="A85" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B85" s="24"/>
       <c r="C85" s="10"/>
@@ -5718,10 +5926,10 @@
     </row>
     <row r="86" spans="1:4" ht="15.95">
       <c r="A86" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C86" s="10">
         <v>10</v>
@@ -5732,10 +5940,10 @@
     </row>
     <row r="87" spans="1:4" ht="15.95">
       <c r="A87" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C87" s="10">
         <v>10</v>
@@ -5746,7 +5954,7 @@
     </row>
     <row r="88" spans="1:4" ht="15.95">
       <c r="A88" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B88" s="24"/>
       <c r="C88" s="10"/>
@@ -5754,7 +5962,7 @@
     </row>
     <row r="89" spans="1:4" ht="15.95">
       <c r="A89" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B89" s="24"/>
       <c r="C89" s="10"/>
@@ -5762,7 +5970,7 @@
     </row>
     <row r="90" spans="1:4" ht="15.95">
       <c r="A90" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B90" s="24"/>
       <c r="C90" s="10"/>
@@ -5770,7 +5978,7 @@
     </row>
     <row r="91" spans="1:4" ht="15.95">
       <c r="A91" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B91" s="10">
         <v>80000</v>
@@ -5784,7 +5992,7 @@
     </row>
     <row r="92" spans="1:4" ht="15.95">
       <c r="A92" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B92" s="24">
         <v>80000</v>
@@ -5798,19 +6006,19 @@
     </row>
     <row r="93" spans="1:4" ht="15.95">
       <c r="A93" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B93" s="70">
         <v>51000</v>
       </c>
       <c r="C93" s="57"/>
       <c r="D93" s="71" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.95">
       <c r="A94" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B94" s="24">
         <v>32000</v>
@@ -5824,7 +6032,7 @@
     </row>
     <row r="95" spans="1:4" ht="15.95">
       <c r="A95" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B95" s="24">
         <v>32000</v>
@@ -5838,7 +6046,7 @@
     </row>
     <row r="96" spans="1:4" ht="15.95">
       <c r="A96" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B96" s="34">
         <v>8000</v>
@@ -5852,19 +6060,19 @@
     </row>
     <row r="97" spans="1:9" ht="15.95">
       <c r="A97" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B97" s="72">
         <v>26000</v>
       </c>
       <c r="C97" s="70"/>
       <c r="D97" s="70" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15.95">
       <c r="A98" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B98" s="24">
         <v>1000</v>
@@ -5878,7 +6086,7 @@
     </row>
     <row r="99" spans="1:9" ht="15.95">
       <c r="A99" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B99" s="24">
         <v>300</v>
@@ -5892,7 +6100,7 @@
     </row>
     <row r="100" spans="1:9" ht="15.95">
       <c r="A100" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B100" s="16"/>
       <c r="C100" s="10"/>
@@ -5900,7 +6108,7 @@
     </row>
     <row r="101" spans="1:9" ht="15.95">
       <c r="A101" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
@@ -5908,7 +6116,7 @@
     </row>
     <row r="102" spans="1:9" ht="15.95">
       <c r="A102" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B102" s="24"/>
       <c r="C102" s="10"/>
@@ -5953,15 +6161,15 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1">
       <c r="A1" s="50" t="s">
-        <v>351</v>
-      </c>
-      <c r="B1" s="37" t="s">
         <v>352</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="B1" s="101" t="s">
+        <v>353</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="38" t="s">
@@ -5982,7 +6190,7 @@
         <v>199</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C3" s="59">
         <v>91</v>
@@ -5996,7 +6204,7 @@
         <v>201</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C4" s="4">
         <v>70</v>
@@ -6005,23 +6213,29 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="59"/>
+      <c r="B5" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C5" s="4">
+        <v>92</v>
+      </c>
+      <c r="D5" s="59">
+        <v>57</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>206</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C6" s="4">
         <v>94</v>
@@ -6035,7 +6249,7 @@
         <v>208</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C7" s="59">
         <v>96</v>
@@ -6049,7 +6263,7 @@
         <v>210</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C8" s="4">
         <v>90</v>
@@ -6063,7 +6277,7 @@
         <v>212</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C9" s="59">
         <v>90</v>
@@ -6077,7 +6291,7 @@
         <v>214</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C10" s="4">
         <v>90</v>
@@ -6086,12 +6300,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" ht="15.95">
       <c r="A11" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C11" s="4">
         <v>92</v>
@@ -6100,7 +6314,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" ht="15.95">
       <c r="A12" s="2" t="s">
         <v>218</v>
       </c>
@@ -6119,7 +6333,7 @@
         <v>220</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C13" s="4">
         <v>90</v>
@@ -6133,7 +6347,7 @@
         <v>222</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C14" s="4">
         <v>90</v>
@@ -6147,7 +6361,7 @@
         <v>224</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C15" s="4">
         <v>94</v>
@@ -6156,12 +6370,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="15.95">
       <c r="A16" s="3" t="s">
         <v>226</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C16" s="4">
         <v>92</v>
@@ -6170,12 +6384,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="15.95">
       <c r="A17" s="43" t="s">
         <v>228</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C17" s="7">
         <v>92</v>
@@ -6189,7 +6403,7 @@
         <v>230</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>197</v>
@@ -6203,7 +6417,7 @@
         <v>231</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C19" s="55">
         <v>92</v>
@@ -6217,7 +6431,7 @@
         <v>233</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C20" s="57">
         <v>95</v>
@@ -6231,7 +6445,7 @@
         <v>235</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C21" s="57">
         <v>95</v>
@@ -6245,7 +6459,7 @@
         <v>237</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C22" s="57">
         <v>93</v>
@@ -6259,7 +6473,7 @@
         <v>239</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C23" s="57">
         <v>92</v>
@@ -6273,7 +6487,7 @@
         <v>241</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C24" s="57">
         <v>92</v>
@@ -6282,7 +6496,7 @@
         <v>67</v>
       </c>
       <c r="F24" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.95">
@@ -6290,7 +6504,7 @@
         <v>243</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C25" s="57">
         <v>92</v>
@@ -6304,7 +6518,7 @@
         <v>245</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C26" s="57">
         <v>90</v>
@@ -6318,7 +6532,7 @@
         <v>247</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C27" s="57">
         <v>90</v>
@@ -6332,7 +6546,7 @@
         <v>249</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C28" s="57">
         <v>92</v>
@@ -6346,53 +6560,86 @@
         <v>251</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>197</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.95">
       <c r="A30" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B30" s="47"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="59"/>
+        <v>254</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C30" s="47">
+        <v>68</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="E30" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="15.95">
       <c r="A31" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C31" s="47">
+        <v>68</v>
+      </c>
+      <c r="D31" s="24" t="s">
         <v>256</v>
       </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="59"/>
+      <c r="E31" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="15.95">
       <c r="A32" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="B32" s="47"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="59"/>
+        <v>258</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C32" s="47">
+        <v>68</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="E32" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="33" spans="1:4" ht="17.45" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="59"/>
+      <c r="B33" s="47" t="s">
+        <v>380</v>
+      </c>
+      <c r="C33" s="57">
+        <v>92</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1">
       <c r="A34" s="29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>197</v>
@@ -6403,7 +6650,7 @@
     </row>
     <row r="35" spans="1:4" ht="15.95">
       <c r="A35" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B35" s="48">
         <v>26000</v>
@@ -6417,7 +6664,7 @@
     </row>
     <row r="36" spans="1:4" ht="15.95">
       <c r="A36" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B36" s="4">
         <v>25400</v>
@@ -6431,7 +6678,7 @@
     </row>
     <row r="37" spans="1:4" ht="15.6" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B37" s="4">
         <v>13300</v>
@@ -6445,7 +6692,7 @@
     </row>
     <row r="38" spans="1:4" ht="15.95">
       <c r="A38" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B38" s="4">
         <v>3200</v>
@@ -6459,7 +6706,7 @@
     </row>
     <row r="39" spans="1:4" ht="15.95">
       <c r="A39" s="22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B39" s="15">
         <v>2700</v>
@@ -6471,9 +6718,9 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" ht="15.95">
       <c r="A40" s="22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B40" s="45">
         <v>1050</v>
@@ -6487,7 +6734,7 @@
     </row>
     <row r="41" spans="1:4" ht="15.95">
       <c r="A41" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B41" s="4">
         <v>1810</v>
@@ -6501,7 +6748,7 @@
     </row>
     <row r="42" spans="1:4" ht="15.95">
       <c r="A42" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B42" s="1">
         <v>460</v>
@@ -6515,7 +6762,7 @@
     </row>
     <row r="43" spans="1:4" ht="15.95">
       <c r="A43" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B43" s="4">
         <v>205</v>
@@ -6529,77 +6776,77 @@
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1">
       <c r="A44" s="29" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>197</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>379</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18.600000000000001" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C45" s="24">
         <v>98</v>
       </c>
       <c r="D45" s="59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="17.45" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C46" s="24">
         <v>98</v>
       </c>
       <c r="D46" s="59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.95">
       <c r="A47" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C47" s="57">
         <v>96</v>
       </c>
       <c r="D47" s="59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.95">
       <c r="A48" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C48" s="57">
         <v>96</v>
       </c>
       <c r="D48" s="59" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.95">
       <c r="A49" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B49" s="23"/>
       <c r="C49" s="57"/>
@@ -6607,119 +6854,119 @@
     </row>
     <row r="50" spans="1:4" ht="15.95">
       <c r="A50" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C50" s="55">
         <v>98</v>
       </c>
       <c r="D50" s="59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C51" s="57">
         <v>98</v>
       </c>
       <c r="D51" s="59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.6" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C52" s="57">
         <v>99</v>
       </c>
       <c r="D52" s="59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C53" s="65">
         <v>99</v>
       </c>
       <c r="D53" s="59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.95">
       <c r="A54" s="18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C54" s="66">
         <v>98</v>
       </c>
       <c r="D54" s="59" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.95">
       <c r="A55" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C55" s="66">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
       <c r="A56" s="19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C56" s="66">
         <v>96</v>
       </c>
       <c r="D56" s="59" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.95">
       <c r="A57" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C57" s="57">
         <v>96</v>
       </c>
       <c r="D57" s="59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="17.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B58" s="23"/>
       <c r="C58" s="55"/>
@@ -6727,7 +6974,7 @@
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B59" s="23"/>
       <c r="C59" s="57"/>
@@ -6735,7 +6982,7 @@
     </row>
     <row r="60" spans="1:4" ht="19.5" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B60" s="23"/>
       <c r="C60" s="57"/>
@@ -6743,7 +6990,7 @@
     </row>
     <row r="61" spans="1:4" ht="18.75" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B61" s="23"/>
       <c r="C61" s="57"/>
@@ -6751,7 +6998,7 @@
     </row>
     <row r="62" spans="1:4" ht="17.45" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B62" s="32"/>
       <c r="C62" s="57"/>
@@ -6759,7 +7006,7 @@
     </row>
     <row r="63" spans="1:4" ht="18" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B63" s="23"/>
       <c r="C63" s="57"/>
@@ -6767,7 +7014,7 @@
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B64" s="53"/>
       <c r="C64" s="57"/>
@@ -6775,7 +7022,7 @@
     </row>
     <row r="65" spans="1:4" ht="32.25" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B65" s="52"/>
       <c r="C65" s="57"/>
@@ -6783,21 +7030,21 @@
     </row>
     <row r="66" spans="1:4" ht="18" customHeight="1">
       <c r="A66" s="28" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B66" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C66" s="67" t="s">
         <v>197</v>
       </c>
       <c r="D66" s="67" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.95">
       <c r="A67" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B67" s="10"/>
       <c r="C67" s="57"/>
@@ -6805,7 +7052,7 @@
     </row>
     <row r="68" spans="1:4" ht="15.95">
       <c r="A68" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B68" s="10"/>
       <c r="C68" s="57"/>
@@ -6813,7 +7060,7 @@
     </row>
     <row r="69" spans="1:4" ht="15.95">
       <c r="A69" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B69" s="10"/>
       <c r="C69" s="57"/>
@@ -6821,7 +7068,7 @@
     </row>
     <row r="70" spans="1:4" ht="15.95">
       <c r="A70" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B70" s="10"/>
       <c r="C70" s="57"/>
@@ -6829,7 +7076,7 @@
     </row>
     <row r="71" spans="1:4" ht="15.95">
       <c r="A71" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B71" s="10"/>
       <c r="C71" s="57"/>
@@ -6837,7 +7084,7 @@
     </row>
     <row r="72" spans="1:4" ht="15.95">
       <c r="A72" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B72" s="10"/>
       <c r="C72" s="57"/>
@@ -6845,7 +7092,7 @@
     </row>
     <row r="73" spans="1:4" ht="15.95">
       <c r="A73" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B73" s="10"/>
       <c r="C73" s="57"/>
@@ -6853,7 +7100,7 @@
     </row>
     <row r="74" spans="1:4" ht="15.95">
       <c r="A74" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B74" s="10">
         <v>1536</v>
@@ -6863,7 +7110,7 @@
     </row>
     <row r="75" spans="1:4" ht="15.95">
       <c r="A75" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B75" s="10"/>
       <c r="C75" s="57"/>
@@ -6871,7 +7118,7 @@
     </row>
     <row r="76" spans="1:4" ht="15.95">
       <c r="A76" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B76" s="10"/>
       <c r="C76" s="57"/>
@@ -6879,7 +7126,7 @@
     </row>
     <row r="77" spans="1:4" ht="15.95">
       <c r="A77" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="57"/>
@@ -6887,7 +7134,7 @@
     </row>
     <row r="78" spans="1:4" ht="15.95">
       <c r="A78" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B78" s="10"/>
       <c r="C78" s="57"/>
@@ -6895,7 +7142,7 @@
     </row>
     <row r="79" spans="1:4" ht="15.95">
       <c r="A79" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B79" s="10"/>
       <c r="C79" s="57"/>
@@ -6903,7 +7150,7 @@
     </row>
     <row r="80" spans="1:4" ht="15.95">
       <c r="A80" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B80" s="23"/>
       <c r="C80" s="57"/>
@@ -6911,7 +7158,7 @@
     </row>
     <row r="81" spans="1:4" ht="15.95">
       <c r="A81" s="43" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B81" s="32"/>
       <c r="C81" s="57"/>
@@ -6919,7 +7166,7 @@
     </row>
     <row r="82" spans="1:4" ht="15.95">
       <c r="A82" s="51" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B82" s="32"/>
       <c r="C82" s="57"/>
@@ -6927,7 +7174,7 @@
     </row>
     <row r="83" spans="1:4" ht="15.95">
       <c r="A83" s="22" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B83" s="23"/>
       <c r="C83" s="57"/>
@@ -6935,7 +7182,7 @@
     </row>
     <row r="84" spans="1:4" ht="15.95">
       <c r="A84" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B84" s="10"/>
       <c r="C84" s="57"/>
@@ -6943,7 +7190,7 @@
     </row>
     <row r="85" spans="1:4" ht="15.95">
       <c r="A85" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B85" s="10"/>
       <c r="C85" s="57"/>
@@ -6951,10 +7198,10 @@
     </row>
     <row r="86" spans="1:4" ht="15.95">
       <c r="A86" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C86" s="10">
         <v>10</v>
@@ -6965,10 +7212,10 @@
     </row>
     <row r="87" spans="1:4" ht="15.95">
       <c r="A87" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C87" s="10">
         <v>10</v>
@@ -6979,7 +7226,7 @@
     </row>
     <row r="88" spans="1:4" ht="15.95">
       <c r="A88" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B88" s="10"/>
       <c r="C88" s="57"/>
@@ -6987,7 +7234,7 @@
     </row>
     <row r="89" spans="1:4" ht="15.95">
       <c r="A89" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="57"/>
@@ -6995,7 +7242,7 @@
     </row>
     <row r="90" spans="1:4" ht="15.95">
       <c r="A90" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="57"/>
@@ -7003,7 +7250,7 @@
     </row>
     <row r="91" spans="1:4" ht="15.95">
       <c r="A91" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B91" s="10">
         <v>96000</v>
@@ -7017,7 +7264,7 @@
     </row>
     <row r="92" spans="1:4" ht="15.95">
       <c r="A92" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B92" s="10">
         <v>96000</v>
@@ -7031,19 +7278,19 @@
     </row>
     <row r="93" spans="1:4" ht="15.95">
       <c r="A93" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B93" s="70">
         <v>51000</v>
       </c>
       <c r="C93" s="57"/>
       <c r="D93" s="71" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.95">
       <c r="A94" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B94" s="73"/>
       <c r="C94" s="56"/>
@@ -7051,7 +7298,7 @@
     </row>
     <row r="95" spans="1:4" ht="15.95">
       <c r="A95" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B95" s="26"/>
       <c r="C95" s="56"/>
@@ -7059,7 +7306,7 @@
     </row>
     <row r="96" spans="1:4" ht="15.95">
       <c r="A96" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B96" s="35"/>
       <c r="C96" s="10"/>
@@ -7067,7 +7314,7 @@
     </row>
     <row r="97" spans="1:9" ht="15.95">
       <c r="A97" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
@@ -7075,7 +7322,7 @@
     </row>
     <row r="98" spans="1:9" ht="15.95">
       <c r="A98" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B98" s="10">
         <v>1200</v>
@@ -7089,7 +7336,7 @@
     </row>
     <row r="99" spans="1:9" ht="15.95">
       <c r="A99" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
@@ -7097,7 +7344,7 @@
     </row>
     <row r="100" spans="1:9" ht="15.95">
       <c r="A100" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
@@ -7105,7 +7352,7 @@
     </row>
     <row r="101" spans="1:9" ht="15.95">
       <c r="A101" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
@@ -7113,7 +7360,7 @@
     </row>
     <row r="102" spans="1:9" ht="15.95">
       <c r="A102" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
@@ -7137,11 +7384,430 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F102" xr:uid="{63A7BD36-8D88-3742-A4AC-48B0AFB67141}"/>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1F4FD9-0BA8-D443-A42F-4E5E606C52A0}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="62.42578125" defaultRowHeight="24"/>
+  <cols>
+    <col min="1" max="1" width="134.85546875" style="82" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" style="82" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" style="82" customWidth="1"/>
+    <col min="4" max="4" width="26" style="82" customWidth="1"/>
+    <col min="5" max="5" width="47.7109375" style="82" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="82" customWidth="1"/>
+    <col min="7" max="7" width="33.85546875" style="82" customWidth="1"/>
+    <col min="8" max="16384" width="62.42578125" style="82"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="75">
+      <c r="A1" s="80" t="s">
+        <v>399</v>
+      </c>
+      <c r="B1" s="103" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" s="104"/>
+      <c r="D1" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" s="103" t="s">
+        <v>353</v>
+      </c>
+      <c r="F1" s="104"/>
+      <c r="G1" s="81" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="50.1">
+      <c r="A2" s="83" t="s">
+        <v>400</v>
+      </c>
+      <c r="B2" s="84" t="s">
+        <v>369</v>
+      </c>
+      <c r="C2" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="84" t="s">
+        <v>401</v>
+      </c>
+      <c r="E2" s="84" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="G2" s="85" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="24.95">
+      <c r="A3" s="86" t="s">
+        <v>402</v>
+      </c>
+      <c r="B3" s="87" t="s">
+        <v>403</v>
+      </c>
+      <c r="C3" s="88">
+        <v>94</v>
+      </c>
+      <c r="D3" s="89">
+        <v>40</v>
+      </c>
+      <c r="E3" s="87" t="s">
+        <v>404</v>
+      </c>
+      <c r="F3" s="88">
+        <v>93</v>
+      </c>
+      <c r="G3" s="89">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="24.95">
+      <c r="A4" s="86" t="s">
+        <v>405</v>
+      </c>
+      <c r="B4" s="89" t="s">
+        <v>406</v>
+      </c>
+      <c r="C4" s="90">
+        <v>95</v>
+      </c>
+      <c r="D4" s="91">
+        <v>40</v>
+      </c>
+      <c r="E4" s="89" t="s">
+        <v>407</v>
+      </c>
+      <c r="F4" s="90">
+        <v>94</v>
+      </c>
+      <c r="G4" s="91">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="24.95">
+      <c r="A5" s="86" t="s">
+        <v>408</v>
+      </c>
+      <c r="B5" s="92" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="93">
+        <v>94</v>
+      </c>
+      <c r="D5" s="94">
+        <v>60</v>
+      </c>
+      <c r="E5" s="92" t="s">
+        <v>409</v>
+      </c>
+      <c r="F5" s="93">
+        <v>91</v>
+      </c>
+      <c r="G5" s="94">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="24.95">
+      <c r="A6" s="95" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" s="96">
+        <v>99</v>
+      </c>
+      <c r="D6" s="97" t="s">
+        <v>273</v>
+      </c>
+      <c r="E6" s="89" t="s">
+        <v>382</v>
+      </c>
+      <c r="F6" s="89">
+        <v>98</v>
+      </c>
+      <c r="G6" s="97" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="24.95">
+      <c r="A7" s="95" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" s="89" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7" s="98">
+        <v>99</v>
+      </c>
+      <c r="D7" s="97" t="s">
+        <v>273</v>
+      </c>
+      <c r="E7" s="89" t="s">
+        <v>383</v>
+      </c>
+      <c r="F7" s="89">
+        <v>98</v>
+      </c>
+      <c r="G7" s="97" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="24.95">
+      <c r="A8" s="99" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" s="92" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="93">
+        <v>90</v>
+      </c>
+      <c r="D8" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="E8" s="89" t="s">
+        <v>384</v>
+      </c>
+      <c r="F8" s="89">
+        <v>96</v>
+      </c>
+      <c r="G8" s="94" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="47.25">
+      <c r="A9" s="86" t="s">
+        <v>303</v>
+      </c>
+      <c r="B9" s="89"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="100" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" s="89"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="100" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="75">
+      <c r="A12" s="80" t="s">
+        <v>410</v>
+      </c>
+      <c r="B12" s="103" t="s">
+        <v>193</v>
+      </c>
+      <c r="C12" s="104"/>
+      <c r="D12" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="E12" s="103" t="s">
+        <v>353</v>
+      </c>
+      <c r="F12" s="104"/>
+      <c r="G12" s="81" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="50.1">
+      <c r="A13" s="83" t="s">
+        <v>400</v>
+      </c>
+      <c r="B13" s="84" t="s">
+        <v>369</v>
+      </c>
+      <c r="C13" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="84" t="s">
+        <v>401</v>
+      </c>
+      <c r="E13" s="84" t="s">
+        <v>196</v>
+      </c>
+      <c r="F13" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13" s="85" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="24.95">
+      <c r="A14" s="86" t="s">
+        <v>402</v>
+      </c>
+      <c r="B14" s="87" t="s">
+        <v>411</v>
+      </c>
+      <c r="C14" s="88">
+        <v>95</v>
+      </c>
+      <c r="D14" s="89">
+        <v>61</v>
+      </c>
+      <c r="E14" s="87" t="s">
+        <v>404</v>
+      </c>
+      <c r="F14" s="88">
+        <v>93</v>
+      </c>
+      <c r="G14" s="89">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="24.95">
+      <c r="A15" s="86" t="s">
+        <v>405</v>
+      </c>
+      <c r="B15" s="89" t="s">
+        <v>406</v>
+      </c>
+      <c r="C15" s="90">
+        <v>95</v>
+      </c>
+      <c r="D15" s="91">
+        <v>61</v>
+      </c>
+      <c r="E15" s="89" t="s">
+        <v>407</v>
+      </c>
+      <c r="F15" s="90">
+        <v>94</v>
+      </c>
+      <c r="G15" s="91">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="24.95">
+      <c r="A16" s="86" t="s">
+        <v>408</v>
+      </c>
+      <c r="B16" s="92" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="93">
+        <v>94</v>
+      </c>
+      <c r="D16" s="94">
+        <v>60</v>
+      </c>
+      <c r="E16" s="92" t="s">
+        <v>412</v>
+      </c>
+      <c r="F16" s="93">
+        <v>91</v>
+      </c>
+      <c r="G16" s="94">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="24.95">
+      <c r="A17" s="95" t="s">
+        <v>271</v>
+      </c>
+      <c r="B17" s="89" t="s">
+        <v>272</v>
+      </c>
+      <c r="C17" s="96">
+        <v>99</v>
+      </c>
+      <c r="D17" s="97" t="s">
+        <v>273</v>
+      </c>
+      <c r="E17" s="89" t="s">
+        <v>382</v>
+      </c>
+      <c r="F17" s="89">
+        <v>98</v>
+      </c>
+      <c r="G17" s="97" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="24.95">
+      <c r="A18" s="95" t="s">
+        <v>274</v>
+      </c>
+      <c r="B18" s="89" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18" s="98">
+        <v>99</v>
+      </c>
+      <c r="D18" s="97" t="s">
+        <v>273</v>
+      </c>
+      <c r="E18" s="89" t="s">
+        <v>383</v>
+      </c>
+      <c r="F18" s="89">
+        <v>98</v>
+      </c>
+      <c r="G18" s="97" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="24.95">
+      <c r="A19" s="99" t="s">
+        <v>276</v>
+      </c>
+      <c r="B19" s="92" t="s">
+        <v>277</v>
+      </c>
+      <c r="C19" s="93">
+        <v>90</v>
+      </c>
+      <c r="D19" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="E19" s="89" t="s">
+        <v>384</v>
+      </c>
+      <c r="F19" s="89">
+        <v>96</v>
+      </c>
+      <c r="G19" s="94" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="47.25">
+      <c r="A20" s="86" t="s">
+        <v>303</v>
+      </c>
+      <c r="B20" s="89"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="100" t="s">
+        <v>302</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="100" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="E12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8EE6899-576B-F44E-A189-C616F2524B03}">
   <dimension ref="A1:C46"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
@@ -7153,10 +7819,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60">
       <c r="A1" s="50" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>194</v>
@@ -7167,34 +7833,34 @@
         <v>195</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C2" s="40"/>
     </row>
     <row r="3" spans="1:3" ht="18.95" hidden="1">
       <c r="A3" s="22" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:3" ht="15.95" hidden="1">
       <c r="A4" s="2" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" ht="15.95" hidden="1">
       <c r="A5" s="2" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="59"/>
     </row>
     <row r="6" spans="1:3" ht="15.95" hidden="1">
       <c r="A6" s="2" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -7211,10 +7877,10 @@
         <v>206</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="C8" s="60" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.95">
@@ -7222,10 +7888,10 @@
         <v>208</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.95" hidden="1">
@@ -7258,14 +7924,14 @@
     </row>
     <row r="14" spans="1:3" ht="15.95" hidden="1">
       <c r="A14" s="2" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="15.95" hidden="1">
       <c r="A15" s="2" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -7324,10 +7990,10 @@
         <v>233</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.95" hidden="1">
@@ -7342,10 +8008,10 @@
         <v>237</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.95">
@@ -7353,10 +8019,10 @@
         <v>239</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.95" hidden="1">
@@ -7403,21 +8069,21 @@
     </row>
     <row r="33" spans="1:3" ht="15.95" hidden="1">
       <c r="A33" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B33" s="47"/>
       <c r="C33" s="57"/>
     </row>
     <row r="34" spans="1:3" ht="15.95" hidden="1">
       <c r="A34" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B34" s="47"/>
       <c r="C34" s="57"/>
     </row>
     <row r="35" spans="1:3" ht="15.95" hidden="1">
       <c r="A35" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B35" s="47"/>
       <c r="C35" s="57"/>
@@ -7431,82 +8097,82 @@
     </row>
     <row r="37" spans="1:3" ht="18.95">
       <c r="A37" s="29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="63"/>
     </row>
     <row r="38" spans="1:3" ht="15.95" hidden="1">
       <c r="A38" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B38" s="48"/>
       <c r="C38" s="64"/>
     </row>
     <row r="39" spans="1:3" ht="15.95" hidden="1">
       <c r="A39" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="64"/>
     </row>
     <row r="40" spans="1:3" ht="15.95">
       <c r="A40" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.95">
       <c r="A41" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.95" hidden="1">
       <c r="A42" s="22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
     </row>
     <row r="43" spans="1:3" ht="15.95" hidden="1">
       <c r="A43" s="22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B43" s="45"/>
       <c r="C43" s="15"/>
     </row>
     <row r="44" spans="1:3" ht="15.95" hidden="1">
       <c r="A44" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
     <row r="45" spans="1:3" ht="15.95">
       <c r="A45" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.95" hidden="1">
       <c r="A46" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -7516,7 +8182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA07167-CEB4-F64B-93AF-8A8BA2B4D0FF}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
@@ -7528,115 +8194,115 @@
   <sheetData>
     <row r="1" spans="1:4" ht="81">
       <c r="A1" s="76" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="C1" s="78" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21.95">
       <c r="A2" s="74" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="B2" s="75" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="C2" s="75" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21.95">
       <c r="A3" s="74" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="B3" s="75" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="21.95">
       <c r="A4" s="74" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="B4" s="79" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="C4" s="79" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21.95">
       <c r="A5" s="74" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="B5" s="79" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="C5" s="79" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="21.95">
       <c r="A6" s="74" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="B6" s="75" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="21.95">
       <c r="A7" s="74" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="B7" s="75" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="C7" s="75" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="D7" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="21.95">
       <c r="A8" s="74" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="B8" s="75" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C8" s="75" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="D8" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="21.95">
       <c r="A9" s="74" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="B9" s="75" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="C9" s="75" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="D9" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="21.95">
       <c r="A10" s="74" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="B10" s="75">
         <v>26000</v>
@@ -7647,7 +8313,7 @@
     </row>
     <row r="11" spans="1:4" ht="21.95">
       <c r="A11" s="74" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="B11" s="75">
         <v>445</v>
@@ -7658,7 +8324,7 @@
     </row>
     <row r="12" spans="1:4" ht="21.95">
       <c r="A12" s="74" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="B12" s="75">
         <v>96000</v>
@@ -7669,7 +8335,7 @@
     </row>
     <row r="13" spans="1:4" ht="21.95">
       <c r="A13" s="74" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="B13" s="75">
         <v>400000</v>
@@ -7680,7 +8346,7 @@
     </row>
     <row r="14" spans="1:4" ht="21.95">
       <c r="A14" s="74" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="B14" s="75">
         <v>200000</v>

--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="637" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39540F41-77DD-4392-B620-9ED377082040}"/>
+  <xr:revisionPtr revIDLastSave="700" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A4293EA-2E13-47A4-B2A5-638E54C39306}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="600" windowWidth="36000" windowHeight="19740" firstSheet="2" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19740" firstSheet="3" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="480">
   <si>
     <t>number</t>
   </si>
@@ -668,13 +668,13 @@
     <t>Global data shm</t>
   </si>
   <si>
-    <t>AppSec</t>
+    <t>AppControl</t>
   </si>
   <si>
     <t>1700 CPS /940 Mbps</t>
   </si>
   <si>
-    <t>AppSec (ASC enabled)</t>
+    <t>AppControl (ASC enabled)</t>
   </si>
   <si>
     <t>3500 CPS / 1950 Mbps</t>
@@ -683,79 +683,79 @@
     <t>* Need Additional Port Pair</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec + AppQOS with ASC enabled </t>
+    <t xml:space="preserve">AppControl + AppQOS with ASC enabled </t>
   </si>
   <si>
     <t>1620 CPS /911 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec + IDP-Recommended policy </t>
+    <t xml:space="preserve">AppControl + IDP-Recommended policy </t>
   </si>
   <si>
     <t>875 CPS / 490 Mbps</t>
   </si>
   <si>
-    <t>AppSec + IDP-Enterprise Rec policy</t>
+    <t>AppControl + IDP-Enterprise Rec policy</t>
   </si>
   <si>
     <t>280 CPS / 160 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec + SecIntel </t>
+    <t xml:space="preserve">AppControl + SecIntel </t>
   </si>
   <si>
     <t>1570 CPS / 894 Mbps</t>
   </si>
   <si>
-    <t>AppSec + SkyATP -Block mode</t>
+    <t>AppControl + AAMW -Block mode</t>
   </si>
   <si>
     <t>556 CPS / 318 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec+ UTM EWF(100% cache) </t>
+    <t xml:space="preserve">AppControl+ UTM EWF(100% cache) </t>
   </si>
   <si>
     <t>1596 CPS /903 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec+ UTM NG-WF(100% cache) </t>
+    <t xml:space="preserve">AppControl+ UTM NG-WF(100% cache) </t>
   </si>
   <si>
     <t>1579 CPS / 893 Mbps</t>
   </si>
   <si>
-    <t>AppSec + UTM SAV</t>
+    <t>AppControl + UTM SAV</t>
   </si>
   <si>
     <t>381 CPS / 211 Mbps</t>
   </si>
   <si>
-    <t>AppSec + SecIntel+ IDP-Rec + UTM EWF</t>
+    <t>AppControl + SecIntel+ IDP-Rec + UTM EWF</t>
   </si>
   <si>
     <t>796 CPS / 440 Mbps</t>
   </si>
   <si>
-    <t>AppSec + SecIntel+ IDP-Rec + SkyATP Block</t>
+    <t>AppControl + SecIntel+ IDP-Rec + AAMW Block</t>
   </si>
   <si>
     <t>448 CPS / 237 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec + SecIntel+ IDP-Rec + UTM EWF + SkyATP Block </t>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + UTM EWF + AAMW Block </t>
   </si>
   <si>
     <t>428 CPS / 228 Mbps</t>
   </si>
   <si>
-    <t>AppSec + SecIntel+ IDP-Rec + UTM EWF + UTM SAV</t>
+    <t>AppControl + SecIntel+ IDP-Rec + UTM EWF + UTM SAV</t>
   </si>
   <si>
     <t>307 CPS / 165 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec + SecIntel+ IDP-Rec + SkyATP Block + DNS </t>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + AAMW Block + DNS </t>
   </si>
   <si>
     <t>444 CPS / 234 Mbps</t>
@@ -764,61 +764,61 @@
     <t xml:space="preserve">HTTPS Throughput via CPS Method (Payload: 64KB) </t>
   </si>
   <si>
-    <t>AppSec + TCP Proxy</t>
+    <t>AppControl + TCP Proxy</t>
   </si>
   <si>
     <t>420 CPS / 240 Mbps</t>
   </si>
   <si>
-    <t>AppSec + SSL(TLS1.2)</t>
+    <t>AppControl + SSL(TLS1.2)</t>
   </si>
   <si>
     <t>190 CPS / 110 Mbps</t>
   </si>
   <si>
-    <t>AppSec + SSL(TLS1.3)</t>
+    <t>AppControl + SSL(TLS1.3)</t>
   </si>
   <si>
     <t>125 CPS / 66 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec + SSL+ IDP-Recommended policy </t>
+    <t xml:space="preserve">AppControl + SSL+ IDP-Recommended policy </t>
   </si>
   <si>
     <t>165 CPS / 91 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec + SSL+ IDP-Enterprise Rec policy </t>
+    <t xml:space="preserve">AppControl + SSL+ IDP-Enterprise Rec policy </t>
   </si>
   <si>
     <t>55 CPS / 30 Mbps</t>
   </si>
   <si>
-    <t>AppSec + SSL + SkyATP Block</t>
+    <t>AppControl + SSL + AAMW Block</t>
   </si>
   <si>
     <t>141 CPS / 85 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec + SSL + SecIntel + IDP-Rec </t>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP-Rec </t>
   </si>
   <si>
     <t>164 CPS / 91 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec + SSL + SecIntel + IDP Rec + UTM EWF </t>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + UTM EWF </t>
   </si>
   <si>
     <t>149 CPS / 86 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec + SSL + SecIntel + IDP Rec + SkyATP Block </t>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + AAMW Block </t>
   </si>
   <si>
     <t>123 CPS / 74 Mbps</t>
   </si>
   <si>
-    <t>AppSec + SSL + SecIntel + IDP Rec + UTM EWF + SkyATP Block</t>
+    <t>AppControl + SSL + SecIntel + IDP Rec + UTM EWF + AAMW Block</t>
   </si>
   <si>
     <t>119 CPS / 71 Mbps</t>
@@ -834,7 +834,7 @@
     <t>Sessions</t>
   </si>
   <si>
-    <t>Firewall + AppSec(Unified policy)</t>
+    <t>Firewall + AppControl(Unified policy)</t>
   </si>
   <si>
     <t>10600 TPS / 3995 Mbps</t>
@@ -843,10 +843,10 @@
     <t>*100 Sessions</t>
   </si>
   <si>
-    <t>AppSec + IDP-Recommended policy template</t>
-  </si>
-  <si>
-    <t>AppSec + IDP-Rec + UTM EWF(100% cache)</t>
+    <t>AppControl + IDP-Recommended policy template</t>
+  </si>
+  <si>
+    <t>AppControl + IDP-Rec + UTM EWF(100% cache)</t>
   </si>
   <si>
     <t>650 TPS / 256 Mbps</t>
@@ -861,10 +861,10 @@
     <t xml:space="preserve">IPv6 Firewall TCP CPS </t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec with ASC enabled CPS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppSec CPS </t>
+    <t xml:space="preserve">AppControl with ASC enabled CPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl CPS </t>
   </si>
   <si>
     <t>UTM EWF-100% cache</t>
@@ -873,13 +873,13 @@
     <t>UTM- SAV</t>
   </si>
   <si>
-    <t xml:space="preserve">AppSec + TCPProxy </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppSec + SSL(TLS1.2) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppSec + SSL(TLS1.3) </t>
+    <t xml:space="preserve">AppControl + TCPProxy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL(TLS1.2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL(TLS1.3) </t>
   </si>
   <si>
     <t xml:space="preserve">UDP/IPSec Throughput </t>
@@ -1089,13 +1089,13 @@
     <t>Max FW HTTP concurrent Session capacity</t>
   </si>
   <si>
-    <t>Max AppSec Sessions(unified policy)</t>
+    <t>Max AppControl Sessions(unified policy)</t>
   </si>
   <si>
     <t>MAX IDP(Rec policy) Sessions capacity</t>
   </si>
   <si>
-    <t>PR 1954327</t>
+    <t>80K</t>
   </si>
   <si>
     <t>Max UTM-EWF Sessions capacity</t>
@@ -1284,6 +1284,9 @@
   </si>
   <si>
     <t>200K</t>
+  </si>
+  <si>
+    <t>96K</t>
   </si>
   <si>
     <t>Max UTM- EWF Sessions capacity</t>
@@ -1325,7 +1328,7 @@
     <t>Global data shm / Comments</t>
   </si>
   <si>
-    <t>AppSec - HTTP Throughput (64KB)</t>
+    <t>AppControl - HTTP Throughput (64KB)</t>
   </si>
   <si>
     <t>1650 CPS / 920 Mbps</t>
@@ -1334,7 +1337,7 @@
     <t>2000 CPS / 1350 Mbps</t>
   </si>
   <si>
-    <t>AppSec - HTTP  CPS (64B)</t>
+    <t>AppControl - HTTP  CPS (64B)</t>
   </si>
   <si>
     <t>2400 CPS</t>
@@ -1343,7 +1346,7 @@
     <t>3000 CPS</t>
   </si>
   <si>
-    <t>AppSec + SSL(TLS1.2) - HTTPS Throughput (64KB)</t>
+    <t>AppControl + SSL(TLS1.2) - HTTPS Throughput (64KB)</t>
   </si>
   <si>
     <t>240 CPS / 140 Mbps</t>
@@ -1386,6 +1389,44 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Release: 25.4X300-D10-202606040154.0-EVO
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>1650  CPS / 920 Mbps</t>
+  </si>
+  <si>
+    <t>170 CPS / 96 Mbps</t>
+  </si>
+  <si>
+    <t>AppControl + SSL(TLS1.2) - HTTPS Throughput (64B)</t>
+  </si>
+  <si>
+    <t>300 CPS</t>
+  </si>
+  <si>
+    <t>There are spikes seen, expected is 370 CPS. Ravi is checking if dpdk upgrade has caused any issues and it is applicable to all ssl cases.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
@@ -1410,13 +1451,13 @@
     <t xml:space="preserve">Basic Firewall </t>
   </si>
   <si>
-    <t>Firewall+ AppSec(unified policy) with ASC enabled</t>
-  </si>
-  <si>
-    <t>Firewall+ AppSec(unified policy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firewall+ IPv6 AppSec(Unified policy) </t>
+    <t>Firewall+ AppControl(unified policy) with ASC enabled</t>
+  </si>
+  <si>
+    <t>Firewall+ AppControl(unified policy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firewall+ IPv6 AppControl(Unified policy) </t>
   </si>
   <si>
     <t>1000 CPS, 570 Mbps</t>
@@ -1431,10 +1472,22 @@
     <t>CPU: 82, Global data shm: 84</t>
   </si>
   <si>
-    <t>AppSec + UTM Avira-Light mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppSec + UTM Avira- Heavy mode </t>
+    <t>AppControl + SkyATP -Block mode</t>
+  </si>
+  <si>
+    <t>AppControl + UTM Avira-Light mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + UTM Avira- Heavy mode </t>
+  </si>
+  <si>
+    <t>AppControl + SecIntel+ IDP-Rec + SkyATP Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + UTM EWF + SkyATP Block </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + SkyATP Block + DNS </t>
   </si>
   <si>
     <t>215 CPS, 125 Mbps</t>
@@ -1453,6 +1506,15 @@
   </si>
   <si>
     <t>CPU: 70, Global data shm: 64</t>
+  </si>
+  <si>
+    <t>AppControl + SSL + SkyATP Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + SkyATP Block </t>
+  </si>
+  <si>
+    <t>AppControl + SSL + SecIntel + IDP Rec + UTM EWF + SkyATP Block</t>
   </si>
   <si>
     <t>11000 CPS</t>
@@ -1591,7 +1653,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1761,6 +1823,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2027,7 +2102,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2309,16 +2384,34 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4878,10 +4971,10 @@
       <c r="A1" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="102"/>
+      <c r="C1" s="110"/>
       <c r="D1" s="36" t="s">
         <v>194</v>
       </c>
@@ -6008,13 +6101,11 @@
       <c r="A93" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B93" s="70">
-        <v>51000</v>
+      <c r="B93" s="52" t="s">
+        <v>341</v>
       </c>
       <c r="C93" s="57"/>
-      <c r="D93" s="71" t="s">
-        <v>341</v>
-      </c>
+      <c r="D93" s="71"/>
     </row>
     <row r="94" spans="1:4" ht="15.95">
       <c r="A94" s="2" t="s">
@@ -6163,10 +6254,10 @@
       <c r="A1" s="50" t="s">
         <v>352</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="109" t="s">
         <v>353</v>
       </c>
-      <c r="C1" s="102"/>
+      <c r="C1" s="110"/>
       <c r="D1" s="36" t="s">
         <v>194</v>
       </c>
@@ -7280,17 +7371,15 @@
       <c r="A93" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B93" s="70">
-        <v>51000</v>
+      <c r="B93" s="52" t="s">
+        <v>397</v>
       </c>
       <c r="C93" s="57"/>
-      <c r="D93" s="71" t="s">
-        <v>341</v>
-      </c>
+      <c r="D93" s="71"/>
     </row>
     <row r="94" spans="1:4" ht="15.95">
       <c r="A94" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B94" s="73"/>
       <c r="C94" s="56"/>
@@ -7298,7 +7387,7 @@
     </row>
     <row r="95" spans="1:4" ht="15.95">
       <c r="A95" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B95" s="26"/>
       <c r="C95" s="56"/>
@@ -7393,11 +7482,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1F4FD9-0BA8-D443-A42F-4E5E606C52A0}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="62.42578125" defaultRowHeight="24"/>
   <cols>
-    <col min="1" max="1" width="134.85546875" style="82" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" style="82" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="162.5703125" style="82" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" style="82" customWidth="1"/>
     <col min="3" max="3" width="29.140625" style="82" customWidth="1"/>
     <col min="4" max="4" width="26" style="82" customWidth="1"/>
     <col min="5" max="5" width="47.7109375" style="82" customWidth="1"/>
@@ -7408,26 +7497,26 @@
   <sheetData>
     <row r="1" spans="1:7" ht="75">
       <c r="A1" s="80" t="s">
-        <v>399</v>
-      </c>
-      <c r="B1" s="103" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" s="107" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="104"/>
+      <c r="C1" s="108"/>
       <c r="D1" s="81" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="103" t="s">
+      <c r="E1" s="107" t="s">
         <v>353</v>
       </c>
-      <c r="F1" s="104"/>
+      <c r="F1" s="108"/>
       <c r="G1" s="81" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="50.1">
       <c r="A2" s="83" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B2" s="84" t="s">
         <v>369</v>
@@ -7436,7 +7525,7 @@
         <v>197</v>
       </c>
       <c r="D2" s="84" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E2" s="84" t="s">
         <v>196</v>
@@ -7450,10 +7539,10 @@
     </row>
     <row r="3" spans="1:7" ht="24.95">
       <c r="A3" s="86" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B3" s="87" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C3" s="88">
         <v>94</v>
@@ -7462,7 +7551,7 @@
         <v>40</v>
       </c>
       <c r="E3" s="87" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F3" s="88">
         <v>93</v>
@@ -7473,10 +7562,10 @@
     </row>
     <row r="4" spans="1:7" ht="24.95">
       <c r="A4" s="86" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B4" s="89" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C4" s="90">
         <v>95</v>
@@ -7485,7 +7574,7 @@
         <v>40</v>
       </c>
       <c r="E4" s="89" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F4" s="90">
         <v>94</v>
@@ -7496,7 +7585,7 @@
     </row>
     <row r="5" spans="1:7" ht="24.95">
       <c r="A5" s="86" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B5" s="92" t="s">
         <v>234</v>
@@ -7508,7 +7597,7 @@
         <v>60</v>
       </c>
       <c r="E5" s="92" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F5" s="93">
         <v>91</v>
@@ -7586,7 +7675,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="47.25">
+    <row r="9" spans="1:7" ht="28.5" customHeight="1">
       <c r="A9" s="86" t="s">
         <v>303</v>
       </c>
@@ -7603,26 +7692,26 @@
     </row>
     <row r="12" spans="1:7" ht="75">
       <c r="A12" s="80" t="s">
-        <v>410</v>
-      </c>
-      <c r="B12" s="103" t="s">
+        <v>411</v>
+      </c>
+      <c r="B12" s="107" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="104"/>
+      <c r="C12" s="108"/>
       <c r="D12" s="81" t="s">
         <v>194</v>
       </c>
-      <c r="E12" s="103" t="s">
+      <c r="E12" s="107" t="s">
         <v>353</v>
       </c>
-      <c r="F12" s="104"/>
+      <c r="F12" s="108"/>
       <c r="G12" s="81" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="50.1">
       <c r="A13" s="83" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B13" s="84" t="s">
         <v>369</v>
@@ -7631,7 +7720,7 @@
         <v>197</v>
       </c>
       <c r="D13" s="84" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E13" s="84" t="s">
         <v>196</v>
@@ -7645,10 +7734,10 @@
     </row>
     <row r="14" spans="1:7" ht="24.95">
       <c r="A14" s="86" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B14" s="87" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C14" s="88">
         <v>95</v>
@@ -7657,7 +7746,7 @@
         <v>61</v>
       </c>
       <c r="E14" s="87" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F14" s="88">
         <v>93</v>
@@ -7668,10 +7757,10 @@
     </row>
     <row r="15" spans="1:7" ht="24.95">
       <c r="A15" s="86" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B15" s="89" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C15" s="90">
         <v>95</v>
@@ -7680,7 +7769,7 @@
         <v>61</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F15" s="90">
         <v>94</v>
@@ -7691,7 +7780,7 @@
     </row>
     <row r="16" spans="1:7" ht="24.95">
       <c r="A16" s="86" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B16" s="92" t="s">
         <v>234</v>
@@ -7703,7 +7792,7 @@
         <v>60</v>
       </c>
       <c r="E16" s="92" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F16" s="93">
         <v>91</v>
@@ -7781,7 +7870,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="47.25">
+    <row r="20" spans="1:7" ht="24.95">
       <c r="A20" s="86" t="s">
         <v>303</v>
       </c>
@@ -7796,12 +7885,148 @@
         <v>302</v>
       </c>
     </row>
+    <row r="23" spans="1:7" ht="70.5">
+      <c r="A23" s="101" t="s">
+        <v>414</v>
+      </c>
+      <c r="B23" s="107" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="108"/>
+      <c r="D23" s="81" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="47.25">
+      <c r="A24" s="83" t="s">
+        <v>401</v>
+      </c>
+      <c r="B24" s="84" t="s">
+        <v>369</v>
+      </c>
+      <c r="C24" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" s="84" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="23.25">
+      <c r="A25" s="86" t="s">
+        <v>403</v>
+      </c>
+      <c r="B25" s="87" t="s">
+        <v>415</v>
+      </c>
+      <c r="C25" s="88">
+        <v>94</v>
+      </c>
+      <c r="D25" s="89">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="23.25">
+      <c r="A26" s="86" t="s">
+        <v>406</v>
+      </c>
+      <c r="B26" s="89" t="s">
+        <v>407</v>
+      </c>
+      <c r="C26" s="90">
+        <v>95</v>
+      </c>
+      <c r="D26" s="91">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="23.25">
+      <c r="A27" s="86" t="s">
+        <v>409</v>
+      </c>
+      <c r="B27" s="92" t="s">
+        <v>416</v>
+      </c>
+      <c r="C27" s="93">
+        <v>75</v>
+      </c>
+      <c r="D27" s="94">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="23.25">
+      <c r="A28" s="95" t="s">
+        <v>271</v>
+      </c>
+      <c r="B28" s="89" t="s">
+        <v>272</v>
+      </c>
+      <c r="C28" s="96">
+        <v>99</v>
+      </c>
+      <c r="D28" s="97" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="23.25">
+      <c r="A29" s="95" t="s">
+        <v>274</v>
+      </c>
+      <c r="B29" s="89" t="s">
+        <v>275</v>
+      </c>
+      <c r="C29" s="98">
+        <v>99</v>
+      </c>
+      <c r="D29" s="97" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="23.25">
+      <c r="A30" s="99" t="s">
+        <v>276</v>
+      </c>
+      <c r="B30" s="92" t="s">
+        <v>277</v>
+      </c>
+      <c r="C30" s="93">
+        <v>90</v>
+      </c>
+      <c r="D30" s="97" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="23.25">
+      <c r="A31" s="86" t="s">
+        <v>303</v>
+      </c>
+      <c r="B31" s="103"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="105"/>
+    </row>
+    <row r="32" spans="1:7" ht="23.25">
+      <c r="A32" s="102" t="s">
+        <v>417</v>
+      </c>
+      <c r="B32" s="106" t="s">
+        <v>418</v>
+      </c>
+      <c r="C32" s="106">
+        <v>75</v>
+      </c>
+      <c r="D32" s="106">
+        <v>60</v>
+      </c>
+      <c r="E32" s="82" t="s">
+        <v>419</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="E12:F12"/>
+    <mergeCell ref="B23:C23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7819,7 +8044,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60">
       <c r="A1" s="50" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>353</v>
@@ -7839,28 +8064,28 @@
     </row>
     <row r="3" spans="1:3" ht="18.95" hidden="1">
       <c r="A3" s="22" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:3" ht="15.95" hidden="1">
       <c r="A4" s="2" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" ht="15.95" hidden="1">
       <c r="A5" s="2" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="59"/>
     </row>
     <row r="6" spans="1:3" ht="15.95" hidden="1">
       <c r="A6" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -7877,10 +8102,10 @@
         <v>206</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C8" s="60" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.95">
@@ -7888,10 +8113,10 @@
         <v>208</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.95" hidden="1">
@@ -7903,7 +8128,7 @@
     </row>
     <row r="11" spans="1:3" ht="15.95" hidden="1">
       <c r="A11" s="2" t="s">
-        <v>212</v>
+        <v>429</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="59"/>
@@ -7924,14 +8149,14 @@
     </row>
     <row r="14" spans="1:3" ht="15.95" hidden="1">
       <c r="A14" s="2" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="15.95" hidden="1">
       <c r="A15" s="2" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -7945,14 +8170,14 @@
     </row>
     <row r="17" spans="1:3" ht="15.95" hidden="1">
       <c r="A17" s="2" t="s">
-        <v>222</v>
+        <v>432</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" ht="15.95" hidden="1">
       <c r="A18" s="2" t="s">
-        <v>224</v>
+        <v>433</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
@@ -7966,7 +8191,7 @@
     </row>
     <row r="20" spans="1:3" ht="15.95" hidden="1">
       <c r="A20" s="43" t="s">
-        <v>228</v>
+        <v>434</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -7990,10 +8215,10 @@
         <v>233</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.95" hidden="1">
@@ -8008,10 +8233,10 @@
         <v>237</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.95">
@@ -8019,15 +8244,15 @@
         <v>239</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.95" hidden="1">
       <c r="A27" s="2" t="s">
-        <v>241</v>
+        <v>441</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="57"/>
@@ -8048,14 +8273,14 @@
     </row>
     <row r="30" spans="1:3" ht="15.95" hidden="1">
       <c r="A30" s="2" t="s">
-        <v>247</v>
+        <v>442</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="57"/>
     </row>
     <row r="31" spans="1:3" ht="15.95" hidden="1">
       <c r="A31" s="2" t="s">
-        <v>249</v>
+        <v>443</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="57"/>
@@ -8121,10 +8346,10 @@
         <v>263</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.95">
@@ -8132,10 +8357,10 @@
         <v>264</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.95" hidden="1">
@@ -8164,10 +8389,10 @@
         <v>268</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.95" hidden="1">
@@ -8194,32 +8419,32 @@
   <sheetData>
     <row r="1" spans="1:4" ht="81">
       <c r="A1" s="76" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="C1" s="78" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21.95">
       <c r="A2" s="74" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="B2" s="75" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="C2" s="75" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21.95">
       <c r="A3" s="74" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="B3" s="75" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="C3" s="75" t="s">
         <v>277</v>
@@ -8227,82 +8452,82 @@
     </row>
     <row r="4" spans="1:4" ht="21.95">
       <c r="A4" s="74" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="B4" s="79" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="C4" s="79" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21.95">
       <c r="A5" s="74" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="B5" s="79" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="C5" s="79" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="21.95">
       <c r="A6" s="74" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="B6" s="75" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="21.95">
       <c r="A7" s="74" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="B7" s="75" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="C7" s="75" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="D7" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="21.95">
       <c r="A8" s="74" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="B8" s="75" t="s">
         <v>364</v>
       </c>
       <c r="C8" s="75" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="D8" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="21.95">
       <c r="A9" s="74" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B9" s="75" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="C9" s="75" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="D9" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="21.95">
       <c r="A10" s="74" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="B10" s="75">
         <v>26000</v>
@@ -8313,7 +8538,7 @@
     </row>
     <row r="11" spans="1:4" ht="21.95">
       <c r="A11" s="74" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="B11" s="75">
         <v>445</v>
@@ -8324,7 +8549,7 @@
     </row>
     <row r="12" spans="1:4" ht="21.95">
       <c r="A12" s="74" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="B12" s="75">
         <v>96000</v>
@@ -8335,7 +8560,7 @@
     </row>
     <row r="13" spans="1:4" ht="21.95">
       <c r="A13" s="74" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="B13" s="75">
         <v>400000</v>
@@ -8346,7 +8571,7 @@
     </row>
     <row r="14" spans="1:4" ht="21.95">
       <c r="A14" s="74" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="B14" s="75">
         <v>200000</v>
@@ -8361,118 +8586,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cb645b5b-9a36-43da-96bf-ab72ec91ddff" xsi:nil="true"/>
-    <SharedWithUsers xmlns="0b7692b1-2532-40e4-a300-4d7fced4a07a">
-      <UserInfo>
-        <DisplayName>Anand Thulasiram</DisplayName>
-        <AccountId>2178</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Vipin Kumar</DisplayName>
-        <AccountId>64</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sunil  Masineni</DisplayName>
-        <AccountId>5184</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Geetha B K</DisplayName>
-        <AccountId>63</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jagadeesh Rajashekharaiah</DisplayName>
-        <AccountId>13</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Deepasri Chittala</DisplayName>
-        <AccountId>4801</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Weibin Chen</DisplayName>
-        <AccountId>317</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Xiaochen Tang</DisplayName>
-        <AccountId>910</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Anand Antur</DisplayName>
-        <AccountId>670</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Venu Maya</DisplayName>
-        <AccountId>33</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Chockalingam Balasubramanian</DisplayName>
-        <AccountId>682</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Neetu Rathee</DisplayName>
-        <AccountId>4709</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Prasad Shroff</DisplayName>
-        <AccountId>4142</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kedar Dhuru</DisplayName>
-        <AccountId>3907</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sarvesh Batta</DisplayName>
-        <AccountId>21</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Shankar Satyamurthy</DisplayName>
-        <AccountId>3116</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>David Passamonte</DisplayName>
-        <AccountId>5189</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010092711BC64AAEC84E9EF800276F1AD52C" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba397f1440615f1339f1f20b24e67478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9bf4d24f-a117-48f7-91e1-2035a8c734fd" xmlns:ns3="0b7692b1-2532-40e4-a300-4d7fced4a07a" xmlns:ns4="cb645b5b-9a36-43da-96bf-ab72ec91ddff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74828cee37efa74eab9b700f6a6651cc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
@@ -8720,18 +8833,130 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cb645b5b-9a36-43da-96bf-ab72ec91ddff" xsi:nil="true"/>
+    <SharedWithUsers xmlns="0b7692b1-2532-40e4-a300-4d7fced4a07a">
+      <UserInfo>
+        <DisplayName>Anand Thulasiram</DisplayName>
+        <AccountId>2178</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Vipin Kumar</DisplayName>
+        <AccountId>64</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sunil  Masineni</DisplayName>
+        <AccountId>5184</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Geetha B K</DisplayName>
+        <AccountId>63</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jagadeesh Rajashekharaiah</DisplayName>
+        <AccountId>13</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Deepasri Chittala</DisplayName>
+        <AccountId>4801</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Weibin Chen</DisplayName>
+        <AccountId>317</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Xiaochen Tang</DisplayName>
+        <AccountId>910</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Anand Antur</DisplayName>
+        <AccountId>670</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Venu Maya</DisplayName>
+        <AccountId>33</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Chockalingam Balasubramanian</DisplayName>
+        <AccountId>682</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Neetu Rathee</DisplayName>
+        <AccountId>4709</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Prasad Shroff</DisplayName>
+        <AccountId>4142</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kedar Dhuru</DisplayName>
+        <AccountId>3907</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sarvesh Batta</DisplayName>
+        <AccountId>21</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Shankar Satyamurthy</DisplayName>
+        <AccountId>3116</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>David Passamonte</DisplayName>
+        <AccountId>5189</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}"/>
 </file>
--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="700" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A4293EA-2E13-47A4-B2A5-638E54C39306}"/>
+  <xr:revisionPtr revIDLastSave="746" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{291A0975-2E99-8E40-9791-D0260B6B2859}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19740" firstSheet="3" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21340" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="488">
   <si>
     <t>number</t>
   </si>
@@ -668,157 +668,82 @@
     <t>Global data shm</t>
   </si>
   <si>
-    <t>AppControl</t>
-  </si>
-  <si>
     <t>1700 CPS /940 Mbps</t>
   </si>
   <si>
-    <t>AppControl (ASC enabled)</t>
-  </si>
-  <si>
     <t>3500 CPS / 1950 Mbps</t>
   </si>
   <si>
     <t>* Need Additional Port Pair</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl + AppQOS with ASC enabled </t>
-  </si>
-  <si>
     <t>1620 CPS /911 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl + IDP-Recommended policy </t>
-  </si>
-  <si>
     <t>875 CPS / 490 Mbps</t>
   </si>
   <si>
-    <t>AppControl + IDP-Enterprise Rec policy</t>
-  </si>
-  <si>
     <t>280 CPS / 160 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl + SecIntel </t>
-  </si>
-  <si>
     <t>1570 CPS / 894 Mbps</t>
   </si>
   <si>
-    <t>AppControl + AAMW -Block mode</t>
-  </si>
-  <si>
     <t>556 CPS / 318 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl+ UTM EWF(100% cache) </t>
-  </si>
-  <si>
     <t>1596 CPS /903 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl+ UTM NG-WF(100% cache) </t>
-  </si>
-  <si>
     <t>1579 CPS / 893 Mbps</t>
   </si>
   <si>
-    <t>AppControl + UTM SAV</t>
-  </si>
-  <si>
     <t>381 CPS / 211 Mbps</t>
   </si>
   <si>
-    <t>AppControl + SecIntel+ IDP-Rec + UTM EWF</t>
-  </si>
-  <si>
     <t>796 CPS / 440 Mbps</t>
   </si>
   <si>
-    <t>AppControl + SecIntel+ IDP-Rec + AAMW Block</t>
-  </si>
-  <si>
     <t>448 CPS / 237 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + UTM EWF + AAMW Block </t>
-  </si>
-  <si>
     <t>428 CPS / 228 Mbps</t>
   </si>
   <si>
-    <t>AppControl + SecIntel+ IDP-Rec + UTM EWF + UTM SAV</t>
-  </si>
-  <si>
     <t>307 CPS / 165 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + AAMW Block + DNS </t>
-  </si>
-  <si>
     <t>444 CPS / 234 Mbps</t>
   </si>
   <si>
     <t xml:space="preserve">HTTPS Throughput via CPS Method (Payload: 64KB) </t>
   </si>
   <si>
-    <t>AppControl + TCP Proxy</t>
-  </si>
-  <si>
     <t>420 CPS / 240 Mbps</t>
   </si>
   <si>
-    <t>AppControl + SSL(TLS1.2)</t>
-  </si>
-  <si>
     <t>190 CPS / 110 Mbps</t>
   </si>
   <si>
-    <t>AppControl + SSL(TLS1.3)</t>
-  </si>
-  <si>
     <t>125 CPS / 66 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl + SSL+ IDP-Recommended policy </t>
-  </si>
-  <si>
     <t>165 CPS / 91 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl + SSL+ IDP-Enterprise Rec policy </t>
-  </si>
-  <si>
     <t>55 CPS / 30 Mbps</t>
   </si>
   <si>
-    <t>AppControl + SSL + AAMW Block</t>
-  </si>
-  <si>
     <t>141 CPS / 85 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP-Rec </t>
-  </si>
-  <si>
     <t>164 CPS / 91 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + UTM EWF </t>
-  </si>
-  <si>
     <t>149 CPS / 86 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + AAMW Block </t>
-  </si>
-  <si>
     <t>123 CPS / 74 Mbps</t>
-  </si>
-  <si>
-    <t>AppControl + SSL + SecIntel + IDP Rec + UTM EWF + AAMW Block</t>
   </si>
   <si>
     <t>119 CPS / 71 Mbps</t>
@@ -831,24 +756,9 @@
 TPS/MBPS</t>
   </si>
   <si>
-    <t>Sessions</t>
-  </si>
-  <si>
-    <t>Firewall + AppControl(Unified policy)</t>
-  </si>
-  <si>
-    <t>10600 TPS / 3995 Mbps</t>
-  </si>
-  <si>
     <t>*100 Sessions</t>
   </si>
   <si>
-    <t>AppControl + IDP-Recommended policy template</t>
-  </si>
-  <si>
-    <t>AppControl + IDP-Rec + UTM EWF(100% cache)</t>
-  </si>
-  <si>
     <t>650 TPS / 256 Mbps</t>
   </si>
   <si>
@@ -861,27 +771,12 @@
     <t xml:space="preserve">IPv6 Firewall TCP CPS </t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl with ASC enabled CPS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl CPS </t>
-  </si>
-  <si>
     <t>UTM EWF-100% cache</t>
   </si>
   <si>
     <t>UTM- SAV</t>
   </si>
   <si>
-    <t xml:space="preserve">AppControl + TCPProxy </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SSL(TLS1.2) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SSL(TLS1.3) </t>
-  </si>
-  <si>
     <t xml:space="preserve">UDP/IPSec Throughput </t>
   </si>
   <si>
@@ -1068,15 +963,9 @@
     <t>BGP- Total RIB Routes/Size</t>
   </si>
   <si>
-    <t>300K</t>
-  </si>
-  <si>
     <t>BGP- Total FIB Routes/Size</t>
   </si>
   <si>
-    <t>150K</t>
-  </si>
-  <si>
     <t>BGP: Peers</t>
   </si>
   <si>
@@ -1089,13 +978,7 @@
     <t>Max FW HTTP concurrent Session capacity</t>
   </si>
   <si>
-    <t>Max AppControl Sessions(unified policy)</t>
-  </si>
-  <si>
     <t>MAX IDP(Rec policy) Sessions capacity</t>
-  </si>
-  <si>
-    <t>80K</t>
   </si>
   <si>
     <t>Max UTM-EWF Sessions capacity</t>
@@ -1166,9 +1049,6 @@
     <t>** Has to be re-tested with more ports</t>
   </si>
   <si>
-    <t>1920 CPS/ 1025 Mbos</t>
-  </si>
-  <si>
     <t>1085 CPS / 622 Mbps</t>
   </si>
   <si>
@@ -1184,115 +1064,308 @@
     <t>1700  CPS / 940 Mbps</t>
   </si>
   <si>
+    <t>875 CPS / 500 Mbps</t>
+  </si>
+  <si>
+    <t>540 CPS / 310 Mbps</t>
+  </si>
+  <si>
+    <t>530 CPS / 300 Mbps</t>
+  </si>
+  <si>
+    <t>Throughput</t>
+  </si>
+  <si>
+    <t>583 CPS / 321 Mbps</t>
+  </si>
+  <si>
+    <t>252 CPS / 140 Mbps</t>
+  </si>
+  <si>
+    <t>150 CPS / 82 Mbps</t>
+  </si>
+  <si>
+    <t>211 CPS / 122 Mbps</t>
+  </si>
+  <si>
+    <t>79 CPS / 41 Mbps</t>
+  </si>
+  <si>
+    <t>170 CPS / 105 Mbps</t>
+  </si>
+  <si>
+    <t>ß</t>
+  </si>
+  <si>
+    <t>200 CPS / 115 Mbps</t>
+  </si>
+  <si>
+    <t>140 CPS / 84 Mbps</t>
+  </si>
+  <si>
+    <t>135 CPS / 81 Mbps</t>
+  </si>
+  <si>
+    <t>CPS</t>
+  </si>
+  <si>
+    <t>Sessions</t>
+  </si>
+  <si>
+    <t>744.1 KPPS/500 Mbps</t>
+  </si>
+  <si>
+    <t>735.6 KPPS/2195 Mbps</t>
+  </si>
+  <si>
+    <t>634.9 KPPS/7812 Mbps</t>
+  </si>
+  <si>
+    <t>731.6 KPPS/2183 Mbps</t>
+  </si>
+  <si>
+    <t>661.2 KPPS / 656 Mbps</t>
+  </si>
+  <si>
+    <t>648.3 KPPS / 1934 Mbps</t>
+  </si>
+  <si>
+    <t>762.4 KPPS/2274 Mbps</t>
+  </si>
+  <si>
+    <t>702.1 KPPS / 2095 Mbps</t>
+  </si>
+  <si>
+    <t>568.4 KPPS/ 1696 Mbps</t>
+  </si>
+  <si>
+    <t>514.9 KPPS / 1537 Mbps</t>
+  </si>
+  <si>
+    <t>414.6 KPPS / 1238 Mbps</t>
+  </si>
+  <si>
+    <t>722.2 KPPS/2155 Mbps</t>
+  </si>
+  <si>
+    <t>400K</t>
+  </si>
+  <si>
+    <t>200K</t>
+  </si>
+  <si>
+    <t>Max UTM- EWF Sessions capacity</t>
+  </si>
+  <si>
+    <t>Max UTM- NG-WF Sessions capacity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Release: 25.4X300-202604130112.0-EVO
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Testcase Description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic Firewall </t>
+  </si>
+  <si>
+    <t>1000 CPS, 570 Mbps</t>
+  </si>
+  <si>
+    <t>CPU:82, Global data shm: 84</t>
+  </si>
+  <si>
+    <t>350 CPS, 200 Mbps</t>
+  </si>
+  <si>
+    <t>CPU: 82, Global data shm: 84</t>
+  </si>
+  <si>
+    <t>215 CPS, 125 Mbps</t>
+  </si>
+  <si>
+    <t>CPU: 81, Global data shm: 76</t>
+  </si>
+  <si>
+    <t>190 CPS, 110 Mbps</t>
+  </si>
+  <si>
+    <t>CPU: 75, Global data shm: 75</t>
+  </si>
+  <si>
+    <t>60 CPS, 34 Mbps</t>
+  </si>
+  <si>
+    <t>CPU: 70, Global data shm: 64</t>
+  </si>
+  <si>
+    <t>11000 CPS</t>
+  </si>
+  <si>
+    <t>CPU: 80, Global data shm: 84</t>
+  </si>
+  <si>
+    <t>2800 CPS</t>
+  </si>
+  <si>
+    <t>CPU: 81, Global Data shm: 81</t>
+  </si>
+  <si>
+    <t>230 CPS</t>
+  </si>
+  <si>
+    <t>CPU: 38, Global Data Shm: 78</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Release: 25.4X300-202604130112.0-EVO
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Testcase Description</t>
+    </r>
+  </si>
+  <si>
+    <t>SRX440</t>
+  </si>
+  <si>
+    <t>SRX400</t>
+  </si>
+  <si>
+    <t>Firewall throughput (IMIX)</t>
+  </si>
+  <si>
+    <t>675.6 KPPS/2016 Mbps</t>
+  </si>
+  <si>
+    <t>601.8 KPPS / 1796 Mbps</t>
+  </si>
+  <si>
+    <t>Firewall throughput (1518B)</t>
+  </si>
+  <si>
+    <t>595.2 KPPS/7324 Mbps</t>
+  </si>
+  <si>
+    <t>IPSec VPN throughput (IMIX)</t>
+  </si>
+  <si>
+    <t>PR 1954277</t>
+  </si>
+  <si>
+    <t>IPSec VPN throughput (1400B)</t>
+  </si>
+  <si>
+    <t>Application security performance (CPS)</t>
+  </si>
+  <si>
+    <t>2077 CPS / 1169 Mbps</t>
+  </si>
+  <si>
+    <t>1611 CPS /891 Mbps</t>
+  </si>
+  <si>
+    <t>Next-generation firewall (CPS)</t>
+  </si>
+  <si>
+    <t>1039 CPS / 596 Mbps</t>
+  </si>
+  <si>
+    <t>829 CPS / 464 Mbps</t>
+  </si>
+  <si>
+    <t>Next-generation firewall performance is measured with firewall, application security, and IPS enabled</t>
+  </si>
+  <si>
+    <t>Secure Web Access Firewall (CPS)</t>
+  </si>
+  <si>
+    <t>762 CPS / 421 Mbps</t>
+  </si>
+  <si>
+    <t>Secure Web Access firewall performance is measured with firewall, application security, IPS, SecIntel, and URL filtering enabled</t>
+  </si>
+  <si>
+    <t>Advanced Threat (CPS)</t>
+  </si>
+  <si>
+    <t>507 CPS / 287 Mbps</t>
+  </si>
+  <si>
+    <t>405 CPS / 216 Mbps</t>
+  </si>
+  <si>
+    <t>Advanced Threat performance is measured with Firewall, Application Security, IPS, SecIntel, URL Filtering and Malware Protection enabled</t>
+  </si>
+  <si>
+    <t>Connections per second (64B)</t>
+  </si>
+  <si>
+    <t>SSL connections per second</t>
+  </si>
+  <si>
+    <t>Maximum concurrent sessions (IPv4 or IPv6)</t>
+  </si>
+  <si>
+    <t>Route table size (RIB) (IPv4)</t>
+  </si>
+  <si>
+    <t>Route table size (FIB) (IPv4)</t>
+  </si>
+  <si>
+    <t>RE Memory</t>
+  </si>
+  <si>
+    <t>300K</t>
+  </si>
+  <si>
+    <t>150K</t>
+  </si>
+  <si>
     <t>1800 CPS / 1000 Mbps</t>
   </si>
   <si>
-    <t>875 CPS / 500 Mbps</t>
-  </si>
-  <si>
-    <t>540 CPS / 310 Mbps</t>
-  </si>
-  <si>
-    <t>530 CPS / 300 Mbps</t>
+    <t>535 CPS / 305 Mbps</t>
   </si>
   <si>
     <t>340 CPS / 190 Mbps</t>
-  </si>
-  <si>
-    <t>535 CPS / 305 Mbps</t>
-  </si>
-  <si>
-    <t>Throughput</t>
-  </si>
-  <si>
-    <t>583 CPS / 321 Mbps</t>
-  </si>
-  <si>
-    <t>252 CPS / 140 Mbps</t>
-  </si>
-  <si>
-    <t>150 CPS / 82 Mbps</t>
-  </si>
-  <si>
-    <t>211 CPS / 122 Mbps</t>
-  </si>
-  <si>
-    <t>79 CPS / 41 Mbps</t>
-  </si>
-  <si>
-    <t>170 CPS / 105 Mbps</t>
-  </si>
-  <si>
-    <t>ß</t>
-  </si>
-  <si>
-    <t>200 CPS / 115 Mbps</t>
-  </si>
-  <si>
-    <t>140 CPS / 84 Mbps</t>
-  </si>
-  <si>
-    <t>135 CPS / 81 Mbps</t>
-  </si>
-  <si>
-    <t>800 TPS / 315 Mbps</t>
-  </si>
-  <si>
-    <t>CPS</t>
-  </si>
-  <si>
-    <t>744.1 KPPS/500 Mbps</t>
-  </si>
-  <si>
-    <t>735.6 KPPS/2195 Mbps</t>
-  </si>
-  <si>
-    <t>634.9 KPPS/7812 Mbps</t>
-  </si>
-  <si>
-    <t>731.6 KPPS/2183 Mbps</t>
-  </si>
-  <si>
-    <t>661.2 KPPS / 656 Mbps</t>
-  </si>
-  <si>
-    <t>648.3 KPPS / 1934 Mbps</t>
-  </si>
-  <si>
-    <t>762.4 KPPS/2274 Mbps</t>
-  </si>
-  <si>
-    <t>702.1 KPPS / 2095 Mbps</t>
-  </si>
-  <si>
-    <t>568.4 KPPS/ 1696 Mbps</t>
-  </si>
-  <si>
-    <t>514.9 KPPS / 1537 Mbps</t>
-  </si>
-  <si>
-    <t>414.6 KPPS / 1238 Mbps</t>
-  </si>
-  <si>
-    <t>722.2 KPPS/2155 Mbps</t>
-  </si>
-  <si>
-    <t>RE Memory</t>
-  </si>
-  <si>
-    <t>400K</t>
-  </si>
-  <si>
-    <t>200K</t>
-  </si>
-  <si>
-    <t>96K</t>
-  </si>
-  <si>
-    <t>Max UTM- EWF Sessions capacity</t>
-  </si>
-  <si>
-    <t>Max UTM- NG-WF Sessions capacity</t>
   </si>
   <si>
     <r>
@@ -1325,31 +1398,13 @@
     <t>Testcase Description</t>
   </si>
   <si>
+    <t>2400 CPS</t>
+  </si>
+  <si>
     <t>Global data shm / Comments</t>
   </si>
   <si>
-    <t>AppControl - HTTP Throughput (64KB)</t>
-  </si>
-  <si>
     <t>1650 CPS / 920 Mbps</t>
-  </si>
-  <si>
-    <t>2000 CPS / 1350 Mbps</t>
-  </si>
-  <si>
-    <t>AppControl - HTTP  CPS (64B)</t>
-  </si>
-  <si>
-    <t>2400 CPS</t>
-  </si>
-  <si>
-    <t>3000 CPS</t>
-  </si>
-  <si>
-    <t>AppControl + SSL(TLS1.2) - HTTPS Throughput (64KB)</t>
-  </si>
-  <si>
-    <t>240 CPS / 140 Mbps</t>
   </si>
   <si>
     <r>
@@ -1382,7 +1437,178 @@
     <t>1650 CPS/928 Mbps</t>
   </si>
   <si>
+    <t>3000 CPS</t>
+  </si>
+  <si>
+    <t>2000 CPS / 1350 Mbps</t>
+  </si>
+  <si>
+    <t>240 CPS / 140 Mbps</t>
+  </si>
+  <si>
     <t>240 CPS / 139 Mbps</t>
+  </si>
+  <si>
+    <t>1920 CPS/ 1025 Mbos</t>
+  </si>
+  <si>
+    <t>800 TPS / 315 Mbps</t>
+  </si>
+  <si>
+    <t>10600 TPS / 3995 Mbps</t>
+  </si>
+  <si>
+    <t>96K</t>
+  </si>
+  <si>
+    <t>80K</t>
+  </si>
+  <si>
+    <t>AppControl</t>
+  </si>
+  <si>
+    <t>AppControl (ASC enabled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + AppQOS with ASC enabled </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + IDP-Recommended policy </t>
+  </si>
+  <si>
+    <t>AppControl + IDP-Enterprise Rec policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SecIntel </t>
+  </si>
+  <si>
+    <t>AppControl + SkyATP -Block mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl+ UTM EWF(100% cache) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl+ UTM NG-WF(100% cache) </t>
+  </si>
+  <si>
+    <t>AppControl + UTM SAV</t>
+  </si>
+  <si>
+    <t>AppControl + SecIntel+ IDP-Rec + UTM EWF</t>
+  </si>
+  <si>
+    <t>AppControl + SecIntel+ IDP-Rec + SkyATP Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + UTM EWF + SkyATP Block </t>
+  </si>
+  <si>
+    <t>AppControl + SecIntel+ IDP-Rec + UTM EWF + UTM SAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + SkyATP Block + DNS </t>
+  </si>
+  <si>
+    <t>AppControl + TCP Proxy</t>
+  </si>
+  <si>
+    <t>AppControl + SSL(TLS1.2)</t>
+  </si>
+  <si>
+    <t>AppControl + SSL(TLS1.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL+ IDP-Recommended policy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL+ IDP-Enterprise Rec policy </t>
+  </si>
+  <si>
+    <t>AppControl + SSL + SkyATP Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP-Rec </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + UTM EWF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + SkyATP Block </t>
+  </si>
+  <si>
+    <t>AppControl + SSL + SecIntel + IDP Rec + UTM EWF + SkyATP Block</t>
+  </si>
+  <si>
+    <t>Firewall + AppControl(Unified policy)</t>
+  </si>
+  <si>
+    <t>AppControl + IDP-Recommended policy template</t>
+  </si>
+  <si>
+    <t>AppControl + IDP-Rec + UTM EWF(100% cache)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl with ASC enabled CPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl CPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + TCPProxy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL(TLS1.2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL(TLS1.3) </t>
+  </si>
+  <si>
+    <t>Max AppControl Sessions(unified policy)</t>
+  </si>
+  <si>
+    <t>AppControl - HTTP Throughput (64KB)</t>
+  </si>
+  <si>
+    <t>AppControl - HTTP  CPS (64B)</t>
+  </si>
+  <si>
+    <t>AppControl + SSL(TLS1.2) - HTTPS Throughput (64KB)</t>
+  </si>
+  <si>
+    <t>Firewall+ AppControl(unified policy) with ASC enabled</t>
+  </si>
+  <si>
+    <t>Firewall+ AppControl(unified policy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firewall+ IPv6 AppControl(Unified policy) </t>
+  </si>
+  <si>
+    <t>AppControl + UTM Avira-Light mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + UTM Avira- Heavy mode </t>
+  </si>
+  <si>
+    <t>AppControl + AAMW -Block mode</t>
+  </si>
+  <si>
+    <t>AppControl + SecIntel+ IDP-Rec + AAMW Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + UTM EWF + AAMW Block </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + AAMW Block + DNS </t>
+  </si>
+  <si>
+    <t>AppControl + SSL + AAMW Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + AAMW Block </t>
+  </si>
+  <si>
+    <t>AppControl + SSL + SecIntel + IDP Rec + UTM EWF + AAMW Block</t>
   </si>
   <si>
     <r>
@@ -1392,6 +1618,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Release: 25.4X300-D10-202606040154.0-EVO
 </t>
@@ -1402,6 +1629,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -1423,237 +1651,35 @@
     <t>There are spikes seen, expected is 370 CPS. Ravi is checking if dpdk upgrade has caused any issues and it is applicable to all ssl cases.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Release: 25.4X300-202604130112.0-EVO
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Testcase Description</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Basic Firewall </t>
-  </si>
-  <si>
-    <t>Firewall+ AppControl(unified policy) with ASC enabled</t>
-  </si>
-  <si>
-    <t>Firewall+ AppControl(unified policy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firewall+ IPv6 AppControl(Unified policy) </t>
-  </si>
-  <si>
-    <t>1000 CPS, 570 Mbps</t>
-  </si>
-  <si>
-    <t>CPU:82, Global data shm: 84</t>
-  </si>
-  <si>
-    <t>350 CPS, 200 Mbps</t>
-  </si>
-  <si>
-    <t>CPU: 82, Global data shm: 84</t>
-  </si>
-  <si>
-    <t>AppControl + SkyATP -Block mode</t>
-  </si>
-  <si>
-    <t>AppControl + UTM Avira-Light mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + UTM Avira- Heavy mode </t>
-  </si>
-  <si>
-    <t>AppControl + SecIntel+ IDP-Rec + SkyATP Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + UTM EWF + SkyATP Block </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + SkyATP Block + DNS </t>
-  </si>
-  <si>
-    <t>215 CPS, 125 Mbps</t>
-  </si>
-  <si>
-    <t>CPU: 81, Global data shm: 76</t>
-  </si>
-  <si>
-    <t>190 CPS, 110 Mbps</t>
-  </si>
-  <si>
-    <t>CPU: 75, Global data shm: 75</t>
-  </si>
-  <si>
-    <t>60 CPS, 34 Mbps</t>
-  </si>
-  <si>
-    <t>CPU: 70, Global data shm: 64</t>
-  </si>
-  <si>
-    <t>AppControl + SSL + SkyATP Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + SkyATP Block </t>
-  </si>
-  <si>
-    <t>AppControl + SSL + SecIntel + IDP Rec + UTM EWF + SkyATP Block</t>
-  </si>
-  <si>
-    <t>11000 CPS</t>
-  </si>
-  <si>
-    <t>CPU: 80, Global data shm: 84</t>
-  </si>
-  <si>
-    <t>2800 CPS</t>
-  </si>
-  <si>
-    <t>CPU: 81, Global Data shm: 81</t>
-  </si>
-  <si>
-    <t>230 CPS</t>
-  </si>
-  <si>
-    <t>CPU: 38, Global Data Shm: 78</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Release: 25.4X300-202604130112.0-EVO
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Testcase Description</t>
-    </r>
-  </si>
-  <si>
-    <t>SRX440</t>
-  </si>
-  <si>
-    <t>SRX400</t>
-  </si>
-  <si>
-    <t>Firewall throughput (IMIX)</t>
-  </si>
-  <si>
-    <t>675.6 KPPS/2016 Mbps</t>
-  </si>
-  <si>
-    <t>601.8 KPPS / 1796 Mbps</t>
-  </si>
-  <si>
-    <t>Firewall throughput (1518B)</t>
-  </si>
-  <si>
-    <t>595.2 KPPS/7324 Mbps</t>
-  </si>
-  <si>
-    <t>IPSec VPN throughput (IMIX)</t>
-  </si>
-  <si>
-    <t>PR 1954277</t>
-  </si>
-  <si>
-    <t>IPSec VPN throughput (1400B)</t>
-  </si>
-  <si>
-    <t>Application security performance (CPS)</t>
-  </si>
-  <si>
-    <t>2077 CPS / 1169 Mbps</t>
-  </si>
-  <si>
-    <t>1611 CPS /891 Mbps</t>
-  </si>
-  <si>
-    <t>Next-generation firewall (CPS)</t>
-  </si>
-  <si>
-    <t>1039 CPS / 596 Mbps</t>
-  </si>
-  <si>
-    <t>829 CPS / 464 Mbps</t>
-  </si>
-  <si>
-    <t>Next-generation firewall performance is measured with firewall, application security, and IPS enabled</t>
-  </si>
-  <si>
-    <t>Secure Web Access Firewall (CPS)</t>
-  </si>
-  <si>
-    <t>762 CPS / 421 Mbps</t>
-  </si>
-  <si>
-    <t>Secure Web Access firewall performance is measured with firewall, application security, IPS, SecIntel, and URL filtering enabled</t>
-  </si>
-  <si>
-    <t>Advanced Threat (CPS)</t>
-  </si>
-  <si>
-    <t>507 CPS / 287 Mbps</t>
-  </si>
-  <si>
-    <t>405 CPS / 216 Mbps</t>
-  </si>
-  <si>
-    <t>Advanced Threat performance is measured with Firewall, Application Security, IPS, SecIntel, URL Filtering and Malware Protection enabled</t>
-  </si>
-  <si>
-    <t>Connections per second (64B)</t>
-  </si>
-  <si>
-    <t>SSL connections per second</t>
-  </si>
-  <si>
-    <t>Maximum concurrent sessions (IPv4 or IPv6)</t>
-  </si>
-  <si>
-    <t>Route table size (RIB) (IPv4)</t>
-  </si>
-  <si>
-    <t>Route table size (FIB) (IPv4)</t>
+    <t>320 KPPS /954 Mbps</t>
+  </si>
+  <si>
+    <t>340 KPPS / 228 Mbps</t>
+  </si>
+  <si>
+    <t>310 KPPS / 1320 Mbps</t>
+  </si>
+  <si>
+    <t>210 KPPS / 626 Mbps</t>
+  </si>
+  <si>
+    <t>*32 Sessions ( 16Tunnels) - PR 1954277 </t>
+  </si>
+  <si>
+    <t>*32 Sessions ( 16Tunnels) -PR 1954277 </t>
+  </si>
+  <si>
+    <t>*1 session (1 Tunnel) - PR 1954277 </t>
+  </si>
+  <si>
+    <t>315 KPPS / 940 Mbps</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1830,12 +1856,14 @@
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2102,7 +2130,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2325,8 +2353,20 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2396,23 +2436,8 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2433,10 +2458,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2474,7 +2503,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2580,7 +2609,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2722,7 +2751,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2732,15 +2761,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{101F05EA-6A87-7646-9D66-36E81A856E36}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:H94"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="18.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="68" customWidth="1"/>
-    <col min="2" max="2" width="179.42578125" style="68" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="68" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.85546875" style="68"/>
+    <col min="1" max="1" width="15.6640625" style="68" customWidth="1"/>
+    <col min="2" max="2" width="179.5" style="68" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="68" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="68"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
@@ -2766,7 +2795,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
         <v>8</v>
       </c>
@@ -2789,7 +2818,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="68" t="s">
         <v>14</v>
       </c>
@@ -2812,7 +2841,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="68" t="s">
         <v>21</v>
       </c>
@@ -2835,7 +2864,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
         <v>25</v>
       </c>
@@ -2858,7 +2887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="68" t="s">
         <v>26</v>
       </c>
@@ -2881,7 +2910,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="68" t="s">
         <v>28</v>
       </c>
@@ -2907,7 +2936,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="68" t="s">
         <v>32</v>
       </c>
@@ -2933,7 +2962,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
         <v>34</v>
       </c>
@@ -2959,7 +2988,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="68" t="s">
         <v>36</v>
       </c>
@@ -2982,7 +3011,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="68" t="s">
         <v>40</v>
       </c>
@@ -3005,7 +3034,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="68" t="s">
         <v>44</v>
       </c>
@@ -3028,7 +3057,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="68" t="s">
         <v>48</v>
       </c>
@@ -3051,7 +3080,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="68" t="s">
         <v>49</v>
       </c>
@@ -3074,7 +3103,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="68" t="s">
         <v>50</v>
       </c>
@@ -3097,7 +3126,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="68" t="s">
         <v>51</v>
       </c>
@@ -3120,7 +3149,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="68" t="s">
         <v>55</v>
       </c>
@@ -3143,7 +3172,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="68" t="s">
         <v>56</v>
       </c>
@@ -3166,7 +3195,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="68" t="s">
         <v>57</v>
       </c>
@@ -3189,7 +3218,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="68" t="s">
         <v>58</v>
       </c>
@@ -3212,7 +3241,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="68" t="s">
         <v>62</v>
       </c>
@@ -3235,7 +3264,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68" t="s">
         <v>63</v>
       </c>
@@ -3258,7 +3287,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="68" t="s">
         <v>64</v>
       </c>
@@ -3281,7 +3310,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="68" t="s">
         <v>66</v>
       </c>
@@ -3304,7 +3333,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="68" t="s">
         <v>67</v>
       </c>
@@ -3327,7 +3356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="68" t="s">
         <v>68</v>
       </c>
@@ -3350,7 +3379,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="68" t="s">
         <v>71</v>
       </c>
@@ -3373,7 +3402,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="68" t="s">
         <v>72</v>
       </c>
@@ -3396,7 +3425,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="68" t="s">
         <v>73</v>
       </c>
@@ -3419,7 +3448,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="68" t="s">
         <v>76</v>
       </c>
@@ -3442,7 +3471,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="68" t="s">
         <v>77</v>
       </c>
@@ -3465,7 +3494,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="68" t="s">
         <v>78</v>
       </c>
@@ -3488,7 +3517,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="68" t="s">
         <v>81</v>
       </c>
@@ -3511,7 +3540,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="68" t="s">
         <v>82</v>
       </c>
@@ -3534,7 +3563,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="68" t="s">
         <v>83</v>
       </c>
@@ -3557,7 +3586,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="68" t="s">
         <v>85</v>
       </c>
@@ -3580,7 +3609,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="68" t="s">
         <v>86</v>
       </c>
@@ -3603,7 +3632,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="68" t="s">
         <v>87</v>
       </c>
@@ -3626,7 +3655,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="68" t="s">
         <v>89</v>
       </c>
@@ -3649,7 +3678,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="68" t="s">
         <v>90</v>
       </c>
@@ -3672,7 +3701,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="68" t="s">
         <v>91</v>
       </c>
@@ -3698,7 +3727,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="68" t="s">
         <v>94</v>
       </c>
@@ -3724,7 +3753,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="68" t="s">
         <v>95</v>
       </c>
@@ -3750,7 +3779,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="68" t="s">
         <v>96</v>
       </c>
@@ -3767,7 +3796,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="68" t="s">
         <v>101</v>
       </c>
@@ -3784,7 +3813,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="68" t="s">
         <v>102</v>
       </c>
@@ -3801,7 +3830,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="68" t="s">
         <v>103</v>
       </c>
@@ -3818,7 +3847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="68" t="s">
         <v>105</v>
       </c>
@@ -3835,7 +3864,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="68" t="s">
         <v>106</v>
       </c>
@@ -3852,7 +3881,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="68" t="s">
         <v>107</v>
       </c>
@@ -3878,7 +3907,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="68" t="s">
         <v>113</v>
       </c>
@@ -3904,7 +3933,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="68" t="s">
         <v>114</v>
       </c>
@@ -3930,7 +3959,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="68" t="s">
         <v>115</v>
       </c>
@@ -3953,7 +3982,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="68" t="s">
         <v>118</v>
       </c>
@@ -3976,7 +4005,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="68" t="s">
         <v>119</v>
       </c>
@@ -3999,7 +4028,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="68" t="s">
         <v>120</v>
       </c>
@@ -4022,7 +4051,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="68" t="s">
         <v>122</v>
       </c>
@@ -4045,7 +4074,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="68" t="s">
         <v>123</v>
       </c>
@@ -4068,7 +4097,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="68" t="s">
         <v>124</v>
       </c>
@@ -4091,7 +4120,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="68" t="s">
         <v>126</v>
       </c>
@@ -4114,7 +4143,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="68" t="s">
         <v>127</v>
       </c>
@@ -4137,7 +4166,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="68" t="s">
         <v>129</v>
       </c>
@@ -4160,7 +4189,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="68" t="s">
         <v>130</v>
       </c>
@@ -4183,7 +4212,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="68" t="s">
         <v>132</v>
       </c>
@@ -4206,7 +4235,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="68" t="s">
         <v>133</v>
       </c>
@@ -4229,7 +4258,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="68" t="s">
         <v>137</v>
       </c>
@@ -4252,7 +4281,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="68" t="s">
         <v>138</v>
       </c>
@@ -4278,7 +4307,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="68" t="s">
         <v>142</v>
       </c>
@@ -4301,7 +4330,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="68" t="s">
         <v>143</v>
       </c>
@@ -4327,7 +4356,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="68" t="s">
         <v>147</v>
       </c>
@@ -4350,7 +4379,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="68" t="s">
         <v>148</v>
       </c>
@@ -4376,7 +4405,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="68" t="s">
         <v>150</v>
       </c>
@@ -4402,7 +4431,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="68" t="s">
         <v>151</v>
       </c>
@@ -4425,7 +4454,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="68" t="s">
         <v>156</v>
       </c>
@@ -4448,7 +4477,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="68" t="s">
         <v>157</v>
       </c>
@@ -4471,7 +4500,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="68" t="s">
         <v>160</v>
       </c>
@@ -4494,7 +4523,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="68" t="s">
         <v>161</v>
       </c>
@@ -4517,7 +4546,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="68" t="s">
         <v>163</v>
       </c>
@@ -4540,7 +4569,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="68" t="s">
         <v>164</v>
       </c>
@@ -4563,7 +4592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="68" t="s">
         <v>166</v>
       </c>
@@ -4586,7 +4615,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="68" t="s">
         <v>167</v>
       </c>
@@ -4609,7 +4638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="68" t="s">
         <v>169</v>
       </c>
@@ -4632,7 +4661,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="68" t="s">
         <v>171</v>
       </c>
@@ -4649,7 +4678,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="68" t="s">
         <v>174</v>
       </c>
@@ -4666,7 +4695,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="68" t="s">
         <v>175</v>
       </c>
@@ -4689,7 +4718,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="68" t="s">
         <v>178</v>
       </c>
@@ -4712,7 +4741,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="68" t="s">
         <v>179</v>
       </c>
@@ -4735,7 +4764,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="68" t="s">
         <v>181</v>
       </c>
@@ -4758,7 +4787,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="68" t="s">
         <v>182</v>
       </c>
@@ -4781,7 +4810,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="68" t="s">
         <v>184</v>
       </c>
@@ -4804,7 +4833,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="68" t="s">
         <v>185</v>
       </c>
@@ -4827,7 +4856,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="68" t="s">
         <v>188</v>
       </c>
@@ -4850,7 +4879,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="68" t="s">
         <v>189</v>
       </c>
@@ -4873,7 +4902,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="68" t="s">
         <v>191</v>
       </c>
@@ -4958,29 +4987,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC397FCC-74C1-4D09-ACC0-E463BF5527EB}">
   <dimension ref="A1:I106"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="87.85546875" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="87.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="19.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" style="5" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57" customHeight="1">
+    <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="80" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="110"/>
+      <c r="C1" s="81"/>
       <c r="D1" s="36" t="s">
         <v>194</v>
       </c>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="32.25" customHeight="1">
+    <row r="2" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>195</v>
       </c>
@@ -4995,12 +5024,12 @@
       </c>
       <c r="E2" s="11"/>
     </row>
-    <row r="3" spans="1:5" ht="17.25" customHeight="1">
+    <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B3" s="41" t="s">
         <v>199</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>200</v>
       </c>
       <c r="C3" s="15">
         <v>95</v>
@@ -5010,12 +5039,12 @@
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1">
+    <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>201</v>
+        <v>426</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C4" s="15">
         <v>80</v>
@@ -5024,15 +5053,15 @@
         <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>204</v>
+        <v>427</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C5" s="4">
         <v>92</v>
@@ -5042,12 +5071,12 @@
       </c>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>206</v>
+        <v>428</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C6" s="1">
         <v>95</v>
@@ -5057,12 +5086,12 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="7" spans="1:5" ht="14.45" customHeight="1">
+    <row r="7" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>208</v>
+        <v>429</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C7" s="4">
         <v>95</v>
@@ -5071,12 +5100,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.1" customHeight="1">
+    <row r="8" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>210</v>
+        <v>430</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C8" s="4">
         <v>91</v>
@@ -5085,12 +5114,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.95">
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>212</v>
+        <v>467</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C9" s="4">
         <v>96</v>
@@ -5099,12 +5128,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.95">
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>214</v>
+        <v>432</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C10" s="4">
         <v>93</v>
@@ -5113,12 +5142,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.95">
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>216</v>
+        <v>433</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C11" s="4">
         <v>93</v>
@@ -5127,12 +5156,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.95">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>218</v>
+        <v>434</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C12" s="1">
         <v>93</v>
@@ -5141,12 +5170,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.95">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>220</v>
+        <v>435</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C13" s="1">
         <v>94</v>
@@ -5155,12 +5184,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.95">
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>222</v>
+        <v>468</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="C14" s="4">
         <v>95</v>
@@ -5169,12 +5198,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.95">
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>224</v>
+        <v>469</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C15" s="1">
         <v>95</v>
@@ -5183,12 +5212,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.95">
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>226</v>
+        <v>438</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="C16" s="46">
         <v>94</v>
@@ -5197,12 +5226,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.95">
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="43" t="s">
-        <v>228</v>
+        <v>470</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C17" s="7">
         <v>96</v>
@@ -5211,9 +5240,9 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="40.5" customHeight="1">
+    <row r="18" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B18" s="39" t="s">
         <v>196</v>
@@ -5225,12 +5254,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.95">
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
-        <v>231</v>
+        <v>440</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C19" s="27">
         <v>85</v>
@@ -5239,12 +5268,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.95">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>233</v>
+        <v>441</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="C20" s="23">
         <v>90</v>
@@ -5253,12 +5282,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.95">
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>235</v>
+        <v>442</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="C21" s="10">
         <v>92</v>
@@ -5267,12 +5296,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.95">
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>237</v>
+        <v>443</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="C22" s="10">
         <v>90</v>
@@ -5281,12 +5310,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.95">
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>239</v>
+        <v>444</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C23" s="10">
         <v>90</v>
@@ -5295,12 +5324,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.95">
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>241</v>
+        <v>471</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="C24" s="10">
         <v>95</v>
@@ -5309,12 +5338,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.95">
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>243</v>
+        <v>446</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="C25" s="10">
         <v>91</v>
@@ -5323,12 +5352,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.95">
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>245</v>
+        <v>447</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="C26" s="10">
         <v>93</v>
@@ -5337,12 +5366,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.95">
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>247</v>
+        <v>472</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="C27" s="10">
         <v>92</v>
@@ -5351,12 +5380,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.95">
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>249</v>
+        <v>473</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="C28" s="10">
         <v>93</v>
@@ -5365,88 +5394,88 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="39" customHeight="1">
+    <row r="29" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>197</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15.95">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>254</v>
+        <v>450</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="C30" s="47">
         <v>77</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="E30" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15.95">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>257</v>
+        <v>451</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="C31" s="47">
         <v>77</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="E31" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15.95">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>258</v>
+        <v>452</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="C32" s="47">
         <v>77</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="E32" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="17.45" customHeight="1">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>233</v>
+        <v>441</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="C33" s="47">
         <v>93</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="41.25" customHeight="1">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="B34" s="39" t="s">
         <v>196</v>
@@ -5458,9 +5487,9 @@
         <v>198</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.95">
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="B35" s="4">
         <v>20000</v>
@@ -5472,9 +5501,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.95">
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="B36" s="4">
         <v>19330</v>
@@ -5486,9 +5515,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6" customHeight="1">
+    <row r="37" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>263</v>
+        <v>453</v>
       </c>
       <c r="B37" s="4">
         <v>10000</v>
@@ -5500,9 +5529,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.95">
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>264</v>
+        <v>454</v>
       </c>
       <c r="B38" s="4">
         <v>2400</v>
@@ -5514,9 +5543,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.95">
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="B39" s="15">
         <v>2250</v>
@@ -5528,9 +5557,9 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.95">
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="B40" s="45">
         <v>975</v>
@@ -5542,9 +5571,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.95">
+    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>267</v>
+        <v>455</v>
       </c>
       <c r="B41" s="4">
         <v>1550</v>
@@ -5556,9 +5585,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.95">
+    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>268</v>
+        <v>456</v>
       </c>
       <c r="B42" s="4">
         <v>400</v>
@@ -5570,9 +5599,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.95">
+    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>269</v>
+        <v>457</v>
       </c>
       <c r="B43" s="4">
         <v>175</v>
@@ -5584,9 +5613,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="32.25" customHeight="1">
+    <row r="44" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="B44" s="39" t="s">
         <v>196</v>
@@ -5595,434 +5624,434 @@
         <v>197</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="18.600000000000001" customHeight="1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="C45" s="33">
         <v>98</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="17.45" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="C46" s="49">
         <v>98</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="15.95">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="C47" s="23">
         <v>90</v>
       </c>
       <c r="D47" s="57" t="s">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="E47" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="15.95">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>279</v>
+        <v>244</v>
       </c>
       <c r="C48" s="23">
         <v>98</v>
       </c>
       <c r="D48" s="59" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="15.95">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>281</v>
+        <v>246</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="23"/>
       <c r="D49" s="57"/>
     </row>
-    <row r="50" spans="1:4" ht="15.95">
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C50" s="23">
         <v>99</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>284</v>
+        <v>249</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="C51" s="32">
         <v>98</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.6" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>286</v>
+        <v>251</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="C52" s="23">
         <v>99</v>
       </c>
       <c r="D52" s="24"/>
     </row>
-    <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
+    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>288</v>
+        <v>253</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="C53" s="31">
         <v>99</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15.95">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="18" t="s">
-        <v>290</v>
+        <v>255</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="C54" s="23">
         <v>98</v>
       </c>
       <c r="D54" s="59" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15.95">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="19" t="s">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>294</v>
+        <v>259</v>
       </c>
       <c r="C55" s="23">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="C56" s="23">
         <v>99</v>
       </c>
       <c r="D56" s="59" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="15.95">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="C57" s="23">
         <v>98</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="58"/>
       <c r="D58" s="70" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="30" customHeight="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="23"/>
       <c r="D59" s="70" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="23"/>
       <c r="D60" s="70" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="23"/>
       <c r="D61" s="70" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="17.45" customHeight="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="32"/>
       <c r="D62" s="70" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="23"/>
       <c r="D63" s="70" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>308</v>
+        <v>273</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="53"/>
       <c r="D64" s="70" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="32.25" customHeight="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>309</v>
+        <v>274</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="52"/>
       <c r="D65" s="57"/>
     </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
-        <v>310</v>
+        <v>275</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>311</v>
+        <v>276</v>
       </c>
       <c r="C66" s="30" t="s">
         <v>197</v>
       </c>
       <c r="D66" s="67"/>
     </row>
-    <row r="67" spans="1:4" ht="15.95">
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>312</v>
+        <v>277</v>
       </c>
       <c r="B67" s="24"/>
       <c r="C67" s="10"/>
       <c r="D67" s="57"/>
     </row>
-    <row r="68" spans="1:4" ht="15.95">
+    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>313</v>
+        <v>278</v>
       </c>
       <c r="B68" s="24"/>
       <c r="C68" s="10"/>
       <c r="D68" s="57"/>
     </row>
-    <row r="69" spans="1:4" ht="15.95">
+    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
       <c r="B69" s="24"/>
       <c r="C69" s="10"/>
       <c r="D69" s="57"/>
     </row>
-    <row r="70" spans="1:4" ht="15.95">
+    <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>315</v>
+        <v>280</v>
       </c>
       <c r="B70" s="24"/>
       <c r="C70" s="10"/>
       <c r="D70" s="57"/>
     </row>
-    <row r="71" spans="1:4" ht="15.95">
+    <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="B71" s="24"/>
       <c r="C71" s="10"/>
       <c r="D71" s="57"/>
     </row>
-    <row r="72" spans="1:4" ht="15.95">
+    <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>317</v>
+        <v>282</v>
       </c>
       <c r="B72" s="24"/>
       <c r="C72" s="10"/>
       <c r="D72" s="57"/>
     </row>
-    <row r="73" spans="1:4" ht="15.95">
+    <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>318</v>
+        <v>283</v>
       </c>
       <c r="B73" s="24"/>
       <c r="C73" s="10"/>
       <c r="D73" s="57"/>
     </row>
-    <row r="74" spans="1:4" ht="15.95">
+    <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>319</v>
+        <v>284</v>
       </c>
       <c r="B74" s="24"/>
       <c r="C74" s="10"/>
       <c r="D74" s="57"/>
     </row>
-    <row r="75" spans="1:4" ht="15.95">
+    <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="B75" s="24"/>
       <c r="C75" s="10"/>
       <c r="D75" s="57"/>
     </row>
-    <row r="76" spans="1:4" ht="15.95">
+    <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>321</v>
+        <v>286</v>
       </c>
       <c r="B76" s="24"/>
       <c r="C76" s="10"/>
       <c r="D76" s="57"/>
     </row>
-    <row r="77" spans="1:4" ht="15.95">
+    <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="B77" s="24"/>
       <c r="C77" s="10"/>
       <c r="D77" s="57"/>
     </row>
-    <row r="78" spans="1:4" ht="15.95">
+    <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>323</v>
+        <v>288</v>
       </c>
       <c r="B78" s="24"/>
       <c r="C78" s="10"/>
       <c r="D78" s="57"/>
     </row>
-    <row r="79" spans="1:4" ht="15.95">
+    <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>324</v>
+        <v>289</v>
       </c>
       <c r="B79" s="24"/>
       <c r="C79" s="10"/>
       <c r="D79" s="57"/>
     </row>
-    <row r="80" spans="1:4" ht="15.95">
+    <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="B80" s="33"/>
       <c r="C80" s="23"/>
       <c r="D80" s="57"/>
     </row>
-    <row r="81" spans="1:4" ht="15.95">
+    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="43" t="s">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="B81" s="24"/>
       <c r="C81" s="32"/>
       <c r="D81" s="57"/>
     </row>
-    <row r="82" spans="1:4" ht="15.95">
+    <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="51" t="s">
-        <v>327</v>
+        <v>292</v>
       </c>
       <c r="B82" s="24"/>
       <c r="C82" s="32"/>
       <c r="D82" s="57"/>
     </row>
-    <row r="83" spans="1:4" ht="15.95">
+    <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="22" t="s">
-        <v>328</v>
+        <v>293</v>
       </c>
       <c r="B83" s="33"/>
       <c r="C83" s="23"/>
       <c r="D83" s="57"/>
     </row>
-    <row r="84" spans="1:4" ht="15.95">
+    <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>329</v>
+        <v>294</v>
       </c>
       <c r="B84" s="24"/>
       <c r="C84" s="10"/>
       <c r="D84" s="57"/>
     </row>
-    <row r="85" spans="1:4" ht="15.95">
+    <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="B85" s="24"/>
       <c r="C85" s="10"/>
       <c r="D85" s="57"/>
     </row>
-    <row r="86" spans="1:4" ht="15.95">
+    <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>332</v>
+        <v>404</v>
       </c>
       <c r="C86" s="10">
         <v>10</v>
@@ -6031,12 +6060,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15.95">
+    <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>334</v>
+        <v>405</v>
       </c>
       <c r="C87" s="10">
         <v>10</v>
@@ -6045,33 +6074,33 @@
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15.95">
+    <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>335</v>
+        <v>298</v>
       </c>
       <c r="B88" s="24"/>
       <c r="C88" s="10"/>
       <c r="D88" s="57"/>
     </row>
-    <row r="89" spans="1:4" ht="15.95">
+    <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>336</v>
+        <v>299</v>
       </c>
       <c r="B89" s="24"/>
       <c r="C89" s="10"/>
       <c r="D89" s="57"/>
     </row>
-    <row r="90" spans="1:4" ht="15.95">
+    <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>337</v>
+        <v>300</v>
       </c>
       <c r="B90" s="24"/>
       <c r="C90" s="10"/>
       <c r="D90" s="57"/>
     </row>
-    <row r="91" spans="1:4" ht="15.95">
+    <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>338</v>
+        <v>301</v>
       </c>
       <c r="B91" s="10">
         <v>80000</v>
@@ -6083,9 +6112,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15.95">
+    <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>339</v>
+        <v>458</v>
       </c>
       <c r="B92" s="24">
         <v>80000</v>
@@ -6097,19 +6126,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="15.95">
+    <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>340</v>
+        <v>302</v>
       </c>
       <c r="B93" s="52" t="s">
-        <v>341</v>
+        <v>424</v>
       </c>
       <c r="C93" s="57"/>
       <c r="D93" s="71"/>
     </row>
-    <row r="94" spans="1:4" ht="15.95">
+    <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>342</v>
+        <v>303</v>
       </c>
       <c r="B94" s="24">
         <v>32000</v>
@@ -6121,9 +6150,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15.95">
+    <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>343</v>
+        <v>304</v>
       </c>
       <c r="B95" s="24">
         <v>32000</v>
@@ -6135,9 +6164,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15.95">
+    <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
-        <v>344</v>
+        <v>305</v>
       </c>
       <c r="B96" s="34">
         <v>8000</v>
@@ -6149,21 +6178,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.95">
+    <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>345</v>
+        <v>306</v>
       </c>
       <c r="B97" s="72">
         <v>26000</v>
       </c>
       <c r="C97" s="70"/>
       <c r="D97" s="70" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="15.95">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>347</v>
+        <v>308</v>
       </c>
       <c r="B98" s="24">
         <v>1000</v>
@@ -6175,9 +6204,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.95">
+    <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>348</v>
+        <v>309</v>
       </c>
       <c r="B99" s="24">
         <v>300</v>
@@ -6189,43 +6218,43 @@
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.95">
+    <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>349</v>
+        <v>310</v>
       </c>
       <c r="B100" s="16"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
     </row>
-    <row r="101" spans="1:9" ht="15.95">
+    <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>350</v>
+        <v>311</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
     </row>
-    <row r="102" spans="1:9" ht="15.95">
+    <row r="102" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>351</v>
+        <v>312</v>
       </c>
       <c r="B102" s="24"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1">
+    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" ht="15" customHeight="1">
+    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" ht="15" customHeight="1">
+    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" ht="15" customHeight="1">
+    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
@@ -6240,29 +6269,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A7BD36-8D88-3742-A4AC-48B0AFB67141}">
   <dimension ref="A1:I106"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="82.42578125" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="85.1640625" customWidth="1"/>
+    <col min="2" max="2" width="32.5" style="5" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="46.5" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57" customHeight="1">
+    <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="50" t="s">
-        <v>352</v>
-      </c>
-      <c r="B1" s="109" t="s">
-        <v>353</v>
-      </c>
-      <c r="C1" s="110"/>
+        <v>313</v>
+      </c>
+      <c r="B1" s="80" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" s="81"/>
       <c r="D1" s="36" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>195</v>
       </c>
@@ -6276,12 +6305,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.100000000000001" customHeight="1">
+    <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>199</v>
+        <v>425</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>354</v>
+        <v>315</v>
       </c>
       <c r="C3" s="59">
         <v>91</v>
@@ -6290,12 +6319,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16.350000000000001" customHeight="1">
+    <row r="4" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>201</v>
+        <v>426</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="C4" s="4">
         <v>70</v>
@@ -6304,15 +6333,15 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>204</v>
+        <v>427</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>357</v>
+        <v>420</v>
       </c>
       <c r="C5" s="4">
         <v>92</v>
@@ -6321,12 +6350,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>206</v>
+        <v>428</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="C6" s="4">
         <v>94</v>
@@ -6335,12 +6364,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.45" customHeight="1">
+    <row r="7" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>208</v>
+        <v>429</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="C7" s="59">
         <v>96</v>
@@ -6349,12 +6378,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.1" customHeight="1">
+    <row r="8" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>210</v>
+        <v>430</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="C8" s="4">
         <v>90</v>
@@ -6363,12 +6392,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.95">
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>212</v>
+        <v>467</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>361</v>
+        <v>321</v>
       </c>
       <c r="C9" s="59">
         <v>90</v>
@@ -6377,12 +6406,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.95">
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>214</v>
+        <v>432</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>362</v>
+        <v>322</v>
       </c>
       <c r="C10" s="4">
         <v>90</v>
@@ -6391,12 +6420,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.95">
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>216</v>
+        <v>433</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>363</v>
+        <v>406</v>
       </c>
       <c r="C11" s="4">
         <v>92</v>
@@ -6405,12 +6434,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.95">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>218</v>
+        <v>434</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C12" s="59">
         <v>92</v>
@@ -6419,12 +6448,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.95">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>220</v>
+        <v>435</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="C13" s="4">
         <v>90</v>
@@ -6433,12 +6462,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.95">
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>222</v>
+        <v>468</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="C14" s="4">
         <v>90</v>
@@ -6447,12 +6476,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.95">
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>224</v>
+        <v>469</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>366</v>
+        <v>325</v>
       </c>
       <c r="C15" s="4">
         <v>94</v>
@@ -6461,12 +6490,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.95">
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>226</v>
+        <v>438</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="C16" s="4">
         <v>92</v>
@@ -6475,12 +6504,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.95">
+    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="43" t="s">
-        <v>228</v>
+        <v>470</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>368</v>
+        <v>407</v>
       </c>
       <c r="C17" s="7">
         <v>92</v>
@@ -6489,12 +6518,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1">
+    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>369</v>
+        <v>326</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>197</v>
@@ -6503,12 +6532,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.95">
+    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
-        <v>231</v>
+        <v>440</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>370</v>
+        <v>327</v>
       </c>
       <c r="C19" s="55">
         <v>92</v>
@@ -6517,12 +6546,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.95">
+    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>233</v>
+        <v>441</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>371</v>
+        <v>328</v>
       </c>
       <c r="C20" s="57">
         <v>95</v>
@@ -6531,12 +6560,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.95">
+    <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>235</v>
+        <v>442</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>372</v>
+        <v>329</v>
       </c>
       <c r="C21" s="57">
         <v>95</v>
@@ -6545,12 +6574,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.95">
+    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>237</v>
+        <v>443</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>373</v>
+        <v>330</v>
       </c>
       <c r="C22" s="57">
         <v>93</v>
@@ -6559,12 +6588,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.95">
+    <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>239</v>
+        <v>444</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>374</v>
+        <v>331</v>
       </c>
       <c r="C23" s="57">
         <v>92</v>
@@ -6573,12 +6602,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.95">
+    <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>241</v>
+        <v>471</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="C24" s="57">
         <v>92</v>
@@ -6587,15 +6616,15 @@
         <v>67</v>
       </c>
       <c r="F24" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.95">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>243</v>
+        <v>446</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>377</v>
+        <v>334</v>
       </c>
       <c r="C25" s="57">
         <v>92</v>
@@ -6604,12 +6633,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.95">
+    <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>245</v>
+        <v>447</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="C26" s="57">
         <v>90</v>
@@ -6618,12 +6647,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.95">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>247</v>
+        <v>472</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>378</v>
+        <v>335</v>
       </c>
       <c r="C27" s="57">
         <v>90</v>
@@ -6632,12 +6661,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.95">
+    <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>249</v>
+        <v>473</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>379</v>
+        <v>336</v>
       </c>
       <c r="C28" s="57">
         <v>92</v>
@@ -6646,91 +6675,91 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1">
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>369</v>
+        <v>326</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>197</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.95">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>254</v>
+        <v>450</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="C30" s="47">
         <v>68</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="E30" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15.95">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>257</v>
+        <v>451</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="C31" s="47">
         <v>68</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="E31" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15.95">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>258</v>
+        <v>452</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="C32" s="47">
         <v>68</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="E32" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="17.45" customHeight="1">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>233</v>
+        <v>441</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>380</v>
+        <v>421</v>
       </c>
       <c r="C33" s="57">
         <v>92</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>197</v>
@@ -6739,9 +6768,9 @@
         <v>198</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.95">
+    <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="B35" s="48">
         <v>26000</v>
@@ -6753,9 +6782,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.95">
+    <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="B36" s="4">
         <v>25400</v>
@@ -6767,9 +6796,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.6" customHeight="1">
+    <row r="37" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>263</v>
+        <v>453</v>
       </c>
       <c r="B37" s="4">
         <v>13300</v>
@@ -6780,10 +6809,19 @@
       <c r="D37" s="59">
         <v>41</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.95">
+      <c r="F37">
+        <v>320000</v>
+      </c>
+      <c r="G37">
+        <v>340000</v>
+      </c>
+      <c r="H37">
+        <v>310000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>264</v>
+        <v>454</v>
       </c>
       <c r="B38" s="4">
         <v>3200</v>
@@ -6794,10 +6832,22 @@
       <c r="D38" s="59">
         <v>38</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="15.95">
+      <c r="F38">
+        <f>F37*8*373/1000000</f>
+        <v>954.88</v>
+      </c>
+      <c r="G38">
+        <f>G37*8*84/1000000</f>
+        <v>228.48</v>
+      </c>
+      <c r="H38">
+        <f>H37*8*532/1000000</f>
+        <v>1319.36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="B39" s="15">
         <v>2700</v>
@@ -6809,9 +6859,9 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.95">
+    <row r="40" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="B40" s="45">
         <v>1050</v>
@@ -6822,10 +6872,13 @@
       <c r="D40" s="59">
         <v>45</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="15.95">
+      <c r="F40">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>267</v>
+        <v>455</v>
       </c>
       <c r="B41" s="4">
         <v>1810</v>
@@ -6836,10 +6889,14 @@
       <c r="D41" s="59">
         <v>68</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="15.95">
+      <c r="F41">
+        <f>F40*8*373/1000000</f>
+        <v>626.64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>268</v>
+        <v>456</v>
       </c>
       <c r="B42" s="1">
         <v>460</v>
@@ -6850,10 +6907,13 @@
       <c r="D42" s="59">
         <v>79</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="15.95">
+      <c r="F42">
+        <v>315000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>269</v>
+        <v>457</v>
       </c>
       <c r="B43" s="4">
         <v>205</v>
@@ -6864,334 +6924,370 @@
       <c r="D43" s="59">
         <v>81</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1">
+      <c r="F43">
+        <f>F42*8*373/1000000</f>
+        <v>939.96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>369</v>
+        <v>326</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>197</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="18.600000000000001" customHeight="1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>382</v>
+        <v>339</v>
       </c>
       <c r="C45" s="24">
         <v>98</v>
       </c>
       <c r="D45" s="59" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="17.45" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>383</v>
+        <v>340</v>
       </c>
       <c r="C46" s="24">
         <v>98</v>
       </c>
       <c r="D46" s="59" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15.95">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>384</v>
+        <v>341</v>
       </c>
       <c r="C47" s="57">
         <v>96</v>
       </c>
       <c r="D47" s="59" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15.95">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="C48" s="57">
         <v>96</v>
       </c>
       <c r="D48" s="59" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="15.95">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>281</v>
+        <v>246</v>
       </c>
       <c r="B49" s="23"/>
       <c r="C49" s="57"/>
       <c r="D49" s="59"/>
     </row>
-    <row r="50" spans="1:4" ht="15.95">
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>386</v>
+        <v>343</v>
       </c>
       <c r="C50" s="55">
         <v>98</v>
       </c>
       <c r="D50" s="59" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>284</v>
+        <v>249</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>387</v>
+        <v>344</v>
       </c>
       <c r="C51" s="57">
         <v>98</v>
       </c>
       <c r="D51" s="59" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.6" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>286</v>
+        <v>251</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>388</v>
+        <v>345</v>
       </c>
       <c r="C52" s="57">
         <v>99</v>
       </c>
       <c r="D52" s="59" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>288</v>
+        <v>253</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>389</v>
+        <v>346</v>
       </c>
       <c r="C53" s="65">
         <v>99</v>
       </c>
       <c r="D53" s="59" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15.95">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="18" t="s">
-        <v>290</v>
+        <v>255</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>390</v>
+        <v>347</v>
       </c>
       <c r="C54" s="66">
         <v>98</v>
       </c>
       <c r="D54" s="59" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15.95">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="19" t="s">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>391</v>
+        <v>348</v>
       </c>
       <c r="C55" s="66">
         <v>98</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="C56" s="66">
         <v>96</v>
       </c>
       <c r="D56" s="59" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="15.95">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="C57" s="57">
         <v>96</v>
       </c>
       <c r="D57" s="59" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="B58" s="23"/>
-      <c r="C58" s="55"/>
-      <c r="D58" s="59"/>
-    </row>
-    <row r="59" spans="1:4" ht="30" customHeight="1">
+        <v>266</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>481</v>
+      </c>
+      <c r="C58" s="55">
+        <v>78</v>
+      </c>
+      <c r="D58" s="59" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B59" s="23"/>
-      <c r="C59" s="57"/>
-      <c r="D59" s="59"/>
-    </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1">
+        <v>268</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="C59" s="57">
+        <v>77</v>
+      </c>
+      <c r="D59" s="59" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B60" s="23"/>
-      <c r="C60" s="57"/>
-      <c r="D60" s="59"/>
-    </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1">
+        <v>269</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="C60" s="57">
+        <v>79</v>
+      </c>
+      <c r="D60" s="59" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="B61" s="23"/>
       <c r="C61" s="57"/>
-      <c r="D61" s="59"/>
-    </row>
-    <row r="62" spans="1:4" ht="17.45" customHeight="1">
+      <c r="D61" s="59" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B62" s="32"/>
-      <c r="C62" s="57"/>
-      <c r="D62" s="59"/>
-    </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1">
+        <v>271</v>
+      </c>
+      <c r="B62" s="32" t="s">
+        <v>483</v>
+      </c>
+      <c r="C62" s="57">
+        <v>88</v>
+      </c>
+      <c r="D62" s="59" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="B63" s="23"/>
       <c r="C63" s="57"/>
       <c r="D63" s="59"/>
     </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1">
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B64" s="53"/>
-      <c r="C64" s="57"/>
-      <c r="D64" s="59"/>
-    </row>
-    <row r="65" spans="1:4" ht="32.25" customHeight="1">
+        <v>273</v>
+      </c>
+      <c r="B64" s="53" t="s">
+        <v>487</v>
+      </c>
+      <c r="C64" s="57">
+        <v>79</v>
+      </c>
+      <c r="D64" s="59" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>309</v>
+        <v>274</v>
       </c>
       <c r="B65" s="52"/>
       <c r="C65" s="57"/>
       <c r="D65" s="59"/>
     </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
-        <v>310</v>
+        <v>275</v>
       </c>
       <c r="B66" s="30" t="s">
-        <v>311</v>
+        <v>276</v>
       </c>
       <c r="C66" s="67" t="s">
         <v>197</v>
       </c>
       <c r="D66" s="67" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15.95">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>312</v>
+        <v>277</v>
       </c>
       <c r="B67" s="10"/>
       <c r="C67" s="57"/>
       <c r="D67" s="57"/>
     </row>
-    <row r="68" spans="1:4" ht="15.95">
+    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>313</v>
+        <v>278</v>
       </c>
       <c r="B68" s="10"/>
       <c r="C68" s="57"/>
       <c r="D68" s="57"/>
     </row>
-    <row r="69" spans="1:4" ht="15.95">
+    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
       <c r="B69" s="10"/>
       <c r="C69" s="57"/>
       <c r="D69" s="57"/>
     </row>
-    <row r="70" spans="1:4" ht="15.95">
+    <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>315</v>
+        <v>280</v>
       </c>
       <c r="B70" s="10"/>
       <c r="C70" s="57"/>
       <c r="D70" s="57"/>
     </row>
-    <row r="71" spans="1:4" ht="15.95">
+    <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="B71" s="10"/>
       <c r="C71" s="57"/>
       <c r="D71" s="57"/>
     </row>
-    <row r="72" spans="1:4" ht="15.95">
+    <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>317</v>
+        <v>282</v>
       </c>
       <c r="B72" s="10"/>
       <c r="C72" s="57"/>
       <c r="D72" s="57"/>
     </row>
-    <row r="73" spans="1:4" ht="15.95">
+    <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>318</v>
+        <v>283</v>
       </c>
       <c r="B73" s="10"/>
       <c r="C73" s="57"/>
       <c r="D73" s="57"/>
     </row>
-    <row r="74" spans="1:4" ht="15.95">
+    <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>319</v>
+        <v>284</v>
       </c>
       <c r="B74" s="10">
         <v>1536</v>
@@ -7199,100 +7295,100 @@
       <c r="C74" s="57"/>
       <c r="D74" s="57"/>
     </row>
-    <row r="75" spans="1:4" ht="15.95">
+    <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="B75" s="10"/>
       <c r="C75" s="57"/>
       <c r="D75" s="57"/>
     </row>
-    <row r="76" spans="1:4" ht="15.95">
+    <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>321</v>
+        <v>286</v>
       </c>
       <c r="B76" s="10"/>
       <c r="C76" s="57"/>
       <c r="D76" s="57"/>
     </row>
-    <row r="77" spans="1:4" ht="15.95">
+    <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="57"/>
       <c r="D77" s="57"/>
     </row>
-    <row r="78" spans="1:4" ht="15.95">
+    <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>323</v>
+        <v>288</v>
       </c>
       <c r="B78" s="10"/>
       <c r="C78" s="57"/>
       <c r="D78" s="57"/>
     </row>
-    <row r="79" spans="1:4" ht="15.95">
+    <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>324</v>
+        <v>289</v>
       </c>
       <c r="B79" s="10"/>
       <c r="C79" s="57"/>
       <c r="D79" s="57"/>
     </row>
-    <row r="80" spans="1:4" ht="15.95">
+    <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="B80" s="23"/>
       <c r="C80" s="57"/>
       <c r="D80" s="57"/>
     </row>
-    <row r="81" spans="1:4" ht="15.95">
+    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="43" t="s">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="B81" s="32"/>
       <c r="C81" s="57"/>
       <c r="D81" s="57"/>
     </row>
-    <row r="82" spans="1:4" ht="15.95">
+    <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="51" t="s">
-        <v>327</v>
+        <v>292</v>
       </c>
       <c r="B82" s="32"/>
       <c r="C82" s="57"/>
       <c r="D82" s="57"/>
     </row>
-    <row r="83" spans="1:4" ht="15.95">
+    <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="22" t="s">
-        <v>328</v>
+        <v>293</v>
       </c>
       <c r="B83" s="23"/>
       <c r="C83" s="57"/>
       <c r="D83" s="57"/>
     </row>
-    <row r="84" spans="1:4" ht="15.95">
+    <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>329</v>
+        <v>294</v>
       </c>
       <c r="B84" s="10"/>
       <c r="C84" s="57"/>
       <c r="D84" s="57"/>
     </row>
-    <row r="85" spans="1:4" ht="15.95">
+    <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="B85" s="10"/>
       <c r="C85" s="57"/>
       <c r="D85" s="57"/>
     </row>
-    <row r="86" spans="1:4" ht="15.95">
+    <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>395</v>
+        <v>351</v>
       </c>
       <c r="C86" s="10">
         <v>10</v>
@@ -7301,12 +7397,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15.95">
+    <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>396</v>
+        <v>352</v>
       </c>
       <c r="C87" s="10">
         <v>10</v>
@@ -7315,33 +7411,33 @@
         <v>84</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15.95">
+    <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>335</v>
+        <v>298</v>
       </c>
       <c r="B88" s="10"/>
       <c r="C88" s="57"/>
       <c r="D88" s="57"/>
     </row>
-    <row r="89" spans="1:4" ht="15.95">
+    <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>336</v>
+        <v>299</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="57"/>
       <c r="D89" s="57"/>
     </row>
-    <row r="90" spans="1:4" ht="15.95">
+    <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>337</v>
+        <v>300</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="57"/>
       <c r="D90" s="57"/>
     </row>
-    <row r="91" spans="1:4" ht="15.95">
+    <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>338</v>
+        <v>301</v>
       </c>
       <c r="B91" s="10">
         <v>96000</v>
@@ -7353,9 +7449,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15.95">
+    <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>339</v>
+        <v>458</v>
       </c>
       <c r="B92" s="10">
         <v>96000</v>
@@ -7367,51 +7463,51 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="15.95">
+    <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>340</v>
+        <v>302</v>
       </c>
       <c r="B93" s="52" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="C93" s="57"/>
       <c r="D93" s="71"/>
     </row>
-    <row r="94" spans="1:4" ht="15.95">
+    <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
       <c r="B94" s="73"/>
       <c r="C94" s="56"/>
       <c r="D94" s="71"/>
     </row>
-    <row r="95" spans="1:4" ht="15.95">
+    <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>399</v>
+        <v>354</v>
       </c>
       <c r="B95" s="26"/>
       <c r="C95" s="56"/>
       <c r="D95" s="57"/>
     </row>
-    <row r="96" spans="1:4" ht="15.95">
+    <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
-        <v>344</v>
+        <v>305</v>
       </c>
       <c r="B96" s="35"/>
       <c r="C96" s="10"/>
       <c r="D96" s="57"/>
     </row>
-    <row r="97" spans="1:9" ht="15.95">
+    <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>345</v>
+        <v>306</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
       <c r="D97" s="57"/>
     </row>
-    <row r="98" spans="1:9" ht="15.95">
+    <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>347</v>
+        <v>308</v>
       </c>
       <c r="B98" s="10">
         <v>1200</v>
@@ -7423,51 +7519,51 @@
         <v>55</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.95">
+    <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>348</v>
+        <v>309</v>
       </c>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
       <c r="D99" s="57"/>
     </row>
-    <row r="100" spans="1:9" ht="15.95">
+    <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>349</v>
+        <v>310</v>
       </c>
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
       <c r="D100" s="57"/>
     </row>
-    <row r="101" spans="1:9" ht="15.95">
+    <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>350</v>
+        <v>311</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="57"/>
     </row>
-    <row r="102" spans="1:9" ht="15.95">
+    <row r="102" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>351</v>
+        <v>312</v>
       </c>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
       <c r="D102" s="57"/>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1">
+    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" ht="15" customHeight="1">
+    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" ht="15" customHeight="1">
+    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" ht="15" customHeight="1">
+    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
@@ -7482,551 +7578,602 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1F4FD9-0BA8-D443-A42F-4E5E606C52A0}">
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultColWidth="62.42578125" defaultRowHeight="24"/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="62.5" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="162.5703125" style="82" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" style="82" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" style="82" customWidth="1"/>
-    <col min="4" max="4" width="26" style="82" customWidth="1"/>
-    <col min="5" max="5" width="47.7109375" style="82" customWidth="1"/>
-    <col min="6" max="6" width="26.42578125" style="82" customWidth="1"/>
-    <col min="7" max="7" width="33.85546875" style="82" customWidth="1"/>
-    <col min="8" max="16384" width="62.42578125" style="82"/>
+    <col min="1" max="1" width="162.5" style="86" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" style="86" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" style="86" customWidth="1"/>
+    <col min="4" max="4" width="26" style="86" customWidth="1"/>
+    <col min="5" max="5" width="47.6640625" style="86" customWidth="1"/>
+    <col min="6" max="6" width="26.5" style="86" customWidth="1"/>
+    <col min="7" max="7" width="33.83203125" style="86" customWidth="1"/>
+    <col min="8" max="16384" width="62.5" style="86"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="75">
-      <c r="A1" s="80" t="s">
-        <v>400</v>
-      </c>
-      <c r="B1" s="107" t="s">
+    <row r="1" spans="1:7" ht="75" x14ac:dyDescent="0.3">
+      <c r="A1" s="82" t="s">
+        <v>409</v>
+      </c>
+      <c r="B1" s="83" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="108"/>
-      <c r="D1" s="81" t="s">
+      <c r="C1" s="84"/>
+      <c r="D1" s="85" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="107" t="s">
-        <v>353</v>
-      </c>
-      <c r="F1" s="108"/>
-      <c r="G1" s="81" t="s">
+      <c r="E1" s="83" t="s">
+        <v>314</v>
+      </c>
+      <c r="F1" s="84"/>
+      <c r="G1" s="85" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="50.1">
-      <c r="A2" s="83" t="s">
-        <v>401</v>
-      </c>
-      <c r="B2" s="84" t="s">
-        <v>369</v>
-      </c>
-      <c r="C2" s="85" t="s">
+    <row r="2" spans="1:7" ht="50" x14ac:dyDescent="0.3">
+      <c r="A2" s="87" t="s">
+        <v>410</v>
+      </c>
+      <c r="B2" s="88" t="s">
+        <v>326</v>
+      </c>
+      <c r="C2" s="89" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="84" t="s">
-        <v>402</v>
-      </c>
-      <c r="E2" s="84" t="s">
+      <c r="D2" s="88" t="s">
+        <v>412</v>
+      </c>
+      <c r="E2" s="88" t="s">
         <v>196</v>
       </c>
-      <c r="F2" s="85" t="s">
+      <c r="F2" s="89" t="s">
         <v>197</v>
       </c>
-      <c r="G2" s="85" t="s">
+      <c r="G2" s="89" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="24.95">
-      <c r="A3" s="86" t="s">
-        <v>403</v>
-      </c>
-      <c r="B3" s="87" t="s">
-        <v>404</v>
-      </c>
-      <c r="C3" s="88">
+    <row r="3" spans="1:7" ht="25" x14ac:dyDescent="0.3">
+      <c r="A3" s="90" t="s">
+        <v>459</v>
+      </c>
+      <c r="B3" s="91" t="s">
+        <v>413</v>
+      </c>
+      <c r="C3" s="92">
         <v>94</v>
       </c>
-      <c r="D3" s="89">
+      <c r="D3" s="93">
         <v>40</v>
       </c>
-      <c r="E3" s="87" t="s">
-        <v>405</v>
-      </c>
-      <c r="F3" s="88">
+      <c r="E3" s="91" t="s">
+        <v>417</v>
+      </c>
+      <c r="F3" s="92">
         <v>93</v>
       </c>
-      <c r="G3" s="89">
+      <c r="G3" s="93">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="24.95">
-      <c r="A4" s="86" t="s">
-        <v>406</v>
-      </c>
-      <c r="B4" s="89" t="s">
-        <v>407</v>
-      </c>
-      <c r="C4" s="90">
+    <row r="4" spans="1:7" ht="25" x14ac:dyDescent="0.3">
+      <c r="A4" s="90" t="s">
+        <v>460</v>
+      </c>
+      <c r="B4" s="93" t="s">
+        <v>411</v>
+      </c>
+      <c r="C4" s="94">
         <v>95</v>
       </c>
-      <c r="D4" s="91">
+      <c r="D4" s="95">
         <v>40</v>
       </c>
-      <c r="E4" s="89" t="s">
-        <v>408</v>
-      </c>
-      <c r="F4" s="90">
+      <c r="E4" s="93" t="s">
+        <v>416</v>
+      </c>
+      <c r="F4" s="94">
         <v>94</v>
       </c>
-      <c r="G4" s="91">
+      <c r="G4" s="95">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="24.95">
-      <c r="A5" s="86" t="s">
-        <v>409</v>
-      </c>
-      <c r="B5" s="92" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="93">
+    <row r="5" spans="1:7" ht="25" x14ac:dyDescent="0.3">
+      <c r="A5" s="90" t="s">
+        <v>461</v>
+      </c>
+      <c r="B5" s="96" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" s="97">
         <v>94</v>
       </c>
-      <c r="D5" s="94">
+      <c r="D5" s="98">
         <v>60</v>
       </c>
-      <c r="E5" s="92" t="s">
+      <c r="E5" s="96" t="s">
+        <v>418</v>
+      </c>
+      <c r="F5" s="97">
+        <v>91</v>
+      </c>
+      <c r="G5" s="98">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="25" x14ac:dyDescent="0.3">
+      <c r="A6" s="99" t="s">
+        <v>236</v>
+      </c>
+      <c r="B6" s="93" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="100">
+        <v>99</v>
+      </c>
+      <c r="D6" s="101" t="s">
+        <v>238</v>
+      </c>
+      <c r="E6" s="93" t="s">
+        <v>339</v>
+      </c>
+      <c r="F6" s="93">
+        <v>98</v>
+      </c>
+      <c r="G6" s="101" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="25" x14ac:dyDescent="0.3">
+      <c r="A7" s="99" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="93" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="102">
+        <v>99</v>
+      </c>
+      <c r="D7" s="101" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="93" t="s">
+        <v>340</v>
+      </c>
+      <c r="F7" s="93">
+        <v>98</v>
+      </c>
+      <c r="G7" s="101" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="25" x14ac:dyDescent="0.3">
+      <c r="A8" s="103" t="s">
+        <v>241</v>
+      </c>
+      <c r="B8" s="96" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="97">
+        <v>90</v>
+      </c>
+      <c r="D8" s="98" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" s="93" t="s">
+        <v>341</v>
+      </c>
+      <c r="F8" s="93">
+        <v>96</v>
+      </c>
+      <c r="G8" s="98" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="90" t="s">
+        <v>268</v>
+      </c>
+      <c r="B9" s="93"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="104" t="s">
+        <v>267</v>
+      </c>
+      <c r="E9" s="93"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="104" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="75" x14ac:dyDescent="0.3">
+      <c r="A12" s="82" t="s">
+        <v>414</v>
+      </c>
+      <c r="B12" s="83" t="s">
+        <v>193</v>
+      </c>
+      <c r="C12" s="84"/>
+      <c r="D12" s="85" t="s">
+        <v>194</v>
+      </c>
+      <c r="E12" s="83" t="s">
+        <v>314</v>
+      </c>
+      <c r="F12" s="84"/>
+      <c r="G12" s="85" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="50" x14ac:dyDescent="0.3">
+      <c r="A13" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="F5" s="93">
+      <c r="B13" s="88" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="89" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="88" t="s">
+        <v>412</v>
+      </c>
+      <c r="E13" s="88" t="s">
+        <v>196</v>
+      </c>
+      <c r="F13" s="89" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13" s="89" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="25" x14ac:dyDescent="0.3">
+      <c r="A14" s="90" t="s">
+        <v>459</v>
+      </c>
+      <c r="B14" s="91" t="s">
+        <v>415</v>
+      </c>
+      <c r="C14" s="92">
+        <v>95</v>
+      </c>
+      <c r="D14" s="93">
+        <v>61</v>
+      </c>
+      <c r="E14" s="91" t="s">
+        <v>417</v>
+      </c>
+      <c r="F14" s="92">
+        <v>93</v>
+      </c>
+      <c r="G14" s="93">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="25" x14ac:dyDescent="0.3">
+      <c r="A15" s="90" t="s">
+        <v>460</v>
+      </c>
+      <c r="B15" s="93" t="s">
+        <v>411</v>
+      </c>
+      <c r="C15" s="94">
+        <v>95</v>
+      </c>
+      <c r="D15" s="95">
+        <v>61</v>
+      </c>
+      <c r="E15" s="93" t="s">
+        <v>416</v>
+      </c>
+      <c r="F15" s="94">
+        <v>94</v>
+      </c>
+      <c r="G15" s="95">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="25" x14ac:dyDescent="0.3">
+      <c r="A16" s="90" t="s">
+        <v>461</v>
+      </c>
+      <c r="B16" s="96" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="97">
+        <v>94</v>
+      </c>
+      <c r="D16" s="98">
+        <v>60</v>
+      </c>
+      <c r="E16" s="96" t="s">
+        <v>419</v>
+      </c>
+      <c r="F16" s="97">
         <v>91</v>
       </c>
-      <c r="G5" s="94">
+      <c r="G16" s="98">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="24.95">
-      <c r="A6" s="95" t="s">
-        <v>271</v>
-      </c>
-      <c r="B6" s="89" t="s">
-        <v>272</v>
-      </c>
-      <c r="C6" s="96">
+    <row r="17" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A17" s="99" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" s="93" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" s="100">
         <v>99</v>
       </c>
-      <c r="D6" s="97" t="s">
-        <v>273</v>
-      </c>
-      <c r="E6" s="89" t="s">
-        <v>382</v>
-      </c>
-      <c r="F6" s="89">
+      <c r="D17" s="101" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" s="93" t="s">
+        <v>339</v>
+      </c>
+      <c r="F17" s="93">
         <v>98</v>
       </c>
-      <c r="G6" s="97" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="24.95">
-      <c r="A7" s="95" t="s">
-        <v>274</v>
-      </c>
-      <c r="B7" s="89" t="s">
-        <v>275</v>
-      </c>
-      <c r="C7" s="98">
+      <c r="G17" s="101" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A18" s="99" t="s">
+        <v>239</v>
+      </c>
+      <c r="B18" s="93" t="s">
+        <v>240</v>
+      </c>
+      <c r="C18" s="102">
         <v>99</v>
       </c>
-      <c r="D7" s="97" t="s">
-        <v>273</v>
-      </c>
-      <c r="E7" s="89" t="s">
-        <v>383</v>
-      </c>
-      <c r="F7" s="89">
+      <c r="D18" s="101" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" s="93" t="s">
+        <v>340</v>
+      </c>
+      <c r="F18" s="93">
         <v>98</v>
       </c>
-      <c r="G7" s="97" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="24.95">
-      <c r="A8" s="99" t="s">
-        <v>276</v>
-      </c>
-      <c r="B8" s="92" t="s">
-        <v>277</v>
-      </c>
-      <c r="C8" s="93">
+      <c r="G18" s="101" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A19" s="103" t="s">
+        <v>241</v>
+      </c>
+      <c r="B19" s="96" t="s">
+        <v>242</v>
+      </c>
+      <c r="C19" s="97">
         <v>90</v>
       </c>
-      <c r="D8" s="94" t="s">
-        <v>273</v>
-      </c>
-      <c r="E8" s="89" t="s">
-        <v>384</v>
-      </c>
-      <c r="F8" s="89">
+      <c r="D19" s="98" t="s">
+        <v>238</v>
+      </c>
+      <c r="E19" s="93" t="s">
+        <v>341</v>
+      </c>
+      <c r="F19" s="93">
         <v>96</v>
       </c>
-      <c r="G8" s="94" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A9" s="86" t="s">
-        <v>303</v>
-      </c>
-      <c r="B9" s="89"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="100" t="s">
-        <v>302</v>
-      </c>
-      <c r="E9" s="89"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="100" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="75">
-      <c r="A12" s="80" t="s">
+      <c r="G19" s="98" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A20" s="90" t="s">
+        <v>268</v>
+      </c>
+      <c r="B20" s="93"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="104" t="s">
+        <v>267</v>
+      </c>
+      <c r="E20" s="93"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="104" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="75" x14ac:dyDescent="0.3">
+      <c r="A23" s="105" t="s">
+        <v>474</v>
+      </c>
+      <c r="B23" s="83" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="84"/>
+      <c r="D23" s="85" t="s">
+        <v>194</v>
+      </c>
+      <c r="E23" s="83" t="s">
+        <v>314</v>
+      </c>
+      <c r="F23" s="84"/>
+      <c r="G23" s="85" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="50" x14ac:dyDescent="0.3">
+      <c r="A24" s="87" t="s">
+        <v>410</v>
+      </c>
+      <c r="B24" s="88" t="s">
+        <v>326</v>
+      </c>
+      <c r="C24" s="89" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" s="88" t="s">
+        <v>412</v>
+      </c>
+      <c r="E24" s="88" t="s">
+        <v>326</v>
+      </c>
+      <c r="F24" s="89" t="s">
+        <v>197</v>
+      </c>
+      <c r="G24" s="88" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A25" s="90" t="s">
+        <v>459</v>
+      </c>
+      <c r="B25" s="91" t="s">
+        <v>475</v>
+      </c>
+      <c r="C25" s="92">
+        <v>94</v>
+      </c>
+      <c r="D25" s="93">
+        <v>40</v>
+      </c>
+      <c r="E25" s="91"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="93"/>
+    </row>
+    <row r="26" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A26" s="90" t="s">
+        <v>460</v>
+      </c>
+      <c r="B26" s="93" t="s">
         <v>411</v>
       </c>
-      <c r="B12" s="107" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" s="108"/>
-      <c r="D12" s="81" t="s">
-        <v>194</v>
-      </c>
-      <c r="E12" s="107" t="s">
-        <v>353</v>
-      </c>
-      <c r="F12" s="108"/>
-      <c r="G12" s="81" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="50.1">
-      <c r="A13" s="83" t="s">
-        <v>401</v>
-      </c>
-      <c r="B13" s="84" t="s">
-        <v>369</v>
-      </c>
-      <c r="C13" s="85" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" s="84" t="s">
-        <v>402</v>
-      </c>
-      <c r="E13" s="84" t="s">
-        <v>196</v>
-      </c>
-      <c r="F13" s="85" t="s">
-        <v>197</v>
-      </c>
-      <c r="G13" s="85" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="24.95">
-      <c r="A14" s="86" t="s">
-        <v>403</v>
-      </c>
-      <c r="B14" s="87" t="s">
-        <v>412</v>
-      </c>
-      <c r="C14" s="88">
+      <c r="C26" s="94">
         <v>95</v>
       </c>
-      <c r="D14" s="89">
-        <v>61</v>
-      </c>
-      <c r="E14" s="87" t="s">
-        <v>405</v>
-      </c>
-      <c r="F14" s="88">
-        <v>93</v>
-      </c>
-      <c r="G14" s="89">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="24.95">
-      <c r="A15" s="86" t="s">
-        <v>406</v>
-      </c>
-      <c r="B15" s="89" t="s">
-        <v>407</v>
-      </c>
-      <c r="C15" s="90">
-        <v>95</v>
-      </c>
-      <c r="D15" s="91">
-        <v>61</v>
-      </c>
-      <c r="E15" s="89" t="s">
-        <v>408</v>
-      </c>
-      <c r="F15" s="90">
-        <v>94</v>
-      </c>
-      <c r="G15" s="91">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="24.95">
-      <c r="A16" s="86" t="s">
-        <v>409</v>
-      </c>
-      <c r="B16" s="92" t="s">
-        <v>234</v>
-      </c>
-      <c r="C16" s="93">
-        <v>94</v>
-      </c>
-      <c r="D16" s="94">
+      <c r="D26" s="95">
+        <v>38</v>
+      </c>
+      <c r="E26" s="93"/>
+      <c r="F26" s="94"/>
+      <c r="G26" s="95"/>
+    </row>
+    <row r="27" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A27" s="90" t="s">
+        <v>461</v>
+      </c>
+      <c r="B27" s="96" t="s">
+        <v>476</v>
+      </c>
+      <c r="C27" s="97">
+        <v>75</v>
+      </c>
+      <c r="D27" s="98">
+        <v>56</v>
+      </c>
+      <c r="E27" s="96"/>
+      <c r="F27" s="97"/>
+      <c r="G27" s="98"/>
+    </row>
+    <row r="28" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A28" s="99" t="s">
+        <v>236</v>
+      </c>
+      <c r="B28" s="93" t="s">
+        <v>237</v>
+      </c>
+      <c r="C28" s="100">
+        <v>99</v>
+      </c>
+      <c r="D28" s="101" t="s">
+        <v>238</v>
+      </c>
+      <c r="E28" s="93"/>
+      <c r="F28" s="100"/>
+      <c r="G28" s="101" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A29" s="99" t="s">
+        <v>239</v>
+      </c>
+      <c r="B29" s="93" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" s="102">
+        <v>99</v>
+      </c>
+      <c r="D29" s="101" t="s">
+        <v>238</v>
+      </c>
+      <c r="E29" s="93"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="101" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A30" s="103" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="96" t="s">
+        <v>242</v>
+      </c>
+      <c r="C30" s="97">
+        <v>90</v>
+      </c>
+      <c r="D30" s="101" t="s">
+        <v>238</v>
+      </c>
+      <c r="E30" s="96"/>
+      <c r="F30" s="97"/>
+      <c r="G30" s="101" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A31" s="90" t="s">
+        <v>268</v>
+      </c>
+      <c r="B31" s="107"/>
+      <c r="C31" s="108"/>
+      <c r="D31" s="104" t="s">
+        <v>267</v>
+      </c>
+      <c r="E31" s="107"/>
+      <c r="F31" s="108"/>
+      <c r="G31" s="104" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="25" x14ac:dyDescent="0.3">
+      <c r="A32" s="106" t="s">
+        <v>477</v>
+      </c>
+      <c r="B32" s="109" t="s">
+        <v>478</v>
+      </c>
+      <c r="C32" s="109">
+        <v>75</v>
+      </c>
+      <c r="D32" s="109">
         <v>60</v>
       </c>
-      <c r="E16" s="92" t="s">
-        <v>413</v>
-      </c>
-      <c r="F16" s="93">
-        <v>91</v>
-      </c>
-      <c r="G16" s="94">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="24.95">
-      <c r="A17" s="95" t="s">
-        <v>271</v>
-      </c>
-      <c r="B17" s="89" t="s">
-        <v>272</v>
-      </c>
-      <c r="C17" s="96">
-        <v>99</v>
-      </c>
-      <c r="D17" s="97" t="s">
-        <v>273</v>
-      </c>
-      <c r="E17" s="89" t="s">
-        <v>382</v>
-      </c>
-      <c r="F17" s="89">
-        <v>98</v>
-      </c>
-      <c r="G17" s="97" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="24.95">
-      <c r="A18" s="95" t="s">
-        <v>274</v>
-      </c>
-      <c r="B18" s="89" t="s">
-        <v>275</v>
-      </c>
-      <c r="C18" s="98">
-        <v>99</v>
-      </c>
-      <c r="D18" s="97" t="s">
-        <v>273</v>
-      </c>
-      <c r="E18" s="89" t="s">
-        <v>383</v>
-      </c>
-      <c r="F18" s="89">
-        <v>98</v>
-      </c>
-      <c r="G18" s="97" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="24.95">
-      <c r="A19" s="99" t="s">
-        <v>276</v>
-      </c>
-      <c r="B19" s="92" t="s">
-        <v>277</v>
-      </c>
-      <c r="C19" s="93">
-        <v>90</v>
-      </c>
-      <c r="D19" s="94" t="s">
-        <v>273</v>
-      </c>
-      <c r="E19" s="89" t="s">
-        <v>384</v>
-      </c>
-      <c r="F19" s="89">
-        <v>96</v>
-      </c>
-      <c r="G19" s="94" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="24.95">
-      <c r="A20" s="86" t="s">
-        <v>303</v>
-      </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="100" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="100" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="70.5">
-      <c r="A23" s="101" t="s">
-        <v>414</v>
-      </c>
-      <c r="B23" s="107" t="s">
-        <v>193</v>
-      </c>
-      <c r="C23" s="108"/>
-      <c r="D23" s="81" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="47.25">
-      <c r="A24" s="83" t="s">
-        <v>401</v>
-      </c>
-      <c r="B24" s="84" t="s">
-        <v>369</v>
-      </c>
-      <c r="C24" s="85" t="s">
-        <v>197</v>
-      </c>
-      <c r="D24" s="84" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="23.25">
-      <c r="A25" s="86" t="s">
-        <v>403</v>
-      </c>
-      <c r="B25" s="87" t="s">
-        <v>415</v>
-      </c>
-      <c r="C25" s="88">
-        <v>94</v>
-      </c>
-      <c r="D25" s="89">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="23.25">
-      <c r="A26" s="86" t="s">
-        <v>406</v>
-      </c>
-      <c r="B26" s="89" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="90">
-        <v>95</v>
-      </c>
-      <c r="D26" s="91">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="23.25">
-      <c r="A27" s="86" t="s">
-        <v>409</v>
-      </c>
-      <c r="B27" s="92" t="s">
-        <v>416</v>
-      </c>
-      <c r="C27" s="93">
-        <v>75</v>
-      </c>
-      <c r="D27" s="94">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="23.25">
-      <c r="A28" s="95" t="s">
-        <v>271</v>
-      </c>
-      <c r="B28" s="89" t="s">
-        <v>272</v>
-      </c>
-      <c r="C28" s="96">
-        <v>99</v>
-      </c>
-      <c r="D28" s="97" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="23.25">
-      <c r="A29" s="95" t="s">
-        <v>274</v>
-      </c>
-      <c r="B29" s="89" t="s">
-        <v>275</v>
-      </c>
-      <c r="C29" s="98">
-        <v>99</v>
-      </c>
-      <c r="D29" s="97" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="23.25">
-      <c r="A30" s="99" t="s">
-        <v>276</v>
-      </c>
-      <c r="B30" s="92" t="s">
-        <v>277</v>
-      </c>
-      <c r="C30" s="93">
-        <v>90</v>
-      </c>
-      <c r="D30" s="97" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="23.25">
-      <c r="A31" s="86" t="s">
-        <v>303</v>
-      </c>
-      <c r="B31" s="103"/>
-      <c r="C31" s="104"/>
-      <c r="D31" s="105"/>
-    </row>
-    <row r="32" spans="1:7" ht="23.25">
-      <c r="A32" s="102" t="s">
-        <v>417</v>
-      </c>
-      <c r="B32" s="106" t="s">
-        <v>418</v>
-      </c>
-      <c r="C32" s="106">
-        <v>75</v>
-      </c>
-      <c r="D32" s="106">
-        <v>60</v>
-      </c>
-      <c r="E32" s="82" t="s">
-        <v>419</v>
+      <c r="E32" s="109"/>
+      <c r="F32" s="109"/>
+      <c r="G32" s="109"/>
+      <c r="H32" s="86" t="s">
+        <v>479</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E23:F23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8035,369 +8182,369 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8EE6899-576B-F44E-A189-C616F2524B03}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="59.140625" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="1" max="1" width="59.1640625" customWidth="1"/>
+    <col min="2" max="2" width="35.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="60">
+    <row r="1" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A1" s="50" t="s">
-        <v>420</v>
+        <v>355</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>353</v>
+        <v>314</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.95">
+    <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>195</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>369</v>
+        <v>326</v>
       </c>
       <c r="C2" s="40"/>
     </row>
-    <row r="3" spans="1:3" ht="18.95" hidden="1">
+    <row r="3" spans="1:3" ht="19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
-        <v>421</v>
+        <v>356</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
-    <row r="4" spans="1:3" ht="15.95" hidden="1">
+    <row r="4" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>422</v>
+        <v>462</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3" ht="15.95" hidden="1">
+    <row r="5" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>423</v>
+        <v>463</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="59"/>
     </row>
-    <row r="6" spans="1:3" ht="15.95" hidden="1">
+    <row r="6" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:3" ht="15.95" hidden="1">
+    <row r="7" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>204</v>
+        <v>427</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:3" ht="15.95">
+    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>206</v>
+        <v>428</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="C8" s="60" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.95">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>208</v>
+        <v>429</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>427</v>
+        <v>359</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.95" hidden="1">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>210</v>
+        <v>430</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:3" ht="15.95" hidden="1">
+    <row r="11" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="59"/>
     </row>
-    <row r="12" spans="1:3" ht="15.95" hidden="1">
+    <row r="12" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>214</v>
+        <v>432</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:3" ht="15.95" hidden="1">
+    <row r="13" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>218</v>
+        <v>434</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="59"/>
     </row>
-    <row r="14" spans="1:3" ht="15.95" hidden="1">
+    <row r="14" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>430</v>
+        <v>465</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:3" ht="15.95" hidden="1">
+    <row r="15" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>431</v>
+        <v>466</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
-    <row r="16" spans="1:3" ht="15.95" hidden="1">
+    <row r="16" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>220</v>
+        <v>435</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:3" ht="15.95" hidden="1">
+    <row r="17" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:3" ht="15.95" hidden="1">
+    <row r="18" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:3" ht="15.95" hidden="1">
+    <row r="19" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>226</v>
+        <v>438</v>
       </c>
       <c r="B19" s="46"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:3" ht="15.95" hidden="1">
+    <row r="20" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="43" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
     </row>
-    <row r="21" spans="1:3" ht="18.95">
+    <row r="21" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="61"/>
     </row>
-    <row r="22" spans="1:3" ht="15.95" hidden="1">
+    <row r="22" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="22" t="s">
-        <v>231</v>
+        <v>440</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="55"/>
     </row>
-    <row r="23" spans="1:3" ht="15.95">
+    <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>233</v>
+        <v>441</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>435</v>
+        <v>361</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.95" hidden="1">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>235</v>
+        <v>442</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="57"/>
     </row>
-    <row r="25" spans="1:3" ht="15.95">
+    <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>237</v>
+        <v>443</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>437</v>
+        <v>363</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.95">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>239</v>
+        <v>444</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>439</v>
+        <v>365</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.95" hidden="1">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="57"/>
     </row>
-    <row r="28" spans="1:3" ht="15.95" hidden="1">
+    <row r="28" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>243</v>
+        <v>446</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="57"/>
     </row>
-    <row r="29" spans="1:3" ht="15.95" hidden="1">
+    <row r="29" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>245</v>
+        <v>447</v>
       </c>
       <c r="B29" s="10"/>
       <c r="C29" s="57"/>
     </row>
-    <row r="30" spans="1:3" ht="15.95" hidden="1">
+    <row r="30" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="57"/>
     </row>
-    <row r="31" spans="1:3" ht="15.95" hidden="1">
+    <row r="31" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="57"/>
     </row>
-    <row r="32" spans="1:3" ht="18.95" hidden="1">
+    <row r="32" spans="1:3" ht="19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="62"/>
     </row>
-    <row r="33" spans="1:3" ht="15.95" hidden="1">
+    <row r="33" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>254</v>
+        <v>450</v>
       </c>
       <c r="B33" s="47"/>
       <c r="C33" s="57"/>
     </row>
-    <row r="34" spans="1:3" ht="15.95" hidden="1">
+    <row r="34" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>257</v>
+        <v>451</v>
       </c>
       <c r="B34" s="47"/>
       <c r="C34" s="57"/>
     </row>
-    <row r="35" spans="1:3" ht="15.95" hidden="1">
+    <row r="35" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>258</v>
+        <v>452</v>
       </c>
       <c r="B35" s="47"/>
       <c r="C35" s="57"/>
     </row>
-    <row r="36" spans="1:3" ht="15.95" hidden="1">
+    <row r="36" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>233</v>
+        <v>441</v>
       </c>
       <c r="B36" s="47"/>
       <c r="C36" s="54"/>
     </row>
-    <row r="37" spans="1:3" ht="18.95">
+    <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="63"/>
     </row>
-    <row r="38" spans="1:3" ht="15.95" hidden="1">
+    <row r="38" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="B38" s="48"/>
       <c r="C38" s="64"/>
     </row>
-    <row r="39" spans="1:3" ht="15.95" hidden="1">
+    <row r="39" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="64"/>
     </row>
-    <row r="40" spans="1:3" ht="15.95">
+    <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>263</v>
+        <v>453</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>444</v>
+        <v>367</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.95">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>264</v>
+        <v>454</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>446</v>
+        <v>369</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.95" hidden="1">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="22" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
     </row>
-    <row r="43" spans="1:3" ht="15.95" hidden="1">
+    <row r="43" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="22" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="B43" s="45"/>
       <c r="C43" s="15"/>
     </row>
-    <row r="44" spans="1:3" ht="15.95" hidden="1">
+    <row r="44" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>267</v>
+        <v>455</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="1:3" ht="15.95">
+    <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>268</v>
+        <v>456</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>448</v>
+        <v>371</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.95" hidden="1">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>269</v>
+        <v>457</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -8410,124 +8557,124 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA07167-CEB4-F64B-93AF-8A8BA2B4D0FF}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="62.140625" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" customWidth="1"/>
-    <col min="3" max="3" width="40.7109375" customWidth="1"/>
+    <col min="1" max="1" width="62.1640625" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="81">
+    <row r="1" spans="1:4" ht="81" x14ac:dyDescent="0.2">
       <c r="A1" s="76" t="s">
-        <v>450</v>
+        <v>373</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>451</v>
+        <v>374</v>
       </c>
       <c r="C1" s="78" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="21.95">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
-        <v>453</v>
+        <v>376</v>
       </c>
       <c r="B2" s="75" t="s">
-        <v>454</v>
+        <v>377</v>
       </c>
       <c r="C2" s="75" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="21.95">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A3" s="74" t="s">
-        <v>456</v>
+        <v>379</v>
       </c>
       <c r="B3" s="75" t="s">
-        <v>457</v>
+        <v>380</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="21.95">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
-        <v>458</v>
+        <v>381</v>
       </c>
       <c r="B4" s="79" t="s">
-        <v>459</v>
+        <v>382</v>
       </c>
       <c r="C4" s="79" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="21.95">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A5" s="74" t="s">
-        <v>460</v>
+        <v>383</v>
       </c>
       <c r="B5" s="79" t="s">
-        <v>459</v>
+        <v>382</v>
       </c>
       <c r="C5" s="79" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="21.95">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A6" s="74" t="s">
-        <v>461</v>
+        <v>384</v>
       </c>
       <c r="B6" s="75" t="s">
-        <v>462</v>
+        <v>385</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="21.95">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A7" s="74" t="s">
-        <v>464</v>
+        <v>387</v>
       </c>
       <c r="B7" s="75" t="s">
-        <v>465</v>
+        <v>388</v>
       </c>
       <c r="C7" s="75" t="s">
-        <v>466</v>
+        <v>389</v>
       </c>
       <c r="D7" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="21.95">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A8" s="74" t="s">
-        <v>468</v>
+        <v>391</v>
       </c>
       <c r="B8" s="75" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="C8" s="75" t="s">
-        <v>469</v>
+        <v>392</v>
       </c>
       <c r="D8" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="21.95">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
-        <v>471</v>
+        <v>394</v>
       </c>
       <c r="B9" s="75" t="s">
-        <v>472</v>
+        <v>395</v>
       </c>
       <c r="C9" s="75" t="s">
-        <v>473</v>
+        <v>396</v>
       </c>
       <c r="D9" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="21.95">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A10" s="74" t="s">
-        <v>475</v>
+        <v>398</v>
       </c>
       <c r="B10" s="75">
         <v>26000</v>
@@ -8536,9 +8683,9 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="21.95">
+    <row r="11" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="s">
-        <v>476</v>
+        <v>399</v>
       </c>
       <c r="B11" s="75">
         <v>445</v>
@@ -8547,9 +8694,9 @@
         <v>371</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="21.95">
+    <row r="12" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A12" s="74" t="s">
-        <v>477</v>
+        <v>400</v>
       </c>
       <c r="B12" s="75">
         <v>96000</v>
@@ -8558,9 +8705,9 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="21.95">
+    <row r="13" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A13" s="74" t="s">
-        <v>478</v>
+        <v>401</v>
       </c>
       <c r="B13" s="75">
         <v>400000</v>
@@ -8569,9 +8716,9 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="21.95">
+    <row r="14" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A14" s="74" t="s">
-        <v>479</v>
+        <v>402</v>
       </c>
       <c r="B14" s="75">
         <v>200000</v>
@@ -8946,17 +9093,55 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
+    <ds:schemaRef ds:uri="0b7692b1-2532-40e4-a300-4d7fced4a07a"/>
+    <ds:schemaRef ds:uri="cb645b5b-9a36-43da-96bf-ab72ec91ddff"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="cb645b5b-9a36-43da-96bf-ab72ec91ddff"/>
+    <ds:schemaRef ds:uri="0b7692b1-2532-40e4-a300-4d7fced4a07a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="746" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{291A0975-2E99-8E40-9791-D0260B6B2859}"/>
+  <xr:revisionPtr revIDLastSave="768" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A07AAB7-1F47-5547-B1A6-8D56B4033169}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21340" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19740" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="491">
   <si>
     <t>number</t>
   </si>
@@ -1673,6 +1673,15 @@
   </si>
   <si>
     <t>315 KPPS / 940 Mbps</t>
+  </si>
+  <si>
+    <t>232 KPPS / 2653 Mbps</t>
+  </si>
+  <si>
+    <t>215 CPS /115 Mbps</t>
+  </si>
+  <si>
+    <t>350 CPS</t>
   </si>
 </sst>
 </file>
@@ -4992,7 +5001,7 @@
     <col min="1" max="1" width="87.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" style="5" customWidth="1"/>
     <col min="3" max="3" width="19.5" style="5" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="41.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5810,8 +5819,8 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="58"/>
-      <c r="D58" s="70" t="s">
-        <v>267</v>
+      <c r="D58" s="59" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -5820,8 +5829,8 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="23"/>
-      <c r="D59" s="70" t="s">
-        <v>267</v>
+      <c r="D59" s="59" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5830,8 +5839,8 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="23"/>
-      <c r="D60" s="70" t="s">
-        <v>267</v>
+      <c r="D60" s="59" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5840,8 +5849,8 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="23"/>
-      <c r="D61" s="70" t="s">
-        <v>267</v>
+      <c r="D61" s="59" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5850,8 +5859,8 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="32"/>
-      <c r="D62" s="70" t="s">
-        <v>267</v>
+      <c r="D62" s="59" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5860,9 +5869,7 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="23"/>
-      <c r="D63" s="70" t="s">
-        <v>267</v>
-      </c>
+      <c r="D63" s="59"/>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
@@ -5870,8 +5877,8 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="53"/>
-      <c r="D64" s="70" t="s">
-        <v>267</v>
+      <c r="D64" s="59" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6740,7 +6747,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>441</v>
       </c>
@@ -6754,7 +6761,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
         <v>230</v>
       </c>
@@ -6768,7 +6775,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>231</v>
       </c>
@@ -6782,7 +6789,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>232</v>
       </c>
@@ -6795,8 +6802,11 @@
       <c r="D36" s="59">
         <v>41</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I36">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>453</v>
       </c>
@@ -6818,8 +6828,12 @@
       <c r="H37">
         <v>310000</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I37">
+        <f>I36*4</f>
+        <v>232000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>454</v>
       </c>
@@ -6844,8 +6858,12 @@
         <f>H37*8*532/1000000</f>
         <v>1319.36</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I38">
+        <f>I37*8*1420/1000000</f>
+        <v>2635.52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
         <v>233</v>
       </c>
@@ -6859,7 +6877,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
         <v>234</v>
       </c>
@@ -6876,7 +6894,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>455</v>
       </c>
@@ -6894,7 +6912,7 @@
         <v>626.64</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>456</v>
       </c>
@@ -6911,7 +6929,7 @@
         <v>315000</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>457</v>
       </c>
@@ -6929,7 +6947,7 @@
         <v>939.96</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
         <v>235</v>
       </c>
@@ -6943,7 +6961,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
         <v>236</v>
       </c>
@@ -6957,7 +6975,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
         <v>239</v>
       </c>
@@ -6971,7 +6989,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>241</v>
       </c>
@@ -6985,7 +7003,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>243</v>
       </c>
@@ -7165,8 +7183,12 @@
       <c r="A61" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B61" s="23"/>
-      <c r="C61" s="57"/>
+      <c r="B61" s="23" t="s">
+        <v>488</v>
+      </c>
+      <c r="C61" s="57">
+        <v>72</v>
+      </c>
       <c r="D61" s="59" t="s">
         <v>484</v>
       </c>
@@ -8036,9 +8058,15 @@
       <c r="D25" s="93">
         <v>40</v>
       </c>
-      <c r="E25" s="91"/>
-      <c r="F25" s="92"/>
-      <c r="G25" s="93"/>
+      <c r="E25" s="91" t="s">
+        <v>417</v>
+      </c>
+      <c r="F25" s="92">
+        <v>93</v>
+      </c>
+      <c r="G25" s="93">
+        <v>59</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A26" s="90" t="s">
@@ -8053,9 +8081,15 @@
       <c r="D26" s="95">
         <v>38</v>
       </c>
-      <c r="E26" s="93"/>
-      <c r="F26" s="94"/>
-      <c r="G26" s="95"/>
+      <c r="E26" s="93" t="s">
+        <v>416</v>
+      </c>
+      <c r="F26" s="94">
+        <v>94</v>
+      </c>
+      <c r="G26" s="95">
+        <v>59</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A27" s="90" t="s">
@@ -8070,9 +8104,18 @@
       <c r="D27" s="98">
         <v>56</v>
       </c>
-      <c r="E27" s="96"/>
-      <c r="F27" s="97"/>
-      <c r="G27" s="98"/>
+      <c r="E27" s="96" t="s">
+        <v>489</v>
+      </c>
+      <c r="F27" s="97">
+        <v>75</v>
+      </c>
+      <c r="G27" s="98">
+        <v>59</v>
+      </c>
+      <c r="H27" s="86" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A28" s="99" t="s">
@@ -8087,8 +8130,12 @@
       <c r="D28" s="101" t="s">
         <v>238</v>
       </c>
-      <c r="E28" s="93"/>
-      <c r="F28" s="100"/>
+      <c r="E28" s="93" t="s">
+        <v>339</v>
+      </c>
+      <c r="F28" s="93">
+        <v>98</v>
+      </c>
       <c r="G28" s="101" t="s">
         <v>238</v>
       </c>
@@ -8106,8 +8153,12 @@
       <c r="D29" s="101" t="s">
         <v>238</v>
       </c>
-      <c r="E29" s="93"/>
-      <c r="F29" s="102"/>
+      <c r="E29" s="93" t="s">
+        <v>340</v>
+      </c>
+      <c r="F29" s="93">
+        <v>98</v>
+      </c>
       <c r="G29" s="101" t="s">
         <v>238</v>
       </c>
@@ -8125,9 +8176,13 @@
       <c r="D30" s="101" t="s">
         <v>238</v>
       </c>
-      <c r="E30" s="96"/>
-      <c r="F30" s="97"/>
-      <c r="G30" s="101" t="s">
+      <c r="E30" s="93" t="s">
+        <v>341</v>
+      </c>
+      <c r="F30" s="93">
+        <v>96</v>
+      </c>
+      <c r="G30" s="98" t="s">
         <v>238</v>
       </c>
     </row>
@@ -8140,8 +8195,12 @@
       <c r="D31" s="104" t="s">
         <v>267</v>
       </c>
-      <c r="E31" s="107"/>
-      <c r="F31" s="108"/>
+      <c r="E31" s="93" t="s">
+        <v>480</v>
+      </c>
+      <c r="F31" s="93">
+        <v>77</v>
+      </c>
       <c r="G31" s="104" t="s">
         <v>267</v>
       </c>
@@ -8159,9 +8218,15 @@
       <c r="D32" s="109">
         <v>60</v>
       </c>
-      <c r="E32" s="109"/>
-      <c r="F32" s="109"/>
-      <c r="G32" s="109"/>
+      <c r="E32" s="109" t="s">
+        <v>490</v>
+      </c>
+      <c r="F32" s="109">
+        <v>62</v>
+      </c>
+      <c r="G32" s="109">
+        <v>60</v>
+      </c>
       <c r="H32" s="86" t="s">
         <v>479</v>
       </c>

--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="768" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A07AAB7-1F47-5547-B1A6-8D56B4033169}"/>
+  <xr:revisionPtr revIDLastSave="809" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1B034F8-2F79-F14D-8B07-CD63CED0B63C}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19740" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19740" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="497">
   <si>
     <t>number</t>
   </si>
@@ -1682,6 +1682,24 @@
   </si>
   <si>
     <t>350 CPS</t>
+  </si>
+  <si>
+    <t>228.8 KPPS / 2600 Mbps</t>
+  </si>
+  <si>
+    <t>285.6 KPPS / 191 Mbps</t>
+  </si>
+  <si>
+    <t>284 KPPS / 1208 Mbps</t>
+  </si>
+  <si>
+    <t>192 KPPS / 566 Mbps</t>
+  </si>
+  <si>
+    <t>280 KPPS / 835 Mbps</t>
+  </si>
+  <si>
+    <t>281.6 KPPS / 841 Mbps</t>
   </si>
 </sst>
 </file>
@@ -2139,7 +2157,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2302,7 +2320,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2438,12 +2455,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2772,2165 +2783,2165 @@
   <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="68" customWidth="1"/>
-    <col min="2" max="2" width="179.5" style="68" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="68" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="68"/>
+    <col min="1" max="1" width="15.6640625" style="67" customWidth="1"/>
+    <col min="2" max="2" width="179.5" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="67"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="67" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="68" t="s">
+      <c r="G2" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="68" t="s">
+      <c r="H2" s="67" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="68" t="s">
+      <c r="F3" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="67" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="C4" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="68" t="s">
+      <c r="F4" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="68" t="s">
+      <c r="H4" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="68" t="s">
+      <c r="F6" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="H6" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="68" t="s">
+      <c r="D7" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="68" t="s">
+      <c r="E7" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="68" t="s">
+      <c r="F7" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="68" t="s">
+      <c r="G7" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="68" t="s">
+      <c r="H7" s="67" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="68" t="s">
+      <c r="C8" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="68" t="s">
+      <c r="D8" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="68" t="s">
+      <c r="E8" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="68" t="s">
+      <c r="F8" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="68" t="s">
+      <c r="H8" s="67" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="68" t="s">
+      <c r="D9" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="68" t="s">
+      <c r="E9" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="68" t="s">
+      <c r="F9" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="67" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="68" t="s">
+      <c r="B10" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="68" t="s">
+      <c r="E10" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="68" t="s">
+      <c r="F10" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="68" t="s">
+      <c r="H10" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="68" t="s">
+      <c r="A11" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="68" t="s">
+      <c r="B11" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="68" t="s">
+      <c r="E11" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="68" t="s">
+      <c r="F11" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="68" t="s">
+      <c r="H11" s="67" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="68" t="s">
+      <c r="H12" s="67" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="68" t="s">
+      <c r="E13" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="68" t="s">
+      <c r="F13" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="G13" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="68" t="s">
+      <c r="H13" s="67" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="68" t="s">
+      <c r="B14" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="68" t="s">
+      <c r="E14" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="68" t="s">
+      <c r="F14" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="68" t="s">
+      <c r="G14" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="68" t="s">
+      <c r="H14" s="67" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="68" t="s">
+      <c r="E15" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="68" t="s">
+      <c r="F15" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="68" t="s">
+      <c r="G15" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="68" t="s">
+      <c r="H15" s="67" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="68" t="s">
+      <c r="B16" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="68" t="s">
+      <c r="E16" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="68" t="s">
+      <c r="F16" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="68" t="s">
+      <c r="G16" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="68" t="s">
+      <c r="H16" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="68" t="s">
+      <c r="E17" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H17" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="68" t="s">
+      <c r="A18" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="68" t="s">
+      <c r="B18" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="68" t="s">
+      <c r="E18" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="68" t="s">
+      <c r="F18" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="68" t="s">
+      <c r="G18" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="68" t="s">
+      <c r="H18" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="68" t="s">
+      <c r="B19" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="68" t="s">
+      <c r="E19" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="68" t="s">
+      <c r="F19" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="68" t="s">
+      <c r="G19" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="68" t="s">
+      <c r="H19" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="68" t="s">
+      <c r="A20" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="68" t="s">
+      <c r="E20" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="68" t="s">
+      <c r="F20" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="G20" s="68" t="s">
+      <c r="G20" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="H20" s="68" t="s">
+      <c r="H20" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="68" t="s">
+      <c r="E21" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="68" t="s">
+      <c r="F21" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="68" t="s">
+      <c r="G21" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="H21" s="68" t="s">
+      <c r="H21" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="68" t="s">
+      <c r="A22" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="68" t="s">
+      <c r="E22" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="68" t="s">
+      <c r="F22" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="68" t="s">
+      <c r="G22" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="H22" s="68" t="s">
+      <c r="H22" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="68" t="s">
+      <c r="B23" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="68" t="s">
+      <c r="E23" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="68" t="s">
+      <c r="F23" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G23" s="68" t="s">
+      <c r="G23" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="68" t="s">
+      <c r="H23" s="67" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="68" t="s">
+      <c r="A24" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="68" t="s">
+      <c r="B24" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="68" t="s">
+      <c r="E24" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="68" t="s">
+      <c r="F24" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G24" s="68" t="s">
+      <c r="G24" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="H24" s="68" t="s">
+      <c r="H24" s="67" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="68" t="s">
+      <c r="A25" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="68" t="s">
+      <c r="C25" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="68" t="s">
+      <c r="E25" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="68" t="s">
+      <c r="F25" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="68" t="s">
+      <c r="G25" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="68" t="s">
+      <c r="H25" s="67" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="68" t="s">
+      <c r="A26" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="68" t="s">
+      <c r="B26" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E26" s="68" t="s">
+      <c r="E26" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="68" t="s">
+      <c r="F26" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G26" s="68" t="s">
+      <c r="G26" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="68" t="s">
+      <c r="H26" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="68" t="s">
+      <c r="A27" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E27" s="68" t="s">
+      <c r="E27" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="68" t="s">
+      <c r="F27" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="68" t="s">
+      <c r="G27" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="H27" s="68" t="s">
+      <c r="H27" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="68" t="s">
+      <c r="A28" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="68" t="s">
+      <c r="B28" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="68" t="s">
+      <c r="E28" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="68" t="s">
+      <c r="F28" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="G28" s="68" t="s">
+      <c r="G28" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="68" t="s">
+      <c r="H28" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="68" t="s">
+      <c r="A29" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="68" t="s">
+      <c r="B29" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="68" t="s">
+      <c r="E29" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="68" t="s">
+      <c r="F29" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G29" s="68" t="s">
+      <c r="G29" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="H29" s="68" t="s">
+      <c r="H29" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="68" t="s">
+      <c r="A30" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="68" t="s">
+      <c r="B30" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="68" t="s">
+      <c r="E30" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="68" t="s">
+      <c r="F30" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G30" s="68" t="s">
+      <c r="G30" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="H30" s="68" t="s">
+      <c r="H30" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="68" t="s">
+      <c r="A31" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="B31" s="68" t="s">
+      <c r="B31" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="68" t="s">
+      <c r="E31" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F31" s="68" t="s">
+      <c r="F31" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="68" t="s">
+      <c r="G31" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="68" t="s">
+      <c r="H31" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="68" t="s">
+      <c r="A32" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="68" t="s">
+      <c r="B32" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="68" t="s">
+      <c r="E32" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="68" t="s">
+      <c r="F32" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="G32" s="68" t="s">
+      <c r="G32" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="H32" s="68" t="s">
+      <c r="H32" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="68" t="s">
+      <c r="A33" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="B33" s="68" t="s">
+      <c r="B33" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="68" t="s">
+      <c r="E33" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F33" s="68" t="s">
+      <c r="F33" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="G33" s="68" t="s">
+      <c r="G33" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="H33" s="68" t="s">
+      <c r="H33" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="68" t="s">
+      <c r="A34" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="68" t="s">
+      <c r="B34" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="68" t="s">
+      <c r="E34" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F34" s="68" t="s">
+      <c r="F34" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="68" t="s">
+      <c r="G34" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="H34" s="68" t="s">
+      <c r="H34" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="68" t="s">
+      <c r="A35" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="69" t="s">
+      <c r="B35" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E35" s="68" t="s">
+      <c r="E35" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F35" s="68" t="s">
+      <c r="F35" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="68" t="s">
+      <c r="G35" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="H35" s="68" t="s">
+      <c r="H35" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="68" t="s">
+      <c r="A36" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="69" t="s">
+      <c r="B36" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E36" s="68" t="s">
+      <c r="E36" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F36" s="68" t="s">
+      <c r="F36" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G36" s="68" t="s">
+      <c r="G36" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="H36" s="68" t="s">
+      <c r="H36" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="68" t="s">
+      <c r="A37" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="69" t="s">
+      <c r="B37" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="68" t="s">
+      <c r="C37" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E37" s="68" t="s">
+      <c r="E37" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F37" s="68" t="s">
+      <c r="F37" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G37" s="68" t="s">
+      <c r="G37" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="H37" s="68" t="s">
+      <c r="H37" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="68" t="s">
+      <c r="A38" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="B38" s="69" t="s">
+      <c r="B38" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="68" t="s">
+      <c r="C38" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="68" t="s">
+      <c r="E38" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F38" s="68" t="s">
+      <c r="F38" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G38" s="68" t="s">
+      <c r="G38" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="H38" s="68" t="s">
+      <c r="H38" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="68" t="s">
+      <c r="A39" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="B39" s="69" t="s">
+      <c r="B39" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="68" t="s">
+      <c r="E39" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F39" s="68" t="s">
+      <c r="F39" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G39" s="68" t="s">
+      <c r="G39" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="H39" s="68" t="s">
+      <c r="H39" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="68" t="s">
+      <c r="A40" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="B40" s="69" t="s">
+      <c r="B40" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="68" t="s">
+      <c r="C40" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E40" s="68" t="s">
+      <c r="E40" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="68" t="s">
+      <c r="F40" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="68" t="s">
+      <c r="G40" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="H40" s="68" t="s">
+      <c r="H40" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="68" t="s">
+      <c r="A41" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="B41" s="69" t="s">
+      <c r="B41" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="C41" s="68" t="s">
+      <c r="C41" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="68" t="s">
+      <c r="D41" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="E41" s="68" t="s">
+      <c r="E41" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F41" s="68" t="s">
+      <c r="F41" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G41" s="68" t="s">
+      <c r="G41" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="H41" s="68" t="s">
+      <c r="H41" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="68" t="s">
+      <c r="A42" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="B42" s="69" t="s">
+      <c r="B42" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="68" t="s">
+      <c r="D42" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="E42" s="68" t="s">
+      <c r="E42" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F42" s="68" t="s">
+      <c r="F42" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G42" s="68" t="s">
+      <c r="G42" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="H42" s="68" t="s">
+      <c r="H42" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="68" t="s">
+      <c r="A43" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="B43" s="69" t="s">
+      <c r="B43" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="68" t="s">
+      <c r="C43" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D43" s="68" t="s">
+      <c r="D43" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="E43" s="68" t="s">
+      <c r="E43" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F43" s="68" t="s">
+      <c r="F43" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G43" s="68" t="s">
+      <c r="G43" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="H43" s="68" t="s">
+      <c r="H43" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="68" t="s">
+      <c r="A44" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="68" t="s">
+      <c r="B44" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="68" t="s">
+      <c r="C44" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="E44" s="68" t="s">
+      <c r="E44" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="F44" s="68" t="s">
+      <c r="F44" s="67" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="68" t="s">
+      <c r="A45" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="68" t="s">
+      <c r="B45" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="E45" s="68" t="s">
+      <c r="E45" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="F45" s="68" t="s">
+      <c r="F45" s="67" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="68" t="s">
+      <c r="A46" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="B46" s="68" t="s">
+      <c r="B46" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="E46" s="68" t="s">
+      <c r="E46" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="F46" s="68" t="s">
+      <c r="F46" s="67" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="68" t="s">
+      <c r="A47" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="68" t="s">
+      <c r="C47" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="68" t="s">
+      <c r="E47" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="F47" s="68" t="s">
+      <c r="F47" s="67" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="68" t="s">
+      <c r="A48" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="C48" s="68" t="s">
+      <c r="C48" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="68" t="s">
+      <c r="E48" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="F48" s="68" t="s">
+      <c r="F48" s="67" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="68" t="s">
+      <c r="A49" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="68" t="s">
+      <c r="C49" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E49" s="68" t="s">
+      <c r="E49" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="F49" s="68" t="s">
+      <c r="F49" s="67" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="68" t="s">
+      <c r="A50" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="B50" s="68" t="s">
+      <c r="B50" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="68" t="s">
+      <c r="D50" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="E50" s="68" t="s">
+      <c r="E50" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F50" s="68" t="s">
+      <c r="F50" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G50" s="68" t="s">
+      <c r="G50" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="H50" s="68" t="s">
+      <c r="H50" s="67" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="68" t="s">
+      <c r="A51" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="B51" s="68" t="s">
+      <c r="B51" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="68" t="s">
+      <c r="C51" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="D51" s="68" t="s">
+      <c r="D51" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="E51" s="68" t="s">
+      <c r="E51" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F51" s="68" t="s">
+      <c r="F51" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G51" s="68" t="s">
+      <c r="G51" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="H51" s="68" t="s">
+      <c r="H51" s="67" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="68" t="s">
+      <c r="A52" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="B52" s="68" t="s">
+      <c r="B52" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="D52" s="68" t="s">
+      <c r="D52" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="E52" s="68" t="s">
+      <c r="E52" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F52" s="68" t="s">
+      <c r="F52" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G52" s="68" t="s">
+      <c r="G52" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="H52" s="68" t="s">
+      <c r="H52" s="67" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="68" t="s">
+      <c r="A53" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="B53" s="68" t="s">
+      <c r="B53" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="68" t="s">
+      <c r="E53" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F53" s="68" t="s">
+      <c r="F53" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="G53" s="68" t="s">
+      <c r="G53" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="H53" s="68" t="s">
+      <c r="H53" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="68" t="s">
+      <c r="A54" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="B54" s="68" t="s">
+      <c r="B54" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E54" s="68" t="s">
+      <c r="E54" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F54" s="68" t="s">
+      <c r="F54" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="G54" s="68" t="s">
+      <c r="G54" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="H54" s="68" t="s">
+      <c r="H54" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="68" t="s">
+      <c r="A55" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="B55" s="68" t="s">
+      <c r="B55" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="68" t="s">
+      <c r="C55" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E55" s="68" t="s">
+      <c r="E55" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F55" s="68" t="s">
+      <c r="F55" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="G55" s="68" t="s">
+      <c r="G55" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="H55" s="68" t="s">
+      <c r="H55" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="68" t="s">
+      <c r="A56" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="B56" s="69" t="s">
+      <c r="B56" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="C56" s="68" t="s">
+      <c r="C56" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="68" t="s">
+      <c r="E56" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F56" s="68" t="s">
+      <c r="F56" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G56" s="68" t="s">
+      <c r="G56" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="H56" s="68" t="s">
+      <c r="H56" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="68" t="s">
+      <c r="A57" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="B57" s="69" t="s">
+      <c r="B57" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="C57" s="68" t="s">
+      <c r="C57" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E57" s="68" t="s">
+      <c r="E57" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F57" s="68" t="s">
+      <c r="F57" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G57" s="68" t="s">
+      <c r="G57" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="H57" s="68" t="s">
+      <c r="H57" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="68" t="s">
+      <c r="A58" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="B58" s="69" t="s">
+      <c r="B58" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="68" t="s">
+      <c r="C58" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="68" t="s">
+      <c r="E58" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F58" s="68" t="s">
+      <c r="F58" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G58" s="68" t="s">
+      <c r="G58" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="H58" s="68" t="s">
+      <c r="H58" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="68" t="s">
+      <c r="A59" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="68" t="s">
+      <c r="B59" s="67" t="s">
         <v>125</v>
       </c>
-      <c r="C59" s="68" t="s">
+      <c r="C59" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="68" t="s">
+      <c r="E59" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F59" s="68" t="s">
+      <c r="F59" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="G59" s="68" t="s">
+      <c r="G59" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="H59" s="68" t="s">
+      <c r="H59" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="68" t="s">
+      <c r="A60" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="68" t="s">
+      <c r="B60" s="67" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="68" t="s">
+      <c r="C60" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E60" s="68" t="s">
+      <c r="E60" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F60" s="68" t="s">
+      <c r="F60" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="G60" s="68" t="s">
+      <c r="G60" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="H60" s="68" t="s">
+      <c r="H60" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="68" t="s">
+      <c r="A61" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="B61" s="68" t="s">
+      <c r="B61" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="68" t="s">
+      <c r="C61" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E61" s="68" t="s">
+      <c r="E61" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F61" s="68" t="s">
+      <c r="F61" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="G61" s="68" t="s">
+      <c r="G61" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="H61" s="68" t="s">
+      <c r="H61" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="68" t="s">
+      <c r="A62" s="67" t="s">
         <v>129</v>
       </c>
-      <c r="B62" s="68" t="s">
+      <c r="B62" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="C62" s="68" t="s">
+      <c r="C62" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="68" t="s">
+      <c r="E62" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F62" s="68" t="s">
+      <c r="F62" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="G62" s="68" t="s">
+      <c r="G62" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="H62" s="68" t="s">
+      <c r="H62" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="68" t="s">
+      <c r="A63" s="67" t="s">
         <v>130</v>
       </c>
-      <c r="B63" s="68" t="s">
+      <c r="B63" s="67" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="68" t="s">
+      <c r="C63" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="68" t="s">
+      <c r="E63" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F63" s="68" t="s">
+      <c r="F63" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="G63" s="68" t="s">
+      <c r="G63" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="H63" s="68" t="s">
+      <c r="H63" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="68" t="s">
+      <c r="A64" s="67" t="s">
         <v>132</v>
       </c>
-      <c r="B64" s="68" t="s">
+      <c r="B64" s="67" t="s">
         <v>131</v>
       </c>
-      <c r="C64" s="68" t="s">
+      <c r="C64" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E64" s="68" t="s">
+      <c r="E64" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F64" s="68" t="s">
+      <c r="F64" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="G64" s="68" t="s">
+      <c r="G64" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="H64" s="68" t="s">
+      <c r="H64" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="68" t="s">
+      <c r="A65" s="67" t="s">
         <v>133</v>
       </c>
-      <c r="B65" s="69" t="s">
+      <c r="B65" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="C65" s="68" t="s">
+      <c r="C65" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E65" s="68" t="s">
+      <c r="E65" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F65" s="68" t="s">
+      <c r="F65" s="67" t="s">
         <v>135</v>
       </c>
-      <c r="G65" s="68" t="s">
+      <c r="G65" s="67" t="s">
         <v>135</v>
       </c>
-      <c r="H65" s="68" t="s">
+      <c r="H65" s="67" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="68" t="s">
+      <c r="A66" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="B66" s="69" t="s">
+      <c r="B66" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="C66" s="68" t="s">
+      <c r="C66" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E66" s="68" t="s">
+      <c r="E66" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F66" s="68" t="s">
+      <c r="F66" s="67" t="s">
         <v>135</v>
       </c>
-      <c r="G66" s="68" t="s">
+      <c r="G66" s="67" t="s">
         <v>135</v>
       </c>
-      <c r="H66" s="68" t="s">
+      <c r="H66" s="67" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="68" t="s">
+      <c r="A67" s="67" t="s">
         <v>138</v>
       </c>
-      <c r="B67" s="69" t="s">
+      <c r="B67" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="68" t="s">
+      <c r="D67" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="E67" s="68" t="s">
+      <c r="E67" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="F67" s="68" t="s">
+      <c r="F67" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G67" s="68" t="s">
+      <c r="G67" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="H67" s="68" t="s">
+      <c r="H67" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="68" t="s">
+      <c r="A68" s="67" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="69" t="s">
+      <c r="B68" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="C68" s="68" t="s">
+      <c r="C68" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E68" s="68" t="s">
+      <c r="E68" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="F68" s="68" t="s">
+      <c r="F68" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G68" s="68" t="s">
+      <c r="G68" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="H68" s="68" t="s">
+      <c r="H68" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="68" t="s">
+      <c r="A69" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="B69" s="69" t="s">
+      <c r="B69" s="68" t="s">
         <v>144</v>
       </c>
-      <c r="C69" s="68" t="s">
+      <c r="C69" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D69" s="68" t="s">
+      <c r="D69" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="E69" s="68" t="s">
+      <c r="E69" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F69" s="68" t="s">
+      <c r="F69" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G69" s="68" t="s">
+      <c r="G69" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="H69" s="68" t="s">
+      <c r="H69" s="67" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="68" t="s">
+      <c r="A70" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="B70" s="69" t="s">
+      <c r="B70" s="68" t="s">
         <v>144</v>
       </c>
-      <c r="C70" s="68" t="s">
+      <c r="C70" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E70" s="68" t="s">
+      <c r="E70" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F70" s="68" t="s">
+      <c r="F70" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="G70" s="68" t="s">
+      <c r="G70" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="H70" s="68" t="s">
+      <c r="H70" s="67" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="68" t="s">
+      <c r="A71" s="67" t="s">
         <v>148</v>
       </c>
-      <c r="B71" s="69" t="s">
+      <c r="B71" s="68" t="s">
         <v>149</v>
       </c>
-      <c r="C71" s="68" t="s">
+      <c r="C71" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D71" s="68" t="s">
+      <c r="D71" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="E71" s="68" t="s">
+      <c r="E71" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F71" s="68" t="s">
+      <c r="F71" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="G71" s="68" t="s">
+      <c r="G71" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="H71" s="68" t="s">
+      <c r="H71" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="68" t="s">
+      <c r="A72" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="B72" s="69" t="s">
+      <c r="B72" s="68" t="s">
         <v>149</v>
       </c>
-      <c r="C72" s="68" t="s">
+      <c r="C72" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D72" s="68" t="s">
+      <c r="D72" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="E72" s="68" t="s">
+      <c r="E72" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F72" s="68" t="s">
+      <c r="F72" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="G72" s="68" t="s">
+      <c r="G72" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="H72" s="68" t="s">
+      <c r="H72" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="68" t="s">
+      <c r="A73" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="B73" s="68" t="s">
+      <c r="B73" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="C73" s="68" t="s">
+      <c r="C73" s="67" t="s">
         <v>153</v>
       </c>
-      <c r="E73" s="68" t="s">
+      <c r="E73" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F73" s="68" t="s">
+      <c r="F73" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="G73" s="68" t="s">
+      <c r="G73" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="H73" s="68" t="s">
+      <c r="H73" s="67" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="68" t="s">
+      <c r="A74" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="B74" s="68" t="s">
+      <c r="B74" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="C74" s="68" t="s">
+      <c r="C74" s="67" t="s">
         <v>153</v>
       </c>
-      <c r="E74" s="68" t="s">
+      <c r="E74" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F74" s="68" t="s">
+      <c r="F74" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="G74" s="68" t="s">
+      <c r="G74" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="H74" s="68" t="s">
+      <c r="H74" s="67" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="68" t="s">
+      <c r="A75" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="B75" s="68" t="s">
+      <c r="B75" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="C75" s="68" t="s">
+      <c r="C75" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E75" s="68" t="s">
+      <c r="E75" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F75" s="68" t="s">
+      <c r="F75" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="G75" s="68" t="s">
+      <c r="G75" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="H75" s="68" t="s">
+      <c r="H75" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="68" t="s">
+      <c r="A76" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="B76" s="68" t="s">
+      <c r="B76" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="C76" s="68" t="s">
+      <c r="C76" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E76" s="68" t="s">
+      <c r="E76" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F76" s="68" t="s">
+      <c r="F76" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="G76" s="68" t="s">
+      <c r="G76" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="H76" s="68" t="s">
+      <c r="H76" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="68" t="s">
+      <c r="A77" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="B77" s="68" t="s">
+      <c r="B77" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="C77" s="68" t="s">
+      <c r="C77" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E77" s="68" t="s">
+      <c r="E77" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F77" s="68" t="s">
+      <c r="F77" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="G77" s="68" t="s">
+      <c r="G77" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="H77" s="68" t="s">
+      <c r="H77" s="67" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="68" t="s">
+      <c r="A78" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="B78" s="68" t="s">
+      <c r="B78" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="C78" s="68" t="s">
+      <c r="C78" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E78" s="68" t="s">
+      <c r="E78" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F78" s="68" t="s">
+      <c r="F78" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="G78" s="68" t="s">
+      <c r="G78" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="H78" s="68" t="s">
+      <c r="H78" s="67" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="68" t="s">
+      <c r="A79" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="B79" s="68" t="s">
+      <c r="B79" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="C79" s="68" t="s">
+      <c r="C79" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E79" s="68" t="s">
+      <c r="E79" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F79" s="68" t="s">
+      <c r="F79" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G79" s="68" t="s">
+      <c r="G79" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="H79" s="68" t="s">
+      <c r="H79" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="68" t="s">
+      <c r="A80" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="B80" s="68" t="s">
+      <c r="B80" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="C80" s="68" t="s">
+      <c r="C80" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E80" s="68" t="s">
+      <c r="E80" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F80" s="68" t="s">
+      <c r="F80" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G80" s="68" t="s">
+      <c r="G80" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="H80" s="68" t="s">
+      <c r="H80" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="68" t="s">
+      <c r="A81" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="B81" s="68" t="s">
+      <c r="B81" s="67" t="s">
         <v>168</v>
       </c>
-      <c r="C81" s="68" t="s">
+      <c r="C81" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E81" s="68" t="s">
+      <c r="E81" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F81" s="68" t="s">
+      <c r="F81" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="G81" s="68" t="s">
+      <c r="G81" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="H81" s="68" t="s">
+      <c r="H81" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="68" t="s">
+      <c r="A82" s="67" t="s">
         <v>169</v>
       </c>
-      <c r="B82" s="68" t="s">
+      <c r="B82" s="67" t="s">
         <v>168</v>
       </c>
-      <c r="C82" s="68" t="s">
+      <c r="C82" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E82" s="68" t="s">
+      <c r="E82" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="F82" s="68" t="s">
+      <c r="F82" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G82" s="68" t="s">
+      <c r="G82" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="H82" s="68" t="s">
+      <c r="H82" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="68" t="s">
+      <c r="A83" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="B83" s="69" t="s">
+      <c r="B83" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="C83" s="68" t="s">
+      <c r="C83" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="E83" s="68" t="s">
+      <c r="E83" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="F83" s="68" t="s">
+      <c r="F83" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="68" t="s">
+      <c r="A84" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="B84" s="69" t="s">
+      <c r="B84" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="C84" s="68" t="s">
+      <c r="C84" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="E84" s="68" t="s">
+      <c r="E84" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="F84" s="68" t="s">
+      <c r="F84" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="68" t="s">
+      <c r="A85" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="B85" s="69" t="s">
+      <c r="B85" s="68" t="s">
         <v>176</v>
       </c>
-      <c r="C85" s="68" t="s">
+      <c r="C85" s="67" t="s">
         <v>177</v>
       </c>
-      <c r="E85" s="68" t="s">
+      <c r="E85" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F85" s="68" t="s">
+      <c r="F85" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="G85" s="68" t="s">
+      <c r="G85" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="H85" s="68" t="s">
+      <c r="H85" s="67" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="68" t="s">
+      <c r="A86" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="B86" s="69" t="s">
+      <c r="B86" s="68" t="s">
         <v>176</v>
       </c>
-      <c r="C86" s="68" t="s">
+      <c r="C86" s="67" t="s">
         <v>177</v>
       </c>
-      <c r="E86" s="68" t="s">
+      <c r="E86" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F86" s="68" t="s">
+      <c r="F86" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="G86" s="68" t="s">
+      <c r="G86" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="H86" s="68" t="s">
+      <c r="H86" s="67" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="68" t="s">
+      <c r="A87" s="67" t="s">
         <v>179</v>
       </c>
-      <c r="B87" s="68" t="s">
+      <c r="B87" s="67" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="68" t="s">
+      <c r="C87" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E87" s="68" t="s">
+      <c r="E87" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F87" s="68" t="s">
+      <c r="F87" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="G87" s="68" t="s">
+      <c r="G87" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="H87" s="68" t="s">
+      <c r="H87" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="68" t="s">
+      <c r="A88" s="67" t="s">
         <v>181</v>
       </c>
-      <c r="B88" s="68" t="s">
+      <c r="B88" s="67" t="s">
         <v>180</v>
       </c>
-      <c r="C88" s="68" t="s">
+      <c r="C88" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E88" s="68" t="s">
+      <c r="E88" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F88" s="68" t="s">
+      <c r="F88" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="G88" s="68" t="s">
+      <c r="G88" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="H88" s="68" t="s">
+      <c r="H88" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="68" t="s">
+      <c r="A89" s="67" t="s">
         <v>182</v>
       </c>
-      <c r="B89" s="68" t="s">
+      <c r="B89" s="67" t="s">
         <v>183</v>
       </c>
-      <c r="C89" s="68" t="s">
+      <c r="C89" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E89" s="68" t="s">
+      <c r="E89" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F89" s="68" t="s">
+      <c r="F89" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="G89" s="68" t="s">
+      <c r="G89" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="H89" s="68" t="s">
+      <c r="H89" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="68" t="s">
+      <c r="A90" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="B90" s="68" t="s">
+      <c r="B90" s="67" t="s">
         <v>183</v>
       </c>
-      <c r="C90" s="68" t="s">
+      <c r="C90" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E90" s="68" t="s">
+      <c r="E90" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F90" s="68" t="s">
+      <c r="F90" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="G90" s="68" t="s">
+      <c r="G90" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="H90" s="68" t="s">
+      <c r="H90" s="67" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="68" t="s">
+      <c r="A91" s="67" t="s">
         <v>185</v>
       </c>
-      <c r="B91" s="68" t="s">
+      <c r="B91" s="67" t="s">
         <v>186</v>
       </c>
-      <c r="C91" s="68" t="s">
+      <c r="C91" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E91" s="68" t="s">
+      <c r="E91" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F91" s="68" t="s">
+      <c r="F91" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="G91" s="68" t="s">
+      <c r="G91" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="H91" s="68" t="s">
+      <c r="H91" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="68" t="s">
+      <c r="A92" s="67" t="s">
         <v>188</v>
       </c>
-      <c r="B92" s="68" t="s">
+      <c r="B92" s="67" t="s">
         <v>186</v>
       </c>
-      <c r="C92" s="68" t="s">
+      <c r="C92" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E92" s="68" t="s">
+      <c r="E92" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F92" s="68" t="s">
+      <c r="F92" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="G92" s="68" t="s">
+      <c r="G92" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="H92" s="68" t="s">
+      <c r="H92" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="68" t="s">
+      <c r="A93" s="67" t="s">
         <v>189</v>
       </c>
-      <c r="B93" s="68" t="s">
+      <c r="B93" s="67" t="s">
         <v>190</v>
       </c>
-      <c r="C93" s="68" t="s">
+      <c r="C93" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E93" s="68" t="s">
+      <c r="E93" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F93" s="68" t="s">
+      <c r="F93" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="G93" s="68" t="s">
+      <c r="G93" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="H93" s="68" t="s">
+      <c r="H93" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="68" t="s">
+      <c r="A94" s="67" t="s">
         <v>191</v>
       </c>
-      <c r="B94" s="68" t="s">
+      <c r="B94" s="67" t="s">
         <v>190</v>
       </c>
-      <c r="C94" s="68" t="s">
+      <c r="C94" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="E94" s="68" t="s">
+      <c r="E94" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="F94" s="68" t="s">
+      <c r="F94" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="G94" s="68" t="s">
+      <c r="G94" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="H94" s="68" t="s">
+      <c r="H94" s="67" t="s">
         <v>54</v>
       </c>
     </row>
@@ -5009,10 +5020,10 @@
       <c r="A1" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="B1" s="79" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="81"/>
+      <c r="C1" s="80"/>
       <c r="D1" s="36" t="s">
         <v>194</v>
       </c>
@@ -5090,7 +5101,7 @@
       <c r="C6" s="1">
         <v>95</v>
       </c>
-      <c r="D6" s="60">
+      <c r="D6" s="59">
         <v>69</v>
       </c>
       <c r="E6" s="21"/>
@@ -5105,7 +5116,7 @@
       <c r="C7" s="4">
         <v>95</v>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="58">
         <v>70</v>
       </c>
     </row>
@@ -5133,7 +5144,7 @@
       <c r="C9" s="4">
         <v>96</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="58">
         <v>73</v>
       </c>
     </row>
@@ -5175,7 +5186,7 @@
       <c r="C12" s="1">
         <v>93</v>
       </c>
-      <c r="D12" s="59">
+      <c r="D12" s="58">
         <v>45</v>
       </c>
     </row>
@@ -5506,7 +5517,7 @@
       <c r="C35" s="48">
         <v>90</v>
       </c>
-      <c r="D35" s="64">
+      <c r="D35" s="63">
         <v>34</v>
       </c>
     </row>
@@ -5520,7 +5531,7 @@
       <c r="C36" s="4">
         <v>92</v>
       </c>
-      <c r="D36" s="64">
+      <c r="D36" s="63">
         <v>42</v>
       </c>
     </row>
@@ -5534,7 +5545,7 @@
       <c r="C37" s="4">
         <v>90</v>
       </c>
-      <c r="D37" s="60">
+      <c r="D37" s="59">
         <v>38</v>
       </c>
     </row>
@@ -5548,7 +5559,7 @@
       <c r="C38" s="4">
         <v>90</v>
       </c>
-      <c r="D38" s="60">
+      <c r="D38" s="59">
         <v>40</v>
       </c>
     </row>
@@ -5691,7 +5702,7 @@
       <c r="C48" s="23">
         <v>98</v>
       </c>
-      <c r="D48" s="59" t="s">
+      <c r="D48" s="58" t="s">
         <v>245</v>
       </c>
     </row>
@@ -5767,7 +5778,7 @@
       <c r="C54" s="23">
         <v>98</v>
       </c>
-      <c r="D54" s="59" t="s">
+      <c r="D54" s="58" t="s">
         <v>257</v>
       </c>
     </row>
@@ -5781,7 +5792,7 @@
       <c r="C55" s="23">
         <v>98</v>
       </c>
-      <c r="D55" s="59" t="s">
+      <c r="D55" s="58" t="s">
         <v>260</v>
       </c>
     </row>
@@ -5795,7 +5806,7 @@
       <c r="C56" s="23">
         <v>99</v>
       </c>
-      <c r="D56" s="59" t="s">
+      <c r="D56" s="58" t="s">
         <v>263</v>
       </c>
     </row>
@@ -5817,19 +5828,27 @@
       <c r="A58" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="59" t="s">
+      <c r="B58" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C58" s="23">
+        <v>80</v>
+      </c>
+      <c r="D58" s="58" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="59" t="s">
+      <c r="B59" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C59" s="23">
+        <v>80</v>
+      </c>
+      <c r="D59" s="58" t="s">
         <v>484</v>
       </c>
     </row>
@@ -5837,9 +5856,13 @@
       <c r="A60" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="59" t="s">
+      <c r="B60" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C60" s="23">
+        <v>80</v>
+      </c>
+      <c r="D60" s="58" t="s">
         <v>484</v>
       </c>
     </row>
@@ -5847,9 +5870,13 @@
       <c r="A61" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="59" t="s">
+      <c r="B61" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C61" s="23">
+        <v>78</v>
+      </c>
+      <c r="D61" s="58" t="s">
         <v>484</v>
       </c>
     </row>
@@ -5857,9 +5884,13 @@
       <c r="A62" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="59" t="s">
+      <c r="B62" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C62" s="23">
+        <v>85</v>
+      </c>
+      <c r="D62" s="58" t="s">
         <v>486</v>
       </c>
     </row>
@@ -5867,17 +5898,20 @@
       <c r="A63" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B63" s="4"/>
       <c r="C63" s="23"/>
-      <c r="D63" s="59"/>
+      <c r="D63" s="58"/>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="53"/>
-      <c r="D64" s="59" t="s">
+      <c r="B64" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C64" s="23">
+        <v>80</v>
+      </c>
+      <c r="D64" s="58" t="s">
         <v>485</v>
       </c>
     </row>
@@ -5899,7 +5933,7 @@
       <c r="C66" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="D66" s="67"/>
+      <c r="D66" s="66"/>
     </row>
     <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
@@ -6141,7 +6175,7 @@
         <v>424</v>
       </c>
       <c r="C93" s="57"/>
-      <c r="D93" s="71"/>
+      <c r="D93" s="70"/>
     </row>
     <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
@@ -6189,11 +6223,11 @@
       <c r="A97" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B97" s="72">
+      <c r="B97" s="71">
         <v>26000</v>
       </c>
-      <c r="C97" s="70"/>
-      <c r="D97" s="70" t="s">
+      <c r="C97" s="69"/>
+      <c r="D97" s="69" t="s">
         <v>307</v>
       </c>
     </row>
@@ -6275,7 +6309,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A7BD36-8D88-3742-A4AC-48B0AFB67141}">
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="85.1640625" customWidth="1"/>
@@ -6290,10 +6324,10 @@
       <c r="A1" s="50" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="B1" s="79" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="81"/>
+      <c r="C1" s="80"/>
       <c r="D1" s="36" t="s">
         <v>194</v>
       </c>
@@ -6319,10 +6353,10 @@
       <c r="B3" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C3" s="59">
+      <c r="C3" s="58">
         <v>91</v>
       </c>
-      <c r="D3" s="59">
+      <c r="D3" s="58">
         <v>39</v>
       </c>
     </row>
@@ -6336,7 +6370,7 @@
       <c r="C4" s="4">
         <v>70</v>
       </c>
-      <c r="D4" s="59">
+      <c r="D4" s="58">
         <v>40</v>
       </c>
       <c r="E4" t="s">
@@ -6353,7 +6387,7 @@
       <c r="C5" s="4">
         <v>92</v>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="58">
         <v>57</v>
       </c>
     </row>
@@ -6367,7 +6401,7 @@
       <c r="C6" s="4">
         <v>94</v>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="58">
         <v>41</v>
       </c>
     </row>
@@ -6378,10 +6412,10 @@
       <c r="B7" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="59">
+      <c r="C7" s="58">
         <v>96</v>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="58">
         <v>43</v>
       </c>
     </row>
@@ -6395,7 +6429,7 @@
       <c r="C8" s="4">
         <v>90</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="58">
         <v>41</v>
       </c>
     </row>
@@ -6406,10 +6440,10 @@
       <c r="B9" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="59">
+      <c r="C9" s="58">
         <v>90</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="58">
         <v>43</v>
       </c>
     </row>
@@ -6423,7 +6457,7 @@
       <c r="C10" s="4">
         <v>90</v>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="58">
         <v>46</v>
       </c>
     </row>
@@ -6437,7 +6471,7 @@
       <c r="C11" s="4">
         <v>92</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="58">
         <v>40</v>
       </c>
     </row>
@@ -6448,10 +6482,10 @@
       <c r="B12" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C12" s="59">
+      <c r="C12" s="58">
         <v>92</v>
       </c>
-      <c r="D12" s="59">
+      <c r="D12" s="58">
         <v>42</v>
       </c>
     </row>
@@ -6465,7 +6499,7 @@
       <c r="C13" s="4">
         <v>90</v>
       </c>
-      <c r="D13" s="59">
+      <c r="D13" s="58">
         <v>47</v>
       </c>
     </row>
@@ -6479,7 +6513,7 @@
       <c r="C14" s="4">
         <v>90</v>
       </c>
-      <c r="D14" s="59">
+      <c r="D14" s="58">
         <v>47</v>
       </c>
     </row>
@@ -6493,7 +6527,7 @@
       <c r="C15" s="4">
         <v>94</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="58">
         <v>47</v>
       </c>
     </row>
@@ -6507,7 +6541,7 @@
       <c r="C16" s="4">
         <v>92</v>
       </c>
-      <c r="D16" s="59">
+      <c r="D16" s="58">
         <v>46</v>
       </c>
     </row>
@@ -6521,7 +6555,7 @@
       <c r="C17" s="7">
         <v>92</v>
       </c>
-      <c r="D17" s="59">
+      <c r="D17" s="58">
         <v>47</v>
       </c>
     </row>
@@ -6549,7 +6583,7 @@
       <c r="C19" s="55">
         <v>92</v>
       </c>
-      <c r="D19" s="59">
+      <c r="D19" s="58">
         <v>63</v>
       </c>
     </row>
@@ -6563,7 +6597,7 @@
       <c r="C20" s="57">
         <v>95</v>
       </c>
-      <c r="D20" s="59">
+      <c r="D20" s="58">
         <v>63</v>
       </c>
     </row>
@@ -6577,7 +6611,7 @@
       <c r="C21" s="57">
         <v>95</v>
       </c>
-      <c r="D21" s="59">
+      <c r="D21" s="58">
         <v>81</v>
       </c>
     </row>
@@ -6591,7 +6625,7 @@
       <c r="C22" s="57">
         <v>93</v>
       </c>
-      <c r="D22" s="59">
+      <c r="D22" s="58">
         <v>64</v>
       </c>
     </row>
@@ -6605,7 +6639,7 @@
       <c r="C23" s="57">
         <v>92</v>
       </c>
-      <c r="D23" s="59">
+      <c r="D23" s="58">
         <v>61</v>
       </c>
     </row>
@@ -6619,7 +6653,7 @@
       <c r="C24" s="57">
         <v>92</v>
       </c>
-      <c r="D24" s="59">
+      <c r="D24" s="58">
         <v>67</v>
       </c>
       <c r="F24" t="s">
@@ -6636,7 +6670,7 @@
       <c r="C25" s="57">
         <v>92</v>
       </c>
-      <c r="D25" s="59">
+      <c r="D25" s="58">
         <v>67</v>
       </c>
     </row>
@@ -6650,7 +6684,7 @@
       <c r="C26" s="57">
         <v>90</v>
       </c>
-      <c r="D26" s="59">
+      <c r="D26" s="58">
         <v>69</v>
       </c>
     </row>
@@ -6664,7 +6698,7 @@
       <c r="C27" s="57">
         <v>90</v>
       </c>
-      <c r="D27" s="59">
+      <c r="D27" s="58">
         <v>65</v>
       </c>
     </row>
@@ -6678,7 +6712,7 @@
       <c r="C28" s="57">
         <v>92</v>
       </c>
-      <c r="D28" s="59">
+      <c r="D28" s="58">
         <v>69</v>
       </c>
     </row>
@@ -6747,7 +6781,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>441</v>
       </c>
@@ -6761,7 +6795,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
         <v>230</v>
       </c>
@@ -6775,95 +6809,118 @@
         <v>198</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>231</v>
       </c>
       <c r="B35" s="48">
         <v>26000</v>
       </c>
-      <c r="C35" s="64">
+      <c r="C35" s="63">
         <v>90</v>
       </c>
-      <c r="D35" s="59">
+      <c r="D35" s="58">
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>232</v>
       </c>
       <c r="B36" s="4">
         <v>25400</v>
       </c>
-      <c r="C36" s="64">
+      <c r="C36" s="63">
         <v>93</v>
       </c>
-      <c r="D36" s="59">
+      <c r="D36" s="58">
         <v>41</v>
+      </c>
+      <c r="F36">
+        <v>70400</v>
+      </c>
+      <c r="G36">
+        <v>71400</v>
+      </c>
+      <c r="H36">
+        <v>71000</v>
       </c>
       <c r="I36">
         <v>58000</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J36">
+        <v>57200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>453</v>
       </c>
       <c r="B37" s="4">
         <v>13300</v>
       </c>
-      <c r="C37" s="60">
+      <c r="C37" s="59">
         <v>95</v>
       </c>
-      <c r="D37" s="59">
+      <c r="D37" s="58">
         <v>41</v>
       </c>
       <c r="F37">
-        <v>320000</v>
+        <f>F36*4</f>
+        <v>281600</v>
       </c>
       <c r="G37">
-        <v>340000</v>
+        <f>G36*4</f>
+        <v>285600</v>
       </c>
       <c r="H37">
-        <v>310000</v>
+        <f>H36*4</f>
+        <v>284000</v>
       </c>
       <c r="I37">
         <f>I36*4</f>
         <v>232000</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="J37">
+        <f>J36*4</f>
+        <v>228800</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>454</v>
       </c>
       <c r="B38" s="4">
         <v>3200</v>
       </c>
-      <c r="C38" s="60">
+      <c r="C38" s="59">
         <v>95</v>
       </c>
-      <c r="D38" s="59">
+      <c r="D38" s="58">
         <v>38</v>
       </c>
       <c r="F38">
         <f>F37*8*373/1000000</f>
-        <v>954.88</v>
+        <v>840.2944</v>
       </c>
       <c r="G38">
         <f>G37*8*84/1000000</f>
-        <v>228.48</v>
+        <v>191.92320000000001</v>
       </c>
       <c r="H38">
         <f>H37*8*532/1000000</f>
-        <v>1319.36</v>
+        <v>1208.704</v>
       </c>
       <c r="I38">
         <f>I37*8*1420/1000000</f>
         <v>2635.52</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="J38">
+        <f>J37*8*1420/1000000</f>
+        <v>2599.1680000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
         <v>233</v>
       </c>
@@ -6873,11 +6930,11 @@
       <c r="C39" s="15">
         <v>96</v>
       </c>
-      <c r="D39" s="59">
+      <c r="D39" s="58">
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
         <v>234</v>
       </c>
@@ -6887,14 +6944,14 @@
       <c r="C40" s="15">
         <v>92</v>
       </c>
-      <c r="D40" s="59">
+      <c r="D40" s="58">
         <v>45</v>
       </c>
       <c r="F40">
-        <v>210000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>455</v>
       </c>
@@ -6904,15 +6961,15 @@
       <c r="C41" s="4">
         <v>93</v>
       </c>
-      <c r="D41" s="59">
+      <c r="D41" s="58">
         <v>68</v>
       </c>
       <c r="F41">
         <f>F40*8*373/1000000</f>
-        <v>626.64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+        <v>835.52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>456</v>
       </c>
@@ -6922,14 +6979,14 @@
       <c r="C42" s="4">
         <v>93</v>
       </c>
-      <c r="D42" s="59">
+      <c r="D42" s="58">
         <v>79</v>
       </c>
       <c r="F42">
         <v>315000</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>457</v>
       </c>
@@ -6939,7 +6996,7 @@
       <c r="C43" s="4">
         <v>90</v>
       </c>
-      <c r="D43" s="59">
+      <c r="D43" s="58">
         <v>81</v>
       </c>
       <c r="F43">
@@ -6947,7 +7004,7 @@
         <v>939.96</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
         <v>235</v>
       </c>
@@ -6961,7 +7018,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
         <v>236</v>
       </c>
@@ -6971,11 +7028,11 @@
       <c r="C45" s="24">
         <v>98</v>
       </c>
-      <c r="D45" s="59" t="s">
+      <c r="D45" s="58" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
         <v>239</v>
       </c>
@@ -6985,11 +7042,11 @@
       <c r="C46" s="24">
         <v>98</v>
       </c>
-      <c r="D46" s="59" t="s">
+      <c r="D46" s="58" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>241</v>
       </c>
@@ -6999,11 +7056,11 @@
       <c r="C47" s="57">
         <v>96</v>
       </c>
-      <c r="D47" s="59" t="s">
+      <c r="D47" s="58" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>243</v>
       </c>
@@ -7013,7 +7070,7 @@
       <c r="C48" s="57">
         <v>96</v>
       </c>
-      <c r="D48" s="59" t="s">
+      <c r="D48" s="58" t="s">
         <v>245</v>
       </c>
     </row>
@@ -7023,7 +7080,7 @@
       </c>
       <c r="B49" s="23"/>
       <c r="C49" s="57"/>
-      <c r="D49" s="59"/>
+      <c r="D49" s="58"/>
     </row>
     <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
@@ -7035,7 +7092,7 @@
       <c r="C50" s="55">
         <v>98</v>
       </c>
-      <c r="D50" s="59" t="s">
+      <c r="D50" s="58" t="s">
         <v>238</v>
       </c>
     </row>
@@ -7049,7 +7106,7 @@
       <c r="C51" s="57">
         <v>98</v>
       </c>
-      <c r="D51" s="59" t="s">
+      <c r="D51" s="58" t="s">
         <v>238</v>
       </c>
     </row>
@@ -7063,7 +7120,7 @@
       <c r="C52" s="57">
         <v>99</v>
       </c>
-      <c r="D52" s="59" t="s">
+      <c r="D52" s="58" t="s">
         <v>238</v>
       </c>
     </row>
@@ -7074,10 +7131,10 @@
       <c r="B53" s="31" t="s">
         <v>346</v>
       </c>
-      <c r="C53" s="65">
+      <c r="C53" s="64">
         <v>99</v>
       </c>
-      <c r="D53" s="59" t="s">
+      <c r="D53" s="58" t="s">
         <v>238</v>
       </c>
     </row>
@@ -7088,10 +7145,10 @@
       <c r="B54" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="C54" s="66">
+      <c r="C54" s="65">
         <v>98</v>
       </c>
-      <c r="D54" s="59" t="s">
+      <c r="D54" s="58" t="s">
         <v>257</v>
       </c>
     </row>
@@ -7102,10 +7159,10 @@
       <c r="B55" s="23" t="s">
         <v>348</v>
       </c>
-      <c r="C55" s="66">
+      <c r="C55" s="65">
         <v>98</v>
       </c>
-      <c r="D55" s="59" t="s">
+      <c r="D55" s="58" t="s">
         <v>260</v>
       </c>
     </row>
@@ -7116,10 +7173,10 @@
       <c r="B56" s="23" t="s">
         <v>349</v>
       </c>
-      <c r="C56" s="66">
+      <c r="C56" s="65">
         <v>96</v>
       </c>
-      <c r="D56" s="59" t="s">
+      <c r="D56" s="58" t="s">
         <v>263</v>
       </c>
     </row>
@@ -7133,7 +7190,7 @@
       <c r="C57" s="57">
         <v>96</v>
       </c>
-      <c r="D57" s="59" t="s">
+      <c r="D57" s="58" t="s">
         <v>238</v>
       </c>
     </row>
@@ -7147,7 +7204,7 @@
       <c r="C58" s="55">
         <v>78</v>
       </c>
-      <c r="D58" s="59" t="s">
+      <c r="D58" s="58" t="s">
         <v>484</v>
       </c>
     </row>
@@ -7161,7 +7218,7 @@
       <c r="C59" s="57">
         <v>77</v>
       </c>
-      <c r="D59" s="59" t="s">
+      <c r="D59" s="58" t="s">
         <v>484</v>
       </c>
     </row>
@@ -7175,7 +7232,7 @@
       <c r="C60" s="57">
         <v>79</v>
       </c>
-      <c r="D60" s="59" t="s">
+      <c r="D60" s="58" t="s">
         <v>484</v>
       </c>
     </row>
@@ -7189,7 +7246,7 @@
       <c r="C61" s="57">
         <v>72</v>
       </c>
-      <c r="D61" s="59" t="s">
+      <c r="D61" s="58" t="s">
         <v>484</v>
       </c>
     </row>
@@ -7203,7 +7260,7 @@
       <c r="C62" s="57">
         <v>88</v>
       </c>
-      <c r="D62" s="59" t="s">
+      <c r="D62" s="58" t="s">
         <v>486</v>
       </c>
     </row>
@@ -7213,7 +7270,7 @@
       </c>
       <c r="B63" s="23"/>
       <c r="C63" s="57"/>
-      <c r="D63" s="59"/>
+      <c r="D63" s="58"/>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
@@ -7225,7 +7282,7 @@
       <c r="C64" s="57">
         <v>79</v>
       </c>
-      <c r="D64" s="59" t="s">
+      <c r="D64" s="58" t="s">
         <v>485</v>
       </c>
     </row>
@@ -7235,7 +7292,7 @@
       </c>
       <c r="B65" s="52"/>
       <c r="C65" s="57"/>
-      <c r="D65" s="59"/>
+      <c r="D65" s="58"/>
     </row>
     <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
@@ -7244,10 +7301,10 @@
       <c r="B66" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="C66" s="67" t="s">
+      <c r="C66" s="66" t="s">
         <v>197</v>
       </c>
-      <c r="D66" s="67" t="s">
+      <c r="D66" s="66" t="s">
         <v>403</v>
       </c>
     </row>
@@ -7493,15 +7550,15 @@
         <v>423</v>
       </c>
       <c r="C93" s="57"/>
-      <c r="D93" s="71"/>
+      <c r="D93" s="70"/>
     </row>
     <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B94" s="73"/>
+      <c r="B94" s="72"/>
       <c r="C94" s="56"/>
-      <c r="D94" s="71"/>
+      <c r="D94" s="70"/>
     </row>
     <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
@@ -7603,631 +7660,635 @@
   <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="62.5" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="162.5" style="86" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" style="86" customWidth="1"/>
-    <col min="3" max="3" width="29.1640625" style="86" customWidth="1"/>
-    <col min="4" max="4" width="26" style="86" customWidth="1"/>
-    <col min="5" max="5" width="47.6640625" style="86" customWidth="1"/>
-    <col min="6" max="6" width="26.5" style="86" customWidth="1"/>
-    <col min="7" max="7" width="33.83203125" style="86" customWidth="1"/>
-    <col min="8" max="16384" width="62.5" style="86"/>
+    <col min="1" max="1" width="162.5" style="85" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" style="85" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" style="85" customWidth="1"/>
+    <col min="4" max="4" width="26" style="85" customWidth="1"/>
+    <col min="5" max="5" width="47.6640625" style="85" customWidth="1"/>
+    <col min="6" max="6" width="26.5" style="85" customWidth="1"/>
+    <col min="7" max="7" width="33.83203125" style="85" customWidth="1"/>
+    <col min="8" max="16384" width="62.5" style="85"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="75" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="81" t="s">
         <v>409</v>
       </c>
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="82" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="84"/>
-      <c r="D1" s="85" t="s">
+      <c r="C1" s="83"/>
+      <c r="D1" s="84" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="83" t="s">
+      <c r="E1" s="82" t="s">
         <v>314</v>
       </c>
-      <c r="F1" s="84"/>
-      <c r="G1" s="85" t="s">
+      <c r="F1" s="83"/>
+      <c r="G1" s="84" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="50" x14ac:dyDescent="0.3">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="86" t="s">
         <v>410</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="87" t="s">
         <v>326</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="88" t="s">
+      <c r="D2" s="87" t="s">
         <v>412</v>
       </c>
-      <c r="E2" s="88" t="s">
+      <c r="E2" s="87" t="s">
         <v>196</v>
       </c>
-      <c r="F2" s="89" t="s">
+      <c r="F2" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="G2" s="89" t="s">
+      <c r="G2" s="88" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="89" t="s">
         <v>459</v>
       </c>
-      <c r="B3" s="91" t="s">
+      <c r="B3" s="90" t="s">
         <v>413</v>
       </c>
-      <c r="C3" s="92">
+      <c r="C3" s="91">
         <v>94</v>
       </c>
-      <c r="D3" s="93">
+      <c r="D3" s="92">
         <v>40</v>
       </c>
-      <c r="E3" s="91" t="s">
+      <c r="E3" s="90" t="s">
         <v>417</v>
       </c>
-      <c r="F3" s="92">
+      <c r="F3" s="91">
         <v>93</v>
       </c>
-      <c r="G3" s="93">
+      <c r="G3" s="92">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="89" t="s">
         <v>460</v>
       </c>
-      <c r="B4" s="93" t="s">
+      <c r="B4" s="92" t="s">
         <v>411</v>
       </c>
-      <c r="C4" s="94">
+      <c r="C4" s="93">
         <v>95</v>
       </c>
-      <c r="D4" s="95">
+      <c r="D4" s="94">
         <v>40</v>
       </c>
-      <c r="E4" s="93" t="s">
+      <c r="E4" s="92" t="s">
         <v>416</v>
       </c>
-      <c r="F4" s="94">
+      <c r="F4" s="93">
         <v>94</v>
       </c>
-      <c r="G4" s="95">
+      <c r="G4" s="94">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="89" t="s">
         <v>461</v>
       </c>
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="C5" s="97">
+      <c r="C5" s="96">
         <v>94</v>
       </c>
-      <c r="D5" s="98">
+      <c r="D5" s="97">
         <v>60</v>
       </c>
-      <c r="E5" s="96" t="s">
+      <c r="E5" s="95" t="s">
         <v>418</v>
       </c>
-      <c r="F5" s="97">
+      <c r="F5" s="96">
         <v>91</v>
       </c>
-      <c r="G5" s="98">
+      <c r="G5" s="97">
         <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="98" t="s">
         <v>236</v>
       </c>
-      <c r="B6" s="93" t="s">
+      <c r="B6" s="92" t="s">
         <v>237</v>
       </c>
-      <c r="C6" s="100">
+      <c r="C6" s="99">
         <v>99</v>
       </c>
-      <c r="D6" s="101" t="s">
+      <c r="D6" s="100" t="s">
         <v>238</v>
       </c>
-      <c r="E6" s="93" t="s">
+      <c r="E6" s="92" t="s">
         <v>339</v>
       </c>
-      <c r="F6" s="93">
+      <c r="F6" s="92">
         <v>98</v>
       </c>
-      <c r="G6" s="101" t="s">
+      <c r="G6" s="100" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A7" s="99" t="s">
+      <c r="A7" s="98" t="s">
         <v>239</v>
       </c>
-      <c r="B7" s="93" t="s">
+      <c r="B7" s="92" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="102">
+      <c r="C7" s="101">
         <v>99</v>
       </c>
-      <c r="D7" s="101" t="s">
+      <c r="D7" s="100" t="s">
         <v>238</v>
       </c>
-      <c r="E7" s="93" t="s">
+      <c r="E7" s="92" t="s">
         <v>340</v>
       </c>
-      <c r="F7" s="93">
+      <c r="F7" s="92">
         <v>98</v>
       </c>
-      <c r="G7" s="101" t="s">
+      <c r="G7" s="100" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="102" t="s">
         <v>241</v>
       </c>
-      <c r="B8" s="96" t="s">
+      <c r="B8" s="95" t="s">
         <v>242</v>
       </c>
-      <c r="C8" s="97">
+      <c r="C8" s="96">
         <v>90</v>
       </c>
-      <c r="D8" s="98" t="s">
+      <c r="D8" s="97" t="s">
         <v>238</v>
       </c>
-      <c r="E8" s="93" t="s">
+      <c r="E8" s="92" t="s">
         <v>341</v>
       </c>
-      <c r="F8" s="93">
+      <c r="F8" s="92">
         <v>96</v>
       </c>
-      <c r="G8" s="98" t="s">
+      <c r="G8" s="97" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="89" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="93"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="104" t="s">
+      <c r="B9" s="92"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="103" t="s">
         <v>267</v>
       </c>
-      <c r="E9" s="93"/>
-      <c r="F9" s="97"/>
-      <c r="G9" s="104" t="s">
+      <c r="E9" s="92"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="103" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="75" x14ac:dyDescent="0.3">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="81" t="s">
         <v>414</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="82" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="84"/>
-      <c r="D12" s="85" t="s">
+      <c r="C12" s="83"/>
+      <c r="D12" s="84" t="s">
         <v>194</v>
       </c>
-      <c r="E12" s="83" t="s">
+      <c r="E12" s="82" t="s">
         <v>314</v>
       </c>
-      <c r="F12" s="84"/>
-      <c r="G12" s="85" t="s">
+      <c r="F12" s="83"/>
+      <c r="G12" s="84" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="50" x14ac:dyDescent="0.3">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="86" t="s">
         <v>410</v>
       </c>
-      <c r="B13" s="88" t="s">
+      <c r="B13" s="87" t="s">
         <v>326</v>
       </c>
-      <c r="C13" s="89" t="s">
+      <c r="C13" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="87" t="s">
         <v>412</v>
       </c>
-      <c r="E13" s="88" t="s">
+      <c r="E13" s="87" t="s">
         <v>196</v>
       </c>
-      <c r="F13" s="89" t="s">
+      <c r="F13" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="G13" s="89" t="s">
+      <c r="G13" s="88" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A14" s="90" t="s">
+      <c r="A14" s="89" t="s">
         <v>459</v>
       </c>
-      <c r="B14" s="91" t="s">
+      <c r="B14" s="90" t="s">
         <v>415</v>
       </c>
-      <c r="C14" s="92">
+      <c r="C14" s="91">
         <v>95</v>
       </c>
-      <c r="D14" s="93">
+      <c r="D14" s="92">
         <v>61</v>
       </c>
-      <c r="E14" s="91" t="s">
+      <c r="E14" s="90" t="s">
         <v>417</v>
       </c>
-      <c r="F14" s="92">
+      <c r="F14" s="91">
         <v>93</v>
       </c>
-      <c r="G14" s="93">
+      <c r="G14" s="92">
         <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="89" t="s">
         <v>460</v>
       </c>
-      <c r="B15" s="93" t="s">
+      <c r="B15" s="92" t="s">
         <v>411</v>
       </c>
-      <c r="C15" s="94">
+      <c r="C15" s="93">
         <v>95</v>
       </c>
-      <c r="D15" s="95">
+      <c r="D15" s="94">
         <v>61</v>
       </c>
-      <c r="E15" s="93" t="s">
+      <c r="E15" s="92" t="s">
         <v>416</v>
       </c>
-      <c r="F15" s="94">
+      <c r="F15" s="93">
         <v>94</v>
       </c>
-      <c r="G15" s="95">
+      <c r="G15" s="94">
         <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A16" s="90" t="s">
+      <c r="A16" s="89" t="s">
         <v>461</v>
       </c>
-      <c r="B16" s="96" t="s">
+      <c r="B16" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="C16" s="97">
+      <c r="C16" s="96">
         <v>94</v>
       </c>
-      <c r="D16" s="98">
+      <c r="D16" s="97">
         <v>60</v>
       </c>
-      <c r="E16" s="96" t="s">
+      <c r="E16" s="95" t="s">
         <v>419</v>
       </c>
-      <c r="F16" s="97">
+      <c r="F16" s="96">
         <v>91</v>
       </c>
-      <c r="G16" s="98">
+      <c r="G16" s="97">
         <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="98" t="s">
         <v>236</v>
       </c>
-      <c r="B17" s="93" t="s">
+      <c r="B17" s="92" t="s">
         <v>237</v>
       </c>
-      <c r="C17" s="100">
+      <c r="C17" s="99">
         <v>99</v>
       </c>
-      <c r="D17" s="101" t="s">
+      <c r="D17" s="100" t="s">
         <v>238</v>
       </c>
-      <c r="E17" s="93" t="s">
+      <c r="E17" s="92" t="s">
         <v>339</v>
       </c>
-      <c r="F17" s="93">
+      <c r="F17" s="92">
         <v>98</v>
       </c>
-      <c r="G17" s="101" t="s">
+      <c r="G17" s="100" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="98" t="s">
         <v>239</v>
       </c>
-      <c r="B18" s="93" t="s">
+      <c r="B18" s="92" t="s">
         <v>240</v>
       </c>
-      <c r="C18" s="102">
+      <c r="C18" s="101">
         <v>99</v>
       </c>
-      <c r="D18" s="101" t="s">
+      <c r="D18" s="100" t="s">
         <v>238</v>
       </c>
-      <c r="E18" s="93" t="s">
+      <c r="E18" s="92" t="s">
         <v>340</v>
       </c>
-      <c r="F18" s="93">
+      <c r="F18" s="92">
         <v>98</v>
       </c>
-      <c r="G18" s="101" t="s">
+      <c r="G18" s="100" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A19" s="103" t="s">
+      <c r="A19" s="102" t="s">
         <v>241</v>
       </c>
-      <c r="B19" s="96" t="s">
+      <c r="B19" s="95" t="s">
         <v>242</v>
       </c>
-      <c r="C19" s="97">
+      <c r="C19" s="96">
         <v>90</v>
       </c>
-      <c r="D19" s="98" t="s">
+      <c r="D19" s="97" t="s">
         <v>238</v>
       </c>
-      <c r="E19" s="93" t="s">
+      <c r="E19" s="92" t="s">
         <v>341</v>
       </c>
-      <c r="F19" s="93">
+      <c r="F19" s="92">
         <v>96</v>
       </c>
-      <c r="G19" s="98" t="s">
+      <c r="G19" s="97" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="89" t="s">
         <v>268</v>
       </c>
-      <c r="B20" s="93"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="104" t="s">
+      <c r="B20" s="92"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="103" t="s">
         <v>267</v>
       </c>
-      <c r="E20" s="93"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="104" t="s">
+      <c r="E20" s="92"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="103" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="75" x14ac:dyDescent="0.3">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="104" t="s">
         <v>474</v>
       </c>
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="82" t="s">
         <v>193</v>
       </c>
-      <c r="C23" s="84"/>
-      <c r="D23" s="85" t="s">
+      <c r="C23" s="83"/>
+      <c r="D23" s="84" t="s">
         <v>194</v>
       </c>
-      <c r="E23" s="83" t="s">
+      <c r="E23" s="82" t="s">
         <v>314</v>
       </c>
-      <c r="F23" s="84"/>
-      <c r="G23" s="85" t="s">
+      <c r="F23" s="83"/>
+      <c r="G23" s="84" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="50" x14ac:dyDescent="0.3">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="86" t="s">
         <v>410</v>
       </c>
-      <c r="B24" s="88" t="s">
+      <c r="B24" s="87" t="s">
         <v>326</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="D24" s="88" t="s">
+      <c r="D24" s="87" t="s">
         <v>412</v>
       </c>
-      <c r="E24" s="88" t="s">
+      <c r="E24" s="87" t="s">
         <v>326</v>
       </c>
-      <c r="F24" s="89" t="s">
+      <c r="F24" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="G24" s="88" t="s">
+      <c r="G24" s="87" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="89" t="s">
         <v>459</v>
       </c>
-      <c r="B25" s="91" t="s">
+      <c r="B25" s="90" t="s">
         <v>475</v>
       </c>
-      <c r="C25" s="92">
+      <c r="C25" s="91">
         <v>94</v>
       </c>
-      <c r="D25" s="93">
+      <c r="D25" s="92">
         <v>40</v>
       </c>
-      <c r="E25" s="91" t="s">
+      <c r="E25" s="90" t="s">
         <v>417</v>
       </c>
-      <c r="F25" s="92">
+      <c r="F25" s="91">
         <v>93</v>
       </c>
-      <c r="G25" s="93">
+      <c r="G25" s="92">
         <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A26" s="90" t="s">
+      <c r="A26" s="89" t="s">
         <v>460</v>
       </c>
-      <c r="B26" s="93" t="s">
+      <c r="B26" s="92" t="s">
         <v>411</v>
       </c>
-      <c r="C26" s="94">
+      <c r="C26" s="93">
         <v>95</v>
       </c>
-      <c r="D26" s="95">
+      <c r="D26" s="94">
         <v>38</v>
       </c>
-      <c r="E26" s="93" t="s">
+      <c r="E26" s="92" t="s">
         <v>416</v>
       </c>
-      <c r="F26" s="94">
+      <c r="F26" s="93">
         <v>94</v>
       </c>
-      <c r="G26" s="95">
+      <c r="G26" s="94">
         <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A27" s="90" t="s">
+      <c r="A27" s="89" t="s">
         <v>461</v>
       </c>
-      <c r="B27" s="96" t="s">
+      <c r="B27" s="95" t="s">
         <v>476</v>
       </c>
-      <c r="C27" s="97">
+      <c r="C27" s="96">
         <v>75</v>
       </c>
-      <c r="D27" s="98">
+      <c r="D27" s="97">
         <v>56</v>
       </c>
-      <c r="E27" s="96" t="s">
+      <c r="E27" s="95" t="s">
         <v>489</v>
       </c>
-      <c r="F27" s="97">
+      <c r="F27" s="96">
         <v>75</v>
       </c>
-      <c r="G27" s="98">
+      <c r="G27" s="97">
         <v>59</v>
       </c>
-      <c r="H27" s="86" t="s">
+      <c r="H27" s="85" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="98" t="s">
         <v>236</v>
       </c>
-      <c r="B28" s="93" t="s">
+      <c r="B28" s="92" t="s">
         <v>237</v>
       </c>
-      <c r="C28" s="100">
+      <c r="C28" s="99">
         <v>99</v>
       </c>
-      <c r="D28" s="101" t="s">
+      <c r="D28" s="100" t="s">
         <v>238</v>
       </c>
-      <c r="E28" s="93" t="s">
+      <c r="E28" s="92" t="s">
         <v>339</v>
       </c>
-      <c r="F28" s="93">
+      <c r="F28" s="92">
         <v>98</v>
       </c>
-      <c r="G28" s="101" t="s">
+      <c r="G28" s="100" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A29" s="99" t="s">
+      <c r="A29" s="98" t="s">
         <v>239</v>
       </c>
-      <c r="B29" s="93" t="s">
+      <c r="B29" s="92" t="s">
         <v>240</v>
       </c>
-      <c r="C29" s="102">
+      <c r="C29" s="101">
         <v>99</v>
       </c>
-      <c r="D29" s="101" t="s">
+      <c r="D29" s="100" t="s">
         <v>238</v>
       </c>
-      <c r="E29" s="93" t="s">
+      <c r="E29" s="92" t="s">
         <v>340</v>
       </c>
-      <c r="F29" s="93">
+      <c r="F29" s="92">
         <v>98</v>
       </c>
-      <c r="G29" s="101" t="s">
+      <c r="G29" s="100" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A30" s="103" t="s">
+      <c r="A30" s="102" t="s">
         <v>241</v>
       </c>
-      <c r="B30" s="96" t="s">
+      <c r="B30" s="95" t="s">
         <v>242</v>
       </c>
-      <c r="C30" s="97">
+      <c r="C30" s="96">
         <v>90</v>
       </c>
-      <c r="D30" s="101" t="s">
+      <c r="D30" s="100" t="s">
         <v>238</v>
       </c>
-      <c r="E30" s="93" t="s">
+      <c r="E30" s="92" t="s">
         <v>341</v>
       </c>
-      <c r="F30" s="93">
+      <c r="F30" s="92">
         <v>96</v>
       </c>
-      <c r="G30" s="98" t="s">
+      <c r="G30" s="97" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="89" t="s">
         <v>268</v>
       </c>
-      <c r="B31" s="107"/>
-      <c r="C31" s="108"/>
-      <c r="D31" s="104" t="s">
+      <c r="B31" s="95" t="s">
+        <v>496</v>
+      </c>
+      <c r="C31" s="95">
+        <v>80</v>
+      </c>
+      <c r="D31" s="103" t="s">
         <v>267</v>
       </c>
-      <c r="E31" s="93" t="s">
+      <c r="E31" s="92" t="s">
         <v>480</v>
       </c>
-      <c r="F31" s="93">
+      <c r="F31" s="92">
         <v>77</v>
       </c>
-      <c r="G31" s="104" t="s">
+      <c r="G31" s="103" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A32" s="106" t="s">
+      <c r="A32" s="105" t="s">
         <v>477</v>
       </c>
-      <c r="B32" s="109" t="s">
+      <c r="B32" s="106" t="s">
         <v>478</v>
       </c>
-      <c r="C32" s="109">
+      <c r="C32" s="106">
         <v>75</v>
       </c>
-      <c r="D32" s="109">
+      <c r="D32" s="106">
         <v>60</v>
       </c>
-      <c r="E32" s="109" t="s">
+      <c r="E32" s="106" t="s">
         <v>490</v>
       </c>
-      <c r="F32" s="109">
+      <c r="F32" s="106">
         <v>62</v>
       </c>
-      <c r="G32" s="109">
+      <c r="G32" s="106">
         <v>60</v>
       </c>
-      <c r="H32" s="86" t="s">
+      <c r="H32" s="85" t="s">
         <v>479</v>
       </c>
     </row>
@@ -8293,7 +8354,7 @@
         <v>463</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="59"/>
+      <c r="C5" s="58"/>
     </row>
     <row r="6" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -8316,7 +8377,7 @@
       <c r="B8" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="59" t="s">
         <v>358</v>
       </c>
     </row>
@@ -8327,7 +8388,7 @@
       <c r="B9" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="58" t="s">
         <v>360</v>
       </c>
     </row>
@@ -8343,7 +8404,7 @@
         <v>431</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="59"/>
+      <c r="C11" s="58"/>
     </row>
     <row r="12" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
@@ -8357,7 +8418,7 @@
         <v>434</v>
       </c>
       <c r="B13" s="1"/>
-      <c r="C13" s="59"/>
+      <c r="C13" s="58"/>
     </row>
     <row r="14" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -8413,7 +8474,7 @@
         <v>215</v>
       </c>
       <c r="B21" s="40"/>
-      <c r="C21" s="61"/>
+      <c r="C21" s="60"/>
     </row>
     <row r="22" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="22" t="s">
@@ -8502,7 +8563,7 @@
         <v>226</v>
       </c>
       <c r="B32" s="14"/>
-      <c r="C32" s="62"/>
+      <c r="C32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
@@ -8537,21 +8598,21 @@
         <v>230</v>
       </c>
       <c r="B37" s="12"/>
-      <c r="C37" s="63"/>
+      <c r="C37" s="62"/>
     </row>
     <row r="38" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>231</v>
       </c>
       <c r="B38" s="48"/>
-      <c r="C38" s="64"/>
+      <c r="C38" s="63"/>
     </row>
     <row r="39" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>232</v>
       </c>
       <c r="B39" s="4"/>
-      <c r="C39" s="64"/>
+      <c r="C39" s="63"/>
     </row>
     <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
@@ -8560,7 +8621,7 @@
       <c r="B40" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="C40" s="60" t="s">
+      <c r="C40" s="59" t="s">
         <v>368</v>
       </c>
     </row>
@@ -8571,7 +8632,7 @@
       <c r="B41" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="C41" s="60" t="s">
+      <c r="C41" s="59" t="s">
         <v>370</v>
       </c>
     </row>
@@ -8630,79 +8691,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="81" x14ac:dyDescent="0.2">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="75" t="s">
         <v>373</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="76" t="s">
         <v>374</v>
       </c>
-      <c r="C1" s="78" t="s">
+      <c r="C1" s="77" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="73" t="s">
         <v>376</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="74" t="s">
         <v>377</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="74" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="73" t="s">
         <v>379</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="74" t="s">
         <v>380</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="74" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="73" t="s">
         <v>381</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="78" t="s">
         <v>382</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="78" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="73" t="s">
         <v>383</v>
       </c>
-      <c r="B5" s="79" t="s">
+      <c r="B5" s="78" t="s">
         <v>382</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="78" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="73" t="s">
         <v>384</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="74" t="s">
         <v>385</v>
       </c>
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="74" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="73" t="s">
         <v>387</v>
       </c>
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="74" t="s">
         <v>388</v>
       </c>
-      <c r="C7" s="75" t="s">
+      <c r="C7" s="74" t="s">
         <v>389</v>
       </c>
       <c r="D7" t="s">
@@ -8710,13 +8771,13 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="73" t="s">
         <v>391</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="74" t="s">
         <v>323</v>
       </c>
-      <c r="C8" s="75" t="s">
+      <c r="C8" s="74" t="s">
         <v>392</v>
       </c>
       <c r="D8" t="s">
@@ -8724,13 +8785,13 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="73" t="s">
         <v>394</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="74" t="s">
         <v>395</v>
       </c>
-      <c r="C9" s="75" t="s">
+      <c r="C9" s="74" t="s">
         <v>396</v>
       </c>
       <c r="D9" t="s">
@@ -8738,57 +8799,57 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="73" t="s">
         <v>398</v>
       </c>
-      <c r="B10" s="75">
+      <c r="B10" s="74">
         <v>26000</v>
       </c>
-      <c r="C10" s="75">
+      <c r="C10" s="74">
         <v>20000</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A11" s="74" t="s">
+      <c r="A11" s="73" t="s">
         <v>399</v>
       </c>
-      <c r="B11" s="75">
+      <c r="B11" s="74">
         <v>445</v>
       </c>
-      <c r="C11" s="75">
+      <c r="C11" s="74">
         <v>371</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="73" t="s">
         <v>400</v>
       </c>
-      <c r="B12" s="75">
+      <c r="B12" s="74">
         <v>96000</v>
       </c>
-      <c r="C12" s="75">
+      <c r="C12" s="74">
         <v>80000</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="73" t="s">
         <v>401</v>
       </c>
-      <c r="B13" s="75">
+      <c r="B13" s="74">
         <v>400000</v>
       </c>
-      <c r="C13" s="75">
+      <c r="C13" s="74">
         <v>300000</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A14" s="74" t="s">
+      <c r="A14" s="73" t="s">
         <v>402</v>
       </c>
-      <c r="B14" s="75">
+      <c r="B14" s="74">
         <v>200000</v>
       </c>
-      <c r="C14" s="75">
+      <c r="C14" s="74">
         <v>150000</v>
       </c>
     </row>

--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="809" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1B034F8-2F79-F14D-8B07-CD63CED0B63C}"/>
+  <xr:revisionPtr revIDLastSave="871" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C550F701-0817-42F4-9970-265909BAE866}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19740" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19740" firstSheet="3" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="515">
   <si>
     <t>number</t>
   </si>
@@ -668,82 +668,157 @@
     <t>Global data shm</t>
   </si>
   <si>
+    <t>AppControl</t>
+  </si>
+  <si>
     <t>1700 CPS /940 Mbps</t>
   </si>
   <si>
+    <t>AppControl (ASC enabled)</t>
+  </si>
+  <si>
     <t>3500 CPS / 1950 Mbps</t>
   </si>
   <si>
     <t>* Need Additional Port Pair</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl + AppQOS with ASC enabled </t>
+  </si>
+  <si>
     <t>1620 CPS /911 Mbps</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl + IDP-Recommended policy </t>
+  </si>
+  <si>
     <t>875 CPS / 490 Mbps</t>
   </si>
   <si>
+    <t>AppControl + IDP-Enterprise Rec policy</t>
+  </si>
+  <si>
     <t>280 CPS / 160 Mbps</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl + SecIntel </t>
+  </si>
+  <si>
     <t>1570 CPS / 894 Mbps</t>
   </si>
   <si>
+    <t>AppControl + AAMW -Block mode</t>
+  </si>
+  <si>
     <t>556 CPS / 318 Mbps</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl+ UTM EWF(100% cache) </t>
+  </si>
+  <si>
     <t>1596 CPS /903 Mbps</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl+ UTM NG-WF(100% cache) </t>
+  </si>
+  <si>
     <t>1579 CPS / 893 Mbps</t>
   </si>
   <si>
+    <t>AppControl + UTM SAV</t>
+  </si>
+  <si>
     <t>381 CPS / 211 Mbps</t>
   </si>
   <si>
+    <t>AppControl + SecIntel+ IDP-Rec + UTM EWF</t>
+  </si>
+  <si>
     <t>796 CPS / 440 Mbps</t>
   </si>
   <si>
+    <t>AppControl + SecIntel+ IDP-Rec + AAMW Block</t>
+  </si>
+  <si>
     <t>448 CPS / 237 Mbps</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + UTM EWF + AAMW Block </t>
+  </si>
+  <si>
     <t>428 CPS / 228 Mbps</t>
   </si>
   <si>
+    <t>AppControl + SecIntel+ IDP-Rec + UTM EWF + UTM SAV</t>
+  </si>
+  <si>
     <t>307 CPS / 165 Mbps</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + AAMW Block + DNS </t>
+  </si>
+  <si>
     <t>444 CPS / 234 Mbps</t>
   </si>
   <si>
     <t xml:space="preserve">HTTPS Throughput via CPS Method (Payload: 64KB) </t>
   </si>
   <si>
+    <t>AppControl + TCP Proxy</t>
+  </si>
+  <si>
     <t>420 CPS / 240 Mbps</t>
   </si>
   <si>
+    <t>AppControl + SSL(TLS1.2)</t>
+  </si>
+  <si>
     <t>190 CPS / 110 Mbps</t>
   </si>
   <si>
+    <t>AppControl + SSL(TLS1.3)</t>
+  </si>
+  <si>
     <t>125 CPS / 66 Mbps</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl + SSL+ IDP-Recommended policy </t>
+  </si>
+  <si>
     <t>165 CPS / 91 Mbps</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl + SSL+ IDP-Enterprise Rec policy </t>
+  </si>
+  <si>
     <t>55 CPS / 30 Mbps</t>
   </si>
   <si>
+    <t>AppControl + SSL + AAMW Block</t>
+  </si>
+  <si>
     <t>141 CPS / 85 Mbps</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP-Rec </t>
+  </si>
+  <si>
     <t>164 CPS / 91 Mbps</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + UTM EWF </t>
+  </si>
+  <si>
     <t>149 CPS / 86 Mbps</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + AAMW Block </t>
+  </si>
+  <si>
     <t>123 CPS / 74 Mbps</t>
+  </si>
+  <si>
+    <t>AppControl + SSL + SecIntel + IDP Rec + UTM EWF + AAMW Block</t>
   </si>
   <si>
     <t>119 CPS / 71 Mbps</t>
@@ -756,9 +831,24 @@
 TPS/MBPS</t>
   </si>
   <si>
+    <t>Sessions</t>
+  </si>
+  <si>
+    <t>Firewall + AppControl(Unified policy)</t>
+  </si>
+  <si>
+    <t>10600 TPS / 3995 Mbps</t>
+  </si>
+  <si>
     <t>*100 Sessions</t>
   </si>
   <si>
+    <t>AppControl + IDP-Recommended policy template</t>
+  </si>
+  <si>
+    <t>AppControl + IDP-Rec + UTM EWF(100% cache)</t>
+  </si>
+  <si>
     <t>650 TPS / 256 Mbps</t>
   </si>
   <si>
@@ -768,15 +858,33 @@
     <t xml:space="preserve">Firewall TCP CPS </t>
   </si>
   <si>
+    <t>20000 (18500)</t>
+  </si>
+  <si>
     <t xml:space="preserve">IPv6 Firewall TCP CPS </t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl with ASC enabled CPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl CPS </t>
+  </si>
+  <si>
     <t>UTM EWF-100% cache</t>
   </si>
   <si>
     <t>UTM- SAV</t>
   </si>
   <si>
+    <t xml:space="preserve">AppControl + TCPProxy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL(TLS1.2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL(TLS1.3) </t>
+  </si>
+  <si>
     <t xml:space="preserve">UDP/IPSec Throughput </t>
   </si>
   <si>
@@ -813,6 +921,9 @@
     <t>Firewall UDP-50% Latency- Packet size 64bytes</t>
   </si>
   <si>
+    <t>15.6 uSec</t>
+  </si>
+  <si>
     <t>IPv6 Firewall UDP throughput- Packet sizes 104Bytes</t>
   </si>
   <si>
@@ -873,30 +984,60 @@
     <t>IPSec(site-2-site) UDP throughput with IKEv2,PSK,AES-GCM256- Packet size 64bytes</t>
   </si>
   <si>
-    <t>PR 1954277 </t>
+    <t>285.6 KPPS / 191 Mbps</t>
+  </si>
+  <si>
+    <t>*32 Sessions ( 16Tunnels) - PR 1954277 </t>
   </si>
   <si>
     <t>IPSec(site-2-site) UDP throughput with IKEv2,PSK,AES-GCM256- Packet size IMIX(ratio 64:7,570:4,1400:1)</t>
   </si>
   <si>
+    <t>281.6 KPPS / 841 Mbps</t>
+  </si>
+  <si>
     <t>IPSec(site-2-site) UDP throughput with IKEv2,PSK,AES-GCM256- Packet size 512Bytes</t>
   </si>
   <si>
+    <t>284 KPPS / 1208 Mbps</t>
+  </si>
+  <si>
     <t>IPSec(site-2-site) UDP throughput with IKEv2,PSK,AES-GCM256- Packet size 1400bytes</t>
   </si>
   <si>
+    <t>228.8 KPPS / 2600 Mbps</t>
+  </si>
+  <si>
     <t>IPSec(site-2-site)  single tunnel UDP throughput with IKEv2,PSK,AES-GCM256- Packet size IMIX</t>
   </si>
   <si>
+    <t>192 KPPS / 566 Mbps</t>
+  </si>
+  <si>
+    <t>*1 session (1 Tunnel) - PR 1954277 </t>
+  </si>
+  <si>
     <t>IPSec(site-2-site) IKEv2,PSK,AES-GCM256 UDP-50% Latency- Packet size 64bytes</t>
   </si>
   <si>
+    <t>145 uSec</t>
+  </si>
+  <si>
     <t>IPSec(site-2-site) UDP throughput with IKEv2,PKI2K,AES256 - Packet size IMIX(64:7,570:4,1400:1)</t>
   </si>
   <si>
+    <t>280 KPPS / 835 Mbps</t>
+  </si>
+  <si>
+    <t>*32 Sessions ( 16Tunnels) -PR 1954277 </t>
+  </si>
+  <si>
     <t>Route based VPN Tunnel setup rate(TPS rate)- PSK, IKE Encryption: AES256, IKE Authentication: SHA256, DH Group: DH14</t>
   </si>
   <si>
+    <t xml:space="preserve">8 TPS </t>
+  </si>
+  <si>
     <t xml:space="preserve">Scaling </t>
   </si>
   <si>
@@ -963,9 +1104,15 @@
     <t>BGP- Total RIB Routes/Size</t>
   </si>
   <si>
+    <t>300K</t>
+  </si>
+  <si>
     <t>BGP- Total FIB Routes/Size</t>
   </si>
   <si>
+    <t>150K</t>
+  </si>
+  <si>
     <t>BGP: Peers</t>
   </si>
   <si>
@@ -978,7 +1125,13 @@
     <t>Max FW HTTP concurrent Session capacity</t>
   </si>
   <si>
+    <t>Max AppControl Sessions(unified policy)</t>
+  </si>
+  <si>
     <t>MAX IDP(Rec policy) Sessions capacity</t>
+  </si>
+  <si>
+    <t>80K</t>
   </si>
   <si>
     <t>Max UTM-EWF Sessions capacity</t>
@@ -1049,6 +1202,9 @@
     <t>** Has to be re-tested with more ports</t>
   </si>
   <si>
+    <t>1920 CPS/ 1025 Mbos</t>
+  </si>
+  <si>
     <t>1085 CPS / 622 Mbps</t>
   </si>
   <si>
@@ -1064,6 +1220,9 @@
     <t>1700  CPS / 940 Mbps</t>
   </si>
   <si>
+    <t>1800 CPS / 1000 Mbps</t>
+  </si>
+  <si>
     <t>875 CPS / 500 Mbps</t>
   </si>
   <si>
@@ -1073,6 +1232,12 @@
     <t>530 CPS / 300 Mbps</t>
   </si>
   <si>
+    <t>340 CPS / 190 Mbps</t>
+  </si>
+  <si>
+    <t>535 CPS / 305 Mbps</t>
+  </si>
+  <si>
     <t>Throughput</t>
   </si>
   <si>
@@ -1106,10 +1271,13 @@
     <t>135 CPS / 81 Mbps</t>
   </si>
   <si>
+    <t>800 TPS / 315 Mbps</t>
+  </si>
+  <si>
     <t>CPS</t>
   </si>
   <si>
-    <t>Sessions</t>
+    <t>26000 (22000)</t>
   </si>
   <si>
     <t>744.1 KPPS/500 Mbps</t>
@@ -1124,6 +1292,9 @@
     <t>731.6 KPPS/2183 Mbps</t>
   </si>
   <si>
+    <t>15.3 uSec</t>
+  </si>
+  <si>
     <t>661.2 KPPS / 656 Mbps</t>
   </si>
   <si>
@@ -1148,16 +1319,237 @@
     <t>722.2 KPPS/2155 Mbps</t>
   </si>
   <si>
+    <t>340 KPPS / 228 Mbps</t>
+  </si>
+  <si>
+    <t>320 KPPS /954 Mbps</t>
+  </si>
+  <si>
+    <t>310 KPPS / 1320 Mbps</t>
+  </si>
+  <si>
+    <t>232 KPPS / 2653 Mbps</t>
+  </si>
+  <si>
+    <t>210 KPPS / 626 Mbps</t>
+  </si>
+  <si>
+    <t>129 uSec</t>
+  </si>
+  <si>
+    <t>315 KPPS / 940 Mbps</t>
+  </si>
+  <si>
+    <t>10 TPS</t>
+  </si>
+  <si>
+    <t>RE Memory</t>
+  </si>
+  <si>
     <t>400K</t>
   </si>
   <si>
     <t>200K</t>
   </si>
   <si>
+    <t>96K</t>
+  </si>
+  <si>
     <t>Max UTM- EWF Sessions capacity</t>
   </si>
   <si>
     <t>Max UTM- NG-WF Sessions capacity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Release: 25.4X300-D10-202605310154.0-EVO
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Testcase Description</t>
+  </si>
+  <si>
+    <t>Global data shm / Comments</t>
+  </si>
+  <si>
+    <t>AppControl - HTTP Throughput (64KB)</t>
+  </si>
+  <si>
+    <t>1650 CPS / 920 Mbps</t>
+  </si>
+  <si>
+    <t>2000 CPS / 1350 Mbps</t>
+  </si>
+  <si>
+    <t>AppControl - HTTP  CPS (64B)</t>
+  </si>
+  <si>
+    <t>2400 CPS</t>
+  </si>
+  <si>
+    <t>3000 CPS</t>
+  </si>
+  <si>
+    <t>AppControl + SSL(TLS1.2) - HTTPS Throughput (64KB)</t>
+  </si>
+  <si>
+    <t>240 CPS / 140 Mbps</t>
+  </si>
+  <si>
+    <t>PR 1954277 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Release: 25.4X300-202605180407.0-EVO
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>1650 CPS/928 Mbps</t>
+  </si>
+  <si>
+    <t>240 CPS / 139 Mbps</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Release: 25.4X300-D10-202606040154.0-EVO
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>1650  CPS / 920 Mbps</t>
+  </si>
+  <si>
+    <t>170 CPS / 96 Mbps</t>
+  </si>
+  <si>
+    <t>215 CPS /115 Mbps</t>
+  </si>
+  <si>
+    <t>There are spikes seen, expected is 370 CPS. Ravi is checking if dpdk upgrade has caused any issues and it is applicable to all ssl cases.</t>
+  </si>
+  <si>
+    <t>AppControl + SSL(TLS1.2) - HTTPS CPS (64B)</t>
+  </si>
+  <si>
+    <t>300 CPS</t>
+  </si>
+  <si>
+    <t>350 CPS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Release: 25.4X300-D10.2-EVO
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>1650 CPS / 926 Mbps</t>
+  </si>
+  <si>
+    <t>2100 CPS / 1150 Mbps</t>
+  </si>
+  <si>
+    <t>2390 CPS</t>
+  </si>
+  <si>
+    <t>168 CPS / 95 Mbps</t>
+  </si>
+  <si>
+    <t>210 CPS/120 Mbps</t>
+  </si>
+  <si>
+    <t>310 KPPS / 925 Mbps</t>
+  </si>
+  <si>
+    <t>AppControl + SSL(TLS1.2) - HTTPS CPS(64B)</t>
+  </si>
+  <si>
+    <t>310 CPS</t>
+  </si>
+  <si>
+    <t>345 CPS</t>
   </si>
   <si>
     <r>
@@ -1188,6 +1580,15 @@
     <t xml:space="preserve">Basic Firewall </t>
   </si>
   <si>
+    <t>Firewall+ AppControl(unified policy) with ASC enabled</t>
+  </si>
+  <si>
+    <t>Firewall+ AppControl(unified policy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firewall+ IPv6 AppControl(Unified policy) </t>
+  </si>
+  <si>
     <t>1000 CPS, 570 Mbps</t>
   </si>
   <si>
@@ -1200,6 +1601,24 @@
     <t>CPU: 82, Global data shm: 84</t>
   </si>
   <si>
+    <t>AppControl + SkyATP -Block mode</t>
+  </si>
+  <si>
+    <t>AppControl + UTM Avira-Light mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + UTM Avira- Heavy mode </t>
+  </si>
+  <si>
+    <t>AppControl + SecIntel+ IDP-Rec + SkyATP Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + UTM EWF + SkyATP Block </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + SkyATP Block + DNS </t>
+  </si>
+  <si>
     <t>215 CPS, 125 Mbps</t>
   </si>
   <si>
@@ -1216,6 +1635,15 @@
   </si>
   <si>
     <t>CPU: 70, Global data shm: 64</t>
+  </si>
+  <si>
+    <t>AppControl + SSL + SkyATP Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + SkyATP Block </t>
+  </si>
+  <si>
+    <t>AppControl + SSL + SecIntel + IDP Rec + UTM EWF + SkyATP Block</t>
   </si>
   <si>
     <t>11000 CPS</t>
@@ -1349,364 +1777,12 @@
   <si>
     <t>Route table size (FIB) (IPv4)</t>
   </si>
-  <si>
-    <t>RE Memory</t>
-  </si>
-  <si>
-    <t>300K</t>
-  </si>
-  <si>
-    <t>150K</t>
-  </si>
-  <si>
-    <t>1800 CPS / 1000 Mbps</t>
-  </si>
-  <si>
-    <t>535 CPS / 305 Mbps</t>
-  </si>
-  <si>
-    <t>340 CPS / 190 Mbps</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Release: 25.4X300-D10-202605310154.0-EVO
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <t>Testcase Description</t>
-  </si>
-  <si>
-    <t>2400 CPS</t>
-  </si>
-  <si>
-    <t>Global data shm / Comments</t>
-  </si>
-  <si>
-    <t>1650 CPS / 920 Mbps</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Release: 25.4X300-202605180407.0-EVO
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <t>1650 CPS/928 Mbps</t>
-  </si>
-  <si>
-    <t>3000 CPS</t>
-  </si>
-  <si>
-    <t>2000 CPS / 1350 Mbps</t>
-  </si>
-  <si>
-    <t>240 CPS / 140 Mbps</t>
-  </si>
-  <si>
-    <t>240 CPS / 139 Mbps</t>
-  </si>
-  <si>
-    <t>1920 CPS/ 1025 Mbos</t>
-  </si>
-  <si>
-    <t>800 TPS / 315 Mbps</t>
-  </si>
-  <si>
-    <t>10600 TPS / 3995 Mbps</t>
-  </si>
-  <si>
-    <t>96K</t>
-  </si>
-  <si>
-    <t>80K</t>
-  </si>
-  <si>
-    <t>AppControl</t>
-  </si>
-  <si>
-    <t>AppControl (ASC enabled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + AppQOS with ASC enabled </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + IDP-Recommended policy </t>
-  </si>
-  <si>
-    <t>AppControl + IDP-Enterprise Rec policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SecIntel </t>
-  </si>
-  <si>
-    <t>AppControl + SkyATP -Block mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl+ UTM EWF(100% cache) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl+ UTM NG-WF(100% cache) </t>
-  </si>
-  <si>
-    <t>AppControl + UTM SAV</t>
-  </si>
-  <si>
-    <t>AppControl + SecIntel+ IDP-Rec + UTM EWF</t>
-  </si>
-  <si>
-    <t>AppControl + SecIntel+ IDP-Rec + SkyATP Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + UTM EWF + SkyATP Block </t>
-  </si>
-  <si>
-    <t>AppControl + SecIntel+ IDP-Rec + UTM EWF + UTM SAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + SkyATP Block + DNS </t>
-  </si>
-  <si>
-    <t>AppControl + TCP Proxy</t>
-  </si>
-  <si>
-    <t>AppControl + SSL(TLS1.2)</t>
-  </si>
-  <si>
-    <t>AppControl + SSL(TLS1.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SSL+ IDP-Recommended policy </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SSL+ IDP-Enterprise Rec policy </t>
-  </si>
-  <si>
-    <t>AppControl + SSL + SkyATP Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP-Rec </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + UTM EWF </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + SkyATP Block </t>
-  </si>
-  <si>
-    <t>AppControl + SSL + SecIntel + IDP Rec + UTM EWF + SkyATP Block</t>
-  </si>
-  <si>
-    <t>Firewall + AppControl(Unified policy)</t>
-  </si>
-  <si>
-    <t>AppControl + IDP-Recommended policy template</t>
-  </si>
-  <si>
-    <t>AppControl + IDP-Rec + UTM EWF(100% cache)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl with ASC enabled CPS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl CPS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + TCPProxy </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SSL(TLS1.2) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SSL(TLS1.3) </t>
-  </si>
-  <si>
-    <t>Max AppControl Sessions(unified policy)</t>
-  </si>
-  <si>
-    <t>AppControl - HTTP Throughput (64KB)</t>
-  </si>
-  <si>
-    <t>AppControl - HTTP  CPS (64B)</t>
-  </si>
-  <si>
-    <t>AppControl + SSL(TLS1.2) - HTTPS Throughput (64KB)</t>
-  </si>
-  <si>
-    <t>Firewall+ AppControl(unified policy) with ASC enabled</t>
-  </si>
-  <si>
-    <t>Firewall+ AppControl(unified policy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firewall+ IPv6 AppControl(Unified policy) </t>
-  </si>
-  <si>
-    <t>AppControl + UTM Avira-Light mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + UTM Avira- Heavy mode </t>
-  </si>
-  <si>
-    <t>AppControl + AAMW -Block mode</t>
-  </si>
-  <si>
-    <t>AppControl + SecIntel+ IDP-Rec + AAMW Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + UTM EWF + AAMW Block </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SecIntel+ IDP-Rec + AAMW Block + DNS </t>
-  </si>
-  <si>
-    <t>AppControl + SSL + AAMW Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppControl + SSL + SecIntel + IDP Rec + AAMW Block </t>
-  </si>
-  <si>
-    <t>AppControl + SSL + SecIntel + IDP Rec + UTM EWF + AAMW Block</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Release: 25.4X300-D10-202606040154.0-EVO
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <t>1650  CPS / 920 Mbps</t>
-  </si>
-  <si>
-    <t>170 CPS / 96 Mbps</t>
-  </si>
-  <si>
-    <t>AppControl + SSL(TLS1.2) - HTTPS Throughput (64B)</t>
-  </si>
-  <si>
-    <t>300 CPS</t>
-  </si>
-  <si>
-    <t>There are spikes seen, expected is 370 CPS. Ravi is checking if dpdk upgrade has caused any issues and it is applicable to all ssl cases.</t>
-  </si>
-  <si>
-    <t>320 KPPS /954 Mbps</t>
-  </si>
-  <si>
-    <t>340 KPPS / 228 Mbps</t>
-  </si>
-  <si>
-    <t>310 KPPS / 1320 Mbps</t>
-  </si>
-  <si>
-    <t>210 KPPS / 626 Mbps</t>
-  </si>
-  <si>
-    <t>*32 Sessions ( 16Tunnels) - PR 1954277 </t>
-  </si>
-  <si>
-    <t>*32 Sessions ( 16Tunnels) -PR 1954277 </t>
-  </si>
-  <si>
-    <t>*1 session (1 Tunnel) - PR 1954277 </t>
-  </si>
-  <si>
-    <t>315 KPPS / 940 Mbps</t>
-  </si>
-  <si>
-    <t>232 KPPS / 2653 Mbps</t>
-  </si>
-  <si>
-    <t>215 CPS /115 Mbps</t>
-  </si>
-  <si>
-    <t>350 CPS</t>
-  </si>
-  <si>
-    <t>228.8 KPPS / 2600 Mbps</t>
-  </si>
-  <si>
-    <t>285.6 KPPS / 191 Mbps</t>
-  </si>
-  <si>
-    <t>284 KPPS / 1208 Mbps</t>
-  </si>
-  <si>
-    <t>192 KPPS / 566 Mbps</t>
-  </si>
-  <si>
-    <t>280 KPPS / 835 Mbps</t>
-  </si>
-  <si>
-    <t>281.6 KPPS / 841 Mbps</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2379,20 +2455,8 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2458,6 +2522,18 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2478,14 +2554,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2523,7 +2595,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2629,7 +2701,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2771,7 +2843,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2781,15 +2853,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{101F05EA-6A87-7646-9D66-36E81A856E36}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="18.95"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="67" customWidth="1"/>
-    <col min="2" max="2" width="179.5" style="67" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="67" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="67"/>
+    <col min="1" max="1" width="15.7109375" style="67" customWidth="1"/>
+    <col min="2" max="2" width="179.42578125" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="10.85546875" style="67"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
@@ -2815,7 +2887,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1">
       <c r="A2" s="67" t="s">
         <v>8</v>
       </c>
@@ -2838,7 +2910,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="67" t="s">
         <v>14</v>
       </c>
@@ -2861,7 +2933,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" s="67" t="s">
         <v>21</v>
       </c>
@@ -2884,7 +2956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1">
       <c r="A5" s="67" t="s">
         <v>25</v>
       </c>
@@ -2907,7 +2979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" hidden="1">
       <c r="A6" s="67" t="s">
         <v>26</v>
       </c>
@@ -2930,7 +3002,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1">
       <c r="A7" s="67" t="s">
         <v>28</v>
       </c>
@@ -2956,7 +3028,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1">
       <c r="A8" s="67" t="s">
         <v>32</v>
       </c>
@@ -2982,7 +3054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1">
       <c r="A9" s="67" t="s">
         <v>34</v>
       </c>
@@ -3008,7 +3080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1">
       <c r="A10" s="67" t="s">
         <v>36</v>
       </c>
@@ -3031,7 +3103,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1">
       <c r="A11" s="67" t="s">
         <v>40</v>
       </c>
@@ -3054,7 +3126,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="67" t="s">
         <v>44</v>
       </c>
@@ -3077,7 +3149,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1">
       <c r="A13" s="67" t="s">
         <v>48</v>
       </c>
@@ -3100,7 +3172,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1">
       <c r="A14" s="67" t="s">
         <v>49</v>
       </c>
@@ -3123,7 +3195,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1">
       <c r="A15" s="67" t="s">
         <v>50</v>
       </c>
@@ -3146,7 +3218,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1">
       <c r="A16" s="67" t="s">
         <v>51</v>
       </c>
@@ -3169,7 +3241,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1">
       <c r="A17" s="67" t="s">
         <v>55</v>
       </c>
@@ -3192,7 +3264,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1">
       <c r="A18" s="67" t="s">
         <v>56</v>
       </c>
@@ -3215,7 +3287,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1">
       <c r="A19" s="67" t="s">
         <v>57</v>
       </c>
@@ -3238,7 +3310,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="67" t="s">
         <v>58</v>
       </c>
@@ -3261,7 +3333,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1">
       <c r="A21" s="67" t="s">
         <v>62</v>
       </c>
@@ -3284,7 +3356,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1">
       <c r="A22" s="67" t="s">
         <v>63</v>
       </c>
@@ -3307,7 +3379,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="67" t="s">
         <v>64</v>
       </c>
@@ -3330,7 +3402,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1">
       <c r="A24" s="67" t="s">
         <v>66</v>
       </c>
@@ -3353,7 +3425,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1">
       <c r="A25" s="67" t="s">
         <v>67</v>
       </c>
@@ -3376,7 +3448,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="67" t="s">
         <v>68</v>
       </c>
@@ -3399,7 +3471,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1">
       <c r="A27" s="67" t="s">
         <v>71</v>
       </c>
@@ -3422,7 +3494,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1">
       <c r="A28" s="67" t="s">
         <v>72</v>
       </c>
@@ -3445,7 +3517,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="67" t="s">
         <v>73</v>
       </c>
@@ -3468,7 +3540,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1">
       <c r="A30" s="67" t="s">
         <v>76</v>
       </c>
@@ -3491,7 +3563,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1">
       <c r="A31" s="67" t="s">
         <v>77</v>
       </c>
@@ -3514,7 +3586,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="67" t="s">
         <v>78</v>
       </c>
@@ -3537,7 +3609,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1">
       <c r="A33" s="67" t="s">
         <v>81</v>
       </c>
@@ -3560,7 +3632,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1">
       <c r="A34" s="67" t="s">
         <v>82</v>
       </c>
@@ -3583,7 +3655,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="67" t="s">
         <v>83</v>
       </c>
@@ -3606,7 +3678,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1">
       <c r="A36" s="67" t="s">
         <v>85</v>
       </c>
@@ -3629,7 +3701,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1">
       <c r="A37" s="67" t="s">
         <v>86</v>
       </c>
@@ -3652,7 +3724,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="67" t="s">
         <v>87</v>
       </c>
@@ -3675,7 +3747,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1">
       <c r="A39" s="67" t="s">
         <v>89</v>
       </c>
@@ -3698,7 +3770,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1">
       <c r="A40" s="67" t="s">
         <v>90</v>
       </c>
@@ -3721,7 +3793,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="67" t="s">
         <v>91</v>
       </c>
@@ -3747,7 +3819,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1">
       <c r="A42" s="67" t="s">
         <v>94</v>
       </c>
@@ -3773,7 +3845,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1">
       <c r="A43" s="67" t="s">
         <v>95</v>
       </c>
@@ -3799,7 +3871,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="67" t="s">
         <v>96</v>
       </c>
@@ -3816,7 +3888,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1">
       <c r="A45" s="67" t="s">
         <v>101</v>
       </c>
@@ -3833,7 +3905,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1">
       <c r="A46" s="67" t="s">
         <v>102</v>
       </c>
@@ -3850,7 +3922,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" s="67" t="s">
         <v>103</v>
       </c>
@@ -3867,7 +3939,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1">
       <c r="A48" s="67" t="s">
         <v>105</v>
       </c>
@@ -3884,7 +3956,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1">
       <c r="A49" s="67" t="s">
         <v>106</v>
       </c>
@@ -3901,7 +3973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8">
       <c r="A50" s="67" t="s">
         <v>107</v>
       </c>
@@ -3927,7 +3999,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1">
       <c r="A51" s="67" t="s">
         <v>113</v>
       </c>
@@ -3953,7 +4025,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" hidden="1">
       <c r="A52" s="67" t="s">
         <v>114</v>
       </c>
@@ -3979,7 +4051,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" hidden="1">
       <c r="A53" s="67" t="s">
         <v>115</v>
       </c>
@@ -4002,7 +4074,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" hidden="1">
       <c r="A54" s="67" t="s">
         <v>118</v>
       </c>
@@ -4025,7 +4097,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1">
       <c r="A55" s="67" t="s">
         <v>119</v>
       </c>
@@ -4048,7 +4120,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" s="67" t="s">
         <v>120</v>
       </c>
@@ -4071,7 +4143,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" hidden="1">
       <c r="A57" s="67" t="s">
         <v>122</v>
       </c>
@@ -4094,7 +4166,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" hidden="1">
       <c r="A58" s="67" t="s">
         <v>123</v>
       </c>
@@ -4117,7 +4189,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" s="67" t="s">
         <v>124</v>
       </c>
@@ -4140,7 +4212,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" hidden="1">
       <c r="A60" s="67" t="s">
         <v>126</v>
       </c>
@@ -4163,7 +4235,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8">
       <c r="A61" s="67" t="s">
         <v>127</v>
       </c>
@@ -4186,7 +4258,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" hidden="1">
       <c r="A62" s="67" t="s">
         <v>129</v>
       </c>
@@ -4209,7 +4281,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8">
       <c r="A63" s="67" t="s">
         <v>130</v>
       </c>
@@ -4232,7 +4304,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" hidden="1">
       <c r="A64" s="67" t="s">
         <v>132</v>
       </c>
@@ -4255,7 +4327,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8">
       <c r="A65" s="67" t="s">
         <v>133</v>
       </c>
@@ -4278,7 +4350,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1">
       <c r="A66" s="67" t="s">
         <v>137</v>
       </c>
@@ -4301,7 +4373,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8">
       <c r="A67" s="67" t="s">
         <v>138</v>
       </c>
@@ -4327,7 +4399,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1">
       <c r="A68" s="67" t="s">
         <v>142</v>
       </c>
@@ -4350,7 +4422,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8">
       <c r="A69" s="67" t="s">
         <v>143</v>
       </c>
@@ -4376,7 +4448,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1">
       <c r="A70" s="67" t="s">
         <v>147</v>
       </c>
@@ -4399,7 +4471,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" s="67" t="s">
         <v>148</v>
       </c>
@@ -4425,7 +4497,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1">
       <c r="A72" s="67" t="s">
         <v>150</v>
       </c>
@@ -4451,7 +4523,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" s="67" t="s">
         <v>151</v>
       </c>
@@ -4474,7 +4546,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1">
       <c r="A74" s="67" t="s">
         <v>156</v>
       </c>
@@ -4497,7 +4569,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8">
       <c r="A75" s="67" t="s">
         <v>157</v>
       </c>
@@ -4520,7 +4592,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1">
       <c r="A76" s="67" t="s">
         <v>160</v>
       </c>
@@ -4543,7 +4615,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8">
       <c r="A77" s="67" t="s">
         <v>161</v>
       </c>
@@ -4566,7 +4638,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1">
       <c r="A78" s="67" t="s">
         <v>163</v>
       </c>
@@ -4589,7 +4661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8">
       <c r="A79" s="67" t="s">
         <v>164</v>
       </c>
@@ -4612,7 +4684,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1">
       <c r="A80" s="67" t="s">
         <v>166</v>
       </c>
@@ -4635,7 +4707,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" s="67" t="s">
         <v>167</v>
       </c>
@@ -4658,7 +4730,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1">
       <c r="A82" s="67" t="s">
         <v>169</v>
       </c>
@@ -4681,7 +4753,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" s="67" t="s">
         <v>171</v>
       </c>
@@ -4698,7 +4770,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1">
       <c r="A84" s="67" t="s">
         <v>174</v>
       </c>
@@ -4715,7 +4787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8">
       <c r="A85" s="67" t="s">
         <v>175</v>
       </c>
@@ -4738,7 +4810,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" hidden="1">
       <c r="A86" s="67" t="s">
         <v>178</v>
       </c>
@@ -4761,7 +4833,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8">
       <c r="A87" s="67" t="s">
         <v>179</v>
       </c>
@@ -4784,7 +4856,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" hidden="1">
       <c r="A88" s="67" t="s">
         <v>181</v>
       </c>
@@ -4807,7 +4879,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8">
       <c r="A89" s="67" t="s">
         <v>182</v>
       </c>
@@ -4830,7 +4902,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1">
       <c r="A90" s="67" t="s">
         <v>184</v>
       </c>
@@ -4853,7 +4925,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8">
       <c r="A91" s="67" t="s">
         <v>185</v>
       </c>
@@ -4876,7 +4948,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1">
       <c r="A92" s="67" t="s">
         <v>188</v>
       </c>
@@ -4899,7 +4971,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8">
       <c r="A93" s="67" t="s">
         <v>189</v>
       </c>
@@ -4922,7 +4994,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1">
       <c r="A94" s="67" t="s">
         <v>191</v>
       </c>
@@ -5007,29 +5079,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC397FCC-74C1-4D09-ACC0-E463BF5527EB}">
   <dimension ref="A1:I106"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="87.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="19.5" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.5" style="5" customWidth="1"/>
+    <col min="1" max="1" width="87.85546875" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="41.42578125" style="5" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="57" customHeight="1">
       <c r="A1" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="105" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="80"/>
+      <c r="C1" s="106"/>
       <c r="D1" s="36" t="s">
         <v>194</v>
       </c>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.25" customHeight="1">
       <c r="A2" s="38" t="s">
         <v>195</v>
       </c>
@@ -5044,12 +5116,12 @@
       </c>
       <c r="E2" s="11"/>
     </row>
-    <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>425</v>
+        <v>199</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C3" s="15">
         <v>95</v>
@@ -5059,12 +5131,12 @@
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15.6" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>426</v>
+        <v>201</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C4" s="15">
         <v>80</v>
@@ -5073,15 +5145,15 @@
         <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.6" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>427</v>
+        <v>204</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C5" s="4">
         <v>92</v>
@@ -5091,12 +5163,12 @@
       </c>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>428</v>
+        <v>206</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C6" s="1">
         <v>95</v>
@@ -5106,12 +5178,12 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="7" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="14.45" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>429</v>
+        <v>208</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C7" s="4">
         <v>95</v>
@@ -5120,12 +5192,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="14.1" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>430</v>
+        <v>210</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C8" s="4">
         <v>91</v>
@@ -5134,12 +5206,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="15.95">
       <c r="A9" s="2" t="s">
-        <v>467</v>
+        <v>212</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C9" s="4">
         <v>96</v>
@@ -5148,12 +5220,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="15.95">
       <c r="A10" s="2" t="s">
-        <v>432</v>
+        <v>214</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C10" s="4">
         <v>93</v>
@@ -5162,12 +5234,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="15.95">
       <c r="A11" s="2" t="s">
-        <v>433</v>
+        <v>216</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C11" s="4">
         <v>93</v>
@@ -5176,12 +5248,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="15.95">
       <c r="A12" s="2" t="s">
-        <v>434</v>
+        <v>218</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C12" s="1">
         <v>93</v>
@@ -5190,12 +5262,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="15.95">
       <c r="A13" s="2" t="s">
-        <v>435</v>
+        <v>220</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C13" s="1">
         <v>94</v>
@@ -5204,12 +5276,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="15.95">
       <c r="A14" s="2" t="s">
-        <v>468</v>
+        <v>222</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C14" s="4">
         <v>95</v>
@@ -5218,12 +5290,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="15.95">
       <c r="A15" s="2" t="s">
-        <v>469</v>
+        <v>224</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C15" s="1">
         <v>95</v>
@@ -5232,12 +5304,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="15.95">
       <c r="A16" s="3" t="s">
-        <v>438</v>
+        <v>226</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C16" s="46">
         <v>94</v>
@@ -5246,12 +5318,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="15.95">
       <c r="A17" s="43" t="s">
-        <v>470</v>
+        <v>228</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="C17" s="7">
         <v>96</v>
@@ -5260,9 +5332,9 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="40.5" customHeight="1">
       <c r="A18" s="38" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="B18" s="39" t="s">
         <v>196</v>
@@ -5274,12 +5346,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="15.95">
       <c r="A19" s="22" t="s">
-        <v>440</v>
+        <v>231</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="C19" s="27">
         <v>85</v>
@@ -5288,12 +5360,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="15.95">
       <c r="A20" s="2" t="s">
-        <v>441</v>
+        <v>233</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="C20" s="23">
         <v>90</v>
@@ -5302,12 +5374,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="15.95">
       <c r="A21" s="2" t="s">
-        <v>442</v>
+        <v>235</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C21" s="10">
         <v>92</v>
@@ -5316,12 +5388,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="15.95">
       <c r="A22" s="2" t="s">
-        <v>443</v>
+        <v>237</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C22" s="10">
         <v>90</v>
@@ -5330,12 +5402,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="15.95">
       <c r="A23" s="2" t="s">
-        <v>444</v>
+        <v>239</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C23" s="10">
         <v>90</v>
@@ -5344,12 +5416,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="15.95">
       <c r="A24" s="2" t="s">
-        <v>471</v>
+        <v>241</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C24" s="10">
         <v>95</v>
@@ -5358,12 +5430,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="15.95">
       <c r="A25" s="2" t="s">
-        <v>446</v>
+        <v>243</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="C25" s="10">
         <v>91</v>
@@ -5372,12 +5444,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="15.95">
       <c r="A26" s="2" t="s">
-        <v>447</v>
+        <v>245</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C26" s="10">
         <v>93</v>
@@ -5386,12 +5458,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="15.95">
       <c r="A27" s="2" t="s">
-        <v>472</v>
+        <v>247</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="C27" s="10">
         <v>92</v>
@@ -5400,12 +5472,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="15.95">
       <c r="A28" s="2" t="s">
-        <v>473</v>
+        <v>249</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="C28" s="10">
         <v>93</v>
@@ -5414,88 +5486,88 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="39" customHeight="1">
       <c r="A29" s="29" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>197</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.95">
       <c r="A30" s="2" t="s">
-        <v>450</v>
+        <v>254</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>422</v>
+        <v>255</v>
       </c>
       <c r="C30" s="47">
         <v>77</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="E30" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.95">
       <c r="A31" s="2" t="s">
-        <v>451</v>
+        <v>257</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>422</v>
+        <v>255</v>
       </c>
       <c r="C31" s="47">
         <v>77</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="E31" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.95">
       <c r="A32" s="2" t="s">
-        <v>452</v>
+        <v>258</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>422</v>
+        <v>255</v>
       </c>
       <c r="C32" s="47">
         <v>77</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="E32" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="17.45" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>441</v>
+        <v>233</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="C33" s="47">
         <v>93</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="41.25" customHeight="1">
       <c r="A34" s="29" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="B34" s="39" t="s">
         <v>196</v>
@@ -5507,12 +5579,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="15.95">
       <c r="A35" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B35" s="4">
-        <v>20000</v>
+        <v>261</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>262</v>
       </c>
       <c r="C35" s="48">
         <v>90</v>
@@ -5521,9 +5593,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" ht="15.95">
       <c r="A36" s="2" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="B36" s="4">
         <v>19330</v>
@@ -5535,9 +5607,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" ht="15.6" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>453</v>
+        <v>264</v>
       </c>
       <c r="B37" s="4">
         <v>10000</v>
@@ -5549,9 +5621,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" ht="15.95">
       <c r="A38" s="2" t="s">
-        <v>454</v>
+        <v>265</v>
       </c>
       <c r="B38" s="4">
         <v>2400</v>
@@ -5563,9 +5635,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" ht="15.95">
       <c r="A39" s="22" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="B39" s="15">
         <v>2250</v>
@@ -5577,9 +5649,9 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" ht="15.95">
       <c r="A40" s="22" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="B40" s="45">
         <v>975</v>
@@ -5591,9 +5663,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" ht="15.95">
       <c r="A41" s="2" t="s">
-        <v>455</v>
+        <v>268</v>
       </c>
       <c r="B41" s="4">
         <v>1550</v>
@@ -5605,9 +5677,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" ht="15.95">
       <c r="A42" s="2" t="s">
-        <v>456</v>
+        <v>269</v>
       </c>
       <c r="B42" s="4">
         <v>400</v>
@@ -5619,9 +5691,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" ht="15.95">
       <c r="A43" s="2" t="s">
-        <v>457</v>
+        <v>270</v>
       </c>
       <c r="B43" s="4">
         <v>175</v>
@@ -5633,9 +5705,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="32.25" customHeight="1">
       <c r="A44" s="29" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="B44" s="39" t="s">
         <v>196</v>
@@ -5644,455 +5716,466 @@
         <v>197</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="18.600000000000001" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="C45" s="33">
         <v>98</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="17.45" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C46" s="49">
         <v>98</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15.95">
       <c r="A47" s="8" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="C47" s="23">
         <v>90</v>
       </c>
       <c r="D47" s="57" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="E47" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15.95">
       <c r="A48" s="2" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="C48" s="23">
         <v>98</v>
       </c>
       <c r="D48" s="58" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.95">
       <c r="A49" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="23"/>
+        <v>282</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C49" s="23">
+        <v>50</v>
+      </c>
       <c r="D49" s="57"/>
     </row>
-    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="15.95">
       <c r="A50" s="8" t="s">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>248</v>
+        <v>285</v>
       </c>
       <c r="C50" s="23">
         <v>99</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="C51" s="32">
         <v>98</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.6" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="C52" s="23">
         <v>99</v>
       </c>
       <c r="D52" s="24"/>
     </row>
-    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="C53" s="31">
         <v>99</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15.95">
       <c r="A54" s="18" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="C54" s="23">
         <v>98</v>
       </c>
       <c r="D54" s="58" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.95">
       <c r="A55" s="19" t="s">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="C55" s="23">
         <v>98</v>
       </c>
       <c r="D55" s="58" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
       <c r="A56" s="19" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>262</v>
+        <v>299</v>
       </c>
       <c r="C56" s="23">
         <v>99</v>
       </c>
       <c r="D56" s="58" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.95">
       <c r="A57" s="9" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="C57" s="23">
         <v>98</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="17.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>492</v>
+        <v>304</v>
       </c>
       <c r="C58" s="23">
         <v>80</v>
       </c>
       <c r="D58" s="58" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.95">
       <c r="A59" s="2" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>496</v>
+        <v>307</v>
       </c>
       <c r="C59" s="23">
         <v>80</v>
       </c>
       <c r="D59" s="58" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="19.5" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>269</v>
+        <v>308</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>493</v>
+        <v>309</v>
       </c>
       <c r="C60" s="23">
         <v>80</v>
       </c>
       <c r="D60" s="58" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18.75" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>491</v>
+        <v>311</v>
       </c>
       <c r="C61" s="23">
         <v>78</v>
       </c>
       <c r="D61" s="58" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="17.45" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>494</v>
+        <v>313</v>
       </c>
       <c r="C62" s="23">
         <v>85</v>
       </c>
       <c r="D62" s="58" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C63" s="23"/>
+        <v>315</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C63" s="23">
+        <v>44</v>
+      </c>
       <c r="D63" s="58"/>
     </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="18" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>273</v>
+        <v>317</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>495</v>
+        <v>318</v>
       </c>
       <c r="C64" s="23">
         <v>80</v>
       </c>
       <c r="D64" s="58" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="32.25" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B65" s="6"/>
+        <v>320</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="C65" s="52"/>
       <c r="D65" s="57"/>
     </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="18" customHeight="1">
       <c r="A66" s="28" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="C66" s="30" t="s">
         <v>197</v>
       </c>
       <c r="D66" s="66"/>
     </row>
-    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="15.95">
       <c r="A67" s="2" t="s">
-        <v>277</v>
+        <v>324</v>
       </c>
       <c r="B67" s="24"/>
       <c r="C67" s="10"/>
       <c r="D67" s="57"/>
     </row>
-    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="15.95">
       <c r="A68" s="2" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="B68" s="24"/>
       <c r="C68" s="10"/>
       <c r="D68" s="57"/>
     </row>
-    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="15.95">
       <c r="A69" s="2" t="s">
-        <v>279</v>
+        <v>326</v>
       </c>
       <c r="B69" s="24"/>
       <c r="C69" s="10"/>
       <c r="D69" s="57"/>
     </row>
-    <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="15.95">
       <c r="A70" s="2" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="B70" s="24"/>
       <c r="C70" s="10"/>
       <c r="D70" s="57"/>
     </row>
-    <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="15.95">
       <c r="A71" s="2" t="s">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="B71" s="24"/>
       <c r="C71" s="10"/>
       <c r="D71" s="57"/>
     </row>
-    <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="15.95">
       <c r="A72" s="2" t="s">
-        <v>282</v>
+        <v>329</v>
       </c>
       <c r="B72" s="24"/>
       <c r="C72" s="10"/>
       <c r="D72" s="57"/>
     </row>
-    <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="15.95">
       <c r="A73" s="2" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="B73" s="24"/>
       <c r="C73" s="10"/>
       <c r="D73" s="57"/>
     </row>
-    <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="15.95">
       <c r="A74" s="2" t="s">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="B74" s="24"/>
       <c r="C74" s="10"/>
       <c r="D74" s="57"/>
     </row>
-    <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="15.95">
       <c r="A75" s="2" t="s">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="B75" s="24"/>
       <c r="C75" s="10"/>
       <c r="D75" s="57"/>
     </row>
-    <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="15.95">
       <c r="A76" s="2" t="s">
-        <v>286</v>
+        <v>333</v>
       </c>
       <c r="B76" s="24"/>
       <c r="C76" s="10"/>
       <c r="D76" s="57"/>
     </row>
-    <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="15.95">
       <c r="A77" s="2" t="s">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="B77" s="24"/>
       <c r="C77" s="10"/>
       <c r="D77" s="57"/>
     </row>
-    <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="15.95">
       <c r="A78" s="2" t="s">
-        <v>288</v>
+        <v>335</v>
       </c>
       <c r="B78" s="24"/>
       <c r="C78" s="10"/>
       <c r="D78" s="57"/>
     </row>
-    <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="15.95">
       <c r="A79" s="2" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="B79" s="24"/>
       <c r="C79" s="10"/>
       <c r="D79" s="57"/>
     </row>
-    <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="15.95">
       <c r="A80" s="2" t="s">
-        <v>290</v>
+        <v>337</v>
       </c>
       <c r="B80" s="33"/>
       <c r="C80" s="23"/>
       <c r="D80" s="57"/>
     </row>
-    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="15.95">
       <c r="A81" s="43" t="s">
-        <v>291</v>
+        <v>338</v>
       </c>
       <c r="B81" s="24"/>
       <c r="C81" s="32"/>
       <c r="D81" s="57"/>
     </row>
-    <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="15.95">
       <c r="A82" s="51" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="B82" s="24"/>
       <c r="C82" s="32"/>
       <c r="D82" s="57"/>
     </row>
-    <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="15.95">
       <c r="A83" s="22" t="s">
-        <v>293</v>
+        <v>340</v>
       </c>
       <c r="B83" s="33"/>
       <c r="C83" s="23"/>
       <c r="D83" s="57"/>
     </row>
-    <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="15.95">
       <c r="A84" s="2" t="s">
-        <v>294</v>
+        <v>341</v>
       </c>
       <c r="B84" s="24"/>
       <c r="C84" s="10"/>
       <c r="D84" s="57"/>
     </row>
-    <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="15.95">
       <c r="A85" s="2" t="s">
-        <v>295</v>
+        <v>342</v>
       </c>
       <c r="B85" s="24"/>
       <c r="C85" s="10"/>
       <c r="D85" s="57"/>
     </row>
-    <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="15.95">
       <c r="A86" s="2" t="s">
-        <v>296</v>
+        <v>343</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="C86" s="10">
         <v>10</v>
@@ -6101,12 +6184,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="15.95">
       <c r="A87" s="2" t="s">
-        <v>297</v>
+        <v>345</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>405</v>
+        <v>346</v>
       </c>
       <c r="C87" s="10">
         <v>10</v>
@@ -6115,33 +6198,33 @@
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="15.95">
       <c r="A88" s="2" t="s">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="B88" s="24"/>
       <c r="C88" s="10"/>
       <c r="D88" s="57"/>
     </row>
-    <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="15.95">
       <c r="A89" s="2" t="s">
-        <v>299</v>
+        <v>348</v>
       </c>
       <c r="B89" s="24"/>
       <c r="C89" s="10"/>
       <c r="D89" s="57"/>
     </row>
-    <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="15.95">
       <c r="A90" s="2" t="s">
-        <v>300</v>
+        <v>349</v>
       </c>
       <c r="B90" s="24"/>
       <c r="C90" s="10"/>
       <c r="D90" s="57"/>
     </row>
-    <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="15.95">
       <c r="A91" s="2" t="s">
-        <v>301</v>
+        <v>350</v>
       </c>
       <c r="B91" s="10">
         <v>80000</v>
@@ -6153,9 +6236,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="15.95">
       <c r="A92" s="2" t="s">
-        <v>458</v>
+        <v>351</v>
       </c>
       <c r="B92" s="24">
         <v>80000</v>
@@ -6167,22 +6250,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="15.95">
       <c r="A93" s="2" t="s">
-        <v>302</v>
+        <v>352</v>
       </c>
       <c r="B93" s="52" t="s">
-        <v>424</v>
+        <v>353</v>
       </c>
       <c r="C93" s="57"/>
       <c r="D93" s="70"/>
     </row>
-    <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="15.95">
       <c r="A94" s="2" t="s">
-        <v>303</v>
+        <v>354</v>
       </c>
       <c r="B94" s="24">
-        <v>32000</v>
+        <v>80000</v>
       </c>
       <c r="C94" s="5">
         <v>56</v>
@@ -6191,9 +6274,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="15.95">
       <c r="A95" s="2" t="s">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="B95" s="24">
         <v>32000</v>
@@ -6205,9 +6288,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="15.95">
       <c r="A96" s="8" t="s">
-        <v>305</v>
+        <v>356</v>
       </c>
       <c r="B96" s="34">
         <v>8000</v>
@@ -6219,21 +6302,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" ht="15.95">
       <c r="A97" s="2" t="s">
-        <v>306</v>
+        <v>357</v>
       </c>
       <c r="B97" s="71">
         <v>26000</v>
       </c>
       <c r="C97" s="69"/>
       <c r="D97" s="69" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15.95">
       <c r="A98" s="2" t="s">
-        <v>308</v>
+        <v>359</v>
       </c>
       <c r="B98" s="24">
         <v>1000</v>
@@ -6245,9 +6328,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="15.95">
       <c r="A99" s="2" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="B99" s="24">
         <v>300</v>
@@ -6259,43 +6342,43 @@
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="15.95">
       <c r="A100" s="2" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="B100" s="16"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
     </row>
-    <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" ht="15.95">
       <c r="A101" s="2" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
     </row>
-    <row r="102" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" ht="15.95">
       <c r="A102" s="2" t="s">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="B102" s="24"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="15" customHeight="1">
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" ht="15" customHeight="1">
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="15" customHeight="1">
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" ht="15" customHeight="1">
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
@@ -6310,29 +6393,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A7BD36-8D88-3742-A4AC-48B0AFB67141}">
   <dimension ref="A1:J106"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="85.1640625" customWidth="1"/>
-    <col min="2" max="2" width="32.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="46.5" customWidth="1"/>
+    <col min="1" max="1" width="85.140625" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="46.42578125" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="57" customHeight="1">
       <c r="A1" s="50" t="s">
-        <v>313</v>
-      </c>
-      <c r="B1" s="79" t="s">
-        <v>314</v>
-      </c>
-      <c r="C1" s="80"/>
+        <v>364</v>
+      </c>
+      <c r="B1" s="105" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1" s="106"/>
       <c r="D1" s="36" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="38" t="s">
         <v>195</v>
       </c>
@@ -6346,12 +6429,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>425</v>
+        <v>199</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="C3" s="58">
         <v>91</v>
@@ -6360,12 +6443,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="16.350000000000001" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>426</v>
+        <v>201</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>316</v>
+        <v>367</v>
       </c>
       <c r="C4" s="4">
         <v>70</v>
@@ -6374,15 +6457,15 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.6" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>427</v>
+        <v>204</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="C5" s="4">
         <v>92</v>
@@ -6391,12 +6474,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>428</v>
+        <v>206</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>318</v>
+        <v>370</v>
       </c>
       <c r="C6" s="4">
         <v>94</v>
@@ -6405,12 +6488,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="14.45" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>429</v>
+        <v>208</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="C7" s="58">
         <v>96</v>
@@ -6419,12 +6502,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="14.1" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>430</v>
+        <v>210</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="C8" s="4">
         <v>90</v>
@@ -6433,12 +6516,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="15.95">
       <c r="A9" s="2" t="s">
-        <v>467</v>
+        <v>212</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
       <c r="C9" s="58">
         <v>90</v>
@@ -6447,12 +6530,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="15.95">
       <c r="A10" s="2" t="s">
-        <v>432</v>
+        <v>214</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="C10" s="4">
         <v>90</v>
@@ -6461,12 +6544,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="15.95">
       <c r="A11" s="2" t="s">
-        <v>433</v>
+        <v>216</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="C11" s="4">
         <v>92</v>
@@ -6475,12 +6558,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="15.95">
       <c r="A12" s="2" t="s">
-        <v>434</v>
+        <v>218</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="C12" s="58">
         <v>92</v>
@@ -6489,12 +6572,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="15.95">
       <c r="A13" s="2" t="s">
-        <v>435</v>
+        <v>220</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="C13" s="4">
         <v>90</v>
@@ -6503,12 +6586,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="15.95">
       <c r="A14" s="2" t="s">
-        <v>468</v>
+        <v>222</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>324</v>
+        <v>377</v>
       </c>
       <c r="C14" s="4">
         <v>90</v>
@@ -6517,12 +6600,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="15.95">
       <c r="A15" s="2" t="s">
-        <v>469</v>
+        <v>224</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>325</v>
+        <v>378</v>
       </c>
       <c r="C15" s="4">
         <v>94</v>
@@ -6531,12 +6614,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="15.95">
       <c r="A16" s="3" t="s">
-        <v>438</v>
+        <v>226</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="C16" s="4">
         <v>92</v>
@@ -6545,12 +6628,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.95">
       <c r="A17" s="43" t="s">
-        <v>470</v>
+        <v>228</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>407</v>
+        <v>380</v>
       </c>
       <c r="C17" s="7">
         <v>92</v>
@@ -6559,12 +6642,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="18" customHeight="1">
       <c r="A18" s="38" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>197</v>
@@ -6573,12 +6656,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="15.95">
       <c r="A19" s="22" t="s">
-        <v>440</v>
+        <v>231</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>327</v>
+        <v>382</v>
       </c>
       <c r="C19" s="55">
         <v>92</v>
@@ -6587,12 +6670,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="15.95">
       <c r="A20" s="2" t="s">
-        <v>441</v>
+        <v>233</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>328</v>
+        <v>383</v>
       </c>
       <c r="C20" s="57">
         <v>95</v>
@@ -6601,12 +6684,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="15.95">
       <c r="A21" s="2" t="s">
-        <v>442</v>
+        <v>235</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>329</v>
+        <v>384</v>
       </c>
       <c r="C21" s="57">
         <v>95</v>
@@ -6615,12 +6698,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="15.95">
       <c r="A22" s="2" t="s">
-        <v>443</v>
+        <v>237</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>330</v>
+        <v>385</v>
       </c>
       <c r="C22" s="57">
         <v>93</v>
@@ -6629,12 +6712,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="15.95">
       <c r="A23" s="2" t="s">
-        <v>444</v>
+        <v>239</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>331</v>
+        <v>386</v>
       </c>
       <c r="C23" s="57">
         <v>92</v>
@@ -6643,12 +6726,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="15.95">
       <c r="A24" s="2" t="s">
-        <v>471</v>
+        <v>241</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>332</v>
+        <v>387</v>
       </c>
       <c r="C24" s="57">
         <v>92</v>
@@ -6657,15 +6740,15 @@
         <v>67</v>
       </c>
       <c r="F24" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.95">
       <c r="A25" s="2" t="s">
-        <v>446</v>
+        <v>243</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>334</v>
+        <v>389</v>
       </c>
       <c r="C25" s="57">
         <v>92</v>
@@ -6674,12 +6757,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="15.95">
       <c r="A26" s="2" t="s">
-        <v>447</v>
+        <v>245</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>332</v>
+        <v>387</v>
       </c>
       <c r="C26" s="57">
         <v>90</v>
@@ -6688,12 +6771,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="15.95">
       <c r="A27" s="2" t="s">
-        <v>472</v>
+        <v>247</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="C27" s="57">
         <v>90</v>
@@ -6702,12 +6785,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="15.95">
       <c r="A28" s="2" t="s">
-        <v>473</v>
+        <v>249</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>336</v>
+        <v>391</v>
       </c>
       <c r="C28" s="57">
         <v>92</v>
@@ -6716,91 +6799,91 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="18" customHeight="1">
       <c r="A29" s="29" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>197</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.95">
       <c r="A30" s="2" t="s">
-        <v>450</v>
+        <v>254</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>422</v>
+        <v>255</v>
       </c>
       <c r="C30" s="47">
         <v>68</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="E30" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.95">
       <c r="A31" s="2" t="s">
-        <v>451</v>
+        <v>257</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>422</v>
+        <v>255</v>
       </c>
       <c r="C31" s="47">
         <v>68</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="E31" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.95">
       <c r="A32" s="2" t="s">
-        <v>452</v>
+        <v>258</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>422</v>
+        <v>255</v>
       </c>
       <c r="C32" s="47">
         <v>68</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="E32" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="17.45" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>441</v>
+        <v>233</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>421</v>
+        <v>392</v>
       </c>
       <c r="C33" s="57">
         <v>92</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="18" customHeight="1">
       <c r="A34" s="29" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>197</v>
@@ -6809,12 +6892,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="15.95">
       <c r="A35" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B35" s="48">
-        <v>26000</v>
+        <v>261</v>
+      </c>
+      <c r="B35" s="48" t="s">
+        <v>394</v>
       </c>
       <c r="C35" s="63">
         <v>90</v>
@@ -6823,9 +6906,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="15.95">
       <c r="A36" s="2" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="B36" s="4">
         <v>25400</v>
@@ -6852,9 +6935,9 @@
         <v>57200</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="15.6" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>453</v>
+        <v>264</v>
       </c>
       <c r="B37" s="4">
         <v>13300</v>
@@ -6886,9 +6969,9 @@
         <v>228800</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="15.95">
       <c r="A38" s="2" t="s">
-        <v>454</v>
+        <v>265</v>
       </c>
       <c r="B38" s="4">
         <v>3200</v>
@@ -6920,9 +7003,9 @@
         <v>2599.1680000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="15.95">
       <c r="A39" s="22" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="B39" s="15">
         <v>2700</v>
@@ -6934,9 +7017,9 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="15.95">
       <c r="A40" s="22" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="B40" s="45">
         <v>1050</v>
@@ -6951,9 +7034,9 @@
         <v>280000</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="15.95">
       <c r="A41" s="2" t="s">
-        <v>455</v>
+        <v>268</v>
       </c>
       <c r="B41" s="4">
         <v>1810</v>
@@ -6969,9 +7052,9 @@
         <v>835.52</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="15.95">
       <c r="A42" s="2" t="s">
-        <v>456</v>
+        <v>269</v>
       </c>
       <c r="B42" s="1">
         <v>460</v>
@@ -6986,9 +7069,9 @@
         <v>315000</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="15.95">
       <c r="A43" s="2" t="s">
-        <v>457</v>
+        <v>270</v>
       </c>
       <c r="B43" s="4">
         <v>205</v>
@@ -7004,369 +7087,379 @@
         <v>939.96</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="18" customHeight="1">
       <c r="A44" s="29" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>197</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="18.600000000000001" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
       <c r="C45" s="24">
         <v>98</v>
       </c>
       <c r="D45" s="58" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="17.45" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>340</v>
+        <v>396</v>
       </c>
       <c r="C46" s="24">
         <v>98</v>
       </c>
       <c r="D46" s="58" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.95">
       <c r="A47" s="8" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>341</v>
+        <v>397</v>
       </c>
       <c r="C47" s="57">
         <v>96</v>
       </c>
       <c r="D47" s="58" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15.95">
       <c r="A48" s="2" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>342</v>
+        <v>398</v>
       </c>
       <c r="C48" s="57">
         <v>96</v>
       </c>
       <c r="D48" s="58" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.95">
       <c r="A49" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B49" s="23"/>
-      <c r="C49" s="57"/>
+        <v>282</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C49" s="23">
+        <v>50</v>
+      </c>
       <c r="D49" s="58"/>
     </row>
-    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="15.95">
       <c r="A50" s="8" t="s">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="C50" s="55">
         <v>98</v>
       </c>
       <c r="D50" s="58" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>344</v>
+        <v>401</v>
       </c>
       <c r="C51" s="57">
         <v>98</v>
       </c>
       <c r="D51" s="58" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.6" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>345</v>
+        <v>402</v>
       </c>
       <c r="C52" s="57">
         <v>99</v>
       </c>
       <c r="D52" s="58" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>346</v>
+        <v>403</v>
       </c>
       <c r="C53" s="64">
         <v>99</v>
       </c>
       <c r="D53" s="58" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15.95">
       <c r="A54" s="18" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="C54" s="65">
         <v>98</v>
       </c>
       <c r="D54" s="58" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.95">
       <c r="A55" s="19" t="s">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>348</v>
+        <v>405</v>
       </c>
       <c r="C55" s="65">
         <v>98</v>
       </c>
       <c r="D55" s="58" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
       <c r="A56" s="19" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="C56" s="65">
         <v>96</v>
       </c>
       <c r="D56" s="58" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.95">
       <c r="A57" s="9" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>350</v>
+        <v>407</v>
       </c>
       <c r="C57" s="57">
         <v>96</v>
       </c>
       <c r="D57" s="58" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="17.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>481</v>
+        <v>408</v>
       </c>
       <c r="C58" s="55">
         <v>78</v>
       </c>
       <c r="D58" s="58" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.95">
       <c r="A59" s="2" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>480</v>
+        <v>409</v>
       </c>
       <c r="C59" s="57">
         <v>77</v>
       </c>
       <c r="D59" s="58" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="19.5" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>269</v>
+        <v>308</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="C60" s="57">
         <v>79</v>
       </c>
       <c r="D60" s="58" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18.75" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>488</v>
+        <v>411</v>
       </c>
       <c r="C61" s="57">
         <v>72</v>
       </c>
       <c r="D61" s="58" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="17.45" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="B62" s="32" t="s">
-        <v>483</v>
+        <v>412</v>
       </c>
       <c r="C62" s="57">
         <v>88</v>
       </c>
       <c r="D62" s="58" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B63" s="23"/>
-      <c r="C63" s="57"/>
+        <v>315</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>413</v>
+      </c>
+      <c r="C63" s="57">
+        <v>50</v>
+      </c>
       <c r="D63" s="58"/>
     </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="18" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>273</v>
+        <v>317</v>
       </c>
       <c r="B64" s="53" t="s">
-        <v>487</v>
+        <v>414</v>
       </c>
       <c r="C64" s="57">
         <v>79</v>
       </c>
       <c r="D64" s="58" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="32.25" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B65" s="52"/>
+        <v>320</v>
+      </c>
+      <c r="B65" s="52" t="s">
+        <v>415</v>
+      </c>
       <c r="C65" s="57"/>
       <c r="D65" s="58"/>
     </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="18" customHeight="1">
       <c r="A66" s="28" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="B66" s="30" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="C66" s="66" t="s">
         <v>197</v>
       </c>
       <c r="D66" s="66" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.95">
       <c r="A67" s="2" t="s">
-        <v>277</v>
+        <v>324</v>
       </c>
       <c r="B67" s="10"/>
       <c r="C67" s="57"/>
       <c r="D67" s="57"/>
     </row>
-    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="15.95">
       <c r="A68" s="2" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="B68" s="10"/>
       <c r="C68" s="57"/>
       <c r="D68" s="57"/>
     </row>
-    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="15.95">
       <c r="A69" s="2" t="s">
-        <v>279</v>
+        <v>326</v>
       </c>
       <c r="B69" s="10"/>
       <c r="C69" s="57"/>
       <c r="D69" s="57"/>
     </row>
-    <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="15.95">
       <c r="A70" s="2" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="B70" s="10"/>
       <c r="C70" s="57"/>
       <c r="D70" s="57"/>
     </row>
-    <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="15.95">
       <c r="A71" s="2" t="s">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="B71" s="10"/>
       <c r="C71" s="57"/>
       <c r="D71" s="57"/>
     </row>
-    <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="15.95">
       <c r="A72" s="2" t="s">
-        <v>282</v>
+        <v>329</v>
       </c>
       <c r="B72" s="10"/>
       <c r="C72" s="57"/>
       <c r="D72" s="57"/>
     </row>
-    <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="15.95">
       <c r="A73" s="2" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="B73" s="10"/>
       <c r="C73" s="57"/>
       <c r="D73" s="57"/>
     </row>
-    <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="15.95">
       <c r="A74" s="2" t="s">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="B74" s="10">
         <v>1536</v>
@@ -7374,100 +7467,100 @@
       <c r="C74" s="57"/>
       <c r="D74" s="57"/>
     </row>
-    <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="15.95">
       <c r="A75" s="2" t="s">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="B75" s="10"/>
       <c r="C75" s="57"/>
       <c r="D75" s="57"/>
     </row>
-    <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="15.95">
       <c r="A76" s="2" t="s">
-        <v>286</v>
+        <v>333</v>
       </c>
       <c r="B76" s="10"/>
       <c r="C76" s="57"/>
       <c r="D76" s="57"/>
     </row>
-    <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="15.95">
       <c r="A77" s="2" t="s">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="57"/>
       <c r="D77" s="57"/>
     </row>
-    <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="15.95">
       <c r="A78" s="2" t="s">
-        <v>288</v>
+        <v>335</v>
       </c>
       <c r="B78" s="10"/>
       <c r="C78" s="57"/>
       <c r="D78" s="57"/>
     </row>
-    <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="15.95">
       <c r="A79" s="2" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="B79" s="10"/>
       <c r="C79" s="57"/>
       <c r="D79" s="57"/>
     </row>
-    <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="15.95">
       <c r="A80" s="2" t="s">
-        <v>290</v>
+        <v>337</v>
       </c>
       <c r="B80" s="23"/>
       <c r="C80" s="57"/>
       <c r="D80" s="57"/>
     </row>
-    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="15.95">
       <c r="A81" s="43" t="s">
-        <v>291</v>
+        <v>338</v>
       </c>
       <c r="B81" s="32"/>
       <c r="C81" s="57"/>
       <c r="D81" s="57"/>
     </row>
-    <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="15.95">
       <c r="A82" s="51" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="B82" s="32"/>
       <c r="C82" s="57"/>
       <c r="D82" s="57"/>
     </row>
-    <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="15.95">
       <c r="A83" s="22" t="s">
-        <v>293</v>
+        <v>340</v>
       </c>
       <c r="B83" s="23"/>
       <c r="C83" s="57"/>
       <c r="D83" s="57"/>
     </row>
-    <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="15.95">
       <c r="A84" s="2" t="s">
-        <v>294</v>
+        <v>341</v>
       </c>
       <c r="B84" s="10"/>
       <c r="C84" s="57"/>
       <c r="D84" s="57"/>
     </row>
-    <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="15.95">
       <c r="A85" s="2" t="s">
-        <v>295</v>
+        <v>342</v>
       </c>
       <c r="B85" s="10"/>
       <c r="C85" s="57"/>
       <c r="D85" s="57"/>
     </row>
-    <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="15.95">
       <c r="A86" s="2" t="s">
-        <v>296</v>
+        <v>343</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>351</v>
+        <v>417</v>
       </c>
       <c r="C86" s="10">
         <v>10</v>
@@ -7476,12 +7569,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="15.95">
       <c r="A87" s="2" t="s">
-        <v>297</v>
+        <v>345</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>352</v>
+        <v>418</v>
       </c>
       <c r="C87" s="10">
         <v>10</v>
@@ -7490,33 +7583,33 @@
         <v>84</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="15.95">
       <c r="A88" s="2" t="s">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="B88" s="10"/>
       <c r="C88" s="57"/>
       <c r="D88" s="57"/>
     </row>
-    <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="15.95">
       <c r="A89" s="2" t="s">
-        <v>299</v>
+        <v>348</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="57"/>
       <c r="D89" s="57"/>
     </row>
-    <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="15.95">
       <c r="A90" s="2" t="s">
-        <v>300</v>
+        <v>349</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="57"/>
       <c r="D90" s="57"/>
     </row>
-    <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="15.95">
       <c r="A91" s="2" t="s">
-        <v>301</v>
+        <v>350</v>
       </c>
       <c r="B91" s="10">
         <v>96000</v>
@@ -7528,9 +7621,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="15.95">
       <c r="A92" s="2" t="s">
-        <v>458</v>
+        <v>351</v>
       </c>
       <c r="B92" s="10">
         <v>96000</v>
@@ -7542,51 +7635,51 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="15.95">
       <c r="A93" s="2" t="s">
-        <v>302</v>
+        <v>352</v>
       </c>
       <c r="B93" s="52" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C93" s="57"/>
       <c r="D93" s="70"/>
     </row>
-    <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="15.95">
       <c r="A94" s="2" t="s">
-        <v>353</v>
+        <v>420</v>
       </c>
       <c r="B94" s="72"/>
       <c r="C94" s="56"/>
       <c r="D94" s="70"/>
     </row>
-    <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="15.95">
       <c r="A95" s="2" t="s">
-        <v>354</v>
+        <v>421</v>
       </c>
       <c r="B95" s="26"/>
       <c r="C95" s="56"/>
       <c r="D95" s="57"/>
     </row>
-    <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="15.95">
       <c r="A96" s="8" t="s">
-        <v>305</v>
+        <v>356</v>
       </c>
       <c r="B96" s="35"/>
       <c r="C96" s="10"/>
       <c r="D96" s="57"/>
     </row>
-    <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" ht="15.95">
       <c r="A97" s="2" t="s">
-        <v>306</v>
+        <v>357</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
       <c r="D97" s="57"/>
     </row>
-    <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" ht="15.95">
       <c r="A98" s="2" t="s">
-        <v>308</v>
+        <v>359</v>
       </c>
       <c r="B98" s="10">
         <v>1200</v>
@@ -7598,51 +7691,51 @@
         <v>55</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="15.95">
       <c r="A99" s="2" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
       <c r="D99" s="57"/>
     </row>
-    <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="15.95">
       <c r="A100" s="2" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
       <c r="D100" s="57"/>
     </row>
-    <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" ht="15.95">
       <c r="A101" s="2" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="57"/>
     </row>
-    <row r="102" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" ht="15.95">
       <c r="A102" s="2" t="s">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
       <c r="D102" s="57"/>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="15" customHeight="1">
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" ht="15" customHeight="1">
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="15" customHeight="1">
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" ht="15" customHeight="1">
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
     </row>
@@ -7657,643 +7750,884 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1F4FD9-0BA8-D443-A42F-4E5E606C52A0}">
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="62.5" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I43"/>
+  <sheetFormatPr defaultColWidth="62.42578125" defaultRowHeight="24"/>
   <cols>
-    <col min="1" max="1" width="162.5" style="85" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" style="85" customWidth="1"/>
-    <col min="3" max="3" width="29.1640625" style="85" customWidth="1"/>
-    <col min="4" max="4" width="26" style="85" customWidth="1"/>
-    <col min="5" max="5" width="47.6640625" style="85" customWidth="1"/>
-    <col min="6" max="6" width="26.5" style="85" customWidth="1"/>
-    <col min="7" max="7" width="33.83203125" style="85" customWidth="1"/>
-    <col min="8" max="16384" width="62.5" style="85"/>
+    <col min="1" max="1" width="162.42578125" style="81" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" style="81" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" style="81" customWidth="1"/>
+    <col min="4" max="4" width="26" style="81" customWidth="1"/>
+    <col min="5" max="5" width="47.7109375" style="81" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="81" customWidth="1"/>
+    <col min="7" max="7" width="33.85546875" style="81" customWidth="1"/>
+    <col min="8" max="16384" width="62.42578125" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="75" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+    <row r="1" spans="1:7" ht="75">
+      <c r="A1" s="79" t="s">
+        <v>422</v>
+      </c>
+      <c r="B1" s="103" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" s="104"/>
+      <c r="D1" s="80" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" s="103" t="s">
+        <v>365</v>
+      </c>
+      <c r="F1" s="104"/>
+      <c r="G1" s="80" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="50.1">
+      <c r="A2" s="82" t="s">
+        <v>423</v>
+      </c>
+      <c r="B2" s="83" t="s">
+        <v>381</v>
+      </c>
+      <c r="C2" s="84" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="83" t="s">
+        <v>424</v>
+      </c>
+      <c r="E2" s="83" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" s="84" t="s">
+        <v>197</v>
+      </c>
+      <c r="G2" s="84" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="24.95">
+      <c r="A3" s="85" t="s">
+        <v>425</v>
+      </c>
+      <c r="B3" s="86" t="s">
+        <v>426</v>
+      </c>
+      <c r="C3" s="87">
+        <v>94</v>
+      </c>
+      <c r="D3" s="88">
+        <v>40</v>
+      </c>
+      <c r="E3" s="86" t="s">
+        <v>427</v>
+      </c>
+      <c r="F3" s="87">
+        <v>93</v>
+      </c>
+      <c r="G3" s="88">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="24.95">
+      <c r="A4" s="85" t="s">
+        <v>428</v>
+      </c>
+      <c r="B4" s="88" t="s">
+        <v>429</v>
+      </c>
+      <c r="C4" s="89">
+        <v>95</v>
+      </c>
+      <c r="D4" s="90">
+        <v>40</v>
+      </c>
+      <c r="E4" s="88" t="s">
+        <v>430</v>
+      </c>
+      <c r="F4" s="89">
+        <v>94</v>
+      </c>
+      <c r="G4" s="90">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="24.95">
+      <c r="A5" s="85" t="s">
+        <v>431</v>
+      </c>
+      <c r="B5" s="91" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="92">
+        <v>94</v>
+      </c>
+      <c r="D5" s="93">
+        <v>60</v>
+      </c>
+      <c r="E5" s="91" t="s">
+        <v>432</v>
+      </c>
+      <c r="F5" s="92">
+        <v>91</v>
+      </c>
+      <c r="G5" s="93">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="24.95">
+      <c r="A6" s="94" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="88" t="s">
+        <v>273</v>
+      </c>
+      <c r="C6" s="95">
+        <v>99</v>
+      </c>
+      <c r="D6" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="E6" s="88" t="s">
+        <v>395</v>
+      </c>
+      <c r="F6" s="88">
+        <v>98</v>
+      </c>
+      <c r="G6" s="96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="24.95">
+      <c r="A7" s="94" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" s="88" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" s="97">
+        <v>99</v>
+      </c>
+      <c r="D7" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="E7" s="88" t="s">
+        <v>396</v>
+      </c>
+      <c r="F7" s="88">
+        <v>98</v>
+      </c>
+      <c r="G7" s="96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="24.95">
+      <c r="A8" s="98" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="91" t="s">
+        <v>278</v>
+      </c>
+      <c r="C8" s="92">
+        <v>90</v>
+      </c>
+      <c r="D8" s="93" t="s">
+        <v>274</v>
+      </c>
+      <c r="E8" s="88" t="s">
+        <v>397</v>
+      </c>
+      <c r="F8" s="88">
+        <v>96</v>
+      </c>
+      <c r="G8" s="93" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.5" customHeight="1">
+      <c r="A9" s="85" t="s">
+        <v>306</v>
+      </c>
+      <c r="B9" s="88"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="99" t="s">
+        <v>433</v>
+      </c>
+      <c r="E9" s="88"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="99" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="75">
+      <c r="A12" s="79" t="s">
+        <v>434</v>
+      </c>
+      <c r="B12" s="103" t="s">
+        <v>193</v>
+      </c>
+      <c r="C12" s="104"/>
+      <c r="D12" s="80" t="s">
+        <v>194</v>
+      </c>
+      <c r="E12" s="103" t="s">
+        <v>365</v>
+      </c>
+      <c r="F12" s="104"/>
+      <c r="G12" s="80" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="50.1">
+      <c r="A13" s="82" t="s">
+        <v>423</v>
+      </c>
+      <c r="B13" s="83" t="s">
+        <v>381</v>
+      </c>
+      <c r="C13" s="84" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="83" t="s">
+        <v>424</v>
+      </c>
+      <c r="E13" s="83" t="s">
+        <v>196</v>
+      </c>
+      <c r="F13" s="84" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13" s="84" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="24.95">
+      <c r="A14" s="85" t="s">
+        <v>425</v>
+      </c>
+      <c r="B14" s="86" t="s">
+        <v>435</v>
+      </c>
+      <c r="C14" s="87">
+        <v>95</v>
+      </c>
+      <c r="D14" s="88">
+        <v>61</v>
+      </c>
+      <c r="E14" s="86" t="s">
+        <v>427</v>
+      </c>
+      <c r="F14" s="87">
+        <v>93</v>
+      </c>
+      <c r="G14" s="88">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="24.95">
+      <c r="A15" s="85" t="s">
+        <v>428</v>
+      </c>
+      <c r="B15" s="88" t="s">
+        <v>429</v>
+      </c>
+      <c r="C15" s="89">
+        <v>95</v>
+      </c>
+      <c r="D15" s="90">
+        <v>61</v>
+      </c>
+      <c r="E15" s="88" t="s">
+        <v>430</v>
+      </c>
+      <c r="F15" s="89">
+        <v>94</v>
+      </c>
+      <c r="G15" s="90">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="24.95">
+      <c r="A16" s="85" t="s">
+        <v>431</v>
+      </c>
+      <c r="B16" s="91" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="92">
+        <v>94</v>
+      </c>
+      <c r="D16" s="93">
+        <v>60</v>
+      </c>
+      <c r="E16" s="91" t="s">
+        <v>436</v>
+      </c>
+      <c r="F16" s="92">
+        <v>91</v>
+      </c>
+      <c r="G16" s="93">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="24.95">
+      <c r="A17" s="94" t="s">
+        <v>272</v>
+      </c>
+      <c r="B17" s="88" t="s">
+        <v>273</v>
+      </c>
+      <c r="C17" s="95">
+        <v>99</v>
+      </c>
+      <c r="D17" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="E17" s="88" t="s">
+        <v>395</v>
+      </c>
+      <c r="F17" s="88">
+        <v>98</v>
+      </c>
+      <c r="G17" s="96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="24.95">
+      <c r="A18" s="94" t="s">
+        <v>275</v>
+      </c>
+      <c r="B18" s="88" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="97">
+        <v>99</v>
+      </c>
+      <c r="D18" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="E18" s="88" t="s">
+        <v>396</v>
+      </c>
+      <c r="F18" s="88">
+        <v>98</v>
+      </c>
+      <c r="G18" s="96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="24.95">
+      <c r="A19" s="98" t="s">
+        <v>277</v>
+      </c>
+      <c r="B19" s="91" t="s">
+        <v>278</v>
+      </c>
+      <c r="C19" s="92">
+        <v>90</v>
+      </c>
+      <c r="D19" s="93" t="s">
+        <v>274</v>
+      </c>
+      <c r="E19" s="88" t="s">
+        <v>397</v>
+      </c>
+      <c r="F19" s="88">
+        <v>96</v>
+      </c>
+      <c r="G19" s="93" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="24.95">
+      <c r="A20" s="85" t="s">
+        <v>306</v>
+      </c>
+      <c r="B20" s="88"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="99" t="s">
+        <v>433</v>
+      </c>
+      <c r="E20" s="88"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="99" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="75">
+      <c r="A23" s="100" t="s">
+        <v>437</v>
+      </c>
+      <c r="B23" s="103" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="104"/>
+      <c r="D23" s="80" t="s">
+        <v>194</v>
+      </c>
+      <c r="E23" s="103" t="s">
+        <v>365</v>
+      </c>
+      <c r="F23" s="104"/>
+      <c r="G23" s="80" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="50.1">
+      <c r="A24" s="82" t="s">
+        <v>423</v>
+      </c>
+      <c r="B24" s="83" t="s">
+        <v>381</v>
+      </c>
+      <c r="C24" s="84" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" s="83" t="s">
+        <v>424</v>
+      </c>
+      <c r="E24" s="83" t="s">
+        <v>381</v>
+      </c>
+      <c r="F24" s="84" t="s">
+        <v>197</v>
+      </c>
+      <c r="G24" s="83" t="s">
+        <v>424</v>
+      </c>
+      <c r="I24" s="81">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="24.95">
+      <c r="A25" s="85" t="s">
+        <v>425</v>
+      </c>
+      <c r="B25" s="86" t="s">
+        <v>438</v>
+      </c>
+      <c r="C25" s="87">
+        <v>94</v>
+      </c>
+      <c r="D25" s="88">
+        <v>40</v>
+      </c>
+      <c r="E25" s="86" t="s">
+        <v>427</v>
+      </c>
+      <c r="F25" s="87">
+        <v>93</v>
+      </c>
+      <c r="G25" s="88">
+        <v>59</v>
+      </c>
+      <c r="I25" s="81">
+        <f>I24*8*373/1000000</f>
+        <v>835.52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="24.95">
+      <c r="A26" s="85" t="s">
+        <v>428</v>
+      </c>
+      <c r="B26" s="88" t="s">
+        <v>429</v>
+      </c>
+      <c r="C26" s="89">
+        <v>95</v>
+      </c>
+      <c r="D26" s="90">
+        <v>38</v>
+      </c>
+      <c r="E26" s="88" t="s">
+        <v>430</v>
+      </c>
+      <c r="F26" s="89">
+        <v>94</v>
+      </c>
+      <c r="G26" s="90">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="24.95">
+      <c r="A27" s="85" t="s">
+        <v>431</v>
+      </c>
+      <c r="B27" s="91" t="s">
+        <v>439</v>
+      </c>
+      <c r="C27" s="92">
+        <v>75</v>
+      </c>
+      <c r="D27" s="93">
+        <v>56</v>
+      </c>
+      <c r="E27" s="91" t="s">
+        <v>440</v>
+      </c>
+      <c r="F27" s="92">
+        <v>75</v>
+      </c>
+      <c r="G27" s="93">
+        <v>59</v>
+      </c>
+      <c r="H27" s="81" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="24.95">
+      <c r="A28" s="94" t="s">
+        <v>272</v>
+      </c>
+      <c r="B28" s="88" t="s">
+        <v>273</v>
+      </c>
+      <c r="C28" s="95">
+        <v>99</v>
+      </c>
+      <c r="D28" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="E28" s="88" t="s">
+        <v>395</v>
+      </c>
+      <c r="F28" s="88">
+        <v>98</v>
+      </c>
+      <c r="G28" s="96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="24.95">
+      <c r="A29" s="94" t="s">
+        <v>275</v>
+      </c>
+      <c r="B29" s="88" t="s">
+        <v>276</v>
+      </c>
+      <c r="C29" s="97">
+        <v>99</v>
+      </c>
+      <c r="D29" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="E29" s="88" t="s">
+        <v>396</v>
+      </c>
+      <c r="F29" s="88">
+        <v>98</v>
+      </c>
+      <c r="G29" s="96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="24.95">
+      <c r="A30" s="98" t="s">
+        <v>277</v>
+      </c>
+      <c r="B30" s="91" t="s">
+        <v>278</v>
+      </c>
+      <c r="C30" s="92">
+        <v>90</v>
+      </c>
+      <c r="D30" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="E30" s="88" t="s">
+        <v>397</v>
+      </c>
+      <c r="F30" s="88">
+        <v>96</v>
+      </c>
+      <c r="G30" s="93" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="24.95">
+      <c r="A31" s="85" t="s">
+        <v>306</v>
+      </c>
+      <c r="B31" s="91" t="s">
+        <v>307</v>
+      </c>
+      <c r="C31" s="91">
+        <v>80</v>
+      </c>
+      <c r="D31" s="99" t="s">
+        <v>433</v>
+      </c>
+      <c r="E31" s="88" t="s">
         <v>409</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="F31" s="88">
+        <v>77</v>
+      </c>
+      <c r="G31" s="99" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="24.95">
+      <c r="A32" s="101" t="s">
+        <v>442</v>
+      </c>
+      <c r="B32" s="102" t="s">
+        <v>443</v>
+      </c>
+      <c r="C32" s="102">
+        <v>75</v>
+      </c>
+      <c r="D32" s="102">
+        <v>60</v>
+      </c>
+      <c r="E32" s="102" t="s">
+        <v>444</v>
+      </c>
+      <c r="F32" s="102">
+        <v>62</v>
+      </c>
+      <c r="G32" s="102">
+        <v>60</v>
+      </c>
+      <c r="H32" s="81" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="75">
+      <c r="A34" s="100" t="s">
+        <v>445</v>
+      </c>
+      <c r="B34" s="103" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="84" t="s">
+      <c r="C34" s="104"/>
+      <c r="D34" s="80" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="82" t="s">
-        <v>314</v>
-      </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="84" t="s">
+      <c r="E34" s="103" t="s">
+        <v>365</v>
+      </c>
+      <c r="F34" s="104"/>
+      <c r="G34" s="80" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="50" x14ac:dyDescent="0.3">
-      <c r="A2" s="86" t="s">
-        <v>410</v>
-      </c>
-      <c r="B2" s="87" t="s">
-        <v>326</v>
-      </c>
-      <c r="C2" s="88" t="s">
+    <row r="35" spans="1:8" ht="50.1">
+      <c r="A35" s="82" t="s">
+        <v>423</v>
+      </c>
+      <c r="B35" s="83" t="s">
+        <v>381</v>
+      </c>
+      <c r="C35" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="87" t="s">
-        <v>412</v>
-      </c>
-      <c r="E2" s="87" t="s">
-        <v>196</v>
-      </c>
-      <c r="F2" s="88" t="s">
+      <c r="D35" s="83" t="s">
+        <v>424</v>
+      </c>
+      <c r="E35" s="83" t="s">
+        <v>381</v>
+      </c>
+      <c r="F35" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="G2" s="88" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A3" s="89" t="s">
-        <v>459</v>
-      </c>
-      <c r="B3" s="90" t="s">
-        <v>413</v>
-      </c>
-      <c r="C3" s="91">
+      <c r="G35" s="83" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="23.25">
+      <c r="A36" s="85" t="s">
+        <v>425</v>
+      </c>
+      <c r="B36" s="86" t="s">
+        <v>446</v>
+      </c>
+      <c r="C36" s="87">
+        <v>93</v>
+      </c>
+      <c r="D36" s="88">
+        <v>40</v>
+      </c>
+      <c r="E36" s="86" t="s">
+        <v>447</v>
+      </c>
+      <c r="F36" s="87">
+        <v>95</v>
+      </c>
+      <c r="G36" s="88">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="24.95">
+      <c r="A37" s="85" t="s">
+        <v>428</v>
+      </c>
+      <c r="B37" s="88" t="s">
+        <v>448</v>
+      </c>
+      <c r="C37" s="89">
         <v>94</v>
       </c>
-      <c r="D3" s="92">
+      <c r="D37" s="90">
         <v>40</v>
       </c>
-      <c r="E3" s="90" t="s">
-        <v>417</v>
-      </c>
-      <c r="F3" s="91">
-        <v>93</v>
-      </c>
-      <c r="G3" s="92">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A4" s="89" t="s">
-        <v>460</v>
-      </c>
-      <c r="B4" s="92" t="s">
-        <v>411</v>
-      </c>
-      <c r="C4" s="93">
+      <c r="E37" s="88">
+        <v>3000</v>
+      </c>
+      <c r="F37" s="89">
         <v>95</v>
       </c>
-      <c r="D4" s="94">
+      <c r="G37" s="90">
         <v>40</v>
       </c>
-      <c r="E4" s="92" t="s">
-        <v>416</v>
-      </c>
-      <c r="F4" s="93">
-        <v>94</v>
-      </c>
-      <c r="G4" s="94">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A5" s="89" t="s">
-        <v>461</v>
-      </c>
-      <c r="B5" s="95" t="s">
-        <v>217</v>
-      </c>
-      <c r="C5" s="96">
-        <v>94</v>
-      </c>
-      <c r="D5" s="97">
+    </row>
+    <row r="38" spans="1:8" ht="24.95">
+      <c r="A38" s="85" t="s">
+        <v>431</v>
+      </c>
+      <c r="B38" s="91" t="s">
+        <v>449</v>
+      </c>
+      <c r="C38" s="92">
+        <v>79</v>
+      </c>
+      <c r="D38" s="93">
+        <v>62</v>
+      </c>
+      <c r="E38" s="91" t="s">
+        <v>450</v>
+      </c>
+      <c r="F38" s="92">
+        <v>80</v>
+      </c>
+      <c r="G38" s="93">
         <v>60</v>
       </c>
-      <c r="E5" s="95" t="s">
-        <v>418</v>
-      </c>
-      <c r="F5" s="96">
-        <v>91</v>
-      </c>
-      <c r="G5" s="97">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A6" s="98" t="s">
-        <v>236</v>
-      </c>
-      <c r="B6" s="92" t="s">
-        <v>237</v>
-      </c>
-      <c r="C6" s="99">
+      <c r="H38" s="81" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="24.95">
+      <c r="A39" s="94" t="s">
+        <v>272</v>
+      </c>
+      <c r="B39" s="88" t="s">
+        <v>273</v>
+      </c>
+      <c r="C39" s="95">
         <v>99</v>
       </c>
-      <c r="D6" s="100" t="s">
-        <v>238</v>
-      </c>
-      <c r="E6" s="92" t="s">
-        <v>339</v>
-      </c>
-      <c r="F6" s="92">
-        <v>98</v>
-      </c>
-      <c r="G6" s="100" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A7" s="98" t="s">
-        <v>239</v>
-      </c>
-      <c r="B7" s="92" t="s">
-        <v>240</v>
-      </c>
-      <c r="C7" s="101">
+      <c r="D39" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="E39" s="88" t="s">
+        <v>395</v>
+      </c>
+      <c r="F39" s="88">
         <v>99</v>
       </c>
-      <c r="D7" s="100" t="s">
-        <v>238</v>
-      </c>
-      <c r="E7" s="92" t="s">
-        <v>340</v>
-      </c>
-      <c r="F7" s="92">
-        <v>98</v>
-      </c>
-      <c r="G7" s="100" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A8" s="102" t="s">
-        <v>241</v>
-      </c>
-      <c r="B8" s="95" t="s">
-        <v>242</v>
-      </c>
-      <c r="C8" s="96">
+      <c r="G39" s="96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="24.95">
+      <c r="A40" s="94" t="s">
+        <v>275</v>
+      </c>
+      <c r="B40" s="88" t="s">
+        <v>276</v>
+      </c>
+      <c r="C40" s="97">
+        <v>99</v>
+      </c>
+      <c r="D40" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="E40" s="88" t="s">
+        <v>396</v>
+      </c>
+      <c r="F40" s="88">
+        <v>99</v>
+      </c>
+      <c r="G40" s="96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="24.95">
+      <c r="A41" s="98" t="s">
+        <v>277</v>
+      </c>
+      <c r="B41" s="91" t="s">
+        <v>278</v>
+      </c>
+      <c r="C41" s="92">
         <v>90</v>
       </c>
-      <c r="D8" s="97" t="s">
-        <v>238</v>
-      </c>
-      <c r="E8" s="92" t="s">
-        <v>341</v>
-      </c>
-      <c r="F8" s="92">
+      <c r="D41" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="E41" s="88" t="s">
+        <v>397</v>
+      </c>
+      <c r="F41" s="88">
         <v>96</v>
       </c>
-      <c r="G8" s="97" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="89" t="s">
-        <v>268</v>
-      </c>
-      <c r="B9" s="92"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="103" t="s">
-        <v>267</v>
-      </c>
-      <c r="E9" s="92"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="103" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="75" x14ac:dyDescent="0.3">
-      <c r="A12" s="81" t="s">
-        <v>414</v>
-      </c>
-      <c r="B12" s="82" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="84" t="s">
-        <v>194</v>
-      </c>
-      <c r="E12" s="82" t="s">
-        <v>314</v>
-      </c>
-      <c r="F12" s="83"/>
-      <c r="G12" s="84" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="50" x14ac:dyDescent="0.3">
-      <c r="A13" s="86" t="s">
-        <v>410</v>
-      </c>
-      <c r="B13" s="87" t="s">
-        <v>326</v>
-      </c>
-      <c r="C13" s="88" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" s="87" t="s">
-        <v>412</v>
-      </c>
-      <c r="E13" s="87" t="s">
-        <v>196</v>
-      </c>
-      <c r="F13" s="88" t="s">
-        <v>197</v>
-      </c>
-      <c r="G13" s="88" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A14" s="89" t="s">
-        <v>459</v>
-      </c>
-      <c r="B14" s="90" t="s">
-        <v>415</v>
-      </c>
-      <c r="C14" s="91">
-        <v>95</v>
-      </c>
-      <c r="D14" s="92">
-        <v>61</v>
-      </c>
-      <c r="E14" s="90" t="s">
-        <v>417</v>
-      </c>
-      <c r="F14" s="91">
-        <v>93</v>
-      </c>
-      <c r="G14" s="92">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A15" s="89" t="s">
-        <v>460</v>
-      </c>
-      <c r="B15" s="92" t="s">
-        <v>411</v>
-      </c>
-      <c r="C15" s="93">
-        <v>95</v>
-      </c>
-      <c r="D15" s="94">
-        <v>61</v>
-      </c>
-      <c r="E15" s="92" t="s">
-        <v>416</v>
-      </c>
-      <c r="F15" s="93">
-        <v>94</v>
-      </c>
-      <c r="G15" s="94">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="25" x14ac:dyDescent="0.3">
-      <c r="A16" s="89" t="s">
-        <v>461</v>
-      </c>
-      <c r="B16" s="95" t="s">
-        <v>217</v>
-      </c>
-      <c r="C16" s="96">
-        <v>94</v>
-      </c>
-      <c r="D16" s="97">
-        <v>60</v>
-      </c>
-      <c r="E16" s="95" t="s">
-        <v>419</v>
-      </c>
-      <c r="F16" s="96">
-        <v>91</v>
-      </c>
-      <c r="G16" s="97">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A17" s="98" t="s">
-        <v>236</v>
-      </c>
-      <c r="B17" s="92" t="s">
-        <v>237</v>
-      </c>
-      <c r="C17" s="99">
-        <v>99</v>
-      </c>
-      <c r="D17" s="100" t="s">
-        <v>238</v>
-      </c>
-      <c r="E17" s="92" t="s">
-        <v>339</v>
-      </c>
-      <c r="F17" s="92">
-        <v>98</v>
-      </c>
-      <c r="G17" s="100" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A18" s="98" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" s="92" t="s">
-        <v>240</v>
-      </c>
-      <c r="C18" s="101">
-        <v>99</v>
-      </c>
-      <c r="D18" s="100" t="s">
-        <v>238</v>
-      </c>
-      <c r="E18" s="92" t="s">
-        <v>340</v>
-      </c>
-      <c r="F18" s="92">
-        <v>98</v>
-      </c>
-      <c r="G18" s="100" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A19" s="102" t="s">
-        <v>241</v>
-      </c>
-      <c r="B19" s="95" t="s">
-        <v>242</v>
-      </c>
-      <c r="C19" s="96">
-        <v>90</v>
-      </c>
-      <c r="D19" s="97" t="s">
-        <v>238</v>
-      </c>
-      <c r="E19" s="92" t="s">
-        <v>341</v>
-      </c>
-      <c r="F19" s="92">
-        <v>96</v>
-      </c>
-      <c r="G19" s="97" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A20" s="89" t="s">
-        <v>268</v>
-      </c>
-      <c r="B20" s="92"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="103" t="s">
-        <v>267</v>
-      </c>
-      <c r="E20" s="92"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="103" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="75" x14ac:dyDescent="0.3">
-      <c r="A23" s="104" t="s">
-        <v>474</v>
-      </c>
-      <c r="B23" s="82" t="s">
-        <v>193</v>
-      </c>
-      <c r="C23" s="83"/>
-      <c r="D23" s="84" t="s">
-        <v>194</v>
-      </c>
-      <c r="E23" s="82" t="s">
-        <v>314</v>
-      </c>
-      <c r="F23" s="83"/>
-      <c r="G23" s="84" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="50" x14ac:dyDescent="0.3">
-      <c r="A24" s="86" t="s">
-        <v>410</v>
-      </c>
-      <c r="B24" s="87" t="s">
-        <v>326</v>
-      </c>
-      <c r="C24" s="88" t="s">
-        <v>197</v>
-      </c>
-      <c r="D24" s="87" t="s">
-        <v>412</v>
-      </c>
-      <c r="E24" s="87" t="s">
-        <v>326</v>
-      </c>
-      <c r="F24" s="88" t="s">
-        <v>197</v>
-      </c>
-      <c r="G24" s="87" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A25" s="89" t="s">
-        <v>459</v>
-      </c>
-      <c r="B25" s="90" t="s">
-        <v>475</v>
-      </c>
-      <c r="C25" s="91">
-        <v>94</v>
-      </c>
-      <c r="D25" s="92">
-        <v>40</v>
-      </c>
-      <c r="E25" s="90" t="s">
-        <v>417</v>
-      </c>
-      <c r="F25" s="91">
-        <v>93</v>
-      </c>
-      <c r="G25" s="92">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A26" s="89" t="s">
-        <v>460</v>
-      </c>
-      <c r="B26" s="92" t="s">
-        <v>411</v>
-      </c>
-      <c r="C26" s="93">
-        <v>95</v>
-      </c>
-      <c r="D26" s="94">
-        <v>38</v>
-      </c>
-      <c r="E26" s="92" t="s">
-        <v>416</v>
-      </c>
-      <c r="F26" s="93">
-        <v>94</v>
-      </c>
-      <c r="G26" s="94">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A27" s="89" t="s">
-        <v>461</v>
-      </c>
-      <c r="B27" s="95" t="s">
-        <v>476</v>
-      </c>
-      <c r="C27" s="96">
+      <c r="G41" s="93" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="24.95">
+      <c r="A42" s="85" t="s">
+        <v>306</v>
+      </c>
+      <c r="B42" s="91" t="s">
+        <v>318</v>
+      </c>
+      <c r="C42" s="91">
+        <v>80</v>
+      </c>
+      <c r="D42" s="99" t="s">
+        <v>433</v>
+      </c>
+      <c r="E42" s="88" t="s">
+        <v>451</v>
+      </c>
+      <c r="F42" s="88">
         <v>75</v>
       </c>
-      <c r="D27" s="97">
-        <v>56</v>
-      </c>
-      <c r="E27" s="95" t="s">
-        <v>489</v>
-      </c>
-      <c r="F27" s="96">
+      <c r="G42" s="99" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="24.95">
+      <c r="A43" s="101" t="s">
+        <v>452</v>
+      </c>
+      <c r="B43" s="102" t="s">
+        <v>453</v>
+      </c>
+      <c r="C43" s="102">
+        <v>77</v>
+      </c>
+      <c r="D43" s="102">
+        <v>68</v>
+      </c>
+      <c r="E43" s="102" t="s">
+        <v>454</v>
+      </c>
+      <c r="F43" s="102">
         <v>75</v>
       </c>
-      <c r="G27" s="97">
-        <v>59</v>
-      </c>
-      <c r="H27" s="85" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A28" s="98" t="s">
-        <v>236</v>
-      </c>
-      <c r="B28" s="92" t="s">
-        <v>237</v>
-      </c>
-      <c r="C28" s="99">
-        <v>99</v>
-      </c>
-      <c r="D28" s="100" t="s">
-        <v>238</v>
-      </c>
-      <c r="E28" s="92" t="s">
-        <v>339</v>
-      </c>
-      <c r="F28" s="92">
-        <v>98</v>
-      </c>
-      <c r="G28" s="100" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A29" s="98" t="s">
-        <v>239</v>
-      </c>
-      <c r="B29" s="92" t="s">
-        <v>240</v>
-      </c>
-      <c r="C29" s="101">
-        <v>99</v>
-      </c>
-      <c r="D29" s="100" t="s">
-        <v>238</v>
-      </c>
-      <c r="E29" s="92" t="s">
-        <v>340</v>
-      </c>
-      <c r="F29" s="92">
-        <v>98</v>
-      </c>
-      <c r="G29" s="100" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A30" s="102" t="s">
-        <v>241</v>
-      </c>
-      <c r="B30" s="95" t="s">
-        <v>242</v>
-      </c>
-      <c r="C30" s="96">
-        <v>90</v>
-      </c>
-      <c r="D30" s="100" t="s">
-        <v>238</v>
-      </c>
-      <c r="E30" s="92" t="s">
-        <v>341</v>
-      </c>
-      <c r="F30" s="92">
-        <v>96</v>
-      </c>
-      <c r="G30" s="97" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A31" s="89" t="s">
-        <v>268</v>
-      </c>
-      <c r="B31" s="95" t="s">
-        <v>496</v>
-      </c>
-      <c r="C31" s="95">
-        <v>80</v>
-      </c>
-      <c r="D31" s="103" t="s">
-        <v>267</v>
-      </c>
-      <c r="E31" s="92" t="s">
-        <v>480</v>
-      </c>
-      <c r="F31" s="92">
-        <v>77</v>
-      </c>
-      <c r="G31" s="103" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="25" x14ac:dyDescent="0.3">
-      <c r="A32" s="105" t="s">
-        <v>477</v>
-      </c>
-      <c r="B32" s="106" t="s">
-        <v>478</v>
-      </c>
-      <c r="C32" s="106">
-        <v>75</v>
-      </c>
-      <c r="D32" s="106">
-        <v>60</v>
-      </c>
-      <c r="E32" s="106" t="s">
-        <v>490</v>
-      </c>
-      <c r="F32" s="106">
-        <v>62</v>
-      </c>
-      <c r="G32" s="106">
-        <v>60</v>
-      </c>
-      <c r="H32" s="85" t="s">
-        <v>479</v>
+      <c r="G43" s="102">
+        <v>70</v>
+      </c>
+      <c r="H43" s="81" t="s">
+        <v>441</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="E34:F34"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="B12:C12"/>
@@ -8308,369 +8642,369 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8EE6899-576B-F44E-A189-C616F2524B03}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="59.1640625" customWidth="1"/>
-    <col min="2" max="2" width="35.6640625" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
+    <col min="1" max="1" width="59.140625" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="60">
       <c r="A1" s="50" t="s">
-        <v>355</v>
+        <v>455</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>314</v>
+        <v>365</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.95">
       <c r="A2" s="38" t="s">
         <v>195</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="C2" s="40"/>
     </row>
-    <row r="3" spans="1:3" ht="19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="18.95" hidden="1">
       <c r="A3" s="22" t="s">
-        <v>356</v>
+        <v>456</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
-    <row r="4" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="15.95" hidden="1">
       <c r="A4" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="15.95" hidden="1">
       <c r="A5" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="58"/>
     </row>
-    <row r="6" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="15.95" hidden="1">
       <c r="A6" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="15.95" hidden="1">
       <c r="A7" s="2" t="s">
-        <v>427</v>
+        <v>204</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="15.95">
       <c r="A8" s="2" t="s">
-        <v>428</v>
+        <v>206</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>357</v>
+        <v>460</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.95">
       <c r="A9" s="2" t="s">
-        <v>429</v>
+        <v>208</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>359</v>
+        <v>462</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.95" hidden="1">
       <c r="A10" s="2" t="s">
-        <v>430</v>
+        <v>210</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="15.95" hidden="1">
       <c r="A11" s="2" t="s">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="58"/>
     </row>
-    <row r="12" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="15.95" hidden="1">
       <c r="A12" s="2" t="s">
-        <v>432</v>
+        <v>214</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="15.95" hidden="1">
       <c r="A13" s="2" t="s">
-        <v>434</v>
+        <v>218</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="58"/>
     </row>
-    <row r="14" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="15.95" hidden="1">
       <c r="A14" s="2" t="s">
         <v>465</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="15.95" hidden="1">
       <c r="A15" s="2" t="s">
         <v>466</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
-    <row r="16" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="15.95" hidden="1">
       <c r="A16" s="2" t="s">
-        <v>435</v>
+        <v>220</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="15.95" hidden="1">
       <c r="A17" s="2" t="s">
-        <v>436</v>
+        <v>467</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="15.95" hidden="1">
       <c r="A18" s="2" t="s">
-        <v>437</v>
+        <v>468</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="15.95" hidden="1">
       <c r="A19" s="3" t="s">
-        <v>438</v>
+        <v>226</v>
       </c>
       <c r="B19" s="46"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="15.95" hidden="1">
       <c r="A20" s="43" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
     </row>
-    <row r="21" spans="1:3" ht="19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="18.95">
       <c r="A21" s="38" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="60"/>
     </row>
-    <row r="22" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="15.95" hidden="1">
       <c r="A22" s="22" t="s">
-        <v>440</v>
+        <v>231</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="55"/>
     </row>
-    <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="15.95">
       <c r="A23" s="2" t="s">
-        <v>441</v>
+        <v>233</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>361</v>
+        <v>470</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.95" hidden="1">
       <c r="A24" s="2" t="s">
-        <v>442</v>
+        <v>235</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="57"/>
     </row>
-    <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="15.95">
       <c r="A25" s="2" t="s">
-        <v>443</v>
+        <v>237</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>363</v>
+        <v>472</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.95">
       <c r="A26" s="2" t="s">
-        <v>444</v>
+        <v>239</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>365</v>
+        <v>474</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.95" hidden="1">
       <c r="A27" s="2" t="s">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="57"/>
     </row>
-    <row r="28" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="15.95" hidden="1">
       <c r="A28" s="2" t="s">
-        <v>446</v>
+        <v>243</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="57"/>
     </row>
-    <row r="29" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="15.95" hidden="1">
       <c r="A29" s="2" t="s">
-        <v>447</v>
+        <v>245</v>
       </c>
       <c r="B29" s="10"/>
       <c r="C29" s="57"/>
     </row>
-    <row r="30" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="15.95" hidden="1">
       <c r="A30" s="2" t="s">
-        <v>448</v>
+        <v>477</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="57"/>
     </row>
-    <row r="31" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="15.95" hidden="1">
       <c r="A31" s="2" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="57"/>
     </row>
-    <row r="32" spans="1:3" ht="19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="18.95" hidden="1">
       <c r="A32" s="29" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="61"/>
     </row>
-    <row r="33" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="15.95" hidden="1">
       <c r="A33" s="2" t="s">
-        <v>450</v>
+        <v>254</v>
       </c>
       <c r="B33" s="47"/>
       <c r="C33" s="57"/>
     </row>
-    <row r="34" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="15.95" hidden="1">
       <c r="A34" s="2" t="s">
-        <v>451</v>
+        <v>257</v>
       </c>
       <c r="B34" s="47"/>
       <c r="C34" s="57"/>
     </row>
-    <row r="35" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="15.95" hidden="1">
       <c r="A35" s="2" t="s">
-        <v>452</v>
+        <v>258</v>
       </c>
       <c r="B35" s="47"/>
       <c r="C35" s="57"/>
     </row>
-    <row r="36" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="15.95" hidden="1">
       <c r="A36" s="2" t="s">
-        <v>441</v>
+        <v>233</v>
       </c>
       <c r="B36" s="47"/>
       <c r="C36" s="54"/>
     </row>
-    <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="18.95">
       <c r="A37" s="29" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="62"/>
     </row>
-    <row r="38" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="15.95" hidden="1">
       <c r="A38" s="2" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="B38" s="48"/>
       <c r="C38" s="63"/>
     </row>
-    <row r="39" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="15.95" hidden="1">
       <c r="A39" s="2" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="63"/>
     </row>
-    <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="15.95">
       <c r="A40" s="2" t="s">
-        <v>453</v>
+        <v>264</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>367</v>
+        <v>479</v>
       </c>
       <c r="C40" s="59" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15.95">
       <c r="A41" s="2" t="s">
-        <v>454</v>
+        <v>265</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>369</v>
+        <v>481</v>
       </c>
       <c r="C41" s="59" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.95" hidden="1">
       <c r="A42" s="22" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
     </row>
-    <row r="43" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="15.95" hidden="1">
       <c r="A43" s="22" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="B43" s="45"/>
       <c r="C43" s="15"/>
     </row>
-    <row r="44" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="15.95" hidden="1">
       <c r="A44" s="2" t="s">
-        <v>455</v>
+        <v>268</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ht="15.95">
       <c r="A45" s="2" t="s">
-        <v>456</v>
+        <v>269</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>371</v>
+        <v>483</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.95" hidden="1">
       <c r="A46" s="2" t="s">
-        <v>457</v>
+        <v>270</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -8683,124 +9017,124 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA07167-CEB4-F64B-93AF-8A8BA2B4D0FF}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="62.1640625" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.6640625" customWidth="1"/>
+    <col min="1" max="1" width="62.140625" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" customWidth="1"/>
+    <col min="3" max="3" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="81" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="81">
       <c r="A1" s="75" t="s">
-        <v>373</v>
+        <v>485</v>
       </c>
       <c r="B1" s="76" t="s">
-        <v>374</v>
+        <v>486</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="21.95">
       <c r="A2" s="73" t="s">
+        <v>488</v>
+      </c>
+      <c r="B2" s="74" t="s">
+        <v>489</v>
+      </c>
+      <c r="C2" s="74" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="21.95">
+      <c r="A3" s="73" t="s">
+        <v>491</v>
+      </c>
+      <c r="B3" s="74" t="s">
+        <v>492</v>
+      </c>
+      <c r="C3" s="74" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="21.95">
+      <c r="A4" s="73" t="s">
+        <v>493</v>
+      </c>
+      <c r="B4" s="78" t="s">
+        <v>494</v>
+      </c>
+      <c r="C4" s="78" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="21.95">
+      <c r="A5" s="73" t="s">
+        <v>495</v>
+      </c>
+      <c r="B5" s="78" t="s">
+        <v>494</v>
+      </c>
+      <c r="C5" s="78" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="21.95">
+      <c r="A6" s="73" t="s">
+        <v>496</v>
+      </c>
+      <c r="B6" s="74" t="s">
+        <v>497</v>
+      </c>
+      <c r="C6" s="74" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="21.95">
+      <c r="A7" s="73" t="s">
+        <v>499</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>500</v>
+      </c>
+      <c r="C7" s="74" t="s">
+        <v>501</v>
+      </c>
+      <c r="D7" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="21.95">
+      <c r="A8" s="73" t="s">
+        <v>503</v>
+      </c>
+      <c r="B8" s="74" t="s">
         <v>376</v>
       </c>
-      <c r="B2" s="74" t="s">
-        <v>377</v>
-      </c>
-      <c r="C2" s="74" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A3" s="73" t="s">
-        <v>379</v>
-      </c>
-      <c r="B3" s="74" t="s">
-        <v>380</v>
-      </c>
-      <c r="C3" s="74" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
-        <v>381</v>
-      </c>
-      <c r="B4" s="78" t="s">
-        <v>382</v>
-      </c>
-      <c r="C4" s="78" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A5" s="73" t="s">
-        <v>383</v>
-      </c>
-      <c r="B5" s="78" t="s">
-        <v>382</v>
-      </c>
-      <c r="C5" s="78" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
-        <v>384</v>
-      </c>
-      <c r="B6" s="74" t="s">
-        <v>385</v>
-      </c>
-      <c r="C6" s="74" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A7" s="73" t="s">
-        <v>387</v>
-      </c>
-      <c r="B7" s="74" t="s">
-        <v>388</v>
-      </c>
-      <c r="C7" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="D7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="22" x14ac:dyDescent="0.25">
-      <c r="A8" s="73" t="s">
-        <v>391</v>
-      </c>
-      <c r="B8" s="74" t="s">
-        <v>323</v>
-      </c>
       <c r="C8" s="74" t="s">
-        <v>392</v>
+        <v>504</v>
       </c>
       <c r="D8" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="21.95">
       <c r="A9" s="73" t="s">
-        <v>394</v>
+        <v>506</v>
       </c>
       <c r="B9" s="74" t="s">
-        <v>395</v>
+        <v>507</v>
       </c>
       <c r="C9" s="74" t="s">
-        <v>396</v>
+        <v>508</v>
       </c>
       <c r="D9" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="21.95">
       <c r="A10" s="73" t="s">
-        <v>398</v>
+        <v>510</v>
       </c>
       <c r="B10" s="74">
         <v>26000</v>
@@ -8809,9 +9143,9 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="21.95">
       <c r="A11" s="73" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="B11" s="74">
         <v>445</v>
@@ -8820,9 +9154,9 @@
         <v>371</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="21.95">
       <c r="A12" s="73" t="s">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="B12" s="74">
         <v>96000</v>
@@ -8831,9 +9165,9 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="21.95">
       <c r="A13" s="73" t="s">
-        <v>401</v>
+        <v>513</v>
       </c>
       <c r="B13" s="74">
         <v>400000</v>
@@ -8842,9 +9176,9 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="21.95">
       <c r="A14" s="73" t="s">
-        <v>402</v>
+        <v>514</v>
       </c>
       <c r="B14" s="74">
         <v>200000</v>
@@ -8859,6 +9193,118 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cb645b5b-9a36-43da-96bf-ab72ec91ddff" xsi:nil="true"/>
+    <SharedWithUsers xmlns="0b7692b1-2532-40e4-a300-4d7fced4a07a">
+      <UserInfo>
+        <DisplayName>Anand Thulasiram</DisplayName>
+        <AccountId>2178</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Vipin Kumar</DisplayName>
+        <AccountId>64</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sunil  Masineni</DisplayName>
+        <AccountId>5184</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Geetha B K</DisplayName>
+        <AccountId>63</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jagadeesh Rajashekharaiah</DisplayName>
+        <AccountId>13</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Deepasri Chittala</DisplayName>
+        <AccountId>4801</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Weibin Chen</DisplayName>
+        <AccountId>317</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Xiaochen Tang</DisplayName>
+        <AccountId>910</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Anand Antur</DisplayName>
+        <AccountId>670</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Venu Maya</DisplayName>
+        <AccountId>33</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Chockalingam Balasubramanian</DisplayName>
+        <AccountId>682</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Neetu Rathee</DisplayName>
+        <AccountId>4709</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Prasad Shroff</DisplayName>
+        <AccountId>4142</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kedar Dhuru</DisplayName>
+        <AccountId>3907</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sarvesh Batta</DisplayName>
+        <AccountId>21</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Shankar Satyamurthy</DisplayName>
+        <AccountId>3116</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>David Passamonte</DisplayName>
+        <AccountId>5189</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010092711BC64AAEC84E9EF800276F1AD52C" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba397f1440615f1339f1f20b24e67478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9bf4d24f-a117-48f7-91e1-2035a8c734fd" xmlns:ns3="0b7692b1-2532-40e4-a300-4d7fced4a07a" xmlns:ns4="cb645b5b-9a36-43da-96bf-ab72ec91ddff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74828cee37efa74eab9b700f6a6651cc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
@@ -9106,168 +9552,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cb645b5b-9a36-43da-96bf-ab72ec91ddff" xsi:nil="true"/>
-    <SharedWithUsers xmlns="0b7692b1-2532-40e4-a300-4d7fced4a07a">
-      <UserInfo>
-        <DisplayName>Anand Thulasiram</DisplayName>
-        <AccountId>2178</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Vipin Kumar</DisplayName>
-        <AccountId>64</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sunil  Masineni</DisplayName>
-        <AccountId>5184</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Geetha B K</DisplayName>
-        <AccountId>63</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jagadeesh Rajashekharaiah</DisplayName>
-        <AccountId>13</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Deepasri Chittala</DisplayName>
-        <AccountId>4801</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Weibin Chen</DisplayName>
-        <AccountId>317</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Xiaochen Tang</DisplayName>
-        <AccountId>910</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Anand Antur</DisplayName>
-        <AccountId>670</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Venu Maya</DisplayName>
-        <AccountId>33</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Chockalingam Balasubramanian</DisplayName>
-        <AccountId>682</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Neetu Rathee</DisplayName>
-        <AccountId>4709</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Prasad Shroff</DisplayName>
-        <AccountId>4142</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kedar Dhuru</DisplayName>
-        <AccountId>3907</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sarvesh Batta</DisplayName>
-        <AccountId>21</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Shankar Satyamurthy</DisplayName>
-        <AccountId>3116</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>David Passamonte</DisplayName>
-        <AccountId>5189</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
-    <ds:schemaRef ds:uri="0b7692b1-2532-40e4-a300-4d7fced4a07a"/>
-    <ds:schemaRef ds:uri="cb645b5b-9a36-43da-96bf-ab72ec91ddff"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="cb645b5b-9a36-43da-96bf-ab72ec91ddff"/>
-    <ds:schemaRef ds:uri="0b7692b1-2532-40e4-a300-4d7fced4a07a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
 </file>
--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1023" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3FC1C92-17E6-495D-84E3-3D79CA451DA0}"/>
+  <xr:revisionPtr revIDLastSave="1038" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7558ED8-9BDD-4EEE-BA08-1951C09F4E01}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="36000" windowHeight="19740" firstSheet="2" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="19740" firstSheet="1" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ISSUES-PR''s'!$A$1:$I$224</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SRX440'!$A$1:$F$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SRX440'!$A$1:$F$100</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="471">
   <si>
     <t>number</t>
   </si>
@@ -948,9 +948,6 @@
     <t>Max IPSec VPN Tunnels supported</t>
   </si>
   <si>
-    <t>Juniper Secure Connect Scale</t>
-  </si>
-  <si>
     <t>Max GRE supported Tunnels</t>
   </si>
   <si>
@@ -991,9 +988,6 @@
   </si>
   <si>
     <t>MAX IDP(Rec policy) Sessions capacity</t>
-  </si>
-  <si>
-    <t>80K</t>
   </si>
   <si>
     <t>Max UTM-EWF Sessions capacity</t>
@@ -1229,13 +1223,10 @@
     <t>Max UTM- NG-WF Sessions capacity</t>
   </si>
   <si>
-    <t>8k</t>
-  </si>
-  <si>
-    <t>255 seconds</t>
-  </si>
-  <si>
-    <t>7 seconds</t>
+    <t>255 sec</t>
+  </si>
+  <si>
+    <t>7 sec</t>
   </si>
   <si>
     <r>
@@ -1305,7 +1296,6 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Release: 25.4X300-202605180407.0-EVO
@@ -1317,7 +1307,6 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -1375,6 +1364,9 @@
   </si>
   <si>
     <t>350 CPS</t>
+  </si>
+  <si>
+    <t>Release: 25.4X300-D10.2-EVO</t>
   </si>
   <si>
     <t>1650 CPS / 926 Mbps</t>
@@ -1634,7 +1626,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1826,6 +1818,21 @@
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2092,7 +2099,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2388,11 +2395,8 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -8854,7 +8858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC397FCC-74C1-4D09-ACC0-E463BF5527EB}">
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="87.85546875" customWidth="1"/>
@@ -9990,77 +9994,77 @@
       <c r="A81" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B81" s="33"/>
-      <c r="C81" s="23"/>
+      <c r="B81" s="24">
+        <v>1750</v>
+      </c>
+      <c r="C81" s="32"/>
       <c r="D81" s="56"/>
     </row>
     <row r="82" spans="1:4" ht="15.95">
       <c r="A82" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B82" s="24">
-        <v>1750</v>
-      </c>
-      <c r="C82" s="32"/>
+      <c r="B82" s="33"/>
+      <c r="C82" s="23"/>
       <c r="D82" s="56"/>
     </row>
     <row r="83" spans="1:4" ht="15.95">
       <c r="A83" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B83" s="33"/>
-      <c r="C83" s="23"/>
+      <c r="B83" s="24"/>
+      <c r="C83" s="10"/>
       <c r="D83" s="56"/>
     </row>
     <row r="84" spans="1:4" ht="15.95">
       <c r="A84" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B84" s="24"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="56"/>
+      <c r="B84" s="24">
+        <v>128</v>
+      </c>
+      <c r="C84" s="10">
+        <v>10</v>
+      </c>
+      <c r="D84" s="56">
+        <v>77</v>
+      </c>
     </row>
     <row r="85" spans="1:4" ht="15.95">
       <c r="A85" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B85" s="24">
-        <v>128</v>
+      <c r="B85" s="10" t="s">
+        <v>297</v>
       </c>
       <c r="C85" s="10">
         <v>10</v>
       </c>
-      <c r="D85" s="56">
-        <v>77</v>
+      <c r="D85" s="51">
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.95">
       <c r="A86" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C86" s="10">
         <v>10</v>
       </c>
-      <c r="D86" s="51">
+      <c r="D86" s="56">
         <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.95">
       <c r="A87" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B87" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C87" s="10">
-        <v>10</v>
-      </c>
-      <c r="D87" s="56">
-        <v>85</v>
-      </c>
+      <c r="B87" s="24"/>
+      <c r="C87" s="10"/>
+      <c r="D87" s="56"/>
     </row>
     <row r="88" spans="1:4" ht="15.95">
       <c r="A88" s="2" t="s">
@@ -10082,139 +10086,145 @@
       <c r="A90" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B90" s="24"/>
-      <c r="C90" s="10"/>
-      <c r="D90" s="56"/>
+      <c r="B90" s="10">
+        <v>80000</v>
+      </c>
+      <c r="C90" s="10">
+        <v>55</v>
+      </c>
+      <c r="D90" s="56">
+        <v>35</v>
+      </c>
     </row>
     <row r="91" spans="1:4" ht="15.95">
       <c r="A91" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="24">
         <v>80000</v>
       </c>
       <c r="C91" s="10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D91" s="56">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.95">
       <c r="A92" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B92" s="24">
+      <c r="B92" s="51">
         <v>80000</v>
       </c>
-      <c r="C92" s="10">
-        <v>60</v>
-      </c>
-      <c r="D92" s="56">
-        <v>37</v>
-      </c>
+      <c r="C92" s="56"/>
+      <c r="D92" s="67"/>
     </row>
     <row r="93" spans="1:4" ht="15.95">
       <c r="A93" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B93" s="51" t="s">
-        <v>307</v>
-      </c>
-      <c r="C93" s="56"/>
-      <c r="D93" s="67"/>
+      <c r="B93" s="24">
+        <v>80000</v>
+      </c>
+      <c r="C93" s="5">
+        <v>56</v>
+      </c>
+      <c r="D93" s="55">
+        <v>40</v>
+      </c>
     </row>
     <row r="94" spans="1:4" ht="15.95">
       <c r="A94" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B94" s="24">
+        <v>32000</v>
+      </c>
+      <c r="C94" s="26">
+        <v>57</v>
+      </c>
+      <c r="D94" s="55">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15.95">
+      <c r="A95" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="B94" s="24">
-        <v>80000</v>
-      </c>
-      <c r="C94" s="5">
-        <v>56</v>
-      </c>
-      <c r="D94" s="55">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="15.95">
-      <c r="A95" s="2" t="s">
+      <c r="B95" s="34">
+        <v>8000</v>
+      </c>
+      <c r="C95" s="35">
+        <v>74</v>
+      </c>
+      <c r="D95" s="10">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15.95">
+      <c r="A96" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B95" s="24">
-        <v>32000</v>
-      </c>
-      <c r="C95" s="26">
-        <v>57</v>
-      </c>
-      <c r="D95" s="55">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="15.95">
-      <c r="A96" s="8" t="s">
+      <c r="B96" s="68">
+        <v>26000</v>
+      </c>
+      <c r="C96" s="66"/>
+      <c r="D96" s="66" t="s">
         <v>310</v>
-      </c>
-      <c r="B96" s="34">
-        <v>8000</v>
-      </c>
-      <c r="C96" s="35">
-        <v>74</v>
-      </c>
-      <c r="D96" s="10">
-        <v>48</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15.95">
       <c r="A97" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B97" s="68">
-        <v>26000</v>
-      </c>
-      <c r="C97" s="66"/>
-      <c r="D97" s="66" t="s">
-        <v>312</v>
+      <c r="B97" s="24">
+        <v>1000</v>
+      </c>
+      <c r="C97" s="24">
+        <v>99</v>
+      </c>
+      <c r="D97" s="24">
+        <v>57</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15.95">
       <c r="A98" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B98" s="24">
-        <v>1000</v>
-      </c>
-      <c r="C98" s="24">
+        <v>300</v>
+      </c>
+      <c r="C98" s="10">
         <v>99</v>
       </c>
-      <c r="D98" s="24">
-        <v>57</v>
+      <c r="D98" s="10">
+        <v>69</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15.95">
       <c r="A99" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B99" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="B99" s="24">
-        <v>300</v>
-      </c>
-      <c r="C99" s="10">
-        <v>99</v>
+      <c r="C99" s="10" t="s">
+        <v>315</v>
       </c>
       <c r="D99" s="10">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15.95">
       <c r="A100" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C100" s="10" t="s">
         <v>315</v>
-      </c>
-      <c r="B100" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>317</v>
       </c>
       <c r="D100" s="10">
         <v>75</v>
@@ -10224,29 +10234,19 @@
       <c r="A101" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B101" s="10" t="s">
-        <v>319</v>
+      <c r="B101" s="24">
+        <v>10</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D101" s="10">
         <v>75</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.95">
-      <c r="A102" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B102" s="24">
-        <v>10</v>
-      </c>
-      <c r="C102" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="D102" s="10">
-        <v>75</v>
-      </c>
+    <row r="102" spans="1:9" ht="15" customHeight="1">
+      <c r="H102" s="11"/>
+      <c r="I102" s="11"/>
     </row>
     <row r="103" spans="1:9" ht="15" customHeight="1">
       <c r="H103" s="11"/>
@@ -10259,10 +10259,6 @@
     <row r="105" spans="1:9" ht="15" customHeight="1">
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
-    </row>
-    <row r="106" spans="1:9" ht="15" customHeight="1">
-      <c r="H106" s="11"/>
-      <c r="I106" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10274,7 +10270,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A7BD36-8D88-3742-A4AC-48B0AFB67141}">
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="85.140625" customWidth="1"/>
@@ -10287,10 +10283,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1">
       <c r="A1" s="50" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B1" s="101" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C1" s="102"/>
       <c r="D1" s="36" t="s">
@@ -10316,7 +10312,7 @@
         <v>153</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C3" s="57">
         <v>91</v>
@@ -10330,7 +10326,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C4" s="4">
         <v>70</v>
@@ -10339,7 +10335,7 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" customHeight="1">
@@ -10347,7 +10343,7 @@
         <v>158</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C5" s="4">
         <v>92</v>
@@ -10361,7 +10357,7 @@
         <v>160</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C6" s="4">
         <v>94</v>
@@ -10375,7 +10371,7 @@
         <v>162</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C7" s="57">
         <v>96</v>
@@ -10389,7 +10385,7 @@
         <v>164</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C8" s="4">
         <v>90</v>
@@ -10403,7 +10399,7 @@
         <v>166</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C9" s="57">
         <v>90</v>
@@ -10417,7 +10413,7 @@
         <v>168</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C10" s="4">
         <v>90</v>
@@ -10431,7 +10427,7 @@
         <v>170</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C11" s="4">
         <v>92</v>
@@ -10459,7 +10455,7 @@
         <v>174</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C13" s="4">
         <v>90</v>
@@ -10473,7 +10469,7 @@
         <v>176</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C14" s="4">
         <v>90</v>
@@ -10487,7 +10483,7 @@
         <v>178</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C15" s="4">
         <v>94</v>
@@ -10501,7 +10497,7 @@
         <v>180</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C16" s="4">
         <v>92</v>
@@ -10515,7 +10511,7 @@
         <v>182</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C17" s="7">
         <v>92</v>
@@ -10529,7 +10525,7 @@
         <v>184</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>151</v>
@@ -10543,7 +10539,7 @@
         <v>185</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C19" s="54">
         <v>92</v>
@@ -10557,7 +10553,7 @@
         <v>187</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C20" s="56">
         <v>95</v>
@@ -10571,7 +10567,7 @@
         <v>189</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C21" s="56">
         <v>95</v>
@@ -10585,7 +10581,7 @@
         <v>191</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C22" s="56">
         <v>93</v>
@@ -10599,7 +10595,7 @@
         <v>193</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C23" s="56">
         <v>92</v>
@@ -10613,7 +10609,7 @@
         <v>195</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C24" s="56">
         <v>92</v>
@@ -10622,7 +10618,7 @@
         <v>67</v>
       </c>
       <c r="F24" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.95">
@@ -10630,7 +10626,7 @@
         <v>197</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C25" s="56">
         <v>92</v>
@@ -10644,7 +10640,7 @@
         <v>199</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C26" s="56">
         <v>90</v>
@@ -10658,7 +10654,7 @@
         <v>201</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C27" s="56">
         <v>90</v>
@@ -10672,7 +10668,7 @@
         <v>203</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C28" s="56">
         <v>92</v>
@@ -10686,7 +10682,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>151</v>
@@ -10751,7 +10747,7 @@
         <v>187</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C33" s="56">
         <v>92</v>
@@ -10765,7 +10761,7 @@
         <v>214</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C34" s="40" t="s">
         <v>151</v>
@@ -10779,7 +10775,7 @@
         <v>215</v>
       </c>
       <c r="B35" s="48" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C35" s="62">
         <v>90</v>
@@ -10974,7 +10970,7 @@
         <v>225</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>151</v>
@@ -10988,7 +10984,7 @@
         <v>226</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C45" s="24">
         <v>98</v>
@@ -11002,7 +10998,7 @@
         <v>229</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C46" s="24">
         <v>98</v>
@@ -11016,7 +11012,7 @@
         <v>231</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C47" s="56">
         <v>96</v>
@@ -11030,7 +11026,7 @@
         <v>233</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C48" s="56">
         <v>96</v>
@@ -11044,7 +11040,7 @@
         <v>236</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C49" s="23">
         <v>50</v>
@@ -11056,7 +11052,7 @@
         <v>238</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C50" s="54">
         <v>98</v>
@@ -11070,7 +11066,7 @@
         <v>240</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C51" s="56">
         <v>98</v>
@@ -11084,7 +11080,7 @@
         <v>242</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C52" s="56">
         <v>99</v>
@@ -11098,7 +11094,7 @@
         <v>244</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C53" s="63">
         <v>99</v>
@@ -11112,7 +11108,7 @@
         <v>246</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C54" s="64">
         <v>98</v>
@@ -11126,7 +11122,7 @@
         <v>249</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C55" s="64">
         <v>98</v>
@@ -11140,7 +11136,7 @@
         <v>252</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C56" s="64">
         <v>96</v>
@@ -11154,7 +11150,7 @@
         <v>255</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C57" s="56">
         <v>96</v>
@@ -11168,7 +11164,7 @@
         <v>257</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C58" s="54">
         <v>78</v>
@@ -11182,7 +11178,7 @@
         <v>260</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C59" s="56">
         <v>77</v>
@@ -11196,7 +11192,7 @@
         <v>262</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C60" s="56">
         <v>79</v>
@@ -11210,7 +11206,7 @@
         <v>264</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C61" s="56">
         <v>72</v>
@@ -11224,7 +11220,7 @@
         <v>266</v>
       </c>
       <c r="B62" s="32" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C62" s="56">
         <v>88</v>
@@ -11238,7 +11234,7 @@
         <v>269</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C63" s="56">
         <v>50</v>
@@ -11250,7 +11246,7 @@
         <v>271</v>
       </c>
       <c r="B64" s="52" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C64" s="56">
         <v>79</v>
@@ -11264,7 +11260,7 @@
         <v>274</v>
       </c>
       <c r="B65" s="51" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C65" s="56"/>
       <c r="D65" s="57"/>
@@ -11280,7 +11276,7 @@
         <v>151</v>
       </c>
       <c r="D66" s="65" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.95">
@@ -11407,7 +11403,7 @@
       <c r="A76" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="66">
         <v>1024</v>
       </c>
       <c r="C76" s="56">
@@ -11424,8 +11420,12 @@
       <c r="B77" s="10">
         <v>1536</v>
       </c>
-      <c r="C77" s="56"/>
-      <c r="D77" s="56"/>
+      <c r="C77" s="56">
+        <v>10</v>
+      </c>
+      <c r="D77" s="56">
+        <v>77</v>
+      </c>
     </row>
     <row r="78" spans="1:4" ht="15.95">
       <c r="A78" s="2" t="s">
@@ -11455,7 +11455,9 @@
       <c r="A80" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B80" s="23"/>
+      <c r="B80" s="32">
+        <v>2000</v>
+      </c>
       <c r="C80" s="56"/>
       <c r="D80" s="56"/>
     </row>
@@ -11463,9 +11465,7 @@
       <c r="A81" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B81" s="32">
-        <v>2000</v>
-      </c>
+      <c r="B81" s="23"/>
       <c r="C81" s="56"/>
       <c r="D81" s="56"/>
     </row>
@@ -11473,7 +11473,7 @@
       <c r="A82" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B82" s="23"/>
+      <c r="B82" s="10"/>
       <c r="C82" s="56"/>
       <c r="D82" s="56"/>
     </row>
@@ -11481,30 +11481,36 @@
       <c r="A83" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B83" s="10"/>
-      <c r="C83" s="56"/>
-      <c r="D83" s="56"/>
+      <c r="B83" s="10">
+        <v>128</v>
+      </c>
+      <c r="C83" s="56">
+        <v>10</v>
+      </c>
+      <c r="D83" s="56">
+        <v>96</v>
+      </c>
     </row>
     <row r="84" spans="1:4" ht="15.95">
       <c r="A84" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B84" s="10">
-        <v>128</v>
-      </c>
-      <c r="C84" s="56">
+      <c r="B84" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="C84" s="10">
         <v>10</v>
       </c>
-      <c r="D84" s="56">
-        <v>96</v>
+      <c r="D84" s="10">
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.95">
       <c r="A85" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C85" s="10">
         <v>10</v>
@@ -11515,17 +11521,11 @@
     </row>
     <row r="86" spans="1:4" ht="15.95">
       <c r="A86" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B86" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="C86" s="10">
-        <v>10</v>
-      </c>
-      <c r="D86" s="10">
-        <v>84</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="B86" s="10"/>
+      <c r="C86" s="56"/>
+      <c r="D86" s="56"/>
     </row>
     <row r="87" spans="1:4" ht="15.95">
       <c r="A87" s="2" t="s">
@@ -11547,9 +11547,15 @@
       <c r="A89" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B89" s="10"/>
-      <c r="C89" s="56"/>
-      <c r="D89" s="56"/>
+      <c r="B89" s="10">
+        <v>96000</v>
+      </c>
+      <c r="C89" s="56">
+        <v>50</v>
+      </c>
+      <c r="D89" s="56">
+        <v>35</v>
+      </c>
     </row>
     <row r="90" spans="1:4" ht="15.95">
       <c r="A90" s="2" t="s">
@@ -11559,7 +11565,7 @@
         <v>96000</v>
       </c>
       <c r="C90" s="56">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D90" s="56">
         <v>35</v>
@@ -11569,112 +11575,108 @@
       <c r="A91" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="51">
         <v>96000</v>
       </c>
-      <c r="C91" s="56">
-        <v>55</v>
-      </c>
+      <c r="C91" s="56"/>
       <c r="D91" s="56">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.95">
       <c r="A92" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B92" s="51">
-        <v>96000</v>
-      </c>
-      <c r="C92" s="56"/>
-      <c r="D92" s="106">
+        <v>374</v>
+      </c>
+      <c r="B92" s="26">
+        <v>48000</v>
+      </c>
+      <c r="C92" s="55"/>
+      <c r="D92" s="56">
         <v>41</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" ht="15.95">
       <c r="A93" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B93" s="105">
+        <v>375</v>
+      </c>
+      <c r="B93" s="26">
         <v>48000</v>
       </c>
       <c r="C93" s="55"/>
-      <c r="D93" s="106">
+      <c r="D93" s="56">
         <v>41</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.95">
-      <c r="A94" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B94" s="26">
-        <v>48000</v>
-      </c>
-      <c r="C94" s="55"/>
+      <c r="A94" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B94" s="35">
+        <v>8000</v>
+      </c>
+      <c r="C94" s="10">
+        <v>99</v>
+      </c>
       <c r="D94" s="56">
         <v>41</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.95">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B95" s="68">
+        <v>26000</v>
+      </c>
+      <c r="C95" s="66"/>
+      <c r="D95" s="66" t="s">
         <v>310</v>
       </c>
-      <c r="B95" s="35" t="s">
-        <v>378</v>
-      </c>
-      <c r="C95" s="10">
-        <v>99</v>
-      </c>
-      <c r="D95" s="56">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+    </row>
+    <row r="96" spans="1:4" ht="15.95">
       <c r="A96" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B96" s="68">
-        <v>26000</v>
-      </c>
-      <c r="C96" s="66"/>
-      <c r="D96" s="66" t="s">
-        <v>312</v>
+      <c r="B96" s="10">
+        <v>1200</v>
+      </c>
+      <c r="C96" s="10">
+        <v>97</v>
+      </c>
+      <c r="D96" s="56">
+        <v>55</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15.95">
       <c r="A97" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B97" s="10">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="C97" s="10">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D97" s="56">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15.95">
       <c r="A98" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B98" s="10">
-        <v>500</v>
-      </c>
-      <c r="C98" s="10">
-        <v>99</v>
-      </c>
-      <c r="D98" s="56">
-        <v>41</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="C98" s="10"/>
+      <c r="D98" s="56"/>
     </row>
     <row r="99" spans="1:9" ht="15.95">
       <c r="A99" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="56"/>
@@ -11683,21 +11685,15 @@
       <c r="A100" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B100" s="10" t="s">
-        <v>380</v>
+      <c r="B100" s="10">
+        <v>10</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="56"/>
     </row>
-    <row r="101" spans="1:9" ht="15.95">
-      <c r="A101" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B101" s="10">
-        <v>10</v>
-      </c>
-      <c r="C101" s="10"/>
-      <c r="D101" s="56"/>
+    <row r="101" spans="1:9" ht="15" customHeight="1">
+      <c r="H101" s="11"/>
+      <c r="I101" s="11"/>
     </row>
     <row r="102" spans="1:9" ht="15" customHeight="1">
       <c r="H102" s="11"/>
@@ -11711,12 +11707,8 @@
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" ht="15" customHeight="1">
-      <c r="H105" s="11"/>
-      <c r="I105" s="11"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F101" xr:uid="{63A7BD36-8D88-3742-A4AC-48B0AFB67141}"/>
+  <autoFilter ref="A1:F100" xr:uid="{63A7BD36-8D88-3742-A4AC-48B0AFB67141}"/>
   <mergeCells count="1">
     <mergeCell ref="B1:C1"/>
   </mergeCells>
@@ -11741,7 +11733,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="75">
       <c r="A1" s="75" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B1" s="103" t="s">
         <v>147</v>
@@ -11751,7 +11743,7 @@
         <v>148</v>
       </c>
       <c r="E1" s="103" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F1" s="104"/>
       <c r="G1" s="76" t="s">
@@ -11760,16 +11752,16 @@
     </row>
     <row r="2" spans="1:7" ht="50.1">
       <c r="A2" s="78" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C2" s="80" t="s">
         <v>151</v>
       </c>
       <c r="D2" s="79" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E2" s="79" t="s">
         <v>150</v>
@@ -11783,10 +11775,10 @@
     </row>
     <row r="3" spans="1:7" ht="24.95">
       <c r="A3" s="81" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B3" s="82" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C3" s="83">
         <v>94</v>
@@ -11795,7 +11787,7 @@
         <v>40</v>
       </c>
       <c r="E3" s="82" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F3" s="83">
         <v>93</v>
@@ -11806,10 +11798,10 @@
     </row>
     <row r="4" spans="1:7" ht="24.95">
       <c r="A4" s="81" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B4" s="84" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C4" s="85">
         <v>95</v>
@@ -11818,7 +11810,7 @@
         <v>40</v>
       </c>
       <c r="E4" s="84" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F4" s="85">
         <v>94</v>
@@ -11829,7 +11821,7 @@
     </row>
     <row r="5" spans="1:7" ht="24.95">
       <c r="A5" s="81" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B5" s="87" t="s">
         <v>188</v>
@@ -11841,7 +11833,7 @@
         <v>60</v>
       </c>
       <c r="E5" s="87" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F5" s="88">
         <v>91</v>
@@ -11864,7 +11856,7 @@
         <v>228</v>
       </c>
       <c r="E6" s="84" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F6" s="84">
         <v>98</v>
@@ -11887,7 +11879,7 @@
         <v>228</v>
       </c>
       <c r="E7" s="84" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F7" s="84">
         <v>98</v>
@@ -11910,7 +11902,7 @@
         <v>228</v>
       </c>
       <c r="E8" s="84" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F8" s="84">
         <v>96</v>
@@ -11926,17 +11918,17 @@
       <c r="B9" s="84"/>
       <c r="C9" s="88"/>
       <c r="D9" s="95" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E9" s="84"/>
       <c r="F9" s="88"/>
       <c r="G9" s="95" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="75">
-      <c r="A12" s="75" t="s">
-        <v>393</v>
+        <v>389</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="70.5">
+      <c r="A12" s="105" t="s">
+        <v>390</v>
       </c>
       <c r="B12" s="103" t="s">
         <v>147</v>
@@ -11946,7 +11938,7 @@
         <v>148</v>
       </c>
       <c r="E12" s="103" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F12" s="104"/>
       <c r="G12" s="76" t="s">
@@ -11955,16 +11947,16 @@
     </row>
     <row r="13" spans="1:7" ht="50.1">
       <c r="A13" s="78" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B13" s="79" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C13" s="80" t="s">
         <v>151</v>
       </c>
       <c r="D13" s="79" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E13" s="79" t="s">
         <v>150</v>
@@ -11978,10 +11970,10 @@
     </row>
     <row r="14" spans="1:7" ht="24.95">
       <c r="A14" s="81" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B14" s="82" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C14" s="83">
         <v>95</v>
@@ -11990,7 +11982,7 @@
         <v>61</v>
       </c>
       <c r="E14" s="82" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F14" s="83">
         <v>93</v>
@@ -12001,10 +11993,10 @@
     </row>
     <row r="15" spans="1:7" ht="24.95">
       <c r="A15" s="81" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B15" s="84" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C15" s="85">
         <v>95</v>
@@ -12013,7 +12005,7 @@
         <v>61</v>
       </c>
       <c r="E15" s="84" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F15" s="85">
         <v>94</v>
@@ -12024,7 +12016,7 @@
     </row>
     <row r="16" spans="1:7" ht="24.95">
       <c r="A16" s="81" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B16" s="87" t="s">
         <v>188</v>
@@ -12036,7 +12028,7 @@
         <v>60</v>
       </c>
       <c r="E16" s="87" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="F16" s="88">
         <v>91</v>
@@ -12059,7 +12051,7 @@
         <v>228</v>
       </c>
       <c r="E17" s="84" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F17" s="84">
         <v>98</v>
@@ -12082,7 +12074,7 @@
         <v>228</v>
       </c>
       <c r="E18" s="84" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F18" s="84">
         <v>98</v>
@@ -12105,7 +12097,7 @@
         <v>228</v>
       </c>
       <c r="E19" s="84" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F19" s="84">
         <v>96</v>
@@ -12121,17 +12113,17 @@
       <c r="B20" s="84"/>
       <c r="C20" s="88"/>
       <c r="D20" s="95" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E20" s="84"/>
       <c r="F20" s="88"/>
       <c r="G20" s="95" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="75">
       <c r="A23" s="96" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B23" s="103" t="s">
         <v>147</v>
@@ -12141,7 +12133,7 @@
         <v>148</v>
       </c>
       <c r="E23" s="103" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F23" s="104"/>
       <c r="G23" s="76" t="s">
@@ -12150,25 +12142,25 @@
     </row>
     <row r="24" spans="1:9" ht="50.1">
       <c r="A24" s="78" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B24" s="79" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C24" s="80" t="s">
         <v>151</v>
       </c>
       <c r="D24" s="79" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E24" s="79" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F24" s="80" t="s">
         <v>151</v>
       </c>
       <c r="G24" s="79" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I24" s="77">
         <v>280000</v>
@@ -12176,10 +12168,10 @@
     </row>
     <row r="25" spans="1:9" ht="24.95">
       <c r="A25" s="81" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B25" s="82" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C25" s="83">
         <v>94</v>
@@ -12188,7 +12180,7 @@
         <v>40</v>
       </c>
       <c r="E25" s="82" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F25" s="83">
         <v>93</v>
@@ -12203,10 +12195,10 @@
     </row>
     <row r="26" spans="1:9" ht="24.95">
       <c r="A26" s="81" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B26" s="84" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C26" s="85">
         <v>95</v>
@@ -12215,7 +12207,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="84" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F26" s="85">
         <v>94</v>
@@ -12226,10 +12218,10 @@
     </row>
     <row r="27" spans="1:9" ht="24.95">
       <c r="A27" s="81" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B27" s="87" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C27" s="88">
         <v>75</v>
@@ -12238,7 +12230,7 @@
         <v>56</v>
       </c>
       <c r="E27" s="87" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F27" s="88">
         <v>75</v>
@@ -12247,7 +12239,7 @@
         <v>59</v>
       </c>
       <c r="H27" s="77" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="24.95">
@@ -12264,7 +12256,7 @@
         <v>228</v>
       </c>
       <c r="E28" s="84" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F28" s="84">
         <v>98</v>
@@ -12287,7 +12279,7 @@
         <v>228</v>
       </c>
       <c r="E29" s="84" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F29" s="84">
         <v>98</v>
@@ -12310,7 +12302,7 @@
         <v>228</v>
       </c>
       <c r="E30" s="84" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F30" s="84">
         <v>96</v>
@@ -12330,24 +12322,24 @@
         <v>80</v>
       </c>
       <c r="D31" s="95" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E31" s="84" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F31" s="84">
         <v>77</v>
       </c>
       <c r="G31" s="95" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="24.95">
       <c r="A32" s="97" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B32" s="98" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C32" s="98">
         <v>75</v>
@@ -12356,7 +12348,7 @@
         <v>60</v>
       </c>
       <c r="E32" s="98" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F32" s="98">
         <v>62</v>
@@ -12365,11 +12357,13 @@
         <v>60</v>
       </c>
       <c r="H32" s="77" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="96"/>
+        <v>397</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="23.25">
+      <c r="A34" s="96" t="s">
+        <v>401</v>
+      </c>
       <c r="B34" s="103" t="s">
         <v>147</v>
       </c>
@@ -12378,7 +12372,7 @@
         <v>148</v>
       </c>
       <c r="E34" s="103" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F34" s="104"/>
       <c r="G34" s="76" t="s">
@@ -12387,33 +12381,33 @@
     </row>
     <row r="35" spans="1:8" ht="50.1">
       <c r="A35" s="78" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B35" s="79" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C35" s="80" t="s">
         <v>151</v>
       </c>
       <c r="D35" s="79" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E35" s="79" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F35" s="80" t="s">
         <v>151</v>
       </c>
       <c r="G35" s="79" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="24.95">
       <c r="A36" s="81" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B36" s="82" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C36" s="83">
         <v>93</v>
@@ -12422,7 +12416,7 @@
         <v>40</v>
       </c>
       <c r="E36" s="82" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F36" s="83">
         <v>95</v>
@@ -12433,10 +12427,10 @@
     </row>
     <row r="37" spans="1:8" ht="24.95">
       <c r="A37" s="81" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B37" s="84" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C37" s="85">
         <v>94</v>
@@ -12456,10 +12450,10 @@
     </row>
     <row r="38" spans="1:8" ht="24.95">
       <c r="A38" s="81" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B38" s="87" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C38" s="88">
         <v>79</v>
@@ -12468,7 +12462,7 @@
         <v>62</v>
       </c>
       <c r="E38" s="87" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F38" s="88">
         <v>80</v>
@@ -12477,7 +12471,7 @@
         <v>60</v>
       </c>
       <c r="H38" s="77" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="24.95">
@@ -12494,7 +12488,7 @@
         <v>228</v>
       </c>
       <c r="E39" s="84" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F39" s="84">
         <v>99</v>
@@ -12517,7 +12511,7 @@
         <v>228</v>
       </c>
       <c r="E40" s="84" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F40" s="84">
         <v>99</v>
@@ -12540,7 +12534,7 @@
         <v>228</v>
       </c>
       <c r="E41" s="84" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F41" s="84">
         <v>96</v>
@@ -12560,24 +12554,24 @@
         <v>80</v>
       </c>
       <c r="D42" s="95" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E42" s="84" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F42" s="84">
         <v>75</v>
       </c>
       <c r="G42" s="95" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="24.95">
       <c r="A43" s="97" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B43" s="98" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C43" s="98">
         <v>77</v>
@@ -12586,7 +12580,7 @@
         <v>68</v>
       </c>
       <c r="E43" s="98" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F43" s="98">
         <v>75</v>
@@ -12595,7 +12589,7 @@
         <v>70</v>
       </c>
       <c r="H43" s="77" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -12625,10 +12619,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60">
       <c r="A1" s="50" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>148</v>
@@ -12639,34 +12633,34 @@
         <v>149</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C2" s="40"/>
     </row>
     <row r="3" spans="1:3" ht="18.95" hidden="1">
       <c r="A3" s="22" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:3" ht="15.95" hidden="1">
       <c r="A4" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" ht="15.95" hidden="1">
       <c r="A5" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="57"/>
     </row>
     <row r="6" spans="1:3" ht="15.95" hidden="1">
       <c r="A6" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -12683,10 +12677,10 @@
         <v>160</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.95">
@@ -12694,10 +12688,10 @@
         <v>162</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.95" hidden="1">
@@ -12709,7 +12703,7 @@
     </row>
     <row r="11" spans="1:3" ht="15.95" hidden="1">
       <c r="A11" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="57"/>
@@ -12730,14 +12724,14 @@
     </row>
     <row r="14" spans="1:3" ht="15.95" hidden="1">
       <c r="A14" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="15.95" hidden="1">
       <c r="A15" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -12751,14 +12745,14 @@
     </row>
     <row r="17" spans="1:3" ht="15.95" hidden="1">
       <c r="A17" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" ht="15.95" hidden="1">
       <c r="A18" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
@@ -12772,7 +12766,7 @@
     </row>
     <row r="20" spans="1:3" ht="15.95" hidden="1">
       <c r="A20" s="43" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -12796,10 +12790,10 @@
         <v>187</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C23" s="56" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.95" hidden="1">
@@ -12814,10 +12808,10 @@
         <v>191</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.95">
@@ -12825,15 +12819,15 @@
         <v>193</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.95" hidden="1">
       <c r="A27" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="56"/>
@@ -12854,14 +12848,14 @@
     </row>
     <row r="30" spans="1:3" ht="15.95" hidden="1">
       <c r="A30" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="56"/>
     </row>
     <row r="31" spans="1:3" ht="15.95" hidden="1">
       <c r="A31" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="56"/>
@@ -12927,10 +12921,10 @@
         <v>218</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.95">
@@ -12938,10 +12932,10 @@
         <v>219</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C41" s="58" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.95" hidden="1">
@@ -12970,10 +12964,10 @@
         <v>223</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.95" hidden="1">
@@ -13000,32 +12994,32 @@
   <sheetData>
     <row r="1" spans="1:4" ht="81">
       <c r="A1" s="71" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="72" t="s">
+        <v>442</v>
+      </c>
+      <c r="C1" s="73" t="s">
         <v>443</v>
-      </c>
-      <c r="B1" s="72" t="s">
-        <v>444</v>
-      </c>
-      <c r="C1" s="73" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21.95">
       <c r="A2" s="69" t="s">
+        <v>444</v>
+      </c>
+      <c r="B2" s="70" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" s="70" t="s">
         <v>446</v>
-      </c>
-      <c r="B2" s="70" t="s">
-        <v>447</v>
-      </c>
-      <c r="C2" s="70" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21.95">
       <c r="A3" s="69" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B3" s="70" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C3" s="70" t="s">
         <v>232</v>
@@ -13033,82 +13027,82 @@
     </row>
     <row r="4" spans="1:4" ht="21.95">
       <c r="A4" s="69" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B4" s="74" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21.95">
       <c r="A5" s="69" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C5" s="74" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="21.95">
       <c r="A6" s="69" t="s">
+        <v>452</v>
+      </c>
+      <c r="B6" s="70" t="s">
+        <v>453</v>
+      </c>
+      <c r="C6" s="70" t="s">
         <v>454</v>
-      </c>
-      <c r="B6" s="70" t="s">
-        <v>455</v>
-      </c>
-      <c r="C6" s="70" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="21.95">
       <c r="A7" s="69" t="s">
+        <v>455</v>
+      </c>
+      <c r="B7" s="70" t="s">
+        <v>456</v>
+      </c>
+      <c r="C7" s="70" t="s">
         <v>457</v>
       </c>
-      <c r="B7" s="70" t="s">
+      <c r="D7" t="s">
         <v>458</v>
-      </c>
-      <c r="C7" s="70" t="s">
-        <v>459</v>
-      </c>
-      <c r="D7" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="21.95">
       <c r="A8" s="69" t="s">
+        <v>459</v>
+      </c>
+      <c r="B8" s="70" t="s">
+        <v>331</v>
+      </c>
+      <c r="C8" s="70" t="s">
+        <v>460</v>
+      </c>
+      <c r="D8" t="s">
         <v>461</v>
-      </c>
-      <c r="B8" s="70" t="s">
-        <v>333</v>
-      </c>
-      <c r="C8" s="70" t="s">
-        <v>462</v>
-      </c>
-      <c r="D8" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="21.95">
       <c r="A9" s="69" t="s">
+        <v>462</v>
+      </c>
+      <c r="B9" s="70" t="s">
+        <v>463</v>
+      </c>
+      <c r="C9" s="70" t="s">
         <v>464</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="D9" t="s">
         <v>465</v>
-      </c>
-      <c r="C9" s="70" t="s">
-        <v>466</v>
-      </c>
-      <c r="D9" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="21.95">
       <c r="A10" s="69" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B10" s="70">
         <v>26000</v>
@@ -13119,7 +13113,7 @@
     </row>
     <row r="11" spans="1:4" ht="21.95">
       <c r="A11" s="69" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B11" s="70">
         <v>445</v>
@@ -13130,7 +13124,7 @@
     </row>
     <row r="12" spans="1:4" ht="21.95">
       <c r="A12" s="69" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B12" s="70">
         <v>96000</v>
@@ -13141,7 +13135,7 @@
     </row>
     <row r="13" spans="1:4" ht="21.95">
       <c r="A13" s="69" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B13" s="70">
         <v>400000</v>
@@ -13152,7 +13146,7 @@
     </row>
     <row r="14" spans="1:4" ht="21.95">
       <c r="A14" s="69" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B14" s="70">
         <v>200000</v>
@@ -13168,10 +13162,19 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
 <SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010092711BC64AAEC84E9EF800276F1AD52C" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba397f1440615f1339f1f20b24e67478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9bf4d24f-a117-48f7-91e1-2035a8c734fd" xmlns:ns3="0b7692b1-2532-40e4-a300-4d7fced4a07a" xmlns:ns4="cb645b5b-9a36-43da-96bf-ab72ec91ddff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74828cee37efa74eab9b700f6a6651cc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
@@ -13419,7 +13422,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
@@ -13517,27 +13520,18 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
 </file>
--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1038" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7558ED8-9BDD-4EEE-BA08-1951C09F4E01}"/>
+  <xr:revisionPtr revIDLastSave="1059" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A0D516E-10E4-466C-BD66-8B079F898EC3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="19740" firstSheet="1" activeTab="2" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="36000" windowHeight="19740" firstSheet="3" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="473">
   <si>
     <t>number</t>
   </si>
@@ -1296,6 +1296,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Release: 25.4X300-202605180407.0-EVO
@@ -1307,6 +1308,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -1394,6 +1396,12 @@
   </si>
   <si>
     <t>345 CPS</t>
+  </si>
+  <si>
+    <t>Release: 25.4X300-202606240112.0-EVO</t>
+  </si>
+  <si>
+    <t>3050 CPS</t>
   </si>
   <si>
     <r>
@@ -1626,7 +1634,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1821,18 +1829,9 @@
     </font>
     <font>
       <b/>
-      <u/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2099,7 +2098,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2383,11 +2382,11 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2395,8 +2394,11 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -8872,10 +8874,10 @@
       <c r="A1" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="102"/>
+      <c r="C1" s="106"/>
       <c r="D1" s="36" t="s">
         <v>148</v>
       </c>
@@ -10278,6 +10280,7 @@
     <col min="3" max="3" width="22.140625" style="5" customWidth="1"/>
     <col min="4" max="4" width="46.42578125" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" customWidth="1"/>
     <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10285,10 +10288,10 @@
       <c r="A1" s="50" t="s">
         <v>319</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="105" t="s">
         <v>320</v>
       </c>
-      <c r="C1" s="102"/>
+      <c r="C1" s="106"/>
       <c r="D1" s="36" t="s">
         <v>148</v>
       </c>
@@ -11255,7 +11258,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="32.25" customHeight="1">
+    <row r="65" spans="1:9" ht="32.25" customHeight="1">
       <c r="A65" s="3" t="s">
         <v>274</v>
       </c>
@@ -11265,7 +11268,7 @@
       <c r="C65" s="56"/>
       <c r="D65" s="57"/>
     </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1">
+    <row r="66" spans="1:9" ht="18" customHeight="1">
       <c r="A66" s="28" t="s">
         <v>276</v>
       </c>
@@ -11279,7 +11282,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15.95">
+    <row r="67" spans="1:9" ht="15.95">
       <c r="A67" s="2" t="s">
         <v>278</v>
       </c>
@@ -11293,7 +11296,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="15.95">
+    <row r="68" spans="1:9" ht="15.95">
       <c r="A68" s="2" t="s">
         <v>279</v>
       </c>
@@ -11306,8 +11309,19 @@
       <c r="D68" s="56">
         <v>76</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" ht="15.95">
+      <c r="G68">
+        <v>123657512</v>
+      </c>
+      <c r="H68">
+        <f>G68/1000</f>
+        <v>123657.512</v>
+      </c>
+      <c r="I68">
+        <f>H68/1000000</f>
+        <v>0.123657512</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="15.95">
       <c r="A69" s="2" t="s">
         <v>280</v>
       </c>
@@ -11315,7 +11329,7 @@
       <c r="C69" s="56"/>
       <c r="D69" s="56"/>
     </row>
-    <row r="70" spans="1:4" ht="15.95">
+    <row r="70" spans="1:9" ht="15.95">
       <c r="A70" s="2" t="s">
         <v>281</v>
       </c>
@@ -11329,7 +11343,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15.95">
+    <row r="71" spans="1:9" ht="15.95">
       <c r="A71" s="2" t="s">
         <v>282</v>
       </c>
@@ -11343,7 +11357,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15.95">
+    <row r="72" spans="1:9" ht="15.95">
       <c r="A72" s="2" t="s">
         <v>283</v>
       </c>
@@ -11357,7 +11371,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15.95">
+    <row r="73" spans="1:9" ht="15.95">
       <c r="A73" s="2" t="s">
         <v>284</v>
       </c>
@@ -11371,7 +11385,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15.95">
+    <row r="74" spans="1:9" ht="15.95">
       <c r="A74" s="2" t="s">
         <v>286</v>
       </c>
@@ -11385,7 +11399,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="15.95">
+    <row r="75" spans="1:9" ht="15.95">
       <c r="A75" s="2" t="s">
         <v>287</v>
       </c>
@@ -11399,7 +11413,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15.95">
+    <row r="76" spans="1:9" ht="15.95">
       <c r="A76" s="2" t="s">
         <v>288</v>
       </c>
@@ -11413,7 +11427,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15.95">
+    <row r="77" spans="1:9" ht="15.95">
       <c r="A77" s="2" t="s">
         <v>289</v>
       </c>
@@ -11427,7 +11441,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15.95">
+    <row r="78" spans="1:9" ht="15.95">
       <c r="A78" s="2" t="s">
         <v>290</v>
       </c>
@@ -11441,7 +11455,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="15.95">
+    <row r="79" spans="1:9" ht="15.95">
       <c r="A79" s="2" t="s">
         <v>291</v>
       </c>
@@ -11451,7 +11465,7 @@
       <c r="C79" s="56"/>
       <c r="D79" s="56"/>
     </row>
-    <row r="80" spans="1:4" ht="15.95">
+    <row r="80" spans="1:9" ht="15.95">
       <c r="A80" s="2" t="s">
         <v>292</v>
       </c>
@@ -11718,7 +11732,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1F4FD9-0BA8-D443-A42F-4E5E606C52A0}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="62.42578125" defaultRowHeight="24"/>
   <cols>
     <col min="1" max="1" width="162.42578125" style="77" customWidth="1"/>
@@ -11926,8 +11940,8 @@
         <v>389</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="70.5">
-      <c r="A12" s="105" t="s">
+    <row r="12" spans="1:7" ht="75">
+      <c r="A12" s="75" t="s">
         <v>390</v>
       </c>
       <c r="B12" s="103" t="s">
@@ -12360,7 +12374,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="23.25">
+    <row r="34" spans="1:8" ht="24.95">
       <c r="A34" s="96" t="s">
         <v>401</v>
       </c>
@@ -12592,8 +12606,147 @@
         <v>397</v>
       </c>
     </row>
+    <row r="45" spans="1:8" ht="23.25">
+      <c r="A45" s="101" t="s">
+        <v>411</v>
+      </c>
+      <c r="B45" s="103" t="s">
+        <v>320</v>
+      </c>
+      <c r="C45" s="104"/>
+      <c r="D45" s="76" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="47.25">
+      <c r="A46" s="78" t="s">
+        <v>379</v>
+      </c>
+      <c r="B46" s="79" t="s">
+        <v>336</v>
+      </c>
+      <c r="C46" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="D46" s="79" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="23.25">
+      <c r="A47" s="81" t="s">
+        <v>381</v>
+      </c>
+      <c r="B47" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="C47" s="83">
+        <v>93</v>
+      </c>
+      <c r="D47" s="84">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="23.25">
+      <c r="A48" s="81" t="s">
+        <v>384</v>
+      </c>
+      <c r="B48" s="84" t="s">
+        <v>412</v>
+      </c>
+      <c r="C48" s="85">
+        <v>94</v>
+      </c>
+      <c r="D48" s="86">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="23.25">
+      <c r="A49" s="81" t="s">
+        <v>387</v>
+      </c>
+      <c r="B49" s="87" t="s">
+        <v>406</v>
+      </c>
+      <c r="C49" s="88">
+        <v>80</v>
+      </c>
+      <c r="D49" s="89">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="23.25">
+      <c r="A50" s="90" t="s">
+        <v>226</v>
+      </c>
+      <c r="B50" s="84" t="s">
+        <v>350</v>
+      </c>
+      <c r="C50" s="84">
+        <v>99</v>
+      </c>
+      <c r="D50" s="92" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="23.25">
+      <c r="A51" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="B51" s="84" t="s">
+        <v>351</v>
+      </c>
+      <c r="C51" s="84">
+        <v>99</v>
+      </c>
+      <c r="D51" s="92" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="23.25">
+      <c r="A52" s="94" t="s">
+        <v>231</v>
+      </c>
+      <c r="B52" s="84" t="s">
+        <v>352</v>
+      </c>
+      <c r="C52" s="84">
+        <v>96</v>
+      </c>
+      <c r="D52" s="92" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="23.25">
+      <c r="A53" s="81" t="s">
+        <v>260</v>
+      </c>
+      <c r="B53" s="102" t="s">
+        <v>407</v>
+      </c>
+      <c r="C53" s="87">
+        <v>80</v>
+      </c>
+      <c r="D53" s="95" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="23.25">
+      <c r="A54" s="97" t="s">
+        <v>408</v>
+      </c>
+      <c r="B54" s="98" t="s">
+        <v>410</v>
+      </c>
+      <c r="C54" s="98">
+        <v>77</v>
+      </c>
+      <c r="D54" s="98">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="B1:C1"/>
@@ -12619,7 +12772,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60">
       <c r="A1" s="50" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>320</v>
@@ -12639,28 +12792,28 @@
     </row>
     <row r="3" spans="1:3" ht="18.95" hidden="1">
       <c r="A3" s="22" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:3" ht="15.95" hidden="1">
       <c r="A4" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" ht="15.95" hidden="1">
       <c r="A5" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="57"/>
     </row>
     <row r="6" spans="1:3" ht="15.95" hidden="1">
       <c r="A6" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -12677,10 +12830,10 @@
         <v>160</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.95">
@@ -12688,10 +12841,10 @@
         <v>162</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.95" hidden="1">
@@ -12703,7 +12856,7 @@
     </row>
     <row r="11" spans="1:3" ht="15.95" hidden="1">
       <c r="A11" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="57"/>
@@ -12724,14 +12877,14 @@
     </row>
     <row r="14" spans="1:3" ht="15.95" hidden="1">
       <c r="A14" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="15.95" hidden="1">
       <c r="A15" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -12745,14 +12898,14 @@
     </row>
     <row r="17" spans="1:3" ht="15.95" hidden="1">
       <c r="A17" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" ht="15.95" hidden="1">
       <c r="A18" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
@@ -12766,7 +12919,7 @@
     </row>
     <row r="20" spans="1:3" ht="15.95" hidden="1">
       <c r="A20" s="43" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -12790,10 +12943,10 @@
         <v>187</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C23" s="56" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.95" hidden="1">
@@ -12808,10 +12961,10 @@
         <v>191</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.95">
@@ -12819,15 +12972,15 @@
         <v>193</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.95" hidden="1">
       <c r="A27" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="56"/>
@@ -12848,14 +13001,14 @@
     </row>
     <row r="30" spans="1:3" ht="15.95" hidden="1">
       <c r="A30" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="56"/>
     </row>
     <row r="31" spans="1:3" ht="15.95" hidden="1">
       <c r="A31" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="56"/>
@@ -12921,10 +13074,10 @@
         <v>218</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.95">
@@ -12932,10 +13085,10 @@
         <v>219</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C41" s="58" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.95" hidden="1">
@@ -12964,10 +13117,10 @@
         <v>223</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.95" hidden="1">
@@ -12994,32 +13147,32 @@
   <sheetData>
     <row r="1" spans="1:4" ht="81">
       <c r="A1" s="71" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B1" s="72" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C1" s="73" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21.95">
       <c r="A2" s="69" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B2" s="70" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C2" s="70" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21.95">
       <c r="A3" s="69" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B3" s="70" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C3" s="70" t="s">
         <v>232</v>
@@ -13027,82 +13180,82 @@
     </row>
     <row r="4" spans="1:4" ht="21.95">
       <c r="A4" s="69" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B4" s="74" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21.95">
       <c r="A5" s="69" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C5" s="74" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="21.95">
       <c r="A6" s="69" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B6" s="70" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="21.95">
       <c r="A7" s="69" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B7" s="70" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C7" s="70" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="21.95">
       <c r="A8" s="69" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B8" s="70" t="s">
         <v>331</v>
       </c>
       <c r="C8" s="70" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="21.95">
       <c r="A9" s="69" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B9" s="70" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C9" s="70" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D9" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="21.95">
       <c r="A10" s="69" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B10" s="70">
         <v>26000</v>
@@ -13113,7 +13266,7 @@
     </row>
     <row r="11" spans="1:4" ht="21.95">
       <c r="A11" s="69" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B11" s="70">
         <v>445</v>
@@ -13124,7 +13277,7 @@
     </row>
     <row r="12" spans="1:4" ht="21.95">
       <c r="A12" s="69" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B12" s="70">
         <v>96000</v>
@@ -13135,7 +13288,7 @@
     </row>
     <row r="13" spans="1:4" ht="21.95">
       <c r="A13" s="69" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B13" s="70">
         <v>400000</v>
@@ -13146,7 +13299,7 @@
     </row>
     <row r="14" spans="1:4" ht="21.95">
       <c r="A14" s="69" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B14" s="70">
         <v>200000</v>
@@ -13161,20 +13314,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010092711BC64AAEC84E9EF800276F1AD52C" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba397f1440615f1339f1f20b24e67478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9bf4d24f-a117-48f7-91e1-2035a8c734fd" xmlns:ns3="0b7692b1-2532-40e4-a300-4d7fced4a07a" xmlns:ns4="cb645b5b-9a36-43da-96bf-ab72ec91ddff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74828cee37efa74eab9b700f6a6651cc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
@@ -13422,6 +13561,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -13521,7 +13674,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13529,7 +13682,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sshivang/Downloads/Panther Sanity/public/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1059" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A0D516E-10E4-466C-BD66-8B079F898EC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8F3957-759D-D040-A631-C1649D393B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="36000" windowHeight="19740" firstSheet="3" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19740" firstSheet="3" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="472">
   <si>
     <t>number</t>
   </si>
@@ -1359,9 +1359,6 @@
     <t>There are spikes seen, expected is 370 CPS. Ravi is checking if dpdk upgrade has caused any issues and it is applicable to all ssl cases.</t>
   </si>
   <si>
-    <t>AppControl + SSL(TLS1.2) - HTTPS CPS (64B)</t>
-  </si>
-  <si>
     <t>300 CPS</t>
   </si>
   <si>
@@ -1634,7 +1631,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2420,9 +2417,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2460,7 +2457,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2566,7 +2563,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2708,7 +2705,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2718,20 +2715,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{101F05EA-6A87-7646-9D66-36E81A856E36}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:I224"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="97.42578125" customWidth="1"/>
-    <col min="3" max="3" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.85546875" customWidth="1"/>
-    <col min="8" max="8" width="22.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97.5" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.1640625" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
         <v>0</v>
       </c>
@@ -2760,7 +2757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1915273-1", "1915273-1")</f>
         <v>1915273-1</v>
@@ -2787,7 +2784,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1915273-2", "1915273-2")</f>
         <v>1915273-2</v>
@@ -2814,7 +2811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1915273-3", "1915273-3")</f>
         <v>1915273-3</v>
@@ -2841,7 +2838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1915273-4", "1915273-4")</f>
         <v>1915273-4</v>
@@ -2865,7 +2862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926402-1", "1926402-1")</f>
         <v>1926402-1</v>
@@ -2892,7 +2889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926402-2", "1926402-2")</f>
         <v>1926402-2</v>
@@ -2922,7 +2919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926402-3", "1926402-3")</f>
         <v>1926402-3</v>
@@ -2952,7 +2949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926402-4", "1926402-4")</f>
         <v>1926402-4</v>
@@ -2976,7 +2973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926405-1", "1926405-1")</f>
         <v>1926405-1</v>
@@ -3003,7 +3000,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926405-2", "1926405-2")</f>
         <v>1926405-2</v>
@@ -3030,7 +3027,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926405-3", "1926405-3")</f>
         <v>1926405-3</v>
@@ -3057,7 +3054,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926480-1", "1926480-1")</f>
         <v>1926480-1</v>
@@ -3087,7 +3084,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926480-2", "1926480-2")</f>
         <v>1926480-2</v>
@@ -3117,7 +3114,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926480-3", "1926480-3")</f>
         <v>1926480-3</v>
@@ -3147,7 +3144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926480-4", "1926480-4")</f>
         <v>1926480-4</v>
@@ -3177,7 +3174,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926480-5", "1926480-5")</f>
         <v>1926480-5</v>
@@ -3207,7 +3204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926694-1", "1926694-1")</f>
         <v>1926694-1</v>
@@ -3234,7 +3231,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926779-1", "1926779-1")</f>
         <v>1926779-1</v>
@@ -3261,7 +3258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926779-2", "1926779-2")</f>
         <v>1926779-2</v>
@@ -3288,7 +3285,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926779-3", "1926779-3")</f>
         <v>1926779-3</v>
@@ -3312,7 +3309,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-1", "1932710-1")</f>
         <v>1932710-1</v>
@@ -3339,7 +3336,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-2", "1932710-2")</f>
         <v>1932710-2</v>
@@ -3366,7 +3363,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-3", "1932710-3")</f>
         <v>1932710-3</v>
@@ -3393,7 +3390,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-4", "1932710-4")</f>
         <v>1932710-4</v>
@@ -3417,7 +3414,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-5", "1932710-5")</f>
         <v>1932710-5</v>
@@ -3444,7 +3441,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-6", "1932710-6")</f>
         <v>1932710-6</v>
@@ -3471,7 +3468,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-7", "1932710-7")</f>
         <v>1932710-7</v>
@@ -3495,7 +3492,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-8", "1932710-8")</f>
         <v>1932710-8</v>
@@ -3525,7 +3522,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-9", "1932710-9")</f>
         <v>1932710-9</v>
@@ -3549,7 +3546,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932916-1", "1932916-1")</f>
         <v>1932916-1</v>
@@ -3576,7 +3573,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932916-2", "1932916-2")</f>
         <v>1932916-2</v>
@@ -3603,7 +3600,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932916-3", "1932916-3")</f>
         <v>1932916-3</v>
@@ -3630,7 +3627,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932916-4", "1932916-4")</f>
         <v>1932916-4</v>
@@ -3654,7 +3651,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932916-5", "1932916-5")</f>
         <v>1932916-5</v>
@@ -3678,7 +3675,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933014-1", "1933014-1")</f>
         <v>1933014-1</v>
@@ -3705,7 +3702,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933014-2", "1933014-2")</f>
         <v>1933014-2</v>
@@ -3732,7 +3729,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933014-3", "1933014-3")</f>
         <v>1933014-3</v>
@@ -3759,7 +3756,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933014-4", "1933014-4")</f>
         <v>1933014-4</v>
@@ -3786,7 +3783,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933021-1", "1933021-1")</f>
         <v>1933021-1</v>
@@ -3813,7 +3810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933021-2", "1933021-2")</f>
         <v>1933021-2</v>
@@ -3840,7 +3837,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933021-3", "1933021-3")</f>
         <v>1933021-3</v>
@@ -3867,7 +3864,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933163-1", "1933163-1")</f>
         <v>1933163-1</v>
@@ -3894,7 +3891,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933163-2", "1933163-2")</f>
         <v>1933163-2</v>
@@ -3921,7 +3918,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933163-3", "1933163-3")</f>
         <v>1933163-3</v>
@@ -3948,7 +3945,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933192-1", "1933192-1")</f>
         <v>1933192-1</v>
@@ -3975,7 +3972,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933192-2", "1933192-2")</f>
         <v>1933192-2</v>
@@ -4002,7 +3999,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933192-3", "1933192-3")</f>
         <v>1933192-3</v>
@@ -4029,7 +4026,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-1", "1933195-1")</f>
         <v>1933195-1</v>
@@ -4056,7 +4053,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-2", "1933195-2")</f>
         <v>1933195-2</v>
@@ -4083,7 +4080,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-3", "1933195-3")</f>
         <v>1933195-3</v>
@@ -4110,7 +4107,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-4", "1933195-4")</f>
         <v>1933195-4</v>
@@ -4137,7 +4134,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-5", "1933195-5")</f>
         <v>1933195-5</v>
@@ -4164,7 +4161,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-6", "1933195-6")</f>
         <v>1933195-6</v>
@@ -4188,7 +4185,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-7", "1933195-7")</f>
         <v>1933195-7</v>
@@ -4218,7 +4215,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933636-1", "1933636-1")</f>
         <v>1933636-1</v>
@@ -4245,7 +4242,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933636-2", "1933636-2")</f>
         <v>1933636-2</v>
@@ -4272,7 +4269,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933636-3", "1933636-3")</f>
         <v>1933636-3</v>
@@ -4299,7 +4296,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933957-1", "1933957-1")</f>
         <v>1933957-1</v>
@@ -4326,7 +4323,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933957-2", "1933957-2")</f>
         <v>1933957-2</v>
@@ -4353,7 +4350,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933957-3", "1933957-3")</f>
         <v>1933957-3</v>
@@ -4380,7 +4377,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933971-1", "1933971-1")</f>
         <v>1933971-1</v>
@@ -4410,7 +4407,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933971-2", "1933971-2")</f>
         <v>1933971-2</v>
@@ -4440,7 +4437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933971-3", "1933971-3")</f>
         <v>1933971-3</v>
@@ -4470,7 +4467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934311-1", "1934311-1")</f>
         <v>1934311-1</v>
@@ -4497,7 +4494,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934311-2", "1934311-2")</f>
         <v>1934311-2</v>
@@ -4524,7 +4521,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934311-3", "1934311-3")</f>
         <v>1934311-3</v>
@@ -4551,7 +4548,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934311-4", "1934311-4")</f>
         <v>1934311-4</v>
@@ -4578,7 +4575,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934315-1", "1934315-1")</f>
         <v>1934315-1</v>
@@ -4608,7 +4605,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934315-2", "1934315-2")</f>
         <v>1934315-2</v>
@@ -4638,7 +4635,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934315-3", "1934315-3")</f>
         <v>1934315-3</v>
@@ -4668,7 +4665,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1935848-1", "1935848-1")</f>
         <v>1935848-1</v>
@@ -4695,7 +4692,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1935848-2", "1935848-2")</f>
         <v>1935848-2</v>
@@ -4722,7 +4719,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1935848-3", "1935848-3")</f>
         <v>1935848-3</v>
@@ -4749,7 +4746,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1936810-1", "1936810-1")</f>
         <v>1936810-1</v>
@@ -4776,7 +4773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1936810-2", "1936810-2")</f>
         <v>1936810-2</v>
@@ -4803,7 +4800,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1936810-3", "1936810-3")</f>
         <v>1936810-3</v>
@@ -4830,7 +4827,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937041-1", "1937041-1")</f>
         <v>1937041-1</v>
@@ -4857,7 +4854,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937041-2", "1937041-2")</f>
         <v>1937041-2</v>
@@ -4884,7 +4881,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937041-3", "1937041-3")</f>
         <v>1937041-3</v>
@@ -4911,7 +4908,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937045-1", "1937045-1")</f>
         <v>1937045-1</v>
@@ -4938,7 +4935,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937045-2", "1937045-2")</f>
         <v>1937045-2</v>
@@ -4965,7 +4962,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937045-3", "1937045-3")</f>
         <v>1937045-3</v>
@@ -4992,7 +4989,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937124-1", "1937124-1")</f>
         <v>1937124-1</v>
@@ -5019,7 +5016,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937124-2", "1937124-2")</f>
         <v>1937124-2</v>
@@ -5046,7 +5043,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937124-3", "1937124-3")</f>
         <v>1937124-3</v>
@@ -5073,7 +5070,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937537-1", "1937537-1")</f>
         <v>1937537-1</v>
@@ -5103,7 +5100,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937537-2", "1937537-2")</f>
         <v>1937537-2</v>
@@ -5133,7 +5130,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937537-3", "1937537-3")</f>
         <v>1937537-3</v>
@@ -5163,7 +5160,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937949-1", "1937949-1")</f>
         <v>1937949-1</v>
@@ -5193,7 +5190,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937949-2", "1937949-2")</f>
         <v>1937949-2</v>
@@ -5220,7 +5217,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937949-3", "1937949-3")</f>
         <v>1937949-3</v>
@@ -5244,7 +5241,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937949-4", "1937949-4")</f>
         <v>1937949-4</v>
@@ -5274,7 +5271,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937950-1", "1937950-1")</f>
         <v>1937950-1</v>
@@ -5304,7 +5301,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937950-2", "1937950-2")</f>
         <v>1937950-2</v>
@@ -5331,7 +5328,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937950-3", "1937950-3")</f>
         <v>1937950-3</v>
@@ -5355,7 +5352,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-1", "1938096-1")</f>
         <v>1938096-1</v>
@@ -5385,7 +5382,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-2", "1938096-2")</f>
         <v>1938096-2</v>
@@ -5415,7 +5412,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-3", "1938096-3")</f>
         <v>1938096-3</v>
@@ -5445,7 +5442,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-4", "1938096-4")</f>
         <v>1938096-4</v>
@@ -5472,7 +5469,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-5", "1938096-5")</f>
         <v>1938096-5</v>
@@ -5502,7 +5499,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-6", "1938096-6")</f>
         <v>1938096-6</v>
@@ -5529,7 +5526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938163-1", "1938163-1")</f>
         <v>1938163-1</v>
@@ -5559,7 +5556,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938163-2", "1938163-2")</f>
         <v>1938163-2</v>
@@ -5586,7 +5583,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938163-3", "1938163-3")</f>
         <v>1938163-3</v>
@@ -5613,7 +5610,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938163-4", "1938163-4")</f>
         <v>1938163-4</v>
@@ -5640,7 +5637,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938163-5", "1938163-5")</f>
         <v>1938163-5</v>
@@ -5667,7 +5664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-1", "1938166-1")</f>
         <v>1938166-1</v>
@@ -5697,7 +5694,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-2", "1938166-2")</f>
         <v>1938166-2</v>
@@ -5724,7 +5721,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-3", "1938166-3")</f>
         <v>1938166-3</v>
@@ -5751,7 +5748,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-4", "1938166-4")</f>
         <v>1938166-4</v>
@@ -5778,7 +5775,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-5", "1938166-5")</f>
         <v>1938166-5</v>
@@ -5808,7 +5805,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-6", "1938166-6")</f>
         <v>1938166-6</v>
@@ -5832,7 +5829,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-7", "1938166-7")</f>
         <v>1938166-7</v>
@@ -5859,7 +5856,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-8", "1938166-8")</f>
         <v>1938166-8</v>
@@ -5886,7 +5883,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-1", "1938338-1")</f>
         <v>1938338-1</v>
@@ -5913,7 +5910,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-2", "1938338-2")</f>
         <v>1938338-2</v>
@@ -5940,7 +5937,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-3", "1938338-3")</f>
         <v>1938338-3</v>
@@ -5967,7 +5964,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-4", "1938338-4")</f>
         <v>1938338-4</v>
@@ -5994,7 +5991,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-5", "1938338-5")</f>
         <v>1938338-5</v>
@@ -6024,7 +6021,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-6", "1938338-6")</f>
         <v>1938338-6</v>
@@ -6051,7 +6048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938381-1", "1938381-1")</f>
         <v>1938381-1</v>
@@ -6078,7 +6075,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938381-2", "1938381-2")</f>
         <v>1938381-2</v>
@@ -6105,7 +6102,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938384-1", "1938384-1")</f>
         <v>1938384-1</v>
@@ -6132,7 +6129,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938384-2", "1938384-2")</f>
         <v>1938384-2</v>
@@ -6159,7 +6156,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938384-3", "1938384-3")</f>
         <v>1938384-3</v>
@@ -6186,7 +6183,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938500-1", "1938500-1")</f>
         <v>1938500-1</v>
@@ -6213,7 +6210,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938500-2", "1938500-2")</f>
         <v>1938500-2</v>
@@ -6240,7 +6237,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938500-3", "1938500-3")</f>
         <v>1938500-3</v>
@@ -6267,7 +6264,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938500-4", "1938500-4")</f>
         <v>1938500-4</v>
@@ -6294,7 +6291,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938573-1", "1938573-1")</f>
         <v>1938573-1</v>
@@ -6321,7 +6318,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938573-2", "1938573-2")</f>
         <v>1938573-2</v>
@@ -6348,7 +6345,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940432-1", "1940432-1")</f>
         <v>1940432-1</v>
@@ -6375,7 +6372,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940432-2", "1940432-2")</f>
         <v>1940432-2</v>
@@ -6402,7 +6399,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-1", "1940444-1")</f>
         <v>1940444-1</v>
@@ -6429,7 +6426,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-2", "1940444-2")</f>
         <v>1940444-2</v>
@@ -6456,7 +6453,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-3", "1940444-3")</f>
         <v>1940444-3</v>
@@ -6483,7 +6480,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-4", "1940444-4")</f>
         <v>1940444-4</v>
@@ -6510,7 +6507,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-5", "1940444-5")</f>
         <v>1940444-5</v>
@@ -6534,7 +6531,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-6", "1940444-6")</f>
         <v>1940444-6</v>
@@ -6564,7 +6561,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-7", "1940444-7")</f>
         <v>1940444-7</v>
@@ -6588,7 +6585,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-8", "1940444-8")</f>
         <v>1940444-8</v>
@@ -6612,7 +6609,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-9", "1940444-9")</f>
         <v>1940444-9</v>
@@ -6636,7 +6633,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-1", "1940445-1")</f>
         <v>1940445-1</v>
@@ -6663,7 +6660,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-2", "1940445-2")</f>
         <v>1940445-2</v>
@@ -6690,7 +6687,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-3", "1940445-3")</f>
         <v>1940445-3</v>
@@ -6717,7 +6714,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-4", "1940445-4")</f>
         <v>1940445-4</v>
@@ -6747,7 +6744,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-5", "1940445-5")</f>
         <v>1940445-5</v>
@@ -6774,7 +6771,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-6", "1940445-6")</f>
         <v>1940445-6</v>
@@ -6801,7 +6798,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-7", "1940445-7")</f>
         <v>1940445-7</v>
@@ -6828,7 +6825,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-8", "1940445-8")</f>
         <v>1940445-8</v>
@@ -6855,7 +6852,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-1", "1940446-1")</f>
         <v>1940446-1</v>
@@ -6882,7 +6879,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-2", "1940446-2")</f>
         <v>1940446-2</v>
@@ -6909,7 +6906,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-3", "1940446-3")</f>
         <v>1940446-3</v>
@@ -6936,7 +6933,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-4", "1940446-4")</f>
         <v>1940446-4</v>
@@ -6963,7 +6960,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-5", "1940446-5")</f>
         <v>1940446-5</v>
@@ -6990,7 +6987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-6", "1940446-6")</f>
         <v>1940446-6</v>
@@ -7020,7 +7017,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-7", "1940446-7")</f>
         <v>1940446-7</v>
@@ -7047,7 +7044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-8", "1940446-8")</f>
         <v>1940446-8</v>
@@ -7071,7 +7068,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-9", "1940446-9")</f>
         <v>1940446-9</v>
@@ -7098,7 +7095,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-10", "1940446-10")</f>
         <v>1940446-10</v>
@@ -7122,7 +7119,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-1", "1942363-1")</f>
         <v>1942363-1</v>
@@ -7149,7 +7146,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-2", "1942363-2")</f>
         <v>1942363-2</v>
@@ -7176,7 +7173,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-3", "1942363-3")</f>
         <v>1942363-3</v>
@@ -7203,7 +7200,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-4", "1942363-4")</f>
         <v>1942363-4</v>
@@ -7230,7 +7227,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942376-1", "1942376-1")</f>
         <v>1942376-1</v>
@@ -7257,7 +7254,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942376-2", "1942376-2")</f>
         <v>1942376-2</v>
@@ -7284,7 +7281,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-1", "1943082-1")</f>
         <v>1943082-1</v>
@@ -7311,7 +7308,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-2", "1943082-2")</f>
         <v>1943082-2</v>
@@ -7338,7 +7335,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-3", "1943082-3")</f>
         <v>1943082-3</v>
@@ -7365,7 +7362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-4", "1943082-4")</f>
         <v>1943082-4</v>
@@ -7392,7 +7389,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-1", "1943084-1")</f>
         <v>1943084-1</v>
@@ -7419,7 +7416,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-2", "1943084-2")</f>
         <v>1943084-2</v>
@@ -7446,7 +7443,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-3", "1943084-3")</f>
         <v>1943084-3</v>
@@ -7470,7 +7467,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-4", "1943084-4")</f>
         <v>1943084-4</v>
@@ -7497,7 +7494,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943461-1", "1943461-1")</f>
         <v>1943461-1</v>
@@ -7524,7 +7521,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943461-2", "1943461-2")</f>
         <v>1943461-2</v>
@@ -7551,7 +7548,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-1", "1943467-1")</f>
         <v>1943467-1</v>
@@ -7578,7 +7575,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-2", "1943467-2")</f>
         <v>1943467-2</v>
@@ -7605,7 +7602,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-3", "1943467-3")</f>
         <v>1943467-3</v>
@@ -7632,7 +7629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-4", "1943467-4")</f>
         <v>1943467-4</v>
@@ -7659,7 +7656,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-5", "1943467-5")</f>
         <v>1943467-5</v>
@@ -7689,7 +7686,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-1", "1943607-1")</f>
         <v>1943607-1</v>
@@ -7719,7 +7716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-2", "1943607-2")</f>
         <v>1943607-2</v>
@@ -7749,7 +7746,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-3", "1943607-3")</f>
         <v>1943607-3</v>
@@ -7773,7 +7770,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946082-1", "1946082-1")</f>
         <v>1946082-1</v>
@@ -7800,7 +7797,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946082-2", "1946082-2")</f>
         <v>1946082-2</v>
@@ -7827,7 +7824,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-1", "1946085-1")</f>
         <v>1946085-1</v>
@@ -7857,7 +7854,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-2", "1946085-2")</f>
         <v>1946085-2</v>
@@ -7884,7 +7881,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-3", "1946085-3")</f>
         <v>1946085-3</v>
@@ -7911,7 +7908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947270-1", "1947270-1")</f>
         <v>1947270-1</v>
@@ -7938,7 +7935,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947270-2", "1947270-2")</f>
         <v>1947270-2</v>
@@ -7965,7 +7962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947337-1", "1947337-1")</f>
         <v>1947337-1</v>
@@ -7992,7 +7989,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947337-2", "1947337-2")</f>
         <v>1947337-2</v>
@@ -8019,7 +8016,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947954-1", "1947954-1")</f>
         <v>1947954-1</v>
@@ -8046,7 +8043,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947954-2", "1947954-2")</f>
         <v>1947954-2</v>
@@ -8073,7 +8070,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947969-1", "1947969-1")</f>
         <v>1947969-1</v>
@@ -8100,7 +8097,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947969-2", "1947969-2")</f>
         <v>1947969-2</v>
@@ -8127,7 +8124,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-1", "1954277-1")</f>
         <v>1954277-1</v>
@@ -8154,7 +8151,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-2", "1954277-2")</f>
         <v>1954277-2</v>
@@ -8181,7 +8178,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-3", "1954277-3")</f>
         <v>1954277-3</v>
@@ -8208,7 +8205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-4", "1954277-4")</f>
         <v>1954277-4</v>
@@ -8235,7 +8232,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-1", "1954326-1")</f>
         <v>1954326-1</v>
@@ -8262,7 +8259,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-2", "1954326-2")</f>
         <v>1954326-2</v>
@@ -8289,7 +8286,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-3", "1954326-3")</f>
         <v>1954326-3</v>
@@ -8316,7 +8313,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-1", "1954327-1")</f>
         <v>1954327-1</v>
@@ -8346,7 +8343,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-2", "1954327-2")</f>
         <v>1954327-2</v>
@@ -8373,7 +8370,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-3", "1954327-3")</f>
         <v>1954327-3</v>
@@ -8400,7 +8397,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954675-1", "1954675-1")</f>
         <v>1954675-1</v>
@@ -8427,7 +8424,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1957107-1", "1957107-1")</f>
         <v>1957107-1</v>
@@ -8454,7 +8451,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-1", "1959073-1")</f>
         <v>1959073-1</v>
@@ -8481,7 +8478,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-2", "1959073-2")</f>
         <v>1959073-2</v>
@@ -8508,7 +8505,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-3", "1959073-3")</f>
         <v>1959073-3</v>
@@ -8535,7 +8532,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-4", "1959073-4")</f>
         <v>1959073-4</v>
@@ -8562,7 +8559,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1960761-1", "1960761-1")</f>
         <v>1960761-1</v>
@@ -8589,7 +8586,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-1", "1961325-1")</f>
         <v>1961325-1</v>
@@ -8619,7 +8616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-2", "1961325-2")</f>
         <v>1961325-2</v>
@@ -8649,7 +8646,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-3", "1961325-3")</f>
         <v>1961325-3</v>
@@ -8676,7 +8673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-4", "1961325-4")</f>
         <v>1961325-4</v>
@@ -8703,7 +8700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-1", "1961327-1")</f>
         <v>1961327-1</v>
@@ -8730,7 +8727,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-2", "1961327-2")</f>
         <v>1961327-2</v>
@@ -8760,7 +8757,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-3", "1961327-3")</f>
         <v>1961327-3</v>
@@ -8787,7 +8784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-4", "1961327-4")</f>
         <v>1961327-4</v>
@@ -8814,7 +8811,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-5", "1961327-5")</f>
         <v>1961327-5</v>
@@ -8861,16 +8858,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC397FCC-74C1-4D09-ACC0-E463BF5527EB}">
   <dimension ref="A1:I105"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="87.85546875" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.42578125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="87.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="19.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="41.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57" customHeight="1">
+    <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
         <v>146</v>
       </c>
@@ -8883,7 +8880,7 @@
       </c>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="32.25" customHeight="1">
+    <row r="2" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>149</v>
       </c>
@@ -8898,7 +8895,7 @@
       </c>
       <c r="E2" s="11"/>
     </row>
-    <row r="3" spans="1:5" ht="17.25" customHeight="1">
+    <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>153</v>
       </c>
@@ -8913,7 +8910,7 @@
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1">
+    <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>155</v>
       </c>
@@ -8930,7 +8927,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1">
+    <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>158</v>
       </c>
@@ -8945,7 +8942,7 @@
       </c>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>160</v>
       </c>
@@ -8960,7 +8957,7 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="7" spans="1:5" ht="14.45" customHeight="1">
+    <row r="7" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>162</v>
       </c>
@@ -8974,7 +8971,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.1" customHeight="1">
+    <row r="8" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>164</v>
       </c>
@@ -8988,7 +8985,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.95">
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>166</v>
       </c>
@@ -9002,7 +8999,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.95">
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>168</v>
       </c>
@@ -9016,7 +9013,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.95">
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>170</v>
       </c>
@@ -9030,7 +9027,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.95">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>172</v>
       </c>
@@ -9044,7 +9041,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.95">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>174</v>
       </c>
@@ -9058,7 +9055,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.95">
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>176</v>
       </c>
@@ -9072,7 +9069,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.95">
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>178</v>
       </c>
@@ -9086,7 +9083,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.95">
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>180</v>
       </c>
@@ -9100,7 +9097,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.95">
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="43" t="s">
         <v>182</v>
       </c>
@@ -9114,7 +9111,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="40.5" customHeight="1">
+    <row r="18" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
         <v>184</v>
       </c>
@@ -9128,7 +9125,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.95">
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
         <v>185</v>
       </c>
@@ -9142,7 +9139,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.95">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>187</v>
       </c>
@@ -9156,7 +9153,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.95">
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>189</v>
       </c>
@@ -9170,7 +9167,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.95">
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>191</v>
       </c>
@@ -9184,7 +9181,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.95">
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>193</v>
       </c>
@@ -9198,7 +9195,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.95">
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>195</v>
       </c>
@@ -9212,7 +9209,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.95">
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>197</v>
       </c>
@@ -9226,7 +9223,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.95">
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>199</v>
       </c>
@@ -9240,7 +9237,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.95">
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>201</v>
       </c>
@@ -9254,7 +9251,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.95">
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>203</v>
       </c>
@@ -9268,7 +9265,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="39" customHeight="1">
+    <row r="29" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
         <v>205</v>
       </c>
@@ -9282,7 +9279,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.95">
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>208</v>
       </c>
@@ -9299,7 +9296,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.95">
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>211</v>
       </c>
@@ -9316,7 +9313,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.95">
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>212</v>
       </c>
@@ -9333,7 +9330,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="17.45" customHeight="1">
+    <row r="33" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>187</v>
       </c>
@@ -9347,7 +9344,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="41.25" customHeight="1">
+    <row r="34" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
         <v>214</v>
       </c>
@@ -9361,7 +9358,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.95">
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>215</v>
       </c>
@@ -9375,7 +9372,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.95">
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>217</v>
       </c>
@@ -9389,7 +9386,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6" customHeight="1">
+    <row r="37" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>218</v>
       </c>
@@ -9403,7 +9400,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.95">
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>219</v>
       </c>
@@ -9417,7 +9414,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.95">
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
         <v>220</v>
       </c>
@@ -9431,7 +9428,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.95">
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
         <v>221</v>
       </c>
@@ -9445,7 +9442,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.95">
+    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>222</v>
       </c>
@@ -9459,7 +9456,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.95">
+    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>223</v>
       </c>
@@ -9473,7 +9470,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.95">
+    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>224</v>
       </c>
@@ -9487,7 +9484,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="32.25" customHeight="1">
+    <row r="44" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
         <v>225</v>
       </c>
@@ -9501,7 +9498,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="18.600000000000001" customHeight="1">
+    <row r="45" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
         <v>226</v>
       </c>
@@ -9515,7 +9512,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="17.45" customHeight="1">
+    <row r="46" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
         <v>229</v>
       </c>
@@ -9529,7 +9526,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.95">
+    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>231</v>
       </c>
@@ -9546,7 +9543,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.95">
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>233</v>
       </c>
@@ -9560,7 +9557,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.95">
+    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>236</v>
       </c>
@@ -9572,7 +9569,7 @@
       </c>
       <c r="D49" s="56"/>
     </row>
-    <row r="50" spans="1:4" ht="15.95">
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>238</v>
       </c>
@@ -9586,7 +9583,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
+    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>240</v>
       </c>
@@ -9600,7 +9597,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15.6" customHeight="1">
+    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>242</v>
       </c>
@@ -9612,7 +9609,7 @@
       </c>
       <c r="D52" s="24"/>
     </row>
-    <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
+    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>244</v>
       </c>
@@ -9626,7 +9623,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.95">
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="18" t="s">
         <v>246</v>
       </c>
@@ -9640,7 +9637,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.95">
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="19" t="s">
         <v>249</v>
       </c>
@@ -9654,7 +9651,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
+    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
         <v>252</v>
       </c>
@@ -9668,7 +9665,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.95">
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
         <v>255</v>
       </c>
@@ -9682,7 +9679,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>257</v>
       </c>
@@ -9696,7 +9693,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.95">
+    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>260</v>
       </c>
@@ -9710,7 +9707,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1">
+    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>262</v>
       </c>
@@ -9724,7 +9721,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1">
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>264</v>
       </c>
@@ -9738,7 +9735,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.45" customHeight="1">
+    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>266</v>
       </c>
@@ -9752,7 +9749,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>269</v>
       </c>
@@ -9764,7 +9761,7 @@
       </c>
       <c r="D63" s="57"/>
     </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1">
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>271</v>
       </c>
@@ -9778,7 +9775,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="32.25" customHeight="1">
+    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>274</v>
       </c>
@@ -9788,7 +9785,7 @@
       <c r="C65" s="51"/>
       <c r="D65" s="56"/>
     </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
         <v>276</v>
       </c>
@@ -9800,7 +9797,7 @@
       </c>
       <c r="D66" s="65"/>
     </row>
-    <row r="67" spans="1:4" ht="15.95">
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>278</v>
       </c>
@@ -9814,7 +9811,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="15.95">
+    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>279</v>
       </c>
@@ -9828,7 +9825,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15.95">
+    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>280</v>
       </c>
@@ -9842,7 +9839,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15.95">
+    <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>281</v>
       </c>
@@ -9856,7 +9853,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15.95">
+    <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>282</v>
       </c>
@@ -9870,7 +9867,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15.95">
+    <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>283</v>
       </c>
@@ -9884,7 +9881,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15.95">
+    <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>284</v>
       </c>
@@ -9898,7 +9895,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15.95">
+    <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>285</v>
       </c>
@@ -9912,7 +9909,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="15.95">
+    <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>286</v>
       </c>
@@ -9926,7 +9923,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15.95">
+    <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>287</v>
       </c>
@@ -9940,7 +9937,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15.95">
+    <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>288</v>
       </c>
@@ -9954,7 +9951,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15.95">
+    <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>289</v>
       </c>
@@ -9968,7 +9965,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="15.95">
+    <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>290</v>
       </c>
@@ -9982,7 +9979,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="15.95">
+    <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>291</v>
       </c>
@@ -9992,7 +9989,7 @@
       <c r="C80" s="10"/>
       <c r="D80" s="56"/>
     </row>
-    <row r="81" spans="1:4" ht="15.95">
+    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>292</v>
       </c>
@@ -10002,7 +9999,7 @@
       <c r="C81" s="32"/>
       <c r="D81" s="56"/>
     </row>
-    <row r="82" spans="1:4" ht="15.95">
+    <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>293</v>
       </c>
@@ -10010,7 +10007,7 @@
       <c r="C82" s="23"/>
       <c r="D82" s="56"/>
     </row>
-    <row r="83" spans="1:4" ht="15.95">
+    <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>294</v>
       </c>
@@ -10018,7 +10015,7 @@
       <c r="C83" s="10"/>
       <c r="D83" s="56"/>
     </row>
-    <row r="84" spans="1:4" ht="15.95">
+    <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>295</v>
       </c>
@@ -10032,7 +10029,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15.95">
+    <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>296</v>
       </c>
@@ -10046,7 +10043,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15.95">
+    <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>298</v>
       </c>
@@ -10060,7 +10057,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15.95">
+    <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>300</v>
       </c>
@@ -10068,7 +10065,7 @@
       <c r="C87" s="10"/>
       <c r="D87" s="56"/>
     </row>
-    <row r="88" spans="1:4" ht="15.95">
+    <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>301</v>
       </c>
@@ -10076,7 +10073,7 @@
       <c r="C88" s="10"/>
       <c r="D88" s="56"/>
     </row>
-    <row r="89" spans="1:4" ht="15.95">
+    <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>302</v>
       </c>
@@ -10084,7 +10081,7 @@
       <c r="C89" s="10"/>
       <c r="D89" s="56"/>
     </row>
-    <row r="90" spans="1:4" ht="15.95">
+    <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>303</v>
       </c>
@@ -10098,7 +10095,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15.95">
+    <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>304</v>
       </c>
@@ -10112,7 +10109,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15.95">
+    <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>305</v>
       </c>
@@ -10122,7 +10119,7 @@
       <c r="C92" s="56"/>
       <c r="D92" s="67"/>
     </row>
-    <row r="93" spans="1:4" ht="15.95">
+    <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>306</v>
       </c>
@@ -10136,7 +10133,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="15.95">
+    <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>307</v>
       </c>
@@ -10150,7 +10147,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15.95">
+    <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>308</v>
       </c>
@@ -10164,7 +10161,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15.95">
+    <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>309</v>
       </c>
@@ -10176,7 +10173,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.95">
+    <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>311</v>
       </c>
@@ -10190,7 +10187,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.95">
+    <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>312</v>
       </c>
@@ -10204,7 +10201,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.95">
+    <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>313</v>
       </c>
@@ -10218,7 +10215,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.95">
+    <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>316</v>
       </c>
@@ -10232,7 +10229,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.95">
+    <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>318</v>
       </c>
@@ -10246,19 +10243,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15" customHeight="1">
+    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1">
+    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" ht="15" customHeight="1">
+    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" ht="15" customHeight="1">
+    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
@@ -10273,18 +10270,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A7BD36-8D88-3742-A4AC-48B0AFB67141}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="85.140625" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="46.42578125" customWidth="1"/>
+    <col min="1" max="1" width="85.1640625" customWidth="1"/>
+    <col min="2" max="2" width="32.5" style="5" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="46.5" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57" customHeight="1">
+    <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="50" t="s">
         <v>319</v>
       </c>
@@ -10296,7 +10293,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>149</v>
       </c>
@@ -10310,7 +10307,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.100000000000001" customHeight="1">
+    <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>153</v>
       </c>
@@ -10324,7 +10321,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16.350000000000001" customHeight="1">
+    <row r="4" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>155</v>
       </c>
@@ -10341,7 +10338,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1">
+    <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>158</v>
       </c>
@@ -10355,7 +10352,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>160</v>
       </c>
@@ -10369,7 +10366,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.45" customHeight="1">
+    <row r="7" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>162</v>
       </c>
@@ -10383,7 +10380,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.1" customHeight="1">
+    <row r="8" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>164</v>
       </c>
@@ -10397,7 +10394,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.95">
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>166</v>
       </c>
@@ -10411,7 +10408,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.95">
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>168</v>
       </c>
@@ -10425,7 +10422,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.95">
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>170</v>
       </c>
@@ -10439,7 +10436,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.95">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>172</v>
       </c>
@@ -10453,7 +10450,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.95">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>174</v>
       </c>
@@ -10467,7 +10464,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.95">
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>176</v>
       </c>
@@ -10481,7 +10478,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.95">
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>178</v>
       </c>
@@ -10495,7 +10492,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.95">
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>180</v>
       </c>
@@ -10509,7 +10506,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.95">
+    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="43" t="s">
         <v>182</v>
       </c>
@@ -10523,7 +10520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1">
+    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
         <v>184</v>
       </c>
@@ -10537,7 +10534,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.95">
+    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
         <v>185</v>
       </c>
@@ -10551,7 +10548,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.95">
+    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>187</v>
       </c>
@@ -10565,7 +10562,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.95">
+    <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>189</v>
       </c>
@@ -10579,7 +10576,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.95">
+    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>191</v>
       </c>
@@ -10593,7 +10590,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.95">
+    <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>193</v>
       </c>
@@ -10607,7 +10604,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.95">
+    <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>195</v>
       </c>
@@ -10624,7 +10621,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.95">
+    <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>197</v>
       </c>
@@ -10638,7 +10635,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.95">
+    <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>199</v>
       </c>
@@ -10652,7 +10649,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.95">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>201</v>
       </c>
@@ -10666,7 +10663,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.95">
+    <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>203</v>
       </c>
@@ -10680,7 +10677,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1">
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
         <v>205</v>
       </c>
@@ -10694,7 +10691,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.95">
+    <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>208</v>
       </c>
@@ -10711,7 +10708,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.95">
+    <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>211</v>
       </c>
@@ -10728,7 +10725,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15.95">
+    <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>212</v>
       </c>
@@ -10745,7 +10742,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="17.45" customHeight="1">
+    <row r="33" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>187</v>
       </c>
@@ -10759,7 +10756,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1">
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
         <v>214</v>
       </c>
@@ -10773,7 +10770,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.95">
+    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>215</v>
       </c>
@@ -10787,7 +10784,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.95">
+    <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>217</v>
       </c>
@@ -10816,7 +10813,7 @@
         <v>57200</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.6" customHeight="1">
+    <row r="37" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>218</v>
       </c>
@@ -10850,7 +10847,7 @@
         <v>228800</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.95">
+    <row r="38" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>219</v>
       </c>
@@ -10884,7 +10881,7 @@
         <v>2599.1680000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.95">
+    <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
         <v>220</v>
       </c>
@@ -10898,7 +10895,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.95">
+    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
         <v>221</v>
       </c>
@@ -10915,7 +10912,7 @@
         <v>280000</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.95">
+    <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>222</v>
       </c>
@@ -10933,7 +10930,7 @@
         <v>835.52</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15.95">
+    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>223</v>
       </c>
@@ -10950,7 +10947,7 @@
         <v>315000</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15.95">
+    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>224</v>
       </c>
@@ -10968,7 +10965,7 @@
         <v>939.96</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="18" customHeight="1">
+    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
         <v>225</v>
       </c>
@@ -10982,7 +10979,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="18.600000000000001" customHeight="1">
+    <row r="45" spans="1:10" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
         <v>226</v>
       </c>
@@ -10996,7 +10993,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="17.45" customHeight="1">
+    <row r="46" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
         <v>229</v>
       </c>
@@ -11010,7 +11007,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15.95">
+    <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>231</v>
       </c>
@@ -11024,7 +11021,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.95">
+    <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>233</v>
       </c>
@@ -11038,7 +11035,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.95">
+    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>236</v>
       </c>
@@ -11050,7 +11047,7 @@
       </c>
       <c r="D49" s="57"/>
     </row>
-    <row r="50" spans="1:4" ht="15.95">
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>238</v>
       </c>
@@ -11064,7 +11061,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
+    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>240</v>
       </c>
@@ -11078,7 +11075,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15.6" customHeight="1">
+    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>242</v>
       </c>
@@ -11092,7 +11089,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
+    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>244</v>
       </c>
@@ -11106,7 +11103,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.95">
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="18" t="s">
         <v>246</v>
       </c>
@@ -11120,7 +11117,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.95">
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="19" t="s">
         <v>249</v>
       </c>
@@ -11134,7 +11131,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
+    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
         <v>252</v>
       </c>
@@ -11148,7 +11145,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.95">
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
         <v>255</v>
       </c>
@@ -11162,7 +11159,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>257</v>
       </c>
@@ -11176,7 +11173,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.95">
+    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>260</v>
       </c>
@@ -11190,7 +11187,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1">
+    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>262</v>
       </c>
@@ -11204,7 +11201,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1">
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>264</v>
       </c>
@@ -11218,7 +11215,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.45" customHeight="1">
+    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>266</v>
       </c>
@@ -11232,7 +11229,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>269</v>
       </c>
@@ -11244,7 +11241,7 @@
       </c>
       <c r="D63" s="57"/>
     </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1">
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>271</v>
       </c>
@@ -11258,7 +11255,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="32.25" customHeight="1">
+    <row r="65" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>274</v>
       </c>
@@ -11268,7 +11265,7 @@
       <c r="C65" s="56"/>
       <c r="D65" s="57"/>
     </row>
-    <row r="66" spans="1:9" ht="18" customHeight="1">
+    <row r="66" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
         <v>276</v>
       </c>
@@ -11282,7 +11279,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.95">
+    <row r="67" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>278</v>
       </c>
@@ -11296,7 +11293,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.95">
+    <row r="68" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>279</v>
       </c>
@@ -11321,7 +11318,7 @@
         <v>0.123657512</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.95">
+    <row r="69" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>280</v>
       </c>
@@ -11329,7 +11326,7 @@
       <c r="C69" s="56"/>
       <c r="D69" s="56"/>
     </row>
-    <row r="70" spans="1:9" ht="15.95">
+    <row r="70" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>281</v>
       </c>
@@ -11343,7 +11340,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.95">
+    <row r="71" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>282</v>
       </c>
@@ -11357,7 +11354,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.95">
+    <row r="72" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>283</v>
       </c>
@@ -11371,7 +11368,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.95">
+    <row r="73" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>284</v>
       </c>
@@ -11385,7 +11382,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.95">
+    <row r="74" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>286</v>
       </c>
@@ -11399,7 +11396,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.95">
+    <row r="75" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>287</v>
       </c>
@@ -11413,7 +11410,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.95">
+    <row r="76" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>288</v>
       </c>
@@ -11427,7 +11424,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.95">
+    <row r="77" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>289</v>
       </c>
@@ -11441,7 +11438,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.95">
+    <row r="78" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>290</v>
       </c>
@@ -11455,7 +11452,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.95">
+    <row r="79" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>291</v>
       </c>
@@ -11465,7 +11462,7 @@
       <c r="C79" s="56"/>
       <c r="D79" s="56"/>
     </row>
-    <row r="80" spans="1:9" ht="15.95">
+    <row r="80" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>292</v>
       </c>
@@ -11475,7 +11472,7 @@
       <c r="C80" s="56"/>
       <c r="D80" s="56"/>
     </row>
-    <row r="81" spans="1:4" ht="15.95">
+    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>293</v>
       </c>
@@ -11483,7 +11480,7 @@
       <c r="C81" s="56"/>
       <c r="D81" s="56"/>
     </row>
-    <row r="82" spans="1:4" ht="15.95">
+    <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>294</v>
       </c>
@@ -11491,7 +11488,7 @@
       <c r="C82" s="56"/>
       <c r="D82" s="56"/>
     </row>
-    <row r="83" spans="1:4" ht="15.95">
+    <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>295</v>
       </c>
@@ -11505,7 +11502,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="15.95">
+    <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>296</v>
       </c>
@@ -11519,7 +11516,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15.95">
+    <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>298</v>
       </c>
@@ -11533,7 +11530,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15.95">
+    <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>300</v>
       </c>
@@ -11541,7 +11538,7 @@
       <c r="C86" s="56"/>
       <c r="D86" s="56"/>
     </row>
-    <row r="87" spans="1:4" ht="15.95">
+    <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>301</v>
       </c>
@@ -11549,7 +11546,7 @@
       <c r="C87" s="56"/>
       <c r="D87" s="56"/>
     </row>
-    <row r="88" spans="1:4" ht="15.95">
+    <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>302</v>
       </c>
@@ -11557,7 +11554,7 @@
       <c r="C88" s="56"/>
       <c r="D88" s="56"/>
     </row>
-    <row r="89" spans="1:4" ht="15.95">
+    <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>303</v>
       </c>
@@ -11571,7 +11568,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="15.95">
+    <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>304</v>
       </c>
@@ -11585,7 +11582,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15.95">
+    <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>305</v>
       </c>
@@ -11597,7 +11594,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15.95">
+    <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>374</v>
       </c>
@@ -11609,7 +11606,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="15.95">
+    <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>375</v>
       </c>
@@ -11621,7 +11618,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="15.95">
+    <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
         <v>308</v>
       </c>
@@ -11635,7 +11632,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15.95">
+    <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>309</v>
       </c>
@@ -11647,7 +11644,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15.95">
+    <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>311</v>
       </c>
@@ -11661,7 +11658,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.95">
+    <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>312</v>
       </c>
@@ -11675,7 +11672,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.95">
+    <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>313</v>
       </c>
@@ -11685,7 +11682,7 @@
       <c r="C98" s="10"/>
       <c r="D98" s="56"/>
     </row>
-    <row r="99" spans="1:9" ht="15.95">
+    <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>316</v>
       </c>
@@ -11695,7 +11692,7 @@
       <c r="C99" s="10"/>
       <c r="D99" s="56"/>
     </row>
-    <row r="100" spans="1:9" ht="15.95">
+    <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>318</v>
       </c>
@@ -11705,19 +11702,19 @@
       <c r="C100" s="10"/>
       <c r="D100" s="56"/>
     </row>
-    <row r="101" spans="1:9" ht="15" customHeight="1">
+    <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9" ht="15" customHeight="1">
+    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1">
+    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" ht="15" customHeight="1">
+    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
@@ -11733,19 +11730,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1F4FD9-0BA8-D443-A42F-4E5E606C52A0}">
   <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultColWidth="62.42578125" defaultRowHeight="24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="62.5" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="162.42578125" style="77" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" style="77" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" style="77" customWidth="1"/>
+    <col min="1" max="1" width="162.5" style="77" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" style="77" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" style="77" customWidth="1"/>
     <col min="4" max="4" width="26" style="77" customWidth="1"/>
-    <col min="5" max="5" width="47.7109375" style="77" customWidth="1"/>
-    <col min="6" max="6" width="26.42578125" style="77" customWidth="1"/>
-    <col min="7" max="7" width="33.85546875" style="77" customWidth="1"/>
-    <col min="8" max="16384" width="62.42578125" style="77"/>
+    <col min="5" max="5" width="47.6640625" style="77" customWidth="1"/>
+    <col min="6" max="6" width="26.5" style="77" customWidth="1"/>
+    <col min="7" max="7" width="33.83203125" style="77" customWidth="1"/>
+    <col min="8" max="16384" width="62.5" style="77"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="75">
+    <row r="1" spans="1:7" ht="75" x14ac:dyDescent="0.3">
       <c r="A1" s="75" t="s">
         <v>378</v>
       </c>
@@ -11764,7 +11761,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="50.1">
+    <row r="2" spans="1:7" ht="50" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
         <v>379</v>
       </c>
@@ -11787,7 +11784,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="24.95">
+    <row r="3" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A3" s="81" t="s">
         <v>381</v>
       </c>
@@ -11810,7 +11807,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="24.95">
+    <row r="4" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A4" s="81" t="s">
         <v>384</v>
       </c>
@@ -11833,7 +11830,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="24.95">
+    <row r="5" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A5" s="81" t="s">
         <v>387</v>
       </c>
@@ -11856,7 +11853,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="24.95">
+    <row r="6" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A6" s="90" t="s">
         <v>226</v>
       </c>
@@ -11879,7 +11876,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="24.95">
+    <row r="7" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A7" s="90" t="s">
         <v>229</v>
       </c>
@@ -11902,7 +11899,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="24.95">
+    <row r="8" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A8" s="94" t="s">
         <v>231</v>
       </c>
@@ -11925,7 +11922,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.5" customHeight="1">
+    <row r="9" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="81" t="s">
         <v>260</v>
       </c>
@@ -11940,7 +11937,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="75">
+    <row r="12" spans="1:7" ht="75" x14ac:dyDescent="0.3">
       <c r="A12" s="75" t="s">
         <v>390</v>
       </c>
@@ -11959,7 +11956,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="50.1">
+    <row r="13" spans="1:7" ht="50" x14ac:dyDescent="0.3">
       <c r="A13" s="78" t="s">
         <v>379</v>
       </c>
@@ -11982,7 +11979,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="24.95">
+    <row r="14" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A14" s="81" t="s">
         <v>381</v>
       </c>
@@ -12005,7 +12002,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="24.95">
+    <row r="15" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A15" s="81" t="s">
         <v>384</v>
       </c>
@@ -12028,7 +12025,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="24.95">
+    <row r="16" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A16" s="81" t="s">
         <v>387</v>
       </c>
@@ -12051,7 +12048,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="24.95">
+    <row r="17" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A17" s="90" t="s">
         <v>226</v>
       </c>
@@ -12074,7 +12071,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="24.95">
+    <row r="18" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A18" s="90" t="s">
         <v>229</v>
       </c>
@@ -12097,7 +12094,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="24.95">
+    <row r="19" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A19" s="94" t="s">
         <v>231</v>
       </c>
@@ -12120,7 +12117,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="24.95">
+    <row r="20" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A20" s="81" t="s">
         <v>260</v>
       </c>
@@ -12135,7 +12132,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="75">
+    <row r="23" spans="1:9" ht="75" x14ac:dyDescent="0.3">
       <c r="A23" s="96" t="s">
         <v>393</v>
       </c>
@@ -12154,7 +12151,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="50.1">
+    <row r="24" spans="1:9" ht="50" x14ac:dyDescent="0.3">
       <c r="A24" s="78" t="s">
         <v>379</v>
       </c>
@@ -12180,7 +12177,7 @@
         <v>280000</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="24.95">
+    <row r="25" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A25" s="81" t="s">
         <v>381</v>
       </c>
@@ -12207,7 +12204,7 @@
         <v>835.52</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="24.95">
+    <row r="26" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A26" s="81" t="s">
         <v>384</v>
       </c>
@@ -12230,7 +12227,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="24.95">
+    <row r="27" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A27" s="81" t="s">
         <v>387</v>
       </c>
@@ -12256,7 +12253,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="24.95">
+    <row r="28" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A28" s="90" t="s">
         <v>226</v>
       </c>
@@ -12279,7 +12276,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="24.95">
+    <row r="29" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A29" s="90" t="s">
         <v>229</v>
       </c>
@@ -12302,7 +12299,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="24.95">
+    <row r="30" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A30" s="94" t="s">
         <v>231</v>
       </c>
@@ -12325,7 +12322,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="24.95">
+    <row r="31" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A31" s="81" t="s">
         <v>260</v>
       </c>
@@ -12348,12 +12345,12 @@
         <v>389</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="24.95">
+    <row r="32" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A32" s="97" t="s">
+        <v>407</v>
+      </c>
+      <c r="B32" s="98" t="s">
         <v>398</v>
-      </c>
-      <c r="B32" s="98" t="s">
-        <v>399</v>
       </c>
       <c r="C32" s="98">
         <v>75</v>
@@ -12362,7 +12359,7 @@
         <v>60</v>
       </c>
       <c r="E32" s="98" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F32" s="98">
         <v>62</v>
@@ -12374,9 +12371,9 @@
         <v>397</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="24.95">
+    <row r="34" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A34" s="96" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B34" s="103" t="s">
         <v>147</v>
@@ -12393,7 +12390,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="50.1">
+    <row r="35" spans="1:8" ht="50" x14ac:dyDescent="0.3">
       <c r="A35" s="78" t="s">
         <v>379</v>
       </c>
@@ -12416,12 +12413,12 @@
         <v>380</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="24.95">
+    <row r="36" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A36" s="81" t="s">
         <v>381</v>
       </c>
       <c r="B36" s="82" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C36" s="83">
         <v>93</v>
@@ -12430,7 +12427,7 @@
         <v>40</v>
       </c>
       <c r="E36" s="82" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F36" s="83">
         <v>95</v>
@@ -12439,12 +12436,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="24.95">
+    <row r="37" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A37" s="81" t="s">
         <v>384</v>
       </c>
       <c r="B37" s="84" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C37" s="85">
         <v>94</v>
@@ -12452,8 +12449,8 @@
       <c r="D37" s="86">
         <v>40</v>
       </c>
-      <c r="E37" s="84">
-        <v>3000</v>
+      <c r="E37" s="84" t="s">
+        <v>386</v>
       </c>
       <c r="F37" s="85">
         <v>95</v>
@@ -12462,12 +12459,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="24.95">
+    <row r="38" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A38" s="81" t="s">
         <v>387</v>
       </c>
       <c r="B38" s="87" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C38" s="88">
         <v>79</v>
@@ -12476,7 +12473,7 @@
         <v>62</v>
       </c>
       <c r="E38" s="87" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F38" s="88">
         <v>80</v>
@@ -12488,7 +12485,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="24.95">
+    <row r="39" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A39" s="90" t="s">
         <v>226</v>
       </c>
@@ -12511,7 +12508,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="24.95">
+    <row r="40" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A40" s="90" t="s">
         <v>229</v>
       </c>
@@ -12534,7 +12531,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="24.95">
+    <row r="41" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A41" s="94" t="s">
         <v>231</v>
       </c>
@@ -12557,7 +12554,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="24.95">
+    <row r="42" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A42" s="81" t="s">
         <v>260</v>
       </c>
@@ -12571,7 +12568,7 @@
         <v>389</v>
       </c>
       <c r="E42" s="84" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F42" s="84">
         <v>75</v>
@@ -12580,12 +12577,12 @@
         <v>389</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="24.95">
+    <row r="43" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A43" s="97" t="s">
+        <v>407</v>
+      </c>
+      <c r="B43" s="98" t="s">
         <v>408</v>
-      </c>
-      <c r="B43" s="98" t="s">
-        <v>409</v>
       </c>
       <c r="C43" s="98">
         <v>77</v>
@@ -12594,7 +12591,7 @@
         <v>68</v>
       </c>
       <c r="E43" s="98" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F43" s="98">
         <v>75</v>
@@ -12606,9 +12603,9 @@
         <v>397</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="23.25">
+    <row r="45" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A45" s="101" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B45" s="103" t="s">
         <v>320</v>
@@ -12618,7 +12615,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="47.25">
+    <row r="46" spans="1:8" ht="50" x14ac:dyDescent="0.3">
       <c r="A46" s="78" t="s">
         <v>379</v>
       </c>
@@ -12632,12 +12629,12 @@
         <v>380</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="23.25">
+    <row r="47" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A47" s="81" t="s">
         <v>381</v>
       </c>
       <c r="B47" s="82" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C47" s="83">
         <v>93</v>
@@ -12646,12 +12643,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="23.25">
+    <row r="48" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A48" s="81" t="s">
         <v>384</v>
       </c>
       <c r="B48" s="84" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C48" s="85">
         <v>94</v>
@@ -12660,12 +12657,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="23.25">
+    <row r="49" spans="1:4" ht="25" x14ac:dyDescent="0.3">
       <c r="A49" s="81" t="s">
         <v>387</v>
       </c>
       <c r="B49" s="87" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C49" s="88">
         <v>80</v>
@@ -12674,7 +12671,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="23.25">
+    <row r="50" spans="1:4" ht="25" x14ac:dyDescent="0.3">
       <c r="A50" s="90" t="s">
         <v>226</v>
       </c>
@@ -12688,7 +12685,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="23.25">
+    <row r="51" spans="1:4" ht="25" x14ac:dyDescent="0.3">
       <c r="A51" s="90" t="s">
         <v>229</v>
       </c>
@@ -12702,7 +12699,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="23.25">
+    <row r="52" spans="1:4" ht="25" x14ac:dyDescent="0.3">
       <c r="A52" s="94" t="s">
         <v>231</v>
       </c>
@@ -12716,12 +12713,12 @@
         <v>228</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="23.25">
+    <row r="53" spans="1:4" ht="25" x14ac:dyDescent="0.3">
       <c r="A53" s="81" t="s">
         <v>260</v>
       </c>
       <c r="B53" s="102" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C53" s="87">
         <v>80</v>
@@ -12730,12 +12727,12 @@
         <v>389</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="23.25">
+    <row r="54" spans="1:4" ht="25" x14ac:dyDescent="0.3">
       <c r="A54" s="97" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B54" s="98" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C54" s="98">
         <v>77</v>
@@ -12763,16 +12760,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8EE6899-576B-F44E-A189-C616F2524B03}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="59.140625" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="1" max="1" width="59.1640625" customWidth="1"/>
+    <col min="2" max="2" width="35.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="60">
+    <row r="1" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A1" s="50" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>320</v>
@@ -12781,7 +12778,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.95">
+    <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>149</v>
       </c>
@@ -12790,340 +12787,340 @@
       </c>
       <c r="C2" s="40"/>
     </row>
-    <row r="3" spans="1:3" ht="18.95" hidden="1">
+    <row r="3" spans="1:3" ht="19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
-    <row r="4" spans="1:3" ht="15.95" hidden="1">
+    <row r="4" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3" ht="15.95" hidden="1">
+    <row r="5" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="57"/>
     </row>
-    <row r="6" spans="1:3" ht="15.95" hidden="1">
+    <row r="6" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:3" ht="15.95" hidden="1">
+    <row r="7" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:3" ht="15.95">
+    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>160</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C8" s="58" t="s">
         <v>418</v>
       </c>
-      <c r="C8" s="58" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.95">
+    </row>
+    <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>162</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C9" s="57" t="s">
         <v>420</v>
       </c>
-      <c r="C9" s="57" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.95" hidden="1">
+    </row>
+    <row r="10" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>164</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:3" ht="15.95" hidden="1">
+    <row r="11" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="57"/>
     </row>
-    <row r="12" spans="1:3" ht="15.95" hidden="1">
+    <row r="12" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>168</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:3" ht="15.95" hidden="1">
+    <row r="13" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="57"/>
     </row>
-    <row r="14" spans="1:3" ht="15.95" hidden="1">
+    <row r="14" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:3" ht="15.95" hidden="1">
+    <row r="15" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
-    <row r="16" spans="1:3" ht="15.95" hidden="1">
+    <row r="16" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>174</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:3" ht="15.95" hidden="1">
+    <row r="17" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:3" ht="15.95" hidden="1">
+    <row r="18" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:3" ht="15.95" hidden="1">
+    <row r="19" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>180</v>
       </c>
       <c r="B19" s="46"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:3" ht="15.95" hidden="1">
+    <row r="20" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="43" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
     </row>
-    <row r="21" spans="1:3" ht="18.95">
+    <row r="21" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
         <v>184</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="59"/>
     </row>
-    <row r="22" spans="1:3" ht="15.95" hidden="1">
+    <row r="22" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="22" t="s">
         <v>185</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="54"/>
     </row>
-    <row r="23" spans="1:3" ht="15.95">
+    <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>187</v>
       </c>
       <c r="B23" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="C23" s="56" t="s">
         <v>428</v>
       </c>
-      <c r="C23" s="56" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.95" hidden="1">
+    </row>
+    <row r="24" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>189</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="56"/>
     </row>
-    <row r="25" spans="1:3" ht="15.95">
+    <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>191</v>
       </c>
       <c r="B25" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="C25" s="56" t="s">
         <v>430</v>
       </c>
-      <c r="C25" s="56" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.95">
+    </row>
+    <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>193</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="C26" s="56" t="s">
         <v>432</v>
       </c>
-      <c r="C26" s="56" t="s">
+    </row>
+    <row r="27" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
         <v>433</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.95" hidden="1">
-      <c r="A27" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="56"/>
     </row>
-    <row r="28" spans="1:3" ht="15.95" hidden="1">
+    <row r="28" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>197</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="56"/>
     </row>
-    <row r="29" spans="1:3" ht="15.95" hidden="1">
+    <row r="29" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>199</v>
       </c>
       <c r="B29" s="10"/>
       <c r="C29" s="56"/>
     </row>
-    <row r="30" spans="1:3" ht="15.95" hidden="1">
+    <row r="30" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="56"/>
     </row>
-    <row r="31" spans="1:3" ht="15.95" hidden="1">
+    <row r="31" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="56"/>
     </row>
-    <row r="32" spans="1:3" ht="18.95" hidden="1">
+    <row r="32" spans="1:3" ht="19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
         <v>205</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="60"/>
     </row>
-    <row r="33" spans="1:3" ht="15.95" hidden="1">
+    <row r="33" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>208</v>
       </c>
       <c r="B33" s="47"/>
       <c r="C33" s="56"/>
     </row>
-    <row r="34" spans="1:3" ht="15.95" hidden="1">
+    <row r="34" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>211</v>
       </c>
       <c r="B34" s="47"/>
       <c r="C34" s="56"/>
     </row>
-    <row r="35" spans="1:3" ht="15.95" hidden="1">
+    <row r="35" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B35" s="47"/>
       <c r="C35" s="56"/>
     </row>
-    <row r="36" spans="1:3" ht="15.95" hidden="1">
+    <row r="36" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>187</v>
       </c>
       <c r="B36" s="47"/>
       <c r="C36" s="53"/>
     </row>
-    <row r="37" spans="1:3" ht="18.95">
+    <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
         <v>214</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="61"/>
     </row>
-    <row r="38" spans="1:3" ht="15.95" hidden="1">
+    <row r="38" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>215</v>
       </c>
       <c r="B38" s="48"/>
       <c r="C38" s="62"/>
     </row>
-    <row r="39" spans="1:3" ht="15.95" hidden="1">
+    <row r="39" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="62"/>
     </row>
-    <row r="40" spans="1:3" ht="15.95">
+    <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>218</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C40" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="C40" s="58" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.95">
+    </row>
+    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>219</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C41" s="58" t="s">
         <v>439</v>
       </c>
-      <c r="C41" s="58" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.95" hidden="1">
+    </row>
+    <row r="42" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="22" t="s">
         <v>220</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
     </row>
-    <row r="43" spans="1:3" ht="15.95" hidden="1">
+    <row r="43" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="22" t="s">
         <v>221</v>
       </c>
       <c r="B43" s="45"/>
       <c r="C43" s="15"/>
     </row>
-    <row r="44" spans="1:3" ht="15.95" hidden="1">
+    <row r="44" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>222</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="1:3" ht="15.95">
+    <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.95" hidden="1">
+    </row>
+    <row r="46" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>224</v>
       </c>
@@ -13138,124 +13135,124 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA07167-CEB4-F64B-93AF-8A8BA2B4D0FF}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="62.140625" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" customWidth="1"/>
-    <col min="3" max="3" width="40.7109375" customWidth="1"/>
+    <col min="1" max="1" width="62.1640625" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="81">
+    <row r="1" spans="1:4" ht="81" x14ac:dyDescent="0.2">
       <c r="A1" s="71" t="s">
+        <v>442</v>
+      </c>
+      <c r="B1" s="72" t="s">
         <v>443</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="C1" s="73" t="s">
         <v>444</v>
       </c>
-      <c r="C1" s="73" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+      <c r="A2" s="69" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="21.95">
-      <c r="A2" s="69" t="s">
+      <c r="B2" s="70" t="s">
         <v>446</v>
       </c>
-      <c r="B2" s="70" t="s">
+      <c r="C2" s="70" t="s">
         <v>447</v>
       </c>
-      <c r="C2" s="70" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+      <c r="A3" s="69" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="21.95">
-      <c r="A3" s="69" t="s">
+      <c r="B3" s="70" t="s">
         <v>449</v>
-      </c>
-      <c r="B3" s="70" t="s">
-        <v>450</v>
       </c>
       <c r="C3" s="70" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="21.95">
+    <row r="4" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A4" s="69" t="s">
+        <v>450</v>
+      </c>
+      <c r="B4" s="74" t="s">
         <v>451</v>
       </c>
-      <c r="B4" s="74" t="s">
+      <c r="C4" s="74" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+      <c r="A5" s="69" t="s">
         <v>452</v>
       </c>
-      <c r="C4" s="74" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="21.95">
-      <c r="A5" s="69" t="s">
+      <c r="B5" s="74" t="s">
+        <v>451</v>
+      </c>
+      <c r="C5" s="74" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+      <c r="A6" s="69" t="s">
         <v>453</v>
       </c>
-      <c r="B5" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="C5" s="74" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="21.95">
-      <c r="A6" s="69" t="s">
+      <c r="B6" s="70" t="s">
         <v>454</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="C6" s="70" t="s">
         <v>455</v>
       </c>
-      <c r="C6" s="70" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+      <c r="A7" s="69" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="21.95">
-      <c r="A7" s="69" t="s">
+      <c r="B7" s="70" t="s">
         <v>457</v>
       </c>
-      <c r="B7" s="70" t="s">
+      <c r="C7" s="70" t="s">
         <v>458</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="D7" t="s">
         <v>459</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+      <c r="A8" s="69" t="s">
         <v>460</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="21.95">
-      <c r="A8" s="69" t="s">
-        <v>461</v>
       </c>
       <c r="B8" s="70" t="s">
         <v>331</v>
       </c>
       <c r="C8" s="70" t="s">
+        <v>461</v>
+      </c>
+      <c r="D8" t="s">
         <v>462</v>
       </c>
-      <c r="D8" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+      <c r="A9" s="69" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="21.95">
-      <c r="A9" s="69" t="s">
+      <c r="B9" s="70" t="s">
         <v>464</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="C9" s="70" t="s">
         <v>465</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="D9" t="s">
         <v>466</v>
       </c>
-      <c r="D9" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="22" x14ac:dyDescent="0.25">
+      <c r="A10" s="69" t="s">
         <v>467</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="21.95">
-      <c r="A10" s="69" t="s">
-        <v>468</v>
       </c>
       <c r="B10" s="70">
         <v>26000</v>
@@ -13264,9 +13261,9 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="21.95">
+    <row r="11" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A11" s="69" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B11" s="70">
         <v>445</v>
@@ -13275,9 +13272,9 @@
         <v>371</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="21.95">
+    <row r="12" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A12" s="69" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B12" s="70">
         <v>96000</v>
@@ -13286,9 +13283,9 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="21.95">
+    <row r="13" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A13" s="69" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B13" s="70">
         <v>400000</v>
@@ -13297,9 +13294,9 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="21.95">
+    <row r="14" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A14" s="69" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B14" s="70">
         <v>200000</v>
@@ -13314,6 +13311,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010092711BC64AAEC84E9EF800276F1AD52C" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba397f1440615f1339f1f20b24e67478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9bf4d24f-a117-48f7-91e1-2035a8c734fd" xmlns:ns3="0b7692b1-2532-40e4-a300-4d7fced4a07a" xmlns:ns4="cb645b5b-9a36-43da-96bf-ab72ec91ddff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74828cee37efa74eab9b700f6a6651cc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
@@ -13561,20 +13572,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -13674,17 +13671,49 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
+    <ds:schemaRef ds:uri="0b7692b1-2532-40e4-a300-4d7fced4a07a"/>
+    <ds:schemaRef ds:uri="cb645b5b-9a36-43da-96bf-ab72ec91ddff"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
+    <ds:schemaRef ds:uri="cb645b5b-9a36-43da-96bf-ab72ec91ddff"/>
+    <ds:schemaRef ds:uri="0b7692b1-2532-40e4-a300-4d7fced4a07a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1079" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3985839-A7F9-4804-B5B4-D23BC972D3EA}"/>
+  <xr:revisionPtr revIDLastSave="1099" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B2F7B2B-B4A1-4689-9167-404DC0019984}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19740" firstSheet="3" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21340" firstSheet="5" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="504">
   <si>
     <t>number</t>
   </si>
@@ -1422,6 +1422,18 @@
     <t>348 CPS</t>
   </si>
   <si>
+    <t>Release: 25.4X300-202607080112.0-EVO</t>
+  </si>
+  <si>
+    <t>200 CPS / 110 Mbps</t>
+  </si>
+  <si>
+    <t>649 KPPS / 437 Mbps</t>
+  </si>
+  <si>
+    <t>740 KPPS/497 Mbps</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1647,12 +1659,322 @@
   <si>
     <t>Route table size (FIB) (IPv4)</t>
   </si>
+  <si>
+    <t>Data Sheet</t>
+  </si>
+  <si>
+    <t>Features- Branch SRX</t>
+  </si>
+  <si>
+    <t>Firewall- packet mode throughput (IMIX) (Mbps)</t>
+  </si>
+  <si>
+    <r>
+      <t>Firewall throughput (IMIX)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (Mbps)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Firewall throughput (1518B)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (Mbps)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>IPSec VPN throughput (IMIX)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (Mbps)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>IPSec VPN throughput (1400B)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (Mbps)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Application Control Performance (CPS</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) (Mbps)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Next-Generation Firewall (CPS</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (Mbps)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Secure Web Access Firewall (CPS</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (Mbps)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Advanced Threat (CPS</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (Mbps)</t>
+    </r>
+  </si>
+  <si>
+    <t>Connections Per Second (64B)</t>
+  </si>
+  <si>
+    <t>            20,000 </t>
+  </si>
+  <si>
+    <t>            25,000</t>
+  </si>
+  <si>
+    <t>Maximum Concurrent Sessions (IPv4 or IPv6)</t>
+  </si>
+  <si>
+    <t>            65,000 </t>
+  </si>
+  <si>
+    <t>            85,000</t>
+  </si>
+  <si>
+    <t>Route table size (RIB/FIB) (IPv4)</t>
+  </si>
+  <si>
+    <t>300K/150K</t>
+  </si>
+  <si>
+    <t>350K/175K</t>
+  </si>
+  <si>
+    <t>IPSec VPN tunnels</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1844,6 +2166,22 @@
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2110,7 +2448,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2397,16 +2735,17 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8883,10 +9222,10 @@
       <c r="A1" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="105"/>
+      <c r="C1" s="104"/>
       <c r="D1" s="36" t="s">
         <v>148</v>
       </c>
@@ -10297,10 +10636,10 @@
       <c r="A1" s="50" t="s">
         <v>319</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="103" t="s">
         <v>320</v>
       </c>
-      <c r="C1" s="105"/>
+      <c r="C1" s="104"/>
       <c r="D1" s="36" t="s">
         <v>148</v>
       </c>
@@ -11741,7 +12080,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1F4FD9-0BA8-D443-A42F-4E5E606C52A0}">
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr defaultColWidth="62.42578125" defaultRowHeight="24"/>
   <cols>
     <col min="1" max="1" width="162.42578125" style="77" customWidth="1"/>
@@ -11758,17 +12097,17 @@
       <c r="A1" s="75" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="102" t="s">
+      <c r="B1" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="103"/>
+      <c r="C1" s="106"/>
       <c r="D1" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="102" t="s">
+      <c r="E1" s="105" t="s">
         <v>320</v>
       </c>
-      <c r="F1" s="103"/>
+      <c r="F1" s="106"/>
       <c r="G1" s="76" t="s">
         <v>148</v>
       </c>
@@ -11953,17 +12292,17 @@
       <c r="A12" s="75" t="s">
         <v>390</v>
       </c>
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="103"/>
+      <c r="C12" s="106"/>
       <c r="D12" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="105" t="s">
         <v>320</v>
       </c>
-      <c r="F12" s="103"/>
+      <c r="F12" s="106"/>
       <c r="G12" s="76" t="s">
         <v>148</v>
       </c>
@@ -12148,17 +12487,17 @@
       <c r="A23" s="96" t="s">
         <v>393</v>
       </c>
-      <c r="B23" s="102" t="s">
+      <c r="B23" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="C23" s="103"/>
+      <c r="C23" s="106"/>
       <c r="D23" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="E23" s="102" t="s">
+      <c r="E23" s="105" t="s">
         <v>320</v>
       </c>
-      <c r="F23" s="103"/>
+      <c r="F23" s="106"/>
       <c r="G23" s="76" t="s">
         <v>148</v>
       </c>
@@ -12357,7 +12696,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="23.25">
+    <row r="32" spans="1:9" ht="24.95">
       <c r="A32" s="97" t="s">
         <v>398</v>
       </c>
@@ -12387,17 +12726,17 @@
       <c r="A34" s="96" t="s">
         <v>401</v>
       </c>
-      <c r="B34" s="102" t="s">
+      <c r="B34" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="C34" s="103"/>
+      <c r="C34" s="106"/>
       <c r="D34" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="E34" s="102" t="s">
+      <c r="E34" s="105" t="s">
         <v>320</v>
       </c>
-      <c r="F34" s="103"/>
+      <c r="F34" s="106"/>
       <c r="G34" s="76" t="s">
         <v>148</v>
       </c>
@@ -12619,10 +12958,10 @@
       <c r="A45" s="96" t="s">
         <v>410</v>
       </c>
-      <c r="B45" s="102" t="s">
+      <c r="B45" s="105" t="s">
         <v>320</v>
       </c>
-      <c r="C45" s="103"/>
+      <c r="C45" s="106"/>
       <c r="D45" s="76" t="s">
         <v>148</v>
       </c>
@@ -12757,17 +13096,17 @@
       <c r="A56" s="96" t="s">
         <v>412</v>
       </c>
-      <c r="B56" s="102" t="s">
+      <c r="B56" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="C56" s="103"/>
+      <c r="C56" s="106"/>
       <c r="D56" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="E56" s="102" t="s">
+      <c r="E56" s="105" t="s">
         <v>320</v>
       </c>
-      <c r="F56" s="103"/>
+      <c r="F56" s="106"/>
       <c r="G56" s="76" t="s">
         <v>148</v>
       </c>
@@ -12979,8 +13318,216 @@
         <v>70</v>
       </c>
     </row>
+    <row r="68" spans="1:7" ht="23.25">
+      <c r="A68" s="96" t="s">
+        <v>419</v>
+      </c>
+      <c r="B68" s="105" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68" s="106"/>
+      <c r="D68" s="76" t="s">
+        <v>148</v>
+      </c>
+      <c r="E68" s="105" t="s">
+        <v>320</v>
+      </c>
+      <c r="F68" s="106"/>
+      <c r="G68" s="76" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="47.25">
+      <c r="A69" s="78" t="s">
+        <v>379</v>
+      </c>
+      <c r="B69" s="79" t="s">
+        <v>336</v>
+      </c>
+      <c r="C69" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="D69" s="79" t="s">
+        <v>380</v>
+      </c>
+      <c r="E69" s="79" t="s">
+        <v>336</v>
+      </c>
+      <c r="F69" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="G69" s="79" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="23.25">
+      <c r="A70" s="81" t="s">
+        <v>381</v>
+      </c>
+      <c r="B70" s="82" t="s">
+        <v>382</v>
+      </c>
+      <c r="C70" s="83">
+        <v>94</v>
+      </c>
+      <c r="D70" s="84">
+        <v>70</v>
+      </c>
+      <c r="E70" s="82" t="s">
+        <v>413</v>
+      </c>
+      <c r="F70" s="83">
+        <v>95</v>
+      </c>
+      <c r="G70" s="84">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="23.25">
+      <c r="A71" s="81" t="s">
+        <v>384</v>
+      </c>
+      <c r="B71" s="84" t="s">
+        <v>414</v>
+      </c>
+      <c r="C71" s="85">
+        <v>94</v>
+      </c>
+      <c r="D71" s="86">
+        <v>70</v>
+      </c>
+      <c r="E71" s="84">
+        <v>3020</v>
+      </c>
+      <c r="F71" s="85">
+        <v>95</v>
+      </c>
+      <c r="G71" s="86">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="23.25">
+      <c r="A72" s="81" t="s">
+        <v>387</v>
+      </c>
+      <c r="B72" s="87" t="s">
+        <v>415</v>
+      </c>
+      <c r="C72" s="88">
+        <v>79</v>
+      </c>
+      <c r="D72" s="89">
+        <v>70</v>
+      </c>
+      <c r="E72" s="87" t="s">
+        <v>420</v>
+      </c>
+      <c r="F72" s="88">
+        <v>80</v>
+      </c>
+      <c r="G72" s="89">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="23.25">
+      <c r="A73" s="90" t="s">
+        <v>226</v>
+      </c>
+      <c r="B73" s="84" t="s">
+        <v>421</v>
+      </c>
+      <c r="C73" s="91">
+        <v>99</v>
+      </c>
+      <c r="D73" s="92" t="s">
+        <v>228</v>
+      </c>
+      <c r="E73" s="84" t="s">
+        <v>422</v>
+      </c>
+      <c r="F73" s="84">
+        <v>99</v>
+      </c>
+      <c r="G73" s="92" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="23.25">
+      <c r="A74" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="B74" s="84" t="s">
+        <v>230</v>
+      </c>
+      <c r="C74" s="93">
+        <v>99</v>
+      </c>
+      <c r="D74" s="92" t="s">
+        <v>228</v>
+      </c>
+      <c r="E74" s="84" t="s">
+        <v>351</v>
+      </c>
+      <c r="F74" s="84">
+        <v>99</v>
+      </c>
+      <c r="G74" s="92" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="23.25">
+      <c r="A75" s="94" t="s">
+        <v>231</v>
+      </c>
+      <c r="B75" s="87" t="s">
+        <v>232</v>
+      </c>
+      <c r="C75" s="88">
+        <v>90</v>
+      </c>
+      <c r="D75" s="92" t="s">
+        <v>228</v>
+      </c>
+      <c r="E75" s="84" t="s">
+        <v>352</v>
+      </c>
+      <c r="F75" s="84">
+        <v>96</v>
+      </c>
+      <c r="G75" s="89" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="23.25">
+      <c r="A76" s="81" t="s">
+        <v>260</v>
+      </c>
+      <c r="B76" s="87"/>
+      <c r="C76" s="87"/>
+      <c r="D76" s="95" t="s">
+        <v>389</v>
+      </c>
+      <c r="E76" s="84"/>
+      <c r="F76" s="84"/>
+      <c r="G76" s="95" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="23.25">
+      <c r="A77" s="97" t="s">
+        <v>398</v>
+      </c>
+      <c r="B77" s="98"/>
+      <c r="C77" s="98"/>
+      <c r="D77" s="98"/>
+      <c r="E77" s="98"/>
+      <c r="F77" s="98"/>
+      <c r="G77" s="98"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E68:F68"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="B12:C12"/>
@@ -13009,7 +13556,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60">
       <c r="A1" s="50" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>320</v>
@@ -13029,28 +13576,28 @@
     </row>
     <row r="3" spans="1:3" ht="18.95" hidden="1">
       <c r="A3" s="22" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:3" ht="15.95" hidden="1">
       <c r="A4" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" ht="15.95" hidden="1">
       <c r="A5" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="57"/>
     </row>
     <row r="6" spans="1:3" ht="15.95" hidden="1">
       <c r="A6" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -13067,10 +13614,10 @@
         <v>160</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.95">
@@ -13078,10 +13625,10 @@
         <v>162</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.95" hidden="1">
@@ -13093,7 +13640,7 @@
     </row>
     <row r="11" spans="1:3" ht="15.95" hidden="1">
       <c r="A11" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="57"/>
@@ -13114,14 +13661,14 @@
     </row>
     <row r="14" spans="1:3" ht="15.95" hidden="1">
       <c r="A14" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="15.95" hidden="1">
       <c r="A15" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -13135,14 +13682,14 @@
     </row>
     <row r="17" spans="1:3" ht="15.95" hidden="1">
       <c r="A17" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" ht="15.95" hidden="1">
       <c r="A18" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
@@ -13156,7 +13703,7 @@
     </row>
     <row r="20" spans="1:3" ht="15.95" hidden="1">
       <c r="A20" s="43" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -13180,10 +13727,10 @@
         <v>187</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C23" s="56" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.95" hidden="1">
@@ -13198,10 +13745,10 @@
         <v>191</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.95">
@@ -13209,15 +13756,15 @@
         <v>193</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.95" hidden="1">
       <c r="A27" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="56"/>
@@ -13238,14 +13785,14 @@
     </row>
     <row r="30" spans="1:3" ht="15.95" hidden="1">
       <c r="A30" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="56"/>
     </row>
     <row r="31" spans="1:3" ht="15.95" hidden="1">
       <c r="A31" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="56"/>
@@ -13311,10 +13858,10 @@
         <v>218</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.95">
@@ -13322,10 +13869,10 @@
         <v>219</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C41" s="58" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.95" hidden="1">
@@ -13354,10 +13901,10 @@
         <v>223</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.95" hidden="1">
@@ -13374,7 +13921,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA07167-CEB4-F64B-93AF-8A8BA2B4D0FF}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="62.140625" customWidth="1"/>
@@ -13384,32 +13931,32 @@
   <sheetData>
     <row r="1" spans="1:4" ht="81">
       <c r="A1" s="71" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B1" s="72" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C1" s="73" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21.95">
       <c r="A2" s="69" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B2" s="70" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C2" s="70" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21.95">
       <c r="A3" s="69" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B3" s="70" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C3" s="70" t="s">
         <v>232</v>
@@ -13417,82 +13964,82 @@
     </row>
     <row r="4" spans="1:4" ht="21.95">
       <c r="A4" s="69" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B4" s="74" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21.95">
       <c r="A5" s="69" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C5" s="74" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="21.95">
       <c r="A6" s="69" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B6" s="70" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="21.95">
       <c r="A7" s="69" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B7" s="70" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C7" s="70" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D7" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="21.95">
       <c r="A8" s="69" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B8" s="70" t="s">
         <v>331</v>
       </c>
       <c r="C8" s="70" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D8" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="21.95">
       <c r="A9" s="69" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B9" s="70" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C9" s="70" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D9" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="21.95">
       <c r="A10" s="69" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B10" s="70">
         <v>26000</v>
@@ -13503,7 +14050,7 @@
     </row>
     <row r="11" spans="1:4" ht="21.95">
       <c r="A11" s="69" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B11" s="70">
         <v>445</v>
@@ -13514,7 +14061,7 @@
     </row>
     <row r="12" spans="1:4" ht="21.95">
       <c r="A12" s="69" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B12" s="70">
         <v>96000</v>
@@ -13525,7 +14072,7 @@
     </row>
     <row r="13" spans="1:4" ht="21.95">
       <c r="A13" s="69" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B13" s="70">
         <v>400000</v>
@@ -13536,13 +14083,175 @@
     </row>
     <row r="14" spans="1:4" ht="21.95">
       <c r="A14" s="69" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B14" s="70">
         <v>200000</v>
       </c>
       <c r="C14" s="70">
         <v>150000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="B25" s="102" t="s">
+        <v>483</v>
+      </c>
+      <c r="C25" s="102" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="102" t="s">
+        <v>484</v>
+      </c>
+      <c r="B26" s="102" t="s">
+        <v>455</v>
+      </c>
+      <c r="C26" s="102" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>485</v>
+      </c>
+      <c r="B27">
+        <v>1100</v>
+      </c>
+      <c r="C27">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>486</v>
+      </c>
+      <c r="B28">
+        <v>1000</v>
+      </c>
+      <c r="C28">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>487</v>
+      </c>
+      <c r="B29">
+        <v>4500</v>
+      </c>
+      <c r="C29">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>488</v>
+      </c>
+      <c r="B30" t="s">
+        <v>462</v>
+      </c>
+      <c r="C30" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>489</v>
+      </c>
+      <c r="B31" t="s">
+        <v>462</v>
+      </c>
+      <c r="C31" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>490</v>
+      </c>
+      <c r="B32">
+        <v>650</v>
+      </c>
+      <c r="C32">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>491</v>
+      </c>
+      <c r="B33">
+        <v>350</v>
+      </c>
+      <c r="C33">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>492</v>
+      </c>
+      <c r="B34">
+        <v>300</v>
+      </c>
+      <c r="C34">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>493</v>
+      </c>
+      <c r="B35">
+        <v>150</v>
+      </c>
+      <c r="C35">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>494</v>
+      </c>
+      <c r="B36" t="s">
+        <v>495</v>
+      </c>
+      <c r="C36" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>497</v>
+      </c>
+      <c r="B37" t="s">
+        <v>498</v>
+      </c>
+      <c r="C37" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>500</v>
+      </c>
+      <c r="B38" t="s">
+        <v>501</v>
+      </c>
+      <c r="C38" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>503</v>
+      </c>
+      <c r="B39">
+        <v>128</v>
+      </c>
+      <c r="C39">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -13551,118 +14260,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cb645b5b-9a36-43da-96bf-ab72ec91ddff" xsi:nil="true"/>
-    <SharedWithUsers xmlns="0b7692b1-2532-40e4-a300-4d7fced4a07a">
-      <UserInfo>
-        <DisplayName>Anand Thulasiram</DisplayName>
-        <AccountId>2178</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Vipin Kumar</DisplayName>
-        <AccountId>64</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sunil  Masineni</DisplayName>
-        <AccountId>5184</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Geetha B K</DisplayName>
-        <AccountId>63</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jagadeesh Rajashekharaiah</DisplayName>
-        <AccountId>13</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Deepasri Chittala</DisplayName>
-        <AccountId>4801</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Weibin Chen</DisplayName>
-        <AccountId>317</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Xiaochen Tang</DisplayName>
-        <AccountId>910</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Anand Antur</DisplayName>
-        <AccountId>670</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Venu Maya</DisplayName>
-        <AccountId>33</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Chockalingam Balasubramanian</DisplayName>
-        <AccountId>682</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Neetu Rathee</DisplayName>
-        <AccountId>4709</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Prasad Shroff</DisplayName>
-        <AccountId>4142</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kedar Dhuru</DisplayName>
-        <AccountId>3907</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sarvesh Batta</DisplayName>
-        <AccountId>21</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Shankar Satyamurthy</DisplayName>
-        <AccountId>3116</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>David Passamonte</DisplayName>
-        <AccountId>5189</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010092711BC64AAEC84E9EF800276F1AD52C" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba397f1440615f1339f1f20b24e67478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9bf4d24f-a117-48f7-91e1-2035a8c734fd" xmlns:ns3="0b7692b1-2532-40e4-a300-4d7fced4a07a" xmlns:ns4="cb645b5b-9a36-43da-96bf-ab72ec91ddff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74828cee37efa74eab9b700f6a6651cc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
@@ -13910,18 +14507,130 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cb645b5b-9a36-43da-96bf-ab72ec91ddff" xsi:nil="true"/>
+    <SharedWithUsers xmlns="0b7692b1-2532-40e4-a300-4d7fced4a07a">
+      <UserInfo>
+        <DisplayName>Anand Thulasiram</DisplayName>
+        <AccountId>2178</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Vipin Kumar</DisplayName>
+        <AccountId>64</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sunil  Masineni</DisplayName>
+        <AccountId>5184</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Geetha B K</DisplayName>
+        <AccountId>63</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jagadeesh Rajashekharaiah</DisplayName>
+        <AccountId>13</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Deepasri Chittala</DisplayName>
+        <AccountId>4801</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Weibin Chen</DisplayName>
+        <AccountId>317</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Xiaochen Tang</DisplayName>
+        <AccountId>910</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Anand Antur</DisplayName>
+        <AccountId>670</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Venu Maya</DisplayName>
+        <AccountId>33</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Chockalingam Balasubramanian</DisplayName>
+        <AccountId>682</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Neetu Rathee</DisplayName>
+        <AccountId>4709</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Prasad Shroff</DisplayName>
+        <AccountId>4142</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kedar Dhuru</DisplayName>
+        <AccountId>3907</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sarvesh Batta</DisplayName>
+        <AccountId>21</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Shankar Satyamurthy</DisplayName>
+        <AccountId>3116</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>David Passamonte</DisplayName>
+        <AccountId>5189</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
 </file>
--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1099" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B2F7B2B-B4A1-4689-9167-404DC0019984}"/>
+  <xr:revisionPtr revIDLastSave="1109" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1753332-495D-47DA-82C3-6AF1FAFA2C4B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21340" firstSheet="5" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21340" firstSheet="3" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="506">
   <si>
     <t>number</t>
   </si>
@@ -1432,6 +1432,12 @@
   </si>
   <si>
     <t>740 KPPS/497 Mbps</t>
+  </si>
+  <si>
+    <t>308 CPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345 CPS </t>
   </si>
   <si>
     <r>
@@ -2736,16 +2742,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9222,10 +9228,10 @@
       <c r="A1" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="104"/>
+      <c r="C1" s="106"/>
       <c r="D1" s="36" t="s">
         <v>148</v>
       </c>
@@ -10636,10 +10642,10 @@
       <c r="A1" s="50" t="s">
         <v>319</v>
       </c>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="105" t="s">
         <v>320</v>
       </c>
-      <c r="C1" s="104"/>
+      <c r="C1" s="106"/>
       <c r="D1" s="36" t="s">
         <v>148</v>
       </c>
@@ -12097,17 +12103,17 @@
       <c r="A1" s="75" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="105" t="s">
+      <c r="B1" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="106"/>
+      <c r="C1" s="104"/>
       <c r="D1" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="105" t="s">
+      <c r="E1" s="103" t="s">
         <v>320</v>
       </c>
-      <c r="F1" s="106"/>
+      <c r="F1" s="104"/>
       <c r="G1" s="76" t="s">
         <v>148</v>
       </c>
@@ -12292,17 +12298,17 @@
       <c r="A12" s="75" t="s">
         <v>390</v>
       </c>
-      <c r="B12" s="105" t="s">
+      <c r="B12" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="106"/>
+      <c r="C12" s="104"/>
       <c r="D12" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="E12" s="105" t="s">
+      <c r="E12" s="103" t="s">
         <v>320</v>
       </c>
-      <c r="F12" s="106"/>
+      <c r="F12" s="104"/>
       <c r="G12" s="76" t="s">
         <v>148</v>
       </c>
@@ -12487,17 +12493,17 @@
       <c r="A23" s="96" t="s">
         <v>393</v>
       </c>
-      <c r="B23" s="105" t="s">
+      <c r="B23" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="C23" s="106"/>
+      <c r="C23" s="104"/>
       <c r="D23" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="E23" s="105" t="s">
+      <c r="E23" s="103" t="s">
         <v>320</v>
       </c>
-      <c r="F23" s="106"/>
+      <c r="F23" s="104"/>
       <c r="G23" s="76" t="s">
         <v>148</v>
       </c>
@@ -12726,17 +12732,17 @@
       <c r="A34" s="96" t="s">
         <v>401</v>
       </c>
-      <c r="B34" s="105" t="s">
+      <c r="B34" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="C34" s="106"/>
+      <c r="C34" s="104"/>
       <c r="D34" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="E34" s="105" t="s">
+      <c r="E34" s="103" t="s">
         <v>320</v>
       </c>
-      <c r="F34" s="106"/>
+      <c r="F34" s="104"/>
       <c r="G34" s="76" t="s">
         <v>148</v>
       </c>
@@ -12958,10 +12964,10 @@
       <c r="A45" s="96" t="s">
         <v>410</v>
       </c>
-      <c r="B45" s="105" t="s">
+      <c r="B45" s="103" t="s">
         <v>320</v>
       </c>
-      <c r="C45" s="106"/>
+      <c r="C45" s="104"/>
       <c r="D45" s="76" t="s">
         <v>148</v>
       </c>
@@ -13096,17 +13102,17 @@
       <c r="A56" s="96" t="s">
         <v>412</v>
       </c>
-      <c r="B56" s="105" t="s">
+      <c r="B56" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="C56" s="106"/>
+      <c r="C56" s="104"/>
       <c r="D56" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="E56" s="105" t="s">
+      <c r="E56" s="103" t="s">
         <v>320</v>
       </c>
-      <c r="F56" s="106"/>
+      <c r="F56" s="104"/>
       <c r="G56" s="76" t="s">
         <v>148</v>
       </c>
@@ -13322,17 +13328,17 @@
       <c r="A68" s="96" t="s">
         <v>419</v>
       </c>
-      <c r="B68" s="105" t="s">
+      <c r="B68" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="C68" s="106"/>
+      <c r="C68" s="104"/>
       <c r="D68" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="E68" s="105" t="s">
+      <c r="E68" s="103" t="s">
         <v>320</v>
       </c>
-      <c r="F68" s="106"/>
+      <c r="F68" s="104"/>
       <c r="G68" s="76" t="s">
         <v>148</v>
       </c>
@@ -13502,13 +13508,21 @@
       <c r="A76" s="81" t="s">
         <v>260</v>
       </c>
-      <c r="B76" s="87"/>
-      <c r="C76" s="87"/>
+      <c r="B76" s="87" t="s">
+        <v>272</v>
+      </c>
+      <c r="C76" s="87">
+        <v>80</v>
+      </c>
       <c r="D76" s="95" t="s">
         <v>389</v>
       </c>
-      <c r="E76" s="84"/>
-      <c r="F76" s="84"/>
+      <c r="E76" s="84" t="s">
+        <v>407</v>
+      </c>
+      <c r="F76" s="84">
+        <v>77</v>
+      </c>
       <c r="G76" s="95" t="s">
         <v>389</v>
       </c>
@@ -13517,12 +13531,24 @@
       <c r="A77" s="97" t="s">
         <v>398</v>
       </c>
-      <c r="B77" s="98"/>
-      <c r="C77" s="98"/>
-      <c r="D77" s="98"/>
-      <c r="E77" s="98"/>
-      <c r="F77" s="98"/>
-      <c r="G77" s="98"/>
+      <c r="B77" s="98" t="s">
+        <v>423</v>
+      </c>
+      <c r="C77" s="98">
+        <v>75</v>
+      </c>
+      <c r="D77" s="98">
+        <v>70</v>
+      </c>
+      <c r="E77" s="98" t="s">
+        <v>424</v>
+      </c>
+      <c r="F77" s="98">
+        <v>76</v>
+      </c>
+      <c r="G77" s="98">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -13556,7 +13582,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60">
       <c r="A1" s="50" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>320</v>
@@ -13576,28 +13602,28 @@
     </row>
     <row r="3" spans="1:3" ht="18.95" hidden="1">
       <c r="A3" s="22" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:3" ht="15.95" hidden="1">
       <c r="A4" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" ht="15.95" hidden="1">
       <c r="A5" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="57"/>
     </row>
     <row r="6" spans="1:3" ht="15.95" hidden="1">
       <c r="A6" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -13614,10 +13640,10 @@
         <v>160</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.95">
@@ -13625,10 +13651,10 @@
         <v>162</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.95" hidden="1">
@@ -13640,7 +13666,7 @@
     </row>
     <row r="11" spans="1:3" ht="15.95" hidden="1">
       <c r="A11" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="57"/>
@@ -13661,14 +13687,14 @@
     </row>
     <row r="14" spans="1:3" ht="15.95" hidden="1">
       <c r="A14" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="15.95" hidden="1">
       <c r="A15" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -13682,14 +13708,14 @@
     </row>
     <row r="17" spans="1:3" ht="15.95" hidden="1">
       <c r="A17" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" ht="15.95" hidden="1">
       <c r="A18" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
@@ -13703,7 +13729,7 @@
     </row>
     <row r="20" spans="1:3" ht="15.95" hidden="1">
       <c r="A20" s="43" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -13727,10 +13753,10 @@
         <v>187</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C23" s="56" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.95" hidden="1">
@@ -13745,10 +13771,10 @@
         <v>191</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.95">
@@ -13756,15 +13782,15 @@
         <v>193</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.95" hidden="1">
       <c r="A27" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="56"/>
@@ -13785,14 +13811,14 @@
     </row>
     <row r="30" spans="1:3" ht="15.95" hidden="1">
       <c r="A30" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="56"/>
     </row>
     <row r="31" spans="1:3" ht="15.95" hidden="1">
       <c r="A31" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="56"/>
@@ -13858,10 +13884,10 @@
         <v>218</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.95">
@@ -13869,10 +13895,10 @@
         <v>219</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C41" s="58" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.95" hidden="1">
@@ -13901,10 +13927,10 @@
         <v>223</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.95" hidden="1">
@@ -13931,32 +13957,32 @@
   <sheetData>
     <row r="1" spans="1:4" ht="81">
       <c r="A1" s="71" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B1" s="72" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C1" s="73" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21.95">
       <c r="A2" s="69" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B2" s="70" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C2" s="70" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21.95">
       <c r="A3" s="69" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B3" s="70" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C3" s="70" t="s">
         <v>232</v>
@@ -13964,82 +13990,82 @@
     </row>
     <row r="4" spans="1:4" ht="21.95">
       <c r="A4" s="69" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B4" s="74" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21.95">
       <c r="A5" s="69" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C5" s="74" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="21.95">
       <c r="A6" s="69" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B6" s="70" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="21.95">
       <c r="A7" s="69" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B7" s="70" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C7" s="70" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="21.95">
       <c r="A8" s="69" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B8" s="70" t="s">
         <v>331</v>
       </c>
       <c r="C8" s="70" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D8" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="21.95">
       <c r="A9" s="69" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B9" s="70" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C9" s="70" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D9" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="21.95">
       <c r="A10" s="69" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B10" s="70">
         <v>26000</v>
@@ -14050,7 +14076,7 @@
     </row>
     <row r="11" spans="1:4" ht="21.95">
       <c r="A11" s="69" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B11" s="70">
         <v>445</v>
@@ -14061,7 +14087,7 @@
     </row>
     <row r="12" spans="1:4" ht="21.95">
       <c r="A12" s="69" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B12" s="70">
         <v>96000</v>
@@ -14072,7 +14098,7 @@
     </row>
     <row r="13" spans="1:4" ht="21.95">
       <c r="A13" s="69" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B13" s="70">
         <v>400000</v>
@@ -14083,7 +14109,7 @@
     </row>
     <row r="14" spans="1:4" ht="21.95">
       <c r="A14" s="69" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B14" s="70">
         <v>200000</v>
@@ -14094,26 +14120,26 @@
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="102" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C25" s="102" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="102" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B26" s="102" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C26" s="102" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B27">
         <v>1100</v>
@@ -14124,7 +14150,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B28">
         <v>1000</v>
@@ -14135,7 +14161,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B29">
         <v>4500</v>
@@ -14146,29 +14172,29 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B30" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C30" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B32">
         <v>650</v>
@@ -14179,7 +14205,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B33">
         <v>350</v>
@@ -14190,7 +14216,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B34">
         <v>300</v>
@@ -14201,7 +14227,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B35">
         <v>150</v>
@@ -14212,40 +14238,40 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B36" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C36" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B37" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C37" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B38" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C38" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B39">
         <v>128</v>
@@ -14260,6 +14286,118 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cb645b5b-9a36-43da-96bf-ab72ec91ddff" xsi:nil="true"/>
+    <SharedWithUsers xmlns="0b7692b1-2532-40e4-a300-4d7fced4a07a">
+      <UserInfo>
+        <DisplayName>Anand Thulasiram</DisplayName>
+        <AccountId>2178</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Vipin Kumar</DisplayName>
+        <AccountId>64</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sunil  Masineni</DisplayName>
+        <AccountId>5184</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Geetha B K</DisplayName>
+        <AccountId>63</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jagadeesh Rajashekharaiah</DisplayName>
+        <AccountId>13</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Deepasri Chittala</DisplayName>
+        <AccountId>4801</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Weibin Chen</DisplayName>
+        <AccountId>317</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Xiaochen Tang</DisplayName>
+        <AccountId>910</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Anand Antur</DisplayName>
+        <AccountId>670</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Venu Maya</DisplayName>
+        <AccountId>33</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Chockalingam Balasubramanian</DisplayName>
+        <AccountId>682</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Neetu Rathee</DisplayName>
+        <AccountId>4709</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Prasad Shroff</DisplayName>
+        <AccountId>4142</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kedar Dhuru</DisplayName>
+        <AccountId>3907</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sarvesh Batta</DisplayName>
+        <AccountId>21</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Shankar Satyamurthy</DisplayName>
+        <AccountId>3116</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>David Passamonte</DisplayName>
+        <AccountId>5189</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010092711BC64AAEC84E9EF800276F1AD52C" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba397f1440615f1339f1f20b24e67478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9bf4d24f-a117-48f7-91e1-2035a8c734fd" xmlns:ns3="0b7692b1-2532-40e4-a300-4d7fced4a07a" xmlns:ns4="cb645b5b-9a36-43da-96bf-ab72ec91ddff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74828cee37efa74eab9b700f6a6651cc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
@@ -14507,130 +14645,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cb645b5b-9a36-43da-96bf-ab72ec91ddff" xsi:nil="true"/>
-    <SharedWithUsers xmlns="0b7692b1-2532-40e4-a300-4d7fced4a07a">
-      <UserInfo>
-        <DisplayName>Anand Thulasiram</DisplayName>
-        <AccountId>2178</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Vipin Kumar</DisplayName>
-        <AccountId>64</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sunil  Masineni</DisplayName>
-        <AccountId>5184</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Geetha B K</DisplayName>
-        <AccountId>63</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jagadeesh Rajashekharaiah</DisplayName>
-        <AccountId>13</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Deepasri Chittala</DisplayName>
-        <AccountId>4801</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Weibin Chen</DisplayName>
-        <AccountId>317</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Xiaochen Tang</DisplayName>
-        <AccountId>910</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Anand Antur</DisplayName>
-        <AccountId>670</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Venu Maya</DisplayName>
-        <AccountId>33</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Chockalingam Balasubramanian</DisplayName>
-        <AccountId>682</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Neetu Rathee</DisplayName>
-        <AccountId>4709</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Prasad Shroff</DisplayName>
-        <AccountId>4142</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kedar Dhuru</DisplayName>
-        <AccountId>3907</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sarvesh Batta</DisplayName>
-        <AccountId>21</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Shankar Satyamurthy</DisplayName>
-        <AccountId>3116</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>David Passamonte</DisplayName>
-        <AccountId>5189</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
 </file>
--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/antony-ruban_alexis_hpe_com/Documents/Microsoft Teams Chat Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sshivang/Downloads/Panther Sanity/public/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1109" documentId="8_{1A74DE8B-9E17-7342-8645-B5886219718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1753332-495D-47DA-82C3-6AF1FAFA2C4B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B488C47-373E-6E47-96E5-422DB83E3EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21340" firstSheet="3" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="508">
   <si>
     <t>number</t>
   </si>
@@ -1975,12 +1975,18 @@
   <si>
     <t>IPSec VPN tunnels</t>
   </si>
+  <si>
+    <t>320 KPPS / 950 Mbps</t>
+  </si>
+  <si>
+    <t>350 KPPS / 1040 Mbps</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2774,9 +2780,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2814,7 +2820,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2920,7 +2926,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3062,7 +3068,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3072,20 +3078,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{101F05EA-6A87-7646-9D66-36E81A856E36}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:I224"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="97.42578125" customWidth="1"/>
-    <col min="3" max="3" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.85546875" customWidth="1"/>
-    <col min="8" max="8" width="22.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97.5" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.1640625" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
         <v>0</v>
       </c>
@@ -3114,7 +3120,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1915273-1", "1915273-1")</f>
         <v>1915273-1</v>
@@ -3141,7 +3147,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1915273-2", "1915273-2")</f>
         <v>1915273-2</v>
@@ -3168,7 +3174,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1915273-3", "1915273-3")</f>
         <v>1915273-3</v>
@@ -3195,7 +3201,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1915273-4", "1915273-4")</f>
         <v>1915273-4</v>
@@ -3219,7 +3225,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926402-1", "1926402-1")</f>
         <v>1926402-1</v>
@@ -3246,7 +3252,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926402-2", "1926402-2")</f>
         <v>1926402-2</v>
@@ -3276,7 +3282,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926402-3", "1926402-3")</f>
         <v>1926402-3</v>
@@ -3306,7 +3312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926402-4", "1926402-4")</f>
         <v>1926402-4</v>
@@ -3330,7 +3336,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926405-1", "1926405-1")</f>
         <v>1926405-1</v>
@@ -3357,7 +3363,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926405-2", "1926405-2")</f>
         <v>1926405-2</v>
@@ -3384,7 +3390,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926405-3", "1926405-3")</f>
         <v>1926405-3</v>
@@ -3411,7 +3417,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926480-1", "1926480-1")</f>
         <v>1926480-1</v>
@@ -3441,7 +3447,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926480-2", "1926480-2")</f>
         <v>1926480-2</v>
@@ -3471,7 +3477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926480-3", "1926480-3")</f>
         <v>1926480-3</v>
@@ -3501,7 +3507,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926480-4", "1926480-4")</f>
         <v>1926480-4</v>
@@ -3531,7 +3537,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926480-5", "1926480-5")</f>
         <v>1926480-5</v>
@@ -3561,7 +3567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926694-1", "1926694-1")</f>
         <v>1926694-1</v>
@@ -3588,7 +3594,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926779-1", "1926779-1")</f>
         <v>1926779-1</v>
@@ -3615,7 +3621,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926779-2", "1926779-2")</f>
         <v>1926779-2</v>
@@ -3642,7 +3648,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1926779-3", "1926779-3")</f>
         <v>1926779-3</v>
@@ -3666,7 +3672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-1", "1932710-1")</f>
         <v>1932710-1</v>
@@ -3693,7 +3699,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-2", "1932710-2")</f>
         <v>1932710-2</v>
@@ -3720,7 +3726,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-3", "1932710-3")</f>
         <v>1932710-3</v>
@@ -3747,7 +3753,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-4", "1932710-4")</f>
         <v>1932710-4</v>
@@ -3771,7 +3777,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-5", "1932710-5")</f>
         <v>1932710-5</v>
@@ -3798,7 +3804,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-6", "1932710-6")</f>
         <v>1932710-6</v>
@@ -3825,7 +3831,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-7", "1932710-7")</f>
         <v>1932710-7</v>
@@ -3849,7 +3855,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-8", "1932710-8")</f>
         <v>1932710-8</v>
@@ -3879,7 +3885,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932710-9", "1932710-9")</f>
         <v>1932710-9</v>
@@ -3903,7 +3909,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932916-1", "1932916-1")</f>
         <v>1932916-1</v>
@@ -3930,7 +3936,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932916-2", "1932916-2")</f>
         <v>1932916-2</v>
@@ -3957,7 +3963,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932916-3", "1932916-3")</f>
         <v>1932916-3</v>
@@ -3984,7 +3990,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932916-4", "1932916-4")</f>
         <v>1932916-4</v>
@@ -4008,7 +4014,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1932916-5", "1932916-5")</f>
         <v>1932916-5</v>
@@ -4032,7 +4038,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933014-1", "1933014-1")</f>
         <v>1933014-1</v>
@@ -4059,7 +4065,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933014-2", "1933014-2")</f>
         <v>1933014-2</v>
@@ -4086,7 +4092,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933014-3", "1933014-3")</f>
         <v>1933014-3</v>
@@ -4113,7 +4119,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933014-4", "1933014-4")</f>
         <v>1933014-4</v>
@@ -4140,7 +4146,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933021-1", "1933021-1")</f>
         <v>1933021-1</v>
@@ -4167,7 +4173,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933021-2", "1933021-2")</f>
         <v>1933021-2</v>
@@ -4194,7 +4200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933021-3", "1933021-3")</f>
         <v>1933021-3</v>
@@ -4221,7 +4227,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933163-1", "1933163-1")</f>
         <v>1933163-1</v>
@@ -4248,7 +4254,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933163-2", "1933163-2")</f>
         <v>1933163-2</v>
@@ -4275,7 +4281,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933163-3", "1933163-3")</f>
         <v>1933163-3</v>
@@ -4302,7 +4308,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933192-1", "1933192-1")</f>
         <v>1933192-1</v>
@@ -4329,7 +4335,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933192-2", "1933192-2")</f>
         <v>1933192-2</v>
@@ -4356,7 +4362,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933192-3", "1933192-3")</f>
         <v>1933192-3</v>
@@ -4383,7 +4389,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-1", "1933195-1")</f>
         <v>1933195-1</v>
@@ -4410,7 +4416,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-2", "1933195-2")</f>
         <v>1933195-2</v>
@@ -4437,7 +4443,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-3", "1933195-3")</f>
         <v>1933195-3</v>
@@ -4464,7 +4470,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-4", "1933195-4")</f>
         <v>1933195-4</v>
@@ -4491,7 +4497,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-5", "1933195-5")</f>
         <v>1933195-5</v>
@@ -4518,7 +4524,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-6", "1933195-6")</f>
         <v>1933195-6</v>
@@ -4542,7 +4548,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933195-7", "1933195-7")</f>
         <v>1933195-7</v>
@@ -4572,7 +4578,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933636-1", "1933636-1")</f>
         <v>1933636-1</v>
@@ -4599,7 +4605,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933636-2", "1933636-2")</f>
         <v>1933636-2</v>
@@ -4626,7 +4632,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933636-3", "1933636-3")</f>
         <v>1933636-3</v>
@@ -4653,7 +4659,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933957-1", "1933957-1")</f>
         <v>1933957-1</v>
@@ -4680,7 +4686,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933957-2", "1933957-2")</f>
         <v>1933957-2</v>
@@ -4707,7 +4713,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933957-3", "1933957-3")</f>
         <v>1933957-3</v>
@@ -4734,7 +4740,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933971-1", "1933971-1")</f>
         <v>1933971-1</v>
@@ -4764,7 +4770,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933971-2", "1933971-2")</f>
         <v>1933971-2</v>
@@ -4794,7 +4800,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1933971-3", "1933971-3")</f>
         <v>1933971-3</v>
@@ -4824,7 +4830,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934311-1", "1934311-1")</f>
         <v>1934311-1</v>
@@ -4851,7 +4857,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934311-2", "1934311-2")</f>
         <v>1934311-2</v>
@@ -4878,7 +4884,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934311-3", "1934311-3")</f>
         <v>1934311-3</v>
@@ -4905,7 +4911,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934311-4", "1934311-4")</f>
         <v>1934311-4</v>
@@ -4932,7 +4938,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934315-1", "1934315-1")</f>
         <v>1934315-1</v>
@@ -4962,7 +4968,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934315-2", "1934315-2")</f>
         <v>1934315-2</v>
@@ -4992,7 +4998,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1934315-3", "1934315-3")</f>
         <v>1934315-3</v>
@@ -5022,7 +5028,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1935848-1", "1935848-1")</f>
         <v>1935848-1</v>
@@ -5049,7 +5055,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1935848-2", "1935848-2")</f>
         <v>1935848-2</v>
@@ -5076,7 +5082,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1935848-3", "1935848-3")</f>
         <v>1935848-3</v>
@@ -5103,7 +5109,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1936810-1", "1936810-1")</f>
         <v>1936810-1</v>
@@ -5130,7 +5136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1936810-2", "1936810-2")</f>
         <v>1936810-2</v>
@@ -5157,7 +5163,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1936810-3", "1936810-3")</f>
         <v>1936810-3</v>
@@ -5184,7 +5190,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937041-1", "1937041-1")</f>
         <v>1937041-1</v>
@@ -5211,7 +5217,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937041-2", "1937041-2")</f>
         <v>1937041-2</v>
@@ -5238,7 +5244,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937041-3", "1937041-3")</f>
         <v>1937041-3</v>
@@ -5265,7 +5271,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937045-1", "1937045-1")</f>
         <v>1937045-1</v>
@@ -5292,7 +5298,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937045-2", "1937045-2")</f>
         <v>1937045-2</v>
@@ -5319,7 +5325,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937045-3", "1937045-3")</f>
         <v>1937045-3</v>
@@ -5346,7 +5352,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937124-1", "1937124-1")</f>
         <v>1937124-1</v>
@@ -5373,7 +5379,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937124-2", "1937124-2")</f>
         <v>1937124-2</v>
@@ -5400,7 +5406,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937124-3", "1937124-3")</f>
         <v>1937124-3</v>
@@ -5427,7 +5433,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937537-1", "1937537-1")</f>
         <v>1937537-1</v>
@@ -5457,7 +5463,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937537-2", "1937537-2")</f>
         <v>1937537-2</v>
@@ -5487,7 +5493,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937537-3", "1937537-3")</f>
         <v>1937537-3</v>
@@ -5517,7 +5523,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937949-1", "1937949-1")</f>
         <v>1937949-1</v>
@@ -5547,7 +5553,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937949-2", "1937949-2")</f>
         <v>1937949-2</v>
@@ -5574,7 +5580,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937949-3", "1937949-3")</f>
         <v>1937949-3</v>
@@ -5598,7 +5604,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937949-4", "1937949-4")</f>
         <v>1937949-4</v>
@@ -5628,7 +5634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937950-1", "1937950-1")</f>
         <v>1937950-1</v>
@@ -5658,7 +5664,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937950-2", "1937950-2")</f>
         <v>1937950-2</v>
@@ -5685,7 +5691,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1937950-3", "1937950-3")</f>
         <v>1937950-3</v>
@@ -5709,7 +5715,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-1", "1938096-1")</f>
         <v>1938096-1</v>
@@ -5739,7 +5745,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-2", "1938096-2")</f>
         <v>1938096-2</v>
@@ -5769,7 +5775,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-3", "1938096-3")</f>
         <v>1938096-3</v>
@@ -5799,7 +5805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-4", "1938096-4")</f>
         <v>1938096-4</v>
@@ -5826,7 +5832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-5", "1938096-5")</f>
         <v>1938096-5</v>
@@ -5856,7 +5862,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938096-6", "1938096-6")</f>
         <v>1938096-6</v>
@@ -5883,7 +5889,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938163-1", "1938163-1")</f>
         <v>1938163-1</v>
@@ -5913,7 +5919,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938163-2", "1938163-2")</f>
         <v>1938163-2</v>
@@ -5940,7 +5946,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938163-3", "1938163-3")</f>
         <v>1938163-3</v>
@@ -5967,7 +5973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938163-4", "1938163-4")</f>
         <v>1938163-4</v>
@@ -5994,7 +6000,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938163-5", "1938163-5")</f>
         <v>1938163-5</v>
@@ -6021,7 +6027,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-1", "1938166-1")</f>
         <v>1938166-1</v>
@@ -6051,7 +6057,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-2", "1938166-2")</f>
         <v>1938166-2</v>
@@ -6078,7 +6084,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-3", "1938166-3")</f>
         <v>1938166-3</v>
@@ -6105,7 +6111,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-4", "1938166-4")</f>
         <v>1938166-4</v>
@@ -6132,7 +6138,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-5", "1938166-5")</f>
         <v>1938166-5</v>
@@ -6162,7 +6168,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-6", "1938166-6")</f>
         <v>1938166-6</v>
@@ -6186,7 +6192,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-7", "1938166-7")</f>
         <v>1938166-7</v>
@@ -6213,7 +6219,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938166-8", "1938166-8")</f>
         <v>1938166-8</v>
@@ -6240,7 +6246,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-1", "1938338-1")</f>
         <v>1938338-1</v>
@@ -6267,7 +6273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-2", "1938338-2")</f>
         <v>1938338-2</v>
@@ -6294,7 +6300,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-3", "1938338-3")</f>
         <v>1938338-3</v>
@@ -6321,7 +6327,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-4", "1938338-4")</f>
         <v>1938338-4</v>
@@ -6348,7 +6354,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-5", "1938338-5")</f>
         <v>1938338-5</v>
@@ -6378,7 +6384,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938338-6", "1938338-6")</f>
         <v>1938338-6</v>
@@ -6405,7 +6411,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938381-1", "1938381-1")</f>
         <v>1938381-1</v>
@@ -6432,7 +6438,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938381-2", "1938381-2")</f>
         <v>1938381-2</v>
@@ -6459,7 +6465,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938384-1", "1938384-1")</f>
         <v>1938384-1</v>
@@ -6486,7 +6492,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938384-2", "1938384-2")</f>
         <v>1938384-2</v>
@@ -6513,7 +6519,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938384-3", "1938384-3")</f>
         <v>1938384-3</v>
@@ -6540,7 +6546,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938500-1", "1938500-1")</f>
         <v>1938500-1</v>
@@ -6567,7 +6573,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938500-2", "1938500-2")</f>
         <v>1938500-2</v>
@@ -6594,7 +6600,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938500-3", "1938500-3")</f>
         <v>1938500-3</v>
@@ -6621,7 +6627,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938500-4", "1938500-4")</f>
         <v>1938500-4</v>
@@ -6648,7 +6654,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938573-1", "1938573-1")</f>
         <v>1938573-1</v>
@@ -6675,7 +6681,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1938573-2", "1938573-2")</f>
         <v>1938573-2</v>
@@ -6702,7 +6708,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940432-1", "1940432-1")</f>
         <v>1940432-1</v>
@@ -6729,7 +6735,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940432-2", "1940432-2")</f>
         <v>1940432-2</v>
@@ -6756,7 +6762,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-1", "1940444-1")</f>
         <v>1940444-1</v>
@@ -6783,7 +6789,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-2", "1940444-2")</f>
         <v>1940444-2</v>
@@ -6810,7 +6816,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-3", "1940444-3")</f>
         <v>1940444-3</v>
@@ -6837,7 +6843,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-4", "1940444-4")</f>
         <v>1940444-4</v>
@@ -6864,7 +6870,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-5", "1940444-5")</f>
         <v>1940444-5</v>
@@ -6888,7 +6894,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-6", "1940444-6")</f>
         <v>1940444-6</v>
@@ -6918,7 +6924,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-7", "1940444-7")</f>
         <v>1940444-7</v>
@@ -6942,7 +6948,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-8", "1940444-8")</f>
         <v>1940444-8</v>
@@ -6966,7 +6972,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940444-9", "1940444-9")</f>
         <v>1940444-9</v>
@@ -6990,7 +6996,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-1", "1940445-1")</f>
         <v>1940445-1</v>
@@ -7017,7 +7023,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-2", "1940445-2")</f>
         <v>1940445-2</v>
@@ -7044,7 +7050,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-3", "1940445-3")</f>
         <v>1940445-3</v>
@@ -7071,7 +7077,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-4", "1940445-4")</f>
         <v>1940445-4</v>
@@ -7101,7 +7107,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-5", "1940445-5")</f>
         <v>1940445-5</v>
@@ -7128,7 +7134,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-6", "1940445-6")</f>
         <v>1940445-6</v>
@@ -7155,7 +7161,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-7", "1940445-7")</f>
         <v>1940445-7</v>
@@ -7182,7 +7188,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940445-8", "1940445-8")</f>
         <v>1940445-8</v>
@@ -7209,7 +7215,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-1", "1940446-1")</f>
         <v>1940446-1</v>
@@ -7236,7 +7242,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-2", "1940446-2")</f>
         <v>1940446-2</v>
@@ -7263,7 +7269,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-3", "1940446-3")</f>
         <v>1940446-3</v>
@@ -7290,7 +7296,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-4", "1940446-4")</f>
         <v>1940446-4</v>
@@ -7317,7 +7323,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-5", "1940446-5")</f>
         <v>1940446-5</v>
@@ -7344,7 +7350,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-6", "1940446-6")</f>
         <v>1940446-6</v>
@@ -7374,7 +7380,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-7", "1940446-7")</f>
         <v>1940446-7</v>
@@ -7401,7 +7407,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-8", "1940446-8")</f>
         <v>1940446-8</v>
@@ -7425,7 +7431,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-9", "1940446-9")</f>
         <v>1940446-9</v>
@@ -7452,7 +7458,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-10", "1940446-10")</f>
         <v>1940446-10</v>
@@ -7476,7 +7482,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-1", "1942363-1")</f>
         <v>1942363-1</v>
@@ -7503,7 +7509,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-2", "1942363-2")</f>
         <v>1942363-2</v>
@@ -7530,7 +7536,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-3", "1942363-3")</f>
         <v>1942363-3</v>
@@ -7557,7 +7563,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-4", "1942363-4")</f>
         <v>1942363-4</v>
@@ -7584,7 +7590,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942376-1", "1942376-1")</f>
         <v>1942376-1</v>
@@ -7611,7 +7617,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942376-2", "1942376-2")</f>
         <v>1942376-2</v>
@@ -7638,7 +7644,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-1", "1943082-1")</f>
         <v>1943082-1</v>
@@ -7665,7 +7671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-2", "1943082-2")</f>
         <v>1943082-2</v>
@@ -7692,7 +7698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-3", "1943082-3")</f>
         <v>1943082-3</v>
@@ -7719,7 +7725,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-4", "1943082-4")</f>
         <v>1943082-4</v>
@@ -7746,7 +7752,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-1", "1943084-1")</f>
         <v>1943084-1</v>
@@ -7773,7 +7779,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-2", "1943084-2")</f>
         <v>1943084-2</v>
@@ -7800,7 +7806,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-3", "1943084-3")</f>
         <v>1943084-3</v>
@@ -7824,7 +7830,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-4", "1943084-4")</f>
         <v>1943084-4</v>
@@ -7851,7 +7857,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943461-1", "1943461-1")</f>
         <v>1943461-1</v>
@@ -7878,7 +7884,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943461-2", "1943461-2")</f>
         <v>1943461-2</v>
@@ -7905,7 +7911,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-1", "1943467-1")</f>
         <v>1943467-1</v>
@@ -7932,7 +7938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-2", "1943467-2")</f>
         <v>1943467-2</v>
@@ -7959,7 +7965,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-3", "1943467-3")</f>
         <v>1943467-3</v>
@@ -7986,7 +7992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-4", "1943467-4")</f>
         <v>1943467-4</v>
@@ -8013,7 +8019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-5", "1943467-5")</f>
         <v>1943467-5</v>
@@ -8043,7 +8049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-1", "1943607-1")</f>
         <v>1943607-1</v>
@@ -8073,7 +8079,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-2", "1943607-2")</f>
         <v>1943607-2</v>
@@ -8103,7 +8109,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-3", "1943607-3")</f>
         <v>1943607-3</v>
@@ -8127,7 +8133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946082-1", "1946082-1")</f>
         <v>1946082-1</v>
@@ -8154,7 +8160,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946082-2", "1946082-2")</f>
         <v>1946082-2</v>
@@ -8181,7 +8187,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-1", "1946085-1")</f>
         <v>1946085-1</v>
@@ -8211,7 +8217,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-2", "1946085-2")</f>
         <v>1946085-2</v>
@@ -8238,7 +8244,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-3", "1946085-3")</f>
         <v>1946085-3</v>
@@ -8265,7 +8271,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947270-1", "1947270-1")</f>
         <v>1947270-1</v>
@@ -8292,7 +8298,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947270-2", "1947270-2")</f>
         <v>1947270-2</v>
@@ -8319,7 +8325,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947337-1", "1947337-1")</f>
         <v>1947337-1</v>
@@ -8346,7 +8352,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947337-2", "1947337-2")</f>
         <v>1947337-2</v>
@@ -8373,7 +8379,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947954-1", "1947954-1")</f>
         <v>1947954-1</v>
@@ -8400,7 +8406,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947954-2", "1947954-2")</f>
         <v>1947954-2</v>
@@ -8427,7 +8433,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947969-1", "1947969-1")</f>
         <v>1947969-1</v>
@@ -8454,7 +8460,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947969-2", "1947969-2")</f>
         <v>1947969-2</v>
@@ -8481,7 +8487,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-1", "1954277-1")</f>
         <v>1954277-1</v>
@@ -8508,7 +8514,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-2", "1954277-2")</f>
         <v>1954277-2</v>
@@ -8535,7 +8541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-3", "1954277-3")</f>
         <v>1954277-3</v>
@@ -8562,7 +8568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-4", "1954277-4")</f>
         <v>1954277-4</v>
@@ -8589,7 +8595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-1", "1954326-1")</f>
         <v>1954326-1</v>
@@ -8616,7 +8622,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-2", "1954326-2")</f>
         <v>1954326-2</v>
@@ -8643,7 +8649,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-3", "1954326-3")</f>
         <v>1954326-3</v>
@@ -8670,7 +8676,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-1", "1954327-1")</f>
         <v>1954327-1</v>
@@ -8700,7 +8706,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-2", "1954327-2")</f>
         <v>1954327-2</v>
@@ -8727,7 +8733,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-3", "1954327-3")</f>
         <v>1954327-3</v>
@@ -8754,7 +8760,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1954675-1", "1954675-1")</f>
         <v>1954675-1</v>
@@ -8781,7 +8787,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1957107-1", "1957107-1")</f>
         <v>1957107-1</v>
@@ -8808,7 +8814,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-1", "1959073-1")</f>
         <v>1959073-1</v>
@@ -8835,7 +8841,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-2", "1959073-2")</f>
         <v>1959073-2</v>
@@ -8862,7 +8868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-3", "1959073-3")</f>
         <v>1959073-3</v>
@@ -8889,7 +8895,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-4", "1959073-4")</f>
         <v>1959073-4</v>
@@ -8916,7 +8922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1960761-1", "1960761-1")</f>
         <v>1960761-1</v>
@@ -8943,7 +8949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-1", "1961325-1")</f>
         <v>1961325-1</v>
@@ -8973,7 +8979,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-2", "1961325-2")</f>
         <v>1961325-2</v>
@@ -9003,7 +9009,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-3", "1961325-3")</f>
         <v>1961325-3</v>
@@ -9030,7 +9036,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-4", "1961325-4")</f>
         <v>1961325-4</v>
@@ -9057,7 +9063,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-1", "1961327-1")</f>
         <v>1961327-1</v>
@@ -9084,7 +9090,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-2", "1961327-2")</f>
         <v>1961327-2</v>
@@ -9114,7 +9120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-3", "1961327-3")</f>
         <v>1961327-3</v>
@@ -9141,7 +9147,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-4", "1961327-4")</f>
         <v>1961327-4</v>
@@ -9168,7 +9174,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-5", "1961327-5")</f>
         <v>1961327-5</v>
@@ -9215,16 +9221,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC397FCC-74C1-4D09-ACC0-E463BF5527EB}">
   <dimension ref="A1:I105"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="87.85546875" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.42578125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="87.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="19.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="41.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57" customHeight="1">
+    <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
         <v>146</v>
       </c>
@@ -9237,7 +9243,7 @@
       </c>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="32.25" customHeight="1">
+    <row r="2" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>149</v>
       </c>
@@ -9252,7 +9258,7 @@
       </c>
       <c r="E2" s="11"/>
     </row>
-    <row r="3" spans="1:5" ht="17.25" customHeight="1">
+    <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>153</v>
       </c>
@@ -9267,7 +9273,7 @@
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1">
+    <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>155</v>
       </c>
@@ -9284,7 +9290,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1">
+    <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>158</v>
       </c>
@@ -9299,7 +9305,7 @@
       </c>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>160</v>
       </c>
@@ -9314,7 +9320,7 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="7" spans="1:5" ht="14.45" customHeight="1">
+    <row r="7" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>162</v>
       </c>
@@ -9328,7 +9334,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.1" customHeight="1">
+    <row r="8" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>164</v>
       </c>
@@ -9342,7 +9348,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.95">
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>166</v>
       </c>
@@ -9356,7 +9362,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.95">
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>168</v>
       </c>
@@ -9370,7 +9376,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.95">
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>170</v>
       </c>
@@ -9384,7 +9390,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.95">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>172</v>
       </c>
@@ -9398,7 +9404,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.95">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>174</v>
       </c>
@@ -9412,7 +9418,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.95">
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>176</v>
       </c>
@@ -9426,7 +9432,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.95">
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>178</v>
       </c>
@@ -9440,7 +9446,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.95">
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>180</v>
       </c>
@@ -9454,7 +9460,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.95">
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="43" t="s">
         <v>182</v>
       </c>
@@ -9468,7 +9474,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="40.5" customHeight="1">
+    <row r="18" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
         <v>184</v>
       </c>
@@ -9482,7 +9488,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.95">
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
         <v>185</v>
       </c>
@@ -9496,7 +9502,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.95">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>187</v>
       </c>
@@ -9510,7 +9516,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.95">
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>189</v>
       </c>
@@ -9524,7 +9530,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.95">
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>191</v>
       </c>
@@ -9538,7 +9544,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.95">
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>193</v>
       </c>
@@ -9552,7 +9558,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.95">
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>195</v>
       </c>
@@ -9566,7 +9572,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.95">
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>197</v>
       </c>
@@ -9580,7 +9586,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.95">
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>199</v>
       </c>
@@ -9594,7 +9600,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.95">
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>201</v>
       </c>
@@ -9608,7 +9614,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.95">
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>203</v>
       </c>
@@ -9622,7 +9628,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="39" customHeight="1">
+    <row r="29" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
         <v>205</v>
       </c>
@@ -9636,7 +9642,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.95">
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>208</v>
       </c>
@@ -9653,7 +9659,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.95">
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>211</v>
       </c>
@@ -9670,7 +9676,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.95">
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>212</v>
       </c>
@@ -9687,7 +9693,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="17.45" customHeight="1">
+    <row r="33" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>187</v>
       </c>
@@ -9701,7 +9707,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="41.25" customHeight="1">
+    <row r="34" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
         <v>214</v>
       </c>
@@ -9715,7 +9721,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.95">
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>215</v>
       </c>
@@ -9729,7 +9735,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.95">
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>217</v>
       </c>
@@ -9743,7 +9749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6" customHeight="1">
+    <row r="37" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>218</v>
       </c>
@@ -9757,7 +9763,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.95">
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>219</v>
       </c>
@@ -9771,7 +9777,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.95">
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
         <v>220</v>
       </c>
@@ -9785,7 +9791,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.95">
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
         <v>221</v>
       </c>
@@ -9799,7 +9805,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.95">
+    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>222</v>
       </c>
@@ -9813,7 +9819,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.95">
+    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>223</v>
       </c>
@@ -9827,7 +9833,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.95">
+    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>224</v>
       </c>
@@ -9841,7 +9847,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="32.25" customHeight="1">
+    <row r="44" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
         <v>225</v>
       </c>
@@ -9855,7 +9861,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="18.600000000000001" customHeight="1">
+    <row r="45" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
         <v>226</v>
       </c>
@@ -9869,7 +9875,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="17.45" customHeight="1">
+    <row r="46" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
         <v>229</v>
       </c>
@@ -9883,7 +9889,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.95">
+    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>231</v>
       </c>
@@ -9900,7 +9906,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.95">
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>233</v>
       </c>
@@ -9914,7 +9920,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.95">
+    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>236</v>
       </c>
@@ -9926,7 +9932,7 @@
       </c>
       <c r="D49" s="56"/>
     </row>
-    <row r="50" spans="1:4" ht="15.95">
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>238</v>
       </c>
@@ -9940,7 +9946,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
+    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>240</v>
       </c>
@@ -9954,7 +9960,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15.6" customHeight="1">
+    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>242</v>
       </c>
@@ -9966,7 +9972,7 @@
       </c>
       <c r="D52" s="24"/>
     </row>
-    <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
+    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>244</v>
       </c>
@@ -9980,7 +9986,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.95">
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="18" t="s">
         <v>246</v>
       </c>
@@ -9994,7 +10000,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.95">
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="19" t="s">
         <v>249</v>
       </c>
@@ -10008,7 +10014,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
+    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
         <v>252</v>
       </c>
@@ -10022,7 +10028,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.95">
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
         <v>255</v>
       </c>
@@ -10036,7 +10042,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>257</v>
       </c>
@@ -10050,7 +10056,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.95">
+    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>260</v>
       </c>
@@ -10064,7 +10070,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1">
+    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>262</v>
       </c>
@@ -10078,7 +10084,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1">
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>264</v>
       </c>
@@ -10092,7 +10098,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.45" customHeight="1">
+    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>266</v>
       </c>
@@ -10106,7 +10112,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>269</v>
       </c>
@@ -10118,7 +10124,7 @@
       </c>
       <c r="D63" s="57"/>
     </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1">
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>271</v>
       </c>
@@ -10132,7 +10138,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="32.25" customHeight="1">
+    <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>274</v>
       </c>
@@ -10142,7 +10148,7 @@
       <c r="C65" s="51"/>
       <c r="D65" s="56"/>
     </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
         <v>276</v>
       </c>
@@ -10154,7 +10160,7 @@
       </c>
       <c r="D66" s="65"/>
     </row>
-    <row r="67" spans="1:4" ht="15.95">
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>278</v>
       </c>
@@ -10168,7 +10174,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="15.95">
+    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>279</v>
       </c>
@@ -10182,7 +10188,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15.95">
+    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>280</v>
       </c>
@@ -10196,7 +10202,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15.95">
+    <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>281</v>
       </c>
@@ -10210,7 +10216,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15.95">
+    <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>282</v>
       </c>
@@ -10224,7 +10230,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15.95">
+    <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>283</v>
       </c>
@@ -10238,7 +10244,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15.95">
+    <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>284</v>
       </c>
@@ -10252,7 +10258,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15.95">
+    <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>285</v>
       </c>
@@ -10266,7 +10272,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="15.95">
+    <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>286</v>
       </c>
@@ -10280,7 +10286,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15.95">
+    <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>287</v>
       </c>
@@ -10294,7 +10300,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15.95">
+    <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>288</v>
       </c>
@@ -10308,7 +10314,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15.95">
+    <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>289</v>
       </c>
@@ -10322,7 +10328,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="15.95">
+    <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>290</v>
       </c>
@@ -10336,7 +10342,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="15.95">
+    <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>291</v>
       </c>
@@ -10346,7 +10352,7 @@
       <c r="C80" s="10"/>
       <c r="D80" s="56"/>
     </row>
-    <row r="81" spans="1:4" ht="15.95">
+    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>292</v>
       </c>
@@ -10356,7 +10362,7 @@
       <c r="C81" s="32"/>
       <c r="D81" s="56"/>
     </row>
-    <row r="82" spans="1:4" ht="15.95">
+    <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>293</v>
       </c>
@@ -10364,7 +10370,7 @@
       <c r="C82" s="23"/>
       <c r="D82" s="56"/>
     </row>
-    <row r="83" spans="1:4" ht="15.95">
+    <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>294</v>
       </c>
@@ -10372,7 +10378,7 @@
       <c r="C83" s="10"/>
       <c r="D83" s="56"/>
     </row>
-    <row r="84" spans="1:4" ht="15.95">
+    <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>295</v>
       </c>
@@ -10386,7 +10392,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15.95">
+    <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>296</v>
       </c>
@@ -10400,7 +10406,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15.95">
+    <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>298</v>
       </c>
@@ -10414,7 +10420,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15.95">
+    <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>300</v>
       </c>
@@ -10422,7 +10428,7 @@
       <c r="C87" s="10"/>
       <c r="D87" s="56"/>
     </row>
-    <row r="88" spans="1:4" ht="15.95">
+    <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>301</v>
       </c>
@@ -10430,7 +10436,7 @@
       <c r="C88" s="10"/>
       <c r="D88" s="56"/>
     </row>
-    <row r="89" spans="1:4" ht="15.95">
+    <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>302</v>
       </c>
@@ -10438,7 +10444,7 @@
       <c r="C89" s="10"/>
       <c r="D89" s="56"/>
     </row>
-    <row r="90" spans="1:4" ht="15.95">
+    <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>303</v>
       </c>
@@ -10452,7 +10458,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15.95">
+    <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>304</v>
       </c>
@@ -10466,7 +10472,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15.95">
+    <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>305</v>
       </c>
@@ -10476,7 +10482,7 @@
       <c r="C92" s="56"/>
       <c r="D92" s="67"/>
     </row>
-    <row r="93" spans="1:4" ht="15.95">
+    <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>306</v>
       </c>
@@ -10490,7 +10496,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="15.95">
+    <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>307</v>
       </c>
@@ -10504,7 +10510,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15.95">
+    <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>308</v>
       </c>
@@ -10518,7 +10524,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15.95">
+    <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>309</v>
       </c>
@@ -10530,7 +10536,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.95">
+    <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>311</v>
       </c>
@@ -10544,7 +10550,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.95">
+    <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>312</v>
       </c>
@@ -10558,7 +10564,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.95">
+    <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>313</v>
       </c>
@@ -10572,7 +10578,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.95">
+    <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>316</v>
       </c>
@@ -10586,7 +10592,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.95">
+    <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>318</v>
       </c>
@@ -10600,19 +10606,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15" customHeight="1">
+    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1">
+    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" ht="15" customHeight="1">
+    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" ht="15" customHeight="1">
+    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
     </row>
@@ -10627,18 +10633,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A7BD36-8D88-3742-A4AC-48B0AFB67141}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="85.140625" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="46.42578125" customWidth="1"/>
+    <col min="1" max="1" width="85.1640625" customWidth="1"/>
+    <col min="2" max="2" width="32.5" style="5" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="46.5" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57" customHeight="1">
+    <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="50" t="s">
         <v>319</v>
       </c>
@@ -10650,7 +10656,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>149</v>
       </c>
@@ -10664,7 +10670,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.100000000000001" customHeight="1">
+    <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>153</v>
       </c>
@@ -10678,7 +10684,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16.350000000000001" customHeight="1">
+    <row r="4" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>155</v>
       </c>
@@ -10695,7 +10701,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1">
+    <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>158</v>
       </c>
@@ -10709,7 +10715,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>160</v>
       </c>
@@ -10723,7 +10729,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.45" customHeight="1">
+    <row r="7" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>162</v>
       </c>
@@ -10737,7 +10743,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.1" customHeight="1">
+    <row r="8" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>164</v>
       </c>
@@ -10751,7 +10757,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.95">
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>166</v>
       </c>
@@ -10765,7 +10771,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.95">
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>168</v>
       </c>
@@ -10779,7 +10785,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.95">
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>170</v>
       </c>
@@ -10793,7 +10799,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.95">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>172</v>
       </c>
@@ -10807,7 +10813,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.95">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>174</v>
       </c>
@@ -10821,7 +10827,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.95">
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>176</v>
       </c>
@@ -10835,7 +10841,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.95">
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>178</v>
       </c>
@@ -10849,7 +10855,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.95">
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>180</v>
       </c>
@@ -10863,7 +10869,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.95">
+    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="43" t="s">
         <v>182</v>
       </c>
@@ -10877,7 +10883,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1">
+    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
         <v>184</v>
       </c>
@@ -10891,7 +10897,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.95">
+    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
         <v>185</v>
       </c>
@@ -10905,7 +10911,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.95">
+    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>187</v>
       </c>
@@ -10919,7 +10925,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.95">
+    <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>189</v>
       </c>
@@ -10933,7 +10939,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.95">
+    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>191</v>
       </c>
@@ -10947,7 +10953,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.95">
+    <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>193</v>
       </c>
@@ -10961,7 +10967,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.95">
+    <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>195</v>
       </c>
@@ -10978,7 +10984,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.95">
+    <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>197</v>
       </c>
@@ -10992,7 +10998,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.95">
+    <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>199</v>
       </c>
@@ -11006,7 +11012,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.95">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>201</v>
       </c>
@@ -11020,7 +11026,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.95">
+    <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>203</v>
       </c>
@@ -11034,7 +11040,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1">
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
         <v>205</v>
       </c>
@@ -11048,7 +11054,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.95">
+    <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>208</v>
       </c>
@@ -11065,7 +11071,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.95">
+    <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>211</v>
       </c>
@@ -11082,7 +11088,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15.95">
+    <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>212</v>
       </c>
@@ -11099,7 +11105,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="17.45" customHeight="1">
+    <row r="33" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>187</v>
       </c>
@@ -11113,7 +11119,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1">
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
         <v>214</v>
       </c>
@@ -11127,7 +11133,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.95">
+    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>215</v>
       </c>
@@ -11141,7 +11147,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.95">
+    <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>217</v>
       </c>
@@ -11170,7 +11176,7 @@
         <v>57200</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.6" customHeight="1">
+    <row r="37" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>218</v>
       </c>
@@ -11204,7 +11210,7 @@
         <v>228800</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.95">
+    <row r="38" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>219</v>
       </c>
@@ -11238,7 +11244,7 @@
         <v>2599.1680000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.95">
+    <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
         <v>220</v>
       </c>
@@ -11252,7 +11258,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.95">
+    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
         <v>221</v>
       </c>
@@ -11269,7 +11275,7 @@
         <v>280000</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.95">
+    <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>222</v>
       </c>
@@ -11287,7 +11293,7 @@
         <v>835.52</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15.95">
+    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>223</v>
       </c>
@@ -11304,7 +11310,7 @@
         <v>315000</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15.95">
+    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>224</v>
       </c>
@@ -11322,7 +11328,7 @@
         <v>939.96</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="18" customHeight="1">
+    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
         <v>225</v>
       </c>
@@ -11336,7 +11342,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="18.600000000000001" customHeight="1">
+    <row r="45" spans="1:10" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
         <v>226</v>
       </c>
@@ -11350,7 +11356,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="17.45" customHeight="1">
+    <row r="46" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
         <v>229</v>
       </c>
@@ -11364,7 +11370,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15.95">
+    <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>231</v>
       </c>
@@ -11378,7 +11384,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.95">
+    <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>233</v>
       </c>
@@ -11392,7 +11398,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.95">
+    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>236</v>
       </c>
@@ -11404,7 +11410,7 @@
       </c>
       <c r="D49" s="57"/>
     </row>
-    <row r="50" spans="1:4" ht="15.95">
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>238</v>
       </c>
@@ -11418,7 +11424,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="16.350000000000001" customHeight="1">
+    <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>240</v>
       </c>
@@ -11432,7 +11438,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15.6" customHeight="1">
+    <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>242</v>
       </c>
@@ -11446,7 +11452,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="16.350000000000001" customHeight="1">
+    <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>244</v>
       </c>
@@ -11460,7 +11466,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.95">
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="18" t="s">
         <v>246</v>
       </c>
@@ -11474,7 +11480,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.95">
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="19" t="s">
         <v>249</v>
       </c>
@@ -11488,7 +11494,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.100000000000001" customHeight="1">
+    <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
         <v>252</v>
       </c>
@@ -11502,7 +11508,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.95">
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
         <v>255</v>
       </c>
@@ -11516,7 +11522,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>257</v>
       </c>
@@ -11530,7 +11536,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.95">
+    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>260</v>
       </c>
@@ -11544,7 +11550,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1">
+    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>262</v>
       </c>
@@ -11558,7 +11564,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1">
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>264</v>
       </c>
@@ -11572,7 +11578,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.45" customHeight="1">
+    <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>266</v>
       </c>
@@ -11586,7 +11592,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>269</v>
       </c>
@@ -11598,7 +11604,7 @@
       </c>
       <c r="D63" s="57"/>
     </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1">
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>271</v>
       </c>
@@ -11612,7 +11618,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="32.25" customHeight="1">
+    <row r="65" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>274</v>
       </c>
@@ -11622,7 +11628,7 @@
       <c r="C65" s="56"/>
       <c r="D65" s="57"/>
     </row>
-    <row r="66" spans="1:9" ht="18" customHeight="1">
+    <row r="66" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
         <v>276</v>
       </c>
@@ -11636,7 +11642,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.95">
+    <row r="67" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>278</v>
       </c>
@@ -11650,7 +11656,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.95">
+    <row r="68" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>279</v>
       </c>
@@ -11675,7 +11681,7 @@
         <v>0.123657512</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.95">
+    <row r="69" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>280</v>
       </c>
@@ -11683,7 +11689,7 @@
       <c r="C69" s="56"/>
       <c r="D69" s="56"/>
     </row>
-    <row r="70" spans="1:9" ht="15.95">
+    <row r="70" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>281</v>
       </c>
@@ -11697,7 +11703,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.95">
+    <row r="71" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>282</v>
       </c>
@@ -11711,7 +11717,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.95">
+    <row r="72" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>283</v>
       </c>
@@ -11725,7 +11731,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.95">
+    <row r="73" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>284</v>
       </c>
@@ -11739,7 +11745,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.95">
+    <row r="74" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>286</v>
       </c>
@@ -11753,7 +11759,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.95">
+    <row r="75" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>287</v>
       </c>
@@ -11767,7 +11773,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.95">
+    <row r="76" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>288</v>
       </c>
@@ -11781,7 +11787,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.95">
+    <row r="77" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>289</v>
       </c>
@@ -11795,7 +11801,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.95">
+    <row r="78" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>290</v>
       </c>
@@ -11809,7 +11815,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.95">
+    <row r="79" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>291</v>
       </c>
@@ -11819,7 +11825,7 @@
       <c r="C79" s="56"/>
       <c r="D79" s="56"/>
     </row>
-    <row r="80" spans="1:9" ht="15.95">
+    <row r="80" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>292</v>
       </c>
@@ -11829,7 +11835,7 @@
       <c r="C80" s="56"/>
       <c r="D80" s="56"/>
     </row>
-    <row r="81" spans="1:4" ht="15.95">
+    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>293</v>
       </c>
@@ -11837,7 +11843,7 @@
       <c r="C81" s="56"/>
       <c r="D81" s="56"/>
     </row>
-    <row r="82" spans="1:4" ht="15.95">
+    <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>294</v>
       </c>
@@ -11845,7 +11851,7 @@
       <c r="C82" s="56"/>
       <c r="D82" s="56"/>
     </row>
-    <row r="83" spans="1:4" ht="15.95">
+    <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>295</v>
       </c>
@@ -11859,7 +11865,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="15.95">
+    <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>296</v>
       </c>
@@ -11873,7 +11879,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15.95">
+    <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>298</v>
       </c>
@@ -11887,7 +11893,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15.95">
+    <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>300</v>
       </c>
@@ -11895,7 +11901,7 @@
       <c r="C86" s="56"/>
       <c r="D86" s="56"/>
     </row>
-    <row r="87" spans="1:4" ht="15.95">
+    <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>301</v>
       </c>
@@ -11903,7 +11909,7 @@
       <c r="C87" s="56"/>
       <c r="D87" s="56"/>
     </row>
-    <row r="88" spans="1:4" ht="15.95">
+    <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>302</v>
       </c>
@@ -11911,7 +11917,7 @@
       <c r="C88" s="56"/>
       <c r="D88" s="56"/>
     </row>
-    <row r="89" spans="1:4" ht="15.95">
+    <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>303</v>
       </c>
@@ -11925,7 +11931,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="15.95">
+    <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>304</v>
       </c>
@@ -11939,7 +11945,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15.95">
+    <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>305</v>
       </c>
@@ -11951,7 +11957,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15.95">
+    <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>374</v>
       </c>
@@ -11963,7 +11969,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="15.95">
+    <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>375</v>
       </c>
@@ -11975,7 +11981,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="15.95">
+    <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
         <v>308</v>
       </c>
@@ -11989,7 +11995,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15.95">
+    <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>309</v>
       </c>
@@ -12001,7 +12007,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15.95">
+    <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>311</v>
       </c>
@@ -12015,7 +12021,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.95">
+    <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>312</v>
       </c>
@@ -12029,7 +12035,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.95">
+    <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>313</v>
       </c>
@@ -12039,7 +12045,7 @@
       <c r="C98" s="10"/>
       <c r="D98" s="56"/>
     </row>
-    <row r="99" spans="1:9" ht="15.95">
+    <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>316</v>
       </c>
@@ -12049,7 +12055,7 @@
       <c r="C99" s="10"/>
       <c r="D99" s="56"/>
     </row>
-    <row r="100" spans="1:9" ht="15.95">
+    <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>318</v>
       </c>
@@ -12059,19 +12065,19 @@
       <c r="C100" s="10"/>
       <c r="D100" s="56"/>
     </row>
-    <row r="101" spans="1:9" ht="15" customHeight="1">
+    <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9" ht="15" customHeight="1">
+    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1">
+    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" ht="15" customHeight="1">
+    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
     </row>
@@ -12087,19 +12093,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1F4FD9-0BA8-D443-A42F-4E5E606C52A0}">
   <dimension ref="A1:I77"/>
-  <sheetFormatPr defaultColWidth="62.42578125" defaultRowHeight="24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="62.5" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="162.42578125" style="77" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" style="77" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" style="77" customWidth="1"/>
+    <col min="1" max="1" width="162.5" style="77" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" style="77" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" style="77" customWidth="1"/>
     <col min="4" max="4" width="26" style="77" customWidth="1"/>
-    <col min="5" max="5" width="47.7109375" style="77" customWidth="1"/>
-    <col min="6" max="6" width="26.42578125" style="77" customWidth="1"/>
-    <col min="7" max="7" width="33.85546875" style="77" customWidth="1"/>
-    <col min="8" max="16384" width="62.42578125" style="77"/>
+    <col min="5" max="5" width="47.6640625" style="77" customWidth="1"/>
+    <col min="6" max="6" width="26.5" style="77" customWidth="1"/>
+    <col min="7" max="7" width="33.83203125" style="77" customWidth="1"/>
+    <col min="8" max="16384" width="62.5" style="77"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="75">
+    <row r="1" spans="1:7" ht="75" x14ac:dyDescent="0.3">
       <c r="A1" s="75" t="s">
         <v>378</v>
       </c>
@@ -12118,7 +12124,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="50.1">
+    <row r="2" spans="1:7" ht="50" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
         <v>379</v>
       </c>
@@ -12141,7 +12147,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="24.95">
+    <row r="3" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A3" s="81" t="s">
         <v>381</v>
       </c>
@@ -12164,7 +12170,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="24.95">
+    <row r="4" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A4" s="81" t="s">
         <v>384</v>
       </c>
@@ -12187,7 +12193,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="24.95">
+    <row r="5" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A5" s="81" t="s">
         <v>387</v>
       </c>
@@ -12210,7 +12216,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="24.95">
+    <row r="6" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A6" s="90" t="s">
         <v>226</v>
       </c>
@@ -12233,7 +12239,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="24.95">
+    <row r="7" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A7" s="90" t="s">
         <v>229</v>
       </c>
@@ -12256,7 +12262,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="24.95">
+    <row r="8" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A8" s="94" t="s">
         <v>231</v>
       </c>
@@ -12279,7 +12285,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.5" customHeight="1">
+    <row r="9" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="81" t="s">
         <v>260</v>
       </c>
@@ -12294,7 +12300,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="75">
+    <row r="12" spans="1:7" ht="75" x14ac:dyDescent="0.3">
       <c r="A12" s="75" t="s">
         <v>390</v>
       </c>
@@ -12313,7 +12319,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="50.1">
+    <row r="13" spans="1:7" ht="50" x14ac:dyDescent="0.3">
       <c r="A13" s="78" t="s">
         <v>379</v>
       </c>
@@ -12336,7 +12342,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="24.95">
+    <row r="14" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A14" s="81" t="s">
         <v>381</v>
       </c>
@@ -12359,7 +12365,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="24.95">
+    <row r="15" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A15" s="81" t="s">
         <v>384</v>
       </c>
@@ -12382,7 +12388,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="24.95">
+    <row r="16" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A16" s="81" t="s">
         <v>387</v>
       </c>
@@ -12405,7 +12411,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="24.95">
+    <row r="17" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A17" s="90" t="s">
         <v>226</v>
       </c>
@@ -12428,7 +12434,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="24.95">
+    <row r="18" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A18" s="90" t="s">
         <v>229</v>
       </c>
@@ -12451,7 +12457,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="24.95">
+    <row r="19" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A19" s="94" t="s">
         <v>231</v>
       </c>
@@ -12474,7 +12480,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="24.95">
+    <row r="20" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A20" s="81" t="s">
         <v>260</v>
       </c>
@@ -12489,7 +12495,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="75">
+    <row r="23" spans="1:9" ht="75" x14ac:dyDescent="0.3">
       <c r="A23" s="96" t="s">
         <v>393</v>
       </c>
@@ -12508,7 +12514,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="50.1">
+    <row r="24" spans="1:9" ht="50" x14ac:dyDescent="0.3">
       <c r="A24" s="78" t="s">
         <v>379</v>
       </c>
@@ -12534,7 +12540,7 @@
         <v>280000</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="24.95">
+    <row r="25" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A25" s="81" t="s">
         <v>381</v>
       </c>
@@ -12561,7 +12567,7 @@
         <v>835.52</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="24.95">
+    <row r="26" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A26" s="81" t="s">
         <v>384</v>
       </c>
@@ -12584,7 +12590,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="24.95">
+    <row r="27" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A27" s="81" t="s">
         <v>387</v>
       </c>
@@ -12610,7 +12616,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="24.95">
+    <row r="28" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A28" s="90" t="s">
         <v>226</v>
       </c>
@@ -12633,7 +12639,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="24.95">
+    <row r="29" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A29" s="90" t="s">
         <v>229</v>
       </c>
@@ -12656,7 +12662,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="24.95">
+    <row r="30" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A30" s="94" t="s">
         <v>231</v>
       </c>
@@ -12679,7 +12685,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="24.95">
+    <row r="31" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A31" s="81" t="s">
         <v>260</v>
       </c>
@@ -12702,7 +12708,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="24.95">
+    <row r="32" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A32" s="97" t="s">
         <v>398</v>
       </c>
@@ -12728,7 +12734,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="24.95">
+    <row r="34" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A34" s="96" t="s">
         <v>401</v>
       </c>
@@ -12747,7 +12753,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="50.1">
+    <row r="35" spans="1:8" ht="50" x14ac:dyDescent="0.3">
       <c r="A35" s="78" t="s">
         <v>379</v>
       </c>
@@ -12770,7 +12776,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="24.95">
+    <row r="36" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A36" s="81" t="s">
         <v>381</v>
       </c>
@@ -12793,7 +12799,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="24.95">
+    <row r="37" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A37" s="81" t="s">
         <v>384</v>
       </c>
@@ -12816,7 +12822,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="24.95">
+    <row r="38" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A38" s="81" t="s">
         <v>387</v>
       </c>
@@ -12842,7 +12848,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="24.95">
+    <row r="39" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A39" s="90" t="s">
         <v>226</v>
       </c>
@@ -12865,7 +12871,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="24.95">
+    <row r="40" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A40" s="90" t="s">
         <v>229</v>
       </c>
@@ -12888,7 +12894,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="24.95">
+    <row r="41" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A41" s="94" t="s">
         <v>231</v>
       </c>
@@ -12911,7 +12917,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="24.95">
+    <row r="42" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A42" s="81" t="s">
         <v>260</v>
       </c>
@@ -12934,7 +12940,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="24.95">
+    <row r="43" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A43" s="97" t="s">
         <v>398</v>
       </c>
@@ -12960,7 +12966,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="24.95">
+    <row r="45" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A45" s="96" t="s">
         <v>410</v>
       </c>
@@ -12972,7 +12978,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="50.1">
+    <row r="46" spans="1:8" ht="50" x14ac:dyDescent="0.3">
       <c r="A46" s="78" t="s">
         <v>379</v>
       </c>
@@ -12986,7 +12992,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="24.95">
+    <row r="47" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A47" s="81" t="s">
         <v>381</v>
       </c>
@@ -13000,7 +13006,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="24.95">
+    <row r="48" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A48" s="81" t="s">
         <v>384</v>
       </c>
@@ -13014,7 +13020,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="24.95">
+    <row r="49" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A49" s="81" t="s">
         <v>387</v>
       </c>
@@ -13028,7 +13034,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="24.95">
+    <row r="50" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A50" s="90" t="s">
         <v>226</v>
       </c>
@@ -13042,7 +13048,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="24.95">
+    <row r="51" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A51" s="90" t="s">
         <v>229</v>
       </c>
@@ -13056,7 +13062,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="24.95">
+    <row r="52" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A52" s="94" t="s">
         <v>231</v>
       </c>
@@ -13070,7 +13076,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="24.95">
+    <row r="53" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A53" s="81" t="s">
         <v>260</v>
       </c>
@@ -13084,7 +13090,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="24.95">
+    <row r="54" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A54" s="97" t="s">
         <v>398</v>
       </c>
@@ -13098,7 +13104,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="24.95">
+    <row r="56" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A56" s="96" t="s">
         <v>412</v>
       </c>
@@ -13117,7 +13123,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="50.1">
+    <row r="57" spans="1:7" ht="50" x14ac:dyDescent="0.3">
       <c r="A57" s="78" t="s">
         <v>379</v>
       </c>
@@ -13140,7 +13146,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="24.95">
+    <row r="58" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A58" s="81" t="s">
         <v>381</v>
       </c>
@@ -13163,7 +13169,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="24.95">
+    <row r="59" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A59" s="81" t="s">
         <v>384</v>
       </c>
@@ -13186,7 +13192,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="24.95">
+    <row r="60" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A60" s="81" t="s">
         <v>387</v>
       </c>
@@ -13209,7 +13215,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="24.95">
+    <row r="61" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A61" s="90" t="s">
         <v>226</v>
       </c>
@@ -13232,7 +13238,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="24.95">
+    <row r="62" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A62" s="90" t="s">
         <v>229</v>
       </c>
@@ -13255,7 +13261,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="24.95">
+    <row r="63" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A63" s="94" t="s">
         <v>231</v>
       </c>
@@ -13278,7 +13284,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="24.95">
+    <row r="64" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A64" s="81" t="s">
         <v>260</v>
       </c>
@@ -13301,7 +13307,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="24.95">
+    <row r="65" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A65" s="97" t="s">
         <v>398</v>
       </c>
@@ -13324,7 +13330,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="23.25">
+    <row r="68" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A68" s="96" t="s">
         <v>419</v>
       </c>
@@ -13343,7 +13349,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="47.25">
+    <row r="69" spans="1:7" ht="50" x14ac:dyDescent="0.3">
       <c r="A69" s="78" t="s">
         <v>379</v>
       </c>
@@ -13366,7 +13372,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="23.25">
+    <row r="70" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A70" s="81" t="s">
         <v>381</v>
       </c>
@@ -13389,7 +13395,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="23.25">
+    <row r="71" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A71" s="81" t="s">
         <v>384</v>
       </c>
@@ -13412,7 +13418,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="23.25">
+    <row r="72" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A72" s="81" t="s">
         <v>387</v>
       </c>
@@ -13435,7 +13441,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="23.25">
+    <row r="73" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A73" s="90" t="s">
         <v>226</v>
       </c>
@@ -13458,7 +13464,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="23.25">
+    <row r="74" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A74" s="90" t="s">
         <v>229</v>
       </c>
@@ -13481,7 +13487,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="23.25">
+    <row r="75" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A75" s="94" t="s">
         <v>231</v>
       </c>
@@ -13504,30 +13510,30 @@
         <v>228</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="23.25">
+    <row r="76" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A76" s="81" t="s">
         <v>260</v>
       </c>
       <c r="B76" s="87" t="s">
-        <v>272</v>
+        <v>506</v>
       </c>
       <c r="C76" s="87">
-        <v>80</v>
-      </c>
-      <c r="D76" s="95" t="s">
-        <v>389</v>
+        <v>97</v>
+      </c>
+      <c r="D76" s="98">
+        <v>50</v>
       </c>
       <c r="E76" s="84" t="s">
-        <v>407</v>
+        <v>507</v>
       </c>
       <c r="F76" s="84">
-        <v>77</v>
-      </c>
-      <c r="G76" s="95" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="23.25">
+        <v>97</v>
+      </c>
+      <c r="G76" s="98">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A77" s="97" t="s">
         <v>398</v>
       </c>
@@ -13573,14 +13579,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8EE6899-576B-F44E-A189-C616F2524B03}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="59.140625" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="1" max="1" width="59.1640625" customWidth="1"/>
+    <col min="2" max="2" width="35.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="60">
+    <row r="1" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A1" s="50" t="s">
         <v>425</v>
       </c>
@@ -13591,7 +13597,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.95">
+    <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>149</v>
       </c>
@@ -13600,42 +13606,42 @@
       </c>
       <c r="C2" s="40"/>
     </row>
-    <row r="3" spans="1:3" ht="18.95" hidden="1">
+    <row r="3" spans="1:3" ht="19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
         <v>426</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
-    <row r="4" spans="1:3" ht="15.95" hidden="1">
+    <row r="4" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3" ht="15.95" hidden="1">
+    <row r="5" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>428</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="57"/>
     </row>
-    <row r="6" spans="1:3" ht="15.95" hidden="1">
+    <row r="6" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>429</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:3" ht="15.95" hidden="1">
+    <row r="7" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:3" ht="15.95">
+    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>160</v>
       </c>
@@ -13646,7 +13652,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.95">
+    <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>162</v>
       </c>
@@ -13657,98 +13663,98 @@
         <v>433</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.95" hidden="1">
+    <row r="10" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>164</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:3" ht="15.95" hidden="1">
+    <row r="11" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>434</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="57"/>
     </row>
-    <row r="12" spans="1:3" ht="15.95" hidden="1">
+    <row r="12" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>168</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:3" ht="15.95" hidden="1">
+    <row r="13" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="57"/>
     </row>
-    <row r="14" spans="1:3" ht="15.95" hidden="1">
+    <row r="14" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>435</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:3" ht="15.95" hidden="1">
+    <row r="15" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>436</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
-    <row r="16" spans="1:3" ht="15.95" hidden="1">
+    <row r="16" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>174</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:3" ht="15.95" hidden="1">
+    <row r="17" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>437</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:3" ht="15.95" hidden="1">
+    <row r="18" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>438</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:3" ht="15.95" hidden="1">
+    <row r="19" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>180</v>
       </c>
       <c r="B19" s="46"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:3" ht="15.95" hidden="1">
+    <row r="20" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="43" t="s">
         <v>439</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
     </row>
-    <row r="21" spans="1:3" ht="18.95">
+    <row r="21" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
         <v>184</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="59"/>
     </row>
-    <row r="22" spans="1:3" ht="15.95" hidden="1">
+    <row r="22" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="22" t="s">
         <v>185</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="54"/>
     </row>
-    <row r="23" spans="1:3" ht="15.95">
+    <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>187</v>
       </c>
@@ -13759,14 +13765,14 @@
         <v>441</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.95" hidden="1">
+    <row r="24" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>189</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="56"/>
     </row>
-    <row r="25" spans="1:3" ht="15.95">
+    <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>191</v>
       </c>
@@ -13777,7 +13783,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.95">
+    <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>193</v>
       </c>
@@ -13788,98 +13794,98 @@
         <v>445</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.95" hidden="1">
+    <row r="27" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>446</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="56"/>
     </row>
-    <row r="28" spans="1:3" ht="15.95" hidden="1">
+    <row r="28" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>197</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="56"/>
     </row>
-    <row r="29" spans="1:3" ht="15.95" hidden="1">
+    <row r="29" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>199</v>
       </c>
       <c r="B29" s="10"/>
       <c r="C29" s="56"/>
     </row>
-    <row r="30" spans="1:3" ht="15.95" hidden="1">
+    <row r="30" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>447</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="56"/>
     </row>
-    <row r="31" spans="1:3" ht="15.95" hidden="1">
+    <row r="31" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>448</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="56"/>
     </row>
-    <row r="32" spans="1:3" ht="18.95" hidden="1">
+    <row r="32" spans="1:3" ht="19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
         <v>205</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="60"/>
     </row>
-    <row r="33" spans="1:3" ht="15.95" hidden="1">
+    <row r="33" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>208</v>
       </c>
       <c r="B33" s="47"/>
       <c r="C33" s="56"/>
     </row>
-    <row r="34" spans="1:3" ht="15.95" hidden="1">
+    <row r="34" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>211</v>
       </c>
       <c r="B34" s="47"/>
       <c r="C34" s="56"/>
     </row>
-    <row r="35" spans="1:3" ht="15.95" hidden="1">
+    <row r="35" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B35" s="47"/>
       <c r="C35" s="56"/>
     </row>
-    <row r="36" spans="1:3" ht="15.95" hidden="1">
+    <row r="36" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>187</v>
       </c>
       <c r="B36" s="47"/>
       <c r="C36" s="53"/>
     </row>
-    <row r="37" spans="1:3" ht="18.95">
+    <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
         <v>214</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="61"/>
     </row>
-    <row r="38" spans="1:3" ht="15.95" hidden="1">
+    <row r="38" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>215</v>
       </c>
       <c r="B38" s="48"/>
       <c r="C38" s="62"/>
     </row>
-    <row r="39" spans="1:3" ht="15.95" hidden="1">
+    <row r="39" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="62"/>
     </row>
-    <row r="40" spans="1:3" ht="15.95">
+    <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>218</v>
       </c>
@@ -13890,7 +13896,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.95">
+    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>219</v>
       </c>
@@ -13901,28 +13907,28 @@
         <v>452</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.95" hidden="1">
+    <row r="42" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="22" t="s">
         <v>220</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
     </row>
-    <row r="43" spans="1:3" ht="15.95" hidden="1">
+    <row r="43" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="22" t="s">
         <v>221</v>
       </c>
       <c r="B43" s="45"/>
       <c r="C43" s="15"/>
     </row>
-    <row r="44" spans="1:3" ht="15.95" hidden="1">
+    <row r="44" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>222</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="1:3" ht="15.95">
+    <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>223</v>
       </c>
@@ -13933,7 +13939,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.95" hidden="1">
+    <row r="46" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>224</v>
       </c>
@@ -13948,14 +13954,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA07167-CEB4-F64B-93AF-8A8BA2B4D0FF}">
   <dimension ref="A1:D39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="62.140625" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" customWidth="1"/>
-    <col min="3" max="3" width="40.7109375" customWidth="1"/>
+    <col min="1" max="1" width="62.1640625" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="81">
+    <row r="1" spans="1:4" ht="81" x14ac:dyDescent="0.2">
       <c r="A1" s="71" t="s">
         <v>455</v>
       </c>
@@ -13966,7 +13972,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="21.95">
+    <row r="2" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
         <v>458</v>
       </c>
@@ -13977,7 +13983,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="21.95">
+    <row r="3" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A3" s="69" t="s">
         <v>461</v>
       </c>
@@ -13988,7 +13994,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="21.95">
+    <row r="4" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A4" s="69" t="s">
         <v>463</v>
       </c>
@@ -13999,7 +14005,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="21.95">
+    <row r="5" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A5" s="69" t="s">
         <v>465</v>
       </c>
@@ -14010,7 +14016,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="21.95">
+    <row r="6" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A6" s="69" t="s">
         <v>466</v>
       </c>
@@ -14021,7 +14027,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="21.95">
+    <row r="7" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A7" s="69" t="s">
         <v>469</v>
       </c>
@@ -14035,7 +14041,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="21.95">
+    <row r="8" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A8" s="69" t="s">
         <v>473</v>
       </c>
@@ -14049,7 +14055,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="21.95">
+    <row r="9" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A9" s="69" t="s">
         <v>476</v>
       </c>
@@ -14063,7 +14069,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="21.95">
+    <row r="10" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A10" s="69" t="s">
         <v>480</v>
       </c>
@@ -14074,7 +14080,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="21.95">
+    <row r="11" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A11" s="69" t="s">
         <v>481</v>
       </c>
@@ -14085,7 +14091,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="21.95">
+    <row r="12" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A12" s="69" t="s">
         <v>482</v>
       </c>
@@ -14096,7 +14102,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="21.95">
+    <row r="13" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A13" s="69" t="s">
         <v>483</v>
       </c>
@@ -14107,7 +14113,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="21.95">
+    <row r="14" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A14" s="69" t="s">
         <v>484</v>
       </c>
@@ -14118,7 +14124,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B25" s="102" t="s">
         <v>485</v>
       </c>
@@ -14126,7 +14132,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="102" t="s">
         <v>486</v>
       </c>
@@ -14137,7 +14143,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>487</v>
       </c>
@@ -14148,7 +14154,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>488</v>
       </c>
@@ -14159,7 +14165,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>489</v>
       </c>
@@ -14170,7 +14176,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>490</v>
       </c>
@@ -14181,7 +14187,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>491</v>
       </c>
@@ -14192,7 +14198,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>492</v>
       </c>
@@ -14203,7 +14209,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>493</v>
       </c>
@@ -14214,7 +14220,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>494</v>
       </c>
@@ -14225,7 +14231,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>495</v>
       </c>
@@ -14236,7 +14242,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>496</v>
       </c>
@@ -14247,7 +14253,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>499</v>
       </c>
@@ -14258,7 +14264,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>502</v>
       </c>
@@ -14269,7 +14275,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>505</v>
       </c>
@@ -14286,20 +14292,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf4d24f-a117-48f7-91e1-2035a8c734fd">
@@ -14395,6 +14387,20 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a3ce5a06-b323-45b4-8d97-2f59321c9a5a" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14646,17 +14652,49 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
+    <ds:schemaRef ds:uri="cb645b5b-9a36-43da-96bf-ab72ec91ddff"/>
+    <ds:schemaRef ds:uri="0b7692b1-2532-40e4-a300-4d7fced4a07a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75EC423-2542-4A93-99FE-CC28AA840E8C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D764E2-0E35-4957-B738-9033D3F0B0F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF876B3-44D4-4080-B40E-3DF67289D40E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C639165A-13FF-4A9F-A5E9-0E8F0976D502}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9bf4d24f-a117-48f7-91e1-2035a8c734fd"/>
+    <ds:schemaRef ds:uri="0b7692b1-2532-40e4-a300-4d7fced4a07a"/>
+    <ds:schemaRef ds:uri="cb645b5b-9a36-43da-96bf-ab72ec91ddff"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sshivang/Downloads/Panther Sanity/public/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B488C47-373E-6E47-96E5-422DB83E3EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1AC373-5448-B647-8BD2-D223756AE718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISSUES-PR's" sheetId="7" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Second Set Data" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ISSUES-PR''s'!$A$1:$I$224</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ISSUES-PR''s'!$A$1:$I$220</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SRX440'!$A$1:$F$100</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="507">
   <si>
     <t>number</t>
   </si>
@@ -360,9 +360,6 @@
   </si>
   <si>
     <t>25.4X300-EVO: Panther: SRX4XX: IPSEC Performance - Only one core is utilized on the decryption side</t>
-  </si>
-  <si>
-    <t>26.4R1-EVO</t>
   </si>
   <si>
     <t>assigned</t>
@@ -3077,7 +3074,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{101F05EA-6A87-7646-9D66-36E81A856E36}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I224"/>
+  <dimension ref="A1:I220"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -7242,16 +7239,16 @@
         <v>51</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-2", "1940446-2")</f>
-        <v>1940446-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-3", "1940446-3")</f>
+        <v>1940446-3</v>
       </c>
       <c r="B153" t="s">
         <v>104</v>
       </c>
       <c r="C153" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D153" t="s">
         <v>47</v>
@@ -7260,10 +7257,10 @@
         <v>12</v>
       </c>
       <c r="G153" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="H153" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="I153" t="s">
         <v>51</v>
@@ -7271,14 +7268,14 @@
     </row>
     <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-3", "1940446-3")</f>
-        <v>1940446-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-4", "1940446-4")</f>
+        <v>1940446-4</v>
       </c>
       <c r="B154" t="s">
         <v>104</v>
       </c>
       <c r="C154" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="D154" t="s">
         <v>47</v>
@@ -7287,19 +7284,19 @@
         <v>12</v>
       </c>
       <c r="G154" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="H154" t="s">
         <v>14</v>
       </c>
       <c r="I154" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-4", "1940446-4")</f>
-        <v>1940446-4</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-5", "1940446-5")</f>
+        <v>1940446-5</v>
       </c>
       <c r="B155" t="s">
         <v>104</v>
@@ -7317,22 +7314,22 @@
         <v>107</v>
       </c>
       <c r="H155" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I155" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-5", "1940446-5")</f>
-        <v>1940446-5</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-6", "1940446-6")</f>
+        <v>1940446-6</v>
       </c>
       <c r="B156" t="s">
         <v>104</v>
       </c>
       <c r="C156" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="D156" t="s">
         <v>47</v>
@@ -7340,26 +7337,29 @@
       <c r="E156" t="s">
         <v>12</v>
       </c>
+      <c r="F156" t="s">
+        <v>30</v>
+      </c>
       <c r="G156" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="H156" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="I156" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
     </row>
     <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-6", "1940446-6")</f>
-        <v>1940446-6</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-7", "1940446-7")</f>
+        <v>1940446-7</v>
       </c>
       <c r="B157" t="s">
         <v>104</v>
       </c>
       <c r="C157" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D157" t="s">
         <v>47</v>
@@ -7367,30 +7367,24 @@
       <c r="E157" t="s">
         <v>12</v>
       </c>
-      <c r="F157" t="s">
-        <v>30</v>
-      </c>
       <c r="G157" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H157" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I157" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
     </row>
     <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-7", "1940446-7")</f>
-        <v>1940446-7</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-8", "1940446-8")</f>
+        <v>1940446-8</v>
       </c>
       <c r="B158" t="s">
         <v>104</v>
       </c>
-      <c r="C158" t="s">
-        <v>17</v>
-      </c>
       <c r="D158" t="s">
         <v>47</v>
       </c>
@@ -7398,7 +7392,7 @@
         <v>12</v>
       </c>
       <c r="G158" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H158" t="s">
         <v>81</v>
@@ -7409,11 +7403,14 @@
     </row>
     <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-8", "1940446-8")</f>
-        <v>1940446-8</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-1", "1942363-1")</f>
+        <v>1942363-1</v>
       </c>
       <c r="B159" t="s">
-        <v>104</v>
+        <v>108</v>
+      </c>
+      <c r="C159" t="s">
+        <v>17</v>
       </c>
       <c r="D159" t="s">
         <v>47</v>
@@ -7422,25 +7419,25 @@
         <v>12</v>
       </c>
       <c r="G159" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="H159" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="I159" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-9", "1940446-9")</f>
-        <v>1940446-9</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-2", "1942363-2")</f>
+        <v>1942363-2</v>
       </c>
       <c r="B160" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C160" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D160" t="s">
         <v>47</v>
@@ -7449,22 +7446,25 @@
         <v>12</v>
       </c>
       <c r="G160" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H160" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="I160" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-10", "1940446-10")</f>
-        <v>1940446-10</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-3", "1942363-3")</f>
+        <v>1942363-3</v>
       </c>
       <c r="B161" t="s">
-        <v>104</v>
+        <v>108</v>
+      </c>
+      <c r="C161" t="s">
+        <v>17</v>
       </c>
       <c r="D161" t="s">
         <v>47</v>
@@ -7476,22 +7476,22 @@
         <v>76</v>
       </c>
       <c r="H161" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="I161" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
     </row>
     <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-1", "1942363-1")</f>
-        <v>1942363-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-4", "1942363-4")</f>
+        <v>1942363-4</v>
       </c>
       <c r="B162" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C162" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D162" t="s">
         <v>47</v>
@@ -7500,22 +7500,22 @@
         <v>12</v>
       </c>
       <c r="G162" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H162" t="s">
         <v>14</v>
       </c>
       <c r="I162" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-2", "1942363-2")</f>
-        <v>1942363-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942376-1", "1942376-1")</f>
+        <v>1942376-1</v>
       </c>
       <c r="B163" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C163" t="s">
         <v>17</v>
@@ -7527,22 +7527,22 @@
         <v>12</v>
       </c>
       <c r="G163" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H163" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I163" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
     </row>
     <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-3", "1942363-3")</f>
-        <v>1942363-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942376-2", "1942376-2")</f>
+        <v>1942376-2</v>
       </c>
       <c r="B164" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
@@ -7554,46 +7554,46 @@
         <v>12</v>
       </c>
       <c r="G164" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="H164" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I164" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
     </row>
     <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-4", "1942363-4")</f>
-        <v>1942363-4</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-1", "1943082-1")</f>
+        <v>1943082-1</v>
       </c>
       <c r="B165" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C165" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D165" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E165" t="s">
         <v>12</v>
       </c>
       <c r="G165" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H165" t="s">
         <v>14</v>
       </c>
       <c r="I165" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
     </row>
     <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942376-1", "1942376-1")</f>
-        <v>1942376-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-2", "1943082-2")</f>
+        <v>1943082-2</v>
       </c>
       <c r="B166" t="s">
         <v>111</v>
@@ -7602,58 +7602,58 @@
         <v>17</v>
       </c>
       <c r="D166" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E166" t="s">
         <v>12</v>
       </c>
       <c r="G166" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H166" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="I166" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1942376-2", "1942376-2")</f>
-        <v>1942376-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-3", "1943082-3")</f>
+        <v>1943082-3</v>
       </c>
       <c r="B167" t="s">
         <v>111</v>
       </c>
       <c r="C167" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D167" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E167" t="s">
         <v>12</v>
       </c>
       <c r="G167" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H167" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="I167" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-1", "1943082-1")</f>
-        <v>1943082-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-4", "1943082-4")</f>
+        <v>1943082-4</v>
       </c>
       <c r="B168" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C168" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D168" t="s">
         <v>11</v>
@@ -7662,7 +7662,7 @@
         <v>12</v>
       </c>
       <c r="G168" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H168" t="s">
         <v>14</v>
@@ -7673,14 +7673,14 @@
     </row>
     <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-2", "1943082-2")</f>
-        <v>1943082-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-1", "1943084-1")</f>
+        <v>1943084-1</v>
       </c>
       <c r="B169" t="s">
         <v>112</v>
       </c>
       <c r="C169" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D169" t="s">
         <v>11</v>
@@ -7695,19 +7695,19 @@
         <v>14</v>
       </c>
       <c r="I169" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
     </row>
     <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-3", "1943082-3")</f>
-        <v>1943082-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-2", "1943084-2")</f>
+        <v>1943084-2</v>
       </c>
       <c r="B170" t="s">
         <v>112</v>
       </c>
       <c r="C170" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="D170" t="s">
         <v>11</v>
@@ -7716,26 +7716,23 @@
         <v>12</v>
       </c>
       <c r="G170" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H170" t="s">
         <v>14</v>
       </c>
       <c r="I170" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
     </row>
     <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-4", "1943082-4")</f>
-        <v>1943082-4</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-3", "1943084-3")</f>
+        <v>1943084-3</v>
       </c>
       <c r="B171" t="s">
         <v>112</v>
       </c>
-      <c r="C171" t="s">
-        <v>42</v>
-      </c>
       <c r="D171" t="s">
         <v>11</v>
       </c>
@@ -7743,25 +7740,25 @@
         <v>12</v>
       </c>
       <c r="G171" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H171" t="s">
         <v>14</v>
       </c>
       <c r="I171" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-1", "1943084-1")</f>
-        <v>1943084-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-4", "1943084-4")</f>
+        <v>1943084-4</v>
       </c>
       <c r="B172" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C172" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D172" t="s">
         <v>11</v>
@@ -7770,25 +7767,25 @@
         <v>12</v>
       </c>
       <c r="G172" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="H172" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I172" t="s">
-        <v>114</v>
+        <v>18</v>
       </c>
     </row>
     <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-2", "1943084-2")</f>
-        <v>1943084-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943461-1", "1943461-1")</f>
+        <v>1943461-1</v>
       </c>
       <c r="B173" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C173" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D173" t="s">
         <v>11</v>
@@ -7803,16 +7800,19 @@
         <v>14</v>
       </c>
       <c r="I173" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
     </row>
     <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-3", "1943084-3")</f>
-        <v>1943084-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943461-2", "1943461-2")</f>
+        <v>1943461-2</v>
       </c>
       <c r="B174" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="C174" t="s">
+        <v>17</v>
       </c>
       <c r="D174" t="s">
         <v>11</v>
@@ -7821,25 +7821,25 @@
         <v>12</v>
       </c>
       <c r="G174" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H174" t="s">
         <v>14</v>
       </c>
       <c r="I174" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-4", "1943084-4")</f>
-        <v>1943084-4</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-1", "1943467-1")</f>
+        <v>1943467-1</v>
       </c>
       <c r="B175" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C175" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D175" t="s">
         <v>11</v>
@@ -7848,19 +7848,19 @@
         <v>12</v>
       </c>
       <c r="G175" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H175" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="I175" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943461-1", "1943461-1")</f>
-        <v>1943461-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-2", "1943467-2")</f>
+        <v>1943467-2</v>
       </c>
       <c r="B176" t="s">
         <v>115</v>
@@ -7875,19 +7875,19 @@
         <v>12</v>
       </c>
       <c r="G176" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H176" t="s">
         <v>14</v>
       </c>
       <c r="I176" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943461-2", "1943461-2")</f>
-        <v>1943461-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-3", "1943467-3")</f>
+        <v>1943467-3</v>
       </c>
       <c r="B177" t="s">
         <v>115</v>
@@ -7902,25 +7902,25 @@
         <v>12</v>
       </c>
       <c r="G177" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H177" t="s">
         <v>14</v>
       </c>
       <c r="I177" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-1", "1943467-1")</f>
-        <v>1943467-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-4", "1943467-4")</f>
+        <v>1943467-4</v>
       </c>
       <c r="B178" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C178" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D178" t="s">
         <v>11</v>
@@ -7929,7 +7929,7 @@
         <v>12</v>
       </c>
       <c r="G178" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H178" t="s">
         <v>14</v>
@@ -7940,14 +7940,14 @@
     </row>
     <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-2", "1943467-2")</f>
-        <v>1943467-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-5", "1943467-5")</f>
+        <v>1943467-5</v>
       </c>
       <c r="B179" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C179" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D179" t="s">
         <v>11</v>
@@ -7955,8 +7955,11 @@
       <c r="E179" t="s">
         <v>12</v>
       </c>
+      <c r="F179" t="s">
+        <v>22</v>
+      </c>
       <c r="G179" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H179" t="s">
         <v>14</v>
@@ -7967,8 +7970,8 @@
     </row>
     <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-3", "1943467-3")</f>
-        <v>1943467-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-1", "1943607-1")</f>
+        <v>1943607-1</v>
       </c>
       <c r="B180" t="s">
         <v>116</v>
@@ -7977,121 +7980,118 @@
         <v>17</v>
       </c>
       <c r="D180" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="E180" t="s">
         <v>12</v>
       </c>
+      <c r="F180" t="s">
+        <v>22</v>
+      </c>
       <c r="G180" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H180" t="s">
         <v>14</v>
       </c>
       <c r="I180" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-4", "1943467-4")</f>
-        <v>1943467-4</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-2", "1943607-2")</f>
+        <v>1943607-2</v>
       </c>
       <c r="B181" t="s">
         <v>116</v>
       </c>
       <c r="C181" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="D181" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="E181" t="s">
         <v>12</v>
       </c>
+      <c r="F181" t="s">
+        <v>22</v>
+      </c>
       <c r="G181" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H181" t="s">
         <v>14</v>
       </c>
       <c r="I181" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-5", "1943467-5")</f>
-        <v>1943467-5</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-3", "1943607-3")</f>
+        <v>1943607-3</v>
       </c>
       <c r="B182" t="s">
         <v>116</v>
       </c>
-      <c r="C182" t="s">
-        <v>32</v>
-      </c>
       <c r="D182" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="E182" t="s">
         <v>12</v>
       </c>
-      <c r="F182" t="s">
-        <v>22</v>
-      </c>
       <c r="G182" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H182" t="s">
         <v>14</v>
       </c>
       <c r="I182" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-1", "1943607-1")</f>
-        <v>1943607-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1946082-2", "1946082-2")</f>
+        <v>1946082-2</v>
       </c>
       <c r="B183" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C183" t="s">
         <v>17</v>
       </c>
       <c r="D183" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E183" t="s">
         <v>12</v>
       </c>
-      <c r="F183" t="s">
-        <v>22</v>
-      </c>
       <c r="G183" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H183" t="s">
         <v>14</v>
       </c>
       <c r="I183" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
     </row>
     <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-2", "1943607-2")</f>
-        <v>1943607-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-1", "1946085-1")</f>
+        <v>1946085-1</v>
       </c>
       <c r="B184" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C184" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D184" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E184" t="s">
         <v>12</v>
@@ -8100,184 +8100,184 @@
         <v>22</v>
       </c>
       <c r="G184" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H184" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I184" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-3", "1943607-3")</f>
-        <v>1943607-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-2", "1946085-2")</f>
+        <v>1946085-2</v>
       </c>
       <c r="B185" t="s">
-        <v>117</v>
+        <v>120</v>
+      </c>
+      <c r="C185" t="s">
+        <v>13</v>
       </c>
       <c r="D185" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E185" t="s">
         <v>12</v>
       </c>
       <c r="G185" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H185" t="s">
         <v>14</v>
       </c>
       <c r="I185" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1946082-1", "1946082-1")</f>
-        <v>1946082-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-3", "1946085-3")</f>
+        <v>1946085-3</v>
       </c>
       <c r="B186" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C186" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D186" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E186" t="s">
         <v>12</v>
       </c>
       <c r="G186" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H186" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="I186" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1946082-2", "1946082-2")</f>
-        <v>1946082-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947270-1", "1947270-1")</f>
+        <v>1947270-1</v>
       </c>
       <c r="B187" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C187" t="s">
         <v>17</v>
       </c>
       <c r="D187" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="E187" t="s">
         <v>12</v>
       </c>
       <c r="G187" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H187" t="s">
         <v>14</v>
       </c>
       <c r="I187" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-1", "1946085-1")</f>
-        <v>1946085-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947270-2", "1947270-2")</f>
+        <v>1947270-2</v>
       </c>
       <c r="B188" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C188" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D188" t="s">
-        <v>122</v>
+        <v>11</v>
       </c>
       <c r="E188" t="s">
         <v>12</v>
       </c>
-      <c r="F188" t="s">
-        <v>22</v>
-      </c>
       <c r="G188" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H188" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="I188" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-2", "1946085-2")</f>
-        <v>1946085-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947337-1", "1947337-1")</f>
+        <v>1947337-1</v>
       </c>
       <c r="B189" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C189" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D189" t="s">
-        <v>122</v>
+        <v>11</v>
       </c>
       <c r="E189" t="s">
         <v>12</v>
       </c>
       <c r="G189" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H189" t="s">
         <v>14</v>
       </c>
       <c r="I189" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
     </row>
     <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-3", "1946085-3")</f>
-        <v>1946085-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947337-2", "1947337-2")</f>
+        <v>1947337-2</v>
       </c>
       <c r="B190" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C190" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D190" t="s">
-        <v>122</v>
+        <v>11</v>
       </c>
       <c r="E190" t="s">
         <v>12</v>
       </c>
       <c r="G190" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H190" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="I190" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
     </row>
     <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947270-1", "1947270-1")</f>
-        <v>1947270-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947954-1", "1947954-1")</f>
+        <v>1947954-1</v>
       </c>
       <c r="B191" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C191" t="s">
         <v>17</v>
@@ -8295,16 +8295,16 @@
         <v>14</v>
       </c>
       <c r="I191" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
     </row>
     <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947270-2", "1947270-2")</f>
-        <v>1947270-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947954-2", "1947954-2")</f>
+        <v>1947954-2</v>
       </c>
       <c r="B192" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C192" t="s">
         <v>17</v>
@@ -8322,16 +8322,16 @@
         <v>14</v>
       </c>
       <c r="I192" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
     </row>
     <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947337-1", "1947337-1")</f>
-        <v>1947337-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947969-1", "1947969-1")</f>
+        <v>1947969-1</v>
       </c>
       <c r="B193" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C193" t="s">
         <v>17</v>
@@ -8349,16 +8349,16 @@
         <v>14</v>
       </c>
       <c r="I193" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947337-2", "1947337-2")</f>
-        <v>1947337-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947969-2", "1947969-2")</f>
+        <v>1947969-2</v>
       </c>
       <c r="B194" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C194" t="s">
         <v>17</v>
@@ -8376,16 +8376,16 @@
         <v>14</v>
       </c>
       <c r="I194" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947954-1", "1947954-1")</f>
-        <v>1947954-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-1", "1954277-1")</f>
+        <v>1954277-1</v>
       </c>
       <c r="B195" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C195" t="s">
         <v>17</v>
@@ -8400,19 +8400,19 @@
         <v>17</v>
       </c>
       <c r="H195" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="I195" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
     </row>
     <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947954-2", "1947954-2")</f>
-        <v>1947954-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-2", "1954277-2")</f>
+        <v>1954277-2</v>
       </c>
       <c r="B196" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C196" t="s">
         <v>17</v>
@@ -8427,19 +8427,19 @@
         <v>13</v>
       </c>
       <c r="H196" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I196" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
     </row>
     <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947969-1", "1947969-1")</f>
-        <v>1947969-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-3", "1954277-3")</f>
+        <v>1954277-3</v>
       </c>
       <c r="B197" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C197" t="s">
         <v>17</v>
@@ -8451,22 +8451,22 @@
         <v>12</v>
       </c>
       <c r="G197" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="H197" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I197" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
     </row>
     <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1947969-2", "1947969-2")</f>
-        <v>1947969-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-4", "1954277-4")</f>
+        <v>1954277-4</v>
       </c>
       <c r="B198" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C198" t="s">
         <v>17</v>
@@ -8478,28 +8478,28 @@
         <v>12</v>
       </c>
       <c r="G198" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="H198" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I198" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-1", "1954277-1")</f>
-        <v>1954277-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-1", "1954326-1")</f>
+        <v>1954326-1</v>
       </c>
       <c r="B199" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C199" t="s">
         <v>17</v>
       </c>
       <c r="D199" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="E199" t="s">
         <v>12</v>
@@ -8508,25 +8508,25 @@
         <v>17</v>
       </c>
       <c r="H199" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="I199" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
     <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-2", "1954277-2")</f>
-        <v>1954277-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-2", "1954326-2")</f>
+        <v>1954326-2</v>
       </c>
       <c r="B200" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C200" t="s">
         <v>17</v>
       </c>
       <c r="D200" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="E200" t="s">
         <v>12</v>
@@ -8535,70 +8535,73 @@
         <v>13</v>
       </c>
       <c r="H200" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="I200" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
     </row>
     <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-3", "1954277-3")</f>
-        <v>1954277-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-3", "1954326-3")</f>
+        <v>1954326-3</v>
       </c>
       <c r="B201" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C201" t="s">
         <v>17</v>
       </c>
       <c r="D201" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="E201" t="s">
         <v>12</v>
       </c>
       <c r="G201" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="H201" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="I201" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
     </row>
     <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954277-4", "1954277-4")</f>
-        <v>1954277-4</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-1", "1954327-1")</f>
+        <v>1954327-1</v>
       </c>
       <c r="B202" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C202" t="s">
         <v>17</v>
       </c>
       <c r="D202" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="E202" t="s">
         <v>12</v>
       </c>
+      <c r="F202" t="s">
+        <v>30</v>
+      </c>
       <c r="G202" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H202" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="I202" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
     </row>
     <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-1", "1954326-1")</f>
-        <v>1954326-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-2", "1954327-2")</f>
+        <v>1954327-2</v>
       </c>
       <c r="B203" t="s">
         <v>132</v>
@@ -8607,13 +8610,13 @@
         <v>17</v>
       </c>
       <c r="D203" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E203" t="s">
         <v>12</v>
       </c>
       <c r="G203" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H203" t="s">
         <v>14</v>
@@ -8624,8 +8627,8 @@
     </row>
     <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-2", "1954326-2")</f>
-        <v>1954326-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-3", "1954327-3")</f>
+        <v>1954327-3</v>
       </c>
       <c r="B204" t="s">
         <v>132</v>
@@ -8634,13 +8637,13 @@
         <v>17</v>
       </c>
       <c r="D204" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E204" t="s">
         <v>12</v>
       </c>
       <c r="G204" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H204" t="s">
         <v>14</v>
@@ -8651,242 +8654,245 @@
     </row>
     <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954326-3", "1954326-3")</f>
-        <v>1954326-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954675-1", "1954675-1")</f>
+        <v>1954675-1</v>
       </c>
       <c r="B205" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C205" t="s">
         <v>17</v>
       </c>
       <c r="D205" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="E205" t="s">
         <v>12</v>
       </c>
       <c r="G205" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H205" t="s">
         <v>14</v>
       </c>
       <c r="I205" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-1", "1954327-1")</f>
-        <v>1954327-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1957107-1", "1957107-1")</f>
+        <v>1957107-1</v>
       </c>
       <c r="B206" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C206" t="s">
         <v>17</v>
       </c>
       <c r="D206" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="E206" t="s">
         <v>12</v>
-      </c>
-      <c r="F206" t="s">
-        <v>30</v>
       </c>
       <c r="G206" t="s">
         <v>17</v>
       </c>
       <c r="H206" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="I206" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-2", "1954327-2")</f>
-        <v>1954327-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-1", "1959073-1")</f>
+        <v>1959073-1</v>
       </c>
       <c r="B207" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C207" t="s">
         <v>17</v>
       </c>
       <c r="D207" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="E207" t="s">
         <v>12</v>
       </c>
       <c r="G207" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H207" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="I207" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954327-3", "1954327-3")</f>
-        <v>1954327-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-2", "1959073-2")</f>
+        <v>1959073-2</v>
       </c>
       <c r="B208" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C208" t="s">
         <v>17</v>
       </c>
       <c r="D208" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="E208" t="s">
         <v>12</v>
       </c>
       <c r="G208" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="H208" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="I208" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
     </row>
     <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1954675-1", "1954675-1")</f>
-        <v>1954675-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-3", "1959073-3")</f>
+        <v>1959073-3</v>
       </c>
       <c r="B209" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C209" t="s">
         <v>17</v>
       </c>
       <c r="D209" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="E209" t="s">
         <v>12</v>
       </c>
       <c r="G209" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="H209" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I209" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1957107-1", "1957107-1")</f>
-        <v>1957107-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-4", "1959073-4")</f>
+        <v>1959073-4</v>
       </c>
       <c r="B210" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C210" t="s">
         <v>17</v>
       </c>
       <c r="D210" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="E210" t="s">
         <v>12</v>
       </c>
       <c r="G210" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H210" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="I210" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-1", "1959073-1")</f>
-        <v>1959073-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1960761-1", "1960761-1")</f>
+        <v>1960761-1</v>
       </c>
       <c r="B211" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C211" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="D211" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E211" t="s">
         <v>12</v>
       </c>
       <c r="G211" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="H211" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I211" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-2", "1959073-2")</f>
-        <v>1959073-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-1", "1961325-1")</f>
+        <v>1961325-1</v>
       </c>
       <c r="B212" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C212" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="D212" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E212" t="s">
         <v>12</v>
       </c>
+      <c r="F212" t="s">
+        <v>22</v>
+      </c>
       <c r="G212" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H212" t="s">
-        <v>139</v>
+        <v>14</v>
       </c>
       <c r="I212" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-3", "1959073-3")</f>
-        <v>1959073-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-2", "1961325-2")</f>
+        <v>1961325-2</v>
       </c>
       <c r="B213" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C213" t="s">
         <v>17</v>
       </c>
       <c r="D213" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E213" t="s">
         <v>12</v>
       </c>
+      <c r="F213" t="s">
+        <v>22</v>
+      </c>
       <c r="G213" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H213" t="s">
         <v>81</v>
@@ -8897,23 +8903,23 @@
     </row>
     <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1959073-4", "1959073-4")</f>
-        <v>1959073-4</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-3", "1961325-3")</f>
+        <v>1961325-3</v>
       </c>
       <c r="B214" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C214" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="D214" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E214" t="s">
         <v>12</v>
       </c>
       <c r="G214" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H214" t="s">
         <v>81</v>
@@ -8922,16 +8928,16 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1960761-1", "1960761-1")</f>
-        <v>1960761-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-4", "1961325-4")</f>
+        <v>1961325-4</v>
       </c>
       <c r="B215" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C215" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D215" t="s">
         <v>11</v>
@@ -8940,10 +8946,10 @@
         <v>12</v>
       </c>
       <c r="G215" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="H215" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="I215" t="s">
         <v>18</v>
@@ -8951,14 +8957,14 @@
     </row>
     <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-1", "1961325-1")</f>
-        <v>1961325-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-1", "1961327-1")</f>
+        <v>1961327-1</v>
       </c>
       <c r="B216" t="s">
         <v>142</v>
       </c>
       <c r="C216" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D216" t="s">
         <v>11</v>
@@ -8966,29 +8972,26 @@
       <c r="E216" t="s">
         <v>12</v>
       </c>
-      <c r="F216" t="s">
-        <v>22</v>
-      </c>
       <c r="G216" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H216" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I216" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-2", "1961325-2")</f>
-        <v>1961325-2</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-2", "1961327-2")</f>
+        <v>1961327-2</v>
       </c>
       <c r="B217" t="s">
         <v>142</v>
       </c>
       <c r="C217" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="D217" t="s">
         <v>11</v>
@@ -9000,7 +9003,7 @@
         <v>22</v>
       </c>
       <c r="G217" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H217" t="s">
         <v>81</v>
@@ -9011,14 +9014,14 @@
     </row>
     <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-3", "1961325-3")</f>
-        <v>1961325-3</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-3", "1961327-3")</f>
+        <v>1961327-3</v>
       </c>
       <c r="B218" t="s">
         <v>142</v>
       </c>
       <c r="C218" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D218" t="s">
         <v>11</v>
@@ -9027,7 +9030,7 @@
         <v>12</v>
       </c>
       <c r="G218" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H218" t="s">
         <v>81</v>
@@ -9038,14 +9041,14 @@
     </row>
     <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961325-4", "1961325-4")</f>
-        <v>1961325-4</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-4", "1961327-4")</f>
+        <v>1961327-4</v>
       </c>
       <c r="B219" t="s">
         <v>142</v>
       </c>
       <c r="C219" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="D219" t="s">
         <v>11</v>
@@ -9054,7 +9057,7 @@
         <v>12</v>
       </c>
       <c r="G219" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H219" t="s">
         <v>81</v>
@@ -9065,14 +9068,14 @@
     </row>
     <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-1", "1961327-1")</f>
-        <v>1961327-1</v>
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-5", "1961327-5")</f>
+        <v>1961327-5</v>
       </c>
       <c r="B220" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C220" t="s">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="D220" t="s">
         <v>11</v>
@@ -9081,7 +9084,7 @@
         <v>12</v>
       </c>
       <c r="G220" t="s">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="H220" t="s">
         <v>81</v>
@@ -9090,119 +9093,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-2", "1961327-2")</f>
-        <v>1961327-2</v>
-      </c>
-      <c r="B221" t="s">
-        <v>143</v>
-      </c>
-      <c r="C221" t="s">
-        <v>144</v>
-      </c>
-      <c r="D221" t="s">
-        <v>11</v>
-      </c>
-      <c r="E221" t="s">
-        <v>12</v>
-      </c>
-      <c r="F221" t="s">
-        <v>22</v>
-      </c>
-      <c r="G221" t="s">
-        <v>32</v>
-      </c>
-      <c r="H221" t="s">
-        <v>81</v>
-      </c>
-      <c r="I221" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-3", "1961327-3")</f>
-        <v>1961327-3</v>
-      </c>
-      <c r="B222" t="s">
-        <v>143</v>
-      </c>
-      <c r="C222" t="s">
-        <v>145</v>
-      </c>
-      <c r="D222" t="s">
-        <v>11</v>
-      </c>
-      <c r="E222" t="s">
-        <v>12</v>
-      </c>
-      <c r="G222" t="s">
-        <v>42</v>
-      </c>
-      <c r="H222" t="s">
-        <v>81</v>
-      </c>
-      <c r="I222" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A223" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-4", "1961327-4")</f>
-        <v>1961327-4</v>
-      </c>
-      <c r="B223" t="s">
-        <v>143</v>
-      </c>
-      <c r="C223" t="s">
-        <v>17</v>
-      </c>
-      <c r="D223" t="s">
-        <v>11</v>
-      </c>
-      <c r="E223" t="s">
-        <v>12</v>
-      </c>
-      <c r="G223" t="s">
-        <v>17</v>
-      </c>
-      <c r="H223" t="s">
-        <v>81</v>
-      </c>
-      <c r="I223" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="100" t="str">
-        <f>HYPERLINK("https://gnats.juniper.net/web/default/1961327-5", "1961327-5")</f>
-        <v>1961327-5</v>
-      </c>
-      <c r="B224" t="s">
-        <v>143</v>
-      </c>
-      <c r="C224" t="s">
-        <v>38</v>
-      </c>
-      <c r="D224" t="s">
-        <v>11</v>
-      </c>
-      <c r="E224" t="s">
-        <v>12</v>
-      </c>
-      <c r="G224" t="s">
-        <v>38</v>
-      </c>
-      <c r="H224" t="s">
-        <v>81</v>
-      </c>
-      <c r="I224" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I224" xr:uid="{101F05EA-6A87-7646-9D66-36E81A856E36}">
+  <autoFilter ref="A1:I220" xr:uid="{101F05EA-6A87-7646-9D66-36E81A856E36}">
     <filterColumn colId="7">
       <filters>
         <filter val="assigned"/>
@@ -9232,38 +9124,38 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="105" t="s">
         <v>146</v>
-      </c>
-      <c r="B1" s="105" t="s">
-        <v>147</v>
       </c>
       <c r="C1" s="106"/>
       <c r="D1" s="36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="C2" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="D2" s="40" t="s">
         <v>151</v>
-      </c>
-      <c r="D2" s="40" t="s">
-        <v>152</v>
       </c>
       <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="41" t="s">
         <v>153</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>154</v>
       </c>
       <c r="C3" s="15">
         <v>95</v>
@@ -9275,10 +9167,10 @@
     </row>
     <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="C4" s="15">
         <v>80</v>
@@ -9287,15 +9179,15 @@
         <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="C5" s="4">
         <v>92</v>
@@ -9307,10 +9199,10 @@
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="C6" s="1">
         <v>95</v>
@@ -9322,10 +9214,10 @@
     </row>
     <row r="7" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="C7" s="4">
         <v>95</v>
@@ -9336,10 +9228,10 @@
     </row>
     <row r="8" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>165</v>
       </c>
       <c r="C8" s="4">
         <v>91</v>
@@ -9350,10 +9242,10 @@
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="C9" s="4">
         <v>96</v>
@@ -9364,10 +9256,10 @@
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>169</v>
       </c>
       <c r="C10" s="4">
         <v>93</v>
@@ -9378,10 +9270,10 @@
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>171</v>
       </c>
       <c r="C11" s="4">
         <v>93</v>
@@ -9392,10 +9284,10 @@
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="C12" s="1">
         <v>93</v>
@@ -9406,10 +9298,10 @@
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>175</v>
       </c>
       <c r="C13" s="1">
         <v>94</v>
@@ -9420,10 +9312,10 @@
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="C14" s="4">
         <v>95</v>
@@ -9434,10 +9326,10 @@
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>179</v>
       </c>
       <c r="C15" s="1">
         <v>95</v>
@@ -9448,10 +9340,10 @@
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="C16" s="46">
         <v>94</v>
@@ -9462,10 +9354,10 @@
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>182</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>183</v>
       </c>
       <c r="C17" s="7">
         <v>96</v>
@@ -9476,24 +9368,24 @@
     </row>
     <row r="18" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B18" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="D18" s="40" t="s">
         <v>151</v>
-      </c>
-      <c r="D18" s="40" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" s="44" t="s">
         <v>185</v>
-      </c>
-      <c r="B19" s="44" t="s">
-        <v>186</v>
       </c>
       <c r="C19" s="27">
         <v>85</v>
@@ -9504,10 +9396,10 @@
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="C20" s="23">
         <v>90</v>
@@ -9518,10 +9410,10 @@
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="C21" s="10">
         <v>92</v>
@@ -9532,10 +9424,10 @@
     </row>
     <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="C22" s="10">
         <v>90</v>
@@ -9546,10 +9438,10 @@
     </row>
     <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="C23" s="10">
         <v>90</v>
@@ -9560,10 +9452,10 @@
     </row>
     <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="C24" s="10">
         <v>95</v>
@@ -9574,10 +9466,10 @@
     </row>
     <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="C25" s="10">
         <v>91</v>
@@ -9588,10 +9480,10 @@
     </row>
     <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="C26" s="10">
         <v>93</v>
@@ -9602,10 +9494,10 @@
     </row>
     <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="C27" s="10">
         <v>92</v>
@@ -9616,10 +9508,10 @@
     </row>
     <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="C28" s="10">
         <v>93</v>
@@ -9630,103 +9522,103 @@
     </row>
     <row r="29" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="B29" s="39" t="s">
         <v>205</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="C29" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="D29" s="40" t="s">
         <v>206</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="D29" s="40" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>209</v>
       </c>
       <c r="C30" s="47">
         <v>77</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C31" s="47">
         <v>77</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E31" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C32" s="47">
         <v>77</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C33" s="47">
         <v>93</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B34" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="40" t="s">
+      <c r="D34" s="40" t="s">
         <v>151</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="C35" s="48">
         <v>90</v>
@@ -9737,7 +9629,7 @@
     </row>
     <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B36" s="4">
         <v>19330</v>
@@ -9751,7 +9643,7 @@
     </row>
     <row r="37" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B37" s="4">
         <v>10000</v>
@@ -9765,7 +9657,7 @@
     </row>
     <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B38" s="4">
         <v>2400</v>
@@ -9779,7 +9671,7 @@
     </row>
     <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B39" s="15">
         <v>2250</v>
@@ -9793,7 +9685,7 @@
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B40" s="45">
         <v>975</v>
@@ -9807,7 +9699,7 @@
     </row>
     <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B41" s="4">
         <v>1550</v>
@@ -9821,7 +9713,7 @@
     </row>
     <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B42" s="4">
         <v>400</v>
@@ -9835,7 +9727,7 @@
     </row>
     <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B43" s="4">
         <v>175</v>
@@ -9849,83 +9741,83 @@
     </row>
     <row r="44" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B44" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C44" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="C44" s="40" t="s">
-        <v>151</v>
-      </c>
       <c r="D44" s="40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>227</v>
       </c>
       <c r="C45" s="33">
         <v>98</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>230</v>
       </c>
       <c r="C46" s="49">
         <v>98</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="C47" s="23">
         <v>90</v>
       </c>
       <c r="D47" s="56" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E47" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>234</v>
       </c>
       <c r="C48" s="23">
         <v>98</v>
       </c>
       <c r="D48" s="57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>237</v>
       </c>
       <c r="C49" s="23">
         <v>50</v>
@@ -9934,38 +9826,38 @@
     </row>
     <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="C50" s="23">
         <v>99</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>240</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>241</v>
       </c>
       <c r="C51" s="32">
         <v>98</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>243</v>
       </c>
       <c r="C52" s="23">
         <v>99</v>
@@ -9974,150 +9866,150 @@
     </row>
     <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B53" s="15" t="s">
         <v>244</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>245</v>
       </c>
       <c r="C53" s="31">
         <v>99</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>247</v>
       </c>
       <c r="C54" s="23">
         <v>98</v>
       </c>
       <c r="D54" s="57" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>250</v>
       </c>
       <c r="C55" s="23">
         <v>98</v>
       </c>
       <c r="D55" s="57" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>253</v>
       </c>
       <c r="C56" s="23">
         <v>99</v>
       </c>
       <c r="D56" s="57" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="C57" s="23">
         <v>98</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="C58" s="23">
         <v>80</v>
       </c>
       <c r="D58" s="57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="C59" s="23">
         <v>80</v>
       </c>
       <c r="D59" s="57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="C60" s="23">
         <v>80</v>
       </c>
       <c r="D60" s="57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>265</v>
       </c>
       <c r="C61" s="23">
         <v>78</v>
       </c>
       <c r="D61" s="57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>267</v>
       </c>
       <c r="C62" s="23">
         <v>85</v>
       </c>
       <c r="D62" s="57" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>269</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>270</v>
       </c>
       <c r="C63" s="23">
         <v>44</v>
@@ -10126,43 +10018,43 @@
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="C64" s="23">
         <v>80</v>
       </c>
       <c r="D64" s="57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B65" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="C65" s="51"/>
       <c r="D65" s="56"/>
     </row>
     <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="B66" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="B66" s="20" t="s">
-        <v>277</v>
-      </c>
       <c r="C66" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D66" s="65"/>
     </row>
     <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B67" s="24">
         <v>48</v>
@@ -10176,7 +10068,7 @@
     </row>
     <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B68" s="24">
         <v>1500</v>
@@ -10190,7 +10082,7 @@
     </row>
     <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B69" s="24">
         <v>2550</v>
@@ -10204,7 +10096,7 @@
     </row>
     <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B70" s="24">
         <v>48</v>
@@ -10218,7 +10110,7 @@
     </row>
     <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B71" s="24">
         <v>1500</v>
@@ -10232,7 +10124,7 @@
     </row>
     <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B72" s="5">
         <v>1280</v>
@@ -10246,7 +10138,7 @@
     </row>
     <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B73" s="24">
         <v>32</v>
@@ -10260,7 +10152,7 @@
     </row>
     <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B74" s="24">
         <v>102</v>
@@ -10274,7 +10166,7 @@
     </row>
     <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B75" s="24">
         <v>1020</v>
@@ -10288,7 +10180,7 @@
     </row>
     <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B76" s="24">
         <v>2000</v>
@@ -10302,7 +10194,7 @@
     </row>
     <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B77" s="68">
         <v>1024</v>
@@ -10316,7 +10208,7 @@
     </row>
     <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B78" s="24">
         <v>1280</v>
@@ -10330,7 +10222,7 @@
     </row>
     <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B79" s="24">
         <v>1280</v>
@@ -10344,7 +10236,7 @@
     </row>
     <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B80" s="24">
         <v>128</v>
@@ -10354,7 +10246,7 @@
     </row>
     <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B81" s="24">
         <v>1750</v>
@@ -10364,7 +10256,7 @@
     </row>
     <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B82" s="33"/>
       <c r="C82" s="23"/>
@@ -10372,7 +10264,7 @@
     </row>
     <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B83" s="24"/>
       <c r="C83" s="10"/>
@@ -10380,7 +10272,7 @@
     </row>
     <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B84" s="24">
         <v>128</v>
@@ -10394,10 +10286,10 @@
     </row>
     <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B85" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="B85" s="10" t="s">
-        <v>297</v>
       </c>
       <c r="C85" s="10">
         <v>10</v>
@@ -10408,10 +10300,10 @@
     </row>
     <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B86" s="10" t="s">
         <v>298</v>
-      </c>
-      <c r="B86" s="10" t="s">
-        <v>299</v>
       </c>
       <c r="C86" s="10">
         <v>10</v>
@@ -10422,7 +10314,7 @@
     </row>
     <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B87" s="24"/>
       <c r="C87" s="10"/>
@@ -10430,7 +10322,7 @@
     </row>
     <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B88" s="24"/>
       <c r="C88" s="10"/>
@@ -10438,7 +10330,7 @@
     </row>
     <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B89" s="24"/>
       <c r="C89" s="10"/>
@@ -10446,7 +10338,7 @@
     </row>
     <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B90" s="10">
         <v>80000</v>
@@ -10460,7 +10352,7 @@
     </row>
     <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B91" s="24">
         <v>80000</v>
@@ -10474,7 +10366,7 @@
     </row>
     <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B92" s="51">
         <v>80000</v>
@@ -10484,7 +10376,7 @@
     </row>
     <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B93" s="24">
         <v>80000</v>
@@ -10498,7 +10390,7 @@
     </row>
     <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B94" s="24">
         <v>32000</v>
@@ -10512,7 +10404,7 @@
     </row>
     <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B95" s="34">
         <v>8000</v>
@@ -10526,19 +10418,19 @@
     </row>
     <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B96" s="68">
         <v>26000</v>
       </c>
       <c r="C96" s="66"/>
       <c r="D96" s="66" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B97" s="24">
         <v>1000</v>
@@ -10552,7 +10444,7 @@
     </row>
     <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B98" s="24">
         <v>300</v>
@@ -10566,13 +10458,13 @@
     </row>
     <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B99" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="B99" s="16" t="s">
+      <c r="C99" s="10" t="s">
         <v>314</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>315</v>
       </c>
       <c r="D99" s="10">
         <v>75</v>
@@ -10580,13 +10472,13 @@
     </row>
     <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B100" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="B100" s="10" t="s">
-        <v>317</v>
-      </c>
       <c r="C100" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D100" s="10">
         <v>75</v>
@@ -10594,13 +10486,13 @@
     </row>
     <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B101" s="24">
         <v>10</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D101" s="10">
         <v>75</v>
@@ -10646,36 +10538,36 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="50" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1" s="105" t="s">
         <v>319</v>
-      </c>
-      <c r="B1" s="105" t="s">
-        <v>320</v>
       </c>
       <c r="C1" s="106"/>
       <c r="D1" s="36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="C2" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="D2" s="40" t="s">
         <v>151</v>
-      </c>
-      <c r="D2" s="40" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C3" s="57">
         <v>91</v>
@@ -10686,10 +10578,10 @@
     </row>
     <row r="4" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C4" s="4">
         <v>70</v>
@@ -10698,15 +10590,15 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C5" s="4">
         <v>92</v>
@@ -10717,10 +10609,10 @@
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C6" s="4">
         <v>94</v>
@@ -10731,10 +10623,10 @@
     </row>
     <row r="7" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C7" s="57">
         <v>96</v>
@@ -10745,10 +10637,10 @@
     </row>
     <row r="8" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C8" s="4">
         <v>90</v>
@@ -10759,10 +10651,10 @@
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C9" s="57">
         <v>90</v>
@@ -10773,10 +10665,10 @@
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C10" s="4">
         <v>90</v>
@@ -10787,10 +10679,10 @@
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C11" s="4">
         <v>92</v>
@@ -10801,10 +10693,10 @@
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C12" s="57">
         <v>92</v>
@@ -10815,10 +10707,10 @@
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C13" s="4">
         <v>90</v>
@@ -10829,10 +10721,10 @@
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C14" s="4">
         <v>90</v>
@@ -10843,10 +10735,10 @@
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C15" s="4">
         <v>94</v>
@@ -10857,10 +10749,10 @@
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C16" s="4">
         <v>92</v>
@@ -10871,10 +10763,10 @@
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C17" s="7">
         <v>92</v>
@@ -10885,24 +10777,24 @@
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C18" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="40" t="s">
         <v>151</v>
-      </c>
-      <c r="D18" s="40" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C19" s="54">
         <v>92</v>
@@ -10913,10 +10805,10 @@
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C20" s="56">
         <v>95</v>
@@ -10927,10 +10819,10 @@
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C21" s="56">
         <v>95</v>
@@ -10941,10 +10833,10 @@
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C22" s="56">
         <v>93</v>
@@ -10955,10 +10847,10 @@
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C23" s="56">
         <v>92</v>
@@ -10969,10 +10861,10 @@
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C24" s="56">
         <v>92</v>
@@ -10981,15 +10873,15 @@
         <v>67</v>
       </c>
       <c r="F24" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C25" s="56">
         <v>92</v>
@@ -11000,10 +10892,10 @@
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C26" s="56">
         <v>90</v>
@@ -11014,10 +10906,10 @@
     </row>
     <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C27" s="56">
         <v>90</v>
@@ -11028,10 +10920,10 @@
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C28" s="56">
         <v>92</v>
@@ -11042,103 +10934,103 @@
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>209</v>
       </c>
       <c r="C30" s="47">
         <v>68</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C31" s="47">
         <v>68</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E31" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C32" s="47">
         <v>68</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C33" s="56">
         <v>92</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C34" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="40" t="s">
         <v>151</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B35" s="48" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C35" s="62">
         <v>90</v>
@@ -11149,7 +11041,7 @@
     </row>
     <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B36" s="4">
         <v>25400</v>
@@ -11178,7 +11070,7 @@
     </row>
     <row r="37" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B37" s="4">
         <v>13300</v>
@@ -11212,7 +11104,7 @@
     </row>
     <row r="38" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B38" s="4">
         <v>3200</v>
@@ -11246,7 +11138,7 @@
     </row>
     <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B39" s="15">
         <v>2700</v>
@@ -11260,7 +11152,7 @@
     </row>
     <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B40" s="45">
         <v>1050</v>
@@ -11277,7 +11169,7 @@
     </row>
     <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B41" s="4">
         <v>1810</v>
@@ -11295,7 +11187,7 @@
     </row>
     <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B42" s="1">
         <v>460</v>
@@ -11312,7 +11204,7 @@
     </row>
     <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B43" s="4">
         <v>205</v>
@@ -11330,80 +11222,80 @@
     </row>
     <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C44" s="40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C45" s="24">
         <v>98</v>
       </c>
       <c r="D45" s="57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C46" s="24">
         <v>98</v>
       </c>
       <c r="D46" s="57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C47" s="56">
         <v>96</v>
       </c>
       <c r="D47" s="57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C48" s="56">
         <v>96</v>
       </c>
       <c r="D48" s="57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C49" s="23">
         <v>50</v>
@@ -11412,192 +11304,192 @@
     </row>
     <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C50" s="54">
         <v>98</v>
       </c>
       <c r="D50" s="57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C51" s="56">
         <v>98</v>
       </c>
       <c r="D51" s="57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C52" s="56">
         <v>99</v>
       </c>
       <c r="D52" s="57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C53" s="63">
         <v>99</v>
       </c>
       <c r="D53" s="57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="18" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C54" s="64">
         <v>98</v>
       </c>
       <c r="D54" s="57" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C55" s="64">
         <v>98</v>
       </c>
       <c r="D55" s="57" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C56" s="64">
         <v>96</v>
       </c>
       <c r="D56" s="57" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C57" s="56">
         <v>96</v>
       </c>
       <c r="D57" s="57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C58" s="54">
         <v>78</v>
       </c>
       <c r="D58" s="57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C59" s="56">
         <v>77</v>
       </c>
       <c r="D59" s="57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C60" s="56">
         <v>79</v>
       </c>
       <c r="D60" s="57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C61" s="56">
         <v>72</v>
       </c>
       <c r="D61" s="57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B62" s="32" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C62" s="56">
         <v>88</v>
       </c>
       <c r="D62" s="57" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C63" s="56">
         <v>50</v>
@@ -11606,45 +11498,45 @@
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B64" s="52" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C64" s="56">
         <v>79</v>
       </c>
       <c r="D64" s="57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B65" s="51" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C65" s="56"/>
       <c r="D65" s="57"/>
     </row>
     <row r="66" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="B66" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="B66" s="30" t="s">
-        <v>277</v>
-      </c>
       <c r="C66" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D66" s="65" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B67" s="10">
         <v>64</v>
@@ -11658,7 +11550,7 @@
     </row>
     <row r="68" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B68" s="10">
         <v>2000</v>
@@ -11683,7 +11575,7 @@
     </row>
     <row r="69" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B69" s="10"/>
       <c r="C69" s="56"/>
@@ -11691,7 +11583,7 @@
     </row>
     <row r="70" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B70" s="10">
         <v>64</v>
@@ -11705,7 +11597,7 @@
     </row>
     <row r="71" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B71" s="10">
         <v>2000</v>
@@ -11719,7 +11611,7 @@
     </row>
     <row r="72" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B72" s="10">
         <v>1536</v>
@@ -11733,7 +11625,7 @@
     </row>
     <row r="73" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B73" s="10">
         <v>48</v>
@@ -11747,7 +11639,7 @@
     </row>
     <row r="74" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B74" s="10">
         <v>1280</v>
@@ -11761,7 +11653,7 @@
     </row>
     <row r="75" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B75" s="10">
         <v>2000</v>
@@ -11775,7 +11667,7 @@
     </row>
     <row r="76" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B76" s="66">
         <v>1024</v>
@@ -11789,7 +11681,7 @@
     </row>
     <row r="77" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B77" s="10">
         <v>1536</v>
@@ -11803,7 +11695,7 @@
     </row>
     <row r="78" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B78" s="10">
         <v>1536</v>
@@ -11817,7 +11709,7 @@
     </row>
     <row r="79" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B79" s="10">
         <v>256</v>
@@ -11827,7 +11719,7 @@
     </row>
     <row r="80" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B80" s="32">
         <v>2000</v>
@@ -11837,7 +11729,7 @@
     </row>
     <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B81" s="23"/>
       <c r="C81" s="56"/>
@@ -11845,7 +11737,7 @@
     </row>
     <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B82" s="10"/>
       <c r="C82" s="56"/>
@@ -11853,7 +11745,7 @@
     </row>
     <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B83" s="10">
         <v>128</v>
@@ -11867,10 +11759,10 @@
     </row>
     <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C84" s="10">
         <v>10</v>
@@ -11881,10 +11773,10 @@
     </row>
     <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C85" s="10">
         <v>10</v>
@@ -11895,7 +11787,7 @@
     </row>
     <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B86" s="10"/>
       <c r="C86" s="56"/>
@@ -11903,7 +11795,7 @@
     </row>
     <row r="87" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B87" s="10"/>
       <c r="C87" s="56"/>
@@ -11911,7 +11803,7 @@
     </row>
     <row r="88" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B88" s="10"/>
       <c r="C88" s="56"/>
@@ -11919,7 +11811,7 @@
     </row>
     <row r="89" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B89" s="10">
         <v>96000</v>
@@ -11933,7 +11825,7 @@
     </row>
     <row r="90" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B90" s="10">
         <v>96000</v>
@@ -11947,7 +11839,7 @@
     </row>
     <row r="91" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B91" s="51">
         <v>96000</v>
@@ -11959,7 +11851,7 @@
     </row>
     <row r="92" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B92" s="26">
         <v>48000</v>
@@ -11971,7 +11863,7 @@
     </row>
     <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B93" s="26">
         <v>48000</v>
@@ -11983,7 +11875,7 @@
     </row>
     <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B94" s="35">
         <v>8000</v>
@@ -11997,19 +11889,19 @@
     </row>
     <row r="95" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B95" s="68">
         <v>26000</v>
       </c>
       <c r="C95" s="66"/>
       <c r="D95" s="66" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B96" s="10">
         <v>1200</v>
@@ -12023,7 +11915,7 @@
     </row>
     <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B97" s="10">
         <v>500</v>
@@ -12037,27 +11929,27 @@
     </row>
     <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="56"/>
     </row>
     <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="56"/>
     </row>
     <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B100" s="10">
         <v>10</v>
@@ -12107,52 +11999,52 @@
   <sheetData>
     <row r="1" spans="1:7" ht="75" x14ac:dyDescent="0.3">
       <c r="A1" s="75" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B1" s="103" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C1" s="104"/>
       <c r="D1" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E1" s="103" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F1" s="104"/>
       <c r="G1" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="50" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
+        <v>378</v>
+      </c>
+      <c r="B2" s="79" t="s">
+        <v>335</v>
+      </c>
+      <c r="C2" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="79" t="s">
         <v>379</v>
       </c>
-      <c r="B2" s="79" t="s">
-        <v>336</v>
-      </c>
-      <c r="C2" s="80" t="s">
+      <c r="E2" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" s="80" t="s">
         <v>151</v>
-      </c>
-      <c r="D2" s="79" t="s">
-        <v>380</v>
-      </c>
-      <c r="E2" s="79" t="s">
-        <v>150</v>
-      </c>
-      <c r="F2" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="G2" s="80" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A3" s="81" t="s">
+        <v>380</v>
+      </c>
+      <c r="B3" s="82" t="s">
         <v>381</v>
-      </c>
-      <c r="B3" s="82" t="s">
-        <v>382</v>
       </c>
       <c r="C3" s="83">
         <v>94</v>
@@ -12161,7 +12053,7 @@
         <v>40</v>
       </c>
       <c r="E3" s="82" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F3" s="83">
         <v>93</v>
@@ -12172,10 +12064,10 @@
     </row>
     <row r="4" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A4" s="81" t="s">
+        <v>383</v>
+      </c>
+      <c r="B4" s="84" t="s">
         <v>384</v>
-      </c>
-      <c r="B4" s="84" t="s">
-        <v>385</v>
       </c>
       <c r="C4" s="85">
         <v>95</v>
@@ -12184,7 +12076,7 @@
         <v>40</v>
       </c>
       <c r="E4" s="84" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F4" s="85">
         <v>94</v>
@@ -12195,10 +12087,10 @@
     </row>
     <row r="5" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A5" s="81" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B5" s="87" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C5" s="88">
         <v>94</v>
@@ -12207,7 +12099,7 @@
         <v>60</v>
       </c>
       <c r="E5" s="87" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F5" s="88">
         <v>91</v>
@@ -12218,136 +12110,136 @@
     </row>
     <row r="6" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A6" s="90" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" s="84" t="s">
         <v>226</v>
-      </c>
-      <c r="B6" s="84" t="s">
-        <v>227</v>
       </c>
       <c r="C6" s="91">
         <v>99</v>
       </c>
       <c r="D6" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E6" s="84" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F6" s="84">
         <v>98</v>
       </c>
       <c r="G6" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A7" s="90" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="84" t="s">
         <v>229</v>
-      </c>
-      <c r="B7" s="84" t="s">
-        <v>230</v>
       </c>
       <c r="C7" s="93">
         <v>99</v>
       </c>
       <c r="D7" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E7" s="84" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F7" s="84">
         <v>98</v>
       </c>
       <c r="G7" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A8" s="94" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="87" t="s">
         <v>231</v>
-      </c>
-      <c r="B8" s="87" t="s">
-        <v>232</v>
       </c>
       <c r="C8" s="88">
         <v>90</v>
       </c>
       <c r="D8" s="89" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E8" s="84" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F8" s="84">
         <v>96</v>
       </c>
       <c r="G8" s="89" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B9" s="84"/>
       <c r="C9" s="88"/>
       <c r="D9" s="95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E9" s="84"/>
       <c r="F9" s="88"/>
       <c r="G9" s="95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="75" x14ac:dyDescent="0.3">
       <c r="A12" s="75" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B12" s="103" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" s="104"/>
       <c r="D12" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E12" s="103" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F12" s="104"/>
       <c r="G12" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="50" x14ac:dyDescent="0.3">
       <c r="A13" s="78" t="s">
+        <v>378</v>
+      </c>
+      <c r="B13" s="79" t="s">
+        <v>335</v>
+      </c>
+      <c r="C13" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="79" t="s">
         <v>379</v>
       </c>
-      <c r="B13" s="79" t="s">
-        <v>336</v>
-      </c>
-      <c r="C13" s="80" t="s">
+      <c r="E13" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13" s="80" t="s">
         <v>151</v>
-      </c>
-      <c r="D13" s="79" t="s">
-        <v>380</v>
-      </c>
-      <c r="E13" s="79" t="s">
-        <v>150</v>
-      </c>
-      <c r="F13" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="G13" s="80" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A14" s="81" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B14" s="82" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C14" s="83">
         <v>95</v>
@@ -12356,7 +12248,7 @@
         <v>61</v>
       </c>
       <c r="E14" s="82" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F14" s="83">
         <v>93</v>
@@ -12367,10 +12259,10 @@
     </row>
     <row r="15" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A15" s="81" t="s">
+        <v>383</v>
+      </c>
+      <c r="B15" s="84" t="s">
         <v>384</v>
-      </c>
-      <c r="B15" s="84" t="s">
-        <v>385</v>
       </c>
       <c r="C15" s="85">
         <v>95</v>
@@ -12379,7 +12271,7 @@
         <v>61</v>
       </c>
       <c r="E15" s="84" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F15" s="85">
         <v>94</v>
@@ -12390,10 +12282,10 @@
     </row>
     <row r="16" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A16" s="81" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B16" s="87" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C16" s="88">
         <v>94</v>
@@ -12402,7 +12294,7 @@
         <v>60</v>
       </c>
       <c r="E16" s="87" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F16" s="88">
         <v>91</v>
@@ -12413,128 +12305,128 @@
     </row>
     <row r="17" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A17" s="90" t="s">
+        <v>225</v>
+      </c>
+      <c r="B17" s="84" t="s">
         <v>226</v>
-      </c>
-      <c r="B17" s="84" t="s">
-        <v>227</v>
       </c>
       <c r="C17" s="91">
         <v>99</v>
       </c>
       <c r="D17" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E17" s="84" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F17" s="84">
         <v>98</v>
       </c>
       <c r="G17" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A18" s="90" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="84" t="s">
         <v>229</v>
-      </c>
-      <c r="B18" s="84" t="s">
-        <v>230</v>
       </c>
       <c r="C18" s="93">
         <v>99</v>
       </c>
       <c r="D18" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E18" s="84" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F18" s="84">
         <v>98</v>
       </c>
       <c r="G18" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A19" s="94" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" s="87" t="s">
         <v>231</v>
-      </c>
-      <c r="B19" s="87" t="s">
-        <v>232</v>
       </c>
       <c r="C19" s="88">
         <v>90</v>
       </c>
       <c r="D19" s="89" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E19" s="84" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F19" s="84">
         <v>96</v>
       </c>
       <c r="G19" s="89" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A20" s="81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B20" s="84"/>
       <c r="C20" s="88"/>
       <c r="D20" s="95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E20" s="84"/>
       <c r="F20" s="88"/>
       <c r="G20" s="95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="75" x14ac:dyDescent="0.3">
       <c r="A23" s="96" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B23" s="103" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C23" s="104"/>
       <c r="D23" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E23" s="103" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F23" s="104"/>
       <c r="G23" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="50" x14ac:dyDescent="0.3">
       <c r="A24" s="78" t="s">
+        <v>378</v>
+      </c>
+      <c r="B24" s="79" t="s">
+        <v>335</v>
+      </c>
+      <c r="C24" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="79" t="s">
         <v>379</v>
       </c>
-      <c r="B24" s="79" t="s">
-        <v>336</v>
-      </c>
-      <c r="C24" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="D24" s="79" t="s">
-        <v>380</v>
-      </c>
       <c r="E24" s="79" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G24" s="79" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I24" s="77">
         <v>280000</v>
@@ -12542,10 +12434,10 @@
     </row>
     <row r="25" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A25" s="81" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B25" s="82" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C25" s="83">
         <v>94</v>
@@ -12554,7 +12446,7 @@
         <v>40</v>
       </c>
       <c r="E25" s="82" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F25" s="83">
         <v>93</v>
@@ -12569,10 +12461,10 @@
     </row>
     <row r="26" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A26" s="81" t="s">
+        <v>383</v>
+      </c>
+      <c r="B26" s="84" t="s">
         <v>384</v>
-      </c>
-      <c r="B26" s="84" t="s">
-        <v>385</v>
       </c>
       <c r="C26" s="85">
         <v>95</v>
@@ -12581,7 +12473,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="84" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F26" s="85">
         <v>94</v>
@@ -12592,10 +12484,10 @@
     </row>
     <row r="27" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A27" s="81" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B27" s="87" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C27" s="88">
         <v>75</v>
@@ -12604,7 +12496,7 @@
         <v>56</v>
       </c>
       <c r="E27" s="87" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F27" s="88">
         <v>75</v>
@@ -12613,107 +12505,107 @@
         <v>59</v>
       </c>
       <c r="H27" s="77" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A28" s="90" t="s">
+        <v>225</v>
+      </c>
+      <c r="B28" s="84" t="s">
         <v>226</v>
-      </c>
-      <c r="B28" s="84" t="s">
-        <v>227</v>
       </c>
       <c r="C28" s="91">
         <v>99</v>
       </c>
       <c r="D28" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E28" s="84" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F28" s="84">
         <v>98</v>
       </c>
       <c r="G28" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A29" s="90" t="s">
+        <v>228</v>
+      </c>
+      <c r="B29" s="84" t="s">
         <v>229</v>
-      </c>
-      <c r="B29" s="84" t="s">
-        <v>230</v>
       </c>
       <c r="C29" s="93">
         <v>99</v>
       </c>
       <c r="D29" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="84" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F29" s="84">
         <v>98</v>
       </c>
       <c r="G29" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A30" s="94" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" s="87" t="s">
         <v>231</v>
-      </c>
-      <c r="B30" s="87" t="s">
-        <v>232</v>
       </c>
       <c r="C30" s="88">
         <v>90</v>
       </c>
       <c r="D30" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E30" s="84" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F30" s="84">
         <v>96</v>
       </c>
       <c r="G30" s="89" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A31" s="81" t="s">
+        <v>259</v>
+      </c>
+      <c r="B31" s="87" t="s">
         <v>260</v>
-      </c>
-      <c r="B31" s="87" t="s">
-        <v>261</v>
       </c>
       <c r="C31" s="87">
         <v>80</v>
       </c>
       <c r="D31" s="95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E31" s="84" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F31" s="84">
         <v>77</v>
       </c>
       <c r="G31" s="95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A32" s="97" t="s">
+        <v>397</v>
+      </c>
+      <c r="B32" s="98" t="s">
         <v>398</v>
-      </c>
-      <c r="B32" s="98" t="s">
-        <v>399</v>
       </c>
       <c r="C32" s="98">
         <v>75</v>
@@ -12722,7 +12614,7 @@
         <v>60</v>
       </c>
       <c r="E32" s="98" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F32" s="98">
         <v>62</v>
@@ -12731,57 +12623,57 @@
         <v>60</v>
       </c>
       <c r="H32" s="77" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A34" s="96" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B34" s="103" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="104"/>
       <c r="D34" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E34" s="103" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F34" s="104"/>
       <c r="G34" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="50" x14ac:dyDescent="0.3">
       <c r="A35" s="78" t="s">
+        <v>378</v>
+      </c>
+      <c r="B35" s="79" t="s">
+        <v>335</v>
+      </c>
+      <c r="C35" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="79" t="s">
         <v>379</v>
       </c>
-      <c r="B35" s="79" t="s">
-        <v>336</v>
-      </c>
-      <c r="C35" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="D35" s="79" t="s">
-        <v>380</v>
-      </c>
       <c r="E35" s="79" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F35" s="80" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G35" s="79" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A36" s="81" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B36" s="82" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C36" s="83">
         <v>93</v>
@@ -12790,7 +12682,7 @@
         <v>40</v>
       </c>
       <c r="E36" s="82" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F36" s="83">
         <v>95</v>
@@ -12801,10 +12693,10 @@
     </row>
     <row r="37" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A37" s="81" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B37" s="84" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C37" s="85">
         <v>94</v>
@@ -12824,10 +12716,10 @@
     </row>
     <row r="38" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A38" s="81" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B38" s="87" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C38" s="88">
         <v>79</v>
@@ -12836,7 +12728,7 @@
         <v>62</v>
       </c>
       <c r="E38" s="87" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F38" s="88">
         <v>80</v>
@@ -12845,107 +12737,107 @@
         <v>60</v>
       </c>
       <c r="H38" s="77" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A39" s="90" t="s">
+        <v>225</v>
+      </c>
+      <c r="B39" s="84" t="s">
         <v>226</v>
-      </c>
-      <c r="B39" s="84" t="s">
-        <v>227</v>
       </c>
       <c r="C39" s="91">
         <v>99</v>
       </c>
       <c r="D39" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E39" s="84" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F39" s="84">
         <v>99</v>
       </c>
       <c r="G39" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A40" s="90" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40" s="84" t="s">
         <v>229</v>
-      </c>
-      <c r="B40" s="84" t="s">
-        <v>230</v>
       </c>
       <c r="C40" s="93">
         <v>99</v>
       </c>
       <c r="D40" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E40" s="84" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F40" s="84">
         <v>99</v>
       </c>
       <c r="G40" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A41" s="94" t="s">
+        <v>230</v>
+      </c>
+      <c r="B41" s="87" t="s">
         <v>231</v>
-      </c>
-      <c r="B41" s="87" t="s">
-        <v>232</v>
       </c>
       <c r="C41" s="88">
         <v>90</v>
       </c>
       <c r="D41" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E41" s="84" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F41" s="84">
         <v>96</v>
       </c>
       <c r="G41" s="89" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A42" s="81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B42" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C42" s="87">
         <v>80</v>
       </c>
       <c r="D42" s="95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E42" s="84" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F42" s="84">
         <v>75</v>
       </c>
       <c r="G42" s="95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A43" s="97" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B43" s="98" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C43" s="98">
         <v>77</v>
@@ -12954,7 +12846,7 @@
         <v>68</v>
       </c>
       <c r="E43" s="98" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F43" s="98">
         <v>75</v>
@@ -12963,41 +12855,41 @@
         <v>70</v>
       </c>
       <c r="H43" s="77" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A45" s="96" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B45" s="103" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C45" s="104"/>
       <c r="D45" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="50" x14ac:dyDescent="0.3">
       <c r="A46" s="78" t="s">
+        <v>378</v>
+      </c>
+      <c r="B46" s="79" t="s">
+        <v>335</v>
+      </c>
+      <c r="C46" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="D46" s="79" t="s">
         <v>379</v>
-      </c>
-      <c r="B46" s="79" t="s">
-        <v>336</v>
-      </c>
-      <c r="C46" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="D46" s="79" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A47" s="81" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B47" s="82" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C47" s="83">
         <v>93</v>
@@ -13008,10 +12900,10 @@
     </row>
     <row r="48" spans="1:8" ht="25" x14ac:dyDescent="0.3">
       <c r="A48" s="81" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B48" s="84" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C48" s="85">
         <v>94</v>
@@ -13022,10 +12914,10 @@
     </row>
     <row r="49" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A49" s="81" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B49" s="87" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C49" s="88">
         <v>80</v>
@@ -13036,66 +12928,66 @@
     </row>
     <row r="50" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A50" s="90" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B50" s="84" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C50" s="84">
         <v>99</v>
       </c>
       <c r="D50" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A51" s="90" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B51" s="84" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C51" s="84">
         <v>99</v>
       </c>
       <c r="D51" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A52" s="94" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B52" s="84" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C52" s="84">
         <v>96</v>
       </c>
       <c r="D52" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A53" s="81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B53" s="101" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C53" s="87">
         <v>80</v>
       </c>
       <c r="D53" s="95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A54" s="97" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B54" s="98" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C54" s="98">
         <v>77</v>
@@ -13106,52 +12998,52 @@
     </row>
     <row r="56" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A56" s="96" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B56" s="103" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C56" s="104"/>
       <c r="D56" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E56" s="103" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F56" s="104"/>
       <c r="G56" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="50" x14ac:dyDescent="0.3">
       <c r="A57" s="78" t="s">
+        <v>378</v>
+      </c>
+      <c r="B57" s="79" t="s">
+        <v>335</v>
+      </c>
+      <c r="C57" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="D57" s="79" t="s">
         <v>379</v>
       </c>
-      <c r="B57" s="79" t="s">
-        <v>336</v>
-      </c>
-      <c r="C57" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="D57" s="79" t="s">
-        <v>380</v>
-      </c>
       <c r="E57" s="79" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F57" s="80" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G57" s="79" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A58" s="81" t="s">
+        <v>380</v>
+      </c>
+      <c r="B58" s="82" t="s">
         <v>381</v>
-      </c>
-      <c r="B58" s="82" t="s">
-        <v>382</v>
       </c>
       <c r="C58" s="83">
         <v>94</v>
@@ -13160,7 +13052,7 @@
         <v>40</v>
       </c>
       <c r="E58" s="82" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F58" s="83">
         <v>95</v>
@@ -13171,10 +13063,10 @@
     </row>
     <row r="59" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A59" s="81" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B59" s="84" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C59" s="85">
         <v>94</v>
@@ -13194,10 +13086,10 @@
     </row>
     <row r="60" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A60" s="81" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B60" s="87" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C60" s="88">
         <v>79</v>
@@ -13206,7 +13098,7 @@
         <v>70</v>
       </c>
       <c r="E60" s="87" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F60" s="88">
         <v>80</v>
@@ -13217,102 +13109,102 @@
     </row>
     <row r="61" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A61" s="90" t="s">
+        <v>225</v>
+      </c>
+      <c r="B61" s="84" t="s">
         <v>226</v>
-      </c>
-      <c r="B61" s="84" t="s">
-        <v>227</v>
       </c>
       <c r="C61" s="91">
         <v>99</v>
       </c>
       <c r="D61" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E61" s="84" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F61" s="84">
         <v>99</v>
       </c>
       <c r="G61" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A62" s="90" t="s">
+        <v>228</v>
+      </c>
+      <c r="B62" s="84" t="s">
         <v>229</v>
-      </c>
-      <c r="B62" s="84" t="s">
-        <v>230</v>
       </c>
       <c r="C62" s="93">
         <v>99</v>
       </c>
       <c r="D62" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E62" s="84" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F62" s="84">
         <v>99</v>
       </c>
       <c r="G62" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A63" s="94" t="s">
+        <v>230</v>
+      </c>
+      <c r="B63" s="87" t="s">
         <v>231</v>
-      </c>
-      <c r="B63" s="87" t="s">
-        <v>232</v>
       </c>
       <c r="C63" s="88">
         <v>90</v>
       </c>
       <c r="D63" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E63" s="84" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F63" s="84">
         <v>96</v>
       </c>
       <c r="G63" s="89" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A64" s="81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B64" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C64" s="87">
         <v>80</v>
       </c>
       <c r="D64" s="95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E64" s="84" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F64" s="84">
         <v>75</v>
       </c>
       <c r="G64" s="95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A65" s="97" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B65" s="98" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C65" s="98">
         <v>77</v>
@@ -13321,7 +13213,7 @@
         <v>70</v>
       </c>
       <c r="E65" s="98" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F65" s="98">
         <v>76</v>
@@ -13332,52 +13224,52 @@
     </row>
     <row r="68" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A68" s="96" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B68" s="103" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C68" s="104"/>
       <c r="D68" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E68" s="103" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F68" s="104"/>
       <c r="G68" s="76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="50" x14ac:dyDescent="0.3">
       <c r="A69" s="78" t="s">
+        <v>378</v>
+      </c>
+      <c r="B69" s="79" t="s">
+        <v>335</v>
+      </c>
+      <c r="C69" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="D69" s="79" t="s">
         <v>379</v>
       </c>
-      <c r="B69" s="79" t="s">
-        <v>336</v>
-      </c>
-      <c r="C69" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="D69" s="79" t="s">
-        <v>380</v>
-      </c>
       <c r="E69" s="79" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F69" s="80" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G69" s="79" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A70" s="81" t="s">
+        <v>380</v>
+      </c>
+      <c r="B70" s="82" t="s">
         <v>381</v>
-      </c>
-      <c r="B70" s="82" t="s">
-        <v>382</v>
       </c>
       <c r="C70" s="83">
         <v>94</v>
@@ -13386,7 +13278,7 @@
         <v>70</v>
       </c>
       <c r="E70" s="82" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F70" s="83">
         <v>95</v>
@@ -13397,10 +13289,10 @@
     </row>
     <row r="71" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A71" s="81" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B71" s="84" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C71" s="85">
         <v>94</v>
@@ -13420,10 +13312,10 @@
     </row>
     <row r="72" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A72" s="81" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B72" s="87" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C72" s="88">
         <v>79</v>
@@ -13432,7 +13324,7 @@
         <v>70</v>
       </c>
       <c r="E72" s="87" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F72" s="88">
         <v>80</v>
@@ -13443,79 +13335,79 @@
     </row>
     <row r="73" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A73" s="90" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B73" s="84" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C73" s="91">
         <v>99</v>
       </c>
       <c r="D73" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E73" s="84" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F73" s="84">
         <v>99</v>
       </c>
       <c r="G73" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A74" s="90" t="s">
+        <v>228</v>
+      </c>
+      <c r="B74" s="84" t="s">
         <v>229</v>
-      </c>
-      <c r="B74" s="84" t="s">
-        <v>230</v>
       </c>
       <c r="C74" s="93">
         <v>99</v>
       </c>
       <c r="D74" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E74" s="84" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F74" s="84">
         <v>99</v>
       </c>
       <c r="G74" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A75" s="94" t="s">
+        <v>230</v>
+      </c>
+      <c r="B75" s="87" t="s">
         <v>231</v>
-      </c>
-      <c r="B75" s="87" t="s">
-        <v>232</v>
       </c>
       <c r="C75" s="88">
         <v>90</v>
       </c>
       <c r="D75" s="92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E75" s="84" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F75" s="84">
         <v>96</v>
       </c>
       <c r="G75" s="89" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A76" s="81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B76" s="87" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C76" s="87">
         <v>97</v>
@@ -13524,7 +13416,7 @@
         <v>50</v>
       </c>
       <c r="E76" s="84" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F76" s="84">
         <v>97</v>
@@ -13535,10 +13427,10 @@
     </row>
     <row r="77" spans="1:7" ht="25" x14ac:dyDescent="0.3">
       <c r="A77" s="97" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B77" s="98" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C77" s="98">
         <v>75</v>
@@ -13547,7 +13439,7 @@
         <v>70</v>
       </c>
       <c r="E77" s="98" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F77" s="98">
         <v>76</v>
@@ -13588,360 +13480,360 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A1" s="50" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C2" s="40"/>
     </row>
     <row r="3" spans="1:3" ht="19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="57"/>
     </row>
     <row r="6" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C8" s="58" t="s">
         <v>430</v>
-      </c>
-      <c r="C8" s="58" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C9" s="57" t="s">
         <v>432</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="57"/>
     </row>
     <row r="12" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="57"/>
     </row>
     <row r="14" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
     <row r="16" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B19" s="46"/>
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
     </row>
     <row r="21" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="59"/>
     </row>
     <row r="22" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="54"/>
     </row>
     <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B23" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="C23" s="56" t="s">
         <v>440</v>
-      </c>
-      <c r="C23" s="56" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="56"/>
     </row>
     <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B25" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="C25" s="56" t="s">
         <v>442</v>
-      </c>
-      <c r="C25" s="56" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="C26" s="56" t="s">
         <v>444</v>
-      </c>
-      <c r="C26" s="56" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="56"/>
     </row>
     <row r="28" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="56"/>
     </row>
     <row r="29" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B29" s="10"/>
       <c r="C29" s="56"/>
     </row>
     <row r="30" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="56"/>
     </row>
     <row r="31" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="56"/>
     </row>
     <row r="32" spans="1:3" ht="19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="60"/>
     </row>
     <row r="33" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B33" s="47"/>
       <c r="C33" s="56"/>
     </row>
     <row r="34" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B34" s="47"/>
       <c r="C34" s="56"/>
     </row>
     <row r="35" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B35" s="47"/>
       <c r="C35" s="56"/>
     </row>
     <row r="36" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B36" s="47"/>
       <c r="C36" s="53"/>
     </row>
     <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="61"/>
     </row>
     <row r="38" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B38" s="48"/>
       <c r="C38" s="62"/>
     </row>
     <row r="39" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="62"/>
     </row>
     <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="C40" s="58" t="s">
         <v>449</v>
-      </c>
-      <c r="C40" s="58" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C41" s="58" t="s">
         <v>451</v>
-      </c>
-      <c r="C41" s="58" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
     </row>
     <row r="43" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B43" s="45"/>
       <c r="C43" s="15"/>
     </row>
     <row r="44" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
     <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -13963,115 +13855,115 @@
   <sheetData>
     <row r="1" spans="1:4" ht="81" x14ac:dyDescent="0.2">
       <c r="A1" s="71" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1" s="72" t="s">
         <v>455</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="C1" s="73" t="s">
         <v>456</v>
-      </c>
-      <c r="C1" s="73" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
+        <v>457</v>
+      </c>
+      <c r="B2" s="70" t="s">
         <v>458</v>
       </c>
-      <c r="B2" s="70" t="s">
+      <c r="C2" s="70" t="s">
         <v>459</v>
-      </c>
-      <c r="C2" s="70" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A3" s="69" t="s">
+        <v>460</v>
+      </c>
+      <c r="B3" s="70" t="s">
         <v>461</v>
       </c>
-      <c r="B3" s="70" t="s">
-        <v>462</v>
-      </c>
       <c r="C3" s="70" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A4" s="69" t="s">
+        <v>462</v>
+      </c>
+      <c r="B4" s="74" t="s">
         <v>463</v>
       </c>
-      <c r="B4" s="74" t="s">
-        <v>464</v>
-      </c>
       <c r="C4" s="74" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A5" s="69" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C5" s="74" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A6" s="69" t="s">
+        <v>465</v>
+      </c>
+      <c r="B6" s="70" t="s">
         <v>466</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="C6" s="70" t="s">
         <v>467</v>
-      </c>
-      <c r="C6" s="70" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A7" s="69" t="s">
+        <v>468</v>
+      </c>
+      <c r="B7" s="70" t="s">
         <v>469</v>
       </c>
-      <c r="B7" s="70" t="s">
+      <c r="C7" s="70" t="s">
         <v>470</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="D7" t="s">
         <v>471</v>
-      </c>
-      <c r="D7" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A8" s="69" t="s">
+        <v>472</v>
+      </c>
+      <c r="B8" s="70" t="s">
+        <v>330</v>
+      </c>
+      <c r="C8" s="70" t="s">
         <v>473</v>
       </c>
-      <c r="B8" s="70" t="s">
-        <v>331</v>
-      </c>
-      <c r="C8" s="70" t="s">
+      <c r="D8" t="s">
         <v>474</v>
-      </c>
-      <c r="D8" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A9" s="69" t="s">
+        <v>475</v>
+      </c>
+      <c r="B9" s="70" t="s">
         <v>476</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="C9" s="70" t="s">
         <v>477</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="D9" t="s">
         <v>478</v>
-      </c>
-      <c r="D9" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A10" s="69" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B10" s="70">
         <v>26000</v>
@@ -14082,7 +13974,7 @@
     </row>
     <row r="11" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A11" s="69" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B11" s="70">
         <v>445</v>
@@ -14093,7 +13985,7 @@
     </row>
     <row r="12" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A12" s="69" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B12" s="70">
         <v>96000</v>
@@ -14104,7 +13996,7 @@
     </row>
     <row r="13" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A13" s="69" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B13" s="70">
         <v>400000</v>
@@ -14115,7 +14007,7 @@
     </row>
     <row r="14" spans="1:4" ht="22" x14ac:dyDescent="0.25">
       <c r="A14" s="69" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B14" s="70">
         <v>200000</v>
@@ -14126,26 +14018,26 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B25" s="102" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C25" s="102" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="102" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B26" s="102" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C26" s="102" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B27">
         <v>1100</v>
@@ -14156,7 +14048,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B28">
         <v>1000</v>
@@ -14167,7 +14059,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B29">
         <v>4500</v>
@@ -14178,29 +14070,29 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B30" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C30" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B31" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C31" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B32">
         <v>650</v>
@@ -14211,7 +14103,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B33">
         <v>350</v>
@@ -14222,7 +14114,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B34">
         <v>300</v>
@@ -14233,7 +14125,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B35">
         <v>150</v>
@@ -14244,40 +14136,40 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>495</v>
+      </c>
+      <c r="B36" t="s">
         <v>496</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>497</v>
-      </c>
-      <c r="C36" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>498</v>
+      </c>
+      <c r="B37" t="s">
         <v>499</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>500</v>
-      </c>
-      <c r="C37" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>501</v>
+      </c>
+      <c r="B38" t="s">
         <v>502</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>503</v>
-      </c>
-      <c r="C38" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B39">
         <v>128</v>

--- a/public/data/SRX4XX_Datasheet.xlsx
+++ b/public/data/SRX4XX_Datasheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sshivang/Downloads/Panther Sanity/public/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1AC373-5448-B647-8BD2-D223756AE718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F603F43-5400-DF4B-995C-1514E23F7609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{982B047A-A65D-41BF-8595-49A5B2074CF1}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Second Set Data" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ISSUES-PR''s'!$A$1:$I$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ISSUES-PR''s'!$A$1:$I$224</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SRX440'!$A$1:$F$100</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="508">
   <si>
     <t>number</t>
   </si>
@@ -360,6 +360,9 @@
   </si>
   <si>
     <t>25.4X300-EVO: Panther: SRX4XX: IPSEC Performance - Only one core is utilized on the decryption side</t>
+  </si>
+  <si>
+    <t>26.4R1-EVO</t>
   </si>
   <si>
     <t>assigned</t>
@@ -3074,7 +3077,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{101F05EA-6A87-7646-9D66-36E81A856E36}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I220"/>
+  <dimension ref="A1:I224"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -7239,1862 +7242,1967 @@
         <v>51</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="100" t="str">
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-2", "1940446-2")</f>
+        <v>1940446-2</v>
+      </c>
+      <c r="B153" t="s">
+        <v>104</v>
+      </c>
+      <c r="C153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" t="s">
+        <v>47</v>
+      </c>
+      <c r="E153" t="s">
+        <v>12</v>
+      </c>
+      <c r="G153" t="s">
+        <v>105</v>
+      </c>
+      <c r="H153" t="s">
+        <v>106</v>
+      </c>
+      <c r="I153" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-3", "1940446-3")</f>
         <v>1940446-3</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B154" t="s">
         <v>104</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C154" t="s">
         <v>13</v>
       </c>
-      <c r="D153" t="s">
+      <c r="D154" t="s">
         <v>47</v>
       </c>
-      <c r="E153" t="s">
-        <v>12</v>
-      </c>
-      <c r="G153" t="s">
+      <c r="E154" t="s">
+        <v>12</v>
+      </c>
+      <c r="G154" t="s">
         <v>13</v>
       </c>
-      <c r="H153" t="s">
-        <v>14</v>
-      </c>
-      <c r="I153" t="s">
+      <c r="H154" t="s">
+        <v>14</v>
+      </c>
+      <c r="I154" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="100" t="str">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-4", "1940446-4")</f>
         <v>1940446-4</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B155" t="s">
         <v>104</v>
       </c>
-      <c r="C154" t="s">
-        <v>106</v>
-      </c>
-      <c r="D154" t="s">
+      <c r="C155" t="s">
+        <v>107</v>
+      </c>
+      <c r="D155" t="s">
         <v>47</v>
       </c>
-      <c r="E154" t="s">
-        <v>12</v>
-      </c>
-      <c r="G154" t="s">
-        <v>106</v>
-      </c>
-      <c r="H154" t="s">
-        <v>14</v>
-      </c>
-      <c r="I154" t="s">
+      <c r="E155" t="s">
+        <v>12</v>
+      </c>
+      <c r="G155" t="s">
+        <v>107</v>
+      </c>
+      <c r="H155" t="s">
+        <v>14</v>
+      </c>
+      <c r="I155" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="100" t="str">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-5", "1940446-5")</f>
         <v>1940446-5</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B156" t="s">
         <v>104</v>
       </c>
-      <c r="C155" t="s">
-        <v>107</v>
-      </c>
-      <c r="D155" t="s">
+      <c r="C156" t="s">
+        <v>108</v>
+      </c>
+      <c r="D156" t="s">
         <v>47</v>
       </c>
-      <c r="E155" t="s">
-        <v>12</v>
-      </c>
-      <c r="G155" t="s">
-        <v>107</v>
-      </c>
-      <c r="H155" t="s">
+      <c r="E156" t="s">
+        <v>12</v>
+      </c>
+      <c r="G156" t="s">
+        <v>108</v>
+      </c>
+      <c r="H156" t="s">
         <v>81</v>
       </c>
-      <c r="I155" t="s">
+      <c r="I156" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="100" t="str">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-6", "1940446-6")</f>
         <v>1940446-6</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B157" t="s">
         <v>104</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C157" t="s">
         <v>32</v>
       </c>
-      <c r="D156" t="s">
+      <c r="D157" t="s">
         <v>47</v>
       </c>
-      <c r="E156" t="s">
-        <v>12</v>
-      </c>
-      <c r="F156" t="s">
+      <c r="E157" t="s">
+        <v>12</v>
+      </c>
+      <c r="F157" t="s">
         <v>30</v>
       </c>
-      <c r="G156" t="s">
+      <c r="G157" t="s">
         <v>32</v>
       </c>
-      <c r="H156" t="s">
-        <v>14</v>
-      </c>
-      <c r="I156" t="s">
+      <c r="H157" t="s">
+        <v>14</v>
+      </c>
+      <c r="I157" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="100" t="str">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-7", "1940446-7")</f>
         <v>1940446-7</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B158" t="s">
         <v>104</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C158" t="s">
         <v>17</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D158" t="s">
         <v>47</v>
       </c>
-      <c r="E157" t="s">
-        <v>12</v>
-      </c>
-      <c r="G157" t="s">
+      <c r="E158" t="s">
+        <v>12</v>
+      </c>
+      <c r="G158" t="s">
         <v>16</v>
       </c>
-      <c r="H157" t="s">
+      <c r="H158" t="s">
         <v>81</v>
       </c>
-      <c r="I157" t="s">
+      <c r="I158" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="100" t="str">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-8", "1940446-8")</f>
         <v>1940446-8</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B159" t="s">
         <v>104</v>
       </c>
-      <c r="D158" t="s">
+      <c r="D159" t="s">
         <v>47</v>
       </c>
-      <c r="E158" t="s">
-        <v>12</v>
-      </c>
-      <c r="G158" t="s">
+      <c r="E159" t="s">
+        <v>12</v>
+      </c>
+      <c r="G159" t="s">
         <v>43</v>
       </c>
-      <c r="H158" t="s">
+      <c r="H159" t="s">
         <v>81</v>
       </c>
-      <c r="I158" t="s">
+      <c r="I159" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="100" t="str">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A160" s="100" t="str">
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-9", "1940446-9")</f>
+        <v>1940446-9</v>
+      </c>
+      <c r="B160" t="s">
+        <v>104</v>
+      </c>
+      <c r="C160" t="s">
+        <v>38</v>
+      </c>
+      <c r="D160" t="s">
+        <v>47</v>
+      </c>
+      <c r="E160" t="s">
+        <v>12</v>
+      </c>
+      <c r="G160" t="s">
+        <v>38</v>
+      </c>
+      <c r="H160" t="s">
+        <v>106</v>
+      </c>
+      <c r="I160" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A161" s="100" t="str">
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1940446-10", "1940446-10")</f>
+        <v>1940446-10</v>
+      </c>
+      <c r="B161" t="s">
+        <v>104</v>
+      </c>
+      <c r="D161" t="s">
+        <v>47</v>
+      </c>
+      <c r="E161" t="s">
+        <v>12</v>
+      </c>
+      <c r="G161" t="s">
+        <v>76</v>
+      </c>
+      <c r="H161" t="s">
+        <v>106</v>
+      </c>
+      <c r="I161" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-1", "1942363-1")</f>
         <v>1942363-1</v>
       </c>
-      <c r="B159" t="s">
-        <v>108</v>
-      </c>
-      <c r="C159" t="s">
+      <c r="B162" t="s">
+        <v>109</v>
+      </c>
+      <c r="C162" t="s">
         <v>17</v>
       </c>
-      <c r="D159" t="s">
+      <c r="D162" t="s">
         <v>47</v>
       </c>
-      <c r="E159" t="s">
-        <v>12</v>
-      </c>
-      <c r="G159" t="s">
+      <c r="E162" t="s">
+        <v>12</v>
+      </c>
+      <c r="G162" t="s">
         <v>17</v>
       </c>
-      <c r="H159" t="s">
-        <v>14</v>
-      </c>
-      <c r="I159" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="100" t="str">
+      <c r="H162" t="s">
+        <v>14</v>
+      </c>
+      <c r="I162" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-2", "1942363-2")</f>
         <v>1942363-2</v>
       </c>
-      <c r="B160" t="s">
-        <v>108</v>
-      </c>
-      <c r="C160" t="s">
+      <c r="B163" t="s">
+        <v>109</v>
+      </c>
+      <c r="C163" t="s">
         <v>17</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D163" t="s">
         <v>47</v>
       </c>
-      <c r="E160" t="s">
-        <v>12</v>
-      </c>
-      <c r="G160" t="s">
+      <c r="E163" t="s">
+        <v>12</v>
+      </c>
+      <c r="G163" t="s">
         <v>13</v>
       </c>
-      <c r="H160" t="s">
-        <v>14</v>
-      </c>
-      <c r="I160" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="100" t="str">
+      <c r="H163" t="s">
+        <v>14</v>
+      </c>
+      <c r="I163" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-3", "1942363-3")</f>
         <v>1942363-3</v>
       </c>
-      <c r="B161" t="s">
-        <v>108</v>
-      </c>
-      <c r="C161" t="s">
+      <c r="B164" t="s">
+        <v>109</v>
+      </c>
+      <c r="C164" t="s">
         <v>17</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D164" t="s">
         <v>47</v>
       </c>
-      <c r="E161" t="s">
-        <v>12</v>
-      </c>
-      <c r="G161" t="s">
+      <c r="E164" t="s">
+        <v>12</v>
+      </c>
+      <c r="G164" t="s">
         <v>76</v>
       </c>
-      <c r="H161" t="s">
-        <v>14</v>
-      </c>
-      <c r="I161" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="100" t="str">
+      <c r="H164" t="s">
+        <v>14</v>
+      </c>
+      <c r="I164" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942363-4", "1942363-4")</f>
         <v>1942363-4</v>
       </c>
-      <c r="B162" t="s">
-        <v>108</v>
-      </c>
-      <c r="C162" t="s">
+      <c r="B165" t="s">
+        <v>109</v>
+      </c>
+      <c r="C165" t="s">
         <v>32</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D165" t="s">
         <v>47</v>
       </c>
-      <c r="E162" t="s">
-        <v>12</v>
-      </c>
-      <c r="G162" t="s">
+      <c r="E165" t="s">
+        <v>12</v>
+      </c>
+      <c r="G165" t="s">
         <v>32</v>
       </c>
-      <c r="H162" t="s">
-        <v>14</v>
-      </c>
-      <c r="I162" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="100" t="str">
+      <c r="H165" t="s">
+        <v>14</v>
+      </c>
+      <c r="I165" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942376-1", "1942376-1")</f>
         <v>1942376-1</v>
       </c>
-      <c r="B163" t="s">
-        <v>110</v>
-      </c>
-      <c r="C163" t="s">
+      <c r="B166" t="s">
+        <v>111</v>
+      </c>
+      <c r="C166" t="s">
         <v>17</v>
       </c>
-      <c r="D163" t="s">
+      <c r="D166" t="s">
         <v>47</v>
       </c>
-      <c r="E163" t="s">
-        <v>12</v>
-      </c>
-      <c r="G163" t="s">
+      <c r="E166" t="s">
+        <v>12</v>
+      </c>
+      <c r="G166" t="s">
         <v>17</v>
       </c>
-      <c r="H163" t="s">
+      <c r="H166" t="s">
         <v>81</v>
       </c>
-      <c r="I163" t="s">
+      <c r="I166" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="100" t="str">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1942376-2", "1942376-2")</f>
         <v>1942376-2</v>
       </c>
-      <c r="B164" t="s">
-        <v>110</v>
-      </c>
-      <c r="C164" t="s">
+      <c r="B167" t="s">
+        <v>111</v>
+      </c>
+      <c r="C167" t="s">
         <v>17</v>
       </c>
-      <c r="D164" t="s">
+      <c r="D167" t="s">
         <v>47</v>
       </c>
-      <c r="E164" t="s">
-        <v>12</v>
-      </c>
-      <c r="G164" t="s">
+      <c r="E167" t="s">
+        <v>12</v>
+      </c>
+      <c r="G167" t="s">
         <v>13</v>
       </c>
-      <c r="H164" t="s">
+      <c r="H167" t="s">
         <v>81</v>
       </c>
-      <c r="I164" t="s">
+      <c r="I167" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="100" t="str">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-1", "1943082-1")</f>
         <v>1943082-1</v>
       </c>
-      <c r="B165" t="s">
-        <v>111</v>
-      </c>
-      <c r="C165" t="s">
+      <c r="B168" t="s">
+        <v>112</v>
+      </c>
+      <c r="C168" t="s">
         <v>17</v>
       </c>
-      <c r="D165" t="s">
+      <c r="D168" t="s">
         <v>11</v>
       </c>
-      <c r="E165" t="s">
-        <v>12</v>
-      </c>
-      <c r="G165" t="s">
+      <c r="E168" t="s">
+        <v>12</v>
+      </c>
+      <c r="G168" t="s">
         <v>17</v>
       </c>
-      <c r="H165" t="s">
-        <v>14</v>
-      </c>
-      <c r="I165" t="s">
+      <c r="H168" t="s">
+        <v>14</v>
+      </c>
+      <c r="I168" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="100" t="str">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-2", "1943082-2")</f>
         <v>1943082-2</v>
       </c>
-      <c r="B166" t="s">
-        <v>111</v>
-      </c>
-      <c r="C166" t="s">
+      <c r="B169" t="s">
+        <v>112</v>
+      </c>
+      <c r="C169" t="s">
         <v>17</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D169" t="s">
         <v>11</v>
       </c>
-      <c r="E166" t="s">
-        <v>12</v>
-      </c>
-      <c r="G166" t="s">
+      <c r="E169" t="s">
+        <v>12</v>
+      </c>
+      <c r="G169" t="s">
         <v>13</v>
       </c>
-      <c r="H166" t="s">
-        <v>14</v>
-      </c>
-      <c r="I166" t="s">
+      <c r="H169" t="s">
+        <v>14</v>
+      </c>
+      <c r="I169" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="100" t="str">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-3", "1943082-3")</f>
         <v>1943082-3</v>
       </c>
-      <c r="B167" t="s">
-        <v>111</v>
-      </c>
-      <c r="C167" t="s">
+      <c r="B170" t="s">
+        <v>112</v>
+      </c>
+      <c r="C170" t="s">
         <v>42</v>
       </c>
-      <c r="D167" t="s">
+      <c r="D170" t="s">
         <v>11</v>
       </c>
-      <c r="E167" t="s">
-        <v>12</v>
-      </c>
-      <c r="G167" t="s">
+      <c r="E170" t="s">
+        <v>12</v>
+      </c>
+      <c r="G170" t="s">
         <v>42</v>
       </c>
-      <c r="H167" t="s">
-        <v>14</v>
-      </c>
-      <c r="I167" t="s">
+      <c r="H170" t="s">
+        <v>14</v>
+      </c>
+      <c r="I170" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="100" t="str">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943082-4", "1943082-4")</f>
         <v>1943082-4</v>
       </c>
-      <c r="B168" t="s">
-        <v>111</v>
-      </c>
-      <c r="C168" t="s">
+      <c r="B171" t="s">
+        <v>112</v>
+      </c>
+      <c r="C171" t="s">
         <v>42</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D171" t="s">
         <v>11</v>
       </c>
-      <c r="E168" t="s">
-        <v>12</v>
-      </c>
-      <c r="G168" t="s">
+      <c r="E171" t="s">
+        <v>12</v>
+      </c>
+      <c r="G171" t="s">
         <v>32</v>
       </c>
-      <c r="H168" t="s">
-        <v>14</v>
-      </c>
-      <c r="I168" t="s">
+      <c r="H171" t="s">
+        <v>14</v>
+      </c>
+      <c r="I171" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="100" t="str">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-1", "1943084-1")</f>
         <v>1943084-1</v>
       </c>
-      <c r="B169" t="s">
-        <v>112</v>
-      </c>
-      <c r="C169" t="s">
+      <c r="B172" t="s">
+        <v>113</v>
+      </c>
+      <c r="C172" t="s">
         <v>13</v>
       </c>
-      <c r="D169" t="s">
+      <c r="D172" t="s">
         <v>11</v>
       </c>
-      <c r="E169" t="s">
-        <v>12</v>
-      </c>
-      <c r="G169" t="s">
+      <c r="E172" t="s">
+        <v>12</v>
+      </c>
+      <c r="G172" t="s">
         <v>13</v>
       </c>
-      <c r="H169" t="s">
-        <v>14</v>
-      </c>
-      <c r="I169" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="100" t="str">
+      <c r="H172" t="s">
+        <v>14</v>
+      </c>
+      <c r="I172" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-2", "1943084-2")</f>
         <v>1943084-2</v>
       </c>
-      <c r="B170" t="s">
-        <v>112</v>
-      </c>
-      <c r="C170" t="s">
+      <c r="B173" t="s">
+        <v>113</v>
+      </c>
+      <c r="C173" t="s">
         <v>13</v>
       </c>
-      <c r="D170" t="s">
+      <c r="D173" t="s">
         <v>11</v>
       </c>
-      <c r="E170" t="s">
-        <v>12</v>
-      </c>
-      <c r="G170" t="s">
+      <c r="E173" t="s">
+        <v>12</v>
+      </c>
+      <c r="G173" t="s">
         <v>17</v>
       </c>
-      <c r="H170" t="s">
-        <v>14</v>
-      </c>
-      <c r="I170" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="100" t="str">
+      <c r="H173" t="s">
+        <v>14</v>
+      </c>
+      <c r="I173" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-3", "1943084-3")</f>
         <v>1943084-3</v>
       </c>
-      <c r="B171" t="s">
-        <v>112</v>
-      </c>
-      <c r="D171" t="s">
+      <c r="B174" t="s">
+        <v>113</v>
+      </c>
+      <c r="D174" t="s">
         <v>11</v>
       </c>
-      <c r="E171" t="s">
-        <v>12</v>
-      </c>
-      <c r="G171" t="s">
+      <c r="E174" t="s">
+        <v>12</v>
+      </c>
+      <c r="G174" t="s">
         <v>16</v>
       </c>
-      <c r="H171" t="s">
-        <v>14</v>
-      </c>
-      <c r="I171" t="s">
+      <c r="H174" t="s">
+        <v>14</v>
+      </c>
+      <c r="I174" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="100" t="str">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943084-4", "1943084-4")</f>
         <v>1943084-4</v>
       </c>
-      <c r="B172" t="s">
-        <v>112</v>
-      </c>
-      <c r="C172" t="s">
+      <c r="B175" t="s">
+        <v>113</v>
+      </c>
+      <c r="C175" t="s">
         <v>10</v>
       </c>
-      <c r="D172" t="s">
+      <c r="D175" t="s">
         <v>11</v>
       </c>
-      <c r="E172" t="s">
-        <v>12</v>
-      </c>
-      <c r="G172" t="s">
+      <c r="E175" t="s">
+        <v>12</v>
+      </c>
+      <c r="G175" t="s">
         <v>76</v>
       </c>
-      <c r="H172" t="s">
+      <c r="H175" t="s">
         <v>81</v>
       </c>
-      <c r="I172" t="s">
+      <c r="I175" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="100" t="str">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943461-1", "1943461-1")</f>
         <v>1943461-1</v>
       </c>
-      <c r="B173" t="s">
-        <v>114</v>
-      </c>
-      <c r="C173" t="s">
+      <c r="B176" t="s">
+        <v>115</v>
+      </c>
+      <c r="C176" t="s">
         <v>17</v>
       </c>
-      <c r="D173" t="s">
+      <c r="D176" t="s">
         <v>11</v>
       </c>
-      <c r="E173" t="s">
-        <v>12</v>
-      </c>
-      <c r="G173" t="s">
+      <c r="E176" t="s">
+        <v>12</v>
+      </c>
+      <c r="G176" t="s">
         <v>17</v>
       </c>
-      <c r="H173" t="s">
-        <v>14</v>
-      </c>
-      <c r="I173" t="s">
+      <c r="H176" t="s">
+        <v>14</v>
+      </c>
+      <c r="I176" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="100" t="str">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943461-2", "1943461-2")</f>
         <v>1943461-2</v>
       </c>
-      <c r="B174" t="s">
-        <v>114</v>
-      </c>
-      <c r="C174" t="s">
+      <c r="B177" t="s">
+        <v>115</v>
+      </c>
+      <c r="C177" t="s">
         <v>17</v>
       </c>
-      <c r="D174" t="s">
+      <c r="D177" t="s">
         <v>11</v>
       </c>
-      <c r="E174" t="s">
-        <v>12</v>
-      </c>
-      <c r="G174" t="s">
+      <c r="E177" t="s">
+        <v>12</v>
+      </c>
+      <c r="G177" t="s">
         <v>13</v>
       </c>
-      <c r="H174" t="s">
-        <v>14</v>
-      </c>
-      <c r="I174" t="s">
+      <c r="H177" t="s">
+        <v>14</v>
+      </c>
+      <c r="I177" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="100" t="str">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-1", "1943467-1")</f>
         <v>1943467-1</v>
       </c>
-      <c r="B175" t="s">
-        <v>115</v>
-      </c>
-      <c r="C175" t="s">
+      <c r="B178" t="s">
+        <v>116</v>
+      </c>
+      <c r="C178" t="s">
         <v>17</v>
       </c>
-      <c r="D175" t="s">
+      <c r="D178" t="s">
         <v>11</v>
       </c>
-      <c r="E175" t="s">
-        <v>12</v>
-      </c>
-      <c r="G175" t="s">
+      <c r="E178" t="s">
+        <v>12</v>
+      </c>
+      <c r="G178" t="s">
         <v>17</v>
       </c>
-      <c r="H175" t="s">
-        <v>14</v>
-      </c>
-      <c r="I175" t="s">
+      <c r="H178" t="s">
+        <v>14</v>
+      </c>
+      <c r="I178" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="100" t="str">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-2", "1943467-2")</f>
         <v>1943467-2</v>
       </c>
-      <c r="B176" t="s">
-        <v>115</v>
-      </c>
-      <c r="C176" t="s">
+      <c r="B179" t="s">
+        <v>116</v>
+      </c>
+      <c r="C179" t="s">
         <v>17</v>
       </c>
-      <c r="D176" t="s">
+      <c r="D179" t="s">
         <v>11</v>
       </c>
-      <c r="E176" t="s">
-        <v>12</v>
-      </c>
-      <c r="G176" t="s">
+      <c r="E179" t="s">
+        <v>12</v>
+      </c>
+      <c r="G179" t="s">
         <v>13</v>
       </c>
-      <c r="H176" t="s">
-        <v>14</v>
-      </c>
-      <c r="I176" t="s">
+      <c r="H179" t="s">
+        <v>14</v>
+      </c>
+      <c r="I179" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="100" t="str">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-3", "1943467-3")</f>
         <v>1943467-3</v>
       </c>
-      <c r="B177" t="s">
-        <v>115</v>
-      </c>
-      <c r="C177" t="s">
+      <c r="B180" t="s">
+        <v>116</v>
+      </c>
+      <c r="C180" t="s">
         <v>17</v>
       </c>
-      <c r="D177" t="s">
+      <c r="D180" t="s">
         <v>11</v>
       </c>
-      <c r="E177" t="s">
-        <v>12</v>
-      </c>
-      <c r="G177" t="s">
+      <c r="E180" t="s">
+        <v>12</v>
+      </c>
+      <c r="G180" t="s">
         <v>38</v>
       </c>
-      <c r="H177" t="s">
-        <v>14</v>
-      </c>
-      <c r="I177" t="s">
+      <c r="H180" t="s">
+        <v>14</v>
+      </c>
+      <c r="I180" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="100" t="str">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-4", "1943467-4")</f>
         <v>1943467-4</v>
       </c>
-      <c r="B178" t="s">
-        <v>115</v>
-      </c>
-      <c r="C178" t="s">
+      <c r="B181" t="s">
+        <v>116</v>
+      </c>
+      <c r="C181" t="s">
         <v>42</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D181" t="s">
         <v>11</v>
       </c>
-      <c r="E178" t="s">
-        <v>12</v>
-      </c>
-      <c r="G178" t="s">
+      <c r="E181" t="s">
+        <v>12</v>
+      </c>
+      <c r="G181" t="s">
         <v>42</v>
       </c>
-      <c r="H178" t="s">
-        <v>14</v>
-      </c>
-      <c r="I178" t="s">
+      <c r="H181" t="s">
+        <v>14</v>
+      </c>
+      <c r="I181" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="100" t="str">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943467-5", "1943467-5")</f>
         <v>1943467-5</v>
       </c>
-      <c r="B179" t="s">
-        <v>115</v>
-      </c>
-      <c r="C179" t="s">
+      <c r="B182" t="s">
+        <v>116</v>
+      </c>
+      <c r="C182" t="s">
         <v>32</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D182" t="s">
         <v>11</v>
       </c>
-      <c r="E179" t="s">
-        <v>12</v>
-      </c>
-      <c r="F179" t="s">
+      <c r="E182" t="s">
+        <v>12</v>
+      </c>
+      <c r="F182" t="s">
         <v>22</v>
       </c>
-      <c r="G179" t="s">
+      <c r="G182" t="s">
         <v>32</v>
       </c>
-      <c r="H179" t="s">
-        <v>14</v>
-      </c>
-      <c r="I179" t="s">
+      <c r="H182" t="s">
+        <v>14</v>
+      </c>
+      <c r="I182" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="100" t="str">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-1", "1943607-1")</f>
         <v>1943607-1</v>
       </c>
-      <c r="B180" t="s">
-        <v>116</v>
-      </c>
-      <c r="C180" t="s">
+      <c r="B183" t="s">
+        <v>117</v>
+      </c>
+      <c r="C183" t="s">
         <v>17</v>
       </c>
-      <c r="D180" t="s">
-        <v>117</v>
-      </c>
-      <c r="E180" t="s">
-        <v>12</v>
-      </c>
-      <c r="F180" t="s">
+      <c r="D183" t="s">
+        <v>118</v>
+      </c>
+      <c r="E183" t="s">
+        <v>12</v>
+      </c>
+      <c r="F183" t="s">
         <v>22</v>
       </c>
-      <c r="G180" t="s">
+      <c r="G183" t="s">
         <v>17</v>
       </c>
-      <c r="H180" t="s">
-        <v>14</v>
-      </c>
-      <c r="I180" t="s">
+      <c r="H183" t="s">
+        <v>14</v>
+      </c>
+      <c r="I183" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="100" t="str">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-2", "1943607-2")</f>
         <v>1943607-2</v>
       </c>
-      <c r="B181" t="s">
-        <v>116</v>
-      </c>
-      <c r="C181" t="s">
+      <c r="B184" t="s">
+        <v>117</v>
+      </c>
+      <c r="C184" t="s">
         <v>17</v>
       </c>
-      <c r="D181" t="s">
-        <v>117</v>
-      </c>
-      <c r="E181" t="s">
-        <v>12</v>
-      </c>
-      <c r="F181" t="s">
+      <c r="D184" t="s">
+        <v>118</v>
+      </c>
+      <c r="E184" t="s">
+        <v>12</v>
+      </c>
+      <c r="F184" t="s">
         <v>22</v>
       </c>
-      <c r="G181" t="s">
+      <c r="G184" t="s">
         <v>13</v>
       </c>
-      <c r="H181" t="s">
-        <v>14</v>
-      </c>
-      <c r="I181" t="s">
+      <c r="H184" t="s">
+        <v>14</v>
+      </c>
+      <c r="I184" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="100" t="str">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1943607-3", "1943607-3")</f>
         <v>1943607-3</v>
       </c>
-      <c r="B182" t="s">
-        <v>116</v>
-      </c>
-      <c r="D182" t="s">
+      <c r="B185" t="s">
         <v>117</v>
       </c>
-      <c r="E182" t="s">
-        <v>12</v>
-      </c>
-      <c r="G182" t="s">
+      <c r="D185" t="s">
+        <v>118</v>
+      </c>
+      <c r="E185" t="s">
+        <v>12</v>
+      </c>
+      <c r="G185" t="s">
         <v>38</v>
       </c>
-      <c r="H182" t="s">
-        <v>14</v>
-      </c>
-      <c r="I182" t="s">
+      <c r="H185" t="s">
+        <v>14</v>
+      </c>
+      <c r="I185" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="100" t="str">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A186" s="100" t="str">
+        <f>HYPERLINK("https://gnats.juniper.net/web/default/1946082-1", "1946082-1")</f>
+        <v>1946082-1</v>
+      </c>
+      <c r="B186" t="s">
+        <v>119</v>
+      </c>
+      <c r="C186" t="s">
+        <v>17</v>
+      </c>
+      <c r="D186" t="s">
+        <v>120</v>
+      </c>
+      <c r="E186" t="s">
+        <v>12</v>
+      </c>
+      <c r="G186" t="s">
+        <v>17</v>
+      </c>
+      <c r="H186" t="s">
+        <v>106</v>
+      </c>
+      <c r="I186" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946082-2", "1946082-2")</f>
         <v>1946082-2</v>
       </c>
-      <c r="B183" t="s">
-        <v>118</v>
-      </c>
-      <c r="C183" t="s">
+      <c r="B187" t="s">
+        <v>119</v>
+      </c>
+      <c r="C187" t="s">
         <v>17</v>
       </c>
-      <c r="D183" t="s">
-        <v>119</v>
-      </c>
-      <c r="E183" t="s">
-        <v>12</v>
-      </c>
-      <c r="G183" t="s">
+      <c r="D187" t="s">
+        <v>120</v>
+      </c>
+      <c r="E187" t="s">
+        <v>12</v>
+      </c>
+      <c r="G187" t="s">
         <v>13</v>
       </c>
-      <c r="H183" t="s">
-        <v>14</v>
-      </c>
-      <c r="I183" t="s">
+      <c r="H187" t="s">
+        <v>14</v>
+      </c>
+      <c r="I187" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="100" t="str">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-1", "1946085-1")</f>
         <v>1946085-1</v>
       </c>
-      <c r="B184" t="s">
-        <v>120</v>
-      </c>
-      <c r="C184" t="s">
+      <c r="B188" t="s">
+        <v>121</v>
+      </c>
+      <c r="C188" t="s">
         <v>32</v>
       </c>
-      <c r="D184" t="s">
-        <v>121</v>
-      </c>
-      <c r="E184" t="s">
-        <v>12</v>
-      </c>
-      <c r="F184" t="s">
+      <c r="D188" t="s">
+        <v>122</v>
+      </c>
+      <c r="E188" t="s">
+        <v>12</v>
+      </c>
+      <c r="F188" t="s">
         <v>22</v>
       </c>
-      <c r="G184" t="s">
+      <c r="G188" t="s">
         <v>32</v>
       </c>
-      <c r="H184" t="s">
+      <c r="H188" t="s">
         <v>81</v>
       </c>
-      <c r="I184" t="s">
+      <c r="I188" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="100" t="str">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-2", "1946085-2")</f>
         <v>1946085-2</v>
       </c>
-      <c r="B185" t="s">
-        <v>120</v>
-      </c>
-      <c r="C185" t="s">
+      <c r="B189" t="s">
+        <v>121</v>
+      </c>
+      <c r="C189" t="s">
         <v>13</v>
       </c>
-      <c r="D185" t="s">
-        <v>121</v>
-      </c>
-      <c r="E185" t="s">
-        <v>12</v>
-      </c>
-      <c r="G185" t="s">
+      <c r="D189" t="s">
+        <v>122</v>
+      </c>
+      <c r="E189" t="s">
+        <v>12</v>
+      </c>
+      <c r="G189" t="s">
         <v>13</v>
       </c>
-      <c r="H185" t="s">
-        <v>14</v>
-      </c>
-      <c r="I185" t="s">
+      <c r="H189" t="s">
+        <v>14</v>
+      </c>
+      <c r="I189" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="100" t="str">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1946085-3", "1946085-3")</f>
         <v>1946085-3</v>
       </c>
-      <c r="B186" t="s">
-        <v>120</v>
-      </c>
-      <c r="C186" t="s">
+      <c r="B190" t="s">
+        <v>121</v>
+      </c>
+      <c r="C190" t="s">
         <v>32</v>
       </c>
-      <c r="D186" t="s">
-        <v>121</v>
-      </c>
-      <c r="E186" t="s">
-        <v>12</v>
-      </c>
-      <c r="G186" t="s">
+      <c r="D190" t="s">
+        <v>122</v>
+      </c>
+      <c r="E190" t="s">
+        <v>12</v>
+      </c>
+      <c r="G190" t="s">
         <v>42</v>
       </c>
-      <c r="H186" t="s">
+      <c r="H190" t="s">
         <v>81</v>
       </c>
-      <c r="I186" t="s">
+      <c r="I190" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="100" t="str">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947270-1", "1947270-1")</f>
         <v>1947270-1</v>
       </c>
-      <c r="B187" t="s">
-        <v>122</v>
-      </c>
-      <c r="C187" t="s">
+      <c r="B191" t="s">
+        <v>123</v>
+      </c>
+      <c r="C191" t="s">
         <v>17</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D191" t="s">
         <v>11</v>
       </c>
-      <c r="E187" t="s">
-        <v>12</v>
-      </c>
-      <c r="G187" t="s">
+      <c r="E191" t="s">
+        <v>12</v>
+      </c>
+      <c r="G191" t="s">
         <v>17</v>
       </c>
-      <c r="H187" t="s">
-        <v>14</v>
-      </c>
-      <c r="I187" t="s">
+      <c r="H191" t="s">
+        <v>14</v>
+      </c>
+      <c r="I191" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="100" t="str">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947270-2", "1947270-2")</f>
         <v>1947270-2</v>
       </c>
-      <c r="B188" t="s">
-        <v>122</v>
-      </c>
-      <c r="C188" t="s">
+      <c r="B192" t="s">
+        <v>123</v>
+      </c>
+      <c r="C192" t="s">
         <v>17</v>
       </c>
-      <c r="D188" t="s">
+      <c r="D192" t="s">
         <v>11</v>
       </c>
-      <c r="E188" t="s">
-        <v>12</v>
-      </c>
-      <c r="G188" t="s">
+      <c r="E192" t="s">
+        <v>12</v>
+      </c>
+      <c r="G192" t="s">
         <v>13</v>
       </c>
-      <c r="H188" t="s">
-        <v>14</v>
-      </c>
-      <c r="I188" t="s">
+      <c r="H192" t="s">
+        <v>14</v>
+      </c>
+      <c r="I192" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="100" t="str">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947337-1", "1947337-1")</f>
         <v>1947337-1</v>
       </c>
-      <c r="B189" t="s">
-        <v>123</v>
-      </c>
-      <c r="C189" t="s">
+      <c r="B193" t="s">
+        <v>124</v>
+      </c>
+      <c r="C193" t="s">
         <v>17</v>
       </c>
-      <c r="D189" t="s">
+      <c r="D193" t="s">
         <v>11</v>
       </c>
-      <c r="E189" t="s">
-        <v>12</v>
-      </c>
-      <c r="G189" t="s">
+      <c r="E193" t="s">
+        <v>12</v>
+      </c>
+      <c r="G193" t="s">
         <v>17</v>
       </c>
-      <c r="H189" t="s">
-        <v>14</v>
-      </c>
-      <c r="I189" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="100" t="str">
+      <c r="H193" t="s">
+        <v>14</v>
+      </c>
+      <c r="I193" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947337-2", "1947337-2")</f>
         <v>1947337-2</v>
       </c>
-      <c r="B190" t="s">
-        <v>123</v>
-      </c>
-      <c r="C190" t="s">
+      <c r="B194" t="s">
+        <v>124</v>
+      </c>
+      <c r="C194" t="s">
         <v>17</v>
       </c>
-      <c r="D190" t="s">
+      <c r="D194" t="s">
         <v>11</v>
       </c>
-      <c r="E190" t="s">
-        <v>12</v>
-      </c>
-      <c r="G190" t="s">
+      <c r="E194" t="s">
+        <v>12</v>
+      </c>
+      <c r="G194" t="s">
         <v>13</v>
       </c>
-      <c r="H190" t="s">
-        <v>14</v>
-      </c>
-      <c r="I190" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="100" t="str">
+      <c r="H194" t="s">
+        <v>14</v>
+      </c>
+      <c r="I194" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947954-1", "1947954-1")</f>
         <v>1947954-1</v>
       </c>
-      <c r="B191" t="s">
-        <v>125</v>
-      </c>
-      <c r="C191" t="s">
+      <c r="B195" t="s">
+        <v>126</v>
+      </c>
+      <c r="C195" t="s">
         <v>17</v>
       </c>
-      <c r="D191" t="s">
+      <c r="D195" t="s">
         <v>11</v>
       </c>
-      <c r="E191" t="s">
-        <v>12</v>
-      </c>
-      <c r="G191" t="s">
+      <c r="E195" t="s">
+        <v>12</v>
+      </c>
+      <c r="G195" t="s">
         <v>17</v>
       </c>
-      <c r="H191" t="s">
-        <v>14</v>
-      </c>
-      <c r="I191" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="100" t="str">
+      <c r="H195" t="s">
+        <v>14</v>
+      </c>
+      <c r="I195" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="100" t="str">
         <f>HYPERLINK("https://gnats.juniper.net/web/default/1947954-2", "1947954-2")</f>
         <v>1947954-2</v>
       </c>
-      <c r="B192" t="s">
-        <v>125</v>
-      </c>
-      <c r="C192" t="s">
+      <c r="B196" t="s">
+        <v>126</v>
+      </c>
+      <c r="C196" t="s">
         <v>17</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D196" t="s">
         <v>11</v>
       </c>
-      <c r="E192" t="s">
-        <v>12</v>
-      </c>
-      <c r="G192" t="s">
+      <c r="E196" t="s">
+        <v>12</v>
+      </c>
+      <c r="G196" t="s">
         <v>13</v>
       </c>
-      <c r="H192" t="s">
-        <v>14</v>
-      </c>
-      <c r="I192" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="100" t="str">
+      <c r="H196" t="s">
+        <v>14</v>
+      </c>
+      <c r="I196" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="1